--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="171">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -23,22 +23,25 @@
     <t>heap_4.o</t>
   </si>
   <si>
+    <t>drv_usart.o</t>
+  </si>
+  <si>
     <t>motor_loop.o</t>
   </si>
   <si>
     <t>dev_commun_uart.o</t>
   </si>
   <si>
+    <t>packer_parser.o</t>
+  </si>
+  <si>
     <t>startup_stm32g474xx.o</t>
   </si>
   <si>
-    <t>packer_parser.o</t>
-  </si>
-  <si>
     <t>runtime_param.o</t>
   </si>
   <si>
-    <t>pid_profile.o</t>
+    <t>motor_pid_profile.o</t>
   </si>
   <si>
     <t>usart.o</t>
@@ -47,6 +50,9 @@
     <t>tasks.o</t>
   </si>
   <si>
+    <t>dev_power_monitor.o</t>
+  </si>
+  <si>
     <t>tim.o</t>
   </si>
   <si>
@@ -56,7 +62,7 @@
     <t>spi.o</t>
   </si>
   <si>
-    <t>dev_power_monitor.o</t>
+    <t>calib_level2_motor.o</t>
   </si>
   <si>
     <t>dev_dwt_counter.o</t>
@@ -71,129 +77,195 @@
     <t>i2c.o</t>
   </si>
   <si>
-    <t>drv_usart.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_timebase_tim.o</t>
   </si>
   <si>
+    <t>dev_led.o</t>
+  </si>
+  <si>
+    <t>calib_mgr.o</t>
+  </si>
+  <si>
+    <t>calib_level5_nonlinear.o</t>
+  </si>
+  <si>
+    <t>dev_encoder_mt6835.o</t>
+  </si>
+  <si>
+    <t>calib_level7_auto.o</t>
+  </si>
+  <si>
     <t>cordic.o</t>
   </si>
   <si>
+    <t>calib_level3_encoder.o</t>
+  </si>
+  <si>
     <t>dev_motor.o</t>
   </si>
   <si>
     <t>thread_management.o</t>
   </si>
   <si>
+    <t>jm_host_commun.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal.o</t>
+  </si>
+  <si>
+    <t>port.o</t>
+  </si>
+  <si>
+    <t>calib_level6_system.o</t>
+  </si>
+  <si>
+    <t>calib_level1_driver.o</t>
+  </si>
+  <si>
     <t>mc_w.l</t>
   </si>
   <si>
-    <t>stm32g4xx_hal.o</t>
-  </si>
-  <si>
-    <t>port.o</t>
-  </si>
-  <si>
-    <t>mvars.o</t>
+    <t>calib_level4_torque.o</t>
+  </si>
+  <si>
+    <t>jm_proto_ops.o</t>
+  </si>
+  <si>
+    <t>stdout.o</t>
+  </si>
+  <si>
+    <t>errno.o</t>
+  </si>
+  <si>
+    <t>system_stm32g4xx.o</t>
+  </si>
+  <si>
+    <t>system_state.o</t>
+  </si>
+  <si>
+    <t>jm_proto_uart.o</t>
+  </si>
+  <si>
+    <t>calib_hw.o</t>
+  </si>
+  <si>
+    <t>app_freertos.o</t>
+  </si>
+  <si>
+    <t>motor_pid_load.o</t>
+  </si>
+  <si>
+    <t>led_manager.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_adc.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_uart.o</t>
+  </si>
+  <si>
+    <t>jm_proto.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_tim.o</t>
+  </si>
+  <si>
+    <t>motor_param.o</t>
+  </si>
+  <si>
+    <t>m_wm.l</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_adc_ex.o</t>
+  </si>
+  <si>
+    <t>arm_cortexM4lf_math.lib</t>
+  </si>
+  <si>
+    <t>printfa.o</t>
+  </si>
+  <si>
+    <t>arm_common_tables.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_rcc.o</t>
+  </si>
+  <si>
+    <t>motion_param.o</t>
+  </si>
+  <si>
+    <t>queue.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_spi.o</t>
+  </si>
+  <si>
+    <t>mf_w.l</t>
+  </si>
+  <si>
+    <t>foc_core.o</t>
+  </si>
+  <si>
+    <t>dev_motor_phase_current.o</t>
+  </si>
+  <si>
+    <t>ctrl_transition.o</t>
+  </si>
+  <si>
+    <t>calib_config_runtime.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_fdcan.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_dma.o</t>
+  </si>
+  <si>
+    <t>multiturn_counter.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_rcc_ex.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_tim_ex.o</t>
+  </si>
+  <si>
+    <t>foc_decoupling.o</t>
+  </si>
+  <si>
+    <t>atan2f.o</t>
+  </si>
+  <si>
+    <t>dev_mt6835.o</t>
+  </si>
+  <si>
+    <t>cascade_control.o</t>
+  </si>
+  <si>
+    <t>dev_half_bridge.o</t>
+  </si>
+  <si>
+    <t>motor_pid_autotune.o</t>
+  </si>
+  <si>
+    <t>current_loop.o</t>
+  </si>
+  <si>
+    <t>crc16.o</t>
   </si>
   <si>
     <t>motor_control.o</t>
   </si>
   <si>
-    <t>foc_core.o</t>
-  </si>
-  <si>
-    <t>stdout.o</t>
-  </si>
-  <si>
-    <t>errno.o</t>
-  </si>
-  <si>
-    <t>system_stm32g4xx.o</t>
-  </si>
-  <si>
-    <t>jm_proto_uart.o</t>
-  </si>
-  <si>
-    <t>app_freertos.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_uart.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_tim.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_adc.o</t>
-  </si>
-  <si>
-    <t>arm_cortexM4lf_math.lib</t>
-  </si>
-  <si>
-    <t>printfa.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_adc_ex.o</t>
-  </si>
-  <si>
-    <t>arm_common_tables.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_rcc.o</t>
-  </si>
-  <si>
-    <t>motion_param.o</t>
-  </si>
-  <si>
-    <t>jm_proto.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_spi.o</t>
-  </si>
-  <si>
-    <t>mf_w.l</t>
-  </si>
-  <si>
-    <t>m_wm.l</t>
-  </si>
-  <si>
-    <t>dev_motor_phase_current.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_fdcan.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_dma.o</t>
-  </si>
-  <si>
-    <t>multiturn_counter.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_rcc_ex.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_tim_ex.o</t>
-  </si>
-  <si>
-    <t>dev_mt6835.o</t>
-  </si>
-  <si>
-    <t>cascade_control.o</t>
-  </si>
-  <si>
-    <t>system_state.o</t>
-  </si>
-  <si>
-    <t>dev_half_bridge.o</t>
-  </si>
-  <si>
-    <t>crc16.o</t>
+    <t>calib_ac_injection.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_gpio.o</t>
   </si>
   <si>
+    <t>ctrl_transition_mgr.o</t>
+  </si>
+  <si>
     <t>drv_tim.o</t>
   </si>
   <si>
@@ -206,172 +278,211 @@
     <t>pid_core.o</t>
   </si>
   <si>
+    <t>cosf.o</t>
+  </si>
+  <si>
     <t>dadd.o</t>
   </si>
   <si>
-    <t>ctrl_transition.o</t>
+    <t>cmsis_os.o</t>
+  </si>
+  <si>
+    <t>dev_config.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_uart_ex.o</t>
   </si>
   <si>
+    <t>gpio.o</t>
+  </si>
+  <si>
+    <t>main.o</t>
+  </si>
+  <si>
+    <t>drv_gpio.o</t>
+  </si>
+  <si>
+    <t>dmul.o</t>
+  </si>
+  <si>
+    <t>drv_adc.o</t>
+  </si>
+  <si>
+    <t>ddiv.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_pwr_ex.o</t>
+  </si>
+  <si>
+    <t>drv_spi.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_i2c.o</t>
+  </si>
+  <si>
+    <t>depilogue.o</t>
+  </si>
+  <si>
+    <t>fmodf.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_it.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_i2c_ex.o</t>
+  </si>
+  <si>
+    <t>motor_profile.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_cortex.o</t>
+  </si>
+  <si>
+    <t>roundf.o</t>
+  </si>
+  <si>
+    <t>arm_cos_f32.o</t>
+  </si>
+  <si>
+    <t>arm_sin_f32.o</t>
+  </si>
+  <si>
+    <t>motor_mode_velocity.o</t>
+  </si>
+  <si>
+    <t>list.o</t>
+  </si>
+  <si>
+    <t>motor_mode_mit.o</t>
+  </si>
+  <si>
+    <t>thread_period.o</t>
+  </si>
+  <si>
+    <t>motor_mode_open_loop.o</t>
+  </si>
+  <si>
+    <t>motor_mode_position.o</t>
+  </si>
+  <si>
+    <t>motor_mode_current.o</t>
+  </si>
+  <si>
+    <t>floorf.o</t>
+  </si>
+  <si>
+    <t>fepilogue.o</t>
+  </si>
+  <si>
+    <t>uldiv.o</t>
+  </si>
+  <si>
+    <t>ldiv.o</t>
+  </si>
+  <si>
+    <t>user_interface.o</t>
+  </si>
+  <si>
+    <t>motor_mode_test_sweep.o</t>
+  </si>
+  <si>
+    <t>motor_mode_torque.o</t>
+  </si>
+  <si>
+    <t>motor_mode_profile_torque.o</t>
+  </si>
+  <si>
+    <t>__dczerorl2.o</t>
+  </si>
+  <si>
+    <t>assert_report.o</t>
+  </si>
+  <si>
+    <t>frem.o</t>
+  </si>
+  <si>
+    <t>motor_mode_profile_velocity.o</t>
+  </si>
+  <si>
+    <t>dma.o</t>
+  </si>
+  <si>
+    <t>motor_mode_duty.o</t>
+  </si>
+  <si>
+    <t>frnd.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_msp.o</t>
+  </si>
+  <si>
+    <t>sqrtf.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_cordic.o</t>
+  </si>
+  <si>
+    <t>control_irq.o</t>
+  </si>
+  <si>
+    <t>dfixul.o</t>
+  </si>
+  <si>
+    <t>cdrcmple.o</t>
+  </si>
+  <si>
+    <t>drv_dwt_timer.o</t>
+  </si>
+  <si>
+    <t>uidiv.o</t>
+  </si>
+  <si>
+    <t>funder.o</t>
+  </si>
+  <si>
+    <t>motor_mode_idle.o</t>
+  </si>
+  <si>
+    <t>motor_mode_hold.o</t>
+  </si>
+  <si>
+    <t>fpclassifyf.o</t>
+  </si>
+  <si>
+    <t>memseta.o</t>
+  </si>
+  <si>
+    <t>memcpya.o</t>
+  </si>
+  <si>
+    <t>llsshr.o</t>
+  </si>
+  <si>
+    <t>init.o</t>
+  </si>
+  <si>
     <t>thread_commun.o</t>
   </si>
   <si>
-    <t>current_loop.o</t>
-  </si>
-  <si>
-    <t>gpio.o</t>
-  </si>
-  <si>
-    <t>main.o</t>
-  </si>
-  <si>
-    <t>dmul.o</t>
-  </si>
-  <si>
-    <t>ddiv.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_pwr_ex.o</t>
-  </si>
-  <si>
-    <t>drv_spi.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_i2c.o</t>
-  </si>
-  <si>
-    <t>malloc.o</t>
-  </si>
-  <si>
-    <t>depilogue.o</t>
-  </si>
-  <si>
-    <t>fmodf.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_i2c_ex.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_cortex.o</t>
-  </si>
-  <si>
-    <t>roundf.o</t>
-  </si>
-  <si>
-    <t>arm_cos_f32.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_it.o</t>
-  </si>
-  <si>
-    <t>arm_sin_f32.o</t>
-  </si>
-  <si>
-    <t>dev_config.o</t>
-  </si>
-  <si>
-    <t>drv_adc.o</t>
-  </si>
-  <si>
-    <t>list.o</t>
-  </si>
-  <si>
-    <t>drv_gpio.o</t>
-  </si>
-  <si>
-    <t>floorf.o</t>
-  </si>
-  <si>
-    <t>fepilogue.o</t>
-  </si>
-  <si>
-    <t>uldiv.o</t>
-  </si>
-  <si>
-    <t>ldiv.o</t>
-  </si>
-  <si>
-    <t>motor_param.o</t>
-  </si>
-  <si>
-    <t>cmsis_os.o</t>
-  </si>
-  <si>
-    <t>assert_report.o</t>
-  </si>
-  <si>
-    <t>frem.o</t>
-  </si>
-  <si>
-    <t>dma.o</t>
-  </si>
-  <si>
-    <t>frnd.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_msp.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_cordic.o</t>
-  </si>
-  <si>
-    <t>control_irq.o</t>
-  </si>
-  <si>
-    <t>dfixul.o</t>
-  </si>
-  <si>
-    <t>cdrcmple.o</t>
-  </si>
-  <si>
-    <t>drv_dwt_timer.o</t>
-  </si>
-  <si>
-    <t>uidiv.o</t>
-  </si>
-  <si>
-    <t>user_interface.o</t>
-  </si>
-  <si>
-    <t>funder.o</t>
-  </si>
-  <si>
-    <t>fpclassifyf.o</t>
-  </si>
-  <si>
-    <t>memseta.o</t>
-  </si>
-  <si>
-    <t>memcpya.o</t>
-  </si>
-  <si>
-    <t>llsshr.o</t>
-  </si>
-  <si>
-    <t>init.o</t>
-  </si>
-  <si>
     <t>llushr.o</t>
   </si>
   <si>
     <t>thread_idle.o</t>
   </si>
   <si>
+    <t>thread_display.o</t>
+  </si>
+  <si>
     <t>thread_control.o</t>
   </si>
   <si>
+    <t>motor_info_calib.o</t>
+  </si>
+  <si>
     <t>llshl.o</t>
   </si>
   <si>
     <t>handlers.o</t>
-  </si>
-  <si>
-    <t>thread_period.o</t>
-  </si>
-  <si>
-    <t>thread_display.o</t>
   </si>
   <si>
     <t>strncpy.o</t>
@@ -506,109 +617,148 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$124</c:f>
+              <c:f>ram_percent!$A$3:$A$162</c:f>
               <c:strCache>
-                <c:ptCount val="122"/>
+                <c:ptCount val="160"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>drv_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>dev_commun_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>startup_stm32g474xx.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>pid_profile.o</c:v>
-                </c:pt>
                 <c:pt idx="7">
+                  <c:v>motor_pid_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>dev_power_monitor.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>dev_power_monitor.o</c:v>
-                </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
+                  <c:v>calib_level2_motor.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
-                  <c:v>drv_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
+                  <c:v>dev_led.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>calib_mgr.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>calib_level5_nonlinear.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>dev_encoder_mt6835.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>calib_level7_auto.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="26">
+                  <c:v>calib_level3_encoder.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="28">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="29">
+                  <c:v>jm_host_commun.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>stm32g4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>port.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>calib_level6_system.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>calib_level1_driver.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="23">
-                  <c:v>stm32g4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>mvars.o</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>motor_control.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>foc_core.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="35">
+                  <c:v>calib_level4_torque.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>jm_proto_ops.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="38">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="39">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="40">
+                  <c:v>system_state.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="42">
+                  <c:v>calib_hw.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="44">
+                  <c:v>motor_pid_load.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>led_manager.o</c:v>
+                </c:pt>
+                <c:pt idx="159">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -616,110 +766,149 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$124</c:f>
+              <c:f>ram_percent!$B$3:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="122"/>
+                <c:ptCount val="160"/>
                 <c:pt idx="0">
-                  <c:v>64.26055145263672</c:v>
+                  <c:v>59.36426544189453</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.513740062713623</c:v>
+                  <c:v>7.391602993011475</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.435449600219727</c:v>
+                  <c:v>6.046360015869141</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.012682914733887</c:v>
+                  <c:v>5.94510555267334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.0358567237854</c:v>
+                  <c:v>3.728347778320313</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.740154981613159</c:v>
+                  <c:v>3.703033924102783</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.393564581871033</c:v>
+                  <c:v>2.58923077583313</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.330932378768921</c:v>
+                  <c:v>1.287382960319519</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.174352169036865</c:v>
+                  <c:v>1.229523062705994</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.8925076127052307</c:v>
+                  <c:v>1.084873199462891</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.8768495917320252</c:v>
+                  <c:v>0.9546884894371033</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.782901406288147</c:v>
+                  <c:v>0.8245036602020264</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.6263211369514465</c:v>
+                  <c:v>0.810038685798645</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.5010569095611572</c:v>
+                  <c:v>0.7232488393783569</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.422766774892807</c:v>
+                  <c:v>0.4773442447185516</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3914507031440735</c:v>
+                  <c:v>0.4628792405128479</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3288185894489288</c:v>
+                  <c:v>0.3905543684959412</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.3288185894489288</c:v>
+                  <c:v>0.3616244196891785</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.2975025475025177</c:v>
+                  <c:v>0.3037645220756531</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.1565802842378616</c:v>
+                  <c:v>0.274834543466568</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.09003366529941559</c:v>
+                  <c:v>0.2603695690631867</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.07829014211893082</c:v>
+                  <c:v>0.2603695690631867</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.06263211369514465</c:v>
+                  <c:v>0.2603695690631867</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.04697408527135849</c:v>
+                  <c:v>0.231439620256424</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.04697408527135849</c:v>
+                  <c:v>0.1591147482395172</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.03131605684757233</c:v>
+                  <c:v>0.1446497738361359</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.03131605684757233</c:v>
+                  <c:v>0.1301847845315933</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.03131605684757233</c:v>
+                  <c:v>0.08317361772060394</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.01565802842378616</c:v>
+                  <c:v>0.07232488691806793</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.01565802842378616</c:v>
+                  <c:v>0.07232488691806793</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.01565802842378616</c:v>
+                  <c:v>0.04339493066072464</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.01565802842378616</c:v>
+                  <c:v>0.04339493066072464</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.01565802842378616</c:v>
-                </c:pt>
-                <c:pt idx="121">
+                  <c:v>0.04339493066072464</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.04339493066072464</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.02892995253205299</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.02892995253205299</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.02169746533036232</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.0144649762660265</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.0144649762660265</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.0144649762660265</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.0144649762660265</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.0144649762660265</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.0144649762660265</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.0144649762660265</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.01084873266518116</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.007232488133013248</c:v>
+                </c:pt>
+                <c:pt idx="159">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -787,373 +976,487 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$124</c:f>
+              <c:f>flash_percent!$A$3:$A$162</c:f>
               <c:strCache>
-                <c:ptCount val="122"/>
+                <c:ptCount val="160"/>
                 <c:pt idx="0">
+                  <c:v>calib_level2_motor.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>stm32g4xx_hal_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>stm32g4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
+                  <c:v>jm_proto.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>stm32g4xx_hal_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
+                  <c:v>motor_param.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>stm32g4xx_hal_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
+                  <c:v>m_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>stm32g4xx_hal_adc_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>arm_cortexM4lf_math.lib</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>printfa.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>stm32g4xx_hal_adc_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>arm_common_tables.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>stm32g4xx_hal_rcc.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>motion_param.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>tasks.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>jm_proto.o</c:v>
+                  <c:v>jm_proto_ops.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>printfa.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>arm_common_tables.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>stm32g4xx_hal_rcc.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>motion_param.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>queue.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>dev_power_monitor.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>stm32g4xx_hal_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="19">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>m_wm.l</c:v>
-                </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="20">
+                  <c:v>foc_core.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>dev_motor_phase_current.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>ctrl_transition.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>motor_pid_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>system_state.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>calib_config_runtime.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>calib_mgr.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>calib_level3_encoder.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>stm32g4xx_hal_fdcan.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>calib_level5_nonlinear.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>stm32g4xx_hal_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>multiturn_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>dev_commun_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>port.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>motor_pid_load.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>tim.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>stm32g4xx_hal_tim_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>foc_decoupling.o</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>jm_host_commun.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>atan2f.o</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>dev_mt6835.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>cascade_control.o</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>dev_half_bridge.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>motor_pid_autotune.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>drv_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>current_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>crc16.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
-                  <c:v>dev_motor_phase_current.o</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>foc_core.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>stm32g4xx_hal_fdcan.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>stm32g4xx_hal_dma.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>motor_loop.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>multiturn_counter.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>pid_profile.o</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>tim.o</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>stm32g4xx_hal_tim_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>dev_mt6835.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>cascade_control.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>system_state.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>dev_commun_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>dev_half_bridge.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>crc16.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="50">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="51">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="52">
+                  <c:v>calib_ac_injection.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>calib_hw.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>packer_parser.o</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>adc.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>stm32g4xx_hal_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>ctrl_transition_mgr.o</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
-                  <c:v>stm32g4xx_hal_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>packer_parser.o</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>drv_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>adc.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="59">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="60">
+                  <c:v>calib_level7_auto.o</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="62">
+                  <c:v>dev_led.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="64">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="65">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="66">
+                  <c:v>cosf.o</c:v>
+                </c:pt>
+                <c:pt idx="67">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="68">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
-                  <c:v>ctrl_transition.o</c:v>
-                </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="69">
+                  <c:v>led_manager.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>cmsis_os.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>dev_config.o</c:v>
+                </c:pt>
+                <c:pt idx="72">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="73">
+                  <c:v>dev_encoder_mt6835.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>jm_proto_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>i2c.o</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>drv_rtos.o</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>drv_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>dmul.o</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>drv_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>ddiv.o</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>fdcan.o</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>drv_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>stm32g4xx_hal_i2c.o</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>thread_management.o</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>depilogue.o</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>fmodf.o</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>stm32g4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>calib_level1_driver.o</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>motor_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>stm32g4xx_hal_cortex.o</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>roundf.o</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>arm_cos_f32.o</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>arm_sin_f32.o</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>motor_mode_velocity.o</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>list.o</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>motor_mode_mit.o</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>calib_level6_system.o</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>thread_period.o</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>dev_dwt_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>motor_mode_open_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>motor_mode_position.o</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>motor_mode_current.o</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>floorf.o</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>fepilogue.o</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>stm32g4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>uldiv.o</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>ldiv.o</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>user_interface.o</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>motor_mode_test_sweep.o</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>motor_mode_torque.o</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>motor_mode_profile_torque.o</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>__dczerorl2.o</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>assert_report.o</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>app_freertos.o</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>frem.o</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>motor_mode_profile_velocity.o</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>cordic.o</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>motor_mode_duty.o</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>frnd.o</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>stm32g4xx_hal_msp.o</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>sqrtf.o</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>stm32g4xx_hal_cordic.o</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>calib_level4_torque.o</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>control_irq.o</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>dfixul.o</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>cdrcmple.o</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>drv_dwt_timer.o</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>uidiv.o</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>funder.o</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>system_stm32g4xx.o</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>motor_mode_idle.o</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>motor_mode_hold.o</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>fpclassifyf.o</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>memseta.o</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>memcpya.o</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>llsshr.o</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>init.o</c:v>
+                </c:pt>
+                <c:pt idx="144">
                   <c:v>thread_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
-                  <c:v>current_loop.o</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>jm_proto_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>i2c.o</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>dmul.o</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>ddiv.o</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>fdcan.o</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>drv_spi.o</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>stm32g4xx_hal_i2c.o</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>malloc.o</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>thread_management.o</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>depilogue.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>fmodf.o</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>drv_rtos.o</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>stm32g4xx_hal_cortex.o</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>roundf.o</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>arm_cos_f32.o</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>stm32g4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>arm_sin_f32.o</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>dev_config.o</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>drv_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>list.o</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>dev_dwt_counter.o</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>drv_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>floorf.o</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>fepilogue.o</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>uldiv.o</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>ldiv.o</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>motor_param.o</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>cmsis_os.o</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>assert_report.o</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>app_freertos.o</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>frem.o</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>dma.o</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>cordic.o</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>stm32g4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>frnd.o</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>stm32g4xx_hal_msp.o</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>stm32g4xx_hal_cordic.o</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>control_irq.o</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>dfixul.o</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>cdrcmple.o</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>drv_dwt_timer.o</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>uidiv.o</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>system_stm32g4xx.o</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>user_interface.o</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>funder.o</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>fpclassifyf.o</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>memseta.o</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>memcpya.o</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>llsshr.o</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>init.o</c:v>
-                </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="145">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="146">
                   <c:v>thread_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="147">
+                  <c:v>thread_display.o</c:v>
+                </c:pt>
+                <c:pt idx="148">
                   <c:v>thread_control.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="149">
+                  <c:v>motor_info_calib.o</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="151">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
-                  <c:v>thread_period.o</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>thread_display.o</c:v>
-                </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="152">
                   <c:v>strncpy.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="153">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
-                  <c:v>mvars.o</c:v>
-                </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="154">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="155">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="156">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="157">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="158">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="159">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1161,374 +1464,488 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$124</c:f>
+              <c:f>flash_percent!$B$3:$B$162</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="122"/>
+                <c:ptCount val="160"/>
                 <c:pt idx="0">
-                  <c:v>5.5169677734375</c:v>
+                  <c:v>4.649857997894287</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.275517463684082</c:v>
+                  <c:v>3.646524429321289</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.891843795776367</c:v>
+                  <c:v>3.575320243835449</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.59747314453125</c:v>
+                  <c:v>3.510588884353638</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.883045673370361</c:v>
+                  <c:v>3.441542387008667</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.668055772781372</c:v>
+                  <c:v>3.0876784324646</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.631672859191895</c:v>
+                  <c:v>3.072574377059937</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.393530368804932</c:v>
+                  <c:v>2.561197996139526</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.142157793045044</c:v>
+                  <c:v>2.537463188171387</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.986703634262085</c:v>
+                  <c:v>2.533147811889648</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.487266063690186</c:v>
+                  <c:v>2.52883243560791</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.31196665763855</c:v>
+                  <c:v>2.446839570999146</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.305351495742798</c:v>
+                  <c:v>2.392896890640259</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.179665327072144</c:v>
+                  <c:v>2.213807106018066</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.133359909057617</c:v>
+                  <c:v>2.049821376800537</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.987828254699707</c:v>
+                  <c:v>1.948409199714661</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.958060503005981</c:v>
+                  <c:v>1.734796285629273</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.782761096954346</c:v>
+                  <c:v>1.622595548629761</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.630614519119263</c:v>
+                  <c:v>1.503921627998352</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.58100152015686</c:v>
+                  <c:v>1.421928763389587</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.461930274963379</c:v>
+                  <c:v>1.374459266662598</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.375934362411499</c:v>
+                  <c:v>1.316201090812683</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.30647611618042</c:v>
+                  <c:v>1.294624090194702</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.296553492546082</c:v>
+                  <c:v>1.251469969749451</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.250248074531555</c:v>
+                  <c:v>1.171634793281555</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.190712451934815</c:v>
+                  <c:v>1.165161609649658</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.180789828300476</c:v>
+                  <c:v>1.143584609031677</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.157637119293213</c:v>
+                  <c:v>1.109061241149902</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.094793915748596</c:v>
+                  <c:v>1.085326552391052</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.081563830375671</c:v>
+                  <c:v>1.063749432563782</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.058411002159119</c:v>
+                  <c:v>1.055118560791016</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.031950831413269</c:v>
+                  <c:v>1.031383872032166</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.91949462890625</c:v>
+                  <c:v>0.8976060152053833</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.8467288613319397</c:v>
+                  <c:v>0.8846597671508789</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.8401137590408325</c:v>
+                  <c:v>0.860925018787384</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.7623867392539978</c:v>
+                  <c:v>0.8458210825920105</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.7475028038024902</c:v>
+                  <c:v>0.8317959904670715</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7475028038024902</c:v>
+                  <c:v>0.8156131505966187</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.7309651374816895</c:v>
+                  <c:v>0.7767744660377502</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7276576161384583</c:v>
+                  <c:v>0.7703013420104981</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.6780445575714111</c:v>
+                  <c:v>0.7487242817878723</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.6615068912506104</c:v>
+                  <c:v>0.7379357218742371</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.6152014136314392</c:v>
+                  <c:v>0.7293049097061157</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.6052788496017456</c:v>
+                  <c:v>0.7185163497924805</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.5688959360122681</c:v>
+                  <c:v>0.6947816014289856</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.5523582696914673</c:v>
+                  <c:v>0.6839930415153503</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.5490507483482361</c:v>
+                  <c:v>0.6688891053199768</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.5258979797363281</c:v>
+                  <c:v>0.6343657970428467</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.5093603134155273</c:v>
+                  <c:v>0.5998424887657166</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.469669908285141</c:v>
+                  <c:v>0.5782654285430908</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.459747314453125</c:v>
+                  <c:v>0.552372932434082</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.4498246908187866</c:v>
+                  <c:v>0.548057496547699</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.4498246908187866</c:v>
+                  <c:v>0.5437421202659607</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.4167493581771851</c:v>
+                  <c:v>0.5415844321250916</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.3869815468788147</c:v>
+                  <c:v>0.5372689962387085</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.3770589530467987</c:v>
+                  <c:v>0.5307958722114563</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.3671363294124603</c:v>
+                  <c:v>0.5049033761024475</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.3638288080692291</c:v>
+                  <c:v>0.4811686277389526</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.3638288080692291</c:v>
+                  <c:v>0.4693012237548828</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.3638288080692291</c:v>
+                  <c:v>0.4423298835754395</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.33736851811409</c:v>
+                  <c:v>0.4401721954345703</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.3109082579612732</c:v>
+                  <c:v>0.4315413534641266</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.3109082579612732</c:v>
+                  <c:v>0.4315413534641266</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.3076007068157196</c:v>
+                  <c:v>0.4013334512710571</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.2910630404949188</c:v>
+                  <c:v>0.3948603570461273</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.2910630404949188</c:v>
+                  <c:v>0.3711255788803101</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.2646027505397797</c:v>
+                  <c:v>0.3624947369098663</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.2612952291965485</c:v>
+                  <c:v>0.3603370189666748</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.2546801567077637</c:v>
+                  <c:v>0.3581793308258057</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.2513726353645325</c:v>
+                  <c:v>0.353863924741745</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.2447575628757477</c:v>
+                  <c:v>0.3495484888553619</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.2381424903869629</c:v>
+                  <c:v>0.3441542387008667</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.2364887148141861</c:v>
+                  <c:v>0.3322868347167969</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.2348349541425705</c:v>
+                  <c:v>0.3085520565509796</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.2282198816537857</c:v>
+                  <c:v>0.2934481203556061</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.2249123454093933</c:v>
+                  <c:v>0.2934481203556061</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.1984520703554153</c:v>
+                  <c:v>0.2718710601329804</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.1885294765233994</c:v>
+                  <c:v>0.2610825300216675</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.185221940279007</c:v>
+                  <c:v>0.2524516880512238</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.1819144040346146</c:v>
+                  <c:v>0.2502939999103546</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.1620691865682602</c:v>
+                  <c:v>0.2459785789251328</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.1620691865682602</c:v>
+                  <c:v>0.2438208609819412</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.158761665225029</c:v>
+                  <c:v>0.2395054548978806</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.1389164477586746</c:v>
+                  <c:v>0.2373477518558502</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.1389164477586746</c:v>
+                  <c:v>0.2373477518558502</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.1389164477586746</c:v>
+                  <c:v>0.2373477518558502</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.1356089115142822</c:v>
+                  <c:v>0.2200860977172852</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.1256863176822662</c:v>
+                  <c:v>0.2071398496627808</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.1256863176822662</c:v>
+                  <c:v>0.2006667256355286</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.1157637089490891</c:v>
+                  <c:v>0.1898781955242157</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.09922603517770767</c:v>
+                  <c:v>0.1898781955242157</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.09922603517770767</c:v>
+                  <c:v>0.1898781955242157</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.08930343389511108</c:v>
+                  <c:v>0.185562789440155</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.08599589765071869</c:v>
+                  <c:v>0.1726165413856506</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.0793808326125145</c:v>
+                  <c:v>0.1704588383436203</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.0793808326125145</c:v>
+                  <c:v>0.1661434173583984</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.0793808326125145</c:v>
+                  <c:v>0.1639857143163681</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.07276576012372971</c:v>
+                  <c:v>0.1553548872470856</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.07276576012372971</c:v>
+                  <c:v>0.1531971842050552</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.06945822387933731</c:v>
+                  <c:v>0.1488817632198334</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.06284315884113312</c:v>
+                  <c:v>0.146724060177803</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.06284315884113312</c:v>
+                  <c:v>0.1424086540937424</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.05953562259674072</c:v>
+                  <c:v>0.1359355300664902</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.05953562259674072</c:v>
+                  <c:v>0.129462406039238</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.05953562259674072</c:v>
+                  <c:v>0.129462406039238</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.05953562259674072</c:v>
+                  <c:v>0.1273047029972076</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.05292055383324623</c:v>
+                  <c:v>0.1251469999551773</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.05292055383324623</c:v>
+                  <c:v>0.1251469999551773</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.05292055383324623</c:v>
+                  <c:v>0.1208315789699554</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.04961301758885384</c:v>
+                  <c:v>0.1186738759279251</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.04961301758885384</c:v>
+                  <c:v>0.1143584623932838</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.04630548506975174</c:v>
+                  <c:v>0.1057276353240013</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.04630548506975174</c:v>
+                  <c:v>0.1057276353240013</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.03969041630625725</c:v>
+                  <c:v>0.1057276353240013</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.02646027691662312</c:v>
+                  <c:v>0.09925451129674912</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.01323013845831156</c:v>
+                  <c:v>0.09493909776210785</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.01323013845831156</c:v>
+                  <c:v>0.09493909776210785</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.01323013845831156</c:v>
+                  <c:v>0.09278139472007752</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.006615069229155779</c:v>
+                  <c:v>0.09062368422746658</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.006615069229155779</c:v>
+                  <c:v>0.09062368422746658</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.006615069229155779</c:v>
+                  <c:v>0.08846598118543625</c:v>
                 </c:pt>
                 <c:pt idx="121">
+                  <c:v>0.08846598118543625</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>0.08199285715818405</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>0.08199285715818405</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>0.07120432704687119</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>0.06473120301961899</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>0.06473120301961899</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>0.06257349997758865</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>0.05825808271765709</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>0.05825808271765709</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>0.05610037595033646</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>0.05178496241569519</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.05178496241569519</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>0.05178496241569519</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.04746954888105393</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>0.04746954888105393</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>0.04746954888105393</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>0.04746954888105393</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>0.04746954888105393</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>0.04099642857909203</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>0.03883872181177139</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.03883872181177139</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>0.03883872181177139</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>0.03883872181177139</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>0.03883872181177139</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>0.03452330827713013</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>0.03452330827713013</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.03452330827713013</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>0.03452330827713013</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>0.03452330827713013</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0.03236560150980949</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>0.03236560150980949</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.0258924812078476</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>0.01726165413856506</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.008630827069282532</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.008630827069282532</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>0.004315413534641266</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.004315413534641266</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.004315413534641266</c:v>
+                </c:pt>
+                <c:pt idx="159">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1633,8 +2050,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H124" totalsRowCount="1">
-  <autoFilter ref="A2:H123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H162" totalsRowCount="1">
+  <autoFilter ref="A2:H161"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1650,8 +2067,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H124" totalsRowCount="1">
-  <autoFilter ref="A2:H123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H162" totalsRowCount="1">
+  <autoFilter ref="A2:H161"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1951,7 +2368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1964,28 +2381,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="G2" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1993,7 +2410,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>64.26055145263672</v>
+        <v>59.36426544189453</v>
       </c>
       <c r="C3" s="1">
         <v>16416</v>
@@ -2019,25 +2436,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>6.513740062713623</v>
+        <v>7.391602993011475</v>
       </c>
       <c r="C4" s="1">
-        <v>1664</v>
+        <v>2044</v>
       </c>
       <c r="D4" s="1">
-        <v>884</v>
+        <v>620</v>
       </c>
       <c r="E4" s="1">
-        <v>884</v>
+        <v>564</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>1664</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2045,25 +2462,25 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>6.435449600219727</v>
+        <v>6.046360015869141</v>
       </c>
       <c r="C5" s="1">
-        <v>1644</v>
+        <v>1672</v>
       </c>
       <c r="D5" s="1">
-        <v>640</v>
+        <v>1160</v>
       </c>
       <c r="E5" s="1">
-        <v>636</v>
+        <v>1160</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>1640</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2071,25 +2488,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>6.012682914733887</v>
+        <v>5.94510555267334</v>
       </c>
       <c r="C6" s="1">
-        <v>1536</v>
+        <v>1644</v>
       </c>
       <c r="D6" s="1">
-        <v>508</v>
+        <v>820</v>
       </c>
       <c r="E6" s="1">
-        <v>36</v>
+        <v>816</v>
       </c>
       <c r="F6" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" s="1">
-        <v>1536</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2097,16 +2514,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.0358567237854</v>
+        <v>3.728347778320313</v>
       </c>
       <c r="C7" s="1">
         <v>1031</v>
       </c>
       <c r="D7" s="1">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="E7" s="1">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -2123,25 +2540,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>2.740154981613159</v>
+        <v>3.703033924102783</v>
       </c>
       <c r="C8" s="1">
-        <v>700</v>
+        <v>1024</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>700</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2149,25 +2566,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>1.393564581871033</v>
+        <v>2.58923077583313</v>
       </c>
       <c r="C9" s="1">
-        <v>356</v>
+        <v>716</v>
       </c>
       <c r="D9" s="1">
-        <v>790</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>434</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>352</v>
+        <v>716</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2175,25 +2592,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>1.330932378768921</v>
+        <v>1.287382960319519</v>
       </c>
       <c r="C10" s="1">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="D10" s="1">
-        <v>344</v>
+        <v>1086</v>
       </c>
       <c r="E10" s="1">
-        <v>344</v>
+        <v>730</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="1">
-        <v>340</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2201,25 +2618,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.174352169036865</v>
+        <v>1.229523062705994</v>
       </c>
       <c r="C11" s="1">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="D11" s="1">
-        <v>1504</v>
+        <v>344</v>
       </c>
       <c r="E11" s="1">
-        <v>1444</v>
+        <v>344</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>240</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2227,25 +2644,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.8925076127052307</v>
+        <v>1.084873199462891</v>
       </c>
       <c r="C12" s="1">
-        <v>228</v>
+        <v>300</v>
       </c>
       <c r="D12" s="1">
-        <v>756</v>
+        <v>2344</v>
       </c>
       <c r="E12" s="1">
-        <v>756</v>
+        <v>2284</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2253,16 +2670,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.8768495917320252</v>
+        <v>0.9546884894371033</v>
       </c>
       <c r="C13" s="1">
-        <v>224</v>
+        <v>264</v>
       </c>
       <c r="D13" s="1">
-        <v>160</v>
+        <v>1504</v>
       </c>
       <c r="E13" s="1">
-        <v>160</v>
+        <v>1504</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2271,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>224</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2279,16 +2696,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.782901406288147</v>
+        <v>0.8245036602020264</v>
       </c>
       <c r="C14" s="1">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="D14" s="1">
-        <v>332</v>
+        <v>756</v>
       </c>
       <c r="E14" s="1">
-        <v>332</v>
+        <v>756</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2297,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>200</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2305,16 +2722,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.6263211369514465</v>
+        <v>0.810038685798645</v>
       </c>
       <c r="C15" s="1">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2323,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>160</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2331,16 +2748,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.5010569095611572</v>
+        <v>0.7232488393783569</v>
       </c>
       <c r="C16" s="1">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="D16" s="1">
-        <v>120</v>
+        <v>332</v>
       </c>
       <c r="E16" s="1">
-        <v>120</v>
+        <v>332</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2349,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>128</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2357,25 +2774,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.422766774892807</v>
+        <v>0.4773442447185516</v>
       </c>
       <c r="C17" s="1">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="D17" s="1">
-        <v>440</v>
+        <v>4310</v>
       </c>
       <c r="E17" s="1">
-        <v>440</v>
+        <v>4298</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2383,16 +2800,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3914507031440735</v>
+        <v>0.4628792405128479</v>
       </c>
       <c r="C18" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="D18" s="1">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="E18" s="1">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2401,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2409,16 +2826,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3288185894489288</v>
+        <v>0.3905543684959412</v>
       </c>
       <c r="C19" s="1">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="D19" s="1">
-        <v>252</v>
+        <v>492</v>
       </c>
       <c r="E19" s="1">
-        <v>252</v>
+        <v>492</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2427,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2435,25 +2852,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.3288185894489288</v>
+        <v>0.3616244196891785</v>
       </c>
       <c r="C20" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D20" s="1">
-        <v>442</v>
+        <v>220</v>
       </c>
       <c r="E20" s="1">
-        <v>386</v>
+        <v>220</v>
       </c>
       <c r="F20" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2461,16 +2878,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.2975025475025177</v>
+        <v>0.3037645220756531</v>
       </c>
       <c r="C21" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D21" s="1">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="E21" s="1">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2479,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2487,25 +2904,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.1565802842378616</v>
+        <v>0.274834543466568</v>
       </c>
       <c r="C22" s="1">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="D22" s="1">
+        <v>136</v>
+      </c>
+      <c r="E22" s="1">
+        <v>136</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
         <v>76</v>
-      </c>
-      <c r="E22" s="1">
-        <v>76</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2513,25 +2930,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.09003366529941559</v>
+        <v>0.2603695690631867</v>
       </c>
       <c r="C23" s="1">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D23" s="1">
-        <v>461</v>
+        <v>400</v>
       </c>
       <c r="E23" s="1">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="F23" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2539,25 +2956,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.07829014211893082</v>
+        <v>0.2603695690631867</v>
       </c>
       <c r="C24" s="1">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D24" s="1">
-        <v>188</v>
+        <v>1028</v>
       </c>
       <c r="E24" s="1">
-        <v>188</v>
+        <v>468</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H24" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2565,25 +2982,25 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.06263211369514465</v>
+        <v>0.2603695690631867</v>
       </c>
       <c r="C25" s="1">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="D25" s="1">
-        <v>2958</v>
+        <v>978</v>
       </c>
       <c r="E25" s="1">
-        <v>2942</v>
+        <v>966</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G25" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -2591,25 +3008,25 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.04697408527135849</v>
+        <v>0.231439620256424</v>
       </c>
       <c r="C26" s="1">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="D26" s="1">
-        <v>70</v>
+        <v>286</v>
       </c>
       <c r="E26" s="1">
-        <v>58</v>
+        <v>286</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -2617,22 +3034,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.04697408527135849</v>
+        <v>0.1591147482395172</v>
       </c>
       <c r="C27" s="1">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D27" s="1">
-        <v>714</v>
+        <v>408</v>
       </c>
       <c r="E27" s="1">
-        <v>702</v>
+        <v>344</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G27" s="1">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2643,25 +3060,25 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.03131605684757233</v>
+        <v>0.1446497738361359</v>
       </c>
       <c r="C28" s="1">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D28" s="1">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="E28" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2669,25 +3086,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.03131605684757233</v>
+        <v>0.1301847845315933</v>
       </c>
       <c r="C29" s="1">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1">
-        <v>1202</v>
+        <v>1006</v>
       </c>
       <c r="E29" s="1">
-        <v>1014</v>
+        <v>994</v>
       </c>
       <c r="F29" s="1">
-        <v>180</v>
+        <v>12</v>
       </c>
       <c r="G29" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -2695,22 +3112,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.03131605684757233</v>
+        <v>0.08317361772060394</v>
       </c>
       <c r="C30" s="1">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D30" s="1">
-        <v>1078</v>
+        <v>435</v>
       </c>
       <c r="E30" s="1">
-        <v>1070</v>
+        <v>400</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G30" s="1">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -2721,25 +3138,25 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.01565802842378616</v>
+        <v>0.07232488691806793</v>
       </c>
       <c r="C31" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1">
-        <v>4</v>
+        <v>192</v>
       </c>
       <c r="E31" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -2747,22 +3164,22 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.01565802842378616</v>
+        <v>0.07232488691806793</v>
       </c>
       <c r="C32" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D32" s="1">
-        <v>16</v>
+        <v>694</v>
       </c>
       <c r="E32" s="1">
-        <v>12</v>
+        <v>674</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2773,22 +3190,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.01565802842378616</v>
+        <v>0.04339493066072464</v>
       </c>
       <c r="C33" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D33" s="1">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="E33" s="1">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="F33" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -2799,22 +3216,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.01565802842378616</v>
+        <v>0.04339493066072464</v>
       </c>
       <c r="C34" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D34" s="1">
-        <v>272</v>
+        <v>798</v>
       </c>
       <c r="E34" s="1">
-        <v>268</v>
+        <v>786</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -2825,56 +3242,394 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.01565802842378616</v>
+        <v>0.04339493066072464</v>
       </c>
       <c r="C35" s="1">
+        <v>12</v>
+      </c>
+      <c r="D35" s="1">
+        <v>126</v>
+      </c>
+      <c r="E35" s="1">
+        <v>102</v>
+      </c>
+      <c r="F35" s="1">
+        <v>12</v>
+      </c>
+      <c r="G35" s="1">
+        <v>12</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.04339493066072464</v>
+      </c>
+      <c r="C36" s="1">
+        <v>12</v>
+      </c>
+      <c r="D36" s="1">
+        <v>172</v>
+      </c>
+      <c r="E36" s="1">
+        <v>148</v>
+      </c>
+      <c r="F36" s="1">
+        <v>12</v>
+      </c>
+      <c r="G36" s="1">
+        <v>12</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.02892995253205299</v>
+      </c>
+      <c r="C37" s="1">
+        <v>8</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2848</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2840</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>8</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.02892995253205299</v>
+      </c>
+      <c r="C38" s="1">
+        <v>8</v>
+      </c>
+      <c r="D38" s="1">
+        <v>54</v>
+      </c>
+      <c r="E38" s="1">
+        <v>34</v>
+      </c>
+      <c r="F38" s="1">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1">
+        <v>8</v>
+      </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.02169746533036232</v>
+      </c>
+      <c r="C39" s="1">
+        <v>6</v>
+      </c>
+      <c r="D39" s="1">
+        <v>2268</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1814</v>
+      </c>
+      <c r="F39" s="1">
+        <v>448</v>
+      </c>
+      <c r="G39" s="1">
+        <v>6</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.0144649762660265</v>
+      </c>
+      <c r="C40" s="1">
         <v>4</v>
       </c>
-      <c r="D35" s="1">
+      <c r="D40" s="1">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>4</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.0144649762660265</v>
+      </c>
+      <c r="C41" s="1">
+        <v>4</v>
+      </c>
+      <c r="D41" s="1">
+        <v>16</v>
+      </c>
+      <c r="E41" s="1">
+        <v>12</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>4</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.0144649762660265</v>
+      </c>
+      <c r="C42" s="1">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1">
+        <v>44</v>
+      </c>
+      <c r="E42" s="1">
+        <v>16</v>
+      </c>
+      <c r="F42" s="1">
+        <v>24</v>
+      </c>
+      <c r="G42" s="1">
+        <v>4</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.0144649762660265</v>
+      </c>
+      <c r="C43" s="1">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1080</v>
+      </c>
+      <c r="E43" s="1">
+        <v>740</v>
+      </c>
+      <c r="F43" s="1">
+        <v>336</v>
+      </c>
+      <c r="G43" s="1">
+        <v>4</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.0144649762660265</v>
+      </c>
+      <c r="C44" s="1">
+        <v>4</v>
+      </c>
+      <c r="D44" s="1">
+        <v>272</v>
+      </c>
+      <c r="E44" s="1">
+        <v>268</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>4</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.0144649762660265</v>
+      </c>
+      <c r="C45" s="1">
+        <v>4</v>
+      </c>
+      <c r="D45" s="1">
+        <v>502</v>
+      </c>
+      <c r="E45" s="1">
+        <v>498</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>4</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.0144649762660265</v>
+      </c>
+      <c r="C46" s="1">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1">
         <v>84</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E46" s="1">
         <v>48</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F46" s="1">
         <v>32</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G46" s="1">
         <v>4</v>
       </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" t="s">
-        <v>125</v>
-      </c>
-      <c r="B124">
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.01084873266518116</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1">
+        <v>771</v>
+      </c>
+      <c r="E47" s="1">
+        <v>768</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>3</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.007232488133013248</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2</v>
+      </c>
+      <c r="D48" s="1">
+        <v>328</v>
+      </c>
+      <c r="E48" s="1">
+        <v>326</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>2</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+      <c r="B162">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C124">
+      <c r="C162">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D124">
+      <c r="D162">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E124">
+      <c r="E162">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F124">
+      <c r="F162">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G124">
+      <c r="G162">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H124">
+      <c r="H162">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2890,7 +3645,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2903,71 +3658,71 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="G2" t="s">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="H2" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2">
-        <v>5.5169677734375</v>
+        <v>4.649857997894287</v>
       </c>
       <c r="C3" s="1">
-        <v>3336</v>
+        <v>4310</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E3" s="1">
-        <v>3312</v>
+        <v>4298</v>
       </c>
       <c r="F3" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2">
-        <v>5.275517463684082</v>
+        <v>3.646524429321289</v>
       </c>
       <c r="C4" s="1">
-        <v>3190</v>
+        <v>3380</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>3190</v>
+        <v>3380</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -2981,25 +3736,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B5" s="2">
-        <v>4.891843795776367</v>
+        <v>3.575320243835449</v>
       </c>
       <c r="C5" s="1">
-        <v>2958</v>
+        <v>3314</v>
       </c>
       <c r="D5" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>2942</v>
+        <v>3290</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -3007,19 +3762,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2">
-        <v>4.59747314453125</v>
+        <v>3.510588884353638</v>
       </c>
       <c r="C6" s="1">
-        <v>2780</v>
+        <v>3254</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>2780</v>
+        <v>3254</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -3033,22 +3788,22 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2">
-        <v>3.883045673370361</v>
+        <v>3.441542387008667</v>
       </c>
       <c r="C7" s="1">
-        <v>2348</v>
+        <v>3190</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>296</v>
+        <v>3190</v>
       </c>
       <c r="F7" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -3059,22 +3814,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2">
-        <v>3.668055772781372</v>
+        <v>3.0876784324646</v>
       </c>
       <c r="C8" s="1">
-        <v>2218</v>
+        <v>2862</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2218</v>
+        <v>2518</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -3085,25 +3840,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2">
-        <v>3.631672859191895</v>
+        <v>3.072574377059937</v>
       </c>
       <c r="C9" s="1">
-        <v>2196</v>
+        <v>2848</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1">
-        <v>2196</v>
+        <v>2840</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -3111,22 +3866,22 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2">
-        <v>3.393530368804932</v>
+        <v>2.561197996139526</v>
       </c>
       <c r="C10" s="1">
-        <v>2052</v>
+        <v>2374</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>2342</v>
       </c>
       <c r="F10" s="1">
-        <v>2052</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -3137,19 +3892,19 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2">
-        <v>3.142157793045044</v>
+        <v>2.537463188171387</v>
       </c>
       <c r="C11" s="1">
-        <v>1900</v>
+        <v>2352</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>1900</v>
+        <v>2352</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -3163,22 +3918,22 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2">
-        <v>2.986703634262085</v>
+        <v>2.533147811889648</v>
       </c>
       <c r="C12" s="1">
-        <v>1806</v>
+        <v>2348</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1806</v>
+        <v>296</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -3189,19 +3944,19 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="2">
-        <v>2.487266063690186</v>
+        <v>2.52883243560791</v>
       </c>
       <c r="C13" s="1">
-        <v>1504</v>
+        <v>2344</v>
       </c>
       <c r="D13" s="1">
         <v>300</v>
       </c>
       <c r="E13" s="1">
-        <v>1444</v>
+        <v>2284</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -3215,25 +3970,25 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B14" s="2">
-        <v>2.31196665763855</v>
+        <v>2.446839570999146</v>
       </c>
       <c r="C14" s="1">
-        <v>1398</v>
+        <v>2268</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1">
-        <v>1398</v>
+        <v>1814</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -3241,19 +3996,19 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2">
-        <v>2.305351495742798</v>
+        <v>2.392896890640259</v>
       </c>
       <c r="C15" s="1">
-        <v>1394</v>
+        <v>2218</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>1394</v>
+        <v>2218</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -3267,22 +4022,22 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2">
-        <v>2.179665327072144</v>
+        <v>2.213807106018066</v>
       </c>
       <c r="C16" s="1">
-        <v>1318</v>
+        <v>2052</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>1318</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -3293,22 +4048,22 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2">
-        <v>2.133359909057617</v>
+        <v>2.049821376800537</v>
       </c>
       <c r="C17" s="1">
-        <v>1290</v>
+        <v>1900</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>1258</v>
+        <v>1900</v>
       </c>
       <c r="F17" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -3319,25 +4074,25 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2">
-        <v>1.987828254699707</v>
+        <v>1.948409199714661</v>
       </c>
       <c r="C18" s="1">
-        <v>1202</v>
+        <v>1806</v>
       </c>
       <c r="D18" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>1014</v>
+        <v>1806</v>
       </c>
       <c r="F18" s="1">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -3345,19 +4100,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2">
-        <v>1.958060503005981</v>
+        <v>1.734796285629273</v>
       </c>
       <c r="C19" s="1">
-        <v>1184</v>
+        <v>1608</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>1184</v>
+        <v>1608</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -3371,45 +4126,45 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B20" s="2">
-        <v>1.782761096954346</v>
+        <v>1.622595548629761</v>
       </c>
       <c r="C20" s="1">
-        <v>1078</v>
+        <v>1504</v>
       </c>
       <c r="D20" s="1">
-        <v>8</v>
+        <v>264</v>
       </c>
       <c r="E20" s="1">
-        <v>1070</v>
+        <v>1504</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B21" s="2">
-        <v>1.630614519119263</v>
+        <v>1.503921627998352</v>
       </c>
       <c r="C21" s="1">
-        <v>986</v>
+        <v>1394</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>986</v>
+        <v>1394</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -3423,19 +4178,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B22" s="2">
-        <v>1.58100152015686</v>
+        <v>1.421928763389587</v>
       </c>
       <c r="C22" s="1">
-        <v>956</v>
+        <v>1318</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>956</v>
+        <v>1318</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -3449,19 +4204,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="B23" s="2">
-        <v>1.461930274963379</v>
+        <v>1.374459266662598</v>
       </c>
       <c r="C23" s="1">
-        <v>884</v>
+        <v>1274</v>
       </c>
       <c r="D23" s="1">
-        <v>1664</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>884</v>
+        <v>1274</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -3470,24 +4225,24 @@
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>1664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B24" s="2">
-        <v>1.375934362411499</v>
+        <v>1.316201090812683</v>
       </c>
       <c r="C24" s="1">
-        <v>832</v>
+        <v>1220</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>832</v>
+        <v>1220</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -3501,45 +4256,45 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="B25" s="2">
-        <v>1.30647611618042</v>
+        <v>1.294624090194702</v>
       </c>
       <c r="C25" s="1">
-        <v>790</v>
+        <v>1200</v>
       </c>
       <c r="D25" s="1">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>434</v>
+        <v>1200</v>
       </c>
       <c r="F25" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="B26" s="2">
-        <v>1.296553492546082</v>
+        <v>1.251469969749451</v>
       </c>
       <c r="C26" s="1">
-        <v>784</v>
+        <v>1160</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>1672</v>
       </c>
       <c r="E26" s="1">
-        <v>784</v>
+        <v>1160</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -3548,56 +4303,56 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B27" s="2">
-        <v>1.250248074531555</v>
+        <v>1.171634793281555</v>
       </c>
       <c r="C27" s="1">
-        <v>756</v>
+        <v>1086</v>
       </c>
       <c r="D27" s="1">
-        <v>228</v>
+        <v>356</v>
       </c>
       <c r="E27" s="1">
-        <v>756</v>
+        <v>730</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="1">
-        <v>228</v>
+        <v>352</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2">
-        <v>1.190712451934815</v>
+        <v>1.165161609649658</v>
       </c>
       <c r="C28" s="1">
-        <v>720</v>
+        <v>1080</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28" s="1">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -3605,25 +4360,25 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="B29" s="2">
-        <v>1.180789828300476</v>
+        <v>1.143584609031677</v>
       </c>
       <c r="C29" s="1">
-        <v>714</v>
+        <v>1060</v>
       </c>
       <c r="D29" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>702</v>
+        <v>1032</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G29" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -3631,74 +4386,74 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2">
-        <v>1.157637119293213</v>
+        <v>1.109061241149902</v>
       </c>
       <c r="C30" s="1">
-        <v>700</v>
+        <v>1028</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E30" s="1">
-        <v>700</v>
+        <v>468</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2">
-        <v>1.094793915748596</v>
+        <v>1.085326552391052</v>
       </c>
       <c r="C31" s="1">
-        <v>662</v>
+        <v>1006</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E31" s="1">
-        <v>662</v>
+        <v>994</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B32" s="2">
-        <v>1.081563830375671</v>
+        <v>1.063749432563782</v>
       </c>
       <c r="C32" s="1">
-        <v>654</v>
+        <v>986</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>318</v>
+        <v>986</v>
       </c>
       <c r="F32" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -3709,45 +4464,45 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="B33" s="2">
-        <v>1.058411002159119</v>
+        <v>1.055118560791016</v>
       </c>
       <c r="C33" s="1">
-        <v>640</v>
+        <v>978</v>
       </c>
       <c r="D33" s="1">
-        <v>1644</v>
+        <v>72</v>
       </c>
       <c r="E33" s="1">
-        <v>636</v>
+        <v>966</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>1640</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B34" s="2">
-        <v>1.031950831413269</v>
+        <v>1.031383872032166</v>
       </c>
       <c r="C34" s="1">
-        <v>624</v>
+        <v>956</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>624</v>
+        <v>956</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -3761,22 +4516,22 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B35" s="2">
-        <v>0.91949462890625</v>
+        <v>0.8976060152053833</v>
       </c>
       <c r="C35" s="1">
-        <v>556</v>
+        <v>832</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>44</v>
+        <v>832</v>
       </c>
       <c r="F35" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -3787,77 +4542,77 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>0.8467288613319397</v>
+        <v>0.8846597671508789</v>
       </c>
       <c r="C36" s="1">
-        <v>512</v>
+        <v>820</v>
       </c>
       <c r="D36" s="1">
-        <v>16416</v>
+        <v>1644</v>
       </c>
       <c r="E36" s="1">
-        <v>480</v>
+        <v>816</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H36" s="1">
-        <v>16384</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B37" s="2">
-        <v>0.8401137590408325</v>
+        <v>0.860925018787384</v>
       </c>
       <c r="C37" s="1">
-        <v>508</v>
+        <v>798</v>
       </c>
       <c r="D37" s="1">
-        <v>1536</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1">
-        <v>36</v>
+        <v>786</v>
       </c>
       <c r="F37" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H37" s="1">
-        <v>1536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B38" s="2">
-        <v>0.7623867392539978</v>
+        <v>0.8458210825920105</v>
       </c>
       <c r="C38" s="1">
-        <v>461</v>
+        <v>784</v>
       </c>
       <c r="D38" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>426</v>
+        <v>784</v>
       </c>
       <c r="F38" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -3865,25 +4620,25 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B39" s="2">
-        <v>0.7475028038024902</v>
+        <v>0.8317959904670715</v>
       </c>
       <c r="C39" s="1">
-        <v>452</v>
+        <v>771</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E39" s="1">
-        <v>452</v>
+        <v>768</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -3891,19 +4646,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B40" s="2">
-        <v>0.7475028038024902</v>
+        <v>0.8156131505966187</v>
       </c>
       <c r="C40" s="1">
-        <v>452</v>
+        <v>756</v>
       </c>
       <c r="D40" s="1">
-        <v>1031</v>
+        <v>228</v>
       </c>
       <c r="E40" s="1">
-        <v>452</v>
+        <v>756</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3912,82 +4667,82 @@
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>1031</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B41" s="2">
-        <v>0.7309651374816895</v>
+        <v>0.7767744660377502</v>
       </c>
       <c r="C41" s="1">
-        <v>442</v>
+        <v>720</v>
       </c>
       <c r="D41" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>386</v>
+        <v>720</v>
       </c>
       <c r="F41" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7276576161384583</v>
+        <v>0.7703013420104981</v>
       </c>
       <c r="C42" s="1">
-        <v>440</v>
+        <v>714</v>
       </c>
       <c r="D42" s="1">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>440</v>
+        <v>706</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B43" s="2">
-        <v>0.6780445575714111</v>
+        <v>0.7487242817878723</v>
       </c>
       <c r="C43" s="1">
-        <v>410</v>
+        <v>694</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E43" s="1">
-        <v>330</v>
+        <v>674</v>
       </c>
       <c r="F43" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -3995,19 +4750,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B44" s="2">
-        <v>0.6615068912506104</v>
+        <v>0.7379357218742371</v>
       </c>
       <c r="C44" s="1">
-        <v>400</v>
+        <v>684</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>400</v>
+        <v>684</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -4021,22 +4776,22 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B45" s="2">
-        <v>0.6152014136314392</v>
+        <v>0.7293049097061157</v>
       </c>
       <c r="C45" s="1">
-        <v>372</v>
+        <v>676</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>340</v>
+        <v>676</v>
       </c>
       <c r="F45" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -4047,19 +4802,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B46" s="2">
-        <v>0.6052788496017456</v>
+        <v>0.7185163497924805</v>
       </c>
       <c r="C46" s="1">
-        <v>366</v>
+        <v>666</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>366</v>
+        <v>666</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -4073,19 +4828,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="B47" s="2">
-        <v>0.5688959360122681</v>
+        <v>0.6947816014289856</v>
       </c>
       <c r="C47" s="1">
-        <v>344</v>
+        <v>644</v>
       </c>
       <c r="D47" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>344</v>
+        <v>644</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -4094,24 +4849,24 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B48" s="2">
-        <v>0.5523582696914673</v>
+        <v>0.6839930415153503</v>
       </c>
       <c r="C48" s="1">
-        <v>334</v>
+        <v>634</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>334</v>
+        <v>634</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -4125,45 +4880,45 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B49" s="2">
-        <v>0.5490507483482361</v>
+        <v>0.6688891053199768</v>
       </c>
       <c r="C49" s="1">
-        <v>332</v>
+        <v>620</v>
       </c>
       <c r="D49" s="1">
-        <v>200</v>
+        <v>2044</v>
       </c>
       <c r="E49" s="1">
-        <v>332</v>
+        <v>564</v>
       </c>
       <c r="F49" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>200</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B50" s="2">
-        <v>0.5258979797363281</v>
+        <v>0.6343657970428467</v>
       </c>
       <c r="C50" s="1">
-        <v>318</v>
+        <v>588</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>318</v>
+        <v>588</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -4177,22 +4932,22 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B51" s="2">
-        <v>0.5093603134155273</v>
+        <v>0.5998424887657166</v>
       </c>
       <c r="C51" s="1">
-        <v>308</v>
+        <v>556</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>292</v>
+        <v>44</v>
       </c>
       <c r="F51" s="1">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
@@ -4203,22 +4958,22 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B52" s="2">
-        <v>0.469669908285141</v>
+        <v>0.5782654285430908</v>
       </c>
       <c r="C52" s="1">
-        <v>284</v>
+        <v>536</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>252</v>
+        <v>344</v>
       </c>
       <c r="F52" s="1">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
@@ -4229,71 +4984,71 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>0.459747314453125</v>
+        <v>0.552372932434082</v>
       </c>
       <c r="C53" s="1">
-        <v>278</v>
+        <v>512</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>16416</v>
       </c>
       <c r="E53" s="1">
-        <v>278</v>
+        <v>480</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B54" s="2">
-        <v>0.4498246908187866</v>
+        <v>0.548057496547699</v>
       </c>
       <c r="C54" s="1">
-        <v>272</v>
+        <v>508</v>
       </c>
       <c r="D54" s="1">
-        <v>4</v>
+        <v>1024</v>
       </c>
       <c r="E54" s="1">
-        <v>268</v>
+        <v>36</v>
       </c>
       <c r="F54" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G54" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B55" s="2">
-        <v>0.4498246908187866</v>
+        <v>0.5437421202659607</v>
       </c>
       <c r="C55" s="1">
-        <v>272</v>
+        <v>504</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>272</v>
+        <v>504</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -4307,45 +5062,45 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B56" s="2">
-        <v>0.4167493581771851</v>
+        <v>0.5415844321250916</v>
       </c>
       <c r="C56" s="1">
-        <v>252</v>
+        <v>502</v>
       </c>
       <c r="D56" s="1">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="E56" s="1">
-        <v>252</v>
+        <v>498</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="B57" s="2">
-        <v>0.3869815468788147</v>
+        <v>0.5372689962387085</v>
       </c>
       <c r="C57" s="1">
-        <v>234</v>
+        <v>498</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="E57" s="1">
-        <v>234</v>
+        <v>498</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -4354,24 +5109,24 @@
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B58" s="2">
-        <v>0.3770589530467987</v>
+        <v>0.5307958722114563</v>
       </c>
       <c r="C58" s="1">
-        <v>228</v>
+        <v>492</v>
       </c>
       <c r="D58" s="1">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="E58" s="1">
-        <v>228</v>
+        <v>492</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -4380,24 +5135,24 @@
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B59" s="2">
-        <v>0.3671363294124603</v>
+        <v>0.5049033761024475</v>
       </c>
       <c r="C59" s="1">
-        <v>222</v>
+        <v>468</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>222</v>
+        <v>468</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -4411,19 +5166,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B60" s="2">
-        <v>0.3638288080692291</v>
+        <v>0.4811686277389526</v>
       </c>
       <c r="C60" s="1">
-        <v>220</v>
+        <v>446</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>220</v>
+        <v>446</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -4437,48 +5192,48 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B61" s="2">
-        <v>0.3638288080692291</v>
+        <v>0.4693012237548828</v>
       </c>
       <c r="C61" s="1">
-        <v>220</v>
+        <v>435</v>
       </c>
       <c r="D61" s="1">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="E61" s="1">
-        <v>220</v>
+        <v>400</v>
       </c>
       <c r="F61" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H61" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B62" s="2">
-        <v>0.3638288080692291</v>
+        <v>0.4423298835754395</v>
       </c>
       <c r="C62" s="1">
-        <v>220</v>
+        <v>410</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>204</v>
+        <v>330</v>
       </c>
       <c r="F62" s="1">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -4489,25 +5244,25 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="B63" s="2">
-        <v>0.33736851811409</v>
+        <v>0.4401721954345703</v>
       </c>
       <c r="C63" s="1">
-        <v>204</v>
+        <v>408</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E63" s="1">
-        <v>204</v>
+        <v>344</v>
       </c>
       <c r="F63" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G63" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H63" s="1">
         <v>0</v>
@@ -4515,19 +5270,19 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B64" s="2">
-        <v>0.3109082579612732</v>
+        <v>0.4315413534641266</v>
       </c>
       <c r="C64" s="1">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -4541,48 +5296,48 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B65" s="2">
-        <v>0.3109082579612732</v>
+        <v>0.4315413534641266</v>
       </c>
       <c r="C65" s="1">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="D65" s="1">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E65" s="1">
-        <v>188</v>
+        <v>392</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H65" s="1">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B66" s="2">
-        <v>0.3076007068157196</v>
+        <v>0.4013334512710571</v>
       </c>
       <c r="C66" s="1">
-        <v>186</v>
+        <v>372</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>186</v>
+        <v>340</v>
       </c>
       <c r="F66" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
@@ -4593,19 +5348,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B67" s="2">
-        <v>0.2910630404949188</v>
+        <v>0.3948603570461273</v>
       </c>
       <c r="C67" s="1">
-        <v>176</v>
+        <v>366</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>176</v>
+        <v>366</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -4619,19 +5374,19 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="B68" s="2">
-        <v>0.2910630404949188</v>
+        <v>0.3711255788803101</v>
       </c>
       <c r="C68" s="1">
-        <v>176</v>
+        <v>344</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E68" s="1">
-        <v>176</v>
+        <v>344</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -4640,24 +5395,24 @@
         <v>0</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="B69" s="2">
-        <v>0.2646027505397797</v>
+        <v>0.3624947369098663</v>
       </c>
       <c r="C69" s="1">
-        <v>160</v>
+        <v>336</v>
       </c>
       <c r="D69" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>160</v>
+        <v>336</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -4666,24 +5421,24 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B70" s="2">
-        <v>0.2612952291965485</v>
+        <v>0.3603370189666748</v>
       </c>
       <c r="C70" s="1">
-        <v>158</v>
+        <v>334</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>158</v>
+        <v>334</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -4697,19 +5452,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B71" s="2">
-        <v>0.2546801567077637</v>
+        <v>0.3581793308258057</v>
       </c>
       <c r="C71" s="1">
-        <v>154</v>
+        <v>332</v>
       </c>
       <c r="D71" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E71" s="1">
-        <v>154</v>
+        <v>332</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -4718,30 +5473,30 @@
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="B72" s="2">
-        <v>0.2513726353645325</v>
+        <v>0.353863924741745</v>
       </c>
       <c r="C72" s="1">
-        <v>152</v>
+        <v>328</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E72" s="1">
-        <v>152</v>
+        <v>326</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -4749,19 +5504,19 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B73" s="2">
-        <v>0.2447575628757477</v>
+        <v>0.3495484888553619</v>
       </c>
       <c r="C73" s="1">
-        <v>148</v>
+        <v>324</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>148</v>
+        <v>324</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -4775,22 +5530,22 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B74" s="2">
-        <v>0.2381424903869629</v>
+        <v>0.3441542387008667</v>
       </c>
       <c r="C74" s="1">
-        <v>144</v>
+        <v>319</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="F74" s="1">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
@@ -4801,22 +5556,22 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B75" s="2">
-        <v>0.2364887148141861</v>
+        <v>0.3322868347167969</v>
       </c>
       <c r="C75" s="1">
-        <v>143</v>
+        <v>308</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="F75" s="1">
-        <v>143</v>
+        <v>16</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
@@ -4827,51 +5582,51 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="B76" s="2">
-        <v>0.2348349541425705</v>
+        <v>0.3085520565509796</v>
       </c>
       <c r="C76" s="1">
-        <v>142</v>
+        <v>286</v>
       </c>
       <c r="D76" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E76" s="1">
-        <v>106</v>
+        <v>286</v>
       </c>
       <c r="F76" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="B77" s="2">
-        <v>0.2282198816537857</v>
+        <v>0.2934481203556061</v>
       </c>
       <c r="C77" s="1">
-        <v>138</v>
+        <v>272</v>
       </c>
       <c r="D77" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E77" s="1">
-        <v>138</v>
+        <v>268</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -4879,19 +5634,19 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="B78" s="2">
-        <v>0.2249123454093933</v>
+        <v>0.2934481203556061</v>
       </c>
       <c r="C78" s="1">
-        <v>136</v>
+        <v>272</v>
       </c>
       <c r="D78" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>136</v>
+        <v>272</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -4900,24 +5655,24 @@
         <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B79" s="2">
-        <v>0.1984520703554153</v>
+        <v>0.2718710601329804</v>
       </c>
       <c r="C79" s="1">
-        <v>120</v>
+        <v>252</v>
       </c>
       <c r="D79" s="1">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="E79" s="1">
-        <v>120</v>
+        <v>252</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -4926,50 +5681,50 @@
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>128</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="B80" s="2">
-        <v>0.1885294765233994</v>
+        <v>0.2610825300216675</v>
       </c>
       <c r="C80" s="1">
-        <v>114</v>
+        <v>242</v>
       </c>
       <c r="D80" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E80" s="1">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="F80" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B81" s="2">
-        <v>0.185221940279007</v>
+        <v>0.2524516880512238</v>
       </c>
       <c r="C81" s="1">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>112</v>
+        <v>234</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -4983,22 +5738,22 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B82" s="2">
-        <v>0.1819144040346146</v>
+        <v>0.2502939999103546</v>
       </c>
       <c r="C82" s="1">
-        <v>110</v>
+        <v>232</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -5009,19 +5764,19 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B83" s="2">
-        <v>0.1620691865682602</v>
+        <v>0.2459785789251328</v>
       </c>
       <c r="C83" s="1">
-        <v>98</v>
+        <v>228</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>98</v>
+        <v>228</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -5035,22 +5790,22 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B84" s="2">
-        <v>0.1620691865682602</v>
+        <v>0.2438208609819412</v>
       </c>
       <c r="C84" s="1">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="F84" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G84" s="1">
         <v>0</v>
@@ -5061,19 +5816,19 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B85" s="2">
-        <v>0.158761665225029</v>
+        <v>0.2395054548978806</v>
       </c>
       <c r="C85" s="1">
-        <v>96</v>
+        <v>222</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>96</v>
+        <v>222</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -5087,19 +5842,19 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B86" s="2">
-        <v>0.1389164477586746</v>
+        <v>0.2373477518558502</v>
       </c>
       <c r="C86" s="1">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -5113,19 +5868,19 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="B87" s="2">
-        <v>0.1389164477586746</v>
+        <v>0.2373477518558502</v>
       </c>
       <c r="C87" s="1">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="D87" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E87" s="1">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -5134,30 +5889,30 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="B88" s="2">
-        <v>0.1389164477586746</v>
+        <v>0.2373477518558502</v>
       </c>
       <c r="C88" s="1">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="D88" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>48</v>
+        <v>204</v>
       </c>
       <c r="F88" s="1">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G88" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -5165,19 +5920,19 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B89" s="2">
-        <v>0.1356089115142822</v>
+        <v>0.2200860977172852</v>
       </c>
       <c r="C89" s="1">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>82</v>
+        <v>204</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5191,19 +5946,19 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
       <c r="B90" s="2">
-        <v>0.1256863176822662</v>
+        <v>0.2071398496627808</v>
       </c>
       <c r="C90" s="1">
-        <v>76</v>
+        <v>192</v>
       </c>
       <c r="D90" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E90" s="1">
-        <v>76</v>
+        <v>192</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -5212,24 +5967,24 @@
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="B91" s="2">
-        <v>0.1256863176822662</v>
+        <v>0.2006667256355286</v>
       </c>
       <c r="C91" s="1">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="D91" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5238,30 +5993,30 @@
         <v>0</v>
       </c>
       <c r="H91" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="B92" s="2">
-        <v>0.1157637089490891</v>
+        <v>0.1898781955242157</v>
       </c>
       <c r="C92" s="1">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="D92" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="F92" s="1">
         <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -5269,19 +6024,19 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B93" s="2">
-        <v>0.09922603517770767</v>
+        <v>0.1898781955242157</v>
       </c>
       <c r="C93" s="1">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -5295,19 +6050,19 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B94" s="2">
-        <v>0.09922603517770767</v>
+        <v>0.1898781955242157</v>
       </c>
       <c r="C94" s="1">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -5321,25 +6076,25 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="B95" s="2">
-        <v>0.08930343389511108</v>
+        <v>0.185562789440155</v>
       </c>
       <c r="C95" s="1">
-        <v>54</v>
+        <v>172</v>
       </c>
       <c r="D95" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E95" s="1">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="F95" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G95" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -5347,19 +6102,19 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B96" s="2">
-        <v>0.08599589765071869</v>
+        <v>0.1726165413856506</v>
       </c>
       <c r="C96" s="1">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -5373,19 +6128,19 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B97" s="2">
-        <v>0.0793808326125145</v>
+        <v>0.1704588383436203</v>
       </c>
       <c r="C97" s="1">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -5399,19 +6154,19 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B98" s="2">
-        <v>0.0793808326125145</v>
+        <v>0.1661434173583984</v>
       </c>
       <c r="C98" s="1">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -5425,19 +6180,19 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B99" s="2">
-        <v>0.0793808326125145</v>
+        <v>0.1639857143163681</v>
       </c>
       <c r="C99" s="1">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>48</v>
+        <v>152</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -5451,19 +6206,19 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B100" s="2">
-        <v>0.07276576012372971</v>
+        <v>0.1553548872470856</v>
       </c>
       <c r="C100" s="1">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -5477,25 +6232,25 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="B101" s="2">
-        <v>0.07276576012372971</v>
+        <v>0.1531971842050552</v>
       </c>
       <c r="C101" s="1">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="D101" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>16</v>
+        <v>142</v>
       </c>
       <c r="F101" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -5503,19 +6258,19 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B102" s="2">
-        <v>0.06945822387933731</v>
+        <v>0.1488817632198334</v>
       </c>
       <c r="C102" s="1">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -5529,19 +6284,19 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="B103" s="2">
-        <v>0.06284315884113312</v>
+        <v>0.146724060177803</v>
       </c>
       <c r="C103" s="1">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="D103" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E103" s="1">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -5550,24 +6305,24 @@
         <v>0</v>
       </c>
       <c r="H103" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B104" s="2">
-        <v>0.06284315884113312</v>
+        <v>0.1424086540937424</v>
       </c>
       <c r="C104" s="1">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -5581,25 +6336,25 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>108</v>
+        <v>33</v>
       </c>
       <c r="B105" s="2">
-        <v>0.05953562259674072</v>
+        <v>0.1359355300664902</v>
       </c>
       <c r="C105" s="1">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="D105" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E105" s="1">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="F105" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G105" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -5607,19 +6362,19 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B106" s="2">
-        <v>0.05953562259674072</v>
+        <v>0.129462406039238</v>
       </c>
       <c r="C106" s="1">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -5633,19 +6388,19 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="B107" s="2">
-        <v>0.05953562259674072</v>
+        <v>0.129462406039238</v>
       </c>
       <c r="C107" s="1">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="D107" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E107" s="1">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -5654,24 +6409,24 @@
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B108" s="2">
-        <v>0.05953562259674072</v>
+        <v>0.1273047029972076</v>
       </c>
       <c r="C108" s="1">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -5685,19 +6440,19 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B109" s="2">
-        <v>0.05292055383324623</v>
+        <v>0.1251469999551773</v>
       </c>
       <c r="C109" s="1">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -5711,19 +6466,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B110" s="2">
-        <v>0.05292055383324623</v>
+        <v>0.1251469999551773</v>
       </c>
       <c r="C110" s="1">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -5737,19 +6492,19 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B111" s="2">
-        <v>0.05292055383324623</v>
+        <v>0.1208315789699554</v>
       </c>
       <c r="C111" s="1">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>32</v>
+        <v>112</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -5763,19 +6518,19 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B112" s="2">
-        <v>0.04961301758885384</v>
+        <v>0.1186738759279251</v>
       </c>
       <c r="C112" s="1">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -5789,25 +6544,25 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="B113" s="2">
-        <v>0.04961301758885384</v>
+        <v>0.1143584623932838</v>
       </c>
       <c r="C113" s="1">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="D113" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E113" s="1">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
       </c>
       <c r="G113" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -5815,19 +6570,19 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B114" s="2">
-        <v>0.04630548506975174</v>
+        <v>0.1057276353240013</v>
       </c>
       <c r="C114" s="1">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -5841,19 +6596,19 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B115" s="2">
-        <v>0.04630548506975174</v>
+        <v>0.1057276353240013</v>
       </c>
       <c r="C115" s="1">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -5867,19 +6622,19 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B116" s="2">
-        <v>0.03969041630625725</v>
+        <v>0.1057276353240013</v>
       </c>
       <c r="C116" s="1">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -5893,25 +6648,25 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="B117" s="2">
-        <v>0.02646027691662312</v>
+        <v>0.09925451129674912</v>
       </c>
       <c r="C117" s="1">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="D117" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E117" s="1">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -5919,25 +6674,25 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="B118" s="2">
-        <v>0.01323013845831156</v>
+        <v>0.09493909776210785</v>
       </c>
       <c r="C118" s="1">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="D118" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E118" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
       </c>
       <c r="G118" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -5945,19 +6700,19 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B119" s="2">
-        <v>0.01323013845831156</v>
+        <v>0.09493909776210785</v>
       </c>
       <c r="C119" s="1">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
       </c>
       <c r="E119" s="1">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -5971,19 +6726,19 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B120" s="2">
-        <v>0.01323013845831156</v>
+        <v>0.09278139472007752</v>
       </c>
       <c r="C120" s="1">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -5997,25 +6752,25 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>29</v>
+        <v>126</v>
       </c>
       <c r="B121" s="2">
-        <v>0.006615069229155779</v>
+        <v>0.09062368422746658</v>
       </c>
       <c r="C121" s="1">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="D121" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E121" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -6023,25 +6778,25 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="B122" s="2">
-        <v>0.006615069229155779</v>
+        <v>0.09062368422746658</v>
       </c>
       <c r="C122" s="1">
+        <v>84</v>
+      </c>
+      <c r="D122" s="1">
         <v>4</v>
       </c>
-      <c r="D122" s="1">
-        <v>0</v>
-      </c>
       <c r="E122" s="1">
+        <v>48</v>
+      </c>
+      <c r="F122" s="1">
+        <v>32</v>
+      </c>
+      <c r="G122" s="1">
         <v>4</v>
-      </c>
-      <c r="F122" s="1">
-        <v>0</v>
-      </c>
-      <c r="G122" s="1">
-        <v>0</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -6049,59 +6804,1047 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B123" s="2">
-        <v>0.006615069229155779</v>
+        <v>0.08846598118543625</v>
       </c>
       <c r="C123" s="1">
+        <v>82</v>
+      </c>
+      <c r="D123" s="1">
+        <v>0</v>
+      </c>
+      <c r="E123" s="1">
+        <v>82</v>
+      </c>
+      <c r="F123" s="1">
+        <v>0</v>
+      </c>
+      <c r="G123" s="1">
+        <v>0</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B124" s="2">
+        <v>0.08846598118543625</v>
+      </c>
+      <c r="C124" s="1">
+        <v>82</v>
+      </c>
+      <c r="D124" s="1">
+        <v>0</v>
+      </c>
+      <c r="E124" s="1">
+        <v>82</v>
+      </c>
+      <c r="F124" s="1">
+        <v>0</v>
+      </c>
+      <c r="G124" s="1">
+        <v>0</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B125" s="2">
+        <v>0.08199285715818405</v>
+      </c>
+      <c r="C125" s="1">
+        <v>76</v>
+      </c>
+      <c r="D125" s="1">
+        <v>0</v>
+      </c>
+      <c r="E125" s="1">
+        <v>76</v>
+      </c>
+      <c r="F125" s="1">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1">
+        <v>0</v>
+      </c>
+      <c r="H125" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B126" s="2">
+        <v>0.08199285715818405</v>
+      </c>
+      <c r="C126" s="1">
+        <v>76</v>
+      </c>
+      <c r="D126" s="1">
+        <v>40</v>
+      </c>
+      <c r="E126" s="1">
+        <v>76</v>
+      </c>
+      <c r="F126" s="1">
+        <v>0</v>
+      </c>
+      <c r="G126" s="1">
+        <v>0</v>
+      </c>
+      <c r="H126" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127" s="2">
+        <v>0.07120432704687119</v>
+      </c>
+      <c r="C127" s="1">
+        <v>66</v>
+      </c>
+      <c r="D127" s="1">
+        <v>0</v>
+      </c>
+      <c r="E127" s="1">
+        <v>66</v>
+      </c>
+      <c r="F127" s="1">
+        <v>0</v>
+      </c>
+      <c r="G127" s="1">
+        <v>0</v>
+      </c>
+      <c r="H127" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128" s="2">
+        <v>0.06473120301961899</v>
+      </c>
+      <c r="C128" s="1">
+        <v>60</v>
+      </c>
+      <c r="D128" s="1">
+        <v>0</v>
+      </c>
+      <c r="E128" s="1">
+        <v>60</v>
+      </c>
+      <c r="F128" s="1">
+        <v>0</v>
+      </c>
+      <c r="G128" s="1">
+        <v>0</v>
+      </c>
+      <c r="H128" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="2">
+        <v>0.06473120301961899</v>
+      </c>
+      <c r="C129" s="1">
+        <v>60</v>
+      </c>
+      <c r="D129" s="1">
+        <v>0</v>
+      </c>
+      <c r="E129" s="1">
+        <v>60</v>
+      </c>
+      <c r="F129" s="1">
+        <v>0</v>
+      </c>
+      <c r="G129" s="1">
+        <v>0</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130" s="2">
+        <v>0.06257349997758865</v>
+      </c>
+      <c r="C130" s="1">
+        <v>58</v>
+      </c>
+      <c r="D130" s="1">
+        <v>0</v>
+      </c>
+      <c r="E130" s="1">
+        <v>58</v>
+      </c>
+      <c r="F130" s="1">
+        <v>0</v>
+      </c>
+      <c r="G130" s="1">
+        <v>0</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131" s="2">
+        <v>0.05825808271765709</v>
+      </c>
+      <c r="C131" s="1">
+        <v>54</v>
+      </c>
+      <c r="D131" s="1">
+        <v>0</v>
+      </c>
+      <c r="E131" s="1">
+        <v>54</v>
+      </c>
+      <c r="F131" s="1">
+        <v>0</v>
+      </c>
+      <c r="G131" s="1">
+        <v>0</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B132" s="2">
+        <v>0.05825808271765709</v>
+      </c>
+      <c r="C132" s="1">
+        <v>54</v>
+      </c>
+      <c r="D132" s="1">
+        <v>8</v>
+      </c>
+      <c r="E132" s="1">
+        <v>34</v>
+      </c>
+      <c r="F132" s="1">
+        <v>12</v>
+      </c>
+      <c r="G132" s="1">
+        <v>8</v>
+      </c>
+      <c r="H132" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B133" s="2">
+        <v>0.05610037595033646</v>
+      </c>
+      <c r="C133" s="1">
+        <v>52</v>
+      </c>
+      <c r="D133" s="1">
+        <v>0</v>
+      </c>
+      <c r="E133" s="1">
+        <v>52</v>
+      </c>
+      <c r="F133" s="1">
+        <v>0</v>
+      </c>
+      <c r="G133" s="1">
+        <v>0</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B134" s="2">
+        <v>0.05178496241569519</v>
+      </c>
+      <c r="C134" s="1">
+        <v>48</v>
+      </c>
+      <c r="D134" s="1">
+        <v>0</v>
+      </c>
+      <c r="E134" s="1">
+        <v>48</v>
+      </c>
+      <c r="F134" s="1">
+        <v>0</v>
+      </c>
+      <c r="G134" s="1">
+        <v>0</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B135" s="2">
+        <v>0.05178496241569519</v>
+      </c>
+      <c r="C135" s="1">
+        <v>48</v>
+      </c>
+      <c r="D135" s="1">
+        <v>0</v>
+      </c>
+      <c r="E135" s="1">
+        <v>48</v>
+      </c>
+      <c r="F135" s="1">
+        <v>0</v>
+      </c>
+      <c r="G135" s="1">
+        <v>0</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B136" s="2">
+        <v>0.05178496241569519</v>
+      </c>
+      <c r="C136" s="1">
+        <v>48</v>
+      </c>
+      <c r="D136" s="1">
+        <v>0</v>
+      </c>
+      <c r="E136" s="1">
+        <v>48</v>
+      </c>
+      <c r="F136" s="1">
+        <v>0</v>
+      </c>
+      <c r="G136" s="1">
+        <v>0</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B137" s="2">
+        <v>0.04746954888105393</v>
+      </c>
+      <c r="C137" s="1">
+        <v>44</v>
+      </c>
+      <c r="D137" s="1">
+        <v>0</v>
+      </c>
+      <c r="E137" s="1">
+        <v>44</v>
+      </c>
+      <c r="F137" s="1">
+        <v>0</v>
+      </c>
+      <c r="G137" s="1">
+        <v>0</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B138" s="2">
+        <v>0.04746954888105393</v>
+      </c>
+      <c r="C138" s="1">
+        <v>44</v>
+      </c>
+      <c r="D138" s="1">
+        <v>0</v>
+      </c>
+      <c r="E138" s="1">
+        <v>44</v>
+      </c>
+      <c r="F138" s="1">
+        <v>0</v>
+      </c>
+      <c r="G138" s="1">
+        <v>0</v>
+      </c>
+      <c r="H138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B139" s="2">
+        <v>0.04746954888105393</v>
+      </c>
+      <c r="C139" s="1">
+        <v>44</v>
+      </c>
+      <c r="D139" s="1">
         <v>4</v>
       </c>
-      <c r="D123" s="1">
-        <v>0</v>
-      </c>
-      <c r="E123" s="1">
+      <c r="E139" s="1">
+        <v>16</v>
+      </c>
+      <c r="F139" s="1">
+        <v>24</v>
+      </c>
+      <c r="G139" s="1">
         <v>4</v>
       </c>
-      <c r="F123" s="1">
-        <v>0</v>
-      </c>
-      <c r="G123" s="1">
-        <v>0</v>
-      </c>
-      <c r="H123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" t="s">
-        <v>125</v>
-      </c>
-      <c r="B124">
+      <c r="H139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B140" s="2">
+        <v>0.04746954888105393</v>
+      </c>
+      <c r="C140" s="1">
+        <v>44</v>
+      </c>
+      <c r="D140" s="1">
+        <v>0</v>
+      </c>
+      <c r="E140" s="1">
+        <v>44</v>
+      </c>
+      <c r="F140" s="1">
+        <v>0</v>
+      </c>
+      <c r="G140" s="1">
+        <v>0</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B141" s="2">
+        <v>0.04746954888105393</v>
+      </c>
+      <c r="C141" s="1">
+        <v>44</v>
+      </c>
+      <c r="D141" s="1">
+        <v>0</v>
+      </c>
+      <c r="E141" s="1">
+        <v>44</v>
+      </c>
+      <c r="F141" s="1">
+        <v>0</v>
+      </c>
+      <c r="G141" s="1">
+        <v>0</v>
+      </c>
+      <c r="H141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B142" s="2">
+        <v>0.04099642857909203</v>
+      </c>
+      <c r="C142" s="1">
+        <v>38</v>
+      </c>
+      <c r="D142" s="1">
+        <v>0</v>
+      </c>
+      <c r="E142" s="1">
+        <v>38</v>
+      </c>
+      <c r="F142" s="1">
+        <v>0</v>
+      </c>
+      <c r="G142" s="1">
+        <v>0</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B143" s="2">
+        <v>0.03883872181177139</v>
+      </c>
+      <c r="C143" s="1">
+        <v>36</v>
+      </c>
+      <c r="D143" s="1">
+        <v>0</v>
+      </c>
+      <c r="E143" s="1">
+        <v>36</v>
+      </c>
+      <c r="F143" s="1">
+        <v>0</v>
+      </c>
+      <c r="G143" s="1">
+        <v>0</v>
+      </c>
+      <c r="H143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B144" s="2">
+        <v>0.03883872181177139</v>
+      </c>
+      <c r="C144" s="1">
+        <v>36</v>
+      </c>
+      <c r="D144" s="1">
+        <v>0</v>
+      </c>
+      <c r="E144" s="1">
+        <v>36</v>
+      </c>
+      <c r="F144" s="1">
+        <v>0</v>
+      </c>
+      <c r="G144" s="1">
+        <v>0</v>
+      </c>
+      <c r="H144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B145" s="2">
+        <v>0.03883872181177139</v>
+      </c>
+      <c r="C145" s="1">
+        <v>36</v>
+      </c>
+      <c r="D145" s="1">
+        <v>0</v>
+      </c>
+      <c r="E145" s="1">
+        <v>36</v>
+      </c>
+      <c r="F145" s="1">
+        <v>0</v>
+      </c>
+      <c r="G145" s="1">
+        <v>0</v>
+      </c>
+      <c r="H145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B146" s="2">
+        <v>0.03883872181177139</v>
+      </c>
+      <c r="C146" s="1">
+        <v>36</v>
+      </c>
+      <c r="D146" s="1">
+        <v>0</v>
+      </c>
+      <c r="E146" s="1">
+        <v>36</v>
+      </c>
+      <c r="F146" s="1">
+        <v>0</v>
+      </c>
+      <c r="G146" s="1">
+        <v>0</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B147" s="2">
+        <v>0.03883872181177139</v>
+      </c>
+      <c r="C147" s="1">
+        <v>36</v>
+      </c>
+      <c r="D147" s="1">
+        <v>0</v>
+      </c>
+      <c r="E147" s="1">
+        <v>36</v>
+      </c>
+      <c r="F147" s="1">
+        <v>0</v>
+      </c>
+      <c r="G147" s="1">
+        <v>0</v>
+      </c>
+      <c r="H147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" s="2">
+        <v>0.03452330827713013</v>
+      </c>
+      <c r="C148" s="1">
+        <v>32</v>
+      </c>
+      <c r="D148" s="1">
+        <v>0</v>
+      </c>
+      <c r="E148" s="1">
+        <v>32</v>
+      </c>
+      <c r="F148" s="1">
+        <v>0</v>
+      </c>
+      <c r="G148" s="1">
+        <v>0</v>
+      </c>
+      <c r="H148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B149" s="2">
+        <v>0.03452330827713013</v>
+      </c>
+      <c r="C149" s="1">
+        <v>32</v>
+      </c>
+      <c r="D149" s="1">
+        <v>0</v>
+      </c>
+      <c r="E149" s="1">
+        <v>32</v>
+      </c>
+      <c r="F149" s="1">
+        <v>0</v>
+      </c>
+      <c r="G149" s="1">
+        <v>0</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B150" s="2">
+        <v>0.03452330827713013</v>
+      </c>
+      <c r="C150" s="1">
+        <v>32</v>
+      </c>
+      <c r="D150" s="1">
+        <v>0</v>
+      </c>
+      <c r="E150" s="1">
+        <v>32</v>
+      </c>
+      <c r="F150" s="1">
+        <v>0</v>
+      </c>
+      <c r="G150" s="1">
+        <v>0</v>
+      </c>
+      <c r="H150" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B151" s="2">
+        <v>0.03452330827713013</v>
+      </c>
+      <c r="C151" s="1">
+        <v>32</v>
+      </c>
+      <c r="D151" s="1">
+        <v>0</v>
+      </c>
+      <c r="E151" s="1">
+        <v>32</v>
+      </c>
+      <c r="F151" s="1">
+        <v>0</v>
+      </c>
+      <c r="G151" s="1">
+        <v>0</v>
+      </c>
+      <c r="H151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B152" s="2">
+        <v>0.03452330827713013</v>
+      </c>
+      <c r="C152" s="1">
+        <v>32</v>
+      </c>
+      <c r="D152" s="1">
+        <v>0</v>
+      </c>
+      <c r="E152" s="1">
+        <v>32</v>
+      </c>
+      <c r="F152" s="1">
+        <v>0</v>
+      </c>
+      <c r="G152" s="1">
+        <v>0</v>
+      </c>
+      <c r="H152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B153" s="2">
+        <v>0.03236560150980949</v>
+      </c>
+      <c r="C153" s="1">
+        <v>30</v>
+      </c>
+      <c r="D153" s="1">
+        <v>0</v>
+      </c>
+      <c r="E153" s="1">
+        <v>30</v>
+      </c>
+      <c r="F153" s="1">
+        <v>0</v>
+      </c>
+      <c r="G153" s="1">
+        <v>0</v>
+      </c>
+      <c r="H153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B154" s="2">
+        <v>0.03236560150980949</v>
+      </c>
+      <c r="C154" s="1">
+        <v>30</v>
+      </c>
+      <c r="D154" s="1">
+        <v>0</v>
+      </c>
+      <c r="E154" s="1">
+        <v>30</v>
+      </c>
+      <c r="F154" s="1">
+        <v>0</v>
+      </c>
+      <c r="G154" s="1">
+        <v>0</v>
+      </c>
+      <c r="H154" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" s="2">
+        <v>0.0258924812078476</v>
+      </c>
+      <c r="C155" s="1">
+        <v>24</v>
+      </c>
+      <c r="D155" s="1">
+        <v>0</v>
+      </c>
+      <c r="E155" s="1">
+        <v>24</v>
+      </c>
+      <c r="F155" s="1">
+        <v>0</v>
+      </c>
+      <c r="G155" s="1">
+        <v>0</v>
+      </c>
+      <c r="H155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B156" s="2">
+        <v>0.01726165413856506</v>
+      </c>
+      <c r="C156" s="1">
+        <v>16</v>
+      </c>
+      <c r="D156" s="1">
+        <v>4</v>
+      </c>
+      <c r="E156" s="1">
+        <v>12</v>
+      </c>
+      <c r="F156" s="1">
+        <v>0</v>
+      </c>
+      <c r="G156" s="1">
+        <v>4</v>
+      </c>
+      <c r="H156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" s="2">
+        <v>0.008630827069282532</v>
+      </c>
+      <c r="C157" s="1">
+        <v>8</v>
+      </c>
+      <c r="D157" s="1">
+        <v>0</v>
+      </c>
+      <c r="E157" s="1">
+        <v>8</v>
+      </c>
+      <c r="F157" s="1">
+        <v>0</v>
+      </c>
+      <c r="G157" s="1">
+        <v>0</v>
+      </c>
+      <c r="H157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B158" s="2">
+        <v>0.008630827069282532</v>
+      </c>
+      <c r="C158" s="1">
+        <v>8</v>
+      </c>
+      <c r="D158" s="1">
+        <v>0</v>
+      </c>
+      <c r="E158" s="1">
+        <v>8</v>
+      </c>
+      <c r="F158" s="1">
+        <v>0</v>
+      </c>
+      <c r="G158" s="1">
+        <v>0</v>
+      </c>
+      <c r="H158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B159" s="2">
+        <v>0.004315413534641266</v>
+      </c>
+      <c r="C159" s="1">
+        <v>4</v>
+      </c>
+      <c r="D159" s="1">
+        <v>4</v>
+      </c>
+      <c r="E159" s="1">
+        <v>0</v>
+      </c>
+      <c r="F159" s="1">
+        <v>0</v>
+      </c>
+      <c r="G159" s="1">
+        <v>4</v>
+      </c>
+      <c r="H159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2">
+        <v>0.004315413534641266</v>
+      </c>
+      <c r="C160" s="1">
+        <v>4</v>
+      </c>
+      <c r="D160" s="1">
+        <v>0</v>
+      </c>
+      <c r="E160" s="1">
+        <v>4</v>
+      </c>
+      <c r="F160" s="1">
+        <v>0</v>
+      </c>
+      <c r="G160" s="1">
+        <v>0</v>
+      </c>
+      <c r="H160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2">
+        <v>0.004315413534641266</v>
+      </c>
+      <c r="C161" s="1">
+        <v>4</v>
+      </c>
+      <c r="D161" s="1">
+        <v>0</v>
+      </c>
+      <c r="E161" s="1">
+        <v>4</v>
+      </c>
+      <c r="F161" s="1">
+        <v>0</v>
+      </c>
+      <c r="G161" s="1">
+        <v>0</v>
+      </c>
+      <c r="H161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+      <c r="B162">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C124">
+      <c r="C162">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D124">
+      <c r="D162">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E124">
+      <c r="E162">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F124">
+      <c r="F162">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G124">
+      <c r="G162">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H124">
+      <c r="H162">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="178">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -23,6 +23,15 @@
     <t>heap_4.o</t>
   </si>
   <si>
+    <t>drv_flash_g4.o</t>
+  </si>
+  <si>
+    <t>dev_flash.o</t>
+  </si>
+  <si>
+    <t>motor_info_storage.o</t>
+  </si>
+  <si>
     <t>drv_usart.o</t>
   </si>
   <si>
@@ -101,6 +110,9 @@
     <t>calib_level3_encoder.o</t>
   </si>
   <si>
+    <t>stm32g4xx_hal_flash.o</t>
+  </si>
+  <si>
     <t>dev_motor.o</t>
   </si>
   <si>
@@ -158,6 +170,9 @@
     <t>led_manager.o</t>
   </si>
   <si>
+    <t>motor_info.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_adc.o</t>
   </si>
   <si>
@@ -227,6 +242,9 @@
     <t>stm32g4xx_hal_rcc_ex.o</t>
   </si>
   <si>
+    <t>dev_mt6835.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_tim_ex.o</t>
   </si>
   <si>
@@ -236,15 +254,15 @@
     <t>atan2f.o</t>
   </si>
   <si>
-    <t>dev_mt6835.o</t>
-  </si>
-  <si>
     <t>cascade_control.o</t>
   </si>
   <si>
     <t>dev_half_bridge.o</t>
   </si>
   <si>
+    <t>motor_profile.o</t>
+  </si>
+  <si>
     <t>motor_pid_autotune.o</t>
   </si>
   <si>
@@ -260,6 +278,9 @@
     <t>calib_ac_injection.o</t>
   </si>
   <si>
+    <t>stm32g4xx_hal_flash_ex.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_gpio.o</t>
   </si>
   <si>
@@ -272,6 +293,9 @@
     <t>sinf.o</t>
   </si>
   <si>
+    <t>motor_info_calib.o</t>
+  </si>
+  <si>
     <t>rredf.o</t>
   </si>
   <si>
@@ -332,9 +356,6 @@
     <t>stm32g4xx_hal_i2c_ex.o</t>
   </si>
   <si>
-    <t>motor_profile.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_cortex.o</t>
   </si>
   <si>
@@ -374,15 +395,15 @@
     <t>fepilogue.o</t>
   </si>
   <si>
+    <t>user_interface.o</t>
+  </si>
+  <si>
     <t>uldiv.o</t>
   </si>
   <si>
     <t>ldiv.o</t>
   </si>
   <si>
-    <t>user_interface.o</t>
-  </si>
-  <si>
     <t>motor_mode_test_sweep.o</t>
   </si>
   <si>
@@ -422,6 +443,9 @@
     <t>stm32g4xx_hal_cordic.o</t>
   </si>
   <si>
+    <t>utils.o</t>
+  </si>
+  <si>
     <t>control_irq.o</t>
   </si>
   <si>
@@ -474,9 +498,6 @@
   </si>
   <si>
     <t>thread_control.o</t>
-  </si>
-  <si>
-    <t>motor_info_calib.o</t>
   </si>
   <si>
     <t>llshl.o</t>
@@ -617,148 +638,160 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$162</c:f>
+              <c:f>ram_percent!$A$3:$A$169</c:f>
               <c:strCache>
-                <c:ptCount val="160"/>
+                <c:ptCount val="167"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>drv_flash_g4.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>dev_flash.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>motor_info_storage.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>motor_pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>dev_power_monitor.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="14">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="18">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="19">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="20">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="21">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="22">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="24">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>calib_level3_encoder.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="30">
+                  <c:v>stm32g4xx_hal_flash.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="32">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="33">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="34">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="35">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="37">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="38">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="39">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="40">
                   <c:v>jm_proto_ops.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="41">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="42">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="43">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="44">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="45">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="46">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="47">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="48">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="49">
                   <c:v>led_manager.o</c:v>
                 </c:pt>
-                <c:pt idx="159">
+                <c:pt idx="166">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -766,149 +799,161 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$162</c:f>
+              <c:f>ram_percent!$B$3:$B$169</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="160"/>
+                <c:ptCount val="167"/>
                 <c:pt idx="0">
-                  <c:v>59.36426544189453</c:v>
+                  <c:v>43.23527145385742</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.391602993011475</c:v>
+                  <c:v>10.78774833679199</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.046360015869141</c:v>
+                  <c:v>10.78774833679199</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.94510555267334</c:v>
+                  <c:v>5.509757995605469</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.728347778320313</c:v>
+                  <c:v>5.383338928222656</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.703033924102783</c:v>
+                  <c:v>4.403592586517334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.58923077583313</c:v>
+                  <c:v>4.329847812652588</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.287382960319519</c:v>
+                  <c:v>2.715373039245606</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.229523062705994</c:v>
+                  <c:v>2.696937084197998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.084873199462891</c:v>
+                  <c:v>1.885748863220215</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9546884894371033</c:v>
+                  <c:v>0.9376069903373718</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8245036602020264</c:v>
+                  <c:v>0.8954673409461975</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.810038685798645</c:v>
+                  <c:v>0.7901182770729065</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.7232488393783569</c:v>
+                  <c:v>0.6953040361404419</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.4773442447185516</c:v>
+                  <c:v>0.6004898548126221</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.4628792405128479</c:v>
+                  <c:v>0.5899549722671509</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3905543684959412</c:v>
+                  <c:v>0.5267454981803894</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.3616244196891785</c:v>
+                  <c:v>0.347652018070221</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.3037645220756531</c:v>
+                  <c:v>0.3371171355247498</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.274834543466568</c:v>
+                  <c:v>0.2844425737857819</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2603695690631867</c:v>
+                  <c:v>0.2633727490901947</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2603695690631867</c:v>
+                  <c:v>0.2212331146001816</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2603695690631867</c:v>
+                  <c:v>0.2001632899045944</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.231439620256424</c:v>
+                  <c:v>0.1896283775568008</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1591147482395172</c:v>
+                  <c:v>0.1896283775568008</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1446497738361359</c:v>
+                  <c:v>0.1896283775568008</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1301847845315933</c:v>
+                  <c:v>0.1685585677623749</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.08317361772060394</c:v>
+                  <c:v>0.1158840134739876</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.07232488691806793</c:v>
+                  <c:v>0.105349101126194</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.07232488691806793</c:v>
+                  <c:v>0.09481418877840042</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.04339493066072464</c:v>
+                  <c:v>0.08427928388118744</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.04339493066072464</c:v>
+                  <c:v>0.06057573109865189</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.04339493066072464</c:v>
+                  <c:v>0.052674550563097</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.04339493066072464</c:v>
+                  <c:v>0.052674550563097</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.02892995253205299</c:v>
+                  <c:v>0.03160472959280014</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.02892995253205299</c:v>
+                  <c:v>0.03160472959280014</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.02169746533036232</c:v>
+                  <c:v>0.03160472959280014</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.0144649762660265</c:v>
+                  <c:v>0.03160472959280014</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.0144649762660265</c:v>
+                  <c:v>0.02106982097029686</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.0144649762660265</c:v>
+                  <c:v>0.02106982097029686</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.0144649762660265</c:v>
+                  <c:v>0.01580236479640007</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.0144649762660265</c:v>
+                  <c:v>0.01053491048514843</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.0144649762660265</c:v>
+                  <c:v>0.01053491048514843</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.0144649762660265</c:v>
+                  <c:v>0.01053491048514843</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01084873266518116</c:v>
+                  <c:v>0.01053491048514843</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.007232488133013248</c:v>
-                </c:pt>
-                <c:pt idx="159">
+                  <c:v>0.01053491048514843</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.01053491048514843</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.01053491048514843</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.007901182398200035</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.005267455242574215</c:v>
+                </c:pt>
+                <c:pt idx="166">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -976,487 +1021,508 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$162</c:f>
+              <c:f>flash_percent!$A$3:$A$169</c:f>
               <c:strCache>
-                <c:ptCount val="160"/>
+                <c:ptCount val="167"/>
                 <c:pt idx="0">
+                  <c:v>motor_info.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>stm32g4xx_hal_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>stm32g4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>jm_proto.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>stm32g4xx_hal_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>motor_param.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
+                  <c:v>jm_proto_ops.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>stm32g4xx_hal_adc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>arm_cortexM4lf_math.lib</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="12">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>jm_proto_ops.o</c:v>
-                </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>printfa.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>arm_common_tables.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>motion_param.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>dev_power_monitor.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>stm32g4xx_hal_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>dev_motor_phase_current.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>ctrl_transition.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>motor_pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>calib_config_runtime.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>calib_level3_encoder.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>stm32g4xx_hal_fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
+                  <c:v>drv_flash_g4.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
+                  <c:v>motor_pid_load.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>multiturn_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="36">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="37">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="38">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
-                  <c:v>motor_pid_load.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="39">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="40">
+                  <c:v>dev_mt6835.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="42">
                   <c:v>foc_decoupling.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="43">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="44">
                   <c:v>atan2f.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
-                  <c:v>dev_mt6835.o</c:v>
-                </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>cascade_control.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="46">
                   <c:v>dev_half_bridge.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="47">
+                  <c:v>motor_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
                   <c:v>motor_pid_autotune.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="49">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="50">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="51">
                   <c:v>crc16.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="52">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="53">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="54">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="55">
+                  <c:v>motor_info_storage.o</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>calib_ac_injection.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="57">
+                  <c:v>dev_flash.o</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="59">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="60">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="61">
+                  <c:v>stm32g4xx_hal_flash_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="63">
+                  <c:v>stm32g4xx_hal_flash.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>ctrl_transition_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="65">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="66">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="67">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="68">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="69">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="70">
+                  <c:v>motor_info_calib.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="72">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="73">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="74">
                   <c:v>cosf.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="75">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="76">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="77">
                   <c:v>led_manager.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="78">
                   <c:v>cmsis_os.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="79">
                   <c:v>dev_config.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="80">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="81">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="82">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="83">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="84">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="85">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="86">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="87">
                   <c:v>drv_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="88">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="89">
                   <c:v>drv_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="90">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="91">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="92">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="93">
                   <c:v>drv_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="94">
                   <c:v>stm32g4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="95">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="96">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="97">
                   <c:v>fmodf.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="98">
                   <c:v>stm32g4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="99">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="100">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
-                  <c:v>motor_profile.o</c:v>
-                </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="101">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="102">
                   <c:v>roundf.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="103">
                   <c:v>arm_cos_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="104">
                   <c:v>arm_sin_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="105">
                   <c:v>motor_mode_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="106">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="107">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="108">
                   <c:v>motor_mode_mit.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="109">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="110">
                   <c:v>thread_period.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="111">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="112">
                   <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="113">
                   <c:v>motor_mode_position.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="114">
                   <c:v>motor_mode_current.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="115">
                   <c:v>floorf.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="116">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="117">
+                  <c:v>user_interface.o</c:v>
+                </c:pt>
+                <c:pt idx="118">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="119">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="120">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
-                  <c:v>user_interface.o</c:v>
-                </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="121">
                   <c:v>motor_mode_test_sweep.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="122">
                   <c:v>motor_mode_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="123">
                   <c:v>motor_mode_profile_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="124">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="125">
                   <c:v>assert_report.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="126">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="127">
                   <c:v>frem.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="128">
                   <c:v>motor_mode_profile_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="129">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="130">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="131">
                   <c:v>motor_mode_duty.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="132">
                   <c:v>frnd.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="133">
                   <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="134">
                   <c:v>sqrtf.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="135">
                   <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="136">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="137">
+                  <c:v>utils.o</c:v>
+                </c:pt>
+                <c:pt idx="138">
                   <c:v>control_irq.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="139">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="140">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="141">
                   <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="142">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="143">
                   <c:v>funder.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="144">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="145">
                   <c:v>motor_mode_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="146">
                   <c:v>motor_mode_hold.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="147">
                   <c:v>fpclassifyf.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="148">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="149">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="150">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="151">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="152">
                   <c:v>thread_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="153">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="146">
+                <c:pt idx="154">
                   <c:v>thread_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="155">
                   <c:v>thread_display.o</c:v>
                 </c:pt>
-                <c:pt idx="148">
+                <c:pt idx="156">
                   <c:v>thread_control.o</c:v>
                 </c:pt>
-                <c:pt idx="149">
-                  <c:v>motor_info_calib.o</c:v>
-                </c:pt>
-                <c:pt idx="150">
+                <c:pt idx="157">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="151">
+                <c:pt idx="158">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="152">
+                <c:pt idx="159">
                   <c:v>strncpy.o</c:v>
                 </c:pt>
-                <c:pt idx="153">
+                <c:pt idx="160">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="154">
+                <c:pt idx="161">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="155">
+                <c:pt idx="162">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="156">
+                <c:pt idx="163">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="157">
+                <c:pt idx="164">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="158">
+                <c:pt idx="165">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="159">
+                <c:pt idx="166">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1464,488 +1530,509 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$162</c:f>
+              <c:f>flash_percent!$B$3:$B$169</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="160"/>
+                <c:ptCount val="167"/>
                 <c:pt idx="0">
-                  <c:v>4.649857997894287</c:v>
+                  <c:v>10.80426692962647</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.646524429321289</c:v>
+                  <c:v>3.953004121780396</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.575320243835449</c:v>
+                  <c:v>3.100035667419434</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.510588884353638</c:v>
+                  <c:v>3.039502620697022</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.441542387008667</c:v>
+                  <c:v>2.984472274780273</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.0876784324646</c:v>
+                  <c:v>2.92577338218689</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.072574377059937</c:v>
+                  <c:v>2.62494158744812</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.561197996139526</c:v>
+                  <c:v>2.612101078033447</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.537463188171387</c:v>
+                  <c:v>2.575414419174194</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.533147811889648</c:v>
+                  <c:v>2.177362442016602</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.52883243560791</c:v>
+                  <c:v>2.157184600830078</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.446839570999146</c:v>
+                  <c:v>2.153516054153442</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.392896890640259</c:v>
+                  <c:v>2.149847269058228</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.213807106018066</c:v>
+                  <c:v>2.034283876419067</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.049821376800537</c:v>
+                  <c:v>1.882033586502075</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.948409199714661</c:v>
+                  <c:v>1.742623686790466</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.734796285629273</c:v>
+                  <c:v>1.656409621238709</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.622595548629761</c:v>
+                  <c:v>1.474809885025024</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.503921627998352</c:v>
+                  <c:v>1.379424214363098</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.421928763389587</c:v>
+                  <c:v>1.278535485267639</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.374459266662598</c:v>
+                  <c:v>1.20883047580719</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.316201090812683</c:v>
+                  <c:v>1.168475031852722</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.294624090194702</c:v>
+                  <c:v>1.118947863578796</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.251469969749451</c:v>
+                  <c:v>1.10060441493988</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.171634793281555</c:v>
+                  <c:v>1.089598417282105</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.165161609649658</c:v>
+                  <c:v>0.9960470199584961</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.143584609031677</c:v>
+                  <c:v>0.9905439615249634</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.109061241149902</c:v>
+                  <c:v>0.9722005724906921</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.085326552391052</c:v>
+                  <c:v>0.9428511261940002</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.063749432563782</c:v>
+                  <c:v>0.9226733446121216</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.055118560791016</c:v>
+                  <c:v>0.9043299555778503</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.031383872032166</c:v>
+                  <c:v>0.8969926238059998</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.8976060152053833</c:v>
+                  <c:v>0.8804835081100464</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.8846597671508789</c:v>
+                  <c:v>0.8768148422241211</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.860925018787384</c:v>
+                  <c:v>0.8025240302085877</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8458210825920105</c:v>
+                  <c:v>0.7630857229232788</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8317959904670715</c:v>
+                  <c:v>0.7520796656608582</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8156131505966187</c:v>
+                  <c:v>0.7319019436836243</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.7767744660377502</c:v>
+                  <c:v>0.719061553478241</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7703013420104981</c:v>
+                  <c:v>0.6933807730674744</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.7487242817878723</c:v>
+                  <c:v>0.6860434412956238</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7379357218742371</c:v>
+                  <c:v>0.6603626608848572</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7293049097061157</c:v>
+                  <c:v>0.6548596024513245</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7185163497924805</c:v>
+                  <c:v>0.6365162134170532</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.6947816014289856</c:v>
+                  <c:v>0.6273444890975952</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.6839930415153503</c:v>
+                  <c:v>0.6108354330062866</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6688891053199768</c:v>
+                  <c:v>0.5906577110290527</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6343657970428467</c:v>
+                  <c:v>0.5888233780860901</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.5998424887657166</c:v>
+                  <c:v>0.5814859867095947</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.5782654285430908</c:v>
+                  <c:v>0.5686455965042114</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.552372932434082</c:v>
+                  <c:v>0.5392961502075195</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.548057496547699</c:v>
+                  <c:v>0.5099467039108276</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5437421202659607</c:v>
+                  <c:v>0.4916033148765564</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5415844321250916</c:v>
+                  <c:v>0.4695912301540375</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5372689962387085</c:v>
+                  <c:v>0.4659225344657898</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.5307958722114563</c:v>
+                  <c:v>0.4659225344657898</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.5049033761024475</c:v>
+                  <c:v>0.4622538685798645</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4811686277389526</c:v>
+                  <c:v>0.4604195058345795</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4693012237548828</c:v>
+                  <c:v>0.4604195058345795</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4423298835754395</c:v>
+                  <c:v>0.4567508399486542</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4401721954345703</c:v>
+                  <c:v>0.4512478113174439</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4315413534641266</c:v>
+                  <c:v>0.4365730881690979</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4315413534641266</c:v>
+                  <c:v>0.4292357265949249</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4013334512710571</c:v>
+                  <c:v>0.4182296693325043</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.3948603570461273</c:v>
+                  <c:v>0.4090579748153687</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.3711255788803101</c:v>
+                  <c:v>0.3989691138267517</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.3624947369098663</c:v>
+                  <c:v>0.3760398328304291</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3603370189666748</c:v>
+                  <c:v>0.3742054998874664</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3581793308258057</c:v>
+                  <c:v>0.3668681383132935</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.353863924741745</c:v>
+                  <c:v>0.3668681383132935</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3495484888553619</c:v>
+                  <c:v>0.3650338053703308</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3441542387008667</c:v>
+                  <c:v>0.3411873579025269</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3322868347167969</c:v>
+                  <c:v>0.3356843590736389</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3085520565509796</c:v>
+                  <c:v>0.3155066072940826</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.2934481203556061</c:v>
+                  <c:v>0.3081692457199097</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.2934481203556061</c:v>
+                  <c:v>0.3063348829746246</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.2718710601329804</c:v>
+                  <c:v>0.304500550031662</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.2610825300216675</c:v>
+                  <c:v>0.304500550031662</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.2524516880512238</c:v>
+                  <c:v>0.297163188457489</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.2502939999103546</c:v>
+                  <c:v>0.29257732629776</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.2459785789251328</c:v>
+                  <c:v>0.2824884653091431</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.2438208609819412</c:v>
+                  <c:v>0.2641450464725494</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.2395054548978806</c:v>
+                  <c:v>0.2494703382253647</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2373477518558502</c:v>
+                  <c:v>0.2494703382253647</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2373477518558502</c:v>
+                  <c:v>0.2311269342899323</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2373477518558502</c:v>
+                  <c:v>0.2219552248716354</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2200860977172852</c:v>
+                  <c:v>0.2146178632974625</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2071398496627808</c:v>
+                  <c:v>0.2127835154533386</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2006667256355286</c:v>
+                  <c:v>0.2091148346662521</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.1898781955242157</c:v>
+                  <c:v>0.2072805017232895</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.1898781955242157</c:v>
+                  <c:v>0.203611820936203</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.1898781955242157</c:v>
+                  <c:v>0.2017774730920792</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.185562789440155</c:v>
+                  <c:v>0.2017774730920792</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.1726165413856506</c:v>
+                  <c:v>0.2017774730920792</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1704588383436203</c:v>
+                  <c:v>0.1871027499437332</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1661434173583984</c:v>
+                  <c:v>0.1760967075824738</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1639857143163681</c:v>
+                  <c:v>0.1705936789512634</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1553548872470856</c:v>
+                  <c:v>0.1614219844341278</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1531971842050552</c:v>
+                  <c:v>0.1614219844341278</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1488817632198334</c:v>
+                  <c:v>0.1614219844341278</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.146724060177803</c:v>
+                  <c:v>0.1577533036470413</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1424086540937424</c:v>
+                  <c:v>0.144912913441658</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1359355300664902</c:v>
+                  <c:v>0.1412442326545715</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.129462406039238</c:v>
+                  <c:v>0.1394098997116089</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.129462406039238</c:v>
+                  <c:v>0.1320725232362747</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1273047029972076</c:v>
+                  <c:v>0.1302381902933121</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1251469999551773</c:v>
+                  <c:v>0.1265695095062256</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1251469999551773</c:v>
+                  <c:v>0.1247351691126823</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1208315789699554</c:v>
+                  <c:v>0.1210664883255959</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1186738759279251</c:v>
+                  <c:v>0.1155634671449661</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1143584623932838</c:v>
+                  <c:v>0.1100604385137558</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1057276353240013</c:v>
+                  <c:v>0.1100604385137558</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1057276353240013</c:v>
+                  <c:v>0.1082260981202126</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1057276353240013</c:v>
+                  <c:v>0.1063917577266693</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.09925451129674912</c:v>
+                  <c:v>0.1063917577266693</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.09493909776210785</c:v>
+                  <c:v>0.1027230769395828</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.09493909776210785</c:v>
+                  <c:v>0.1008887365460396</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.09278139472007752</c:v>
+                  <c:v>0.09722005575895309</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.09062368422746658</c:v>
+                  <c:v>0.09722005575895309</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.09062368422746658</c:v>
+                  <c:v>0.08988269418478012</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.08846598118543625</c:v>
+                  <c:v>0.08988269418478012</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.08846598118543625</c:v>
+                  <c:v>0.08437967300415039</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.08199285715818405</c:v>
+                  <c:v>0.0807109922170639</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.08199285715818405</c:v>
+                  <c:v>0.0807109922170639</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.07120432704687119</c:v>
+                  <c:v>0.07887665182352066</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.06473120301961899</c:v>
+                  <c:v>0.07704231142997742</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.06473120301961899</c:v>
+                  <c:v>0.07704231142997742</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.06257349997758865</c:v>
+                  <c:v>0.07520797103643417</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.05825808271765709</c:v>
+                  <c:v>0.07520797103643417</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.05825808271765709</c:v>
+                  <c:v>0.06970494985580444</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.05610037595033646</c:v>
+                  <c:v>0.06970494985580444</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.05178496241569519</c:v>
+                  <c:v>0.06053324416279793</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.05178496241569519</c:v>
+                  <c:v>0.0550302192568779</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.05178496241569519</c:v>
+                  <c:v>0.0550302192568779</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.04746954888105393</c:v>
+                  <c:v>0.05319587886333466</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.04746954888105393</c:v>
+                  <c:v>0.04952719807624817</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.04746954888105393</c:v>
+                  <c:v>0.04952719807624817</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.04746954888105393</c:v>
+                  <c:v>0.04769285768270493</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.04746954888105393</c:v>
+                  <c:v>0.04769285768270493</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.04099642857909203</c:v>
+                  <c:v>0.04402417689561844</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.03883872181177139</c:v>
+                  <c:v>0.04402417689561844</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.03883872181177139</c:v>
+                  <c:v>0.04402417689561844</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.03883872181177139</c:v>
+                  <c:v>0.04035549610853195</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.03883872181177139</c:v>
+                  <c:v>0.04035549610853195</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.03883872181177139</c:v>
+                  <c:v>0.04035549610853195</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.03452330827713013</c:v>
+                  <c:v>0.04035549610853195</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.03452330827713013</c:v>
+                  <c:v>0.04035549610853195</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.03452330827713013</c:v>
+                  <c:v>0.03485247492790222</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.03452330827713013</c:v>
+                  <c:v>0.03301813080906868</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.03452330827713013</c:v>
+                  <c:v>0.03301813080906868</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03236560150980949</c:v>
+                  <c:v>0.03301813080906868</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03236560150980949</c:v>
+                  <c:v>0.03301813080906868</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.0258924812078476</c:v>
+                  <c:v>0.03301813080906868</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.01726165413856506</c:v>
+                  <c:v>0.02934945188462734</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.008630827069282532</c:v>
+                  <c:v>0.02934945188462734</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.008630827069282532</c:v>
+                  <c:v>0.02934945188462734</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.004315413534641266</c:v>
+                  <c:v>0.02934945188462734</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.004315413534641266</c:v>
+                  <c:v>0.02751510962843895</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.004315413534641266</c:v>
+                  <c:v>0.02751510962843895</c:v>
                 </c:pt>
                 <c:pt idx="159">
+                  <c:v>0.02201208844780922</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.01467472594231367</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.007337362971156836</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.007337362971156836</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.003668681485578418</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.003668681485578418</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.003668681485578418</c:v>
+                </c:pt>
+                <c:pt idx="166">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2050,8 +2137,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H162" totalsRowCount="1">
-  <autoFilter ref="A2:H161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H169" totalsRowCount="1">
+  <autoFilter ref="A2:H168"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -2067,8 +2154,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H162" totalsRowCount="1">
-  <autoFilter ref="A2:H161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H169" totalsRowCount="1">
+  <autoFilter ref="A2:H168"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2368,7 +2455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2381,28 +2468,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2410,7 +2497,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>59.36426544189453</v>
+        <v>43.23527145385742</v>
       </c>
       <c r="C3" s="1">
         <v>16416</v>
@@ -2436,25 +2523,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>7.391602993011475</v>
+        <v>10.78774833679199</v>
       </c>
       <c r="C4" s="1">
-        <v>2044</v>
+        <v>4096</v>
       </c>
       <c r="D4" s="1">
-        <v>620</v>
+        <v>960</v>
       </c>
       <c r="E4" s="1">
-        <v>564</v>
+        <v>960</v>
       </c>
       <c r="F4" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>2044</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2462,16 +2549,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>6.046360015869141</v>
+        <v>10.78774833679199</v>
       </c>
       <c r="C5" s="1">
-        <v>1672</v>
+        <v>4096</v>
       </c>
       <c r="D5" s="1">
-        <v>1160</v>
+        <v>502</v>
       </c>
       <c r="E5" s="1">
-        <v>1160</v>
+        <v>502</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2480,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>1672</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2488,25 +2575,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>5.94510555267334</v>
+        <v>5.509757995605469</v>
       </c>
       <c r="C6" s="1">
-        <v>1644</v>
+        <v>2092</v>
       </c>
       <c r="D6" s="1">
-        <v>820</v>
+        <v>508</v>
       </c>
       <c r="E6" s="1">
-        <v>816</v>
+        <v>492</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>1640</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2514,25 +2601,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.728347778320313</v>
+        <v>5.383338928222656</v>
       </c>
       <c r="C7" s="1">
-        <v>1031</v>
+        <v>2044</v>
       </c>
       <c r="D7" s="1">
-        <v>498</v>
+        <v>620</v>
       </c>
       <c r="E7" s="1">
-        <v>498</v>
+        <v>564</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>1031</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2540,25 +2627,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.703033924102783</v>
+        <v>4.403592586517334</v>
       </c>
       <c r="C8" s="1">
-        <v>1024</v>
+        <v>1672</v>
       </c>
       <c r="D8" s="1">
-        <v>508</v>
+        <v>1188</v>
       </c>
       <c r="E8" s="1">
-        <v>36</v>
+        <v>1188</v>
       </c>
       <c r="F8" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>1024</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2566,25 +2653,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.58923077583313</v>
+        <v>4.329847812652588</v>
       </c>
       <c r="C9" s="1">
-        <v>716</v>
+        <v>1644</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>820</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1">
-        <v>716</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2592,25 +2679,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>1.287382960319519</v>
+        <v>2.715373039245606</v>
       </c>
       <c r="C10" s="1">
-        <v>356</v>
+        <v>1031</v>
       </c>
       <c r="D10" s="1">
-        <v>1086</v>
+        <v>498</v>
       </c>
       <c r="E10" s="1">
-        <v>730</v>
+        <v>498</v>
       </c>
       <c r="F10" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>352</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2618,25 +2705,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.229523062705994</v>
+        <v>2.696937084197998</v>
       </c>
       <c r="C11" s="1">
-        <v>340</v>
+        <v>1024</v>
       </c>
       <c r="D11" s="1">
-        <v>344</v>
+        <v>508</v>
       </c>
       <c r="E11" s="1">
-        <v>344</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>340</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2644,25 +2731,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.084873199462891</v>
+        <v>1.885748863220215</v>
       </c>
       <c r="C12" s="1">
-        <v>300</v>
+        <v>716</v>
       </c>
       <c r="D12" s="1">
-        <v>2344</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>2284</v>
+        <v>0</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>240</v>
+        <v>716</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2670,25 +2757,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.9546884894371033</v>
+        <v>0.9376069903373718</v>
       </c>
       <c r="C13" s="1">
-        <v>264</v>
+        <v>356</v>
       </c>
       <c r="D13" s="1">
-        <v>1504</v>
+        <v>1086</v>
       </c>
       <c r="E13" s="1">
-        <v>1504</v>
+        <v>730</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" s="1">
-        <v>264</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2696,16 +2783,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.8245036602020264</v>
+        <v>0.8954673409461975</v>
       </c>
       <c r="C14" s="1">
-        <v>228</v>
+        <v>340</v>
       </c>
       <c r="D14" s="1">
-        <v>756</v>
+        <v>344</v>
       </c>
       <c r="E14" s="1">
-        <v>756</v>
+        <v>344</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2714,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>228</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2722,25 +2809,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.810038685798645</v>
+        <v>0.7901182770729065</v>
       </c>
       <c r="C15" s="1">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="D15" s="1">
-        <v>242</v>
+        <v>2344</v>
       </c>
       <c r="E15" s="1">
-        <v>242</v>
+        <v>2284</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H15" s="1">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2748,16 +2835,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.7232488393783569</v>
+        <v>0.6953040361404419</v>
       </c>
       <c r="C16" s="1">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="D16" s="1">
-        <v>332</v>
+        <v>1504</v>
       </c>
       <c r="E16" s="1">
-        <v>332</v>
+        <v>1504</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -2766,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>200</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2774,25 +2861,25 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.4773442447185516</v>
+        <v>0.6004898548126221</v>
       </c>
       <c r="C17" s="1">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="D17" s="1">
-        <v>4310</v>
+        <v>756</v>
       </c>
       <c r="E17" s="1">
-        <v>4298</v>
+        <v>756</v>
       </c>
       <c r="F17" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>132</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2800,16 +2887,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.4628792405128479</v>
+        <v>0.5899549722671509</v>
       </c>
       <c r="C18" s="1">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="D18" s="1">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="E18" s="1">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2818,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>128</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2826,16 +2913,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3905543684959412</v>
+        <v>0.5267454981803894</v>
       </c>
       <c r="C19" s="1">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="D19" s="1">
-        <v>492</v>
+        <v>332</v>
       </c>
       <c r="E19" s="1">
-        <v>492</v>
+        <v>332</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2844,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>108</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2852,25 +2939,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.3616244196891785</v>
+        <v>0.347652018070221</v>
       </c>
       <c r="C20" s="1">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D20" s="1">
-        <v>220</v>
+        <v>4310</v>
       </c>
       <c r="E20" s="1">
-        <v>220</v>
+        <v>4298</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2878,16 +2965,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.3037645220756531</v>
+        <v>0.3371171355247498</v>
       </c>
       <c r="C21" s="1">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="D21" s="1">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="E21" s="1">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2896,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2904,16 +2991,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.274834543466568</v>
+        <v>0.2844425737857819</v>
       </c>
       <c r="C22" s="1">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="D22" s="1">
-        <v>136</v>
+        <v>492</v>
       </c>
       <c r="E22" s="1">
-        <v>136</v>
+        <v>492</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2922,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>76</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -2930,25 +3017,25 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2603695690631867</v>
+        <v>0.2633727490901947</v>
       </c>
       <c r="C23" s="1">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D23" s="1">
-        <v>400</v>
+        <v>220</v>
       </c>
       <c r="E23" s="1">
-        <v>392</v>
+        <v>220</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>64</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -2956,25 +3043,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2603695690631867</v>
+        <v>0.2212331146001816</v>
       </c>
       <c r="C24" s="1">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D24" s="1">
-        <v>1028</v>
+        <v>252</v>
       </c>
       <c r="E24" s="1">
-        <v>468</v>
+        <v>252</v>
       </c>
       <c r="F24" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -2982,25 +3069,25 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2603695690631867</v>
+        <v>0.2001632899045944</v>
       </c>
       <c r="C25" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D25" s="1">
-        <v>978</v>
+        <v>136</v>
       </c>
       <c r="E25" s="1">
-        <v>966</v>
+        <v>136</v>
       </c>
       <c r="F25" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3008,22 +3095,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.231439620256424</v>
+        <v>0.1896283775568008</v>
       </c>
       <c r="C26" s="1">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D26" s="1">
-        <v>286</v>
+        <v>400</v>
       </c>
       <c r="E26" s="1">
-        <v>286</v>
+        <v>392</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H26" s="1">
         <v>64</v>
@@ -3034,25 +3121,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1591147482395172</v>
+        <v>0.1896283775568008</v>
       </c>
       <c r="C27" s="1">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D27" s="1">
-        <v>408</v>
+        <v>1028</v>
       </c>
       <c r="E27" s="1">
-        <v>344</v>
+        <v>468</v>
       </c>
       <c r="F27" s="1">
-        <v>20</v>
+        <v>512</v>
       </c>
       <c r="G27" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H27" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3060,25 +3147,25 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1446497738361359</v>
+        <v>0.1896283775568008</v>
       </c>
       <c r="C28" s="1">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D28" s="1">
-        <v>76</v>
+        <v>978</v>
       </c>
       <c r="E28" s="1">
-        <v>76</v>
+        <v>966</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>40</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3086,25 +3173,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1301847845315933</v>
+        <v>0.1685585677623749</v>
       </c>
       <c r="C29" s="1">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D29" s="1">
-        <v>1006</v>
+        <v>288</v>
       </c>
       <c r="E29" s="1">
-        <v>994</v>
+        <v>288</v>
       </c>
       <c r="F29" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3112,22 +3199,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.08317361772060394</v>
+        <v>0.1158840134739876</v>
       </c>
       <c r="C30" s="1">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D30" s="1">
-        <v>435</v>
+        <v>408</v>
       </c>
       <c r="E30" s="1">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="F30" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G30" s="1">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -3138,16 +3225,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.07232488691806793</v>
+        <v>0.105349101126194</v>
       </c>
       <c r="C31" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D31" s="1">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="E31" s="1">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -3156,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3164,25 +3251,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.07232488691806793</v>
+        <v>0.09481418877840042</v>
       </c>
       <c r="C32" s="1">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1">
-        <v>694</v>
+        <v>1006</v>
       </c>
       <c r="E32" s="1">
-        <v>674</v>
+        <v>994</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G32" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3190,22 +3277,22 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.04339493066072464</v>
+        <v>0.08427928388118744</v>
       </c>
       <c r="C33" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D33" s="1">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="E33" s="1">
-        <v>94</v>
+        <v>424</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -3216,22 +3303,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.04339493066072464</v>
+        <v>0.06057573109865189</v>
       </c>
       <c r="C34" s="1">
+        <v>23</v>
+      </c>
+      <c r="D34" s="1">
+        <v>435</v>
+      </c>
+      <c r="E34" s="1">
+        <v>400</v>
+      </c>
+      <c r="F34" s="1">
         <v>12</v>
       </c>
-      <c r="D34" s="1">
-        <v>798</v>
-      </c>
-      <c r="E34" s="1">
-        <v>786</v>
-      </c>
-      <c r="F34" s="1">
-        <v>0</v>
-      </c>
       <c r="G34" s="1">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -3242,25 +3329,25 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.04339493066072464</v>
+        <v>0.052674550563097</v>
       </c>
       <c r="C35" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D35" s="1">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="E35" s="1">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="F35" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3268,22 +3355,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.04339493066072464</v>
+        <v>0.052674550563097</v>
       </c>
       <c r="C36" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D36" s="1">
-        <v>172</v>
+        <v>694</v>
       </c>
       <c r="E36" s="1">
-        <v>148</v>
+        <v>674</v>
       </c>
       <c r="F36" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -3294,22 +3381,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.02892995253205299</v>
+        <v>0.03160472959280014</v>
       </c>
       <c r="C37" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D37" s="1">
-        <v>2848</v>
+        <v>106</v>
       </c>
       <c r="E37" s="1">
-        <v>2840</v>
+        <v>94</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -3320,22 +3407,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.02892995253205299</v>
+        <v>0.03160472959280014</v>
       </c>
       <c r="C38" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1">
-        <v>54</v>
+        <v>798</v>
       </c>
       <c r="E38" s="1">
-        <v>34</v>
+        <v>786</v>
       </c>
       <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
         <v>12</v>
-      </c>
-      <c r="G38" s="1">
-        <v>8</v>
       </c>
       <c r="H38" s="1">
         <v>0</v>
@@ -3346,22 +3433,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.02169746533036232</v>
+        <v>0.03160472959280014</v>
       </c>
       <c r="C39" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D39" s="1">
-        <v>2268</v>
+        <v>126</v>
       </c>
       <c r="E39" s="1">
-        <v>1814</v>
+        <v>102</v>
       </c>
       <c r="F39" s="1">
-        <v>448</v>
+        <v>12</v>
       </c>
       <c r="G39" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -3372,22 +3459,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.0144649762660265</v>
+        <v>0.03160472959280014</v>
       </c>
       <c r="C40" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1">
-        <v>4</v>
+        <v>172</v>
       </c>
       <c r="E40" s="1">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G40" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -3398,22 +3485,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.0144649762660265</v>
+        <v>0.02106982097029686</v>
       </c>
       <c r="C41" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D41" s="1">
-        <v>16</v>
+        <v>2848</v>
       </c>
       <c r="E41" s="1">
-        <v>12</v>
+        <v>2840</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -3424,22 +3511,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.0144649762660265</v>
+        <v>0.02106982097029686</v>
       </c>
       <c r="C42" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D42" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E42" s="1">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F42" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G42" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -3450,22 +3537,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.0144649762660265</v>
+        <v>0.01580236479640007</v>
       </c>
       <c r="C43" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D43" s="1">
-        <v>1080</v>
+        <v>2808</v>
       </c>
       <c r="E43" s="1">
-        <v>740</v>
+        <v>2354</v>
       </c>
       <c r="F43" s="1">
-        <v>336</v>
+        <v>448</v>
       </c>
       <c r="G43" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -3476,16 +3563,16 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.0144649762660265</v>
+        <v>0.01053491048514843</v>
       </c>
       <c r="C44" s="1">
         <v>4</v>
       </c>
       <c r="D44" s="1">
-        <v>272</v>
+        <v>4</v>
       </c>
       <c r="E44" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3502,16 +3589,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.0144649762660265</v>
+        <v>0.01053491048514843</v>
       </c>
       <c r="C45" s="1">
         <v>4</v>
       </c>
       <c r="D45" s="1">
-        <v>502</v>
+        <v>16</v>
       </c>
       <c r="E45" s="1">
-        <v>498</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3528,19 +3615,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.0144649762660265</v>
+        <v>0.01053491048514843</v>
       </c>
       <c r="C46" s="1">
         <v>4</v>
       </c>
       <c r="D46" s="1">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="E46" s="1">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F46" s="1">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G46" s="1">
         <v>4</v>
@@ -3554,22 +3641,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01084873266518116</v>
+        <v>0.01053491048514843</v>
       </c>
       <c r="C47" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" s="1">
-        <v>771</v>
+        <v>1080</v>
       </c>
       <c r="E47" s="1">
-        <v>768</v>
+        <v>740</v>
       </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G47" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -3580,56 +3667,160 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.007232488133013248</v>
+        <v>0.01053491048514843</v>
       </c>
       <c r="C48" s="1">
+        <v>4</v>
+      </c>
+      <c r="D48" s="1">
+        <v>272</v>
+      </c>
+      <c r="E48" s="1">
+        <v>268</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>4</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.01053491048514843</v>
+      </c>
+      <c r="C49" s="1">
+        <v>4</v>
+      </c>
+      <c r="D49" s="1">
+        <v>502</v>
+      </c>
+      <c r="E49" s="1">
+        <v>498</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>4</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.01053491048514843</v>
+      </c>
+      <c r="C50" s="1">
+        <v>4</v>
+      </c>
+      <c r="D50" s="1">
+        <v>84</v>
+      </c>
+      <c r="E50" s="1">
+        <v>48</v>
+      </c>
+      <c r="F50" s="1">
+        <v>32</v>
+      </c>
+      <c r="G50" s="1">
+        <v>4</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.007901182398200035</v>
+      </c>
+      <c r="C51" s="1">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1">
+        <v>875</v>
+      </c>
+      <c r="E51" s="1">
+        <v>872</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>3</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0.005267455242574215</v>
+      </c>
+      <c r="C52" s="1">
         <v>2</v>
       </c>
-      <c r="D48" s="1">
-        <v>328</v>
-      </c>
-      <c r="E48" s="1">
-        <v>326</v>
-      </c>
-      <c r="F48" s="1">
-        <v>0</v>
-      </c>
-      <c r="G48" s="1">
+      <c r="D52" s="1">
+        <v>332</v>
+      </c>
+      <c r="E52" s="1">
+        <v>330</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
         <v>2</v>
       </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
-      <c r="A162" t="s">
-        <v>162</v>
-      </c>
-      <c r="B162">
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C162">
+      <c r="C169">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D162">
+      <c r="D169">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E162">
+      <c r="E169">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F162">
+      <c r="F169">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G162">
+      <c r="G169">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H162">
+      <c r="H169">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -3645,7 +3836,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -3658,100 +3849,100 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="H2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2">
-        <v>4.649857997894287</v>
+        <v>10.80426692962647</v>
       </c>
       <c r="C3" s="1">
-        <v>4310</v>
+        <v>11780</v>
       </c>
       <c r="D3" s="1">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>4298</v>
+        <v>11780</v>
       </c>
       <c r="F3" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2">
-        <v>3.646524429321289</v>
+        <v>3.953004121780396</v>
       </c>
       <c r="C4" s="1">
-        <v>3380</v>
+        <v>4310</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E4" s="1">
-        <v>3380</v>
+        <v>4298</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2">
-        <v>3.575320243835449</v>
+        <v>3.100035667419434</v>
       </c>
       <c r="C5" s="1">
-        <v>3314</v>
+        <v>3380</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>3290</v>
+        <v>3380</v>
       </c>
       <c r="F5" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -3762,22 +3953,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B6" s="2">
-        <v>3.510588884353638</v>
+        <v>3.039502620697022</v>
       </c>
       <c r="C6" s="1">
-        <v>3254</v>
+        <v>3314</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>3254</v>
+        <v>3290</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -3788,19 +3979,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B7" s="2">
-        <v>3.441542387008667</v>
+        <v>2.984472274780273</v>
       </c>
       <c r="C7" s="1">
-        <v>3190</v>
+        <v>3254</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>3190</v>
+        <v>3254</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -3814,22 +4005,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2">
-        <v>3.0876784324646</v>
+        <v>2.92577338218689</v>
       </c>
       <c r="C8" s="1">
-        <v>2862</v>
+        <v>3190</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>2518</v>
+        <v>3190</v>
       </c>
       <c r="F8" s="1">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -3840,25 +4031,25 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B9" s="2">
-        <v>3.072574377059937</v>
+        <v>2.62494158744812</v>
       </c>
       <c r="C9" s="1">
-        <v>2848</v>
+        <v>2862</v>
       </c>
       <c r="D9" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>2840</v>
+        <v>2518</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="G9" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -3866,25 +4057,25 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B10" s="2">
-        <v>2.561197996139526</v>
+        <v>2.612101078033447</v>
       </c>
       <c r="C10" s="1">
-        <v>2374</v>
+        <v>2848</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1">
-        <v>2342</v>
+        <v>2840</v>
       </c>
       <c r="F10" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -3892,25 +4083,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2">
-        <v>2.537463188171387</v>
+        <v>2.575414419174194</v>
       </c>
       <c r="C11" s="1">
-        <v>2352</v>
+        <v>2808</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E11" s="1">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -3918,22 +4109,22 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2">
-        <v>2.533147811889648</v>
+        <v>2.177362442016602</v>
       </c>
       <c r="C12" s="1">
-        <v>2348</v>
+        <v>2374</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>296</v>
+        <v>2342</v>
       </c>
       <c r="F12" s="1">
-        <v>2052</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -3944,51 +4135,51 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2">
-        <v>2.52883243560791</v>
+        <v>2.157184600830078</v>
       </c>
       <c r="C13" s="1">
-        <v>2344</v>
+        <v>2352</v>
       </c>
       <c r="D13" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>2284</v>
+        <v>2352</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2">
-        <v>2.446839570999146</v>
+        <v>2.153516054153442</v>
       </c>
       <c r="C14" s="1">
-        <v>2268</v>
+        <v>2348</v>
       </c>
       <c r="D14" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>1814</v>
+        <v>296</v>
       </c>
       <c r="F14" s="1">
-        <v>448</v>
+        <v>2052</v>
       </c>
       <c r="G14" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
         <v>0</v>
@@ -3996,48 +4187,48 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>2.392896890640259</v>
+        <v>2.149847269058228</v>
       </c>
       <c r="C15" s="1">
-        <v>2218</v>
+        <v>2344</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="1">
-        <v>2218</v>
+        <v>2284</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2">
-        <v>2.213807106018066</v>
+        <v>2.034283876419067</v>
       </c>
       <c r="C16" s="1">
-        <v>2052</v>
+        <v>2218</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>0</v>
+        <v>2218</v>
       </c>
       <c r="F16" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -4048,22 +4239,22 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2">
-        <v>2.049821376800537</v>
+        <v>1.882033586502075</v>
       </c>
       <c r="C17" s="1">
-        <v>1900</v>
+        <v>2052</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -4074,19 +4265,19 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2">
-        <v>1.948409199714661</v>
+        <v>1.742623686790466</v>
       </c>
       <c r="C18" s="1">
-        <v>1806</v>
+        <v>1900</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>1806</v>
+        <v>1900</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -4100,19 +4291,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B19" s="2">
-        <v>1.734796285629273</v>
+        <v>1.656409621238709</v>
       </c>
       <c r="C19" s="1">
-        <v>1608</v>
+        <v>1806</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>1608</v>
+        <v>1806</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -4126,19 +4317,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="B20" s="2">
-        <v>1.622595548629761</v>
+        <v>1.474809885025024</v>
       </c>
       <c r="C20" s="1">
-        <v>1504</v>
+        <v>1608</v>
       </c>
       <c r="D20" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>1504</v>
+        <v>1608</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -4147,24 +4338,24 @@
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B21" s="2">
-        <v>1.503921627998352</v>
+        <v>1.379424214363098</v>
       </c>
       <c r="C21" s="1">
-        <v>1394</v>
+        <v>1504</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="E21" s="1">
-        <v>1394</v>
+        <v>1504</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -4173,24 +4364,24 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2">
-        <v>1.421928763389587</v>
+        <v>1.278535485267639</v>
       </c>
       <c r="C22" s="1">
-        <v>1318</v>
+        <v>1394</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>1318</v>
+        <v>1394</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -4204,19 +4395,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B23" s="2">
-        <v>1.374459266662598</v>
+        <v>1.20883047580719</v>
       </c>
       <c r="C23" s="1">
-        <v>1274</v>
+        <v>1318</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>1274</v>
+        <v>1318</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -4230,19 +4421,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B24" s="2">
-        <v>1.316201090812683</v>
+        <v>1.168475031852722</v>
       </c>
       <c r="C24" s="1">
-        <v>1220</v>
+        <v>1274</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1220</v>
+        <v>1274</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -4256,19 +4447,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B25" s="2">
-        <v>1.294624090194702</v>
+        <v>1.118947863578796</v>
       </c>
       <c r="C25" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -4282,19 +4473,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2">
-        <v>1.251469969749451</v>
+        <v>1.10060441493988</v>
       </c>
       <c r="C26" s="1">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="D26" s="1">
-        <v>1672</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -4303,82 +4494,82 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>1672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B27" s="2">
-        <v>1.171634793281555</v>
+        <v>1.089598417282105</v>
       </c>
       <c r="C27" s="1">
-        <v>1086</v>
+        <v>1188</v>
       </c>
       <c r="D27" s="1">
-        <v>356</v>
+        <v>1672</v>
       </c>
       <c r="E27" s="1">
-        <v>730</v>
+        <v>1188</v>
       </c>
       <c r="F27" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>352</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="B28" s="2">
-        <v>1.165161609649658</v>
+        <v>0.9960470199584961</v>
       </c>
       <c r="C28" s="1">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D28" s="1">
-        <v>4</v>
+        <v>356</v>
       </c>
       <c r="E28" s="1">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="F28" s="1">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="G28" s="1">
         <v>4</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2">
-        <v>1.143584609031677</v>
+        <v>0.9905439615249634</v>
       </c>
       <c r="C29" s="1">
-        <v>1060</v>
+        <v>1080</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E29" s="1">
-        <v>1032</v>
+        <v>740</v>
       </c>
       <c r="F29" s="1">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -4386,149 +4577,149 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="B30" s="2">
-        <v>1.109061241149902</v>
+        <v>0.9722005724906921</v>
       </c>
       <c r="C30" s="1">
-        <v>1028</v>
+        <v>1060</v>
       </c>
       <c r="D30" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>468</v>
+        <v>1032</v>
       </c>
       <c r="F30" s="1">
-        <v>512</v>
+        <v>28</v>
       </c>
       <c r="G30" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2">
-        <v>1.085326552391052</v>
+        <v>0.9428511261940002</v>
       </c>
       <c r="C31" s="1">
-        <v>1006</v>
+        <v>1028</v>
       </c>
       <c r="D31" s="1">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E31" s="1">
-        <v>994</v>
+        <v>468</v>
       </c>
       <c r="F31" s="1">
-        <v>12</v>
+        <v>512</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H31" s="1">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>1.063749432563782</v>
+        <v>0.9226733446121216</v>
       </c>
       <c r="C32" s="1">
-        <v>986</v>
+        <v>1006</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E32" s="1">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="B33" s="2">
-        <v>1.055118560791016</v>
+        <v>0.9043299555778503</v>
       </c>
       <c r="C33" s="1">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="D33" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>966</v>
+        <v>986</v>
       </c>
       <c r="F33" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B34" s="2">
-        <v>1.031383872032166</v>
+        <v>0.8969926238059998</v>
       </c>
       <c r="C34" s="1">
-        <v>956</v>
+        <v>978</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E34" s="1">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="B35" s="2">
-        <v>0.8976060152053833</v>
+        <v>0.8804835081100464</v>
       </c>
       <c r="C35" s="1">
-        <v>832</v>
+        <v>960</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="E35" s="1">
-        <v>832</v>
+        <v>960</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -4537,56 +4728,56 @@
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="B36" s="2">
-        <v>0.8846597671508789</v>
+        <v>0.8768148422241211</v>
       </c>
       <c r="C36" s="1">
-        <v>820</v>
+        <v>956</v>
       </c>
       <c r="D36" s="1">
-        <v>1644</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>816</v>
+        <v>956</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>1640</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B37" s="2">
-        <v>0.860925018787384</v>
+        <v>0.8025240302085877</v>
       </c>
       <c r="C37" s="1">
-        <v>798</v>
+        <v>875</v>
       </c>
       <c r="D37" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E37" s="1">
-        <v>786</v>
+        <v>872</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -4594,19 +4785,19 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8458210825920105</v>
+        <v>0.7630857229232788</v>
       </c>
       <c r="C38" s="1">
-        <v>784</v>
+        <v>832</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>784</v>
+        <v>832</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -4620,71 +4811,71 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8317959904670715</v>
+        <v>0.7520796656608582</v>
       </c>
       <c r="C39" s="1">
-        <v>771</v>
+        <v>820</v>
       </c>
       <c r="D39" s="1">
-        <v>3</v>
+        <v>1644</v>
       </c>
       <c r="E39" s="1">
-        <v>768</v>
+        <v>816</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.7319019436836243</v>
+      </c>
+      <c r="C40" s="1">
+        <v>798</v>
+      </c>
+      <c r="D40" s="1">
         <v>12</v>
       </c>
-      <c r="B40" s="2">
-        <v>0.8156131505966187</v>
-      </c>
-      <c r="C40" s="1">
-        <v>756</v>
-      </c>
-      <c r="D40" s="1">
-        <v>228</v>
-      </c>
       <c r="E40" s="1">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H40" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B41" s="2">
-        <v>0.7767744660377502</v>
+        <v>0.719061553478241</v>
       </c>
       <c r="C41" s="1">
-        <v>720</v>
+        <v>784</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>720</v>
+        <v>784</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -4698,51 +4889,51 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7703013420104981</v>
+        <v>0.6933807730674744</v>
       </c>
       <c r="C42" s="1">
-        <v>714</v>
+        <v>756</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E42" s="1">
-        <v>706</v>
+        <v>756</v>
       </c>
       <c r="F42" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="B43" s="2">
-        <v>0.7487242817878723</v>
+        <v>0.6860434412956238</v>
       </c>
       <c r="C43" s="1">
-        <v>694</v>
+        <v>748</v>
       </c>
       <c r="D43" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>674</v>
+        <v>748</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -4750,19 +4941,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7379357218742371</v>
+        <v>0.6603626608848572</v>
       </c>
       <c r="C44" s="1">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -4776,22 +4967,22 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7293049097061157</v>
+        <v>0.6548596024513245</v>
       </c>
       <c r="C45" s="1">
-        <v>676</v>
+        <v>714</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>676</v>
+        <v>706</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -4802,25 +4993,25 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7185163497924805</v>
+        <v>0.6365162134170532</v>
       </c>
       <c r="C46" s="1">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E46" s="1">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4828,19 +5019,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B47" s="2">
-        <v>0.6947816014289856</v>
+        <v>0.6273444890975952</v>
       </c>
       <c r="C47" s="1">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -4854,19 +5045,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B48" s="2">
-        <v>0.6839930415153503</v>
+        <v>0.6108354330062866</v>
       </c>
       <c r="C48" s="1">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>634</v>
+        <v>666</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -4880,45 +5071,45 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6688891053199768</v>
+        <v>0.5906577110290527</v>
       </c>
       <c r="C49" s="1">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="D49" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>564</v>
+        <v>644</v>
       </c>
       <c r="F49" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6343657970428467</v>
+        <v>0.5888233780860901</v>
       </c>
       <c r="C50" s="1">
-        <v>588</v>
+        <v>642</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>588</v>
+        <v>642</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -4932,22 +5123,22 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B51" s="2">
-        <v>0.5998424887657166</v>
+        <v>0.5814859867095947</v>
       </c>
       <c r="C51" s="1">
-        <v>556</v>
+        <v>634</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>44</v>
+        <v>634</v>
       </c>
       <c r="F51" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
@@ -4958,100 +5149,100 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="B52" s="2">
-        <v>0.5782654285430908</v>
+        <v>0.5686455965042114</v>
       </c>
       <c r="C52" s="1">
-        <v>536</v>
+        <v>620</v>
       </c>
       <c r="D52" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
       <c r="E52" s="1">
-        <v>344</v>
+        <v>564</v>
       </c>
       <c r="F52" s="1">
-        <v>192</v>
+        <v>56</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="B53" s="2">
-        <v>0.552372932434082</v>
+        <v>0.5392961502075195</v>
       </c>
       <c r="C53" s="1">
-        <v>512</v>
+        <v>588</v>
       </c>
       <c r="D53" s="1">
-        <v>16416</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>480</v>
+        <v>588</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>16384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="B54" s="2">
-        <v>0.548057496547699</v>
+        <v>0.5099467039108276</v>
       </c>
       <c r="C54" s="1">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="D54" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F54" s="1">
-        <v>472</v>
+        <v>512</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5437421202659607</v>
+        <v>0.4916033148765564</v>
       </c>
       <c r="C55" s="1">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>504</v>
+        <v>344</v>
       </c>
       <c r="F55" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
@@ -5062,97 +5253,97 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5415844321250916</v>
+        <v>0.4695912301540375</v>
       </c>
       <c r="C56" s="1">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="D56" s="1">
-        <v>4</v>
+        <v>16416</v>
       </c>
       <c r="E56" s="1">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
       <c r="G56" s="1">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5372689962387085</v>
+        <v>0.4659225344657898</v>
       </c>
       <c r="C57" s="1">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="D57" s="1">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="E57" s="1">
-        <v>498</v>
+        <v>36</v>
       </c>
       <c r="F57" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>1031</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>0.5307958722114563</v>
+        <v>0.4659225344657898</v>
       </c>
       <c r="C58" s="1">
-        <v>492</v>
+        <v>508</v>
       </c>
       <c r="D58" s="1">
-        <v>108</v>
+        <v>2092</v>
       </c>
       <c r="E58" s="1">
         <v>492</v>
       </c>
       <c r="F58" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>108</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B59" s="2">
-        <v>0.5049033761024475</v>
+        <v>0.4622538685798645</v>
       </c>
       <c r="C59" s="1">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>468</v>
+        <v>504</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -5166,19 +5357,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4811686277389526</v>
+        <v>0.4604195058345795</v>
       </c>
       <c r="C60" s="1">
-        <v>446</v>
+        <v>502</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="E60" s="1">
-        <v>446</v>
+        <v>502</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -5187,30 +5378,30 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4693012237548828</v>
+        <v>0.4604195058345795</v>
       </c>
       <c r="C61" s="1">
-        <v>435</v>
+        <v>502</v>
       </c>
       <c r="D61" s="1">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E61" s="1">
-        <v>400</v>
+        <v>498</v>
       </c>
       <c r="F61" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H61" s="1">
         <v>0</v>
@@ -5218,71 +5409,71 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4423298835754395</v>
+        <v>0.4567508399486542</v>
       </c>
       <c r="C62" s="1">
-        <v>410</v>
+        <v>498</v>
       </c>
       <c r="D62" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="E62" s="1">
-        <v>330</v>
+        <v>498</v>
       </c>
       <c r="F62" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4401721954345703</v>
+        <v>0.4512478113174439</v>
       </c>
       <c r="C63" s="1">
-        <v>408</v>
+        <v>492</v>
       </c>
       <c r="D63" s="1">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="E63" s="1">
-        <v>344</v>
+        <v>492</v>
       </c>
       <c r="F63" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4315413534641266</v>
+        <v>0.4365730881690979</v>
       </c>
       <c r="C64" s="1">
-        <v>400</v>
+        <v>476</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>400</v>
+        <v>476</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -5296,51 +5487,51 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4315413534641266</v>
+        <v>0.4292357265949249</v>
       </c>
       <c r="C65" s="1">
-        <v>400</v>
+        <v>468</v>
       </c>
       <c r="D65" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>392</v>
+        <v>468</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4013334512710571</v>
+        <v>0.4182296693325043</v>
       </c>
       <c r="C66" s="1">
-        <v>372</v>
+        <v>456</v>
       </c>
       <c r="D66" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E66" s="1">
-        <v>340</v>
+        <v>424</v>
       </c>
       <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
         <v>32</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -5348,19 +5539,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B67" s="2">
-        <v>0.3948603570461273</v>
+        <v>0.4090579748153687</v>
       </c>
       <c r="C67" s="1">
-        <v>366</v>
+        <v>446</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>366</v>
+        <v>446</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -5374,48 +5565,48 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B68" s="2">
-        <v>0.3711255788803101</v>
+        <v>0.3989691138267517</v>
       </c>
       <c r="C68" s="1">
-        <v>344</v>
+        <v>435</v>
       </c>
       <c r="D68" s="1">
-        <v>340</v>
+        <v>23</v>
       </c>
       <c r="E68" s="1">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="F68" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H68" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B69" s="2">
-        <v>0.3624947369098663</v>
+        <v>0.3760398328304291</v>
       </c>
       <c r="C69" s="1">
-        <v>336</v>
+        <v>410</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="F69" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -5426,25 +5617,25 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3603370189666748</v>
+        <v>0.3742054998874664</v>
       </c>
       <c r="C70" s="1">
-        <v>334</v>
+        <v>408</v>
       </c>
       <c r="D70" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E70" s="1">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F70" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -5452,19 +5643,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3581793308258057</v>
+        <v>0.3668681383132935</v>
       </c>
       <c r="C71" s="1">
-        <v>332</v>
+        <v>400</v>
       </c>
       <c r="D71" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>332</v>
+        <v>400</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -5473,50 +5664,50 @@
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B72" s="2">
-        <v>0.353863924741745</v>
+        <v>0.3668681383132935</v>
       </c>
       <c r="C72" s="1">
-        <v>328</v>
+        <v>400</v>
       </c>
       <c r="D72" s="1">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="E72" s="1">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3495484888553619</v>
+        <v>0.3650338053703308</v>
       </c>
       <c r="C73" s="1">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>324</v>
+        <v>398</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -5530,22 +5721,22 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3441542387008667</v>
+        <v>0.3411873579025269</v>
       </c>
       <c r="C74" s="1">
-        <v>319</v>
+        <v>372</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="F74" s="1">
-        <v>319</v>
+        <v>32</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
@@ -5556,22 +5747,22 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3322868347167969</v>
+        <v>0.3356843590736389</v>
       </c>
       <c r="C75" s="1">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>292</v>
+        <v>366</v>
       </c>
       <c r="F75" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
@@ -5582,19 +5773,19 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3085520565509796</v>
+        <v>0.3155066072940826</v>
       </c>
       <c r="C76" s="1">
-        <v>286</v>
+        <v>344</v>
       </c>
       <c r="D76" s="1">
-        <v>64</v>
+        <v>340</v>
       </c>
       <c r="E76" s="1">
-        <v>286</v>
+        <v>344</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -5603,30 +5794,30 @@
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>64</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="B77" s="2">
-        <v>0.2934481203556061</v>
+        <v>0.3081692457199097</v>
       </c>
       <c r="C77" s="1">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="D77" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
       </c>
       <c r="G77" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -5634,19 +5825,19 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B78" s="2">
-        <v>0.2934481203556061</v>
+        <v>0.3063348829746246</v>
       </c>
       <c r="C78" s="1">
-        <v>272</v>
+        <v>334</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>272</v>
+        <v>334</v>
       </c>
       <c r="F78" s="1">
         <v>0</v>
@@ -5660,19 +5851,19 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B79" s="2">
-        <v>0.2718710601329804</v>
+        <v>0.304500550031662</v>
       </c>
       <c r="C79" s="1">
-        <v>252</v>
+        <v>332</v>
       </c>
       <c r="D79" s="1">
-        <v>84</v>
+        <v>200</v>
       </c>
       <c r="E79" s="1">
-        <v>252</v>
+        <v>332</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -5681,50 +5872,50 @@
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>84</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="B80" s="2">
-        <v>0.2610825300216675</v>
+        <v>0.304500550031662</v>
       </c>
       <c r="C80" s="1">
-        <v>242</v>
+        <v>332</v>
       </c>
       <c r="D80" s="1">
-        <v>224</v>
+        <v>2</v>
       </c>
       <c r="E80" s="1">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H80" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B81" s="2">
-        <v>0.2524516880512238</v>
+        <v>0.297163188457489</v>
       </c>
       <c r="C81" s="1">
-        <v>234</v>
+        <v>324</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>234</v>
+        <v>324</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
@@ -5738,22 +5929,22 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B82" s="2">
-        <v>0.2502939999103546</v>
+        <v>0.29257732629776</v>
       </c>
       <c r="C82" s="1">
-        <v>232</v>
+        <v>319</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>32</v>
+        <v>319</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -5764,22 +5955,22 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B83" s="2">
-        <v>0.2459785789251328</v>
+        <v>0.2824884653091431</v>
       </c>
       <c r="C83" s="1">
-        <v>228</v>
+        <v>308</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="F83" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G83" s="1">
         <v>0</v>
@@ -5790,51 +5981,51 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="B84" s="2">
-        <v>0.2438208609819412</v>
+        <v>0.2641450464725494</v>
       </c>
       <c r="C84" s="1">
-        <v>226</v>
+        <v>288</v>
       </c>
       <c r="D84" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E84" s="1">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="F84" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G84" s="1">
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="B85" s="2">
-        <v>0.2395054548978806</v>
+        <v>0.2494703382253647</v>
       </c>
       <c r="C85" s="1">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="D85" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E85" s="1">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -5842,19 +6033,19 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2373477518558502</v>
+        <v>0.2494703382253647</v>
       </c>
       <c r="C86" s="1">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -5868,19 +6059,19 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2373477518558502</v>
+        <v>0.2311269342899323</v>
       </c>
       <c r="C87" s="1">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="D87" s="1">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E87" s="1">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -5889,50 +6080,50 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2373477518558502</v>
+        <v>0.2219552248716354</v>
       </c>
       <c r="C88" s="1">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="D88" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E88" s="1">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="F88" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G88" s="1">
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2200860977172852</v>
+        <v>0.2146178632974625</v>
       </c>
       <c r="C89" s="1">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -5946,45 +6137,45 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2071398496627808</v>
+        <v>0.2127835154533386</v>
       </c>
       <c r="C90" s="1">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="D90" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F90" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G90" s="1">
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2006667256355286</v>
+        <v>0.2091148346662521</v>
       </c>
       <c r="C91" s="1">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -5998,22 +6189,22 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B92" s="2">
-        <v>0.1898781955242157</v>
+        <v>0.2072805017232895</v>
       </c>
       <c r="C92" s="1">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F92" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G92" s="1">
         <v>0</v>
@@ -6024,19 +6215,19 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B93" s="2">
-        <v>0.1898781955242157</v>
+        <v>0.203611820936203</v>
       </c>
       <c r="C93" s="1">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -6050,19 +6241,19 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B94" s="2">
-        <v>0.1898781955242157</v>
+        <v>0.2017774730920792</v>
       </c>
       <c r="C94" s="1">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
@@ -6076,48 +6267,48 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B95" s="2">
-        <v>0.185562789440155</v>
+        <v>0.2017774730920792</v>
       </c>
       <c r="C95" s="1">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="D95" s="1">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="E95" s="1">
-        <v>148</v>
+        <v>220</v>
       </c>
       <c r="F95" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H95" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B96" s="2">
-        <v>0.1726165413856506</v>
+        <v>0.2017774730920792</v>
       </c>
       <c r="C96" s="1">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="F96" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G96" s="1">
         <v>0</v>
@@ -6128,19 +6319,19 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1704588383436203</v>
+        <v>0.1871027499437332</v>
       </c>
       <c r="C97" s="1">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -6154,19 +6345,19 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1661434173583984</v>
+        <v>0.1760967075824738</v>
       </c>
       <c r="C98" s="1">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="D98" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E98" s="1">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -6175,24 +6366,24 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1639857143163681</v>
+        <v>0.1705936789512634</v>
       </c>
       <c r="C99" s="1">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -6206,19 +6397,19 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1553548872470856</v>
+        <v>0.1614219844341278</v>
       </c>
       <c r="C100" s="1">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -6232,19 +6423,19 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1531971842050552</v>
+        <v>0.1614219844341278</v>
       </c>
       <c r="C101" s="1">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -6258,19 +6449,19 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1488817632198334</v>
+        <v>0.1614219844341278</v>
       </c>
       <c r="C102" s="1">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -6284,45 +6475,45 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B103" s="2">
-        <v>0.146724060177803</v>
+        <v>0.1577533036470413</v>
       </c>
       <c r="C103" s="1">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="D103" s="1">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="E103" s="1">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F103" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G103" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H103" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1424086540937424</v>
+        <v>0.144912913441658</v>
       </c>
       <c r="C104" s="1">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -6336,25 +6527,25 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1359355300664902</v>
+        <v>0.1412442326545715</v>
       </c>
       <c r="C105" s="1">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="D105" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>102</v>
+        <v>154</v>
       </c>
       <c r="F105" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G105" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -6362,19 +6553,19 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B106" s="2">
-        <v>0.129462406039238</v>
+        <v>0.1394098997116089</v>
       </c>
       <c r="C106" s="1">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -6388,19 +6579,19 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="B107" s="2">
-        <v>0.129462406039238</v>
+        <v>0.1320725232362747</v>
       </c>
       <c r="C107" s="1">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="D107" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -6409,24 +6600,24 @@
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1273047029972076</v>
+        <v>0.1302381902933121</v>
       </c>
       <c r="C108" s="1">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -6440,19 +6631,19 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1251469999551773</v>
+        <v>0.1265695095062256</v>
       </c>
       <c r="C109" s="1">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -6466,19 +6657,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1251469999551773</v>
+        <v>0.1247351691126823</v>
       </c>
       <c r="C110" s="1">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="D110" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E110" s="1">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -6487,24 +6678,24 @@
         <v>0</v>
       </c>
       <c r="H110" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1208315789699554</v>
+        <v>0.1210664883255959</v>
       </c>
       <c r="C111" s="1">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -6518,25 +6709,25 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1186738759279251</v>
+        <v>0.1155634671449661</v>
       </c>
       <c r="C112" s="1">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D112" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E112" s="1">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F112" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G112" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -6544,25 +6735,25 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1143584623932838</v>
+        <v>0.1100604385137558</v>
       </c>
       <c r="C113" s="1">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D113" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
       </c>
       <c r="G113" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -6570,19 +6761,19 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1057276353240013</v>
+        <v>0.1100604385137558</v>
       </c>
       <c r="C114" s="1">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="D114" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E114" s="1">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -6591,24 +6782,24 @@
         <v>0</v>
       </c>
       <c r="H114" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1057276353240013</v>
+        <v>0.1082260981202126</v>
       </c>
       <c r="C115" s="1">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -6622,19 +6813,19 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1057276353240013</v>
+        <v>0.1063917577266693</v>
       </c>
       <c r="C116" s="1">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -6648,19 +6839,19 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B117" s="2">
-        <v>0.09925451129674912</v>
+        <v>0.1063917577266693</v>
       </c>
       <c r="C117" s="1">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
       </c>
       <c r="E117" s="1">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -6674,19 +6865,19 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B118" s="2">
-        <v>0.09493909776210785</v>
+        <v>0.1027230769395828</v>
       </c>
       <c r="C118" s="1">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D118" s="1">
         <v>0</v>
       </c>
       <c r="E118" s="1">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
@@ -6700,19 +6891,19 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B119" s="2">
-        <v>0.09493909776210785</v>
+        <v>0.1008887365460396</v>
       </c>
       <c r="C119" s="1">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
       </c>
       <c r="E119" s="1">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -6726,19 +6917,19 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B120" s="2">
-        <v>0.09278139472007752</v>
+        <v>0.09722005575895309</v>
       </c>
       <c r="C120" s="1">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -6752,25 +6943,25 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="B121" s="2">
-        <v>0.09062368422746658</v>
+        <v>0.09722005575895309</v>
       </c>
       <c r="C121" s="1">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D121" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E121" s="1">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -6778,25 +6969,25 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="B122" s="2">
-        <v>0.09062368422746658</v>
+        <v>0.08988269418478012</v>
       </c>
       <c r="C122" s="1">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D122" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E122" s="1">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F122" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G122" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -6804,19 +6995,19 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B123" s="2">
-        <v>0.08846598118543625</v>
+        <v>0.08988269418478012</v>
       </c>
       <c r="C123" s="1">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -6830,19 +7021,19 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B124" s="2">
-        <v>0.08846598118543625</v>
+        <v>0.08437967300415039</v>
       </c>
       <c r="C124" s="1">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
       </c>
       <c r="E124" s="1">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
@@ -6856,19 +7047,19 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B125" s="2">
-        <v>0.08199285715818405</v>
+        <v>0.0807109922170639</v>
       </c>
       <c r="C125" s="1">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
       </c>
       <c r="E125" s="1">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -6882,19 +7073,19 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="B126" s="2">
-        <v>0.08199285715818405</v>
+        <v>0.0807109922170639</v>
       </c>
       <c r="C126" s="1">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D126" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -6903,24 +7094,24 @@
         <v>0</v>
       </c>
       <c r="H126" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B127" s="2">
-        <v>0.07120432704687119</v>
+        <v>0.07887665182352066</v>
       </c>
       <c r="C127" s="1">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -6934,19 +7125,19 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B128" s="2">
-        <v>0.06473120301961899</v>
+        <v>0.07704231142997742</v>
       </c>
       <c r="C128" s="1">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -6960,25 +7151,25 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="B129" s="2">
-        <v>0.06473120301961899</v>
+        <v>0.07704231142997742</v>
       </c>
       <c r="C129" s="1">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D129" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E129" s="1">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F129" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G129" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
@@ -6986,19 +7177,19 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B130" s="2">
-        <v>0.06257349997758865</v>
+        <v>0.07520797103643417</v>
       </c>
       <c r="C130" s="1">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -7012,19 +7203,19 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B131" s="2">
-        <v>0.05825808271765709</v>
+        <v>0.07520797103643417</v>
       </c>
       <c r="C131" s="1">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -7038,25 +7229,25 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="B132" s="2">
-        <v>0.05825808271765709</v>
+        <v>0.06970494985580444</v>
       </c>
       <c r="C132" s="1">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D132" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="F132" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G132" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H132" s="1">
         <v>0</v>
@@ -7064,19 +7255,19 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="B133" s="2">
-        <v>0.05610037595033646</v>
+        <v>0.06970494985580444</v>
       </c>
       <c r="C133" s="1">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D133" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E133" s="1">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -7085,24 +7276,24 @@
         <v>0</v>
       </c>
       <c r="H133" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B134" s="2">
-        <v>0.05178496241569519</v>
+        <v>0.06053324416279793</v>
       </c>
       <c r="C134" s="1">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D134" s="1">
         <v>0</v>
       </c>
       <c r="E134" s="1">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -7116,19 +7307,19 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B135" s="2">
-        <v>0.05178496241569519</v>
+        <v>0.0550302192568779</v>
       </c>
       <c r="C135" s="1">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D135" s="1">
         <v>0</v>
       </c>
       <c r="E135" s="1">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -7142,19 +7333,19 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B136" s="2">
-        <v>0.05178496241569519</v>
+        <v>0.0550302192568779</v>
       </c>
       <c r="C136" s="1">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -7168,19 +7359,19 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B137" s="2">
-        <v>0.04746954888105393</v>
+        <v>0.05319587886333466</v>
       </c>
       <c r="C137" s="1">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D137" s="1">
         <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -7194,19 +7385,19 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B138" s="2">
-        <v>0.04746954888105393</v>
+        <v>0.04952719807624817</v>
       </c>
       <c r="C138" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
       </c>
       <c r="E138" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -7223,22 +7414,22 @@
         <v>40</v>
       </c>
       <c r="B139" s="2">
-        <v>0.04746954888105393</v>
+        <v>0.04952719807624817</v>
       </c>
       <c r="C139" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D139" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E139" s="1">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F139" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G139" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
@@ -7246,19 +7437,19 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B140" s="2">
-        <v>0.04746954888105393</v>
+        <v>0.04769285768270493</v>
       </c>
       <c r="C140" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -7272,19 +7463,19 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B141" s="2">
-        <v>0.04746954888105393</v>
+        <v>0.04769285768270493</v>
       </c>
       <c r="C141" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
       </c>
       <c r="E141" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -7298,19 +7489,19 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B142" s="2">
-        <v>0.04099642857909203</v>
+        <v>0.04402417689561844</v>
       </c>
       <c r="C142" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -7324,19 +7515,19 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B143" s="2">
-        <v>0.03883872181177139</v>
+        <v>0.04402417689561844</v>
       </c>
       <c r="C143" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D143" s="1">
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -7350,19 +7541,19 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B144" s="2">
-        <v>0.03883872181177139</v>
+        <v>0.04402417689561844</v>
       </c>
       <c r="C144" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D144" s="1">
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7376,19 +7567,19 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B145" s="2">
-        <v>0.03883872181177139</v>
+        <v>0.04035549610853195</v>
       </c>
       <c r="C145" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D145" s="1">
         <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F145" s="1">
         <v>0</v>
@@ -7402,19 +7593,19 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B146" s="2">
-        <v>0.03883872181177139</v>
+        <v>0.04035549610853195</v>
       </c>
       <c r="C146" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -7428,25 +7619,25 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1" t="s">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="B147" s="2">
-        <v>0.03883872181177139</v>
+        <v>0.04035549610853195</v>
       </c>
       <c r="C147" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D147" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E147" s="1">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F147" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G147" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
@@ -7457,16 +7648,16 @@
         <v>149</v>
       </c>
       <c r="B148" s="2">
-        <v>0.03452330827713013</v>
+        <v>0.04035549610853195</v>
       </c>
       <c r="C148" s="1">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D148" s="1">
         <v>0</v>
       </c>
       <c r="E148" s="1">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F148" s="1">
         <v>0</v>
@@ -7483,16 +7674,16 @@
         <v>150</v>
       </c>
       <c r="B149" s="2">
-        <v>0.03452330827713013</v>
+        <v>0.04035549610853195</v>
       </c>
       <c r="C149" s="1">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D149" s="1">
         <v>0</v>
       </c>
       <c r="E149" s="1">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F149" s="1">
         <v>0</v>
@@ -7509,16 +7700,16 @@
         <v>151</v>
       </c>
       <c r="B150" s="2">
-        <v>0.03452330827713013</v>
+        <v>0.03485247492790222</v>
       </c>
       <c r="C150" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
       </c>
       <c r="E150" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F150" s="1">
         <v>0</v>
@@ -7535,16 +7726,16 @@
         <v>152</v>
       </c>
       <c r="B151" s="2">
-        <v>0.03452330827713013</v>
+        <v>0.03301813080906868</v>
       </c>
       <c r="C151" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D151" s="1">
         <v>0</v>
       </c>
       <c r="E151" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F151" s="1">
         <v>0</v>
@@ -7561,16 +7752,16 @@
         <v>153</v>
       </c>
       <c r="B152" s="2">
-        <v>0.03452330827713013</v>
+        <v>0.03301813080906868</v>
       </c>
       <c r="C152" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D152" s="1">
         <v>0</v>
       </c>
       <c r="E152" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F152" s="1">
         <v>0</v>
@@ -7587,16 +7778,16 @@
         <v>154</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03236560150980949</v>
+        <v>0.03301813080906868</v>
       </c>
       <c r="C153" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D153" s="1">
         <v>0</v>
       </c>
       <c r="E153" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F153" s="1">
         <v>0</v>
@@ -7613,16 +7804,16 @@
         <v>155</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03236560150980949</v>
+        <v>0.03301813080906868</v>
       </c>
       <c r="C154" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D154" s="1">
         <v>0</v>
       </c>
       <c r="E154" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F154" s="1">
         <v>0</v>
@@ -7639,16 +7830,16 @@
         <v>156</v>
       </c>
       <c r="B155" s="2">
-        <v>0.0258924812078476</v>
+        <v>0.03301813080906868</v>
       </c>
       <c r="C155" s="1">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
       </c>
       <c r="E155" s="1">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F155" s="1">
         <v>0</v>
@@ -7662,25 +7853,25 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1" t="s">
-        <v>39</v>
+        <v>157</v>
       </c>
       <c r="B156" s="2">
-        <v>0.01726165413856506</v>
+        <v>0.02934945188462734</v>
       </c>
       <c r="C156" s="1">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D156" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E156" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
       </c>
       <c r="G156" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H156" s="1">
         <v>0</v>
@@ -7688,19 +7879,19 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B157" s="2">
-        <v>0.008630827069282532</v>
+        <v>0.02934945188462734</v>
       </c>
       <c r="C157" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
       </c>
       <c r="E157" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -7714,19 +7905,19 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B158" s="2">
-        <v>0.008630827069282532</v>
+        <v>0.02934945188462734</v>
       </c>
       <c r="C158" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D158" s="1">
         <v>0</v>
       </c>
       <c r="E158" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F158" s="1">
         <v>0</v>
@@ -7740,25 +7931,25 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1" t="s">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="B159" s="2">
-        <v>0.004315413534641266</v>
+        <v>0.02934945188462734</v>
       </c>
       <c r="C159" s="1">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D159" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E159" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F159" s="1">
         <v>0</v>
       </c>
       <c r="G159" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -7766,19 +7957,19 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B160" s="2">
-        <v>0.004315413534641266</v>
+        <v>0.02751510962843895</v>
       </c>
       <c r="C160" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D160" s="1">
         <v>0</v>
       </c>
       <c r="E160" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F160" s="1">
         <v>0</v>
@@ -7792,59 +7983,241 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B161" s="2">
-        <v>0.004315413534641266</v>
+        <v>0.02751510962843895</v>
       </c>
       <c r="C161" s="1">
+        <v>30</v>
+      </c>
+      <c r="D161" s="1">
+        <v>0</v>
+      </c>
+      <c r="E161" s="1">
+        <v>30</v>
+      </c>
+      <c r="F161" s="1">
+        <v>0</v>
+      </c>
+      <c r="G161" s="1">
+        <v>0</v>
+      </c>
+      <c r="H161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B162" s="2">
+        <v>0.02201208844780922</v>
+      </c>
+      <c r="C162" s="1">
+        <v>24</v>
+      </c>
+      <c r="D162" s="1">
+        <v>0</v>
+      </c>
+      <c r="E162" s="1">
+        <v>24</v>
+      </c>
+      <c r="F162" s="1">
+        <v>0</v>
+      </c>
+      <c r="G162" s="1">
+        <v>0</v>
+      </c>
+      <c r="H162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
+      <c r="A163" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B163" s="2">
+        <v>0.01467472594231367</v>
+      </c>
+      <c r="C163" s="1">
+        <v>16</v>
+      </c>
+      <c r="D163" s="1">
         <v>4</v>
       </c>
-      <c r="D161" s="1">
-        <v>0</v>
-      </c>
-      <c r="E161" s="1">
+      <c r="E163" s="1">
+        <v>12</v>
+      </c>
+      <c r="F163" s="1">
+        <v>0</v>
+      </c>
+      <c r="G163" s="1">
         <v>4</v>
       </c>
-      <c r="F161" s="1">
-        <v>0</v>
-      </c>
-      <c r="G161" s="1">
-        <v>0</v>
-      </c>
-      <c r="H161" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
-      <c r="A162" t="s">
-        <v>162</v>
-      </c>
-      <c r="B162">
+      <c r="H163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
+      <c r="A164" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B164" s="2">
+        <v>0.007337362971156836</v>
+      </c>
+      <c r="C164" s="1">
+        <v>8</v>
+      </c>
+      <c r="D164" s="1">
+        <v>0</v>
+      </c>
+      <c r="E164" s="1">
+        <v>8</v>
+      </c>
+      <c r="F164" s="1">
+        <v>0</v>
+      </c>
+      <c r="G164" s="1">
+        <v>0</v>
+      </c>
+      <c r="H164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B165" s="2">
+        <v>0.007337362971156836</v>
+      </c>
+      <c r="C165" s="1">
+        <v>8</v>
+      </c>
+      <c r="D165" s="1">
+        <v>0</v>
+      </c>
+      <c r="E165" s="1">
+        <v>8</v>
+      </c>
+      <c r="F165" s="1">
+        <v>0</v>
+      </c>
+      <c r="G165" s="1">
+        <v>0</v>
+      </c>
+      <c r="H165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B166" s="2">
+        <v>0.003668681485578418</v>
+      </c>
+      <c r="C166" s="1">
+        <v>4</v>
+      </c>
+      <c r="D166" s="1">
+        <v>4</v>
+      </c>
+      <c r="E166" s="1">
+        <v>0</v>
+      </c>
+      <c r="F166" s="1">
+        <v>0</v>
+      </c>
+      <c r="G166" s="1">
+        <v>4</v>
+      </c>
+      <c r="H166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2">
+        <v>0.003668681485578418</v>
+      </c>
+      <c r="C167" s="1">
+        <v>4</v>
+      </c>
+      <c r="D167" s="1">
+        <v>0</v>
+      </c>
+      <c r="E167" s="1">
+        <v>4</v>
+      </c>
+      <c r="F167" s="1">
+        <v>0</v>
+      </c>
+      <c r="G167" s="1">
+        <v>0</v>
+      </c>
+      <c r="H167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2">
+        <v>0.003668681485578418</v>
+      </c>
+      <c r="C168" s="1">
+        <v>4</v>
+      </c>
+      <c r="D168" s="1">
+        <v>0</v>
+      </c>
+      <c r="E168" s="1">
+        <v>4</v>
+      </c>
+      <c r="F168" s="1">
+        <v>0</v>
+      </c>
+      <c r="G168" s="1">
+        <v>0</v>
+      </c>
+      <c r="H168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+      <c r="B169">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C162">
+      <c r="C169">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D162">
+      <c r="D169">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E162">
+      <c r="E169">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F162">
+      <c r="F169">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G162">
+      <c r="G169">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H162">
+      <c r="H169">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="183">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -29,6 +29,9 @@
     <t>dev_flash.o</t>
   </si>
   <si>
+    <t>dev_commun_can.o</t>
+  </si>
+  <si>
     <t>motor_info_storage.o</t>
   </si>
   <si>
@@ -68,6 +71,9 @@
     <t>drv_rtos.o</t>
   </si>
   <si>
+    <t>adc.o</t>
+  </si>
+  <si>
     <t>spi.o</t>
   </si>
   <si>
@@ -77,9 +83,6 @@
     <t>dev_dwt_counter.o</t>
   </si>
   <si>
-    <t>adc.o</t>
-  </si>
-  <si>
     <t>fdcan.o</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
     <t>dev_encoder_mt6835.o</t>
   </si>
   <si>
+    <t>drv_can.o</t>
+  </si>
+  <si>
     <t>calib_level7_auto.o</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
     <t>stm32g4xx_hal_flash.o</t>
   </si>
   <si>
+    <t>jm_proto_ops.o</t>
+  </si>
+  <si>
     <t>dev_motor.o</t>
   </si>
   <si>
@@ -137,12 +146,12 @@
     <t>mc_w.l</t>
   </si>
   <si>
+    <t>led_manager.o</t>
+  </si>
+  <si>
     <t>calib_level4_torque.o</t>
   </si>
   <si>
-    <t>jm_proto_ops.o</t>
-  </si>
-  <si>
     <t>stdout.o</t>
   </si>
   <si>
@@ -167,27 +176,27 @@
     <t>motor_pid_load.o</t>
   </si>
   <si>
-    <t>led_manager.o</t>
-  </si>
-  <si>
     <t>motor_info.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_adc.o</t>
   </si>
   <si>
+    <t>jm_proto.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_uart.o</t>
   </si>
   <si>
-    <t>jm_proto.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_tim.o</t>
   </si>
   <si>
     <t>motor_param.o</t>
   </si>
   <si>
+    <t>stm32g4xx_hal_fdcan.o</t>
+  </si>
+  <si>
     <t>m_wm.l</t>
   </si>
   <si>
@@ -206,6 +215,9 @@
     <t>stm32g4xx_hal_rcc.o</t>
   </si>
   <si>
+    <t>jm_proto_can.o</t>
+  </si>
+  <si>
     <t>motion_param.o</t>
   </si>
   <si>
@@ -218,57 +230,54 @@
     <t>mf_w.l</t>
   </si>
   <si>
+    <t>dev_motor_phase_current.o</t>
+  </si>
+  <si>
+    <t>ctrl_transition.o</t>
+  </si>
+  <si>
+    <t>calib_config_runtime.o</t>
+  </si>
+  <si>
     <t>foc_core.o</t>
   </si>
   <si>
-    <t>dev_motor_phase_current.o</t>
-  </si>
-  <si>
-    <t>ctrl_transition.o</t>
-  </si>
-  <si>
-    <t>calib_config_runtime.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_fdcan.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_dma.o</t>
   </si>
   <si>
+    <t>current_loop.o</t>
+  </si>
+  <si>
+    <t>dev_mt6835.o</t>
+  </si>
+  <si>
     <t>multiturn_counter.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_rcc_ex.o</t>
   </si>
   <si>
-    <t>dev_mt6835.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_tim_ex.o</t>
   </si>
   <si>
+    <t>motor_profile.o</t>
+  </si>
+  <si>
+    <t>atan2f.o</t>
+  </si>
+  <si>
+    <t>motor_pid_autotune.o</t>
+  </si>
+  <si>
+    <t>dev_half_bridge.o</t>
+  </si>
+  <si>
+    <t>cascade_control.o</t>
+  </si>
+  <si>
     <t>foc_decoupling.o</t>
   </si>
   <si>
-    <t>atan2f.o</t>
-  </si>
-  <si>
-    <t>cascade_control.o</t>
-  </si>
-  <si>
-    <t>dev_half_bridge.o</t>
-  </si>
-  <si>
-    <t>motor_profile.o</t>
-  </si>
-  <si>
-    <t>motor_pid_autotune.o</t>
-  </si>
-  <si>
-    <t>current_loop.o</t>
-  </si>
-  <si>
     <t>crc16.o</t>
   </si>
   <si>
@@ -287,21 +296,24 @@
     <t>ctrl_transition_mgr.o</t>
   </si>
   <si>
+    <t>motor_info_calib.o</t>
+  </si>
+  <si>
     <t>drv_tim.o</t>
   </si>
   <si>
     <t>sinf.o</t>
   </si>
   <si>
-    <t>motor_info_calib.o</t>
-  </si>
-  <si>
     <t>rredf.o</t>
   </si>
   <si>
     <t>pid_core.o</t>
   </si>
   <si>
+    <t>dev_config.o</t>
+  </si>
+  <si>
     <t>cosf.o</t>
   </si>
   <si>
@@ -311,15 +323,15 @@
     <t>cmsis_os.o</t>
   </si>
   <si>
-    <t>dev_config.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_uart_ex.o</t>
   </si>
   <si>
     <t>gpio.o</t>
   </si>
   <si>
+    <t>drv_adc.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
@@ -329,9 +341,6 @@
     <t>dmul.o</t>
   </si>
   <si>
-    <t>drv_adc.o</t>
-  </si>
-  <si>
     <t>ddiv.o</t>
   </si>
   <si>
@@ -344,15 +353,15 @@
     <t>stm32g4xx_hal_i2c.o</t>
   </si>
   <si>
+    <t>stm32g4xx_it.o</t>
+  </si>
+  <si>
     <t>depilogue.o</t>
   </si>
   <si>
     <t>fmodf.o</t>
   </si>
   <si>
-    <t>stm32g4xx_it.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_i2c_ex.o</t>
   </si>
   <si>
@@ -368,30 +377,30 @@
     <t>arm_sin_f32.o</t>
   </si>
   <si>
+    <t>list.o</t>
+  </si>
+  <si>
+    <t>thread_period.o</t>
+  </si>
+  <si>
+    <t>motor_mode_mit.o</t>
+  </si>
+  <si>
     <t>motor_mode_velocity.o</t>
   </si>
   <si>
-    <t>list.o</t>
-  </si>
-  <si>
-    <t>motor_mode_mit.o</t>
-  </si>
-  <si>
-    <t>thread_period.o</t>
-  </si>
-  <si>
     <t>motor_mode_open_loop.o</t>
   </si>
   <si>
+    <t>floorf.o</t>
+  </si>
+  <si>
     <t>motor_mode_position.o</t>
   </si>
   <si>
     <t>motor_mode_current.o</t>
   </si>
   <si>
-    <t>floorf.o</t>
-  </si>
-  <si>
     <t>fepilogue.o</t>
   </si>
   <si>
@@ -407,15 +416,18 @@
     <t>motor_mode_test_sweep.o</t>
   </si>
   <si>
+    <t>dma.o</t>
+  </si>
+  <si>
+    <t>__dczerorl2.o</t>
+  </si>
+  <si>
     <t>motor_mode_torque.o</t>
   </si>
   <si>
     <t>motor_mode_profile_torque.o</t>
   </si>
   <si>
-    <t>__dczerorl2.o</t>
-  </si>
-  <si>
     <t>assert_report.o</t>
   </si>
   <si>
@@ -425,9 +437,6 @@
     <t>motor_mode_profile_velocity.o</t>
   </si>
   <si>
-    <t>dma.o</t>
-  </si>
-  <si>
     <t>motor_mode_duty.o</t>
   </si>
   <si>
@@ -464,12 +473,18 @@
     <t>funder.o</t>
   </si>
   <si>
+    <t>thread_commun.o</t>
+  </si>
+  <si>
     <t>motor_mode_idle.o</t>
   </si>
   <si>
     <t>motor_mode_hold.o</t>
   </si>
   <si>
+    <t>drv_delay.o</t>
+  </si>
+  <si>
     <t>fpclassifyf.o</t>
   </si>
   <si>
@@ -485,9 +500,6 @@
     <t>init.o</t>
   </si>
   <si>
-    <t>thread_commun.o</t>
-  </si>
-  <si>
     <t>llushr.o</t>
   </si>
   <si>
@@ -504,6 +516,9 @@
   </si>
   <si>
     <t>handlers.o</t>
+  </si>
+  <si>
+    <t>memcmp.o</t>
   </si>
   <si>
     <t>strncpy.o</t>
@@ -638,9 +653,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$169</c:f>
+              <c:f>ram_percent!$A$3:$A$175</c:f>
               <c:strCache>
-                <c:ptCount val="167"/>
+                <c:ptCount val="173"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -651,147 +666,153 @@
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>dev_commun_can.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>motor_info_storage.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>motor_pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>dev_power_monitor.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
+                  <c:v>adc.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
-                  <c:v>adc.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
+                  <c:v>drv_can.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>calib_level3_encoder.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
+                  <c:v>jm_proto_ops.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="35">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="36">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="37">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="38">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="39">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="40">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="41">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="42">
+                  <c:v>led_manager.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
-                  <c:v>jm_proto_ops.o</c:v>
-                </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="44">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="45">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="46">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="47">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="48">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="49">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="50">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="51">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
-                  <c:v>led_manager.o</c:v>
-                </c:pt>
-                <c:pt idx="166">
+                <c:pt idx="172">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -799,161 +820,167 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$169</c:f>
+              <c:f>ram_percent!$B$3:$B$175</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="167"/>
+                <c:ptCount val="173"/>
                 <c:pt idx="0">
-                  <c:v>43.23527145385742</c:v>
+                  <c:v>39.14816665649414</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.78774833679199</c:v>
+                  <c:v>9.767963409423828</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.78774833679199</c:v>
+                  <c:v>9.767963409423828</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.509757995605469</c:v>
+                  <c:v>8.947607040405273</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.383338928222656</c:v>
+                  <c:v>4.988910675048828</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.403592586517334</c:v>
+                  <c:v>4.874442577362061</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.329847812652588</c:v>
+                  <c:v>4.01593017578125</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.715373039245606</c:v>
+                  <c:v>3.930078983306885</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.696937084197998</c:v>
+                  <c:v>2.458684206008911</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.885748863220215</c:v>
+                  <c:v>2.441990852355957</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.9376069903373718</c:v>
+                  <c:v>1.707485795021057</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8954673409461975</c:v>
+                  <c:v>0.8489733338356018</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.7901182770729065</c:v>
+                  <c:v>0.8108172416687012</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6953040361404419</c:v>
+                  <c:v>0.7154269814491272</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.6004898548126221</c:v>
+                  <c:v>0.6391147971153259</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.5899549722671509</c:v>
+                  <c:v>0.543724536895752</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.5267454981803894</c:v>
+                  <c:v>0.5341854691505432</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.347652018070221</c:v>
+                  <c:v>0.4864903390407562</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.3371171355247498</c:v>
+                  <c:v>0.4769513309001923</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.2844425737857819</c:v>
+                  <c:v>0.3147878646850586</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2633727490901947</c:v>
+                  <c:v>0.3052488565444946</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2212331146001816</c:v>
+                  <c:v>0.2384756654500961</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2001632899045944</c:v>
+                  <c:v>0.2003195583820343</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.1896283775568008</c:v>
+                  <c:v>0.1812414973974228</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1896283775568008</c:v>
+                  <c:v>0.1717024743556976</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1896283775568008</c:v>
+                  <c:v>0.1717024743556976</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1685585677623749</c:v>
+                  <c:v>0.1717024743556976</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1158840134739876</c:v>
+                  <c:v>0.1621634513139725</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.105349101126194</c:v>
+                  <c:v>0.1526244282722473</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.09481418877840042</c:v>
+                  <c:v>0.1049292907118797</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.08427928388118744</c:v>
+                  <c:v>0.09539026767015457</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.06057573109865189</c:v>
+                  <c:v>0.08585123717784882</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.052674550563097</c:v>
+                  <c:v>0.07631221413612366</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.052674550563097</c:v>
+                  <c:v>0.0667731836438179</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.03160472959280014</c:v>
+                  <c:v>0.05484940111637116</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.03160472959280014</c:v>
+                  <c:v>0.04769513383507729</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03160472959280014</c:v>
+                  <c:v>0.04769513383507729</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.03160472959280014</c:v>
+                  <c:v>0.02861708030104637</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.02106982097029686</c:v>
+                  <c:v>0.02861708030104637</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.02106982097029686</c:v>
+                  <c:v>0.02861708030104637</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.01580236479640007</c:v>
+                  <c:v>0.02861708030104637</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.01053491048514843</c:v>
+                  <c:v>0.01907805353403091</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01053491048514843</c:v>
+                  <c:v>0.01907805353403091</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01053491048514843</c:v>
+                  <c:v>0.01907805353403091</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01053491048514843</c:v>
+                  <c:v>0.009539026767015457</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.01053491048514843</c:v>
+                  <c:v>0.009539026767015457</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.01053491048514843</c:v>
+                  <c:v>0.009539026767015457</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.01053491048514843</c:v>
+                  <c:v>0.009539026767015457</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.007901182398200035</c:v>
+                  <c:v>0.009539026767015457</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.005267455242574215</c:v>
-                </c:pt>
-                <c:pt idx="166">
+                  <c:v>0.009539026767015457</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.009539026767015457</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.007154270075261593</c:v>
+                </c:pt>
+                <c:pt idx="172">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1021,9 +1048,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$169</c:f>
+              <c:f>flash_percent!$A$3:$A$175</c:f>
               <c:strCache>
-                <c:ptCount val="167"/>
+                <c:ptCount val="173"/>
                 <c:pt idx="0">
                   <c:v>motor_info.o</c:v>
                 </c:pt>
@@ -1031,498 +1058,516 @@
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>jm_proto_ops.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>stm32g4xx_hal_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>stm32g4xx_hal_uart.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>jm_proto.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>stm32g4xx_hal_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>stm32g4xx_hal_tim.o</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>motor_param.o</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>jm_proto_ops.o</c:v>
+                  <c:v>motor_param.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>stm32g4xx_hal_fdcan.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>m_wm.l</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>stm32g4xx_hal_adc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>arm_cortexM4lf_math.lib</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>printfa.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
+                  <c:v>dev_commun_can.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>arm_common_tables.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
+                  <c:v>jm_proto_can.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>motion_param.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="20">
+                  <c:v>system_state.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>dev_power_monitor.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>stm32g4xx_hal_spi.o</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>mf_w.l</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>foc_core.o</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>dev_motor_phase_current.o</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>ctrl_transition.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>mf_w.l</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>dev_motor_phase_current.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>ctrl_transition.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>calib_config_runtime.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>foc_core.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>drv_can.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>calib_level3_encoder.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>motor_pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
-                  <c:v>system_state.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>calib_config_runtime.o</c:v>
-                </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="33">
+                  <c:v>jm_host_commun.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
-                  <c:v>calib_level3_encoder.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>stm32g4xx_hal_fdcan.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="35">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="36">
                   <c:v>drv_flash_g4.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="37">
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="38">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
-                  <c:v>multiturn_counter.o</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>dev_commun_uart.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
-                </c:pt>
                 <c:pt idx="39">
-                  <c:v>tim.o</c:v>
+                  <c:v>current_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
+                  <c:v>multiturn_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>dev_commun_uart.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>port.o</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>tim.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>foc_decoupling.o</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>jm_host_commun.o</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>atan2f.o</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>cascade_control.o</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>dev_half_bridge.o</c:v>
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>motor_profile.o</c:v>
                 </c:pt>
                 <c:pt idx="48">
+                  <c:v>atan2f.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>motor_pid_autotune.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
+                  <c:v>dev_half_bridge.o</c:v>
+                </c:pt>
+                <c:pt idx="51">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
-                  <c:v>current_loop.o</c:v>
-                </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
+                  <c:v>cascade_control.o</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>motor_info_storage.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>foc_decoupling.o</c:v>
+                </c:pt>
+                <c:pt idx="55">
                   <c:v>crc16.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="56">
+                  <c:v>adc.o</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="58">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="59">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
-                  <c:v>motor_info_storage.o</c:v>
-                </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="60">
                   <c:v>calib_ac_injection.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="61">
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="62">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="63">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
-                  <c:v>adc.o</c:v>
-                </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="64">
                   <c:v>stm32g4xx_hal_flash_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="65">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="66">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="67">
+                  <c:v>dev_motor.o</c:v>
+                </c:pt>
+                <c:pt idx="68">
                   <c:v>ctrl_transition_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
-                  <c:v>dev_motor.o</c:v>
-                </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="69">
+                  <c:v>motor_info_calib.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>led_manager.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="72">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="73">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="74">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
-                  <c:v>motor_info_calib.o</c:v>
-                </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="75">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="76">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="77">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="78">
+                  <c:v>dev_config.o</c:v>
+                </c:pt>
+                <c:pt idx="79">
                   <c:v>cosf.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="80">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="81">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
-                  <c:v>led_manager.o</c:v>
-                </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="82">
                   <c:v>cmsis_os.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
-                  <c:v>dev_config.o</c:v>
-                </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="83">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="84">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="85">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="86">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="87">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="88">
+                  <c:v>drv_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="89">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="90">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="91">
                   <c:v>drv_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="92">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
-                  <c:v>drv_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="93">
+                  <c:v>fdcan.o</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="95">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
-                  <c:v>fdcan.o</c:v>
-                </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="96">
                   <c:v>drv_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="97">
                   <c:v>stm32g4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="98">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="99">
+                  <c:v>stm32g4xx_it.o</c:v>
+                </c:pt>
+                <c:pt idx="100">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="101">
                   <c:v>fmodf.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
-                  <c:v>stm32g4xx_it.o</c:v>
-                </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="102">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="103">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="104">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="105">
                   <c:v>roundf.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="106">
                   <c:v>arm_cos_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="107">
                   <c:v>arm_sin_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="108">
+                  <c:v>stm32g4xx_hal.o</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>list.o</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>thread_period.o</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>motor_mode_mit.o</c:v>
+                </c:pt>
+                <c:pt idx="113">
                   <c:v>motor_mode_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
-                  <c:v>list.o</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>motor_mode_mit.o</c:v>
-                </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="114">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
-                  <c:v>thread_period.o</c:v>
-                </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="115">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="116">
                   <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="117">
+                  <c:v>floorf.o</c:v>
+                </c:pt>
+                <c:pt idx="118">
                   <c:v>motor_mode_position.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="119">
                   <c:v>motor_mode_current.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
-                  <c:v>floorf.o</c:v>
-                </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="120">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="121">
                   <c:v>user_interface.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
-                  <c:v>stm32g4xx_hal.o</c:v>
-                </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="122">
+                  <c:v>runtime_param.o</c:v>
+                </c:pt>
+                <c:pt idx="123">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="124">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="125">
                   <c:v>motor_mode_test_sweep.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="126">
+                  <c:v>dma.o</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>__dczerorl2.o</c:v>
+                </c:pt>
+                <c:pt idx="128">
                   <c:v>motor_mode_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="129">
                   <c:v>motor_mode_profile_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
-                  <c:v>__dczerorl2.o</c:v>
-                </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="130">
                   <c:v>assert_report.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="131">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="132">
                   <c:v>frem.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="133">
                   <c:v>motor_mode_profile_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
-                  <c:v>dma.o</c:v>
-                </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="134">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="135">
                   <c:v>motor_mode_duty.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="136">
                   <c:v>frnd.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="137">
                   <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="138">
                   <c:v>sqrtf.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="139">
                   <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="140">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="141">
                   <c:v>utils.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="142">
                   <c:v>control_irq.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="143">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="144">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="145">
                   <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="146">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="147">
                   <c:v>funder.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="148">
+                  <c:v>thread_commun.o</c:v>
+                </c:pt>
+                <c:pt idx="149">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="150">
                   <c:v>motor_mode_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="146">
+                <c:pt idx="151">
                   <c:v>motor_mode_hold.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="152">
+                  <c:v>drv_delay.o</c:v>
+                </c:pt>
+                <c:pt idx="153">
                   <c:v>fpclassifyf.o</c:v>
                 </c:pt>
-                <c:pt idx="148">
+                <c:pt idx="154">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="149">
+                <c:pt idx="155">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="150">
+                <c:pt idx="156">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="151">
+                <c:pt idx="157">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="152">
-                  <c:v>thread_commun.o</c:v>
-                </c:pt>
-                <c:pt idx="153">
+                <c:pt idx="158">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="154">
+                <c:pt idx="159">
                   <c:v>thread_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="155">
+                <c:pt idx="160">
                   <c:v>thread_display.o</c:v>
                 </c:pt>
-                <c:pt idx="156">
+                <c:pt idx="161">
                   <c:v>thread_control.o</c:v>
                 </c:pt>
-                <c:pt idx="157">
+                <c:pt idx="162">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="158">
+                <c:pt idx="163">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="159">
+                <c:pt idx="164">
+                  <c:v>memcmp.o</c:v>
+                </c:pt>
+                <c:pt idx="165">
                   <c:v>strncpy.o</c:v>
                 </c:pt>
-                <c:pt idx="160">
+                <c:pt idx="166">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="161">
+                <c:pt idx="167">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="162">
+                <c:pt idx="168">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="163">
+                <c:pt idx="169">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="164">
+                <c:pt idx="170">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="165">
+                <c:pt idx="171">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="166">
+                <c:pt idx="172">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1530,509 +1575,527 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$169</c:f>
+              <c:f>flash_percent!$B$3:$B$175</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="167"/>
+                <c:ptCount val="173"/>
                 <c:pt idx="0">
-                  <c:v>10.80426692962647</c:v>
+                  <c:v>4.232955455780029</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.953004121780396</c:v>
+                  <c:v>3.792171239852905</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.100035667419434</c:v>
+                  <c:v>3.315696001052856</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.039502620697022</c:v>
+                  <c:v>3.283574104309082</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.984472274780273</c:v>
+                  <c:v>3.160439968109131</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.92577338218689</c:v>
+                  <c:v>2.957001209259033</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.62494158744812</c:v>
+                  <c:v>2.846359014511108</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.612101078033447</c:v>
+                  <c:v>2.56439995765686</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.575414419174194</c:v>
+                  <c:v>2.542985439300537</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.177362442016602</c:v>
+                  <c:v>2.141461372375488</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.157184600830078</c:v>
+                  <c:v>2.11826229095459</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.153516054153442</c:v>
+                  <c:v>2.098632097244263</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.149847269058228</c:v>
+                  <c:v>2.095062971115112</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.034283876419067</c:v>
+                  <c:v>2.091493844985962</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.882033586502075</c:v>
+                  <c:v>1.979067206382752</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.742623686790466</c:v>
+                  <c:v>1.909469723701477</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.656409621238709</c:v>
+                  <c:v>1.830949425697327</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.474809885025024</c:v>
+                  <c:v>1.695323586463928</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.379424214363098</c:v>
+                  <c:v>1.695323586463928</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.278535485267639</c:v>
+                  <c:v>1.611449718475342</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.20883047580719</c:v>
+                  <c:v>1.454409122467041</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.168475031852722</c:v>
+                  <c:v>1.434779167175293</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.118947863578796</c:v>
+                  <c:v>1.431210041046143</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.10060441493988</c:v>
+                  <c:v>1.243832111358643</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.089598417282105</c:v>
+                  <c:v>1.181372880935669</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.9960470199584961</c:v>
+                  <c:v>1.176019191741943</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.9905439615249634</c:v>
+                  <c:v>1.088576197624207</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.9722005724906921</c:v>
+                  <c:v>1.070730686187744</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.9428511261940002</c:v>
+                  <c:v>1.067161560058594</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.9226733446121216</c:v>
+                  <c:v>1.043962359428406</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.9043299555778503</c:v>
+                  <c:v>1.026116847991943</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.8969926238059998</c:v>
+                  <c:v>0.9654421806335449</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.8804835081100464</c:v>
+                  <c:v>0.9368893504142761</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.8768148422241211</c:v>
+                  <c:v>0.9333202242851257</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.8025240302085877</c:v>
+                  <c:v>0.9172592759132385</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.7630857229232788</c:v>
+                  <c:v>0.8655073046684265</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.7520796656608582</c:v>
+                  <c:v>0.8565845489501953</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7319019436836243</c:v>
+                  <c:v>0.8530154228210449</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.719061553478241</c:v>
+                  <c:v>0.7807410955429077</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.6933807730674744</c:v>
+                  <c:v>0.7637878656387329</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.6860434412956238</c:v>
+                  <c:v>0.7584342360496521</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.6603626608848572</c:v>
+                  <c:v>0.7423732876777649</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.6548596024513245</c:v>
+                  <c:v>0.7316659688949585</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.6365162134170532</c:v>
+                  <c:v>0.7120358943939209</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.6273444890975952</c:v>
+                  <c:v>0.6995440721511841</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.6108354330062866</c:v>
+                  <c:v>0.6745603084564209</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.5906577110290527</c:v>
+                  <c:v>0.6424384117126465</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.5888233780860901</c:v>
+                  <c:v>0.6424384117126465</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.5814859867095947</c:v>
+                  <c:v>0.6103165149688721</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.5686455965042114</c:v>
+                  <c:v>0.5978246331214905</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.5392961502075195</c:v>
+                  <c:v>0.5746254920959473</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5099467039108276</c:v>
+                  <c:v>0.5532108545303345</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.4916033148765564</c:v>
+                  <c:v>0.5514262914657593</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.4695912301540375</c:v>
+                  <c:v>0.5210889577865601</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.4659225344657898</c:v>
+                  <c:v>0.5103816390037537</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.4659225344657898</c:v>
+                  <c:v>0.4961052238941193</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.4622538685798645</c:v>
+                  <c:v>0.4889670014381409</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4604195058345795</c:v>
+                  <c:v>0.4639832973480225</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4604195058345795</c:v>
+                  <c:v>0.4568451046943665</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4567508399486542</c:v>
+                  <c:v>0.4532759785652161</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4512478113174439</c:v>
+                  <c:v>0.4497068822383881</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4365730881690979</c:v>
+                  <c:v>0.4479223489761353</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4292357265949249</c:v>
+                  <c:v>0.4479223489761353</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4182296693325043</c:v>
+                  <c:v>0.4443532228469849</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.4090579748153687</c:v>
+                  <c:v>0.4247231781482697</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.3989691138267517</c:v>
+                  <c:v>0.4175849556922913</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.3760398328304291</c:v>
+                  <c:v>0.4068776667118073</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3742054998874664</c:v>
+                  <c:v>0.4059853851795197</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3668681383132935</c:v>
+                  <c:v>0.3979549109935761</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3668681383132935</c:v>
+                  <c:v>0.3801093995571137</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3650338053703308</c:v>
+                  <c:v>0.3801093995571137</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3411873579025269</c:v>
+                  <c:v>0.3658329844474793</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3356843590736389</c:v>
+                  <c:v>0.3640484213829041</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3155066072940826</c:v>
+                  <c:v>0.3569102287292481</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3081692457199097</c:v>
+                  <c:v>0.3569102287292481</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3063348829746246</c:v>
+                  <c:v>0.3319265246391296</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.304500550031662</c:v>
+                  <c:v>0.3265728652477264</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.304500550031662</c:v>
+                  <c:v>0.3069427907466888</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.297163188457489</c:v>
+                  <c:v>0.3060505092144013</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.29257732629776</c:v>
+                  <c:v>0.2998045980930328</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.2824884653091431</c:v>
+                  <c:v>0.2980200350284576</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.2641450464725494</c:v>
+                  <c:v>0.2962355017662048</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.2494703382253647</c:v>
+                  <c:v>0.2890972793102264</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2494703382253647</c:v>
+                  <c:v>0.274820864200592</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2311269342899323</c:v>
+                  <c:v>0.26054447889328</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2219552248716354</c:v>
+                  <c:v>0.2426989525556564</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2146178632974625</c:v>
+                  <c:v>0.2426989525556564</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2127835154533386</c:v>
+                  <c:v>0.224853441119194</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2091148346662521</c:v>
+                  <c:v>0.219499796628952</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2072805017232895</c:v>
+                  <c:v>0.2159306854009628</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.203611820936203</c:v>
+                  <c:v>0.2087924778461456</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2017774730920792</c:v>
+                  <c:v>0.2070079296827316</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2017774730920792</c:v>
+                  <c:v>0.2034388333559036</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.2017774730920792</c:v>
+                  <c:v>0.2034388333559036</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1871027499437332</c:v>
+                  <c:v>0.1980851739645004</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1760967075824738</c:v>
+                  <c:v>0.1963006258010864</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1705936789512634</c:v>
+                  <c:v>0.1963006258010864</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1614219844341278</c:v>
+                  <c:v>0.182024210691452</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1614219844341278</c:v>
+                  <c:v>0.1713169068098068</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1614219844341278</c:v>
+                  <c:v>0.1677478104829788</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1577533036470413</c:v>
+                  <c:v>0.1659632623195648</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.144912913441658</c:v>
+                  <c:v>0.1570405066013336</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1412442326545715</c:v>
+                  <c:v>0.1570405066013336</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1394098997116089</c:v>
+                  <c:v>0.1534713953733444</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1320725232362747</c:v>
+                  <c:v>0.1409795433282852</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1302381902933121</c:v>
+                  <c:v>0.137410432100296</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1265695095062256</c:v>
+                  <c:v>0.135625883936882</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1247351691126823</c:v>
+                  <c:v>0.1284876763820648</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1210664883255959</c:v>
+                  <c:v>0.1267031282186508</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1155634671449661</c:v>
+                  <c:v>0.1231340318918228</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1100604385137558</c:v>
+                  <c:v>0.1213494762778282</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1100604385137558</c:v>
+                  <c:v>0.1142112761735916</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1082260981202126</c:v>
+                  <c:v>0.1142112761735916</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1063917577266693</c:v>
+                  <c:v>0.112426720559597</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1063917577266693</c:v>
+                  <c:v>0.112426720559597</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1027230769395828</c:v>
+                  <c:v>0.1070730686187744</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1008887365460396</c:v>
+                  <c:v>0.1017194166779518</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.09722005575895309</c:v>
+                  <c:v>0.09993486106395721</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.09722005575895309</c:v>
+                  <c:v>0.09993486106395721</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.08988269418478012</c:v>
+                  <c:v>0.09993486106395721</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.08988269418478012</c:v>
+                  <c:v>0.09815031290054321</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.08437967300415039</c:v>
+                  <c:v>0.09815031290054321</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.0807109922170639</c:v>
+                  <c:v>0.09636576473712921</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.0807109922170639</c:v>
+                  <c:v>0.08744300901889801</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.07887665182352066</c:v>
+                  <c:v>0.08744300901889801</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.07704231142997742</c:v>
+                  <c:v>0.08208934962749481</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.07704231142997742</c:v>
+                  <c:v>0.08208934962749481</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.07520797103643417</c:v>
+                  <c:v>0.07673569768667221</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.07520797103643417</c:v>
+                  <c:v>0.07495114952325821</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.06970494985580444</c:v>
+                  <c:v>0.07495114952325821</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.06970494985580444</c:v>
+                  <c:v>0.07495114952325821</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.06053324416279793</c:v>
+                  <c:v>0.07495114952325821</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.0550302192568779</c:v>
+                  <c:v>0.07316659390926361</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.0550302192568779</c:v>
+                  <c:v>0.06959749758243561</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.05319587886333466</c:v>
+                  <c:v>0.06781294196844101</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.04952719807624817</c:v>
+                  <c:v>0.05889018625020981</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.04952719807624817</c:v>
+                  <c:v>0.05353653430938721</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.04769285768270493</c:v>
+                  <c:v>0.05353653430938721</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.04769285768270493</c:v>
+                  <c:v>0.05175198242068291</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.04402417689561844</c:v>
+                  <c:v>0.04818288236856461</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.04402417689561844</c:v>
+                  <c:v>0.04818288236856461</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.04402417689561844</c:v>
+                  <c:v>0.04639833047986031</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.04035549610853195</c:v>
+                  <c:v>0.04639833047986031</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.04035549610853195</c:v>
+                  <c:v>0.04282922670245171</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04035549610853195</c:v>
+                  <c:v>0.04282922670245171</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04035549610853195</c:v>
+                  <c:v>0.04282922670245171</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04035549610853195</c:v>
+                  <c:v>0.03926012665033341</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.03485247492790222</c:v>
+                  <c:v>0.03926012665033341</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.03301813080906868</c:v>
+                  <c:v>0.03926012665033341</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.03301813080906868</c:v>
+                  <c:v>0.03926012665033341</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03301813080906868</c:v>
+                  <c:v>0.03926012665033341</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03301813080906868</c:v>
+                  <c:v>0.03926012665033341</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03301813080906868</c:v>
+                  <c:v>0.03569102287292481</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.02934945188462734</c:v>
+                  <c:v>0.03390647098422051</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.02934945188462734</c:v>
+                  <c:v>0.03212191909551621</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.02934945188462734</c:v>
+                  <c:v>0.03212191909551621</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.02934945188462734</c:v>
+                  <c:v>0.03212191909551621</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.02751510962843895</c:v>
+                  <c:v>0.03212191909551621</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.02751510962843895</c:v>
+                  <c:v>0.0285528190433979</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.02201208844780922</c:v>
+                  <c:v>0.0285528190433979</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.01467472594231367</c:v>
+                  <c:v>0.0285528190433979</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.007337362971156836</c:v>
+                  <c:v>0.0285528190433979</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.007337362971156836</c:v>
+                  <c:v>0.0267682671546936</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.003668681485578418</c:v>
+                  <c:v>0.0267682671546936</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.003668681485578418</c:v>
+                  <c:v>0.02319916523993015</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.003668681485578418</c:v>
+                  <c:v>0.02141461335122585</c:v>
                 </c:pt>
                 <c:pt idx="166">
+                  <c:v>0.01427640952169895</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.007138204760849476</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.007138204760849476</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.003569102380424738</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.003569102380424738</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.003569102380424738</c:v>
+                </c:pt>
+                <c:pt idx="172">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2137,8 +2200,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H169" totalsRowCount="1">
-  <autoFilter ref="A2:H168"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H175" totalsRowCount="1">
+  <autoFilter ref="A2:H174"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -2154,8 +2217,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H169" totalsRowCount="1">
-  <autoFilter ref="A2:H168"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H175" totalsRowCount="1">
+  <autoFilter ref="A2:H174"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2455,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2468,28 +2531,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2497,7 +2560,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>43.23527145385742</v>
+        <v>39.14816665649414</v>
       </c>
       <c r="C3" s="1">
         <v>16416</v>
@@ -2523,7 +2586,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>10.78774833679199</v>
+        <v>9.767963409423828</v>
       </c>
       <c r="C4" s="1">
         <v>4096</v>
@@ -2549,7 +2612,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>10.78774833679199</v>
+        <v>9.767963409423828</v>
       </c>
       <c r="C5" s="1">
         <v>4096</v>
@@ -2575,25 +2638,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>5.509757995605469</v>
+        <v>8.947607040405273</v>
       </c>
       <c r="C6" s="1">
-        <v>2092</v>
+        <v>3752</v>
       </c>
       <c r="D6" s="1">
-        <v>508</v>
+        <v>2140</v>
       </c>
       <c r="E6" s="1">
-        <v>492</v>
+        <v>2136</v>
       </c>
       <c r="F6" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" s="1">
-        <v>2092</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2601,25 +2664,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>5.383338928222656</v>
+        <v>4.988910675048828</v>
       </c>
       <c r="C7" s="1">
-        <v>2044</v>
+        <v>2092</v>
       </c>
       <c r="D7" s="1">
-        <v>620</v>
+        <v>584</v>
       </c>
       <c r="E7" s="1">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F7" s="1">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>2044</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2627,25 +2690,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.403592586517334</v>
+        <v>4.874442577362061</v>
       </c>
       <c r="C8" s="1">
-        <v>1672</v>
+        <v>2044</v>
       </c>
       <c r="D8" s="1">
-        <v>1188</v>
+        <v>620</v>
       </c>
       <c r="E8" s="1">
-        <v>1188</v>
+        <v>564</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>1672</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2653,25 +2716,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>4.329847812652588</v>
+        <v>4.01593017578125</v>
       </c>
       <c r="C9" s="1">
-        <v>1644</v>
+        <v>1684</v>
       </c>
       <c r="D9" s="1">
-        <v>820</v>
+        <v>1324</v>
       </c>
       <c r="E9" s="1">
-        <v>816</v>
+        <v>1324</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>1640</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2679,25 +2742,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.715373039245606</v>
+        <v>3.930078983306885</v>
       </c>
       <c r="C10" s="1">
-        <v>1031</v>
+        <v>1648</v>
       </c>
       <c r="D10" s="1">
-        <v>498</v>
+        <v>820</v>
       </c>
       <c r="E10" s="1">
-        <v>498</v>
+        <v>816</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="1">
-        <v>1031</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2705,25 +2768,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.696937084197998</v>
+        <v>2.458684206008911</v>
       </c>
       <c r="C11" s="1">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="D11" s="1">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E11" s="1">
-        <v>36</v>
+        <v>498</v>
       </c>
       <c r="F11" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>1024</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2731,25 +2794,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.885748863220215</v>
+        <v>2.441990852355957</v>
       </c>
       <c r="C12" s="1">
-        <v>716</v>
+        <v>1024</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="E12" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>716</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2757,25 +2820,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.9376069903373718</v>
+        <v>1.707485795021057</v>
       </c>
       <c r="C13" s="1">
-        <v>356</v>
+        <v>716</v>
       </c>
       <c r="D13" s="1">
-        <v>1086</v>
+        <v>108</v>
       </c>
       <c r="E13" s="1">
-        <v>730</v>
+        <v>108</v>
       </c>
       <c r="F13" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>352</v>
+        <v>716</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2783,25 +2846,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.8954673409461975</v>
+        <v>0.8489733338356018</v>
       </c>
       <c r="C14" s="1">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="D14" s="1">
-        <v>344</v>
+        <v>1050</v>
       </c>
       <c r="E14" s="1">
-        <v>344</v>
+        <v>694</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" s="1">
-        <v>340</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2809,25 +2872,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.7901182770729065</v>
+        <v>0.8108172416687012</v>
       </c>
       <c r="C15" s="1">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="D15" s="1">
-        <v>2344</v>
+        <v>344</v>
       </c>
       <c r="E15" s="1">
-        <v>2284</v>
+        <v>344</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>240</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2835,25 +2898,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.6953040361404419</v>
+        <v>0.7154269814491272</v>
       </c>
       <c r="C16" s="1">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="D16" s="1">
-        <v>1504</v>
+        <v>2344</v>
       </c>
       <c r="E16" s="1">
-        <v>1504</v>
+        <v>2284</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H16" s="1">
-        <v>264</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2861,16 +2924,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.6004898548126221</v>
+        <v>0.6391147971153259</v>
       </c>
       <c r="C17" s="1">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="D17" s="1">
-        <v>756</v>
+        <v>1604</v>
       </c>
       <c r="E17" s="1">
-        <v>756</v>
+        <v>1604</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2879,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>228</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2887,16 +2950,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.5899549722671509</v>
+        <v>0.543724536895752</v>
       </c>
       <c r="C18" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D18" s="1">
-        <v>242</v>
+        <v>756</v>
       </c>
       <c r="E18" s="1">
-        <v>242</v>
+        <v>756</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -2905,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2913,16 +2976,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.5267454981803894</v>
+        <v>0.5341854691505432</v>
       </c>
       <c r="C19" s="1">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="D19" s="1">
-        <v>332</v>
+        <v>242</v>
       </c>
       <c r="E19" s="1">
-        <v>332</v>
+        <v>242</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2931,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>200</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -2939,25 +3002,25 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.347652018070221</v>
+        <v>0.4864903390407562</v>
       </c>
       <c r="C20" s="1">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="D20" s="1">
-        <v>4310</v>
+        <v>548</v>
       </c>
       <c r="E20" s="1">
-        <v>4298</v>
+        <v>548</v>
       </c>
       <c r="F20" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>132</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -2965,16 +3028,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.3371171355247498</v>
+        <v>0.4769513309001923</v>
       </c>
       <c r="C21" s="1">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="D21" s="1">
-        <v>120</v>
+        <v>332</v>
       </c>
       <c r="E21" s="1">
-        <v>120</v>
+        <v>332</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2983,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>128</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -2991,25 +3054,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.2844425737857819</v>
+        <v>0.3147878646850586</v>
       </c>
       <c r="C22" s="1">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="D22" s="1">
-        <v>492</v>
+        <v>4250</v>
       </c>
       <c r="E22" s="1">
-        <v>492</v>
+        <v>4238</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>108</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3017,16 +3080,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2633727490901947</v>
+        <v>0.3052488565444946</v>
       </c>
       <c r="C23" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="D23" s="1">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="E23" s="1">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -3035,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3043,16 +3106,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2212331146001816</v>
+        <v>0.2384756654500961</v>
       </c>
       <c r="C24" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D24" s="1">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="E24" s="1">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -3061,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3069,16 +3132,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2001632899045944</v>
+        <v>0.2003195583820343</v>
       </c>
       <c r="C25" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D25" s="1">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="E25" s="1">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -3087,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3095,25 +3158,25 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.1896283775568008</v>
+        <v>0.1812414973974228</v>
       </c>
       <c r="C26" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D26" s="1">
-        <v>400</v>
+        <v>136</v>
       </c>
       <c r="E26" s="1">
-        <v>392</v>
+        <v>136</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3121,25 +3184,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1896283775568008</v>
+        <v>0.1717024743556976</v>
       </c>
       <c r="C27" s="1">
         <v>72</v>
       </c>
       <c r="D27" s="1">
-        <v>1028</v>
+        <v>400</v>
       </c>
       <c r="E27" s="1">
-        <v>468</v>
+        <v>392</v>
       </c>
       <c r="F27" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H27" s="1">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3147,25 +3210,25 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1896283775568008</v>
+        <v>0.1717024743556976</v>
       </c>
       <c r="C28" s="1">
         <v>72</v>
       </c>
       <c r="D28" s="1">
-        <v>978</v>
+        <v>1028</v>
       </c>
       <c r="E28" s="1">
-        <v>966</v>
+        <v>468</v>
       </c>
       <c r="F28" s="1">
-        <v>12</v>
+        <v>512</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H28" s="1">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3173,25 +3236,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1685585677623749</v>
+        <v>0.1717024743556976</v>
       </c>
       <c r="C29" s="1">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D29" s="1">
-        <v>288</v>
+        <v>970</v>
       </c>
       <c r="E29" s="1">
-        <v>288</v>
+        <v>958</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3199,25 +3262,25 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1158840134739876</v>
+        <v>0.1621634513139725</v>
       </c>
       <c r="C30" s="1">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D30" s="1">
-        <v>408</v>
+        <v>292</v>
       </c>
       <c r="E30" s="1">
-        <v>344</v>
+        <v>292</v>
       </c>
       <c r="F30" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3225,25 +3288,25 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.105349101126194</v>
+        <v>0.1526244282722473</v>
       </c>
       <c r="C31" s="1">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1">
-        <v>76</v>
+        <v>1150</v>
       </c>
       <c r="E31" s="1">
-        <v>76</v>
+        <v>1126</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H31" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3251,25 +3314,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.09481418877840042</v>
+        <v>0.1049292907118797</v>
       </c>
       <c r="C32" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D32" s="1">
-        <v>1006</v>
+        <v>408</v>
       </c>
       <c r="E32" s="1">
-        <v>994</v>
+        <v>344</v>
       </c>
       <c r="F32" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H32" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3277,25 +3340,25 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.08427928388118744</v>
+        <v>0.09539026767015457</v>
       </c>
       <c r="C33" s="1">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D33" s="1">
-        <v>456</v>
+        <v>76</v>
       </c>
       <c r="E33" s="1">
-        <v>424</v>
+        <v>76</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3303,25 +3366,25 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.06057573109865189</v>
+        <v>0.08585123717784882</v>
       </c>
       <c r="C34" s="1">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D34" s="1">
-        <v>435</v>
+        <v>1082</v>
       </c>
       <c r="E34" s="1">
-        <v>400</v>
+        <v>1070</v>
       </c>
       <c r="F34" s="1">
         <v>12</v>
       </c>
       <c r="G34" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3329,25 +3392,25 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.052674550563097</v>
+        <v>0.07631221413612366</v>
       </c>
       <c r="C35" s="1">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D35" s="1">
-        <v>192</v>
+        <v>456</v>
       </c>
       <c r="E35" s="1">
-        <v>192</v>
+        <v>424</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H35" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3355,22 +3418,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.052674550563097</v>
+        <v>0.0667731836438179</v>
       </c>
       <c r="C36" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D36" s="1">
-        <v>694</v>
+        <v>3716</v>
       </c>
       <c r="E36" s="1">
-        <v>674</v>
+        <v>3232</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="G36" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -3381,22 +3444,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.03160472959280014</v>
+        <v>0.05484940111637116</v>
       </c>
       <c r="C37" s="1">
+        <v>23</v>
+      </c>
+      <c r="D37" s="1">
+        <v>455</v>
+      </c>
+      <c r="E37" s="1">
+        <v>420</v>
+      </c>
+      <c r="F37" s="1">
         <v>12</v>
       </c>
-      <c r="D37" s="1">
-        <v>106</v>
-      </c>
-      <c r="E37" s="1">
-        <v>94</v>
-      </c>
-      <c r="F37" s="1">
-        <v>0</v>
-      </c>
       <c r="G37" s="1">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -3407,25 +3470,25 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.03160472959280014</v>
+        <v>0.04769513383507729</v>
       </c>
       <c r="C38" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D38" s="1">
-        <v>798</v>
+        <v>192</v>
       </c>
       <c r="E38" s="1">
-        <v>786</v>
+        <v>192</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3433,22 +3496,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03160472959280014</v>
+        <v>0.04769513383507729</v>
       </c>
       <c r="C39" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D39" s="1">
-        <v>126</v>
+        <v>1046</v>
       </c>
       <c r="E39" s="1">
-        <v>102</v>
+        <v>1026</v>
       </c>
       <c r="F39" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -3459,19 +3522,19 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.03160472959280014</v>
+        <v>0.02861708030104637</v>
       </c>
       <c r="C40" s="1">
         <v>12</v>
       </c>
       <c r="D40" s="1">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="E40" s="1">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="F40" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
         <v>12</v>
@@ -3485,22 +3548,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.02106982097029686</v>
+        <v>0.02861708030104637</v>
       </c>
       <c r="C41" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D41" s="1">
-        <v>2848</v>
+        <v>798</v>
       </c>
       <c r="E41" s="1">
-        <v>2840</v>
+        <v>786</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -3511,22 +3574,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.02106982097029686</v>
+        <v>0.02861708030104637</v>
       </c>
       <c r="C42" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D42" s="1">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="E42" s="1">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="F42" s="1">
         <v>12</v>
       </c>
       <c r="G42" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -3537,22 +3600,22 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.01580236479640007</v>
+        <v>0.02861708030104637</v>
       </c>
       <c r="C43" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D43" s="1">
-        <v>2808</v>
+        <v>172</v>
       </c>
       <c r="E43" s="1">
-        <v>2354</v>
+        <v>148</v>
       </c>
       <c r="F43" s="1">
-        <v>448</v>
+        <v>12</v>
       </c>
       <c r="G43" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -3563,22 +3626,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.01053491048514843</v>
+        <v>0.01907805353403091</v>
       </c>
       <c r="C44" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1">
-        <v>4</v>
+        <v>2874</v>
       </c>
       <c r="E44" s="1">
-        <v>0</v>
+        <v>2866</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3589,22 +3652,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01053491048514843</v>
+        <v>0.01907805353403091</v>
       </c>
       <c r="C45" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1">
-        <v>16</v>
+        <v>426</v>
       </c>
       <c r="E45" s="1">
-        <v>12</v>
+        <v>418</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -3615,22 +3678,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01053491048514843</v>
+        <v>0.01907805353403091</v>
       </c>
       <c r="C46" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D46" s="1">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E46" s="1">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F46" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G46" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -3641,19 +3704,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01053491048514843</v>
+        <v>0.009539026767015457</v>
       </c>
       <c r="C47" s="1">
         <v>4</v>
       </c>
       <c r="D47" s="1">
-        <v>1080</v>
+        <v>4</v>
       </c>
       <c r="E47" s="1">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="F47" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1">
         <v>4</v>
@@ -3667,16 +3730,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.01053491048514843</v>
+        <v>0.009539026767015457</v>
       </c>
       <c r="C48" s="1">
         <v>4</v>
       </c>
       <c r="D48" s="1">
-        <v>272</v>
+        <v>16</v>
       </c>
       <c r="E48" s="1">
-        <v>268</v>
+        <v>12</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3693,19 +3756,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.01053491048514843</v>
+        <v>0.009539026767015457</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
       </c>
       <c r="D49" s="1">
-        <v>502</v>
+        <v>44</v>
       </c>
       <c r="E49" s="1">
-        <v>498</v>
+        <v>16</v>
       </c>
       <c r="F49" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G49" s="1">
         <v>4</v>
@@ -3719,19 +3782,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.01053491048514843</v>
+        <v>0.009539026767015457</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
       </c>
       <c r="D50" s="1">
-        <v>84</v>
+        <v>1630</v>
       </c>
       <c r="E50" s="1">
-        <v>48</v>
+        <v>1290</v>
       </c>
       <c r="F50" s="1">
-        <v>32</v>
+        <v>336</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -3745,22 +3808,22 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.007901182398200035</v>
+        <v>0.009539026767015457</v>
       </c>
       <c r="C51" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" s="1">
-        <v>875</v>
+        <v>272</v>
       </c>
       <c r="E51" s="1">
-        <v>872</v>
+        <v>268</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="1">
         <v>0</v>
@@ -3771,56 +3834,108 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.005267455242574215</v>
+        <v>0.009539026767015457</v>
       </c>
       <c r="C52" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D52" s="1">
-        <v>332</v>
+        <v>502</v>
       </c>
       <c r="E52" s="1">
-        <v>330</v>
+        <v>498</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H52" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8">
-      <c r="A169" t="s">
-        <v>169</v>
-      </c>
-      <c r="B169">
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.009539026767015457</v>
+      </c>
+      <c r="C53" s="1">
+        <v>4</v>
+      </c>
+      <c r="D53" s="1">
+        <v>84</v>
+      </c>
+      <c r="E53" s="1">
+        <v>48</v>
+      </c>
+      <c r="F53" s="1">
+        <v>32</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.007154270075261593</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1">
+        <v>875</v>
+      </c>
+      <c r="E54" s="1">
+        <v>872</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>174</v>
+      </c>
+      <c r="B175">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C169">
+      <c r="C175">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D169">
+      <c r="D175">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E169">
+      <c r="E175">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F169">
+      <c r="F175">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G169">
+      <c r="G175">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H169">
+      <c r="H175">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -3836,7 +3951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -3849,48 +3964,48 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" t="s">
         <v>177</v>
       </c>
-      <c r="C2" t="s">
-        <v>172</v>
-      </c>
       <c r="D2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G2" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H2" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2">
-        <v>10.80426692962647</v>
+        <v>4.232955455780029</v>
       </c>
       <c r="C3" s="1">
-        <v>11780</v>
+        <v>4744</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>11780</v>
+        <v>3132</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>1612</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -3901,19 +4016,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2">
-        <v>3.953004121780396</v>
+        <v>3.792171239852905</v>
       </c>
       <c r="C4" s="1">
-        <v>4310</v>
+        <v>4250</v>
       </c>
       <c r="D4" s="1">
         <v>132</v>
       </c>
       <c r="E4" s="1">
-        <v>4298</v>
+        <v>4238</v>
       </c>
       <c r="F4" s="1">
         <v>12</v>
@@ -3927,25 +4042,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2">
-        <v>3.100035667419434</v>
+        <v>3.315696001052856</v>
       </c>
       <c r="C5" s="1">
-        <v>3380</v>
+        <v>3716</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1">
-        <v>3380</v>
+        <v>3232</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>456</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -3953,22 +4068,22 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2">
-        <v>3.039502620697022</v>
+        <v>3.283574104309082</v>
       </c>
       <c r="C6" s="1">
-        <v>3314</v>
+        <v>3680</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>3290</v>
+        <v>3680</v>
       </c>
       <c r="F6" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -3979,19 +4094,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" s="2">
-        <v>2.984472274780273</v>
+        <v>3.160439968109131</v>
       </c>
       <c r="C7" s="1">
-        <v>3254</v>
+        <v>3542</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>3254</v>
+        <v>3542</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -4005,22 +4120,22 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" s="2">
-        <v>2.92577338218689</v>
+        <v>2.957001209259033</v>
       </c>
       <c r="C8" s="1">
-        <v>3190</v>
+        <v>3314</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>3190</v>
+        <v>3290</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -4031,22 +4146,22 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B9" s="2">
-        <v>2.62494158744812</v>
+        <v>2.846359014511108</v>
       </c>
       <c r="C9" s="1">
-        <v>2862</v>
+        <v>3190</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>2518</v>
+        <v>3190</v>
       </c>
       <c r="F9" s="1">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -4057,19 +4172,19 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2">
-        <v>2.612101078033447</v>
+        <v>2.56439995765686</v>
       </c>
       <c r="C10" s="1">
-        <v>2848</v>
+        <v>2874</v>
       </c>
       <c r="D10" s="1">
         <v>8</v>
       </c>
       <c r="E10" s="1">
-        <v>2840</v>
+        <v>2866</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -4083,25 +4198,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2">
-        <v>2.575414419174194</v>
+        <v>2.542985439300537</v>
       </c>
       <c r="C11" s="1">
-        <v>2808</v>
+        <v>2850</v>
       </c>
       <c r="D11" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>2354</v>
+        <v>2506</v>
       </c>
       <c r="F11" s="1">
-        <v>448</v>
+        <v>344</v>
       </c>
       <c r="G11" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -4109,22 +4224,22 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2">
-        <v>2.177362442016602</v>
+        <v>2.141461372375488</v>
       </c>
       <c r="C12" s="1">
-        <v>2374</v>
+        <v>2400</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>2342</v>
+        <v>2384</v>
       </c>
       <c r="F12" s="1">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -4135,22 +4250,22 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2">
-        <v>2.157184600830078</v>
+        <v>2.11826229095459</v>
       </c>
       <c r="C13" s="1">
-        <v>2352</v>
+        <v>2374</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>2352</v>
+        <v>2342</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -4161,22 +4276,22 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2">
-        <v>2.153516054153442</v>
+        <v>2.098632097244263</v>
       </c>
       <c r="C14" s="1">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>296</v>
+        <v>2352</v>
       </c>
       <c r="F14" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -4187,74 +4302,74 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2">
-        <v>2.149847269058228</v>
+        <v>2.095062971115112</v>
       </c>
       <c r="C15" s="1">
-        <v>2344</v>
+        <v>2348</v>
       </c>
       <c r="D15" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>2284</v>
+        <v>296</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G15" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2.091493844985962</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2344</v>
+      </c>
+      <c r="D16" s="1">
+        <v>300</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2284</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
         <v>60</v>
       </c>
-      <c r="B16" s="2">
-        <v>2.034283876419067</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2218</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2218</v>
-      </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2">
-        <v>1.882033586502075</v>
+        <v>1.979067206382752</v>
       </c>
       <c r="C17" s="1">
-        <v>2052</v>
+        <v>2218</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>0</v>
+        <v>2218</v>
       </c>
       <c r="F17" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
@@ -4265,48 +4380,48 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>1.742623686790466</v>
+        <v>1.909469723701477</v>
       </c>
       <c r="C18" s="1">
-        <v>1900</v>
+        <v>2140</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>3752</v>
       </c>
       <c r="E18" s="1">
-        <v>1900</v>
+        <v>2136</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2">
-        <v>1.656409621238709</v>
+        <v>1.830949425697327</v>
       </c>
       <c r="C19" s="1">
-        <v>1806</v>
+        <v>2052</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>1806</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -4317,19 +4432,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2">
-        <v>1.474809885025024</v>
+        <v>1.695323586463928</v>
       </c>
       <c r="C20" s="1">
-        <v>1608</v>
+        <v>1900</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>1608</v>
+        <v>1900</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -4343,45 +4458,45 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1.695323586463928</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1900</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1886</v>
+      </c>
+      <c r="F21" s="1">
         <v>14</v>
       </c>
-      <c r="B21" s="2">
-        <v>1.379424214363098</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1504</v>
-      </c>
-      <c r="D21" s="1">
-        <v>264</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1504</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2">
-        <v>1.278535485267639</v>
+        <v>1.611449718475342</v>
       </c>
       <c r="C22" s="1">
-        <v>1394</v>
+        <v>1806</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>1394</v>
+        <v>1806</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -4395,25 +4510,25 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B23" s="2">
-        <v>1.20883047580719</v>
+        <v>1.454409122467041</v>
       </c>
       <c r="C23" s="1">
-        <v>1318</v>
+        <v>1630</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E23" s="1">
-        <v>1318</v>
+        <v>1290</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -4421,19 +4536,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2">
-        <v>1.168475031852722</v>
+        <v>1.434779167175293</v>
       </c>
       <c r="C24" s="1">
-        <v>1274</v>
+        <v>1608</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1274</v>
+        <v>1608</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -4447,19 +4562,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2">
-        <v>1.118947863578796</v>
+        <v>1.431210041046143</v>
       </c>
       <c r="C25" s="1">
-        <v>1220</v>
+        <v>1604</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="E25" s="1">
-        <v>1220</v>
+        <v>1604</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -4468,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4476,16 +4591,16 @@
         <v>69</v>
       </c>
       <c r="B26" s="2">
-        <v>1.10060441493988</v>
+        <v>1.243832111358643</v>
       </c>
       <c r="C26" s="1">
-        <v>1200</v>
+        <v>1394</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>1200</v>
+        <v>1394</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -4499,19 +4614,19 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" s="2">
-        <v>1.089598417282105</v>
+        <v>1.181372880935669</v>
       </c>
       <c r="C27" s="1">
-        <v>1188</v>
+        <v>1324</v>
       </c>
       <c r="D27" s="1">
-        <v>1672</v>
+        <v>1684</v>
       </c>
       <c r="E27" s="1">
-        <v>1188</v>
+        <v>1324</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -4520,56 +4635,56 @@
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>1672</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="B28" s="2">
-        <v>0.9960470199584961</v>
+        <v>1.176019191741943</v>
       </c>
       <c r="C28" s="1">
-        <v>1086</v>
+        <v>1318</v>
       </c>
       <c r="D28" s="1">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>730</v>
+        <v>1318</v>
       </c>
       <c r="F28" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B29" s="2">
-        <v>0.9905439615249634</v>
+        <v>1.088576197624207</v>
       </c>
       <c r="C29" s="1">
-        <v>1080</v>
+        <v>1220</v>
       </c>
       <c r="D29" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>740</v>
+        <v>1220</v>
       </c>
       <c r="F29" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -4577,22 +4692,22 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B30" s="2">
-        <v>0.9722005724906921</v>
+        <v>1.070730686187744</v>
       </c>
       <c r="C30" s="1">
-        <v>1060</v>
+        <v>1200</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>1032</v>
+        <v>1200</v>
       </c>
       <c r="F30" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -4603,97 +4718,97 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="B31" s="2">
-        <v>0.9428511261940002</v>
+        <v>1.067161560058594</v>
       </c>
       <c r="C31" s="1">
-        <v>1028</v>
+        <v>1196</v>
       </c>
       <c r="D31" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>468</v>
+        <v>1168</v>
       </c>
       <c r="F31" s="1">
-        <v>512</v>
+        <v>28</v>
       </c>
       <c r="G31" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B32" s="2">
-        <v>0.9226733446121216</v>
+        <v>1.043962359428406</v>
       </c>
       <c r="C32" s="1">
-        <v>1006</v>
+        <v>1170</v>
       </c>
       <c r="D32" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>994</v>
+        <v>1170</v>
       </c>
       <c r="F32" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2">
-        <v>0.9043299555778503</v>
+        <v>1.026116847991943</v>
       </c>
       <c r="C33" s="1">
-        <v>986</v>
+        <v>1150</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E33" s="1">
-        <v>986</v>
+        <v>1126</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.8969926238059998</v>
+        <v>0.9654421806335449</v>
       </c>
       <c r="C34" s="1">
-        <v>978</v>
+        <v>1082</v>
       </c>
       <c r="D34" s="1">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="E34" s="1">
-        <v>966</v>
+        <v>1070</v>
       </c>
       <c r="F34" s="1">
         <v>12</v>
@@ -4702,56 +4817,56 @@
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B35" s="2">
-        <v>0.8804835081100464</v>
+        <v>0.9368893504142761</v>
       </c>
       <c r="C35" s="1">
-        <v>960</v>
+        <v>1050</v>
       </c>
       <c r="D35" s="1">
-        <v>4096</v>
+        <v>356</v>
       </c>
       <c r="E35" s="1">
-        <v>960</v>
+        <v>694</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H35" s="1">
-        <v>4096</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>0.8768148422241211</v>
+        <v>0.9333202242851257</v>
       </c>
       <c r="C36" s="1">
-        <v>956</v>
+        <v>1046</v>
       </c>
       <c r="D36" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1">
-        <v>956</v>
+        <v>1026</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -4759,103 +4874,103 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2">
-        <v>0.8025240302085877</v>
+        <v>0.9172592759132385</v>
       </c>
       <c r="C37" s="1">
-        <v>875</v>
+        <v>1028</v>
       </c>
       <c r="D37" s="1">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="E37" s="1">
-        <v>872</v>
+        <v>468</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G37" s="1">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="B38" s="2">
-        <v>0.7630857229232788</v>
+        <v>0.8655073046684265</v>
       </c>
       <c r="C38" s="1">
-        <v>832</v>
+        <v>970</v>
       </c>
       <c r="D38" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E38" s="1">
-        <v>832</v>
+        <v>958</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B39" s="2">
-        <v>0.7520796656608582</v>
+        <v>0.8565845489501953</v>
       </c>
       <c r="C39" s="1">
-        <v>820</v>
+        <v>960</v>
       </c>
       <c r="D39" s="1">
-        <v>1644</v>
+        <v>4096</v>
       </c>
       <c r="E39" s="1">
-        <v>816</v>
+        <v>960</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>1640</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B40" s="2">
-        <v>0.7319019436836243</v>
+        <v>0.8530154228210449</v>
       </c>
       <c r="C40" s="1">
-        <v>798</v>
+        <v>956</v>
       </c>
       <c r="D40" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>786</v>
+        <v>956</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -4863,25 +4978,25 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B41" s="2">
-        <v>0.719061553478241</v>
+        <v>0.7807410955429077</v>
       </c>
       <c r="C41" s="1">
-        <v>784</v>
+        <v>875</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E41" s="1">
-        <v>784</v>
+        <v>872</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -4889,19 +5004,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="B42" s="2">
-        <v>0.6933807730674744</v>
+        <v>0.7637878656387329</v>
       </c>
       <c r="C42" s="1">
-        <v>756</v>
+        <v>856</v>
       </c>
       <c r="D42" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>756</v>
+        <v>856</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -4910,24 +5025,24 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B43" s="2">
-        <v>0.6860434412956238</v>
+        <v>0.7584342360496521</v>
       </c>
       <c r="C43" s="1">
-        <v>748</v>
+        <v>850</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>748</v>
+        <v>850</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -4941,19 +5056,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B44" s="2">
-        <v>0.6603626608848572</v>
+        <v>0.7423732876777649</v>
       </c>
       <c r="C44" s="1">
-        <v>720</v>
+        <v>832</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>720</v>
+        <v>832</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -4967,51 +5082,51 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="B45" s="2">
-        <v>0.6548596024513245</v>
+        <v>0.7316659688949585</v>
       </c>
       <c r="C45" s="1">
-        <v>714</v>
+        <v>820</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <v>1648</v>
       </c>
       <c r="E45" s="1">
-        <v>706</v>
+        <v>816</v>
       </c>
       <c r="F45" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B46" s="2">
-        <v>0.6365162134170532</v>
+        <v>0.7120358943939209</v>
       </c>
       <c r="C46" s="1">
-        <v>694</v>
+        <v>798</v>
       </c>
       <c r="D46" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1">
-        <v>674</v>
+        <v>786</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -5019,19 +5134,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B47" s="2">
-        <v>0.6273444890975952</v>
+        <v>0.6995440721511841</v>
       </c>
       <c r="C47" s="1">
-        <v>684</v>
+        <v>784</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>684</v>
+        <v>784</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -5045,19 +5160,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="B48" s="2">
-        <v>0.6108354330062866</v>
+        <v>0.6745603084564209</v>
       </c>
       <c r="C48" s="1">
-        <v>666</v>
+        <v>756</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E48" s="1">
-        <v>666</v>
+        <v>756</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -5066,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -5074,16 +5189,16 @@
         <v>80</v>
       </c>
       <c r="B49" s="2">
-        <v>0.5906577110290527</v>
+        <v>0.6424384117126465</v>
       </c>
       <c r="C49" s="1">
-        <v>644</v>
+        <v>720</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>644</v>
+        <v>720</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -5100,16 +5215,16 @@
         <v>81</v>
       </c>
       <c r="B50" s="2">
-        <v>0.5888233780860901</v>
+        <v>0.6424384117126465</v>
       </c>
       <c r="C50" s="1">
-        <v>642</v>
+        <v>720</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>642</v>
+        <v>720</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -5126,16 +5241,16 @@
         <v>82</v>
       </c>
       <c r="B51" s="2">
-        <v>0.5814859867095947</v>
+        <v>0.6103165149688721</v>
       </c>
       <c r="C51" s="1">
-        <v>634</v>
+        <v>684</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>634</v>
+        <v>684</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -5149,45 +5264,45 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="B52" s="2">
-        <v>0.5686455965042114</v>
+        <v>0.5978246331214905</v>
       </c>
       <c r="C52" s="1">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="D52" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>564</v>
+        <v>670</v>
       </c>
       <c r="F52" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B53" s="2">
-        <v>0.5392961502075195</v>
+        <v>0.5746254920959473</v>
       </c>
       <c r="C53" s="1">
-        <v>588</v>
+        <v>644</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>588</v>
+        <v>644</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -5201,28 +5316,28 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="B54" s="2">
-        <v>0.5099467039108276</v>
+        <v>0.5532108545303345</v>
       </c>
       <c r="C54" s="1">
-        <v>556</v>
+        <v>620</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
       <c r="E54" s="1">
-        <v>44</v>
+        <v>564</v>
       </c>
       <c r="F54" s="1">
-        <v>512</v>
+        <v>56</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -5230,19 +5345,19 @@
         <v>85</v>
       </c>
       <c r="B55" s="2">
-        <v>0.4916033148765564</v>
+        <v>0.5514262914657593</v>
       </c>
       <c r="C55" s="1">
-        <v>536</v>
+        <v>618</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>344</v>
+        <v>618</v>
       </c>
       <c r="F55" s="1">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
@@ -5253,97 +5368,97 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B56" s="2">
-        <v>0.4695912301540375</v>
+        <v>0.5210889577865601</v>
       </c>
       <c r="C56" s="1">
-        <v>512</v>
+        <v>584</v>
       </c>
       <c r="D56" s="1">
-        <v>16416</v>
+        <v>2092</v>
       </c>
       <c r="E56" s="1">
-        <v>480</v>
+        <v>568</v>
       </c>
       <c r="F56" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G56" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>16384</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="B57" s="2">
-        <v>0.4659225344657898</v>
+        <v>0.5103816390037537</v>
       </c>
       <c r="C57" s="1">
-        <v>508</v>
+        <v>572</v>
       </c>
       <c r="D57" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>36</v>
+        <v>564</v>
       </c>
       <c r="F57" s="1">
-        <v>472</v>
+        <v>8</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="B58" s="2">
-        <v>0.4659225344657898</v>
+        <v>0.4961052238941193</v>
       </c>
       <c r="C58" s="1">
-        <v>508</v>
+        <v>556</v>
       </c>
       <c r="D58" s="1">
-        <v>2092</v>
+        <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>492</v>
+        <v>44</v>
       </c>
       <c r="F58" s="1">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>2092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="B59" s="2">
-        <v>0.4622538685798645</v>
+        <v>0.4889670014381409</v>
       </c>
       <c r="C59" s="1">
-        <v>504</v>
+        <v>548</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="E59" s="1">
-        <v>504</v>
+        <v>548</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -5352,102 +5467,102 @@
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4604195058345795</v>
+        <v>0.4639832973480225</v>
       </c>
       <c r="C60" s="1">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="D60" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>502</v>
+        <v>328</v>
       </c>
       <c r="F60" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4604195058345795</v>
+        <v>0.4568451046943665</v>
       </c>
       <c r="C61" s="1">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="D61" s="1">
-        <v>4</v>
+        <v>16416</v>
       </c>
       <c r="E61" s="1">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4567508399486542</v>
+        <v>0.4532759785652161</v>
       </c>
       <c r="C62" s="1">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="D62" s="1">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="E62" s="1">
-        <v>498</v>
+        <v>36</v>
       </c>
       <c r="F62" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>1031</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4512478113174439</v>
+        <v>0.4497068822383881</v>
       </c>
       <c r="C63" s="1">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="D63" s="1">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -5456,24 +5571,24 @@
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4365730881690979</v>
+        <v>0.4479223489761353</v>
       </c>
       <c r="C64" s="1">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="D64" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="E64" s="1">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -5482,30 +5597,30 @@
         <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4292357265949249</v>
+        <v>0.4479223489761353</v>
       </c>
       <c r="C65" s="1">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="D65" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E65" s="1">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65" s="1">
         <v>0</v>
@@ -5513,45 +5628,45 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4182296693325043</v>
+        <v>0.4443532228469849</v>
       </c>
       <c r="C66" s="1">
-        <v>456</v>
+        <v>498</v>
       </c>
       <c r="D66" s="1">
-        <v>32</v>
+        <v>1031</v>
       </c>
       <c r="E66" s="1">
-        <v>424</v>
+        <v>498</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H66" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B67" s="2">
-        <v>0.4090579748153687</v>
+        <v>0.4247231781482697</v>
       </c>
       <c r="C67" s="1">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -5565,25 +5680,25 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="B68" s="2">
-        <v>0.3989691138267517</v>
+        <v>0.4175849556922913</v>
       </c>
       <c r="C68" s="1">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="D68" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>400</v>
+        <v>468</v>
       </c>
       <c r="F68" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -5591,25 +5706,25 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="B69" s="2">
-        <v>0.3760398328304291</v>
+        <v>0.4068776667118073</v>
       </c>
       <c r="C69" s="1">
-        <v>410</v>
+        <v>456</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E69" s="1">
-        <v>330</v>
+        <v>424</v>
       </c>
       <c r="F69" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -5617,25 +5732,25 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3742054998874664</v>
+        <v>0.4059853851795197</v>
       </c>
       <c r="C70" s="1">
-        <v>408</v>
+        <v>455</v>
       </c>
       <c r="D70" s="1">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E70" s="1">
-        <v>344</v>
+        <v>420</v>
       </c>
       <c r="F70" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G70" s="1">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -5643,19 +5758,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3668681383132935</v>
+        <v>0.3979549109935761</v>
       </c>
       <c r="C71" s="1">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -5669,51 +5784,51 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3668681383132935</v>
+        <v>0.3801093995571137</v>
       </c>
       <c r="C72" s="1">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="D72" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>392</v>
+        <v>426</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3650338053703308</v>
+        <v>0.3801093995571137</v>
       </c>
       <c r="C73" s="1">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="D73" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E73" s="1">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -5721,22 +5836,22 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3411873579025269</v>
+        <v>0.3658329844474793</v>
       </c>
       <c r="C74" s="1">
-        <v>372</v>
+        <v>410</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="F74" s="1">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
@@ -5747,25 +5862,25 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3356843590736389</v>
+        <v>0.3640484213829041</v>
       </c>
       <c r="C75" s="1">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="D75" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E75" s="1">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="F75" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -5773,19 +5888,19 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3155066072940826</v>
+        <v>0.3569102287292481</v>
       </c>
       <c r="C76" s="1">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="D76" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -5794,33 +5909,33 @@
         <v>0</v>
       </c>
       <c r="H76" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3081692457199097</v>
+        <v>0.3569102287292481</v>
       </c>
       <c r="C77" s="1">
-        <v>336</v>
+        <v>400</v>
       </c>
       <c r="D77" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E77" s="1">
-        <v>336</v>
+        <v>392</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H77" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -5828,19 +5943,19 @@
         <v>96</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3063348829746246</v>
+        <v>0.3319265246391296</v>
       </c>
       <c r="C78" s="1">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F78" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -5851,19 +5966,19 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="B79" s="2">
-        <v>0.304500550031662</v>
+        <v>0.3265728652477264</v>
       </c>
       <c r="C79" s="1">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="D79" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>332</v>
+        <v>366</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
@@ -5872,53 +5987,53 @@
         <v>0</v>
       </c>
       <c r="H79" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B80" s="2">
-        <v>0.304500550031662</v>
+        <v>0.3069427907466888</v>
       </c>
       <c r="C80" s="1">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="D80" s="1">
-        <v>2</v>
+        <v>340</v>
       </c>
       <c r="E80" s="1">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B81" s="2">
-        <v>0.297163188457489</v>
+        <v>0.3060505092144013</v>
       </c>
       <c r="C81" s="1">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="F81" s="1">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
@@ -5929,22 +6044,22 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B82" s="2">
-        <v>0.29257732629776</v>
+        <v>0.2998045980930328</v>
       </c>
       <c r="C82" s="1">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="F82" s="1">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -5955,22 +6070,22 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B83" s="2">
-        <v>0.2824884653091431</v>
+        <v>0.2980200350284576</v>
       </c>
       <c r="C83" s="1">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="F83" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G83" s="1">
         <v>0</v>
@@ -5981,19 +6096,19 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B84" s="2">
-        <v>0.2641450464725494</v>
+        <v>0.2962355017662048</v>
       </c>
       <c r="C84" s="1">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="D84" s="1">
-        <v>64</v>
+        <v>200</v>
       </c>
       <c r="E84" s="1">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -6002,30 +6117,30 @@
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>64</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="B85" s="2">
-        <v>0.2494703382253647</v>
+        <v>0.2890972793102264</v>
       </c>
       <c r="C85" s="1">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="D85" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -6033,22 +6148,22 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2494703382253647</v>
+        <v>0.274820864200592</v>
       </c>
       <c r="C86" s="1">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="F86" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G86" s="1">
         <v>0</v>
@@ -6059,19 +6174,19 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2311269342899323</v>
+        <v>0.26054447889328</v>
       </c>
       <c r="C87" s="1">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="D87" s="1">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E87" s="1">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -6080,50 +6195,50 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2219552248716354</v>
+        <v>0.2426989525556564</v>
       </c>
       <c r="C88" s="1">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="D88" s="1">
-        <v>224</v>
+        <v>4</v>
       </c>
       <c r="E88" s="1">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
       </c>
       <c r="G88" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H88" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2146178632974625</v>
+        <v>0.2426989525556564</v>
       </c>
       <c r="C89" s="1">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -6137,48 +6252,48 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2127835154533386</v>
+        <v>0.224853441119194</v>
       </c>
       <c r="C90" s="1">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="D90" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E90" s="1">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="F90" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G90" s="1">
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2091148346662521</v>
+        <v>0.219499796628952</v>
       </c>
       <c r="C91" s="1">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="F91" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G91" s="1">
         <v>0</v>
@@ -6189,28 +6304,28 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2072805017232895</v>
+        <v>0.2159306854009628</v>
       </c>
       <c r="C92" s="1">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="D92" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E92" s="1">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="F92" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G92" s="1">
         <v>0</v>
       </c>
       <c r="H92" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -6218,16 +6333,16 @@
         <v>105</v>
       </c>
       <c r="B93" s="2">
-        <v>0.203611820936203</v>
+        <v>0.2087924778461456</v>
       </c>
       <c r="C93" s="1">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="D93" s="1">
         <v>0</v>
       </c>
       <c r="E93" s="1">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -6244,19 +6359,19 @@
         <v>106</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2017774730920792</v>
+        <v>0.2070079296827316</v>
       </c>
       <c r="C94" s="1">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F94" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G94" s="1">
         <v>0</v>
@@ -6267,19 +6382,19 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2017774730920792</v>
+        <v>0.2034388333559036</v>
       </c>
       <c r="C95" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D95" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -6288,33 +6403,33 @@
         <v>0</v>
       </c>
       <c r="H95" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="B96" s="2">
-        <v>0.2017774730920792</v>
+        <v>0.2034388333559036</v>
       </c>
       <c r="C96" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D96" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E96" s="1">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="F96" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G96" s="1">
         <v>0</v>
       </c>
       <c r="H96" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -6322,16 +6437,16 @@
         <v>108</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1871027499437332</v>
+        <v>0.1980851739645004</v>
       </c>
       <c r="C97" s="1">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -6345,19 +6460,19 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1760967075824738</v>
+        <v>0.1963006258010864</v>
       </c>
       <c r="C98" s="1">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="D98" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -6366,27 +6481,27 @@
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1705936789512634</v>
+        <v>0.1963006258010864</v>
       </c>
       <c r="C99" s="1">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="F99" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
@@ -6397,19 +6512,19 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1614219844341278</v>
+        <v>0.182024210691452</v>
       </c>
       <c r="C100" s="1">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -6423,19 +6538,19 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1614219844341278</v>
+        <v>0.1713169068098068</v>
       </c>
       <c r="C101" s="1">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D101" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E101" s="1">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -6444,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -6452,16 +6567,16 @@
         <v>112</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1614219844341278</v>
+        <v>0.1677478104829788</v>
       </c>
       <c r="C102" s="1">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -6475,25 +6590,25 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1577533036470413</v>
+        <v>0.1659632623195648</v>
       </c>
       <c r="C103" s="1">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D103" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="F103" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -6501,19 +6616,19 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B104" s="2">
-        <v>0.144912913441658</v>
+        <v>0.1570405066013336</v>
       </c>
       <c r="C104" s="1">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -6527,19 +6642,19 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1412442326545715</v>
+        <v>0.1570405066013336</v>
       </c>
       <c r="C105" s="1">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -6553,25 +6668,25 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1394098997116089</v>
+        <v>0.1534713953733444</v>
       </c>
       <c r="C106" s="1">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D106" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E106" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F106" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G106" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -6582,16 +6697,16 @@
         <v>116</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1320725232362747</v>
+        <v>0.1409795433282852</v>
       </c>
       <c r="C107" s="1">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D107" s="1">
         <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -6608,16 +6723,16 @@
         <v>117</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1302381902933121</v>
+        <v>0.137410432100296</v>
       </c>
       <c r="C108" s="1">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -6634,16 +6749,16 @@
         <v>118</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1265695095062256</v>
+        <v>0.135625883936882</v>
       </c>
       <c r="C109" s="1">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -6657,19 +6772,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1247351691126823</v>
+        <v>0.1284876763820648</v>
       </c>
       <c r="C110" s="1">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D110" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -6678,30 +6793,30 @@
         <v>0</v>
       </c>
       <c r="H110" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1210664883255959</v>
+        <v>0.1267031282186508</v>
       </c>
       <c r="C111" s="1">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D111" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E111" s="1">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -6709,25 +6824,25 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1155634671449661</v>
+        <v>0.1231340318918228</v>
       </c>
       <c r="C112" s="1">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D112" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="F112" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -6735,19 +6850,19 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1100604385137558</v>
+        <v>0.1213494762778282</v>
       </c>
       <c r="C113" s="1">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D113" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E113" s="1">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -6756,25 +6871,25 @@
         <v>0</v>
       </c>
       <c r="H113" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1100604385137558</v>
+        <v>0.1142112761735916</v>
       </c>
       <c r="C114" s="1">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D114" s="1">
+        <v>0</v>
+      </c>
+      <c r="E114" s="1">
         <v>128</v>
       </c>
-      <c r="E114" s="1">
-        <v>120</v>
-      </c>
       <c r="F114" s="1">
         <v>0</v>
       </c>
@@ -6782,24 +6897,24 @@
         <v>0</v>
       </c>
       <c r="H114" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1082260981202126</v>
+        <v>0.1142112761735916</v>
       </c>
       <c r="C115" s="1">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -6813,19 +6928,19 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1063917577266693</v>
+        <v>0.112426720559597</v>
       </c>
       <c r="C116" s="1">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -6839,25 +6954,25 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>123</v>
+        <v>40</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1063917577266693</v>
+        <v>0.112426720559597</v>
       </c>
       <c r="C117" s="1">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D117" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E117" s="1">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F117" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -6865,19 +6980,19 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1027230769395828</v>
+        <v>0.1070730686187744</v>
       </c>
       <c r="C118" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D118" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E118" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
@@ -6886,24 +7001,24 @@
         <v>0</v>
       </c>
       <c r="H118" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1008887365460396</v>
+        <v>0.1017194166779518</v>
       </c>
       <c r="C119" s="1">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
       </c>
       <c r="E119" s="1">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -6917,19 +7032,19 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B120" s="2">
-        <v>0.09722005575895309</v>
+        <v>0.09993486106395721</v>
       </c>
       <c r="C120" s="1">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -6943,25 +7058,25 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B121" s="2">
-        <v>0.09722005575895309</v>
+        <v>0.09993486106395721</v>
       </c>
       <c r="C121" s="1">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D121" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E121" s="1">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -6972,16 +7087,16 @@
         <v>127</v>
       </c>
       <c r="B122" s="2">
-        <v>0.08988269418478012</v>
+        <v>0.09993486106395721</v>
       </c>
       <c r="C122" s="1">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D122" s="1">
         <v>0</v>
       </c>
       <c r="E122" s="1">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -6998,16 +7113,16 @@
         <v>128</v>
       </c>
       <c r="B123" s="2">
-        <v>0.08988269418478012</v>
+        <v>0.09815031290054321</v>
       </c>
       <c r="C123" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -7024,16 +7139,16 @@
         <v>129</v>
       </c>
       <c r="B124" s="2">
-        <v>0.08437967300415039</v>
+        <v>0.09815031290054321</v>
       </c>
       <c r="C124" s="1">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
       </c>
       <c r="E124" s="1">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
@@ -7047,19 +7162,19 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="B125" s="2">
-        <v>0.0807109922170639</v>
+        <v>0.09636576473712921</v>
       </c>
       <c r="C125" s="1">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="D125" s="1">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="E125" s="1">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -7068,24 +7183,24 @@
         <v>0</v>
       </c>
       <c r="H125" s="1">
-        <v>0</v>
+        <v>716</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B126" s="2">
-        <v>0.0807109922170639</v>
+        <v>0.08744300901889801</v>
       </c>
       <c r="C126" s="1">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -7099,19 +7214,19 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B127" s="2">
-        <v>0.07887665182352066</v>
+        <v>0.08744300901889801</v>
       </c>
       <c r="C127" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -7125,19 +7240,19 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B128" s="2">
-        <v>0.07704231142997742</v>
+        <v>0.08208934962749481</v>
       </c>
       <c r="C128" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -7151,25 +7266,25 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="B129" s="2">
-        <v>0.07704231142997742</v>
+        <v>0.08208934962749481</v>
       </c>
       <c r="C129" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D129" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E129" s="1">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="F129" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G129" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
@@ -7180,16 +7295,16 @@
         <v>134</v>
       </c>
       <c r="B130" s="2">
-        <v>0.07520797103643417</v>
+        <v>0.07673569768667221</v>
       </c>
       <c r="C130" s="1">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -7206,16 +7321,16 @@
         <v>135</v>
       </c>
       <c r="B131" s="2">
-        <v>0.07520797103643417</v>
+        <v>0.07495114952325821</v>
       </c>
       <c r="C131" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -7232,16 +7347,16 @@
         <v>136</v>
       </c>
       <c r="B132" s="2">
-        <v>0.06970494985580444</v>
+        <v>0.07495114952325821</v>
       </c>
       <c r="C132" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D132" s="1">
         <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -7255,19 +7370,19 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="B133" s="2">
-        <v>0.06970494985580444</v>
+        <v>0.07495114952325821</v>
       </c>
       <c r="C133" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D133" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E133" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -7276,30 +7391,30 @@
         <v>0</v>
       </c>
       <c r="H133" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1" t="s">
-        <v>137</v>
+        <v>51</v>
       </c>
       <c r="B134" s="2">
-        <v>0.06053324416279793</v>
+        <v>0.07495114952325821</v>
       </c>
       <c r="C134" s="1">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D134" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E134" s="1">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F134" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G134" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H134" s="1">
         <v>0</v>
@@ -7310,16 +7425,16 @@
         <v>138</v>
       </c>
       <c r="B135" s="2">
-        <v>0.0550302192568779</v>
+        <v>0.07316659390926361</v>
       </c>
       <c r="C135" s="1">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D135" s="1">
         <v>0</v>
       </c>
       <c r="E135" s="1">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -7336,16 +7451,16 @@
         <v>139</v>
       </c>
       <c r="B136" s="2">
-        <v>0.0550302192568779</v>
+        <v>0.06959749758243561</v>
       </c>
       <c r="C136" s="1">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -7359,19 +7474,19 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="B137" s="2">
-        <v>0.05319587886333466</v>
+        <v>0.06781294196844101</v>
       </c>
       <c r="C137" s="1">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D137" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E137" s="1">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -7380,24 +7495,24 @@
         <v>0</v>
       </c>
       <c r="H137" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B138" s="2">
-        <v>0.04952719807624817</v>
+        <v>0.05889018625020981</v>
       </c>
       <c r="C138" s="1">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
       </c>
       <c r="E138" s="1">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -7411,25 +7526,25 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="B139" s="2">
-        <v>0.04952719807624817</v>
+        <v>0.05353653430938721</v>
       </c>
       <c r="C139" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D139" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E139" s="1">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F139" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G139" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
@@ -7440,16 +7555,16 @@
         <v>142</v>
       </c>
       <c r="B140" s="2">
-        <v>0.04769285768270493</v>
+        <v>0.05353653430938721</v>
       </c>
       <c r="C140" s="1">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -7466,16 +7581,16 @@
         <v>143</v>
       </c>
       <c r="B141" s="2">
-        <v>0.04769285768270493</v>
+        <v>0.05175198242068291</v>
       </c>
       <c r="C141" s="1">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
       </c>
       <c r="E141" s="1">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -7492,16 +7607,16 @@
         <v>144</v>
       </c>
       <c r="B142" s="2">
-        <v>0.04402417689561844</v>
+        <v>0.04818288236856461</v>
       </c>
       <c r="C142" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -7515,25 +7630,25 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
-        <v>145</v>
+        <v>44</v>
       </c>
       <c r="B143" s="2">
-        <v>0.04402417689561844</v>
+        <v>0.04818288236856461</v>
       </c>
       <c r="C143" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D143" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E143" s="1">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F143" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G143" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
@@ -7541,19 +7656,19 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B144" s="2">
-        <v>0.04402417689561844</v>
+        <v>0.04639833047986031</v>
       </c>
       <c r="C144" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D144" s="1">
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7567,19 +7682,19 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B145" s="2">
-        <v>0.04035549610853195</v>
+        <v>0.04639833047986031</v>
       </c>
       <c r="C145" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D145" s="1">
         <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F145" s="1">
         <v>0</v>
@@ -7593,19 +7708,19 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B146" s="2">
-        <v>0.04035549610853195</v>
+        <v>0.04282922670245171</v>
       </c>
       <c r="C146" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -7619,25 +7734,25 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1" t="s">
-        <v>44</v>
+        <v>148</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04035549610853195</v>
+        <v>0.04282922670245171</v>
       </c>
       <c r="C147" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D147" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E147" s="1">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F147" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G147" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
@@ -7648,16 +7763,16 @@
         <v>149</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04035549610853195</v>
+        <v>0.04282922670245171</v>
       </c>
       <c r="C148" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D148" s="1">
         <v>0</v>
       </c>
       <c r="E148" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F148" s="1">
         <v>0</v>
@@ -7674,7 +7789,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04035549610853195</v>
+        <v>0.03926012665033341</v>
       </c>
       <c r="C149" s="1">
         <v>44</v>
@@ -7700,16 +7815,16 @@
         <v>151</v>
       </c>
       <c r="B150" s="2">
-        <v>0.03485247492790222</v>
+        <v>0.03926012665033341</v>
       </c>
       <c r="C150" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
       </c>
       <c r="E150" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F150" s="1">
         <v>0</v>
@@ -7726,16 +7841,16 @@
         <v>152</v>
       </c>
       <c r="B151" s="2">
-        <v>0.03301813080906868</v>
+        <v>0.03926012665033341</v>
       </c>
       <c r="C151" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D151" s="1">
         <v>0</v>
       </c>
       <c r="E151" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F151" s="1">
         <v>0</v>
@@ -7749,25 +7864,25 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1" t="s">
-        <v>153</v>
+        <v>47</v>
       </c>
       <c r="B152" s="2">
-        <v>0.03301813080906868</v>
+        <v>0.03926012665033341</v>
       </c>
       <c r="C152" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D152" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E152" s="1">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F152" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
@@ -7775,19 +7890,19 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03301813080906868</v>
+        <v>0.03926012665033341</v>
       </c>
       <c r="C153" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D153" s="1">
         <v>0</v>
       </c>
       <c r="E153" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F153" s="1">
         <v>0</v>
@@ -7801,19 +7916,19 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03301813080906868</v>
+        <v>0.03926012665033341</v>
       </c>
       <c r="C154" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D154" s="1">
         <v>0</v>
       </c>
       <c r="E154" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F154" s="1">
         <v>0</v>
@@ -7827,19 +7942,19 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B155" s="2">
-        <v>0.03301813080906868</v>
+        <v>0.03569102287292481</v>
       </c>
       <c r="C155" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
       </c>
       <c r="E155" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F155" s="1">
         <v>0</v>
@@ -7853,19 +7968,19 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B156" s="2">
-        <v>0.02934945188462734</v>
+        <v>0.03390647098422051</v>
       </c>
       <c r="C156" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D156" s="1">
         <v>0</v>
       </c>
       <c r="E156" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -7879,19 +7994,19 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B157" s="2">
-        <v>0.02934945188462734</v>
+        <v>0.03212191909551621</v>
       </c>
       <c r="C157" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
       </c>
       <c r="E157" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -7905,19 +8020,19 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B158" s="2">
-        <v>0.02934945188462734</v>
+        <v>0.03212191909551621</v>
       </c>
       <c r="C158" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D158" s="1">
         <v>0</v>
       </c>
       <c r="E158" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F158" s="1">
         <v>0</v>
@@ -7931,19 +8046,19 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B159" s="2">
-        <v>0.02934945188462734</v>
+        <v>0.03212191909551621</v>
       </c>
       <c r="C159" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D159" s="1">
         <v>0</v>
       </c>
       <c r="E159" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F159" s="1">
         <v>0</v>
@@ -7957,19 +8072,19 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B160" s="2">
-        <v>0.02751510962843895</v>
+        <v>0.03212191909551621</v>
       </c>
       <c r="C160" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D160" s="1">
         <v>0</v>
       </c>
       <c r="E160" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F160" s="1">
         <v>0</v>
@@ -7983,19 +8098,19 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.02751510962843895</v>
+        <v>0.0285528190433979</v>
       </c>
       <c r="C161" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D161" s="1">
         <v>0</v>
       </c>
       <c r="E161" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F161" s="1">
         <v>0</v>
@@ -8009,19 +8124,19 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.02201208844780922</v>
+        <v>0.0285528190433979</v>
       </c>
       <c r="C162" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
       </c>
       <c r="E162" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F162" s="1">
         <v>0</v>
@@ -8035,25 +8150,25 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="1" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.01467472594231367</v>
+        <v>0.0285528190433979</v>
       </c>
       <c r="C163" s="1">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D163" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E163" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F163" s="1">
         <v>0</v>
       </c>
       <c r="G163" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H163" s="1">
         <v>0</v>
@@ -8064,16 +8179,16 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.007337362971156836</v>
+        <v>0.0285528190433979</v>
       </c>
       <c r="C164" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
       </c>
       <c r="E164" s="1">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F164" s="1">
         <v>0</v>
@@ -8090,16 +8205,16 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.007337362971156836</v>
+        <v>0.0267682671546936</v>
       </c>
       <c r="C165" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
       </c>
       <c r="E165" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F165" s="1">
         <v>0</v>
@@ -8113,25 +8228,25 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="1" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.003668681485578418</v>
+        <v>0.0267682671546936</v>
       </c>
       <c r="C166" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D166" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E166" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F166" s="1">
         <v>0</v>
       </c>
       <c r="G166" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H166" s="1">
         <v>0</v>
@@ -8139,19 +8254,19 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.003668681485578418</v>
+        <v>0.02319916523993015</v>
       </c>
       <c r="C167" s="1">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
       </c>
       <c r="E167" s="1">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F167" s="1">
         <v>0</v>
@@ -8165,59 +8280,215 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.003668681485578418</v>
+        <v>0.02141461335122585</v>
       </c>
       <c r="C168" s="1">
+        <v>24</v>
+      </c>
+      <c r="D168" s="1">
+        <v>0</v>
+      </c>
+      <c r="E168" s="1">
+        <v>24</v>
+      </c>
+      <c r="F168" s="1">
+        <v>0</v>
+      </c>
+      <c r="G168" s="1">
+        <v>0</v>
+      </c>
+      <c r="H168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B169" s="2">
+        <v>0.01427640952169895</v>
+      </c>
+      <c r="C169" s="1">
+        <v>16</v>
+      </c>
+      <c r="D169" s="1">
         <v>4</v>
       </c>
-      <c r="D168" s="1">
-        <v>0</v>
-      </c>
-      <c r="E168" s="1">
+      <c r="E169" s="1">
+        <v>12</v>
+      </c>
+      <c r="F169" s="1">
+        <v>0</v>
+      </c>
+      <c r="G169" s="1">
         <v>4</v>
       </c>
-      <c r="F168" s="1">
-        <v>0</v>
-      </c>
-      <c r="G168" s="1">
-        <v>0</v>
-      </c>
-      <c r="H168" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
-      <c r="A169" t="s">
+      <c r="H169" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B169">
+      <c r="B170" s="2">
+        <v>0.007138204760849476</v>
+      </c>
+      <c r="C170" s="1">
+        <v>8</v>
+      </c>
+      <c r="D170" s="1">
+        <v>0</v>
+      </c>
+      <c r="E170" s="1">
+        <v>8</v>
+      </c>
+      <c r="F170" s="1">
+        <v>0</v>
+      </c>
+      <c r="G170" s="1">
+        <v>0</v>
+      </c>
+      <c r="H170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2">
+        <v>0.007138204760849476</v>
+      </c>
+      <c r="C171" s="1">
+        <v>8</v>
+      </c>
+      <c r="D171" s="1">
+        <v>0</v>
+      </c>
+      <c r="E171" s="1">
+        <v>8</v>
+      </c>
+      <c r="F171" s="1">
+        <v>0</v>
+      </c>
+      <c r="G171" s="1">
+        <v>0</v>
+      </c>
+      <c r="H171" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B172" s="2">
+        <v>0.003569102380424738</v>
+      </c>
+      <c r="C172" s="1">
+        <v>4</v>
+      </c>
+      <c r="D172" s="1">
+        <v>4</v>
+      </c>
+      <c r="E172" s="1">
+        <v>0</v>
+      </c>
+      <c r="F172" s="1">
+        <v>0</v>
+      </c>
+      <c r="G172" s="1">
+        <v>4</v>
+      </c>
+      <c r="H172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B173" s="2">
+        <v>0.003569102380424738</v>
+      </c>
+      <c r="C173" s="1">
+        <v>4</v>
+      </c>
+      <c r="D173" s="1">
+        <v>0</v>
+      </c>
+      <c r="E173" s="1">
+        <v>4</v>
+      </c>
+      <c r="F173" s="1">
+        <v>0</v>
+      </c>
+      <c r="G173" s="1">
+        <v>0</v>
+      </c>
+      <c r="H173" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B174" s="2">
+        <v>0.003569102380424738</v>
+      </c>
+      <c r="C174" s="1">
+        <v>4</v>
+      </c>
+      <c r="D174" s="1">
+        <v>0</v>
+      </c>
+      <c r="E174" s="1">
+        <v>4</v>
+      </c>
+      <c r="F174" s="1">
+        <v>0</v>
+      </c>
+      <c r="G174" s="1">
+        <v>0</v>
+      </c>
+      <c r="H174" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" t="s">
+        <v>174</v>
+      </c>
+      <c r="B175">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C169">
+      <c r="C175">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D169">
+      <c r="D175">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E169">
+      <c r="E175">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F169">
+      <c r="F175">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G169">
+      <c r="G175">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H169">
+      <c r="H175">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="184">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -23,6 +23,9 @@
     <t>heap_4.o</t>
   </si>
   <si>
+    <t>motor_observer.o</t>
+  </si>
+  <si>
     <t>drv_flash_g4.o</t>
   </si>
   <si>
@@ -53,6 +56,9 @@
     <t>runtime_param.o</t>
   </si>
   <si>
+    <t>jm_proto_ops.o</t>
+  </si>
+  <si>
     <t>motor_pid_profile.o</t>
   </si>
   <si>
@@ -119,9 +125,6 @@
     <t>stm32g4xx_hal_flash.o</t>
   </si>
   <si>
-    <t>jm_proto_ops.o</t>
-  </si>
-  <si>
     <t>dev_motor.o</t>
   </si>
   <si>
@@ -179,12 +182,12 @@
     <t>motor_info.o</t>
   </si>
   <si>
+    <t>jm_proto.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_adc.o</t>
   </si>
   <si>
-    <t>jm_proto.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_uart.o</t>
   </si>
   <si>
@@ -230,6 +233,9 @@
     <t>mf_w.l</t>
   </si>
   <si>
+    <t>motor_pid_autotune.o</t>
+  </si>
+  <si>
     <t>dev_motor_phase_current.o</t>
   </si>
   <si>
@@ -266,9 +272,6 @@
     <t>atan2f.o</t>
   </si>
   <si>
-    <t>motor_pid_autotune.o</t>
-  </si>
-  <si>
     <t>dev_half_bridge.o</t>
   </si>
   <si>
@@ -446,6 +449,9 @@
     <t>stm32g4xx_hal_msp.o</t>
   </si>
   <si>
+    <t>control_irq.o</t>
+  </si>
+  <si>
     <t>sqrtf.o</t>
   </si>
   <si>
@@ -453,9 +459,6 @@
   </si>
   <si>
     <t>utils.o</t>
-  </si>
-  <si>
-    <t>control_irq.o</t>
   </si>
   <si>
     <t>dfixul.o</t>
@@ -653,166 +656,169 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$175</c:f>
+              <c:f>ram_percent!$A$3:$A$176</c:f>
               <c:strCache>
-                <c:ptCount val="173"/>
+                <c:ptCount val="174"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>motor_observer.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>drv_flash_g4.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>dev_commun_can.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>motor_info_storage.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
+                  <c:v>jm_proto_ops.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>motor_pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="16">
                   <c:v>dev_power_monitor.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="17">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>drv_can.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>calib_level3_encoder.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
-                  <c:v>jm_proto_ops.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>led_manager.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="172">
+                <c:pt idx="173">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -820,167 +826,170 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$175</c:f>
+              <c:f>ram_percent!$B$3:$B$176</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="173"/>
+                <c:ptCount val="174"/>
                 <c:pt idx="0">
-                  <c:v>39.14816665649414</c:v>
+                  <c:v>32.43435668945313</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.767963409423828</c:v>
+                  <c:v>16.4384651184082</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.767963409423828</c:v>
+                  <c:v>8.092782020568848</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.947607040405273</c:v>
+                  <c:v>8.092782020568848</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.988910675048828</c:v>
+                  <c:v>7.41311502456665</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.874442577362061</c:v>
+                  <c:v>4.133325576782227</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.01593017578125</c:v>
+                  <c:v>4.038487911224365</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.930078983306885</c:v>
+                  <c:v>3.319305419921875</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.458684206008911</c:v>
+                  <c:v>3.256080389022827</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.441990852355957</c:v>
+                  <c:v>2.037026166915894</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.707485795021057</c:v>
+                  <c:v>2.023195505142212</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.8489733338356018</c:v>
+                  <c:v>1.414656281471252</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8108172416687012</c:v>
+                  <c:v>0.7745046019554138</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.7154269814491272</c:v>
+                  <c:v>0.7033765912055969</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.6391147971153259</c:v>
+                  <c:v>0.6717641949653626</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.543724536895752</c:v>
+                  <c:v>0.5927330851554871</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.5341854691505432</c:v>
+                  <c:v>0.5295082330703735</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.4864903390407562</c:v>
+                  <c:v>0.4504771530628204</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.4769513309001923</c:v>
+                  <c:v>0.4425740540027618</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.3147878646850586</c:v>
+                  <c:v>0.4030584990978241</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.3052488565444946</c:v>
+                  <c:v>0.3951554000377655</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2384756654500961</c:v>
+                  <c:v>0.2608025670051575</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2003195583820343</c:v>
+                  <c:v>0.2528994381427765</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.1812414973974228</c:v>
+                  <c:v>0.1975777000188828</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1717024743556976</c:v>
+                  <c:v>0.1659652590751648</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1717024743556976</c:v>
+                  <c:v>0.1501590460538864</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1717024743556976</c:v>
+                  <c:v>0.1422559469938278</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1621634513139725</c:v>
+                  <c:v>0.1422559469938278</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1526244282722473</c:v>
+                  <c:v>0.1422559469938278</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1049292907118797</c:v>
+                  <c:v>0.134352833032608</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.09539026767015457</c:v>
+                  <c:v>0.1264497190713882</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.08585123717784882</c:v>
+                  <c:v>0.08693418651819229</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.07631221413612366</c:v>
+                  <c:v>0.0790310800075531</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.0667731836438179</c:v>
+                  <c:v>0.07112797349691391</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.05484940111637116</c:v>
+                  <c:v>0.06322485953569412</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.04769513383507729</c:v>
+                  <c:v>0.04544287174940109</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.04769513383507729</c:v>
+                  <c:v>0.03951554000377655</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.02861708030104637</c:v>
+                  <c:v>0.03951554000377655</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.02861708030104637</c:v>
+                  <c:v>0.02370932325720787</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.02861708030104637</c:v>
+                  <c:v>0.02370932325720787</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.02861708030104637</c:v>
+                  <c:v>0.02370932325720787</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.01907805353403091</c:v>
+                  <c:v>0.02370932325720787</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01907805353403091</c:v>
+                  <c:v>0.01580621488392353</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01907805353403091</c:v>
+                  <c:v>0.01580621488392353</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.009539026767015457</c:v>
+                  <c:v>0.01580621488392353</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.009539026767015457</c:v>
+                  <c:v>0.007903107441961765</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.009539026767015457</c:v>
+                  <c:v>0.007903107441961765</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.009539026767015457</c:v>
+                  <c:v>0.007903107441961765</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.009539026767015457</c:v>
+                  <c:v>0.007903107441961765</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.009539026767015457</c:v>
+                  <c:v>0.007903107441961765</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.009539026767015457</c:v>
+                  <c:v>0.007903107441961765</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.007154270075261593</c:v>
-                </c:pt>
-                <c:pt idx="172">
+                  <c:v>0.007903107441961765</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.005927330814301968</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1048,23 +1057,23 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$175</c:f>
+              <c:f>flash_percent!$A$3:$A$176</c:f>
               <c:strCache>
-                <c:ptCount val="173"/>
+                <c:ptCount val="174"/>
                 <c:pt idx="0">
                   <c:v>motor_info.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>jm_proto_ops.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>jm_proto_ops.o</c:v>
-                </c:pt>
                 <c:pt idx="3">
+                  <c:v>jm_proto.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>stm32g4xx_hal_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>jm_proto.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>stm32g4xx_hal_uart.o</c:v>
@@ -1121,453 +1130,456 @@
                   <c:v>dev_power_monitor.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>motor_pid_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>motor_observer.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>stm32g4xx_hal_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
-                  <c:v>motor_loop.o</c:v>
-                </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
+                  <c:v>motor_pid_autotune.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>dev_motor_phase_current.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>ctrl_transition.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>calib_config_runtime.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>drv_can.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>calib_level3_encoder.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>motor_pid_profile.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
+                  <c:v>calib_level3_encoder.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
+                  <c:v>motor_pid_load.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="39">
                   <c:v>drv_flash_g4.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="40">
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
-                  <c:v>motor_pid_load.o</c:v>
-                </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="41">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="42">
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="43">
                   <c:v>multiturn_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="44">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="46">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="47">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="48">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="49">
                   <c:v>motor_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="50">
                   <c:v>atan2f.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
-                  <c:v>motor_pid_autotune.o</c:v>
-                </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>dev_half_bridge.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>cascade_control.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>motor_info_storage.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>foc_decoupling.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>crc16.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>calib_ac_injection.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>stm32g4xx_hal_flash_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="67">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="68">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="69">
                   <c:v>ctrl_transition_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="70">
                   <c:v>motor_info_calib.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>led_manager.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="76">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="77">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="78">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="79">
                   <c:v>dev_config.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="80">
                   <c:v>cosf.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="81">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="82">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="83">
                   <c:v>cmsis_os.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="89">
                   <c:v>drv_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="90">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="91">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="92">
                   <c:v>drv_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="93">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="94">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="95">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="96">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="97">
                   <c:v>drv_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="98">
                   <c:v>stm32g4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="99">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="100">
                   <c:v>stm32g4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="101">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="102">
                   <c:v>fmodf.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="103">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="104">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="105">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="106">
                   <c:v>roundf.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="107">
                   <c:v>arm_cos_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="108">
                   <c:v>arm_sin_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="109">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="110">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="111">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="112">
                   <c:v>thread_period.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="113">
                   <c:v>motor_mode_mit.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="114">
                   <c:v>motor_mode_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="115">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="116">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="117">
                   <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="118">
                   <c:v>floorf.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="119">
                   <c:v>motor_mode_position.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="120">
                   <c:v>motor_mode_current.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="121">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="122">
                   <c:v>user_interface.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="123">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="124">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="125">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="126">
                   <c:v>motor_mode_test_sweep.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="127">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="128">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="129">
                   <c:v>motor_mode_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="130">
                   <c:v>motor_mode_profile_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="131">
                   <c:v>assert_report.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="132">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="133">
                   <c:v>frem.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="134">
                   <c:v>motor_mode_profile_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="135">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="136">
                   <c:v>motor_mode_duty.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="137">
                   <c:v>frnd.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="138">
                   <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="139">
+                  <c:v>control_irq.o</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>sqrtf.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="141">
                   <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="142">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="143">
                   <c:v>utils.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
-                  <c:v>control_irq.o</c:v>
-                </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="144">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="145">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="146">
                   <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="146">
+                <c:pt idx="147">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="148">
                   <c:v>funder.o</c:v>
                 </c:pt>
-                <c:pt idx="148">
+                <c:pt idx="149">
                   <c:v>thread_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="149">
+                <c:pt idx="150">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="150">
+                <c:pt idx="151">
                   <c:v>motor_mode_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="151">
+                <c:pt idx="152">
                   <c:v>motor_mode_hold.o</c:v>
                 </c:pt>
-                <c:pt idx="152">
+                <c:pt idx="153">
                   <c:v>drv_delay.o</c:v>
                 </c:pt>
-                <c:pt idx="153">
+                <c:pt idx="154">
                   <c:v>fpclassifyf.o</c:v>
                 </c:pt>
-                <c:pt idx="154">
+                <c:pt idx="155">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="155">
+                <c:pt idx="156">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="156">
+                <c:pt idx="157">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="157">
+                <c:pt idx="158">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="158">
+                <c:pt idx="159">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="159">
+                <c:pt idx="160">
                   <c:v>thread_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="160">
+                <c:pt idx="161">
                   <c:v>thread_display.o</c:v>
                 </c:pt>
-                <c:pt idx="161">
+                <c:pt idx="162">
                   <c:v>thread_control.o</c:v>
                 </c:pt>
-                <c:pt idx="162">
+                <c:pt idx="163">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="163">
+                <c:pt idx="164">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="164">
+                <c:pt idx="165">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="165">
+                <c:pt idx="166">
                   <c:v>strncpy.o</c:v>
                 </c:pt>
-                <c:pt idx="166">
+                <c:pt idx="167">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="167">
+                <c:pt idx="168">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="168">
+                <c:pt idx="169">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="169">
+                <c:pt idx="170">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="170">
+                <c:pt idx="171">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="171">
+                <c:pt idx="172">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="172">
+                <c:pt idx="173">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1575,527 +1587,530 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$175</c:f>
+              <c:f>flash_percent!$B$3:$B$176</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="173"/>
+                <c:ptCount val="174"/>
                 <c:pt idx="0">
-                  <c:v>4.232955455780029</c:v>
+                  <c:v>4.109814643859863</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.792171239852905</c:v>
+                  <c:v>3.865512847900391</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.315696001052856</c:v>
+                  <c:v>3.681853294372559</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.283574104309082</c:v>
+                  <c:v>3.375176429748535</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.160439968109131</c:v>
+                  <c:v>3.188051700592041</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.957001209259033</c:v>
+                  <c:v>2.870979309082031</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.846359014511108</c:v>
+                  <c:v>2.763555765151978</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.56439995765686</c:v>
+                  <c:v>2.489799022674561</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.542985439300537</c:v>
+                  <c:v>2.46900749206543</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.141461372375488</c:v>
+                  <c:v>2.079164266586304</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.11826229095459</c:v>
+                  <c:v>2.056639909744263</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.098632097244263</c:v>
+                  <c:v>2.037580966949463</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.095062971115112</c:v>
+                  <c:v>2.034115552902222</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.091493844985962</c:v>
+                  <c:v>2.03065037727356</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.979067206382752</c:v>
+                  <c:v>1.921494245529175</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.909469723701477</c:v>
+                  <c:v>1.853921413421631</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.830949425697327</c:v>
+                  <c:v>1.777685403823853</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.695323586463928</c:v>
+                  <c:v>1.646004915237427</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.695323586463928</c:v>
+                  <c:v>1.646004915237427</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.611449718475342</c:v>
+                  <c:v>1.564571022987366</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.454409122467041</c:v>
+                  <c:v>1.406901121139526</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.434779167175293</c:v>
+                  <c:v>1.39303994178772</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.431210041046143</c:v>
+                  <c:v>1.389574766159058</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.243832111358643</c:v>
+                  <c:v>1.245765924453735</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.181372880935669</c:v>
+                  <c:v>1.242300629615784</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.176019191741943</c:v>
+                  <c:v>1.207647800445557</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.088576197624207</c:v>
+                  <c:v>1.141807675361633</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.070730686187744</c:v>
+                  <c:v>1.081165313720703</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.067161560058594</c:v>
+                  <c:v>1.056908488273621</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.043962359428406</c:v>
+                  <c:v>1.039582133293152</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.026116847991943</c:v>
+                  <c:v>1.0361168384552</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.9654421806335449</c:v>
+                  <c:v>1.013592481613159</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.9368893504142761</c:v>
+                  <c:v>0.9962661862373352</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9333202242851257</c:v>
+                  <c:v>0.9477523565292358</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9172592759132385</c:v>
+                  <c:v>0.9373565316200256</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8655073046684265</c:v>
+                  <c:v>0.8905753493309021</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8565845489501953</c:v>
+                  <c:v>0.8758479356765747</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8530154228210449</c:v>
+                  <c:v>0.8628531098365784</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.7807410955429077</c:v>
+                  <c:v>0.8403288722038269</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7637878656387329</c:v>
+                  <c:v>0.8316656947135925</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.7584342360496521</c:v>
+                  <c:v>0.8282003998756409</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7423732876777649</c:v>
+                  <c:v>0.7415685653686523</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7316659688949585</c:v>
+                  <c:v>0.7363706231117249</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7120358943939209</c:v>
+                  <c:v>0.7207769155502319</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.6995440721511841</c:v>
+                  <c:v>0.7103810906410217</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.6745603084564209</c:v>
+                  <c:v>0.6913220882415772</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6424384117126465</c:v>
+                  <c:v>0.6791936159133911</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6424384117126465</c:v>
+                  <c:v>0.6549367308616638</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6103165149688721</c:v>
+                  <c:v>0.6237492561340332</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.5978246331214905</c:v>
+                  <c:v>0.6237492561340332</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.5746254920959473</c:v>
+                  <c:v>0.5925617814064026</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5532108545303345</c:v>
+                  <c:v>0.5579090714454651</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5514262914657593</c:v>
+                  <c:v>0.5371174216270447</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5210889577865601</c:v>
+                  <c:v>0.5353847742080689</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5103816390037537</c:v>
+                  <c:v>0.5059299468994141</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.4961052238941193</c:v>
+                  <c:v>0.4955341219902039</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.4889670014381409</c:v>
+                  <c:v>0.4816730320453644</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4639832973480225</c:v>
+                  <c:v>0.4747424721717835</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4568451046943665</c:v>
+                  <c:v>0.4504855573177338</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4532759785652161</c:v>
+                  <c:v>0.4435550272464752</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4497068822383881</c:v>
+                  <c:v>0.440089762210846</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4479223489761353</c:v>
+                  <c:v>0.4366244673728943</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4479223489761353</c:v>
+                  <c:v>0.4348918497562408</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4443532228469849</c:v>
+                  <c:v>0.4348918497562408</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.4247231781482697</c:v>
+                  <c:v>0.4314265549182892</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.4175849556922913</c:v>
+                  <c:v>0.4123675525188446</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.4068776667118073</c:v>
+                  <c:v>0.4054370224475861</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.4059853851795197</c:v>
+                  <c:v>0.3950411975383759</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3979549109935761</c:v>
+                  <c:v>0.3941748738288879</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3801093995571137</c:v>
+                  <c:v>0.3863780200481415</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3801093995571137</c:v>
+                  <c:v>0.3690516352653503</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3658329844474793</c:v>
+                  <c:v>0.3690516352653503</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3640484213829041</c:v>
+                  <c:v>0.3551905453205109</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3569102287292481</c:v>
+                  <c:v>0.353457897901535</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3569102287292481</c:v>
+                  <c:v>0.3465273678302765</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3319265246391296</c:v>
+                  <c:v>0.3465273678302765</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.3265728652477264</c:v>
+                  <c:v>0.3222704529762268</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.3069427907466888</c:v>
+                  <c:v>0.3170725405216217</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.3060505092144013</c:v>
+                  <c:v>0.2980135381221771</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.2998045980930328</c:v>
+                  <c:v>0.2971472144126892</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.2980200350284576</c:v>
+                  <c:v>0.2910829782485962</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.2962355017662048</c:v>
+                  <c:v>0.2893503606319428</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.2890972793102264</c:v>
+                  <c:v>0.2876177132129669</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.274820864200592</c:v>
+                  <c:v>0.280687153339386</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.26054447889328</c:v>
+                  <c:v>0.2668260633945465</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2426989525556564</c:v>
+                  <c:v>0.252964973449707</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2426989525556564</c:v>
+                  <c:v>0.2356386035680771</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.224853441119194</c:v>
+                  <c:v>0.2356386035680771</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.219499796628952</c:v>
+                  <c:v>0.2183122336864471</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2159306854009628</c:v>
+                  <c:v>0.213114321231842</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2087924778461456</c:v>
+                  <c:v>0.2096490561962128</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2070079296827316</c:v>
+                  <c:v>0.202718511223793</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2034388333559036</c:v>
+                  <c:v>0.2009858638048172</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.2034388333559036</c:v>
+                  <c:v>0.1975205987691879</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1980851739645004</c:v>
+                  <c:v>0.1975205987691879</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1963006258010864</c:v>
+                  <c:v>0.1923226863145828</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1963006258010864</c:v>
+                  <c:v>0.1905900537967682</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.182024210691452</c:v>
+                  <c:v>0.1905900537967682</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1713169068098068</c:v>
+                  <c:v>0.1767289489507675</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1677478104829788</c:v>
+                  <c:v>0.1663331389427185</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1659632623195648</c:v>
+                  <c:v>0.162867859005928</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1570405066013336</c:v>
+                  <c:v>0.1611352264881134</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1570405066013336</c:v>
+                  <c:v>0.1524720340967178</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1534713953733444</c:v>
+                  <c:v>0.1524720340967178</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1409795433282852</c:v>
+                  <c:v>0.1490067690610886</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.137410432100296</c:v>
+                  <c:v>0.1368783116340637</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.135625883936882</c:v>
+                  <c:v>0.1334130316972733</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1284876763820648</c:v>
+                  <c:v>0.1316803991794586</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1267031282186508</c:v>
+                  <c:v>0.1247498542070389</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1231340318918228</c:v>
+                  <c:v>0.1230172142386437</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1213494762778282</c:v>
+                  <c:v>0.1195519417524338</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1142112761735916</c:v>
+                  <c:v>0.1178193017840385</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1142112761735916</c:v>
+                  <c:v>0.1108887568116188</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.112426720559597</c:v>
+                  <c:v>0.1108887568116188</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.112426720559597</c:v>
+                  <c:v>0.1091561168432236</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1070730686187744</c:v>
+                  <c:v>0.1091561168432236</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1017194166779518</c:v>
+                  <c:v>0.1039582118391991</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.09993486106395721</c:v>
+                  <c:v>0.09876029938459396</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.09993486106395721</c:v>
+                  <c:v>0.09702765941619873</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.09993486106395721</c:v>
+                  <c:v>0.09702765941619873</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.09815031290054321</c:v>
+                  <c:v>0.09702765941619873</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.09815031290054321</c:v>
+                  <c:v>0.09529502689838409</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.09636576473712921</c:v>
+                  <c:v>0.09529502689838409</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.08744300901889801</c:v>
+                  <c:v>0.09356238692998886</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.08744300901889801</c:v>
+                  <c:v>0.08489920198917389</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.08208934962749481</c:v>
+                  <c:v>0.08489920198917389</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.08208934962749481</c:v>
+                  <c:v>0.07970129698514938</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.07673569768667221</c:v>
+                  <c:v>0.07970129698514938</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.07495114952325821</c:v>
+                  <c:v>0.07450338453054428</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.07495114952325821</c:v>
+                  <c:v>0.07277074456214905</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.07495114952325821</c:v>
+                  <c:v>0.07277074456214905</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07495114952325821</c:v>
+                  <c:v>0.07277074456214905</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07316659390926361</c:v>
+                  <c:v>0.07277074456214905</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.06959749758243561</c:v>
+                  <c:v>0.07103811204433441</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06781294196844101</c:v>
+                  <c:v>0.06757283210754395</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.05889018625020981</c:v>
+                  <c:v>0.06584019958972931</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.05353653430938721</c:v>
+                  <c:v>0.05717701464891434</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.05353653430938721</c:v>
+                  <c:v>0.05197910591959953</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.05175198242068291</c:v>
+                  <c:v>0.05197910591959953</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.04818288236856461</c:v>
+                  <c:v>0.05197910591959953</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.04818288236856461</c:v>
+                  <c:v>0.0502464659512043</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.04639833047986031</c:v>
+                  <c:v>0.04678119346499443</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.04639833047986031</c:v>
+                  <c:v>0.04678119346499443</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.04282922670245171</c:v>
+                  <c:v>0.0450485572218895</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04282922670245171</c:v>
+                  <c:v>0.04158328473567963</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04282922670245171</c:v>
+                  <c:v>0.04158328473567963</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.03926012665033341</c:v>
+                  <c:v>0.04158328473567963</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.03926012665033341</c:v>
+                  <c:v>0.03811800852417946</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.03926012665033341</c:v>
+                  <c:v>0.03811800852417946</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.03926012665033341</c:v>
+                  <c:v>0.03811800852417946</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03926012665033341</c:v>
+                  <c:v>0.03811800852417946</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03926012665033341</c:v>
+                  <c:v>0.03811800852417946</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03569102287292481</c:v>
+                  <c:v>0.03811800852417946</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03390647098422051</c:v>
+                  <c:v>0.03465273603796959</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.03212191909551621</c:v>
+                  <c:v>0.03292009979486466</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.03212191909551621</c:v>
+                  <c:v>0.03118746355175972</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.03212191909551621</c:v>
+                  <c:v>0.03118746355175972</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.03212191909551621</c:v>
+                  <c:v>0.03118746355175972</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.0285528190433979</c:v>
+                  <c:v>0.03118746355175972</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.0285528190433979</c:v>
+                  <c:v>0.0277221892029047</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.0285528190433979</c:v>
+                  <c:v>0.0277221892029047</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.0285528190433979</c:v>
+                  <c:v>0.0277221892029047</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.0267682671546936</c:v>
+                  <c:v>0.0277221892029047</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.0267682671546936</c:v>
+                  <c:v>0.02598955295979977</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02319916523993015</c:v>
+                  <c:v>0.02598955295979977</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02141461335122585</c:v>
+                  <c:v>0.02252427861094475</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.01427640952169895</c:v>
+                  <c:v>0.02079164236783981</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.007138204760849476</c:v>
+                  <c:v>0.01386109460145235</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.007138204760849476</c:v>
+                  <c:v>0.006930547300726175</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.003569102380424738</c:v>
+                  <c:v>0.006930547300726175</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.003569102380424738</c:v>
+                  <c:v>0.003465273650363088</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.003569102380424738</c:v>
+                  <c:v>0.003465273650363088</c:v>
                 </c:pt>
                 <c:pt idx="172">
+                  <c:v>0.003465273650363088</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2200,8 +2215,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H175" totalsRowCount="1">
-  <autoFilter ref="A2:H174"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H176" totalsRowCount="1">
+  <autoFilter ref="A2:H175"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -2217,8 +2232,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H175" totalsRowCount="1">
-  <autoFilter ref="A2:H174"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H176" totalsRowCount="1">
+  <autoFilter ref="A2:H175"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2518,7 +2533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2531,28 +2546,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2560,7 +2575,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>39.14816665649414</v>
+        <v>32.43435668945313</v>
       </c>
       <c r="C3" s="1">
         <v>16416</v>
@@ -2586,25 +2601,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>9.767963409423828</v>
+        <v>16.4384651184082</v>
       </c>
       <c r="C4" s="1">
-        <v>4096</v>
+        <v>8320</v>
       </c>
       <c r="D4" s="1">
-        <v>960</v>
+        <v>1434</v>
       </c>
       <c r="E4" s="1">
-        <v>960</v>
+        <v>1402</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H4" s="1">
-        <v>4096</v>
+        <v>8288</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2612,16 +2627,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>9.767963409423828</v>
+        <v>8.092782020568848</v>
       </c>
       <c r="C5" s="1">
         <v>4096</v>
       </c>
       <c r="D5" s="1">
-        <v>502</v>
+        <v>960</v>
       </c>
       <c r="E5" s="1">
-        <v>502</v>
+        <v>960</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2638,25 +2653,25 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>8.947607040405273</v>
+        <v>8.092782020568848</v>
       </c>
       <c r="C6" s="1">
-        <v>3752</v>
+        <v>4096</v>
       </c>
       <c r="D6" s="1">
-        <v>2140</v>
+        <v>502</v>
       </c>
       <c r="E6" s="1">
-        <v>2136</v>
+        <v>502</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>3748</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -2664,25 +2679,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>4.988910675048828</v>
+        <v>7.41311502456665</v>
       </c>
       <c r="C7" s="1">
-        <v>2092</v>
+        <v>3752</v>
       </c>
       <c r="D7" s="1">
-        <v>584</v>
+        <v>2140</v>
       </c>
       <c r="E7" s="1">
-        <v>568</v>
+        <v>2136</v>
       </c>
       <c r="F7" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1">
-        <v>2092</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2690,25 +2705,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.874442577362061</v>
+        <v>4.133325576782227</v>
       </c>
       <c r="C8" s="1">
-        <v>2044</v>
+        <v>2092</v>
       </c>
       <c r="D8" s="1">
-        <v>620</v>
+        <v>584</v>
       </c>
       <c r="E8" s="1">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F8" s="1">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>2044</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2716,25 +2731,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>4.01593017578125</v>
+        <v>4.038487911224365</v>
       </c>
       <c r="C9" s="1">
-        <v>1684</v>
+        <v>2044</v>
       </c>
       <c r="D9" s="1">
-        <v>1324</v>
+        <v>620</v>
       </c>
       <c r="E9" s="1">
-        <v>1324</v>
+        <v>564</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>1684</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2742,25 +2757,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>3.930078983306885</v>
+        <v>3.319305419921875</v>
       </c>
       <c r="C10" s="1">
-        <v>1648</v>
+        <v>1680</v>
       </c>
       <c r="D10" s="1">
-        <v>820</v>
+        <v>996</v>
       </c>
       <c r="E10" s="1">
-        <v>816</v>
+        <v>996</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>1644</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2768,25 +2783,25 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.458684206008911</v>
+        <v>3.256080389022827</v>
       </c>
       <c r="C11" s="1">
-        <v>1031</v>
+        <v>1648</v>
       </c>
       <c r="D11" s="1">
-        <v>498</v>
+        <v>820</v>
       </c>
       <c r="E11" s="1">
-        <v>498</v>
+        <v>816</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" s="1">
-        <v>1031</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -2794,25 +2809,25 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>2.441990852355957</v>
+        <v>2.037026166915894</v>
       </c>
       <c r="C12" s="1">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="D12" s="1">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="E12" s="1">
-        <v>36</v>
+        <v>498</v>
       </c>
       <c r="F12" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>1024</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -2820,25 +2835,25 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.707485795021057</v>
+        <v>2.023195505142212</v>
       </c>
       <c r="C13" s="1">
-        <v>716</v>
+        <v>1024</v>
       </c>
       <c r="D13" s="1">
-        <v>108</v>
+        <v>508</v>
       </c>
       <c r="E13" s="1">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>716</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -2846,25 +2861,25 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.8489733338356018</v>
+        <v>1.414656281471252</v>
       </c>
       <c r="C14" s="1">
-        <v>356</v>
+        <v>716</v>
       </c>
       <c r="D14" s="1">
-        <v>1050</v>
+        <v>108</v>
       </c>
       <c r="E14" s="1">
-        <v>694</v>
+        <v>108</v>
       </c>
       <c r="F14" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>352</v>
+        <v>716</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2872,25 +2887,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.8108172416687012</v>
+        <v>0.7745046019554138</v>
       </c>
       <c r="C15" s="1">
-        <v>340</v>
+        <v>392</v>
       </c>
       <c r="D15" s="1">
-        <v>344</v>
+        <v>4462</v>
       </c>
       <c r="E15" s="1">
-        <v>344</v>
+        <v>3966</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H15" s="1">
-        <v>340</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -2898,25 +2913,25 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.7154269814491272</v>
+        <v>0.7033765912055969</v>
       </c>
       <c r="C16" s="1">
-        <v>300</v>
+        <v>356</v>
       </c>
       <c r="D16" s="1">
-        <v>2344</v>
+        <v>1438</v>
       </c>
       <c r="E16" s="1">
-        <v>2284</v>
+        <v>1082</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G16" s="1">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="H16" s="1">
-        <v>240</v>
+        <v>352</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -2924,16 +2939,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.6391147971153259</v>
+        <v>0.6717641949653626</v>
       </c>
       <c r="C17" s="1">
-        <v>268</v>
+        <v>340</v>
       </c>
       <c r="D17" s="1">
-        <v>1604</v>
+        <v>344</v>
       </c>
       <c r="E17" s="1">
-        <v>1604</v>
+        <v>344</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -2942,7 +2957,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>268</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -2950,25 +2965,25 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.543724536895752</v>
+        <v>0.5927330851554871</v>
       </c>
       <c r="C18" s="1">
-        <v>228</v>
+        <v>300</v>
       </c>
       <c r="D18" s="1">
-        <v>756</v>
+        <v>2344</v>
       </c>
       <c r="E18" s="1">
-        <v>756</v>
+        <v>2284</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H18" s="1">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -2976,16 +2991,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.5341854691505432</v>
+        <v>0.5295082330703735</v>
       </c>
       <c r="C19" s="1">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="D19" s="1">
-        <v>242</v>
+        <v>1604</v>
       </c>
       <c r="E19" s="1">
-        <v>242</v>
+        <v>1604</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -2994,7 +3009,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>224</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3002,16 +3017,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.4864903390407562</v>
+        <v>0.4504771530628204</v>
       </c>
       <c r="C20" s="1">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="D20" s="1">
-        <v>548</v>
+        <v>756</v>
       </c>
       <c r="E20" s="1">
-        <v>548</v>
+        <v>756</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -3020,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>204</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3028,16 +3043,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.4769513309001923</v>
+        <v>0.4425740540027618</v>
       </c>
       <c r="C21" s="1">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="D21" s="1">
-        <v>332</v>
+        <v>242</v>
       </c>
       <c r="E21" s="1">
-        <v>332</v>
+        <v>242</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -3046,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>200</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3054,25 +3069,25 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.3147878646850586</v>
+        <v>0.4030584990978241</v>
       </c>
       <c r="C22" s="1">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="D22" s="1">
-        <v>4250</v>
+        <v>548</v>
       </c>
       <c r="E22" s="1">
-        <v>4238</v>
+        <v>548</v>
       </c>
       <c r="F22" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>132</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3080,16 +3095,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.3052488565444946</v>
+        <v>0.3951554000377655</v>
       </c>
       <c r="C23" s="1">
-        <v>128</v>
+        <v>200</v>
       </c>
       <c r="D23" s="1">
-        <v>120</v>
+        <v>332</v>
       </c>
       <c r="E23" s="1">
-        <v>120</v>
+        <v>332</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -3098,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>128</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3106,25 +3121,25 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2384756654500961</v>
+        <v>0.2608025670051575</v>
       </c>
       <c r="C24" s="1">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D24" s="1">
-        <v>228</v>
+        <v>4250</v>
       </c>
       <c r="E24" s="1">
-        <v>228</v>
+        <v>4238</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3132,16 +3147,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2003195583820343</v>
+        <v>0.2528994381427765</v>
       </c>
       <c r="C25" s="1">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="D25" s="1">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="E25" s="1">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -3150,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3158,16 +3173,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.1812414973974228</v>
+        <v>0.1975777000188828</v>
       </c>
       <c r="C26" s="1">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="D26" s="1">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="E26" s="1">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -3176,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3184,25 +3199,25 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1717024743556976</v>
+        <v>0.1659652590751648</v>
       </c>
       <c r="C27" s="1">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D27" s="1">
-        <v>400</v>
+        <v>252</v>
       </c>
       <c r="E27" s="1">
-        <v>392</v>
+        <v>252</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3210,25 +3225,25 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1717024743556976</v>
+        <v>0.1501590460538864</v>
       </c>
       <c r="C28" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D28" s="1">
-        <v>1028</v>
+        <v>136</v>
       </c>
       <c r="E28" s="1">
-        <v>468</v>
+        <v>136</v>
       </c>
       <c r="F28" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>24</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3236,25 +3251,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1717024743556976</v>
+        <v>0.1422559469938278</v>
       </c>
       <c r="C29" s="1">
         <v>72</v>
       </c>
       <c r="D29" s="1">
-        <v>970</v>
+        <v>400</v>
       </c>
       <c r="E29" s="1">
-        <v>958</v>
+        <v>392</v>
       </c>
       <c r="F29" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H29" s="1">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3262,25 +3277,25 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1621634513139725</v>
+        <v>0.1422559469938278</v>
       </c>
       <c r="C30" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D30" s="1">
-        <v>292</v>
+        <v>1028</v>
       </c>
       <c r="E30" s="1">
-        <v>292</v>
+        <v>468</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H30" s="1">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3288,25 +3303,25 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1526244282722473</v>
+        <v>0.1422559469938278</v>
       </c>
       <c r="C31" s="1">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D31" s="1">
-        <v>1150</v>
+        <v>970</v>
       </c>
       <c r="E31" s="1">
-        <v>1126</v>
+        <v>958</v>
       </c>
       <c r="F31" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3314,25 +3329,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1049292907118797</v>
+        <v>0.134352833032608</v>
       </c>
       <c r="C32" s="1">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D32" s="1">
-        <v>408</v>
+        <v>292</v>
       </c>
       <c r="E32" s="1">
-        <v>344</v>
+        <v>292</v>
       </c>
       <c r="F32" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3340,25 +3355,25 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.09539026767015457</v>
+        <v>0.1264497190713882</v>
       </c>
       <c r="C33" s="1">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D33" s="1">
-        <v>76</v>
+        <v>1150</v>
       </c>
       <c r="E33" s="1">
-        <v>76</v>
+        <v>1126</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H33" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3366,25 +3381,25 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.08585123717784882</v>
+        <v>0.08693418651819229</v>
       </c>
       <c r="C34" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D34" s="1">
-        <v>1082</v>
+        <v>408</v>
       </c>
       <c r="E34" s="1">
-        <v>1070</v>
+        <v>344</v>
       </c>
       <c r="F34" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H34" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3392,25 +3407,25 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.07631221413612366</v>
+        <v>0.0790310800075531</v>
       </c>
       <c r="C35" s="1">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D35" s="1">
-        <v>456</v>
+        <v>76</v>
       </c>
       <c r="E35" s="1">
-        <v>424</v>
+        <v>76</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3418,25 +3433,25 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.0667731836438179</v>
+        <v>0.07112797349691391</v>
       </c>
       <c r="C36" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D36" s="1">
-        <v>3716</v>
+        <v>1082</v>
       </c>
       <c r="E36" s="1">
-        <v>3232</v>
+        <v>1070</v>
       </c>
       <c r="F36" s="1">
-        <v>456</v>
+        <v>12</v>
       </c>
       <c r="G36" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -3444,22 +3459,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.05484940111637116</v>
+        <v>0.06322485953569412</v>
       </c>
       <c r="C37" s="1">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D37" s="1">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E37" s="1">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F37" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -3470,25 +3485,25 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.04769513383507729</v>
+        <v>0.04544287174940109</v>
       </c>
       <c r="C38" s="1">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D38" s="1">
-        <v>192</v>
+        <v>455</v>
       </c>
       <c r="E38" s="1">
-        <v>192</v>
+        <v>420</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H38" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3496,25 +3511,25 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.04769513383507729</v>
+        <v>0.03951554000377655</v>
       </c>
       <c r="C39" s="1">
         <v>20</v>
       </c>
       <c r="D39" s="1">
-        <v>1046</v>
+        <v>192</v>
       </c>
       <c r="E39" s="1">
-        <v>1026</v>
+        <v>192</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
         <v>20</v>
-      </c>
-      <c r="H39" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3522,22 +3537,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.02861708030104637</v>
+        <v>0.03951554000377655</v>
       </c>
       <c r="C40" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D40" s="1">
-        <v>142</v>
+        <v>1094</v>
       </c>
       <c r="E40" s="1">
-        <v>130</v>
+        <v>1074</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H40" s="1">
         <v>0</v>
@@ -3548,16 +3563,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.02861708030104637</v>
+        <v>0.02370932325720787</v>
       </c>
       <c r="C41" s="1">
         <v>12</v>
       </c>
       <c r="D41" s="1">
-        <v>798</v>
+        <v>142</v>
       </c>
       <c r="E41" s="1">
-        <v>786</v>
+        <v>130</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -3574,19 +3589,19 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.02861708030104637</v>
+        <v>0.02370932325720787</v>
       </c>
       <c r="C42" s="1">
         <v>12</v>
       </c>
       <c r="D42" s="1">
-        <v>126</v>
+        <v>798</v>
       </c>
       <c r="E42" s="1">
-        <v>102</v>
+        <v>786</v>
       </c>
       <c r="F42" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
         <v>12</v>
@@ -3600,16 +3615,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.02861708030104637</v>
+        <v>0.02370932325720787</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
       </c>
       <c r="D43" s="1">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="E43" s="1">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="F43" s="1">
         <v>12</v>
@@ -3626,22 +3641,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.01907805353403091</v>
+        <v>0.02370932325720787</v>
       </c>
       <c r="C44" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D44" s="1">
-        <v>2874</v>
+        <v>172</v>
       </c>
       <c r="E44" s="1">
-        <v>2866</v>
+        <v>148</v>
       </c>
       <c r="F44" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G44" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3652,16 +3667,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01907805353403091</v>
+        <v>0.01580621488392353</v>
       </c>
       <c r="C45" s="1">
         <v>8</v>
       </c>
       <c r="D45" s="1">
-        <v>426</v>
+        <v>2874</v>
       </c>
       <c r="E45" s="1">
-        <v>418</v>
+        <v>2866</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3678,19 +3693,19 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01907805353403091</v>
+        <v>0.01580621488392353</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
       </c>
       <c r="D46" s="1">
-        <v>54</v>
+        <v>426</v>
       </c>
       <c r="E46" s="1">
-        <v>34</v>
+        <v>418</v>
       </c>
       <c r="F46" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
         <v>8</v>
@@ -3704,22 +3719,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.009539026767015457</v>
+        <v>0.01580621488392353</v>
       </c>
       <c r="C47" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D47" s="1">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="E47" s="1">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G47" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
@@ -3730,16 +3745,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.009539026767015457</v>
+        <v>0.007903107441961765</v>
       </c>
       <c r="C48" s="1">
         <v>4</v>
       </c>
       <c r="D48" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E48" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3756,19 +3771,19 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.009539026767015457</v>
+        <v>0.007903107441961765</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
       </c>
       <c r="D49" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E49" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1">
         <v>4</v>
@@ -3782,19 +3797,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.009539026767015457</v>
+        <v>0.007903107441961765</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
       </c>
       <c r="D50" s="1">
-        <v>1630</v>
+        <v>44</v>
       </c>
       <c r="E50" s="1">
-        <v>1290</v>
+        <v>16</v>
       </c>
       <c r="F50" s="1">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -3808,19 +3823,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.009539026767015457</v>
+        <v>0.007903107441961765</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
       </c>
       <c r="D51" s="1">
-        <v>272</v>
+        <v>1624</v>
       </c>
       <c r="E51" s="1">
-        <v>268</v>
+        <v>1284</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G51" s="1">
         <v>4</v>
@@ -3834,16 +3849,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.009539026767015457</v>
+        <v>0.007903107441961765</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
       </c>
       <c r="D52" s="1">
-        <v>502</v>
+        <v>272</v>
       </c>
       <c r="E52" s="1">
-        <v>498</v>
+        <v>268</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3860,19 +3875,19 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.009539026767015457</v>
+        <v>0.007903107441961765</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
       </c>
       <c r="D53" s="1">
-        <v>84</v>
+        <v>502</v>
       </c>
       <c r="E53" s="1">
-        <v>48</v>
+        <v>498</v>
       </c>
       <c r="F53" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G53" s="1">
         <v>4</v>
@@ -3886,56 +3901,82 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.007154270075261593</v>
+        <v>0.007903107441961765</v>
       </c>
       <c r="C54" s="1">
+        <v>4</v>
+      </c>
+      <c r="D54" s="1">
+        <v>84</v>
+      </c>
+      <c r="E54" s="1">
+        <v>48</v>
+      </c>
+      <c r="F54" s="1">
+        <v>32</v>
+      </c>
+      <c r="G54" s="1">
+        <v>4</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.005927330814301968</v>
+      </c>
+      <c r="C55" s="1">
         <v>3</v>
       </c>
-      <c r="D54" s="1">
-        <v>875</v>
-      </c>
-      <c r="E54" s="1">
-        <v>872</v>
-      </c>
-      <c r="F54" s="1">
-        <v>0</v>
-      </c>
-      <c r="G54" s="1">
+      <c r="D55" s="1">
+        <v>1011</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1008</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
         <v>3</v>
       </c>
-      <c r="H54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8">
-      <c r="A175" t="s">
-        <v>174</v>
-      </c>
-      <c r="B175">
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" t="s">
+        <v>175</v>
+      </c>
+      <c r="B176">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C175">
+      <c r="C176">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D175">
+      <c r="D176">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E175">
+      <c r="E176">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F175">
+      <c r="F176">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G175">
+      <c r="G176">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H175">
+      <c r="H176">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -3951,7 +3992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -3964,36 +4005,36 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H2" t="s">
         <v>182</v>
-      </c>
-      <c r="C2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H2" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2">
-        <v>4.232955455780029</v>
+        <v>4.109814643859863</v>
       </c>
       <c r="C3" s="1">
         <v>4744</v>
@@ -4016,71 +4057,71 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>3.792171239852905</v>
+        <v>3.865512847900391</v>
       </c>
       <c r="C4" s="1">
-        <v>4250</v>
+        <v>4462</v>
       </c>
       <c r="D4" s="1">
-        <v>132</v>
+        <v>392</v>
       </c>
       <c r="E4" s="1">
-        <v>4238</v>
+        <v>3966</v>
       </c>
       <c r="F4" s="1">
-        <v>12</v>
+        <v>468</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H4" s="1">
-        <v>132</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>3.315696001052856</v>
+        <v>3.681853294372559</v>
       </c>
       <c r="C5" s="1">
-        <v>3716</v>
+        <v>4250</v>
       </c>
       <c r="D5" s="1">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="E5" s="1">
-        <v>3232</v>
+        <v>4238</v>
       </c>
       <c r="F5" s="1">
-        <v>456</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>3.283574104309082</v>
+        <v>3.375176429748535</v>
       </c>
       <c r="C6" s="1">
-        <v>3680</v>
+        <v>3896</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>3680</v>
+        <v>3896</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -4094,19 +4135,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>3.160439968109131</v>
+        <v>3.188051700592041</v>
       </c>
       <c r="C7" s="1">
-        <v>3542</v>
+        <v>3680</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>3542</v>
+        <v>3680</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -4120,10 +4161,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>2.957001209259033</v>
+        <v>2.870979309082031</v>
       </c>
       <c r="C8" s="1">
         <v>3314</v>
@@ -4146,10 +4187,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>2.846359014511108</v>
+        <v>2.763555765151978</v>
       </c>
       <c r="C9" s="1">
         <v>3190</v>
@@ -4172,10 +4213,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2">
-        <v>2.56439995765686</v>
+        <v>2.489799022674561</v>
       </c>
       <c r="C10" s="1">
         <v>2874</v>
@@ -4198,10 +4239,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2">
-        <v>2.542985439300537</v>
+        <v>2.46900749206543</v>
       </c>
       <c r="C11" s="1">
         <v>2850</v>
@@ -4224,10 +4265,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2">
-        <v>2.141461372375488</v>
+        <v>2.079164266586304</v>
       </c>
       <c r="C12" s="1">
         <v>2400</v>
@@ -4250,10 +4291,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="2">
-        <v>2.11826229095459</v>
+        <v>2.056639909744263</v>
       </c>
       <c r="C13" s="1">
         <v>2374</v>
@@ -4276,10 +4317,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2">
-        <v>2.098632097244263</v>
+        <v>2.037580966949463</v>
       </c>
       <c r="C14" s="1">
         <v>2352</v>
@@ -4302,10 +4343,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2">
-        <v>2.095062971115112</v>
+        <v>2.034115552902222</v>
       </c>
       <c r="C15" s="1">
         <v>2348</v>
@@ -4328,10 +4369,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>2.091493844985962</v>
+        <v>2.03065037727356</v>
       </c>
       <c r="C16" s="1">
         <v>2344</v>
@@ -4354,10 +4395,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2">
-        <v>1.979067206382752</v>
+        <v>1.921494245529175</v>
       </c>
       <c r="C17" s="1">
         <v>2218</v>
@@ -4380,10 +4421,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" s="2">
-        <v>1.909469723701477</v>
+        <v>1.853921413421631</v>
       </c>
       <c r="C18" s="1">
         <v>2140</v>
@@ -4406,10 +4447,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2">
-        <v>1.830949425697327</v>
+        <v>1.777685403823853</v>
       </c>
       <c r="C19" s="1">
         <v>2052</v>
@@ -4432,10 +4473,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2">
-        <v>1.695323586463928</v>
+        <v>1.646004915237427</v>
       </c>
       <c r="C20" s="1">
         <v>1900</v>
@@ -4458,10 +4499,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2">
-        <v>1.695323586463928</v>
+        <v>1.646004915237427</v>
       </c>
       <c r="C21" s="1">
         <v>1900</v>
@@ -4484,10 +4525,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2">
-        <v>1.611449718475342</v>
+        <v>1.564571022987366</v>
       </c>
       <c r="C22" s="1">
         <v>1806</v>
@@ -4510,19 +4551,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2">
-        <v>1.454409122467041</v>
+        <v>1.406901121139526</v>
       </c>
       <c r="C23" s="1">
-        <v>1630</v>
+        <v>1624</v>
       </c>
       <c r="D23" s="1">
         <v>4</v>
       </c>
       <c r="E23" s="1">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="F23" s="1">
         <v>336</v>
@@ -4536,10 +4577,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="2">
-        <v>1.434779167175293</v>
+        <v>1.39303994178772</v>
       </c>
       <c r="C24" s="1">
         <v>1608</v>
@@ -4562,10 +4603,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B25" s="2">
-        <v>1.431210041046143</v>
+        <v>1.389574766159058</v>
       </c>
       <c r="C25" s="1">
         <v>1604</v>
@@ -4588,54 +4629,54 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="B26" s="2">
-        <v>1.243832111358643</v>
+        <v>1.245765924453735</v>
       </c>
       <c r="C26" s="1">
-        <v>1394</v>
+        <v>1438</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E26" s="1">
-        <v>1394</v>
+        <v>1082</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B27" s="2">
-        <v>1.181372880935669</v>
+        <v>1.242300629615784</v>
       </c>
       <c r="C27" s="1">
-        <v>1324</v>
+        <v>1434</v>
       </c>
       <c r="D27" s="1">
-        <v>1684</v>
+        <v>8320</v>
       </c>
       <c r="E27" s="1">
-        <v>1324</v>
+        <v>1402</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H27" s="1">
-        <v>1684</v>
+        <v>8288</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4643,16 +4684,16 @@
         <v>70</v>
       </c>
       <c r="B28" s="2">
-        <v>1.176019191741943</v>
+        <v>1.207647800445557</v>
       </c>
       <c r="C28" s="1">
-        <v>1318</v>
+        <v>1394</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>1318</v>
+        <v>1394</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -4669,16 +4710,16 @@
         <v>71</v>
       </c>
       <c r="B29" s="2">
-        <v>1.088576197624207</v>
+        <v>1.141807675361633</v>
       </c>
       <c r="C29" s="1">
-        <v>1220</v>
+        <v>1318</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>1220</v>
+        <v>1318</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -4695,16 +4736,16 @@
         <v>72</v>
       </c>
       <c r="B30" s="2">
-        <v>1.070730686187744</v>
+        <v>1.081165313720703</v>
       </c>
       <c r="C30" s="1">
-        <v>1200</v>
+        <v>1248</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>1200</v>
+        <v>1248</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -4721,19 +4762,19 @@
         <v>73</v>
       </c>
       <c r="B31" s="2">
-        <v>1.067161560058594</v>
+        <v>1.056908488273621</v>
       </c>
       <c r="C31" s="1">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>1168</v>
+        <v>1220</v>
       </c>
       <c r="F31" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
@@ -4747,16 +4788,16 @@
         <v>74</v>
       </c>
       <c r="B32" s="2">
-        <v>1.043962359428406</v>
+        <v>1.039582133293152</v>
       </c>
       <c r="C32" s="1">
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -4770,97 +4811,97 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="B33" s="2">
-        <v>1.026116847991943</v>
+        <v>1.0361168384552</v>
       </c>
       <c r="C33" s="1">
-        <v>1150</v>
+        <v>1196</v>
       </c>
       <c r="D33" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>1126</v>
+        <v>1168</v>
       </c>
       <c r="F33" s="1">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G33" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="B34" s="2">
-        <v>0.9654421806335449</v>
+        <v>1.013592481613159</v>
       </c>
       <c r="C34" s="1">
-        <v>1082</v>
+        <v>1170</v>
       </c>
       <c r="D34" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>1070</v>
+        <v>1170</v>
       </c>
       <c r="F34" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B35" s="2">
-        <v>0.9368893504142761</v>
+        <v>0.9962661862373352</v>
       </c>
       <c r="C35" s="1">
-        <v>1050</v>
+        <v>1150</v>
       </c>
       <c r="D35" s="1">
-        <v>356</v>
+        <v>64</v>
       </c>
       <c r="E35" s="1">
-        <v>694</v>
+        <v>1126</v>
       </c>
       <c r="F35" s="1">
-        <v>352</v>
+        <v>8</v>
       </c>
       <c r="G35" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H35" s="1">
-        <v>352</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9333202242851257</v>
+        <v>0.9477523565292358</v>
       </c>
       <c r="C36" s="1">
-        <v>1046</v>
+        <v>1094</v>
       </c>
       <c r="D36" s="1">
         <v>20</v>
       </c>
       <c r="E36" s="1">
-        <v>1026</v>
+        <v>1074</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -4874,97 +4915,97 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9172592759132385</v>
+        <v>0.9373565316200256</v>
       </c>
       <c r="C37" s="1">
-        <v>1028</v>
+        <v>1082</v>
       </c>
       <c r="D37" s="1">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="E37" s="1">
-        <v>468</v>
+        <v>1070</v>
       </c>
       <c r="F37" s="1">
-        <v>512</v>
+        <v>12</v>
       </c>
       <c r="G37" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8655073046684265</v>
+        <v>0.8905753493309021</v>
       </c>
       <c r="C38" s="1">
-        <v>970</v>
+        <v>1028</v>
       </c>
       <c r="D38" s="1">
         <v>72</v>
       </c>
       <c r="E38" s="1">
-        <v>958</v>
+        <v>468</v>
       </c>
       <c r="F38" s="1">
-        <v>12</v>
+        <v>512</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H38" s="1">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8565845489501953</v>
+        <v>0.8758479356765747</v>
       </c>
       <c r="C39" s="1">
-        <v>960</v>
+        <v>1011</v>
       </c>
       <c r="D39" s="1">
-        <v>4096</v>
+        <v>3</v>
       </c>
       <c r="E39" s="1">
-        <v>960</v>
+        <v>1008</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="B40" s="2">
-        <v>0.8530154228210449</v>
+        <v>0.8628531098365784</v>
       </c>
       <c r="C40" s="1">
-        <v>956</v>
+        <v>996</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="E40" s="1">
-        <v>956</v>
+        <v>996</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -4973,50 +5014,50 @@
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="B41" s="2">
-        <v>0.7807410955429077</v>
+        <v>0.8403288722038269</v>
       </c>
       <c r="C41" s="1">
-        <v>875</v>
+        <v>970</v>
       </c>
       <c r="D41" s="1">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="E41" s="1">
-        <v>872</v>
+        <v>958</v>
       </c>
       <c r="F41" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G41" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7637878656387329</v>
+        <v>0.8316656947135925</v>
       </c>
       <c r="C42" s="1">
-        <v>856</v>
+        <v>960</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="E42" s="1">
-        <v>856</v>
+        <v>960</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -5025,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -5033,16 +5074,16 @@
         <v>77</v>
       </c>
       <c r="B43" s="2">
-        <v>0.7584342360496521</v>
+        <v>0.8282003998756409</v>
       </c>
       <c r="C43" s="1">
-        <v>850</v>
+        <v>956</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>850</v>
+        <v>956</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -5059,16 +5100,16 @@
         <v>78</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7423732876777649</v>
+        <v>0.7415685653686523</v>
       </c>
       <c r="C44" s="1">
-        <v>832</v>
+        <v>856</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>832</v>
+        <v>856</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -5082,51 +5123,51 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7316659688949585</v>
+        <v>0.7363706231117249</v>
       </c>
       <c r="C45" s="1">
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="D45" s="1">
-        <v>1648</v>
+        <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>816</v>
+        <v>850</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
       <c r="G45" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>1644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7120358943939209</v>
+        <v>0.7207769155502319</v>
       </c>
       <c r="C46" s="1">
-        <v>798</v>
+        <v>832</v>
       </c>
       <c r="D46" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>786</v>
+        <v>832</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
       </c>
       <c r="G46" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -5134,71 +5175,71 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="B47" s="2">
-        <v>0.6995440721511841</v>
+        <v>0.7103810906410217</v>
       </c>
       <c r="C47" s="1">
-        <v>784</v>
+        <v>820</v>
       </c>
       <c r="D47" s="1">
-        <v>0</v>
+        <v>1648</v>
       </c>
       <c r="E47" s="1">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B48" s="2">
-        <v>0.6745603084564209</v>
+        <v>0.6913220882415772</v>
       </c>
       <c r="C48" s="1">
-        <v>756</v>
+        <v>798</v>
       </c>
       <c r="D48" s="1">
-        <v>228</v>
+        <v>12</v>
       </c>
       <c r="E48" s="1">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H48" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6424384117126465</v>
+        <v>0.6791936159133911</v>
       </c>
       <c r="C49" s="1">
-        <v>720</v>
+        <v>784</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>720</v>
+        <v>784</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -5212,19 +5253,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6424384117126465</v>
+        <v>0.6549367308616638</v>
       </c>
       <c r="C50" s="1">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E50" s="1">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -5233,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -5241,16 +5282,16 @@
         <v>82</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6103165149688721</v>
+        <v>0.6237492561340332</v>
       </c>
       <c r="C51" s="1">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -5267,16 +5308,16 @@
         <v>83</v>
       </c>
       <c r="B52" s="2">
-        <v>0.5978246331214905</v>
+        <v>0.6237492561340332</v>
       </c>
       <c r="C52" s="1">
-        <v>670</v>
+        <v>720</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>670</v>
+        <v>720</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -5293,16 +5334,16 @@
         <v>84</v>
       </c>
       <c r="B53" s="2">
-        <v>0.5746254920959473</v>
+        <v>0.5925617814064026</v>
       </c>
       <c r="C53" s="1">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -5316,106 +5357,106 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="B54" s="2">
-        <v>0.5532108545303345</v>
+        <v>0.5579090714454651</v>
       </c>
       <c r="C54" s="1">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="D54" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>564</v>
+        <v>644</v>
       </c>
       <c r="F54" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5514262914657593</v>
+        <v>0.5371174216270447</v>
       </c>
       <c r="C55" s="1">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D55" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
       <c r="E55" s="1">
-        <v>618</v>
+        <v>564</v>
       </c>
       <c r="F55" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5210889577865601</v>
+        <v>0.5353847742080689</v>
       </c>
       <c r="C56" s="1">
-        <v>584</v>
+        <v>618</v>
       </c>
       <c r="D56" s="1">
-        <v>2092</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>568</v>
+        <v>618</v>
       </c>
       <c r="F56" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>2092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5103816390037537</v>
+        <v>0.5059299468994141</v>
       </c>
       <c r="C57" s="1">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <v>2092</v>
       </c>
       <c r="E57" s="1">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="F57" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5423,19 +5464,19 @@
         <v>87</v>
       </c>
       <c r="B58" s="2">
-        <v>0.4961052238941193</v>
+        <v>0.4955341219902039</v>
       </c>
       <c r="C58" s="1">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>44</v>
+        <v>564</v>
       </c>
       <c r="F58" s="1">
-        <v>512</v>
+        <v>8</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
@@ -5446,149 +5487,149 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="B59" s="2">
-        <v>0.4889670014381409</v>
+        <v>0.4816730320453644</v>
       </c>
       <c r="C59" s="1">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="D59" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>548</v>
+        <v>44</v>
       </c>
       <c r="F59" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4639832973480225</v>
+        <v>0.4747424721717835</v>
       </c>
       <c r="C60" s="1">
-        <v>520</v>
+        <v>548</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="E60" s="1">
-        <v>328</v>
+        <v>548</v>
       </c>
       <c r="F60" s="1">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4568451046943665</v>
+        <v>0.4504855573177338</v>
       </c>
       <c r="C61" s="1">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D61" s="1">
-        <v>16416</v>
+        <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>480</v>
+        <v>328</v>
       </c>
       <c r="F61" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G61" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>16384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4532759785652161</v>
+        <v>0.4435550272464752</v>
       </c>
       <c r="C62" s="1">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D62" s="1">
-        <v>1024</v>
+        <v>16416</v>
       </c>
       <c r="E62" s="1">
-        <v>36</v>
+        <v>480</v>
       </c>
       <c r="F62" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H62" s="1">
-        <v>1024</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4497068822383881</v>
+        <v>0.440089762210846</v>
       </c>
       <c r="C63" s="1">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E63" s="1">
-        <v>504</v>
+        <v>36</v>
       </c>
       <c r="F63" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>3</v>
+        <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4479223489761353</v>
+        <v>0.4366244673728943</v>
       </c>
       <c r="C64" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D64" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -5597,47 +5638,47 @@
         <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4479223489761353</v>
+        <v>0.4348918497562408</v>
       </c>
       <c r="C65" s="1">
         <v>502</v>
       </c>
       <c r="D65" s="1">
-        <v>4</v>
+        <v>4096</v>
       </c>
       <c r="E65" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4443532228469849</v>
+        <v>0.4348918497562408</v>
       </c>
       <c r="C66" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D66" s="1">
-        <v>1031</v>
+        <v>4</v>
       </c>
       <c r="E66" s="1">
         <v>498</v>
@@ -5646,27 +5687,27 @@
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H66" s="1">
-        <v>1031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="B67" s="2">
-        <v>0.4247231781482697</v>
+        <v>0.4314265549182892</v>
       </c>
       <c r="C67" s="1">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="D67" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="E67" s="1">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -5675,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -5683,16 +5724,16 @@
         <v>91</v>
       </c>
       <c r="B68" s="2">
-        <v>0.4175849556922913</v>
+        <v>0.4123675525188446</v>
       </c>
       <c r="C68" s="1">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -5706,25 +5747,25 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="B69" s="2">
-        <v>0.4068776667118073</v>
+        <v>0.4054370224475861</v>
       </c>
       <c r="C69" s="1">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="D69" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H69" s="1">
         <v>0</v>
@@ -5735,22 +5776,22 @@
         <v>35</v>
       </c>
       <c r="B70" s="2">
-        <v>0.4059853851795197</v>
+        <v>0.3950411975383759</v>
       </c>
       <c r="C70" s="1">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D70" s="1">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E70" s="1">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F70" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -5758,25 +5799,25 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3979549109935761</v>
+        <v>0.3941748738288879</v>
       </c>
       <c r="C71" s="1">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="D71" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E71" s="1">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="F71" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -5787,16 +5828,16 @@
         <v>93</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3801093995571137</v>
+        <v>0.3863780200481415</v>
       </c>
       <c r="C72" s="1">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -5810,25 +5851,25 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3801093995571137</v>
+        <v>0.3690516352653503</v>
       </c>
       <c r="C73" s="1">
         <v>426</v>
       </c>
       <c r="D73" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -5836,25 +5877,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3658329844474793</v>
+        <v>0.3690516352653503</v>
       </c>
       <c r="C74" s="1">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="D74" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E74" s="1">
-        <v>330</v>
+        <v>418</v>
       </c>
       <c r="F74" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -5862,25 +5903,25 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3640484213829041</v>
+        <v>0.3551905453205109</v>
       </c>
       <c r="C75" s="1">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D75" s="1">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="F75" s="1">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G75" s="1">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -5888,25 +5929,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3569102287292481</v>
+        <v>0.353457897901535</v>
       </c>
       <c r="C76" s="1">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D76" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E76" s="1">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="F76" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -5914,54 +5955,54 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3569102287292481</v>
+        <v>0.3465273678302765</v>
       </c>
       <c r="C77" s="1">
         <v>400</v>
       </c>
       <c r="D77" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
       </c>
       <c r="G77" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H77" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3319265246391296</v>
+        <v>0.3465273678302765</v>
       </c>
       <c r="C78" s="1">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="D78" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E78" s="1">
-        <v>340</v>
+        <v>392</v>
       </c>
       <c r="F78" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G78" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H78" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -5969,19 +6010,19 @@
         <v>97</v>
       </c>
       <c r="B79" s="2">
-        <v>0.3265728652477264</v>
+        <v>0.3222704529762268</v>
       </c>
       <c r="C79" s="1">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="F79" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
@@ -5992,19 +6033,19 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="B80" s="2">
-        <v>0.3069427907466888</v>
+        <v>0.3170725405216217</v>
       </c>
       <c r="C80" s="1">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="D80" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -6013,33 +6054,33 @@
         <v>0</v>
       </c>
       <c r="H80" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="B81" s="2">
-        <v>0.3060505092144013</v>
+        <v>0.2980135381221771</v>
       </c>
       <c r="C81" s="1">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D81" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E81" s="1">
-        <v>0</v>
+        <v>344</v>
       </c>
       <c r="F81" s="1">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -6047,19 +6088,19 @@
         <v>99</v>
       </c>
       <c r="B82" s="2">
-        <v>0.2998045980930328</v>
+        <v>0.2971472144126892</v>
       </c>
       <c r="C82" s="1">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -6073,16 +6114,16 @@
         <v>100</v>
       </c>
       <c r="B83" s="2">
-        <v>0.2980200350284576</v>
+        <v>0.2910829782485962</v>
       </c>
       <c r="C83" s="1">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -6096,19 +6137,19 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="B84" s="2">
-        <v>0.2962355017662048</v>
+        <v>0.2893503606319428</v>
       </c>
       <c r="C84" s="1">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D84" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -6117,24 +6158,24 @@
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="B85" s="2">
-        <v>0.2890972793102264</v>
+        <v>0.2876177132129669</v>
       </c>
       <c r="C85" s="1">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="D85" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E85" s="1">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -6143,7 +6184,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -6151,19 +6192,19 @@
         <v>102</v>
       </c>
       <c r="B86" s="2">
-        <v>0.274820864200592</v>
+        <v>0.280687153339386</v>
       </c>
       <c r="C86" s="1">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="F86" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G86" s="1">
         <v>0</v>
@@ -6174,77 +6215,77 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="B87" s="2">
-        <v>0.26054447889328</v>
+        <v>0.2668260633945465</v>
       </c>
       <c r="C87" s="1">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="D87" s="1">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E87" s="1">
         <v>292</v>
       </c>
       <c r="F87" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2426989525556564</v>
+        <v>0.252964973449707</v>
       </c>
       <c r="C88" s="1">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="D88" s="1">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="E88" s="1">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
       </c>
       <c r="G88" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2426989525556564</v>
+        <v>0.2356386035680771</v>
       </c>
       <c r="C89" s="1">
         <v>272</v>
       </c>
       <c r="D89" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E89" s="1">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
       </c>
       <c r="G89" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -6252,19 +6293,19 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="B90" s="2">
-        <v>0.224853441119194</v>
+        <v>0.2356386035680771</v>
       </c>
       <c r="C90" s="1">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="D90" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -6273,76 +6314,76 @@
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="B91" s="2">
-        <v>0.219499796628952</v>
+        <v>0.2183122336864471</v>
       </c>
       <c r="C91" s="1">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D91" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E91" s="1">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="F91" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G91" s="1">
         <v>0</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2159306854009628</v>
+        <v>0.213114321231842</v>
       </c>
       <c r="C92" s="1">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D92" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F92" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G92" s="1">
         <v>0</v>
       </c>
       <c r="H92" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2087924778461456</v>
+        <v>0.2096490561962128</v>
       </c>
       <c r="C93" s="1">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="D93" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E93" s="1">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -6351,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -6359,19 +6400,19 @@
         <v>106</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2070079296827316</v>
+        <v>0.202718511223793</v>
       </c>
       <c r="C94" s="1">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="F94" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G94" s="1">
         <v>0</v>
@@ -6385,19 +6426,19 @@
         <v>107</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2034388333559036</v>
+        <v>0.2009858638048172</v>
       </c>
       <c r="C95" s="1">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="F95" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G95" s="1">
         <v>0</v>
@@ -6408,16 +6449,16 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="B96" s="2">
-        <v>0.2034388333559036</v>
+        <v>0.1975205987691879</v>
       </c>
       <c r="C96" s="1">
         <v>228</v>
       </c>
       <c r="D96" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E96" s="1">
         <v>228</v>
@@ -6429,24 +6470,24 @@
         <v>0</v>
       </c>
       <c r="H96" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1980851739645004</v>
+        <v>0.1975205987691879</v>
       </c>
       <c r="C97" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D97" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E97" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -6455,7 +6496,7 @@
         <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -6463,16 +6504,16 @@
         <v>109</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1963006258010864</v>
+        <v>0.1923226863145828</v>
       </c>
       <c r="C98" s="1">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F98" s="1">
         <v>0</v>
@@ -6489,7 +6530,7 @@
         <v>110</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1963006258010864</v>
+        <v>0.1905900537967682</v>
       </c>
       <c r="C99" s="1">
         <v>220</v>
@@ -6498,10 +6539,10 @@
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="F99" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
@@ -6515,10 +6556,10 @@
         <v>111</v>
       </c>
       <c r="B100" s="2">
-        <v>0.182024210691452</v>
+        <v>0.1905900537967682</v>
       </c>
       <c r="C100" s="1">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
@@ -6527,7 +6568,7 @@
         <v>204</v>
       </c>
       <c r="F100" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G100" s="1">
         <v>0</v>
@@ -6538,19 +6579,19 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1713169068098068</v>
+        <v>0.1767289489507675</v>
       </c>
       <c r="C101" s="1">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="D101" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -6559,24 +6600,24 @@
         <v>0</v>
       </c>
       <c r="H101" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1677478104829788</v>
+        <v>0.1663331389427185</v>
       </c>
       <c r="C102" s="1">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D102" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E102" s="1">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -6585,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -6593,16 +6634,16 @@
         <v>113</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1659632623195648</v>
+        <v>0.162867859005928</v>
       </c>
       <c r="C103" s="1">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
@@ -6619,16 +6660,16 @@
         <v>114</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1570405066013336</v>
+        <v>0.1611352264881134</v>
       </c>
       <c r="C104" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D104" s="1">
         <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -6645,7 +6686,7 @@
         <v>115</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1570405066013336</v>
+        <v>0.1524720340967178</v>
       </c>
       <c r="C105" s="1">
         <v>176</v>
@@ -6668,25 +6709,25 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1534713953733444</v>
+        <v>0.1524720340967178</v>
       </c>
       <c r="C106" s="1">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D106" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="F106" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G106" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -6694,25 +6735,25 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1409795433282852</v>
+        <v>0.1490067690610886</v>
       </c>
       <c r="C107" s="1">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D107" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E107" s="1">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F107" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G107" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -6723,16 +6764,16 @@
         <v>117</v>
       </c>
       <c r="B108" s="2">
-        <v>0.137410432100296</v>
+        <v>0.1368783116340637</v>
       </c>
       <c r="C108" s="1">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -6749,16 +6790,16 @@
         <v>118</v>
       </c>
       <c r="B109" s="2">
-        <v>0.135625883936882</v>
+        <v>0.1334130316972733</v>
       </c>
       <c r="C109" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -6775,16 +6816,16 @@
         <v>119</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1284876763820648</v>
+        <v>0.1316803991794586</v>
       </c>
       <c r="C110" s="1">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -6798,25 +6839,25 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1267031282186508</v>
+        <v>0.1247498542070389</v>
       </c>
       <c r="C111" s="1">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D111" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -6824,25 +6865,25 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1231340318918228</v>
+        <v>0.1230172142386437</v>
       </c>
       <c r="C112" s="1">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D112" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E112" s="1">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -6850,19 +6891,19 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1213494762778282</v>
+        <v>0.1195519417524338</v>
       </c>
       <c r="C113" s="1">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D113" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -6871,24 +6912,24 @@
         <v>0</v>
       </c>
       <c r="H113" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1142112761735916</v>
+        <v>0.1178193017840385</v>
       </c>
       <c r="C114" s="1">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D114" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E114" s="1">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -6897,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6905,7 +6946,7 @@
         <v>122</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1142112761735916</v>
+        <v>0.1108887568116188</v>
       </c>
       <c r="C115" s="1">
         <v>128</v>
@@ -6931,16 +6972,16 @@
         <v>123</v>
       </c>
       <c r="B116" s="2">
-        <v>0.112426720559597</v>
+        <v>0.1108887568116188</v>
       </c>
       <c r="C116" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -6954,25 +6995,25 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="B117" s="2">
-        <v>0.112426720559597</v>
+        <v>0.1091561168432236</v>
       </c>
       <c r="C117" s="1">
         <v>126</v>
       </c>
       <c r="D117" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E117" s="1">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F117" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -6980,45 +7021,45 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1070730686187744</v>
+        <v>0.1091561168432236</v>
       </c>
       <c r="C118" s="1">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D118" s="1">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="E118" s="1">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F118" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H118" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1017194166779518</v>
+        <v>0.1039582118391991</v>
       </c>
       <c r="C119" s="1">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D119" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E119" s="1">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -7027,7 +7068,7 @@
         <v>0</v>
       </c>
       <c r="H119" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -7035,16 +7076,16 @@
         <v>125</v>
       </c>
       <c r="B120" s="2">
-        <v>0.09993486106395721</v>
+        <v>0.09876029938459396</v>
       </c>
       <c r="C120" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -7061,7 +7102,7 @@
         <v>126</v>
       </c>
       <c r="B121" s="2">
-        <v>0.09993486106395721</v>
+        <v>0.09702765941619873</v>
       </c>
       <c r="C121" s="1">
         <v>112</v>
@@ -7087,7 +7128,7 @@
         <v>127</v>
       </c>
       <c r="B122" s="2">
-        <v>0.09993486106395721</v>
+        <v>0.09702765941619873</v>
       </c>
       <c r="C122" s="1">
         <v>112</v>
@@ -7113,16 +7154,16 @@
         <v>128</v>
       </c>
       <c r="B123" s="2">
-        <v>0.09815031290054321</v>
+        <v>0.09702765941619873</v>
       </c>
       <c r="C123" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -7139,7 +7180,7 @@
         <v>129</v>
       </c>
       <c r="B124" s="2">
-        <v>0.09815031290054321</v>
+        <v>0.09529502689838409</v>
       </c>
       <c r="C124" s="1">
         <v>110</v>
@@ -7162,19 +7203,19 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>11</v>
+        <v>130</v>
       </c>
       <c r="B125" s="2">
-        <v>0.09636576473712921</v>
+        <v>0.09529502689838409</v>
       </c>
       <c r="C125" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D125" s="1">
-        <v>716</v>
+        <v>0</v>
       </c>
       <c r="E125" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -7183,24 +7224,24 @@
         <v>0</v>
       </c>
       <c r="H125" s="1">
-        <v>716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
-        <v>130</v>
+        <v>12</v>
       </c>
       <c r="B126" s="2">
-        <v>0.08744300901889801</v>
+        <v>0.09356238692998886</v>
       </c>
       <c r="C126" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D126" s="1">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="E126" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -7209,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="H126" s="1">
-        <v>0</v>
+        <v>716</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -7217,7 +7258,7 @@
         <v>131</v>
       </c>
       <c r="B127" s="2">
-        <v>0.08744300901889801</v>
+        <v>0.08489920198917389</v>
       </c>
       <c r="C127" s="1">
         <v>98</v>
@@ -7243,16 +7284,16 @@
         <v>132</v>
       </c>
       <c r="B128" s="2">
-        <v>0.08208934962749481</v>
+        <v>0.08489920198917389</v>
       </c>
       <c r="C128" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -7269,7 +7310,7 @@
         <v>133</v>
       </c>
       <c r="B129" s="2">
-        <v>0.08208934962749481</v>
+        <v>0.07970129698514938</v>
       </c>
       <c r="C129" s="1">
         <v>92</v>
@@ -7295,16 +7336,16 @@
         <v>134</v>
       </c>
       <c r="B130" s="2">
-        <v>0.07673569768667221</v>
+        <v>0.07970129698514938</v>
       </c>
       <c r="C130" s="1">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -7321,16 +7362,16 @@
         <v>135</v>
       </c>
       <c r="B131" s="2">
-        <v>0.07495114952325821</v>
+        <v>0.07450338453054428</v>
       </c>
       <c r="C131" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -7347,7 +7388,7 @@
         <v>136</v>
       </c>
       <c r="B132" s="2">
-        <v>0.07495114952325821</v>
+        <v>0.07277074456214905</v>
       </c>
       <c r="C132" s="1">
         <v>84</v>
@@ -7373,7 +7414,7 @@
         <v>137</v>
       </c>
       <c r="B133" s="2">
-        <v>0.07495114952325821</v>
+        <v>0.07277074456214905</v>
       </c>
       <c r="C133" s="1">
         <v>84</v>
@@ -7396,25 +7437,25 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="1" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07495114952325821</v>
+        <v>0.07277074456214905</v>
       </c>
       <c r="C134" s="1">
         <v>84</v>
       </c>
       <c r="D134" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E134" s="1">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F134" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G134" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H134" s="1">
         <v>0</v>
@@ -7422,25 +7463,25 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07316659390926361</v>
+        <v>0.07277074456214905</v>
       </c>
       <c r="C135" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D135" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E135" s="1">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F135" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G135" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H135" s="1">
         <v>0</v>
@@ -7451,16 +7492,16 @@
         <v>139</v>
       </c>
       <c r="B136" s="2">
-        <v>0.06959749758243561</v>
+        <v>0.07103811204433441</v>
       </c>
       <c r="C136" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -7474,19 +7515,19 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="B137" s="2">
-        <v>0.06781294196844101</v>
+        <v>0.06757283210754395</v>
       </c>
       <c r="C137" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D137" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -7495,24 +7536,24 @@
         <v>0</v>
       </c>
       <c r="H137" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="B138" s="2">
-        <v>0.05889018625020981</v>
+        <v>0.06584019958972931</v>
       </c>
       <c r="C138" s="1">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D138" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E138" s="1">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -7521,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="H138" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -7529,16 +7570,16 @@
         <v>141</v>
       </c>
       <c r="B139" s="2">
-        <v>0.05353653430938721</v>
+        <v>0.05717701464891434</v>
       </c>
       <c r="C139" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D139" s="1">
         <v>0</v>
       </c>
       <c r="E139" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
@@ -7555,7 +7596,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="2">
-        <v>0.05353653430938721</v>
+        <v>0.05197910591959953</v>
       </c>
       <c r="C140" s="1">
         <v>60</v>
@@ -7581,16 +7622,16 @@
         <v>143</v>
       </c>
       <c r="B141" s="2">
-        <v>0.05175198242068291</v>
+        <v>0.05197910591959953</v>
       </c>
       <c r="C141" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
       </c>
       <c r="E141" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -7607,16 +7648,16 @@
         <v>144</v>
       </c>
       <c r="B142" s="2">
-        <v>0.04818288236856461</v>
+        <v>0.05197910591959953</v>
       </c>
       <c r="C142" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -7630,25 +7671,25 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="B143" s="2">
-        <v>0.04818288236856461</v>
+        <v>0.0502464659512043</v>
       </c>
       <c r="C143" s="1">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D143" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="F143" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G143" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
@@ -7656,19 +7697,19 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B144" s="2">
-        <v>0.04639833047986031</v>
+        <v>0.04678119346499443</v>
       </c>
       <c r="C144" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D144" s="1">
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7682,25 +7723,25 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
-        <v>146</v>
+        <v>45</v>
       </c>
       <c r="B145" s="2">
-        <v>0.04639833047986031</v>
+        <v>0.04678119346499443</v>
       </c>
       <c r="C145" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D145" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E145" s="1">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="F145" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G145" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
@@ -7711,16 +7752,16 @@
         <v>147</v>
       </c>
       <c r="B146" s="2">
-        <v>0.04282922670245171</v>
+        <v>0.0450485572218895</v>
       </c>
       <c r="C146" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -7737,7 +7778,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04282922670245171</v>
+        <v>0.04158328473567963</v>
       </c>
       <c r="C147" s="1">
         <v>48</v>
@@ -7763,7 +7804,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04282922670245171</v>
+        <v>0.04158328473567963</v>
       </c>
       <c r="C148" s="1">
         <v>48</v>
@@ -7789,16 +7830,16 @@
         <v>150</v>
       </c>
       <c r="B149" s="2">
-        <v>0.03926012665033341</v>
+        <v>0.04158328473567963</v>
       </c>
       <c r="C149" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D149" s="1">
         <v>0</v>
       </c>
       <c r="E149" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F149" s="1">
         <v>0</v>
@@ -7815,7 +7856,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="2">
-        <v>0.03926012665033341</v>
+        <v>0.03811800852417946</v>
       </c>
       <c r="C150" s="1">
         <v>44</v>
@@ -7841,7 +7882,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="2">
-        <v>0.03926012665033341</v>
+        <v>0.03811800852417946</v>
       </c>
       <c r="C151" s="1">
         <v>44</v>
@@ -7864,25 +7905,25 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="B152" s="2">
-        <v>0.03926012665033341</v>
+        <v>0.03811800852417946</v>
       </c>
       <c r="C152" s="1">
         <v>44</v>
       </c>
       <c r="D152" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E152" s="1">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F152" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G152" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
@@ -7890,25 +7931,25 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1" t="s">
-        <v>153</v>
+        <v>48</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03926012665033341</v>
+        <v>0.03811800852417946</v>
       </c>
       <c r="C153" s="1">
         <v>44</v>
       </c>
       <c r="D153" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E153" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F153" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G153" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H153" s="1">
         <v>0</v>
@@ -7919,7 +7960,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03926012665033341</v>
+        <v>0.03811800852417946</v>
       </c>
       <c r="C154" s="1">
         <v>44</v>
@@ -7945,16 +7986,16 @@
         <v>155</v>
       </c>
       <c r="B155" s="2">
-        <v>0.03569102287292481</v>
+        <v>0.03811800852417946</v>
       </c>
       <c r="C155" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
       </c>
       <c r="E155" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F155" s="1">
         <v>0</v>
@@ -7971,16 +8012,16 @@
         <v>156</v>
       </c>
       <c r="B156" s="2">
-        <v>0.03390647098422051</v>
+        <v>0.03465273603796959</v>
       </c>
       <c r="C156" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D156" s="1">
         <v>0</v>
       </c>
       <c r="E156" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -7997,16 +8038,16 @@
         <v>157</v>
       </c>
       <c r="B157" s="2">
-        <v>0.03212191909551621</v>
+        <v>0.03292009979486466</v>
       </c>
       <c r="C157" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
       </c>
       <c r="E157" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -8023,7 +8064,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="2">
-        <v>0.03212191909551621</v>
+        <v>0.03118746355175972</v>
       </c>
       <c r="C158" s="1">
         <v>36</v>
@@ -8049,7 +8090,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="2">
-        <v>0.03212191909551621</v>
+        <v>0.03118746355175972</v>
       </c>
       <c r="C159" s="1">
         <v>36</v>
@@ -8075,7 +8116,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="2">
-        <v>0.03212191909551621</v>
+        <v>0.03118746355175972</v>
       </c>
       <c r="C160" s="1">
         <v>36</v>
@@ -8101,16 +8142,16 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.0285528190433979</v>
+        <v>0.03118746355175972</v>
       </c>
       <c r="C161" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D161" s="1">
         <v>0</v>
       </c>
       <c r="E161" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F161" s="1">
         <v>0</v>
@@ -8127,7 +8168,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.0285528190433979</v>
+        <v>0.0277221892029047</v>
       </c>
       <c r="C162" s="1">
         <v>32</v>
@@ -8153,7 +8194,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.0285528190433979</v>
+        <v>0.0277221892029047</v>
       </c>
       <c r="C163" s="1">
         <v>32</v>
@@ -8179,7 +8220,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.0285528190433979</v>
+        <v>0.0277221892029047</v>
       </c>
       <c r="C164" s="1">
         <v>32</v>
@@ -8205,16 +8246,16 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.0267682671546936</v>
+        <v>0.0277221892029047</v>
       </c>
       <c r="C165" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
       </c>
       <c r="E165" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F165" s="1">
         <v>0</v>
@@ -8231,7 +8272,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.0267682671546936</v>
+        <v>0.02598955295979977</v>
       </c>
       <c r="C166" s="1">
         <v>30</v>
@@ -8257,16 +8298,16 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.02319916523993015</v>
+        <v>0.02598955295979977</v>
       </c>
       <c r="C167" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
       </c>
       <c r="E167" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F167" s="1">
         <v>0</v>
@@ -8283,16 +8324,16 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.02141461335122585</v>
+        <v>0.02252427861094475</v>
       </c>
       <c r="C168" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D168" s="1">
         <v>0</v>
       </c>
       <c r="E168" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F168" s="1">
         <v>0</v>
@@ -8306,25 +8347,25 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="1" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.01427640952169895</v>
+        <v>0.02079164236783981</v>
       </c>
       <c r="C169" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D169" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E169" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F169" s="1">
         <v>0</v>
       </c>
       <c r="G169" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
@@ -8332,25 +8373,25 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="1" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="B170" s="2">
-        <v>0.007138204760849476</v>
+        <v>0.01386109460145235</v>
       </c>
       <c r="C170" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D170" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E170" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F170" s="1">
         <v>0</v>
       </c>
       <c r="G170" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H170" s="1">
         <v>0</v>
@@ -8361,7 +8402,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="2">
-        <v>0.007138204760849476</v>
+        <v>0.006930547300726175</v>
       </c>
       <c r="C171" s="1">
         <v>8</v>
@@ -8384,25 +8425,25 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1" t="s">
-        <v>45</v>
+        <v>171</v>
       </c>
       <c r="B172" s="2">
-        <v>0.003569102380424738</v>
+        <v>0.006930547300726175</v>
       </c>
       <c r="C172" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D172" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E172" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1">
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
@@ -8410,25 +8451,25 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1" t="s">
-        <v>171</v>
+        <v>46</v>
       </c>
       <c r="B173" s="2">
-        <v>0.003569102380424738</v>
+        <v>0.003465273650363088</v>
       </c>
       <c r="C173" s="1">
         <v>4</v>
       </c>
       <c r="D173" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E173" s="1">
+        <v>0</v>
+      </c>
+      <c r="F173" s="1">
+        <v>0</v>
+      </c>
+      <c r="G173" s="1">
         <v>4</v>
-      </c>
-      <c r="F173" s="1">
-        <v>0</v>
-      </c>
-      <c r="G173" s="1">
-        <v>0</v>
       </c>
       <c r="H173" s="1">
         <v>0</v>
@@ -8439,7 +8480,7 @@
         <v>172</v>
       </c>
       <c r="B174" s="2">
-        <v>0.003569102380424738</v>
+        <v>0.003465273650363088</v>
       </c>
       <c r="C174" s="1">
         <v>4</v>
@@ -8461,34 +8502,60 @@
       </c>
     </row>
     <row r="175" spans="1:8">
-      <c r="A175" t="s">
-        <v>174</v>
-      </c>
-      <c r="B175">
+      <c r="A175" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B175" s="2">
+        <v>0.003465273650363088</v>
+      </c>
+      <c r="C175" s="1">
+        <v>4</v>
+      </c>
+      <c r="D175" s="1">
+        <v>0</v>
+      </c>
+      <c r="E175" s="1">
+        <v>4</v>
+      </c>
+      <c r="F175" s="1">
+        <v>0</v>
+      </c>
+      <c r="G175" s="1">
+        <v>0</v>
+      </c>
+      <c r="H175" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" t="s">
+        <v>175</v>
+      </c>
+      <c r="B176">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C175">
+      <c r="C176">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D175">
+      <c r="D176">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E175">
+      <c r="E176">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F175">
+      <c r="F176">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G175">
+      <c r="G176">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H175">
+      <c r="H176">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -215,10 +215,10 @@
     <t>arm_common_tables.o</t>
   </si>
   <si>
+    <t>jm_proto_can.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_rcc.o</t>
-  </si>
-  <si>
-    <t>jm_proto_can.o</t>
   </si>
   <si>
     <t>motion_param.o</t>
@@ -831,163 +831,163 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="174"/>
                 <c:pt idx="0">
-                  <c:v>32.43435668945313</c:v>
+                  <c:v>35.27819061279297</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.4384651184082</c:v>
+                  <c:v>9.111813545227051</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.092782020568848</c:v>
+                  <c:v>8.802355766296387</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.092782020568848</c:v>
+                  <c:v>8.802355766296387</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.41311502456665</c:v>
+                  <c:v>8.063095092773438</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.133325576782227</c:v>
+                  <c:v>4.495734214782715</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.038487911224365</c:v>
+                  <c:v>4.392581462860107</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.319305419921875</c:v>
+                  <c:v>3.61034107208252</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.256080389022827</c:v>
+                  <c:v>3.541572570800781</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.037026166915894</c:v>
+                  <c:v>2.21563196182251</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.023195505142212</c:v>
+                  <c:v>2.200588941574097</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.414656281471252</c:v>
+                  <c:v>1.538692951202393</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.7745046019554138</c:v>
+                  <c:v>0.8424128890037537</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.7033765912055969</c:v>
+                  <c:v>0.7650484442710877</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.6717641949653626</c:v>
+                  <c:v>0.7306642532348633</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.5927330851554871</c:v>
+                  <c:v>0.64470374584198</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.5295082330703735</c:v>
+                  <c:v>0.5759353637695313</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.4504771530628204</c:v>
+                  <c:v>0.489974856376648</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.4425740540027618</c:v>
+                  <c:v>0.4813787937164307</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.4030584990978241</c:v>
+                  <c:v>0.4383985698223114</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.3951554000377655</c:v>
+                  <c:v>0.4298025071620941</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2608025670051575</c:v>
+                  <c:v>0.283669650554657</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2528994381427765</c:v>
+                  <c:v>0.2750736176967621</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.1975777000188828</c:v>
+                  <c:v>0.2149012535810471</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1659652590751648</c:v>
+                  <c:v>0.1805170476436615</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1501590460538864</c:v>
+                  <c:v>0.1633249521255493</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1422559469938278</c:v>
+                  <c:v>0.1547289043664932</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1422559469938278</c:v>
+                  <c:v>0.1547289043664932</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1422559469938278</c:v>
+                  <c:v>0.1547289043664932</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.134352833032608</c:v>
+                  <c:v>0.1461328566074371</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1264497190713882</c:v>
+                  <c:v>0.137536808848381</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.08693418651819229</c:v>
+                  <c:v>0.0945565477013588</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.0790310800075531</c:v>
+                  <c:v>0.0859604999423027</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.07112797349691391</c:v>
+                  <c:v>0.07736445218324661</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.06322485953569412</c:v>
+                  <c:v>0.06876840442419052</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.04544287174940109</c:v>
+                  <c:v>0.04942728951573372</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03951554000377655</c:v>
+                  <c:v>0.04298024997115135</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.03951554000377655</c:v>
+                  <c:v>0.04298024997115135</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.02370932325720787</c:v>
+                  <c:v>0.02578815072774887</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.02370932325720787</c:v>
+                  <c:v>0.02578815072774887</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.02370932325720787</c:v>
+                  <c:v>0.02578815072774887</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.02370932325720787</c:v>
+                  <c:v>0.02578815072774887</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01580621488392353</c:v>
+                  <c:v>0.01719210110604763</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01580621488392353</c:v>
+                  <c:v>0.01719210110604763</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01580621488392353</c:v>
+                  <c:v>0.01719210110604763</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.007903107441961765</c:v>
+                  <c:v>0.008596050553023815</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.007903107441961765</c:v>
+                  <c:v>0.008596050553023815</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.007903107441961765</c:v>
+                  <c:v>0.008596050553023815</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.007903107441961765</c:v>
+                  <c:v>0.008596050553023815</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.007903107441961765</c:v>
+                  <c:v>0.008596050553023815</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.007903107441961765</c:v>
+                  <c:v>0.008596050553023815</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.007903107441961765</c:v>
+                  <c:v>0.008596050553023815</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.005927330814301968</c:v>
+                  <c:v>0.006447037681937218</c:v>
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>0</c:v>
@@ -1112,10 +1112,10 @@
                   <c:v>arm_common_tables.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>jm_proto_can.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>jm_proto_can.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>motion_param.o</c:v>
@@ -1130,10 +1130,10 @@
                   <c:v>dev_power_monitor.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
+                  <c:v>motor_observer.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>motor_pid_profile.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>motor_observer.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>stm32g4xx_hal_spi.o</c:v>
@@ -1154,13 +1154,13 @@
                   <c:v>calib_config_runtime.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>jm_host_commun.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>drv_can.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>jm_host_commun.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>calib_level3_encoder.o</c:v>
@@ -1592,523 +1592,523 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="174"/>
                 <c:pt idx="0">
-                  <c:v>4.109814643859863</c:v>
+                  <c:v>4.102989673614502</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.865512847900391</c:v>
+                  <c:v>3.921365022659302</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.681853294372559</c:v>
+                  <c:v>3.675739288330078</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.375176429748535</c:v>
+                  <c:v>3.229461193084717</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.188051700592041</c:v>
+                  <c:v>3.18275785446167</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.870979309082031</c:v>
+                  <c:v>2.866211652755737</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.763555765151978</c:v>
+                  <c:v>2.758966684341431</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.489799022674561</c:v>
+                  <c:v>2.48566460609436</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.46900749206543</c:v>
+                  <c:v>2.46490740776062</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.079164266586304</c:v>
+                  <c:v>2.075711488723755</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.056639909744263</c:v>
+                  <c:v>2.053224802017212</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.037580966949463</c:v>
+                  <c:v>2.034197330474854</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.034115552902222</c:v>
+                  <c:v>2.03073787689209</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.03065037727356</c:v>
+                  <c:v>2.027278423309326</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.921494245529175</c:v>
+                  <c:v>1.918303489685059</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.853921413421631</c:v>
+                  <c:v>1.850842833518982</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.777685403823853</c:v>
+                  <c:v>1.774733424186707</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.646004915237427</c:v>
+                  <c:v>1.681326389312744</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.646004915237427</c:v>
+                  <c:v>1.643271684646606</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.564571022987366</c:v>
+                  <c:v>1.561972975730896</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.406901121139526</c:v>
+                  <c:v>1.40456485748291</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.39303994178772</c:v>
+                  <c:v>1.390726804733276</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.389574766159058</c:v>
+                  <c:v>1.387267231941223</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.245765924453735</c:v>
+                  <c:v>1.364780306816101</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.242300629615784</c:v>
+                  <c:v>1.243697166442871</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.207647800445557</c:v>
+                  <c:v>1.205642461776733</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.141807675361633</c:v>
+                  <c:v>1.139911651611328</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.081165313720703</c:v>
+                  <c:v>1.079370021820068</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.056908488273621</c:v>
+                  <c:v>1.055153369903565</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.039582133293152</c:v>
+                  <c:v>1.037855744361877</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.0361168384552</c:v>
+                  <c:v>1.034396290779114</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.013592481613159</c:v>
+                  <c:v>1.027477264404297</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.9962661862373352</c:v>
+                  <c:v>1.011909365653992</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9477523565292358</c:v>
+                  <c:v>0.9946117997169495</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9373565316200256</c:v>
+                  <c:v>0.9357999563217163</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8905753493309021</c:v>
+                  <c:v>0.8890964388847351</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8758479356765747</c:v>
+                  <c:v>0.8743935227394104</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8628531098365784</c:v>
+                  <c:v>0.8614203333854675</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.8403288722038269</c:v>
+                  <c:v>0.8389334082603455</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.8316656947135925</c:v>
+                  <c:v>0.8302846550941467</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.8282003998756409</c:v>
+                  <c:v>0.8268251419067383</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7415685653686523</c:v>
+                  <c:v>0.7403371334075928</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7363706231117249</c:v>
+                  <c:v>0.7351478338241577</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7207769155502319</c:v>
+                  <c:v>0.7195799946784973</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.7103810906410217</c:v>
+                  <c:v>0.709201455116272</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.6913220882415772</c:v>
+                  <c:v>0.6901741027832031</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6791936159133911</c:v>
+                  <c:v>0.6780657768249512</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6549367308616638</c:v>
+                  <c:v>0.6538491249084473</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6237492561340332</c:v>
+                  <c:v>0.6227134466171265</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.6237492561340332</c:v>
+                  <c:v>0.6227134466171265</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.5925617814064026</c:v>
+                  <c:v>0.5915778279304504</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5579090714454651</c:v>
+                  <c:v>0.5569826364517212</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5371174216270447</c:v>
+                  <c:v>0.5362254977226257</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5353847742080689</c:v>
+                  <c:v>0.5344957113265991</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5059299468994141</c:v>
+                  <c:v>0.5050898194313049</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.4955341219902039</c:v>
+                  <c:v>0.4947112500667572</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.4816730320453644</c:v>
+                  <c:v>0.4808731973171234</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4747424721717835</c:v>
+                  <c:v>0.4739541411399841</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4504855573177338</c:v>
+                  <c:v>0.4497375190258026</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4435550272464752</c:v>
+                  <c:v>0.4428184628486633</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.440089762210846</c:v>
+                  <c:v>0.4393589496612549</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4366244673728943</c:v>
+                  <c:v>0.4358994364738464</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4348918497562408</c:v>
+                  <c:v>0.4341696798801422</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4348918497562408</c:v>
+                  <c:v>0.4341696798801422</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.4314265549182892</c:v>
+                  <c:v>0.4307101666927338</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.4123675525188446</c:v>
+                  <c:v>0.4116827845573425</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.4054370224475861</c:v>
+                  <c:v>0.4047637581825256</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3950411975383759</c:v>
+                  <c:v>0.3943851888179779</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3941748738288879</c:v>
+                  <c:v>0.393520325422287</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3863780200481415</c:v>
+                  <c:v>0.3857364058494568</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3690516352653503</c:v>
+                  <c:v>0.3684388101100922</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3690516352653503</c:v>
+                  <c:v>0.3684388101100922</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3551905453205109</c:v>
+                  <c:v>0.354600727558136</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.353457897901535</c:v>
+                  <c:v>0.3528709709644318</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3465273678302765</c:v>
+                  <c:v>0.3459519445896149</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3465273678302765</c:v>
+                  <c:v>0.3459519445896149</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.3222704529762268</c:v>
+                  <c:v>0.321735292673111</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.3170725405216217</c:v>
+                  <c:v>0.3165460228919983</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.2980135381221771</c:v>
+                  <c:v>0.2975186705589294</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.2971472144126892</c:v>
+                  <c:v>0.2966537773609161</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.2910829782485962</c:v>
+                  <c:v>0.2905996143817902</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.2893503606319428</c:v>
+                  <c:v>0.2888698577880859</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.2876177132129669</c:v>
+                  <c:v>0.2871401011943817</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.280687153339386</c:v>
+                  <c:v>0.2802210748195648</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2668260633945465</c:v>
+                  <c:v>0.2663829922676086</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.252964973449707</c:v>
+                  <c:v>0.2525449097156525</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2356386035680771</c:v>
+                  <c:v>0.2352473139762878</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2356386035680771</c:v>
+                  <c:v>0.2352473139762878</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2183122336864471</c:v>
+                  <c:v>0.2179497182369232</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.213114321231842</c:v>
+                  <c:v>0.2127604335546494</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2096490561962128</c:v>
+                  <c:v>0.2093009203672409</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.202718511223793</c:v>
+                  <c:v>0.2023818790912628</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2009858638048172</c:v>
+                  <c:v>0.2006521224975586</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.1975205987691879</c:v>
+                  <c:v>0.197192594408989</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1975205987691879</c:v>
+                  <c:v>0.197192594408989</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1923226863145828</c:v>
+                  <c:v>0.1920033246278763</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1905900537967682</c:v>
+                  <c:v>0.1902735680341721</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1905900537967682</c:v>
+                  <c:v>0.1902735680341721</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1767289489507675</c:v>
+                  <c:v>0.1764354854822159</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1663331389427185</c:v>
+                  <c:v>0.1660569310188294</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.162867859005928</c:v>
+                  <c:v>0.1625974029302597</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1611352264881134</c:v>
+                  <c:v>0.1608676463365555</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1524720340967178</c:v>
+                  <c:v>0.1522188484668732</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1524720340967178</c:v>
+                  <c:v>0.1522188484668732</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1490067690610886</c:v>
+                  <c:v>0.1487593352794647</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1368783116340637</c:v>
+                  <c:v>0.1366510093212128</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1334130316972733</c:v>
+                  <c:v>0.1331914961338043</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1316803991794586</c:v>
+                  <c:v>0.1314617395401001</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1247498542070389</c:v>
+                  <c:v>0.124542698264122</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1230172142386437</c:v>
+                  <c:v>0.1228129342198372</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1195519417524338</c:v>
+                  <c:v>0.1193534135818481</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1178193017840385</c:v>
+                  <c:v>0.1176236569881439</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1108887568116188</c:v>
+                  <c:v>0.1107046157121658</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1108887568116188</c:v>
+                  <c:v>0.1107046157121658</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1091561168432236</c:v>
+                  <c:v>0.1089748591184616</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1091561168432236</c:v>
+                  <c:v>0.1089748591184616</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1039582118391991</c:v>
+                  <c:v>0.1037855818867683</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.09876029938459396</c:v>
+                  <c:v>0.09859629720449448</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.09702765941619873</c:v>
+                  <c:v>0.09686654061079025</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.09702765941619873</c:v>
+                  <c:v>0.09686654061079025</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.09702765941619873</c:v>
+                  <c:v>0.09686654061079025</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.09529502689838409</c:v>
+                  <c:v>0.09513678401708603</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.09529502689838409</c:v>
+                  <c:v>0.09513678401708603</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.09356238692998886</c:v>
+                  <c:v>0.09340701997280121</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.08489920198917389</c:v>
+                  <c:v>0.0847582221031189</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.08489920198917389</c:v>
+                  <c:v>0.0847582221031189</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.07970129698514938</c:v>
+                  <c:v>0.07956894487142563</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.07970129698514938</c:v>
+                  <c:v>0.07956894487142563</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.07450338453054428</c:v>
+                  <c:v>0.07437966763973236</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.07277074456214905</c:v>
+                  <c:v>0.07264990359544754</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.07277074456214905</c:v>
+                  <c:v>0.07264990359544754</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07277074456214905</c:v>
+                  <c:v>0.07264990359544754</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07277074456214905</c:v>
+                  <c:v>0.07264990359544754</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.07103811204433441</c:v>
+                  <c:v>0.07092014700174332</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06757283210754395</c:v>
+                  <c:v>0.06746062636375427</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06584019958972931</c:v>
+                  <c:v>0.06573086977005005</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.05717701464891434</c:v>
+                  <c:v>0.05708206817507744</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.05197910591959953</c:v>
+                  <c:v>0.05189279094338417</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.05197910591959953</c:v>
+                  <c:v>0.05189279094338417</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.05197910591959953</c:v>
+                  <c:v>0.05189279094338417</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.0502464659512043</c:v>
+                  <c:v>0.05016303062438965</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.04678119346499443</c:v>
+                  <c:v>0.0467035099864006</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.04678119346499443</c:v>
+                  <c:v>0.0467035099864006</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.0450485572218895</c:v>
+                  <c:v>0.04497374966740608</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04158328473567963</c:v>
+                  <c:v>0.04151423275470734</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04158328473567963</c:v>
+                  <c:v>0.04151423275470734</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04158328473567963</c:v>
+                  <c:v>0.04151423275470734</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.03811800852417946</c:v>
+                  <c:v>0.03805471211671829</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.03811800852417946</c:v>
+                  <c:v>0.03805471211671829</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.03811800852417946</c:v>
+                  <c:v>0.03805471211671829</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03811800852417946</c:v>
+                  <c:v>0.03805471211671829</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03811800852417946</c:v>
+                  <c:v>0.03805471211671829</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03811800852417946</c:v>
+                  <c:v>0.03805471211671829</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03465273603796959</c:v>
+                  <c:v>0.03459519147872925</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.03292009979486466</c:v>
+                  <c:v>0.03286543488502502</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.03118746355175972</c:v>
+                  <c:v>0.0311356745660305</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.03118746355175972</c:v>
+                  <c:v>0.0311356745660305</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.03118746355175972</c:v>
+                  <c:v>0.0311356745660305</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.03118746355175972</c:v>
+                  <c:v>0.0311356745660305</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.0277221892029047</c:v>
+                  <c:v>0.02767615392804146</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.0277221892029047</c:v>
+                  <c:v>0.02767615392804146</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.0277221892029047</c:v>
+                  <c:v>0.02767615392804146</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.0277221892029047</c:v>
+                  <c:v>0.02767615392804146</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.02598955295979977</c:v>
+                  <c:v>0.02594639547169209</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02598955295979977</c:v>
+                  <c:v>0.02594639547169209</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02252427861094475</c:v>
+                  <c:v>0.02248687483370304</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02079164236783981</c:v>
+                  <c:v>0.02075711637735367</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.01386109460145235</c:v>
+                  <c:v>0.01383807696402073</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.006930547300726175</c:v>
+                  <c:v>0.006919038482010365</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.006930547300726175</c:v>
+                  <c:v>0.006919038482010365</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.003465273650363088</c:v>
+                  <c:v>0.003459519241005182</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.003465273650363088</c:v>
+                  <c:v>0.003459519241005182</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.003465273650363088</c:v>
+                  <c:v>0.003459519241005182</c:v>
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>0</c:v>
@@ -2575,7 +2575,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>32.43435668945313</v>
+        <v>35.27819061279297</v>
       </c>
       <c r="C3" s="1">
         <v>16416</v>
@@ -2601,25 +2601,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>16.4384651184082</v>
+        <v>9.111813545227051</v>
       </c>
       <c r="C4" s="1">
-        <v>8320</v>
+        <v>4240</v>
       </c>
       <c r="D4" s="1">
-        <v>1434</v>
+        <v>1578</v>
       </c>
       <c r="E4" s="1">
-        <v>1402</v>
+        <v>1530</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H4" s="1">
-        <v>8288</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2627,7 +2627,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>8.092782020568848</v>
+        <v>8.802355766296387</v>
       </c>
       <c r="C5" s="1">
         <v>4096</v>
@@ -2653,7 +2653,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>8.092782020568848</v>
+        <v>8.802355766296387</v>
       </c>
       <c r="C6" s="1">
         <v>4096</v>
@@ -2679,7 +2679,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>7.41311502456665</v>
+        <v>8.063095092773438</v>
       </c>
       <c r="C7" s="1">
         <v>3752</v>
@@ -2705,7 +2705,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.133325576782227</v>
+        <v>4.495734214782715</v>
       </c>
       <c r="C8" s="1">
         <v>2092</v>
@@ -2731,7 +2731,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>4.038487911224365</v>
+        <v>4.392581462860107</v>
       </c>
       <c r="C9" s="1">
         <v>2044</v>
@@ -2757,7 +2757,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>3.319305419921875</v>
+        <v>3.61034107208252</v>
       </c>
       <c r="C10" s="1">
         <v>1680</v>
@@ -2783,7 +2783,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.256080389022827</v>
+        <v>3.541572570800781</v>
       </c>
       <c r="C11" s="1">
         <v>1648</v>
@@ -2809,7 +2809,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>2.037026166915894</v>
+        <v>2.21563196182251</v>
       </c>
       <c r="C12" s="1">
         <v>1031</v>
@@ -2835,7 +2835,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>2.023195505142212</v>
+        <v>2.200588941574097</v>
       </c>
       <c r="C13" s="1">
         <v>1024</v>
@@ -2861,7 +2861,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>1.414656281471252</v>
+        <v>1.538692951202393</v>
       </c>
       <c r="C14" s="1">
         <v>716</v>
@@ -2887,19 +2887,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.7745046019554138</v>
+        <v>0.8424128890037537</v>
       </c>
       <c r="C15" s="1">
         <v>392</v>
       </c>
       <c r="D15" s="1">
-        <v>4462</v>
+        <v>4534</v>
       </c>
       <c r="E15" s="1">
-        <v>3966</v>
+        <v>4042</v>
       </c>
       <c r="F15" s="1">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G15" s="1">
         <v>28</v>
@@ -2913,7 +2913,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.7033765912055969</v>
+        <v>0.7650484442710877</v>
       </c>
       <c r="C16" s="1">
         <v>356</v>
@@ -2939,7 +2939,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.6717641949653626</v>
+        <v>0.7306642532348633</v>
       </c>
       <c r="C17" s="1">
         <v>340</v>
@@ -2965,7 +2965,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.5927330851554871</v>
+        <v>0.64470374584198</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -2991,7 +2991,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.5295082330703735</v>
+        <v>0.5759353637695313</v>
       </c>
       <c r="C19" s="1">
         <v>268</v>
@@ -3017,7 +3017,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.4504771530628204</v>
+        <v>0.489974856376648</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -3043,7 +3043,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.4425740540027618</v>
+        <v>0.4813787937164307</v>
       </c>
       <c r="C21" s="1">
         <v>224</v>
@@ -3069,7 +3069,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.4030584990978241</v>
+        <v>0.4383985698223114</v>
       </c>
       <c r="C22" s="1">
         <v>204</v>
@@ -3095,7 +3095,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.3951554000377655</v>
+        <v>0.4298025071620941</v>
       </c>
       <c r="C23" s="1">
         <v>200</v>
@@ -3121,7 +3121,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2608025670051575</v>
+        <v>0.283669650554657</v>
       </c>
       <c r="C24" s="1">
         <v>132</v>
@@ -3147,7 +3147,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2528994381427765</v>
+        <v>0.2750736176967621</v>
       </c>
       <c r="C25" s="1">
         <v>128</v>
@@ -3173,7 +3173,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.1975777000188828</v>
+        <v>0.2149012535810471</v>
       </c>
       <c r="C26" s="1">
         <v>100</v>
@@ -3199,7 +3199,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1659652590751648</v>
+        <v>0.1805170476436615</v>
       </c>
       <c r="C27" s="1">
         <v>84</v>
@@ -3225,7 +3225,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1501590460538864</v>
+        <v>0.1633249521255493</v>
       </c>
       <c r="C28" s="1">
         <v>76</v>
@@ -3251,7 +3251,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1422559469938278</v>
+        <v>0.1547289043664932</v>
       </c>
       <c r="C29" s="1">
         <v>72</v>
@@ -3277,7 +3277,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1422559469938278</v>
+        <v>0.1547289043664932</v>
       </c>
       <c r="C30" s="1">
         <v>72</v>
@@ -3303,7 +3303,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1422559469938278</v>
+        <v>0.1547289043664932</v>
       </c>
       <c r="C31" s="1">
         <v>72</v>
@@ -3329,7 +3329,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.134352833032608</v>
+        <v>0.1461328566074371</v>
       </c>
       <c r="C32" s="1">
         <v>68</v>
@@ -3355,7 +3355,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1264497190713882</v>
+        <v>0.137536808848381</v>
       </c>
       <c r="C33" s="1">
         <v>64</v>
@@ -3381,7 +3381,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.08693418651819229</v>
+        <v>0.0945565477013588</v>
       </c>
       <c r="C34" s="1">
         <v>44</v>
@@ -3407,7 +3407,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.0790310800075531</v>
+        <v>0.0859604999423027</v>
       </c>
       <c r="C35" s="1">
         <v>40</v>
@@ -3433,7 +3433,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.07112797349691391</v>
+        <v>0.07736445218324661</v>
       </c>
       <c r="C36" s="1">
         <v>36</v>
@@ -3459,7 +3459,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.06322485953569412</v>
+        <v>0.06876840442419052</v>
       </c>
       <c r="C37" s="1">
         <v>32</v>
@@ -3485,7 +3485,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.04544287174940109</v>
+        <v>0.04942728951573372</v>
       </c>
       <c r="C38" s="1">
         <v>23</v>
@@ -3511,7 +3511,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03951554000377655</v>
+        <v>0.04298024997115135</v>
       </c>
       <c r="C39" s="1">
         <v>20</v>
@@ -3537,16 +3537,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.03951554000377655</v>
+        <v>0.04298024997115135</v>
       </c>
       <c r="C40" s="1">
         <v>20</v>
       </c>
       <c r="D40" s="1">
-        <v>1094</v>
+        <v>1188</v>
       </c>
       <c r="E40" s="1">
-        <v>1074</v>
+        <v>1168</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3563,7 +3563,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.02370932325720787</v>
+        <v>0.02578815072774887</v>
       </c>
       <c r="C41" s="1">
         <v>12</v>
@@ -3589,7 +3589,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.02370932325720787</v>
+        <v>0.02578815072774887</v>
       </c>
       <c r="C42" s="1">
         <v>12</v>
@@ -3615,7 +3615,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.02370932325720787</v>
+        <v>0.02578815072774887</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
@@ -3641,7 +3641,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.02370932325720787</v>
+        <v>0.02578815072774887</v>
       </c>
       <c r="C44" s="1">
         <v>12</v>
@@ -3667,7 +3667,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01580621488392353</v>
+        <v>0.01719210110604763</v>
       </c>
       <c r="C45" s="1">
         <v>8</v>
@@ -3693,7 +3693,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01580621488392353</v>
+        <v>0.01719210110604763</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
@@ -3719,7 +3719,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01580621488392353</v>
+        <v>0.01719210110604763</v>
       </c>
       <c r="C47" s="1">
         <v>8</v>
@@ -3745,7 +3745,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.007903107441961765</v>
+        <v>0.008596050553023815</v>
       </c>
       <c r="C48" s="1">
         <v>4</v>
@@ -3771,7 +3771,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.007903107441961765</v>
+        <v>0.008596050553023815</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
@@ -3797,7 +3797,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.007903107441961765</v>
+        <v>0.008596050553023815</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
@@ -3823,7 +3823,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.007903107441961765</v>
+        <v>0.008596050553023815</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
@@ -3849,7 +3849,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.007903107441961765</v>
+        <v>0.008596050553023815</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
@@ -3875,7 +3875,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.007903107441961765</v>
+        <v>0.008596050553023815</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -3901,7 +3901,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.007903107441961765</v>
+        <v>0.008596050553023815</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
@@ -3927,7 +3927,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.005927330814301968</v>
+        <v>0.006447037681937218</v>
       </c>
       <c r="C55" s="1">
         <v>3</v>
@@ -4034,7 +4034,7 @@
         <v>54</v>
       </c>
       <c r="B3" s="2">
-        <v>4.109814643859863</v>
+        <v>4.102989673614502</v>
       </c>
       <c r="C3" s="1">
         <v>4744</v>
@@ -4060,19 +4060,19 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>3.865512847900391</v>
+        <v>3.921365022659302</v>
       </c>
       <c r="C4" s="1">
-        <v>4462</v>
+        <v>4534</v>
       </c>
       <c r="D4" s="1">
         <v>392</v>
       </c>
       <c r="E4" s="1">
-        <v>3966</v>
+        <v>4042</v>
       </c>
       <c r="F4" s="1">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G4" s="1">
         <v>28</v>
@@ -4086,7 +4086,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>3.681853294372559</v>
+        <v>3.675739288330078</v>
       </c>
       <c r="C5" s="1">
         <v>4250</v>
@@ -4112,16 +4112,16 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>3.375176429748535</v>
+        <v>3.229461193084717</v>
       </c>
       <c r="C6" s="1">
-        <v>3896</v>
+        <v>3734</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>3896</v>
+        <v>3734</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>3.188051700592041</v>
+        <v>3.18275785446167</v>
       </c>
       <c r="C7" s="1">
         <v>3680</v>
@@ -4164,7 +4164,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>2.870979309082031</v>
+        <v>2.866211652755737</v>
       </c>
       <c r="C8" s="1">
         <v>3314</v>
@@ -4190,7 +4190,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>2.763555765151978</v>
+        <v>2.758966684341431</v>
       </c>
       <c r="C9" s="1">
         <v>3190</v>
@@ -4216,7 +4216,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="2">
-        <v>2.489799022674561</v>
+        <v>2.48566460609436</v>
       </c>
       <c r="C10" s="1">
         <v>2874</v>
@@ -4242,7 +4242,7 @@
         <v>59</v>
       </c>
       <c r="B11" s="2">
-        <v>2.46900749206543</v>
+        <v>2.46490740776062</v>
       </c>
       <c r="C11" s="1">
         <v>2850</v>
@@ -4268,7 +4268,7 @@
         <v>60</v>
       </c>
       <c r="B12" s="2">
-        <v>2.079164266586304</v>
+        <v>2.075711488723755</v>
       </c>
       <c r="C12" s="1">
         <v>2400</v>
@@ -4294,7 +4294,7 @@
         <v>61</v>
       </c>
       <c r="B13" s="2">
-        <v>2.056639909744263</v>
+        <v>2.053224802017212</v>
       </c>
       <c r="C13" s="1">
         <v>2374</v>
@@ -4320,7 +4320,7 @@
         <v>62</v>
       </c>
       <c r="B14" s="2">
-        <v>2.037580966949463</v>
+        <v>2.034197330474854</v>
       </c>
       <c r="C14" s="1">
         <v>2352</v>
@@ -4346,7 +4346,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="2">
-        <v>2.034115552902222</v>
+        <v>2.03073787689209</v>
       </c>
       <c r="C15" s="1">
         <v>2348</v>
@@ -4372,7 +4372,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>2.03065037727356</v>
+        <v>2.027278423309326</v>
       </c>
       <c r="C16" s="1">
         <v>2344</v>
@@ -4398,7 +4398,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="2">
-        <v>1.921494245529175</v>
+        <v>1.918303489685059</v>
       </c>
       <c r="C17" s="1">
         <v>2218</v>
@@ -4424,7 +4424,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="2">
-        <v>1.853921413421631</v>
+        <v>1.850842833518982</v>
       </c>
       <c r="C18" s="1">
         <v>2140</v>
@@ -4450,7 +4450,7 @@
         <v>65</v>
       </c>
       <c r="B19" s="2">
-        <v>1.777685403823853</v>
+        <v>1.774733424186707</v>
       </c>
       <c r="C19" s="1">
         <v>2052</v>
@@ -4476,19 +4476,19 @@
         <v>66</v>
       </c>
       <c r="B20" s="2">
-        <v>1.646004915237427</v>
+        <v>1.681326389312744</v>
       </c>
       <c r="C20" s="1">
-        <v>1900</v>
+        <v>1944</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>1900</v>
+        <v>1930</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -4502,7 +4502,7 @@
         <v>67</v>
       </c>
       <c r="B21" s="2">
-        <v>1.646004915237427</v>
+        <v>1.643271684646606</v>
       </c>
       <c r="C21" s="1">
         <v>1900</v>
@@ -4511,10 +4511,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>1886</v>
+        <v>1900</v>
       </c>
       <c r="F21" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -4528,7 +4528,7 @@
         <v>68</v>
       </c>
       <c r="B22" s="2">
-        <v>1.564571022987366</v>
+        <v>1.561972975730896</v>
       </c>
       <c r="C22" s="1">
         <v>1806</v>
@@ -4554,7 +4554,7 @@
         <v>49</v>
       </c>
       <c r="B23" s="2">
-        <v>1.406901121139526</v>
+        <v>1.40456485748291</v>
       </c>
       <c r="C23" s="1">
         <v>1624</v>
@@ -4580,7 +4580,7 @@
         <v>69</v>
       </c>
       <c r="B24" s="2">
-        <v>1.39303994178772</v>
+        <v>1.390726804733276</v>
       </c>
       <c r="C24" s="1">
         <v>1608</v>
@@ -4606,7 +4606,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="2">
-        <v>1.389574766159058</v>
+        <v>1.387267231941223</v>
       </c>
       <c r="C25" s="1">
         <v>1604</v>
@@ -4629,54 +4629,54 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B26" s="2">
-        <v>1.245765924453735</v>
+        <v>1.364780306816101</v>
       </c>
       <c r="C26" s="1">
-        <v>1438</v>
+        <v>1578</v>
       </c>
       <c r="D26" s="1">
-        <v>356</v>
+        <v>4240</v>
       </c>
       <c r="E26" s="1">
-        <v>1082</v>
+        <v>1530</v>
       </c>
       <c r="F26" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H26" s="1">
-        <v>352</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B27" s="2">
-        <v>1.242300629615784</v>
+        <v>1.243697166442871</v>
       </c>
       <c r="C27" s="1">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D27" s="1">
-        <v>8320</v>
+        <v>356</v>
       </c>
       <c r="E27" s="1">
-        <v>1402</v>
+        <v>1082</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G27" s="1">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H27" s="1">
-        <v>8288</v>
+        <v>352</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4684,7 +4684,7 @@
         <v>70</v>
       </c>
       <c r="B28" s="2">
-        <v>1.207647800445557</v>
+        <v>1.205642461776733</v>
       </c>
       <c r="C28" s="1">
         <v>1394</v>
@@ -4710,7 +4710,7 @@
         <v>71</v>
       </c>
       <c r="B29" s="2">
-        <v>1.141807675361633</v>
+        <v>1.139911651611328</v>
       </c>
       <c r="C29" s="1">
         <v>1318</v>
@@ -4736,7 +4736,7 @@
         <v>72</v>
       </c>
       <c r="B30" s="2">
-        <v>1.081165313720703</v>
+        <v>1.079370021820068</v>
       </c>
       <c r="C30" s="1">
         <v>1248</v>
@@ -4762,7 +4762,7 @@
         <v>73</v>
       </c>
       <c r="B31" s="2">
-        <v>1.056908488273621</v>
+        <v>1.055153369903565</v>
       </c>
       <c r="C31" s="1">
         <v>1220</v>
@@ -4788,7 +4788,7 @@
         <v>74</v>
       </c>
       <c r="B32" s="2">
-        <v>1.039582133293152</v>
+        <v>1.037855744361877</v>
       </c>
       <c r="C32" s="1">
         <v>1200</v>
@@ -4814,7 +4814,7 @@
         <v>75</v>
       </c>
       <c r="B33" s="2">
-        <v>1.0361168384552</v>
+        <v>1.034396290779114</v>
       </c>
       <c r="C33" s="1">
         <v>1196</v>
@@ -4837,25 +4837,25 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="B34" s="2">
-        <v>1.013592481613159</v>
+        <v>1.027477264404297</v>
       </c>
       <c r="C34" s="1">
-        <v>1170</v>
+        <v>1188</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E34" s="1">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -4863,54 +4863,54 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B35" s="2">
-        <v>0.9962661862373352</v>
+        <v>1.011909365653992</v>
       </c>
       <c r="C35" s="1">
-        <v>1150</v>
+        <v>1170</v>
       </c>
       <c r="D35" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>1126</v>
+        <v>1170</v>
       </c>
       <c r="F35" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9477523565292358</v>
+        <v>0.9946117997169495</v>
       </c>
       <c r="C36" s="1">
-        <v>1094</v>
+        <v>1150</v>
       </c>
       <c r="D36" s="1">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="E36" s="1">
-        <v>1074</v>
+        <v>1126</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G36" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -4918,7 +4918,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9373565316200256</v>
+        <v>0.9357999563217163</v>
       </c>
       <c r="C37" s="1">
         <v>1082</v>
@@ -4944,7 +4944,7 @@
         <v>28</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8905753493309021</v>
+        <v>0.8890964388847351</v>
       </c>
       <c r="C38" s="1">
         <v>1028</v>
@@ -4970,7 +4970,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8758479356765747</v>
+        <v>0.8743935227394104</v>
       </c>
       <c r="C39" s="1">
         <v>1011</v>
@@ -4996,7 +4996,7 @@
         <v>8</v>
       </c>
       <c r="B40" s="2">
-        <v>0.8628531098365784</v>
+        <v>0.8614203333854675</v>
       </c>
       <c r="C40" s="1">
         <v>996</v>
@@ -5022,7 +5022,7 @@
         <v>29</v>
       </c>
       <c r="B41" s="2">
-        <v>0.8403288722038269</v>
+        <v>0.8389334082603455</v>
       </c>
       <c r="C41" s="1">
         <v>970</v>
@@ -5048,7 +5048,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="2">
-        <v>0.8316656947135925</v>
+        <v>0.8302846550941467</v>
       </c>
       <c r="C42" s="1">
         <v>960</v>
@@ -5074,7 +5074,7 @@
         <v>77</v>
       </c>
       <c r="B43" s="2">
-        <v>0.8282003998756409</v>
+        <v>0.8268251419067383</v>
       </c>
       <c r="C43" s="1">
         <v>956</v>
@@ -5100,7 +5100,7 @@
         <v>78</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7415685653686523</v>
+        <v>0.7403371334075928</v>
       </c>
       <c r="C44" s="1">
         <v>856</v>
@@ -5126,7 +5126,7 @@
         <v>79</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7363706231117249</v>
+        <v>0.7351478338241577</v>
       </c>
       <c r="C45" s="1">
         <v>850</v>
@@ -5152,7 +5152,7 @@
         <v>80</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7207769155502319</v>
+        <v>0.7195799946784973</v>
       </c>
       <c r="C46" s="1">
         <v>832</v>
@@ -5178,7 +5178,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7103810906410217</v>
+        <v>0.709201455116272</v>
       </c>
       <c r="C47" s="1">
         <v>820</v>
@@ -5204,7 +5204,7 @@
         <v>40</v>
       </c>
       <c r="B48" s="2">
-        <v>0.6913220882415772</v>
+        <v>0.6901741027832031</v>
       </c>
       <c r="C48" s="1">
         <v>798</v>
@@ -5230,7 +5230,7 @@
         <v>81</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6791936159133911</v>
+        <v>0.6780657768249512</v>
       </c>
       <c r="C49" s="1">
         <v>784</v>
@@ -5256,7 +5256,7 @@
         <v>18</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6549367308616638</v>
+        <v>0.6538491249084473</v>
       </c>
       <c r="C50" s="1">
         <v>756</v>
@@ -5282,7 +5282,7 @@
         <v>82</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6237492561340332</v>
+        <v>0.6227134466171265</v>
       </c>
       <c r="C51" s="1">
         <v>720</v>
@@ -5308,7 +5308,7 @@
         <v>83</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6237492561340332</v>
+        <v>0.6227134466171265</v>
       </c>
       <c r="C52" s="1">
         <v>720</v>
@@ -5334,7 +5334,7 @@
         <v>84</v>
       </c>
       <c r="B53" s="2">
-        <v>0.5925617814064026</v>
+        <v>0.5915778279304504</v>
       </c>
       <c r="C53" s="1">
         <v>684</v>
@@ -5360,7 +5360,7 @@
         <v>85</v>
       </c>
       <c r="B54" s="2">
-        <v>0.5579090714454651</v>
+        <v>0.5569826364517212</v>
       </c>
       <c r="C54" s="1">
         <v>644</v>
@@ -5386,7 +5386,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5371174216270447</v>
+        <v>0.5362254977226257</v>
       </c>
       <c r="C55" s="1">
         <v>620</v>
@@ -5412,7 +5412,7 @@
         <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5353847742080689</v>
+        <v>0.5344957113265991</v>
       </c>
       <c r="C56" s="1">
         <v>618</v>
@@ -5438,7 +5438,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5059299468994141</v>
+        <v>0.5050898194313049</v>
       </c>
       <c r="C57" s="1">
         <v>584</v>
@@ -5464,7 +5464,7 @@
         <v>87</v>
       </c>
       <c r="B58" s="2">
-        <v>0.4955341219902039</v>
+        <v>0.4947112500667572</v>
       </c>
       <c r="C58" s="1">
         <v>572</v>
@@ -5490,7 +5490,7 @@
         <v>88</v>
       </c>
       <c r="B59" s="2">
-        <v>0.4816730320453644</v>
+        <v>0.4808731973171234</v>
       </c>
       <c r="C59" s="1">
         <v>556</v>
@@ -5516,7 +5516,7 @@
         <v>20</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4747424721717835</v>
+        <v>0.4739541411399841</v>
       </c>
       <c r="C60" s="1">
         <v>548</v>
@@ -5542,7 +5542,7 @@
         <v>89</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4504855573177338</v>
+        <v>0.4497375190258026</v>
       </c>
       <c r="C61" s="1">
         <v>520</v>
@@ -5568,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4435550272464752</v>
+        <v>0.4428184628486633</v>
       </c>
       <c r="C62" s="1">
         <v>512</v>
@@ -5594,7 +5594,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="2">
-        <v>0.440089762210846</v>
+        <v>0.4393589496612549</v>
       </c>
       <c r="C63" s="1">
         <v>508</v>
@@ -5620,7 +5620,7 @@
         <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4366244673728943</v>
+        <v>0.4358994364738464</v>
       </c>
       <c r="C64" s="1">
         <v>504</v>
@@ -5646,7 +5646,7 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4348918497562408</v>
+        <v>0.4341696798801422</v>
       </c>
       <c r="C65" s="1">
         <v>502</v>
@@ -5672,7 +5672,7 @@
         <v>51</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4348918497562408</v>
+        <v>0.4341696798801422</v>
       </c>
       <c r="C66" s="1">
         <v>502</v>
@@ -5698,7 +5698,7 @@
         <v>10</v>
       </c>
       <c r="B67" s="2">
-        <v>0.4314265549182892</v>
+        <v>0.4307101666927338</v>
       </c>
       <c r="C67" s="1">
         <v>498</v>
@@ -5724,7 +5724,7 @@
         <v>91</v>
       </c>
       <c r="B68" s="2">
-        <v>0.4123675525188446</v>
+        <v>0.4116827845573425</v>
       </c>
       <c r="C68" s="1">
         <v>476</v>
@@ -5750,7 +5750,7 @@
         <v>92</v>
       </c>
       <c r="B69" s="2">
-        <v>0.4054370224475861</v>
+        <v>0.4047637581825256</v>
       </c>
       <c r="C69" s="1">
         <v>468</v>
@@ -5776,7 +5776,7 @@
         <v>35</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3950411975383759</v>
+        <v>0.3943851888179779</v>
       </c>
       <c r="C70" s="1">
         <v>456</v>
@@ -5802,7 +5802,7 @@
         <v>36</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3941748738288879</v>
+        <v>0.393520325422287</v>
       </c>
       <c r="C71" s="1">
         <v>455</v>
@@ -5828,7 +5828,7 @@
         <v>93</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3863780200481415</v>
+        <v>0.3857364058494568</v>
       </c>
       <c r="C72" s="1">
         <v>446</v>
@@ -5854,7 +5854,7 @@
         <v>94</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3690516352653503</v>
+        <v>0.3684388101100922</v>
       </c>
       <c r="C73" s="1">
         <v>426</v>
@@ -5880,7 +5880,7 @@
         <v>44</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3690516352653503</v>
+        <v>0.3684388101100922</v>
       </c>
       <c r="C74" s="1">
         <v>426</v>
@@ -5906,7 +5906,7 @@
         <v>95</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3551905453205109</v>
+        <v>0.354600727558136</v>
       </c>
       <c r="C75" s="1">
         <v>410</v>
@@ -5932,7 +5932,7 @@
         <v>32</v>
       </c>
       <c r="B76" s="2">
-        <v>0.353457897901535</v>
+        <v>0.3528709709644318</v>
       </c>
       <c r="C76" s="1">
         <v>408</v>
@@ -5958,7 +5958,7 @@
         <v>96</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3465273678302765</v>
+        <v>0.3459519445896149</v>
       </c>
       <c r="C77" s="1">
         <v>400</v>
@@ -5984,7 +5984,7 @@
         <v>27</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3465273678302765</v>
+        <v>0.3459519445896149</v>
       </c>
       <c r="C78" s="1">
         <v>400</v>
@@ -6010,7 +6010,7 @@
         <v>97</v>
       </c>
       <c r="B79" s="2">
-        <v>0.3222704529762268</v>
+        <v>0.321735292673111</v>
       </c>
       <c r="C79" s="1">
         <v>372</v>
@@ -6036,7 +6036,7 @@
         <v>98</v>
       </c>
       <c r="B80" s="2">
-        <v>0.3170725405216217</v>
+        <v>0.3165460228919983</v>
       </c>
       <c r="C80" s="1">
         <v>366</v>
@@ -6062,7 +6062,7 @@
         <v>15</v>
       </c>
       <c r="B81" s="2">
-        <v>0.2980135381221771</v>
+        <v>0.2975186705589294</v>
       </c>
       <c r="C81" s="1">
         <v>344</v>
@@ -6088,7 +6088,7 @@
         <v>99</v>
       </c>
       <c r="B82" s="2">
-        <v>0.2971472144126892</v>
+        <v>0.2966537773609161</v>
       </c>
       <c r="C82" s="1">
         <v>343</v>
@@ -6114,7 +6114,7 @@
         <v>100</v>
       </c>
       <c r="B83" s="2">
-        <v>0.2910829782485962</v>
+        <v>0.2905996143817902</v>
       </c>
       <c r="C83" s="1">
         <v>336</v>
@@ -6140,7 +6140,7 @@
         <v>101</v>
       </c>
       <c r="B84" s="2">
-        <v>0.2893503606319428</v>
+        <v>0.2888698577880859</v>
       </c>
       <c r="C84" s="1">
         <v>334</v>
@@ -6166,7 +6166,7 @@
         <v>21</v>
       </c>
       <c r="B85" s="2">
-        <v>0.2876177132129669</v>
+        <v>0.2871401011943817</v>
       </c>
       <c r="C85" s="1">
         <v>332</v>
@@ -6192,7 +6192,7 @@
         <v>102</v>
       </c>
       <c r="B86" s="2">
-        <v>0.280687153339386</v>
+        <v>0.2802210748195648</v>
       </c>
       <c r="C86" s="1">
         <v>324</v>
@@ -6218,7 +6218,7 @@
         <v>103</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2668260633945465</v>
+        <v>0.2663829922676086</v>
       </c>
       <c r="C87" s="1">
         <v>308</v>
@@ -6244,7 +6244,7 @@
         <v>30</v>
       </c>
       <c r="B88" s="2">
-        <v>0.252964973449707</v>
+        <v>0.2525449097156525</v>
       </c>
       <c r="C88" s="1">
         <v>292</v>
@@ -6270,7 +6270,7 @@
         <v>50</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2356386035680771</v>
+        <v>0.2352473139762878</v>
       </c>
       <c r="C89" s="1">
         <v>272</v>
@@ -6296,7 +6296,7 @@
         <v>104</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2356386035680771</v>
+        <v>0.2352473139762878</v>
       </c>
       <c r="C90" s="1">
         <v>272</v>
@@ -6322,7 +6322,7 @@
         <v>25</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2183122336864471</v>
+        <v>0.2179497182369232</v>
       </c>
       <c r="C91" s="1">
         <v>252</v>
@@ -6348,7 +6348,7 @@
         <v>105</v>
       </c>
       <c r="B92" s="2">
-        <v>0.213114321231842</v>
+        <v>0.2127604335546494</v>
       </c>
       <c r="C92" s="1">
         <v>246</v>
@@ -6374,7 +6374,7 @@
         <v>19</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2096490561962128</v>
+        <v>0.2093009203672409</v>
       </c>
       <c r="C93" s="1">
         <v>242</v>
@@ -6400,7 +6400,7 @@
         <v>106</v>
       </c>
       <c r="B94" s="2">
-        <v>0.202718511223793</v>
+        <v>0.2023818790912628</v>
       </c>
       <c r="C94" s="1">
         <v>234</v>
@@ -6426,7 +6426,7 @@
         <v>107</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2009858638048172</v>
+        <v>0.2006521224975586</v>
       </c>
       <c r="C95" s="1">
         <v>232</v>
@@ -6452,7 +6452,7 @@
         <v>108</v>
       </c>
       <c r="B96" s="2">
-        <v>0.1975205987691879</v>
+        <v>0.197192594408989</v>
       </c>
       <c r="C96" s="1">
         <v>228</v>
@@ -6478,7 +6478,7 @@
         <v>24</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1975205987691879</v>
+        <v>0.197192594408989</v>
       </c>
       <c r="C97" s="1">
         <v>228</v>
@@ -6504,7 +6504,7 @@
         <v>109</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1923226863145828</v>
+        <v>0.1920033246278763</v>
       </c>
       <c r="C98" s="1">
         <v>222</v>
@@ -6530,7 +6530,7 @@
         <v>110</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1905900537967682</v>
+        <v>0.1902735680341721</v>
       </c>
       <c r="C99" s="1">
         <v>220</v>
@@ -6556,7 +6556,7 @@
         <v>111</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1905900537967682</v>
+        <v>0.1902735680341721</v>
       </c>
       <c r="C100" s="1">
         <v>220</v>
@@ -6582,7 +6582,7 @@
         <v>112</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1767289489507675</v>
+        <v>0.1764354854822159</v>
       </c>
       <c r="C101" s="1">
         <v>204</v>
@@ -6608,7 +6608,7 @@
         <v>37</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1663331389427185</v>
+        <v>0.1660569310188294</v>
       </c>
       <c r="C102" s="1">
         <v>192</v>
@@ -6634,7 +6634,7 @@
         <v>113</v>
       </c>
       <c r="B103" s="2">
-        <v>0.162867859005928</v>
+        <v>0.1625974029302597</v>
       </c>
       <c r="C103" s="1">
         <v>188</v>
@@ -6660,7 +6660,7 @@
         <v>114</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1611352264881134</v>
+        <v>0.1608676463365555</v>
       </c>
       <c r="C104" s="1">
         <v>186</v>
@@ -6686,7 +6686,7 @@
         <v>115</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1524720340967178</v>
+        <v>0.1522188484668732</v>
       </c>
       <c r="C105" s="1">
         <v>176</v>
@@ -6712,7 +6712,7 @@
         <v>116</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1524720340967178</v>
+        <v>0.1522188484668732</v>
       </c>
       <c r="C106" s="1">
         <v>176</v>
@@ -6738,7 +6738,7 @@
         <v>42</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1490067690610886</v>
+        <v>0.1487593352794647</v>
       </c>
       <c r="C107" s="1">
         <v>172</v>
@@ -6764,7 +6764,7 @@
         <v>117</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1368783116340637</v>
+        <v>0.1366510093212128</v>
       </c>
       <c r="C108" s="1">
         <v>158</v>
@@ -6790,7 +6790,7 @@
         <v>118</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1334130316972733</v>
+        <v>0.1331914961338043</v>
       </c>
       <c r="C109" s="1">
         <v>154</v>
@@ -6816,7 +6816,7 @@
         <v>119</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1316803991794586</v>
+        <v>0.1314617395401001</v>
       </c>
       <c r="C110" s="1">
         <v>152</v>
@@ -6842,7 +6842,7 @@
         <v>120</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1247498542070389</v>
+        <v>0.124542698264122</v>
       </c>
       <c r="C111" s="1">
         <v>144</v>
@@ -6868,7 +6868,7 @@
         <v>39</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1230172142386437</v>
+        <v>0.1228129342198372</v>
       </c>
       <c r="C112" s="1">
         <v>142</v>
@@ -6894,7 +6894,7 @@
         <v>121</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1195519417524338</v>
+        <v>0.1193534135818481</v>
       </c>
       <c r="C113" s="1">
         <v>138</v>
@@ -6920,7 +6920,7 @@
         <v>26</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1178193017840385</v>
+        <v>0.1176236569881439</v>
       </c>
       <c r="C114" s="1">
         <v>136</v>
@@ -6946,7 +6946,7 @@
         <v>122</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1108887568116188</v>
+        <v>0.1107046157121658</v>
       </c>
       <c r="C115" s="1">
         <v>128</v>
@@ -6972,7 +6972,7 @@
         <v>123</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1108887568116188</v>
+        <v>0.1107046157121658</v>
       </c>
       <c r="C116" s="1">
         <v>128</v>
@@ -6998,7 +6998,7 @@
         <v>124</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1091561168432236</v>
+        <v>0.1089748591184616</v>
       </c>
       <c r="C117" s="1">
         <v>126</v>
@@ -7024,7 +7024,7 @@
         <v>41</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1091561168432236</v>
+        <v>0.1089748591184616</v>
       </c>
       <c r="C118" s="1">
         <v>126</v>
@@ -7050,7 +7050,7 @@
         <v>23</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1039582118391991</v>
+        <v>0.1037855818867683</v>
       </c>
       <c r="C119" s="1">
         <v>120</v>
@@ -7076,7 +7076,7 @@
         <v>125</v>
       </c>
       <c r="B120" s="2">
-        <v>0.09876029938459396</v>
+        <v>0.09859629720449448</v>
       </c>
       <c r="C120" s="1">
         <v>114</v>
@@ -7102,7 +7102,7 @@
         <v>126</v>
       </c>
       <c r="B121" s="2">
-        <v>0.09702765941619873</v>
+        <v>0.09686654061079025</v>
       </c>
       <c r="C121" s="1">
         <v>112</v>
@@ -7128,7 +7128,7 @@
         <v>127</v>
       </c>
       <c r="B122" s="2">
-        <v>0.09702765941619873</v>
+        <v>0.09686654061079025</v>
       </c>
       <c r="C122" s="1">
         <v>112</v>
@@ -7154,7 +7154,7 @@
         <v>128</v>
       </c>
       <c r="B123" s="2">
-        <v>0.09702765941619873</v>
+        <v>0.09686654061079025</v>
       </c>
       <c r="C123" s="1">
         <v>112</v>
@@ -7180,7 +7180,7 @@
         <v>129</v>
       </c>
       <c r="B124" s="2">
-        <v>0.09529502689838409</v>
+        <v>0.09513678401708603</v>
       </c>
       <c r="C124" s="1">
         <v>110</v>
@@ -7206,7 +7206,7 @@
         <v>130</v>
       </c>
       <c r="B125" s="2">
-        <v>0.09529502689838409</v>
+        <v>0.09513678401708603</v>
       </c>
       <c r="C125" s="1">
         <v>110</v>
@@ -7232,7 +7232,7 @@
         <v>12</v>
       </c>
       <c r="B126" s="2">
-        <v>0.09356238692998886</v>
+        <v>0.09340701997280121</v>
       </c>
       <c r="C126" s="1">
         <v>108</v>
@@ -7258,7 +7258,7 @@
         <v>131</v>
       </c>
       <c r="B127" s="2">
-        <v>0.08489920198917389</v>
+        <v>0.0847582221031189</v>
       </c>
       <c r="C127" s="1">
         <v>98</v>
@@ -7284,7 +7284,7 @@
         <v>132</v>
       </c>
       <c r="B128" s="2">
-        <v>0.08489920198917389</v>
+        <v>0.0847582221031189</v>
       </c>
       <c r="C128" s="1">
         <v>98</v>
@@ -7310,7 +7310,7 @@
         <v>133</v>
       </c>
       <c r="B129" s="2">
-        <v>0.07970129698514938</v>
+        <v>0.07956894487142563</v>
       </c>
       <c r="C129" s="1">
         <v>92</v>
@@ -7336,7 +7336,7 @@
         <v>134</v>
       </c>
       <c r="B130" s="2">
-        <v>0.07970129698514938</v>
+        <v>0.07956894487142563</v>
       </c>
       <c r="C130" s="1">
         <v>92</v>
@@ -7362,7 +7362,7 @@
         <v>135</v>
       </c>
       <c r="B131" s="2">
-        <v>0.07450338453054428</v>
+        <v>0.07437966763973236</v>
       </c>
       <c r="C131" s="1">
         <v>86</v>
@@ -7388,7 +7388,7 @@
         <v>136</v>
       </c>
       <c r="B132" s="2">
-        <v>0.07277074456214905</v>
+        <v>0.07264990359544754</v>
       </c>
       <c r="C132" s="1">
         <v>84</v>
@@ -7414,7 +7414,7 @@
         <v>137</v>
       </c>
       <c r="B133" s="2">
-        <v>0.07277074456214905</v>
+        <v>0.07264990359544754</v>
       </c>
       <c r="C133" s="1">
         <v>84</v>
@@ -7440,7 +7440,7 @@
         <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07277074456214905</v>
+        <v>0.07264990359544754</v>
       </c>
       <c r="C134" s="1">
         <v>84</v>
@@ -7466,7 +7466,7 @@
         <v>52</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07277074456214905</v>
+        <v>0.07264990359544754</v>
       </c>
       <c r="C135" s="1">
         <v>84</v>
@@ -7492,7 +7492,7 @@
         <v>139</v>
       </c>
       <c r="B136" s="2">
-        <v>0.07103811204433441</v>
+        <v>0.07092014700174332</v>
       </c>
       <c r="C136" s="1">
         <v>82</v>
@@ -7518,7 +7518,7 @@
         <v>140</v>
       </c>
       <c r="B137" s="2">
-        <v>0.06757283210754395</v>
+        <v>0.06746062636375427</v>
       </c>
       <c r="C137" s="1">
         <v>78</v>
@@ -7544,7 +7544,7 @@
         <v>33</v>
       </c>
       <c r="B138" s="2">
-        <v>0.06584019958972931</v>
+        <v>0.06573086977005005</v>
       </c>
       <c r="C138" s="1">
         <v>76</v>
@@ -7570,7 +7570,7 @@
         <v>141</v>
       </c>
       <c r="B139" s="2">
-        <v>0.05717701464891434</v>
+        <v>0.05708206817507744</v>
       </c>
       <c r="C139" s="1">
         <v>66</v>
@@ -7596,7 +7596,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="2">
-        <v>0.05197910591959953</v>
+        <v>0.05189279094338417</v>
       </c>
       <c r="C140" s="1">
         <v>60</v>
@@ -7622,7 +7622,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="2">
-        <v>0.05197910591959953</v>
+        <v>0.05189279094338417</v>
       </c>
       <c r="C141" s="1">
         <v>60</v>
@@ -7648,7 +7648,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="2">
-        <v>0.05197910591959953</v>
+        <v>0.05189279094338417</v>
       </c>
       <c r="C142" s="1">
         <v>60</v>
@@ -7674,7 +7674,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="2">
-        <v>0.0502464659512043</v>
+        <v>0.05016303062438965</v>
       </c>
       <c r="C143" s="1">
         <v>58</v>
@@ -7700,7 +7700,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="2">
-        <v>0.04678119346499443</v>
+        <v>0.0467035099864006</v>
       </c>
       <c r="C144" s="1">
         <v>54</v>
@@ -7726,7 +7726,7 @@
         <v>45</v>
       </c>
       <c r="B145" s="2">
-        <v>0.04678119346499443</v>
+        <v>0.0467035099864006</v>
       </c>
       <c r="C145" s="1">
         <v>54</v>
@@ -7752,7 +7752,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="2">
-        <v>0.0450485572218895</v>
+        <v>0.04497374966740608</v>
       </c>
       <c r="C146" s="1">
         <v>52</v>
@@ -7778,7 +7778,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04158328473567963</v>
+        <v>0.04151423275470734</v>
       </c>
       <c r="C147" s="1">
         <v>48</v>
@@ -7804,7 +7804,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04158328473567963</v>
+        <v>0.04151423275470734</v>
       </c>
       <c r="C148" s="1">
         <v>48</v>
@@ -7830,7 +7830,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04158328473567963</v>
+        <v>0.04151423275470734</v>
       </c>
       <c r="C149" s="1">
         <v>48</v>
@@ -7856,7 +7856,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="2">
-        <v>0.03811800852417946</v>
+        <v>0.03805471211671829</v>
       </c>
       <c r="C150" s="1">
         <v>44</v>
@@ -7882,7 +7882,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="2">
-        <v>0.03811800852417946</v>
+        <v>0.03805471211671829</v>
       </c>
       <c r="C151" s="1">
         <v>44</v>
@@ -7908,7 +7908,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="2">
-        <v>0.03811800852417946</v>
+        <v>0.03805471211671829</v>
       </c>
       <c r="C152" s="1">
         <v>44</v>
@@ -7934,7 +7934,7 @@
         <v>48</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03811800852417946</v>
+        <v>0.03805471211671829</v>
       </c>
       <c r="C153" s="1">
         <v>44</v>
@@ -7960,7 +7960,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03811800852417946</v>
+        <v>0.03805471211671829</v>
       </c>
       <c r="C154" s="1">
         <v>44</v>
@@ -7986,7 +7986,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="2">
-        <v>0.03811800852417946</v>
+        <v>0.03805471211671829</v>
       </c>
       <c r="C155" s="1">
         <v>44</v>
@@ -8012,7 +8012,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="2">
-        <v>0.03465273603796959</v>
+        <v>0.03459519147872925</v>
       </c>
       <c r="C156" s="1">
         <v>40</v>
@@ -8038,7 +8038,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="2">
-        <v>0.03292009979486466</v>
+        <v>0.03286543488502502</v>
       </c>
       <c r="C157" s="1">
         <v>38</v>
@@ -8064,7 +8064,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="2">
-        <v>0.03118746355175972</v>
+        <v>0.0311356745660305</v>
       </c>
       <c r="C158" s="1">
         <v>36</v>
@@ -8090,7 +8090,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="2">
-        <v>0.03118746355175972</v>
+        <v>0.0311356745660305</v>
       </c>
       <c r="C159" s="1">
         <v>36</v>
@@ -8116,7 +8116,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="2">
-        <v>0.03118746355175972</v>
+        <v>0.0311356745660305</v>
       </c>
       <c r="C160" s="1">
         <v>36</v>
@@ -8142,7 +8142,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.03118746355175972</v>
+        <v>0.0311356745660305</v>
       </c>
       <c r="C161" s="1">
         <v>36</v>
@@ -8168,7 +8168,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.0277221892029047</v>
+        <v>0.02767615392804146</v>
       </c>
       <c r="C162" s="1">
         <v>32</v>
@@ -8194,7 +8194,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.0277221892029047</v>
+        <v>0.02767615392804146</v>
       </c>
       <c r="C163" s="1">
         <v>32</v>
@@ -8220,7 +8220,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.0277221892029047</v>
+        <v>0.02767615392804146</v>
       </c>
       <c r="C164" s="1">
         <v>32</v>
@@ -8246,7 +8246,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.0277221892029047</v>
+        <v>0.02767615392804146</v>
       </c>
       <c r="C165" s="1">
         <v>32</v>
@@ -8272,7 +8272,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.02598955295979977</v>
+        <v>0.02594639547169209</v>
       </c>
       <c r="C166" s="1">
         <v>30</v>
@@ -8298,7 +8298,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.02598955295979977</v>
+        <v>0.02594639547169209</v>
       </c>
       <c r="C167" s="1">
         <v>30</v>
@@ -8324,7 +8324,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.02252427861094475</v>
+        <v>0.02248687483370304</v>
       </c>
       <c r="C168" s="1">
         <v>26</v>
@@ -8350,7 +8350,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.02079164236783981</v>
+        <v>0.02075711637735367</v>
       </c>
       <c r="C169" s="1">
         <v>24</v>
@@ -8376,7 +8376,7 @@
         <v>47</v>
       </c>
       <c r="B170" s="2">
-        <v>0.01386109460145235</v>
+        <v>0.01383807696402073</v>
       </c>
       <c r="C170" s="1">
         <v>16</v>
@@ -8402,7 +8402,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="2">
-        <v>0.006930547300726175</v>
+        <v>0.006919038482010365</v>
       </c>
       <c r="C171" s="1">
         <v>8</v>
@@ -8428,7 +8428,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2">
-        <v>0.006930547300726175</v>
+        <v>0.006919038482010365</v>
       </c>
       <c r="C172" s="1">
         <v>8</v>
@@ -8454,7 +8454,7 @@
         <v>46</v>
       </c>
       <c r="B173" s="2">
-        <v>0.003465273650363088</v>
+        <v>0.003459519241005182</v>
       </c>
       <c r="C173" s="1">
         <v>4</v>
@@ -8480,7 +8480,7 @@
         <v>172</v>
       </c>
       <c r="B174" s="2">
-        <v>0.003465273650363088</v>
+        <v>0.003459519241005182</v>
       </c>
       <c r="C174" s="1">
         <v>4</v>
@@ -8506,7 +8506,7 @@
         <v>173</v>
       </c>
       <c r="B175" s="2">
-        <v>0.003465273650363088</v>
+        <v>0.003459519241005182</v>
       </c>
       <c r="C175" s="1">
         <v>4</v>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -263,10 +263,10 @@
     <t>stm32g4xx_hal_rcc_ex.o</t>
   </si>
   <si>
+    <t>motor_profile.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_tim_ex.o</t>
-  </si>
-  <si>
-    <t>motor_profile.o</t>
   </si>
   <si>
     <t>atan2f.o</t>
@@ -1205,10 +1205,10 @@
                   <c:v>tim.o</c:v>
                 </c:pt>
                 <c:pt idx="48">
+                  <c:v>motor_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>motor_profile.o</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>atan2f.o</c:v>
@@ -1592,523 +1592,523 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="174"/>
                 <c:pt idx="0">
-                  <c:v>4.102989673614502</c:v>
+                  <c:v>4.102564334869385</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.921365022659302</c:v>
+                  <c:v>3.920958280563355</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.675739288330078</c:v>
+                  <c:v>3.675357818603516</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.229461193084717</c:v>
+                  <c:v>3.229126214981079</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.18275785446167</c:v>
+                  <c:v>3.182427406311035</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.866211652755737</c:v>
+                  <c:v>2.865914344787598</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.758966684341431</c:v>
+                  <c:v>2.75868034362793</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.48566460609436</c:v>
+                  <c:v>2.485406637191773</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.46490740776062</c:v>
+                  <c:v>2.464651823043823</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.075711488723755</c:v>
+                  <c:v>2.075496196746826</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.053224802017212</c:v>
+                  <c:v>2.053011655807495</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.034197330474854</c:v>
+                  <c:v>2.033986330032349</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.03073787689209</c:v>
+                  <c:v>2.030527114868164</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.027278423309326</c:v>
+                  <c:v>2.02706789970398</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.918303489685059</c:v>
+                  <c:v>1.918104410171509</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.850842833518982</c:v>
+                  <c:v>1.850650787353516</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.774733424186707</c:v>
+                  <c:v>1.774549245834351</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.681326389312744</c:v>
+                  <c:v>1.681151866912842</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.643271684646606</c:v>
+                  <c:v>1.643101096153259</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.561972975730896</c:v>
+                  <c:v>1.561810851097107</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.40456485748291</c:v>
+                  <c:v>1.40441906452179</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.390726804733276</c:v>
+                  <c:v>1.39058244228363</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.387267231941223</c:v>
+                  <c:v>1.387123227119446</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.364780306816101</c:v>
+                  <c:v>1.364638686180115</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.243697166442871</c:v>
+                  <c:v>1.243568181991577</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.205642461776733</c:v>
+                  <c:v>1.205517411231995</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.139911651611328</c:v>
+                  <c:v>1.139793276786804</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.079370021820068</c:v>
+                  <c:v>1.079257965087891</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.055153369903565</c:v>
+                  <c:v>1.055043935775757</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.037855744361877</c:v>
+                  <c:v>1.037748098373413</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.034396290779114</c:v>
+                  <c:v>1.034288883209229</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.027477264404297</c:v>
+                  <c:v>1.027370572090149</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.011909365653992</c:v>
+                  <c:v>1.011804342269898</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9946117997169495</c:v>
+                  <c:v>0.9945085644721985</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9357999563217163</c:v>
+                  <c:v>0.9357028603553772</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8890964388847351</c:v>
+                  <c:v>0.8890041708946228</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8743935227394104</c:v>
+                  <c:v>0.8743027448654175</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8614203333854675</c:v>
+                  <c:v>0.8613309264183044</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.8389334082603455</c:v>
+                  <c:v>0.8388463854789734</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.8302846550941467</c:v>
+                  <c:v>0.8301984667778015</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.8268251419067383</c:v>
+                  <c:v>0.8267393112182617</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7403371334075928</c:v>
+                  <c:v>0.7402603030204773</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7351478338241577</c:v>
+                  <c:v>0.7350715398788452</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7195799946784973</c:v>
+                  <c:v>0.7195053696632385</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.709201455116272</c:v>
+                  <c:v>0.7091278433799744</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.6901741027832031</c:v>
+                  <c:v>0.6901024580001831</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6780657768249512</c:v>
+                  <c:v>0.6779954433441162</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6538491249084473</c:v>
+                  <c:v>0.6537812948226929</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6227134466171265</c:v>
+                  <c:v>0.6330263614654541</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.6227134466171265</c:v>
+                  <c:v>0.6226488351821899</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.5915778279304504</c:v>
+                  <c:v>0.5915164351463318</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5569826364517212</c:v>
+                  <c:v>0.5569248199462891</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5362254977226257</c:v>
+                  <c:v>0.5361698269844055</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5344957113265991</c:v>
+                  <c:v>0.534440279006958</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5050898194313049</c:v>
+                  <c:v>0.5050374269485474</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.4947112500667572</c:v>
+                  <c:v>0.4946599304676056</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.4808731973171234</c:v>
+                  <c:v>0.480823278427124</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4739541411399841</c:v>
+                  <c:v>0.4739049673080444</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4497375190258026</c:v>
+                  <c:v>0.4496908485889435</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4428184628486633</c:v>
+                  <c:v>0.4427725076675415</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4393589496612549</c:v>
+                  <c:v>0.4393133521080017</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4358994364738464</c:v>
+                  <c:v>0.4358541965484619</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4341696798801422</c:v>
+                  <c:v>0.434124618768692</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4341696798801422</c:v>
+                  <c:v>0.434124618768692</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.4307101666927338</c:v>
+                  <c:v>0.4306654632091522</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.4116827845573425</c:v>
+                  <c:v>0.411640077829361</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.4047637581825256</c:v>
+                  <c:v>0.4047217667102814</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3943851888179779</c:v>
+                  <c:v>0.3943442702293396</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.393520325422287</c:v>
+                  <c:v>0.3934794962406158</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3857364058494568</c:v>
+                  <c:v>0.3856963813304901</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3684388101100922</c:v>
+                  <c:v>0.3684005737304688</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3684388101100922</c:v>
+                  <c:v>0.3684005737304688</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.354600727558136</c:v>
+                  <c:v>0.3545639216899872</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3528709709644318</c:v>
+                  <c:v>0.3528343439102173</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3459519445896149</c:v>
+                  <c:v>0.3459160327911377</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3459519445896149</c:v>
+                  <c:v>0.3459160327911377</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.321735292673111</c:v>
+                  <c:v>0.3217019140720367</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.3165460228919983</c:v>
+                  <c:v>0.3165131807327271</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.2975186705589294</c:v>
+                  <c:v>0.2974877953529358</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.2966537773609161</c:v>
+                  <c:v>0.2966229915618897</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.2905996143817902</c:v>
+                  <c:v>0.2905694544315338</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.2888698577880859</c:v>
+                  <c:v>0.2888398766517639</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.2871401011943817</c:v>
+                  <c:v>0.287110298871994</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2802210748195648</c:v>
+                  <c:v>0.2801919877529144</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2663829922676086</c:v>
+                  <c:v>0.2663553357124329</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2525449097156525</c:v>
+                  <c:v>0.2525187134742737</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2352473139762878</c:v>
+                  <c:v>0.2352229058742523</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2352473139762878</c:v>
+                  <c:v>0.2352229058742523</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2179497182369232</c:v>
+                  <c:v>0.217927098274231</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2127604335546494</c:v>
+                  <c:v>0.2127383649349213</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2093009203672409</c:v>
+                  <c:v>0.2092791944742203</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2023818790912628</c:v>
+                  <c:v>0.2023608833551407</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2006521224975586</c:v>
+                  <c:v>0.2006312906742096</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.197192594408989</c:v>
+                  <c:v>0.1971721351146698</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.197192594408989</c:v>
+                  <c:v>0.1971721351146698</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1920033246278763</c:v>
+                  <c:v>0.1919834017753601</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1902735680341721</c:v>
+                  <c:v>0.190253809094429</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1902735680341721</c:v>
+                  <c:v>0.190253809094429</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1764354854822159</c:v>
+                  <c:v>0.1764171719551086</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1660569310188294</c:v>
+                  <c:v>0.1660396903753281</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1625974029302597</c:v>
+                  <c:v>0.1625805348157883</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1608676463365555</c:v>
+                  <c:v>0.1608509570360184</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1522188484668732</c:v>
+                  <c:v>0.1522030532360077</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1522188484668732</c:v>
+                  <c:v>0.1522030532360077</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1487593352794647</c:v>
+                  <c:v>0.1487438976764679</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1366510093212128</c:v>
+                  <c:v>0.1366368383169174</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1331914961338043</c:v>
+                  <c:v>0.1331776678562164</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1314617395401001</c:v>
+                  <c:v>0.1314480900764465</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.124542698264122</c:v>
+                  <c:v>0.1245297715067864</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1228129342198372</c:v>
+                  <c:v>0.1228001937270165</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1193534135818481</c:v>
+                  <c:v>0.1193410307168961</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1176236569881439</c:v>
+                  <c:v>0.1176114529371262</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1107046157121658</c:v>
+                  <c:v>0.1106931269168854</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1107046157121658</c:v>
+                  <c:v>0.1106931269168854</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1089748591184616</c:v>
+                  <c:v>0.1089635491371155</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1089748591184616</c:v>
+                  <c:v>0.1089635491371155</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1037855818867683</c:v>
+                  <c:v>0.1037748083472252</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.09859629720449448</c:v>
+                  <c:v>0.0985860675573349</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.09686654061079025</c:v>
+                  <c:v>0.096856489777565</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.09686654061079025</c:v>
+                  <c:v>0.096856489777565</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.09686654061079025</c:v>
+                  <c:v>0.096856489777565</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.09513678401708603</c:v>
+                  <c:v>0.09512690454721451</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.09513678401708603</c:v>
+                  <c:v>0.09512690454721451</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.09340701997280121</c:v>
+                  <c:v>0.09339732676744461</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.0847582221031189</c:v>
+                  <c:v>0.08474943041801453</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.0847582221031189</c:v>
+                  <c:v>0.08474943041801453</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.07956894487142563</c:v>
+                  <c:v>0.07956068962812424</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.07956894487142563</c:v>
+                  <c:v>0.07956068962812424</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.07437966763973236</c:v>
+                  <c:v>0.07437194883823395</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.07264990359544754</c:v>
+                  <c:v>0.07264236360788345</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.07264990359544754</c:v>
+                  <c:v>0.07264236360788345</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07264990359544754</c:v>
+                  <c:v>0.07264236360788345</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07264990359544754</c:v>
+                  <c:v>0.07264236360788345</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.07092014700174332</c:v>
+                  <c:v>0.07091278582811356</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06746062636375427</c:v>
+                  <c:v>0.06745362281799316</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06573086977005005</c:v>
+                  <c:v>0.06572404503822327</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.05708206817507744</c:v>
+                  <c:v>0.05707614496350288</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.05189279094338417</c:v>
+                  <c:v>0.0518874041736126</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.05189279094338417</c:v>
+                  <c:v>0.0518874041736126</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.05189279094338417</c:v>
+                  <c:v>0.0518874041736126</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.05016303062438965</c:v>
+                  <c:v>0.0501578226685524</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.0467035099864006</c:v>
+                  <c:v>0.04669866338372231</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.0467035099864006</c:v>
+                  <c:v>0.04669866338372231</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.04497374966740608</c:v>
+                  <c:v>0.04496908560395241</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04151423275470734</c:v>
+                  <c:v>0.04150992259383202</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04151423275470734</c:v>
+                  <c:v>0.04150992259383202</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04151423275470734</c:v>
+                  <c:v>0.04150992259383202</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.03805471211671829</c:v>
+                  <c:v>0.03805076330900192</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.03805471211671829</c:v>
+                  <c:v>0.03805076330900192</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.03805471211671829</c:v>
+                  <c:v>0.03805076330900192</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03805471211671829</c:v>
+                  <c:v>0.03805076330900192</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03805471211671829</c:v>
+                  <c:v>0.03805076330900192</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03805471211671829</c:v>
+                  <c:v>0.03805076330900192</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03459519147872925</c:v>
+                  <c:v>0.03459160402417183</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.03286543488502502</c:v>
+                  <c:v>0.03286202251911163</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.0311356745660305</c:v>
+                  <c:v>0.03113244287669659</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.0311356745660305</c:v>
+                  <c:v>0.03113244287669659</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.0311356745660305</c:v>
+                  <c:v>0.03113244287669659</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.0311356745660305</c:v>
+                  <c:v>0.03113244287669659</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.02767615392804146</c:v>
+                  <c:v>0.02767328172922134</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.02767615392804146</c:v>
+                  <c:v>0.02767328172922134</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.02767615392804146</c:v>
+                  <c:v>0.02767328172922134</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.02767615392804146</c:v>
+                  <c:v>0.02767328172922134</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.02594639547169209</c:v>
+                  <c:v>0.0259437020868063</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02594639547169209</c:v>
+                  <c:v>0.0259437020868063</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02248687483370304</c:v>
+                  <c:v>0.0224845428019762</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02075711637735367</c:v>
+                  <c:v>0.02075496129691601</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.01383807696402073</c:v>
+                  <c:v>0.01383664086461067</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.006919038482010365</c:v>
+                  <c:v>0.006918320432305336</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.006919038482010365</c:v>
+                  <c:v>0.006918320432305336</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.003459519241005182</c:v>
+                  <c:v>0.003459160216152668</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.003459519241005182</c:v>
+                  <c:v>0.003459160216152668</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.003459519241005182</c:v>
+                  <c:v>0.003459160216152668</c:v>
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>0</c:v>
@@ -4034,7 +4034,7 @@
         <v>54</v>
       </c>
       <c r="B3" s="2">
-        <v>4.102989673614502</v>
+        <v>4.102564334869385</v>
       </c>
       <c r="C3" s="1">
         <v>4744</v>
@@ -4060,7 +4060,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>3.921365022659302</v>
+        <v>3.920958280563355</v>
       </c>
       <c r="C4" s="1">
         <v>4534</v>
@@ -4086,7 +4086,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>3.675739288330078</v>
+        <v>3.675357818603516</v>
       </c>
       <c r="C5" s="1">
         <v>4250</v>
@@ -4112,7 +4112,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>3.229461193084717</v>
+        <v>3.229126214981079</v>
       </c>
       <c r="C6" s="1">
         <v>3734</v>
@@ -4138,7 +4138,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>3.18275785446167</v>
+        <v>3.182427406311035</v>
       </c>
       <c r="C7" s="1">
         <v>3680</v>
@@ -4164,7 +4164,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>2.866211652755737</v>
+        <v>2.865914344787598</v>
       </c>
       <c r="C8" s="1">
         <v>3314</v>
@@ -4190,7 +4190,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>2.758966684341431</v>
+        <v>2.75868034362793</v>
       </c>
       <c r="C9" s="1">
         <v>3190</v>
@@ -4216,7 +4216,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="2">
-        <v>2.48566460609436</v>
+        <v>2.485406637191773</v>
       </c>
       <c r="C10" s="1">
         <v>2874</v>
@@ -4242,7 +4242,7 @@
         <v>59</v>
       </c>
       <c r="B11" s="2">
-        <v>2.46490740776062</v>
+        <v>2.464651823043823</v>
       </c>
       <c r="C11" s="1">
         <v>2850</v>
@@ -4268,7 +4268,7 @@
         <v>60</v>
       </c>
       <c r="B12" s="2">
-        <v>2.075711488723755</v>
+        <v>2.075496196746826</v>
       </c>
       <c r="C12" s="1">
         <v>2400</v>
@@ -4294,7 +4294,7 @@
         <v>61</v>
       </c>
       <c r="B13" s="2">
-        <v>2.053224802017212</v>
+        <v>2.053011655807495</v>
       </c>
       <c r="C13" s="1">
         <v>2374</v>
@@ -4320,7 +4320,7 @@
         <v>62</v>
       </c>
       <c r="B14" s="2">
-        <v>2.034197330474854</v>
+        <v>2.033986330032349</v>
       </c>
       <c r="C14" s="1">
         <v>2352</v>
@@ -4346,7 +4346,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="2">
-        <v>2.03073787689209</v>
+        <v>2.030527114868164</v>
       </c>
       <c r="C15" s="1">
         <v>2348</v>
@@ -4372,7 +4372,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>2.027278423309326</v>
+        <v>2.02706789970398</v>
       </c>
       <c r="C16" s="1">
         <v>2344</v>
@@ -4398,7 +4398,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="2">
-        <v>1.918303489685059</v>
+        <v>1.918104410171509</v>
       </c>
       <c r="C17" s="1">
         <v>2218</v>
@@ -4424,7 +4424,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="2">
-        <v>1.850842833518982</v>
+        <v>1.850650787353516</v>
       </c>
       <c r="C18" s="1">
         <v>2140</v>
@@ -4450,7 +4450,7 @@
         <v>65</v>
       </c>
       <c r="B19" s="2">
-        <v>1.774733424186707</v>
+        <v>1.774549245834351</v>
       </c>
       <c r="C19" s="1">
         <v>2052</v>
@@ -4476,7 +4476,7 @@
         <v>66</v>
       </c>
       <c r="B20" s="2">
-        <v>1.681326389312744</v>
+        <v>1.681151866912842</v>
       </c>
       <c r="C20" s="1">
         <v>1944</v>
@@ -4502,7 +4502,7 @@
         <v>67</v>
       </c>
       <c r="B21" s="2">
-        <v>1.643271684646606</v>
+        <v>1.643101096153259</v>
       </c>
       <c r="C21" s="1">
         <v>1900</v>
@@ -4528,7 +4528,7 @@
         <v>68</v>
       </c>
       <c r="B22" s="2">
-        <v>1.561972975730896</v>
+        <v>1.561810851097107</v>
       </c>
       <c r="C22" s="1">
         <v>1806</v>
@@ -4554,7 +4554,7 @@
         <v>49</v>
       </c>
       <c r="B23" s="2">
-        <v>1.40456485748291</v>
+        <v>1.40441906452179</v>
       </c>
       <c r="C23" s="1">
         <v>1624</v>
@@ -4580,7 +4580,7 @@
         <v>69</v>
       </c>
       <c r="B24" s="2">
-        <v>1.390726804733276</v>
+        <v>1.39058244228363</v>
       </c>
       <c r="C24" s="1">
         <v>1608</v>
@@ -4606,7 +4606,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="2">
-        <v>1.387267231941223</v>
+        <v>1.387123227119446</v>
       </c>
       <c r="C25" s="1">
         <v>1604</v>
@@ -4632,7 +4632,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="2">
-        <v>1.364780306816101</v>
+        <v>1.364638686180115</v>
       </c>
       <c r="C26" s="1">
         <v>1578</v>
@@ -4658,7 +4658,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="2">
-        <v>1.243697166442871</v>
+        <v>1.243568181991577</v>
       </c>
       <c r="C27" s="1">
         <v>1438</v>
@@ -4684,7 +4684,7 @@
         <v>70</v>
       </c>
       <c r="B28" s="2">
-        <v>1.205642461776733</v>
+        <v>1.205517411231995</v>
       </c>
       <c r="C28" s="1">
         <v>1394</v>
@@ -4710,7 +4710,7 @@
         <v>71</v>
       </c>
       <c r="B29" s="2">
-        <v>1.139911651611328</v>
+        <v>1.139793276786804</v>
       </c>
       <c r="C29" s="1">
         <v>1318</v>
@@ -4736,7 +4736,7 @@
         <v>72</v>
       </c>
       <c r="B30" s="2">
-        <v>1.079370021820068</v>
+        <v>1.079257965087891</v>
       </c>
       <c r="C30" s="1">
         <v>1248</v>
@@ -4762,7 +4762,7 @@
         <v>73</v>
       </c>
       <c r="B31" s="2">
-        <v>1.055153369903565</v>
+        <v>1.055043935775757</v>
       </c>
       <c r="C31" s="1">
         <v>1220</v>
@@ -4788,7 +4788,7 @@
         <v>74</v>
       </c>
       <c r="B32" s="2">
-        <v>1.037855744361877</v>
+        <v>1.037748098373413</v>
       </c>
       <c r="C32" s="1">
         <v>1200</v>
@@ -4814,7 +4814,7 @@
         <v>75</v>
       </c>
       <c r="B33" s="2">
-        <v>1.034396290779114</v>
+        <v>1.034288883209229</v>
       </c>
       <c r="C33" s="1">
         <v>1196</v>
@@ -4840,7 +4840,7 @@
         <v>38</v>
       </c>
       <c r="B34" s="2">
-        <v>1.027477264404297</v>
+        <v>1.027370572090149</v>
       </c>
       <c r="C34" s="1">
         <v>1188</v>
@@ -4866,7 +4866,7 @@
         <v>76</v>
       </c>
       <c r="B35" s="2">
-        <v>1.011909365653992</v>
+        <v>1.011804342269898</v>
       </c>
       <c r="C35" s="1">
         <v>1170</v>
@@ -4892,7 +4892,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9946117997169495</v>
+        <v>0.9945085644721985</v>
       </c>
       <c r="C36" s="1">
         <v>1150</v>
@@ -4918,7 +4918,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9357999563217163</v>
+        <v>0.9357028603553772</v>
       </c>
       <c r="C37" s="1">
         <v>1082</v>
@@ -4944,7 +4944,7 @@
         <v>28</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8890964388847351</v>
+        <v>0.8890041708946228</v>
       </c>
       <c r="C38" s="1">
         <v>1028</v>
@@ -4970,7 +4970,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8743935227394104</v>
+        <v>0.8743027448654175</v>
       </c>
       <c r="C39" s="1">
         <v>1011</v>
@@ -4996,7 +4996,7 @@
         <v>8</v>
       </c>
       <c r="B40" s="2">
-        <v>0.8614203333854675</v>
+        <v>0.8613309264183044</v>
       </c>
       <c r="C40" s="1">
         <v>996</v>
@@ -5022,7 +5022,7 @@
         <v>29</v>
       </c>
       <c r="B41" s="2">
-        <v>0.8389334082603455</v>
+        <v>0.8388463854789734</v>
       </c>
       <c r="C41" s="1">
         <v>970</v>
@@ -5048,7 +5048,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="2">
-        <v>0.8302846550941467</v>
+        <v>0.8301984667778015</v>
       </c>
       <c r="C42" s="1">
         <v>960</v>
@@ -5074,7 +5074,7 @@
         <v>77</v>
       </c>
       <c r="B43" s="2">
-        <v>0.8268251419067383</v>
+        <v>0.8267393112182617</v>
       </c>
       <c r="C43" s="1">
         <v>956</v>
@@ -5100,7 +5100,7 @@
         <v>78</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7403371334075928</v>
+        <v>0.7402603030204773</v>
       </c>
       <c r="C44" s="1">
         <v>856</v>
@@ -5126,7 +5126,7 @@
         <v>79</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7351478338241577</v>
+        <v>0.7350715398788452</v>
       </c>
       <c r="C45" s="1">
         <v>850</v>
@@ -5152,7 +5152,7 @@
         <v>80</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7195799946784973</v>
+        <v>0.7195053696632385</v>
       </c>
       <c r="C46" s="1">
         <v>832</v>
@@ -5178,7 +5178,7 @@
         <v>9</v>
       </c>
       <c r="B47" s="2">
-        <v>0.709201455116272</v>
+        <v>0.7091278433799744</v>
       </c>
       <c r="C47" s="1">
         <v>820</v>
@@ -5204,7 +5204,7 @@
         <v>40</v>
       </c>
       <c r="B48" s="2">
-        <v>0.6901741027832031</v>
+        <v>0.6901024580001831</v>
       </c>
       <c r="C48" s="1">
         <v>798</v>
@@ -5230,7 +5230,7 @@
         <v>81</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6780657768249512</v>
+        <v>0.6779954433441162</v>
       </c>
       <c r="C49" s="1">
         <v>784</v>
@@ -5256,7 +5256,7 @@
         <v>18</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6538491249084473</v>
+        <v>0.6537812948226929</v>
       </c>
       <c r="C50" s="1">
         <v>756</v>
@@ -5282,16 +5282,16 @@
         <v>82</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6227134466171265</v>
+        <v>0.6330263614654541</v>
       </c>
       <c r="C51" s="1">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -5308,7 +5308,7 @@
         <v>83</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6227134466171265</v>
+        <v>0.6226488351821899</v>
       </c>
       <c r="C52" s="1">
         <v>720</v>
@@ -5334,7 +5334,7 @@
         <v>84</v>
       </c>
       <c r="B53" s="2">
-        <v>0.5915778279304504</v>
+        <v>0.5915164351463318</v>
       </c>
       <c r="C53" s="1">
         <v>684</v>
@@ -5360,7 +5360,7 @@
         <v>85</v>
       </c>
       <c r="B54" s="2">
-        <v>0.5569826364517212</v>
+        <v>0.5569248199462891</v>
       </c>
       <c r="C54" s="1">
         <v>644</v>
@@ -5386,7 +5386,7 @@
         <v>7</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5362254977226257</v>
+        <v>0.5361698269844055</v>
       </c>
       <c r="C55" s="1">
         <v>620</v>
@@ -5412,7 +5412,7 @@
         <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5344957113265991</v>
+        <v>0.534440279006958</v>
       </c>
       <c r="C56" s="1">
         <v>618</v>
@@ -5438,7 +5438,7 @@
         <v>6</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5050898194313049</v>
+        <v>0.5050374269485474</v>
       </c>
       <c r="C57" s="1">
         <v>584</v>
@@ -5464,7 +5464,7 @@
         <v>87</v>
       </c>
       <c r="B58" s="2">
-        <v>0.4947112500667572</v>
+        <v>0.4946599304676056</v>
       </c>
       <c r="C58" s="1">
         <v>572</v>
@@ -5490,7 +5490,7 @@
         <v>88</v>
       </c>
       <c r="B59" s="2">
-        <v>0.4808731973171234</v>
+        <v>0.480823278427124</v>
       </c>
       <c r="C59" s="1">
         <v>556</v>
@@ -5516,7 +5516,7 @@
         <v>20</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4739541411399841</v>
+        <v>0.4739049673080444</v>
       </c>
       <c r="C60" s="1">
         <v>548</v>
@@ -5542,7 +5542,7 @@
         <v>89</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4497375190258026</v>
+        <v>0.4496908485889435</v>
       </c>
       <c r="C61" s="1">
         <v>520</v>
@@ -5568,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4428184628486633</v>
+        <v>0.4427725076675415</v>
       </c>
       <c r="C62" s="1">
         <v>512</v>
@@ -5594,7 +5594,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4393589496612549</v>
+        <v>0.4393133521080017</v>
       </c>
       <c r="C63" s="1">
         <v>508</v>
@@ -5620,7 +5620,7 @@
         <v>90</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4358994364738464</v>
+        <v>0.4358541965484619</v>
       </c>
       <c r="C64" s="1">
         <v>504</v>
@@ -5646,7 +5646,7 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4341696798801422</v>
+        <v>0.434124618768692</v>
       </c>
       <c r="C65" s="1">
         <v>502</v>
@@ -5672,7 +5672,7 @@
         <v>51</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4341696798801422</v>
+        <v>0.434124618768692</v>
       </c>
       <c r="C66" s="1">
         <v>502</v>
@@ -5698,7 +5698,7 @@
         <v>10</v>
       </c>
       <c r="B67" s="2">
-        <v>0.4307101666927338</v>
+        <v>0.4306654632091522</v>
       </c>
       <c r="C67" s="1">
         <v>498</v>
@@ -5724,7 +5724,7 @@
         <v>91</v>
       </c>
       <c r="B68" s="2">
-        <v>0.4116827845573425</v>
+        <v>0.411640077829361</v>
       </c>
       <c r="C68" s="1">
         <v>476</v>
@@ -5750,7 +5750,7 @@
         <v>92</v>
       </c>
       <c r="B69" s="2">
-        <v>0.4047637581825256</v>
+        <v>0.4047217667102814</v>
       </c>
       <c r="C69" s="1">
         <v>468</v>
@@ -5776,7 +5776,7 @@
         <v>35</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3943851888179779</v>
+        <v>0.3943442702293396</v>
       </c>
       <c r="C70" s="1">
         <v>456</v>
@@ -5802,7 +5802,7 @@
         <v>36</v>
       </c>
       <c r="B71" s="2">
-        <v>0.393520325422287</v>
+        <v>0.3934794962406158</v>
       </c>
       <c r="C71" s="1">
         <v>455</v>
@@ -5828,7 +5828,7 @@
         <v>93</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3857364058494568</v>
+        <v>0.3856963813304901</v>
       </c>
       <c r="C72" s="1">
         <v>446</v>
@@ -5854,7 +5854,7 @@
         <v>94</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3684388101100922</v>
+        <v>0.3684005737304688</v>
       </c>
       <c r="C73" s="1">
         <v>426</v>
@@ -5880,7 +5880,7 @@
         <v>44</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3684388101100922</v>
+        <v>0.3684005737304688</v>
       </c>
       <c r="C74" s="1">
         <v>426</v>
@@ -5906,7 +5906,7 @@
         <v>95</v>
       </c>
       <c r="B75" s="2">
-        <v>0.354600727558136</v>
+        <v>0.3545639216899872</v>
       </c>
       <c r="C75" s="1">
         <v>410</v>
@@ -5932,7 +5932,7 @@
         <v>32</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3528709709644318</v>
+        <v>0.3528343439102173</v>
       </c>
       <c r="C76" s="1">
         <v>408</v>
@@ -5958,7 +5958,7 @@
         <v>96</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3459519445896149</v>
+        <v>0.3459160327911377</v>
       </c>
       <c r="C77" s="1">
         <v>400</v>
@@ -5984,7 +5984,7 @@
         <v>27</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3459519445896149</v>
+        <v>0.3459160327911377</v>
       </c>
       <c r="C78" s="1">
         <v>400</v>
@@ -6010,7 +6010,7 @@
         <v>97</v>
       </c>
       <c r="B79" s="2">
-        <v>0.321735292673111</v>
+        <v>0.3217019140720367</v>
       </c>
       <c r="C79" s="1">
         <v>372</v>
@@ -6036,7 +6036,7 @@
         <v>98</v>
       </c>
       <c r="B80" s="2">
-        <v>0.3165460228919983</v>
+        <v>0.3165131807327271</v>
       </c>
       <c r="C80" s="1">
         <v>366</v>
@@ -6062,7 +6062,7 @@
         <v>15</v>
       </c>
       <c r="B81" s="2">
-        <v>0.2975186705589294</v>
+        <v>0.2974877953529358</v>
       </c>
       <c r="C81" s="1">
         <v>344</v>
@@ -6088,7 +6088,7 @@
         <v>99</v>
       </c>
       <c r="B82" s="2">
-        <v>0.2966537773609161</v>
+        <v>0.2966229915618897</v>
       </c>
       <c r="C82" s="1">
         <v>343</v>
@@ -6114,7 +6114,7 @@
         <v>100</v>
       </c>
       <c r="B83" s="2">
-        <v>0.2905996143817902</v>
+        <v>0.2905694544315338</v>
       </c>
       <c r="C83" s="1">
         <v>336</v>
@@ -6140,7 +6140,7 @@
         <v>101</v>
       </c>
       <c r="B84" s="2">
-        <v>0.2888698577880859</v>
+        <v>0.2888398766517639</v>
       </c>
       <c r="C84" s="1">
         <v>334</v>
@@ -6166,7 +6166,7 @@
         <v>21</v>
       </c>
       <c r="B85" s="2">
-        <v>0.2871401011943817</v>
+        <v>0.287110298871994</v>
       </c>
       <c r="C85" s="1">
         <v>332</v>
@@ -6192,7 +6192,7 @@
         <v>102</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2802210748195648</v>
+        <v>0.2801919877529144</v>
       </c>
       <c r="C86" s="1">
         <v>324</v>
@@ -6218,7 +6218,7 @@
         <v>103</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2663829922676086</v>
+        <v>0.2663553357124329</v>
       </c>
       <c r="C87" s="1">
         <v>308</v>
@@ -6244,7 +6244,7 @@
         <v>30</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2525449097156525</v>
+        <v>0.2525187134742737</v>
       </c>
       <c r="C88" s="1">
         <v>292</v>
@@ -6270,7 +6270,7 @@
         <v>50</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2352473139762878</v>
+        <v>0.2352229058742523</v>
       </c>
       <c r="C89" s="1">
         <v>272</v>
@@ -6296,7 +6296,7 @@
         <v>104</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2352473139762878</v>
+        <v>0.2352229058742523</v>
       </c>
       <c r="C90" s="1">
         <v>272</v>
@@ -6322,7 +6322,7 @@
         <v>25</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2179497182369232</v>
+        <v>0.217927098274231</v>
       </c>
       <c r="C91" s="1">
         <v>252</v>
@@ -6348,7 +6348,7 @@
         <v>105</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2127604335546494</v>
+        <v>0.2127383649349213</v>
       </c>
       <c r="C92" s="1">
         <v>246</v>
@@ -6374,7 +6374,7 @@
         <v>19</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2093009203672409</v>
+        <v>0.2092791944742203</v>
       </c>
       <c r="C93" s="1">
         <v>242</v>
@@ -6400,7 +6400,7 @@
         <v>106</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2023818790912628</v>
+        <v>0.2023608833551407</v>
       </c>
       <c r="C94" s="1">
         <v>234</v>
@@ -6426,7 +6426,7 @@
         <v>107</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2006521224975586</v>
+        <v>0.2006312906742096</v>
       </c>
       <c r="C95" s="1">
         <v>232</v>
@@ -6452,7 +6452,7 @@
         <v>108</v>
       </c>
       <c r="B96" s="2">
-        <v>0.197192594408989</v>
+        <v>0.1971721351146698</v>
       </c>
       <c r="C96" s="1">
         <v>228</v>
@@ -6478,7 +6478,7 @@
         <v>24</v>
       </c>
       <c r="B97" s="2">
-        <v>0.197192594408989</v>
+        <v>0.1971721351146698</v>
       </c>
       <c r="C97" s="1">
         <v>228</v>
@@ -6504,7 +6504,7 @@
         <v>109</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1920033246278763</v>
+        <v>0.1919834017753601</v>
       </c>
       <c r="C98" s="1">
         <v>222</v>
@@ -6530,7 +6530,7 @@
         <v>110</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1902735680341721</v>
+        <v>0.190253809094429</v>
       </c>
       <c r="C99" s="1">
         <v>220</v>
@@ -6556,7 +6556,7 @@
         <v>111</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1902735680341721</v>
+        <v>0.190253809094429</v>
       </c>
       <c r="C100" s="1">
         <v>220</v>
@@ -6582,7 +6582,7 @@
         <v>112</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1764354854822159</v>
+        <v>0.1764171719551086</v>
       </c>
       <c r="C101" s="1">
         <v>204</v>
@@ -6608,7 +6608,7 @@
         <v>37</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1660569310188294</v>
+        <v>0.1660396903753281</v>
       </c>
       <c r="C102" s="1">
         <v>192</v>
@@ -6634,7 +6634,7 @@
         <v>113</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1625974029302597</v>
+        <v>0.1625805348157883</v>
       </c>
       <c r="C103" s="1">
         <v>188</v>
@@ -6660,7 +6660,7 @@
         <v>114</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1608676463365555</v>
+        <v>0.1608509570360184</v>
       </c>
       <c r="C104" s="1">
         <v>186</v>
@@ -6686,7 +6686,7 @@
         <v>115</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1522188484668732</v>
+        <v>0.1522030532360077</v>
       </c>
       <c r="C105" s="1">
         <v>176</v>
@@ -6712,7 +6712,7 @@
         <v>116</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1522188484668732</v>
+        <v>0.1522030532360077</v>
       </c>
       <c r="C106" s="1">
         <v>176</v>
@@ -6738,7 +6738,7 @@
         <v>42</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1487593352794647</v>
+        <v>0.1487438976764679</v>
       </c>
       <c r="C107" s="1">
         <v>172</v>
@@ -6764,7 +6764,7 @@
         <v>117</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1366510093212128</v>
+        <v>0.1366368383169174</v>
       </c>
       <c r="C108" s="1">
         <v>158</v>
@@ -6790,7 +6790,7 @@
         <v>118</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1331914961338043</v>
+        <v>0.1331776678562164</v>
       </c>
       <c r="C109" s="1">
         <v>154</v>
@@ -6816,7 +6816,7 @@
         <v>119</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1314617395401001</v>
+        <v>0.1314480900764465</v>
       </c>
       <c r="C110" s="1">
         <v>152</v>
@@ -6842,7 +6842,7 @@
         <v>120</v>
       </c>
       <c r="B111" s="2">
-        <v>0.124542698264122</v>
+        <v>0.1245297715067864</v>
       </c>
       <c r="C111" s="1">
         <v>144</v>
@@ -6868,7 +6868,7 @@
         <v>39</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1228129342198372</v>
+        <v>0.1228001937270165</v>
       </c>
       <c r="C112" s="1">
         <v>142</v>
@@ -6894,7 +6894,7 @@
         <v>121</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1193534135818481</v>
+        <v>0.1193410307168961</v>
       </c>
       <c r="C113" s="1">
         <v>138</v>
@@ -6920,7 +6920,7 @@
         <v>26</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1176236569881439</v>
+        <v>0.1176114529371262</v>
       </c>
       <c r="C114" s="1">
         <v>136</v>
@@ -6946,7 +6946,7 @@
         <v>122</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1107046157121658</v>
+        <v>0.1106931269168854</v>
       </c>
       <c r="C115" s="1">
         <v>128</v>
@@ -6972,7 +6972,7 @@
         <v>123</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1107046157121658</v>
+        <v>0.1106931269168854</v>
       </c>
       <c r="C116" s="1">
         <v>128</v>
@@ -6998,7 +6998,7 @@
         <v>124</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1089748591184616</v>
+        <v>0.1089635491371155</v>
       </c>
       <c r="C117" s="1">
         <v>126</v>
@@ -7024,7 +7024,7 @@
         <v>41</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1089748591184616</v>
+        <v>0.1089635491371155</v>
       </c>
       <c r="C118" s="1">
         <v>126</v>
@@ -7050,7 +7050,7 @@
         <v>23</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1037855818867683</v>
+        <v>0.1037748083472252</v>
       </c>
       <c r="C119" s="1">
         <v>120</v>
@@ -7076,7 +7076,7 @@
         <v>125</v>
       </c>
       <c r="B120" s="2">
-        <v>0.09859629720449448</v>
+        <v>0.0985860675573349</v>
       </c>
       <c r="C120" s="1">
         <v>114</v>
@@ -7102,7 +7102,7 @@
         <v>126</v>
       </c>
       <c r="B121" s="2">
-        <v>0.09686654061079025</v>
+        <v>0.096856489777565</v>
       </c>
       <c r="C121" s="1">
         <v>112</v>
@@ -7128,7 +7128,7 @@
         <v>127</v>
       </c>
       <c r="B122" s="2">
-        <v>0.09686654061079025</v>
+        <v>0.096856489777565</v>
       </c>
       <c r="C122" s="1">
         <v>112</v>
@@ -7154,7 +7154,7 @@
         <v>128</v>
       </c>
       <c r="B123" s="2">
-        <v>0.09686654061079025</v>
+        <v>0.096856489777565</v>
       </c>
       <c r="C123" s="1">
         <v>112</v>
@@ -7180,7 +7180,7 @@
         <v>129</v>
       </c>
       <c r="B124" s="2">
-        <v>0.09513678401708603</v>
+        <v>0.09512690454721451</v>
       </c>
       <c r="C124" s="1">
         <v>110</v>
@@ -7206,7 +7206,7 @@
         <v>130</v>
       </c>
       <c r="B125" s="2">
-        <v>0.09513678401708603</v>
+        <v>0.09512690454721451</v>
       </c>
       <c r="C125" s="1">
         <v>110</v>
@@ -7232,7 +7232,7 @@
         <v>12</v>
       </c>
       <c r="B126" s="2">
-        <v>0.09340701997280121</v>
+        <v>0.09339732676744461</v>
       </c>
       <c r="C126" s="1">
         <v>108</v>
@@ -7258,7 +7258,7 @@
         <v>131</v>
       </c>
       <c r="B127" s="2">
-        <v>0.0847582221031189</v>
+        <v>0.08474943041801453</v>
       </c>
       <c r="C127" s="1">
         <v>98</v>
@@ -7284,7 +7284,7 @@
         <v>132</v>
       </c>
       <c r="B128" s="2">
-        <v>0.0847582221031189</v>
+        <v>0.08474943041801453</v>
       </c>
       <c r="C128" s="1">
         <v>98</v>
@@ -7310,7 +7310,7 @@
         <v>133</v>
       </c>
       <c r="B129" s="2">
-        <v>0.07956894487142563</v>
+        <v>0.07956068962812424</v>
       </c>
       <c r="C129" s="1">
         <v>92</v>
@@ -7336,7 +7336,7 @@
         <v>134</v>
       </c>
       <c r="B130" s="2">
-        <v>0.07956894487142563</v>
+        <v>0.07956068962812424</v>
       </c>
       <c r="C130" s="1">
         <v>92</v>
@@ -7362,7 +7362,7 @@
         <v>135</v>
       </c>
       <c r="B131" s="2">
-        <v>0.07437966763973236</v>
+        <v>0.07437194883823395</v>
       </c>
       <c r="C131" s="1">
         <v>86</v>
@@ -7388,7 +7388,7 @@
         <v>136</v>
       </c>
       <c r="B132" s="2">
-        <v>0.07264990359544754</v>
+        <v>0.07264236360788345</v>
       </c>
       <c r="C132" s="1">
         <v>84</v>
@@ -7414,7 +7414,7 @@
         <v>137</v>
       </c>
       <c r="B133" s="2">
-        <v>0.07264990359544754</v>
+        <v>0.07264236360788345</v>
       </c>
       <c r="C133" s="1">
         <v>84</v>
@@ -7440,7 +7440,7 @@
         <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07264990359544754</v>
+        <v>0.07264236360788345</v>
       </c>
       <c r="C134" s="1">
         <v>84</v>
@@ -7466,7 +7466,7 @@
         <v>52</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07264990359544754</v>
+        <v>0.07264236360788345</v>
       </c>
       <c r="C135" s="1">
         <v>84</v>
@@ -7492,7 +7492,7 @@
         <v>139</v>
       </c>
       <c r="B136" s="2">
-        <v>0.07092014700174332</v>
+        <v>0.07091278582811356</v>
       </c>
       <c r="C136" s="1">
         <v>82</v>
@@ -7518,7 +7518,7 @@
         <v>140</v>
       </c>
       <c r="B137" s="2">
-        <v>0.06746062636375427</v>
+        <v>0.06745362281799316</v>
       </c>
       <c r="C137" s="1">
         <v>78</v>
@@ -7544,7 +7544,7 @@
         <v>33</v>
       </c>
       <c r="B138" s="2">
-        <v>0.06573086977005005</v>
+        <v>0.06572404503822327</v>
       </c>
       <c r="C138" s="1">
         <v>76</v>
@@ -7570,7 +7570,7 @@
         <v>141</v>
       </c>
       <c r="B139" s="2">
-        <v>0.05708206817507744</v>
+        <v>0.05707614496350288</v>
       </c>
       <c r="C139" s="1">
         <v>66</v>
@@ -7596,7 +7596,7 @@
         <v>142</v>
       </c>
       <c r="B140" s="2">
-        <v>0.05189279094338417</v>
+        <v>0.0518874041736126</v>
       </c>
       <c r="C140" s="1">
         <v>60</v>
@@ -7622,7 +7622,7 @@
         <v>143</v>
       </c>
       <c r="B141" s="2">
-        <v>0.05189279094338417</v>
+        <v>0.0518874041736126</v>
       </c>
       <c r="C141" s="1">
         <v>60</v>
@@ -7648,7 +7648,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="2">
-        <v>0.05189279094338417</v>
+        <v>0.0518874041736126</v>
       </c>
       <c r="C142" s="1">
         <v>60</v>
@@ -7674,7 +7674,7 @@
         <v>145</v>
       </c>
       <c r="B143" s="2">
-        <v>0.05016303062438965</v>
+        <v>0.0501578226685524</v>
       </c>
       <c r="C143" s="1">
         <v>58</v>
@@ -7700,7 +7700,7 @@
         <v>146</v>
       </c>
       <c r="B144" s="2">
-        <v>0.0467035099864006</v>
+        <v>0.04669866338372231</v>
       </c>
       <c r="C144" s="1">
         <v>54</v>
@@ -7726,7 +7726,7 @@
         <v>45</v>
       </c>
       <c r="B145" s="2">
-        <v>0.0467035099864006</v>
+        <v>0.04669866338372231</v>
       </c>
       <c r="C145" s="1">
         <v>54</v>
@@ -7752,7 +7752,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="2">
-        <v>0.04497374966740608</v>
+        <v>0.04496908560395241</v>
       </c>
       <c r="C146" s="1">
         <v>52</v>
@@ -7778,7 +7778,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04151423275470734</v>
+        <v>0.04150992259383202</v>
       </c>
       <c r="C147" s="1">
         <v>48</v>
@@ -7804,7 +7804,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04151423275470734</v>
+        <v>0.04150992259383202</v>
       </c>
       <c r="C148" s="1">
         <v>48</v>
@@ -7830,7 +7830,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04151423275470734</v>
+        <v>0.04150992259383202</v>
       </c>
       <c r="C149" s="1">
         <v>48</v>
@@ -7856,7 +7856,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="2">
-        <v>0.03805471211671829</v>
+        <v>0.03805076330900192</v>
       </c>
       <c r="C150" s="1">
         <v>44</v>
@@ -7882,7 +7882,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="2">
-        <v>0.03805471211671829</v>
+        <v>0.03805076330900192</v>
       </c>
       <c r="C151" s="1">
         <v>44</v>
@@ -7908,7 +7908,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="2">
-        <v>0.03805471211671829</v>
+        <v>0.03805076330900192</v>
       </c>
       <c r="C152" s="1">
         <v>44</v>
@@ -7934,7 +7934,7 @@
         <v>48</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03805471211671829</v>
+        <v>0.03805076330900192</v>
       </c>
       <c r="C153" s="1">
         <v>44</v>
@@ -7960,7 +7960,7 @@
         <v>154</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03805471211671829</v>
+        <v>0.03805076330900192</v>
       </c>
       <c r="C154" s="1">
         <v>44</v>
@@ -7986,7 +7986,7 @@
         <v>155</v>
       </c>
       <c r="B155" s="2">
-        <v>0.03805471211671829</v>
+        <v>0.03805076330900192</v>
       </c>
       <c r="C155" s="1">
         <v>44</v>
@@ -8012,7 +8012,7 @@
         <v>156</v>
       </c>
       <c r="B156" s="2">
-        <v>0.03459519147872925</v>
+        <v>0.03459160402417183</v>
       </c>
       <c r="C156" s="1">
         <v>40</v>
@@ -8038,7 +8038,7 @@
         <v>157</v>
       </c>
       <c r="B157" s="2">
-        <v>0.03286543488502502</v>
+        <v>0.03286202251911163</v>
       </c>
       <c r="C157" s="1">
         <v>38</v>
@@ -8064,7 +8064,7 @@
         <v>158</v>
       </c>
       <c r="B158" s="2">
-        <v>0.0311356745660305</v>
+        <v>0.03113244287669659</v>
       </c>
       <c r="C158" s="1">
         <v>36</v>
@@ -8090,7 +8090,7 @@
         <v>159</v>
       </c>
       <c r="B159" s="2">
-        <v>0.0311356745660305</v>
+        <v>0.03113244287669659</v>
       </c>
       <c r="C159" s="1">
         <v>36</v>
@@ -8116,7 +8116,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="2">
-        <v>0.0311356745660305</v>
+        <v>0.03113244287669659</v>
       </c>
       <c r="C160" s="1">
         <v>36</v>
@@ -8142,7 +8142,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.0311356745660305</v>
+        <v>0.03113244287669659</v>
       </c>
       <c r="C161" s="1">
         <v>36</v>
@@ -8168,7 +8168,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.02767615392804146</v>
+        <v>0.02767328172922134</v>
       </c>
       <c r="C162" s="1">
         <v>32</v>
@@ -8194,7 +8194,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.02767615392804146</v>
+        <v>0.02767328172922134</v>
       </c>
       <c r="C163" s="1">
         <v>32</v>
@@ -8220,7 +8220,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.02767615392804146</v>
+        <v>0.02767328172922134</v>
       </c>
       <c r="C164" s="1">
         <v>32</v>
@@ -8246,7 +8246,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.02767615392804146</v>
+        <v>0.02767328172922134</v>
       </c>
       <c r="C165" s="1">
         <v>32</v>
@@ -8272,7 +8272,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.02594639547169209</v>
+        <v>0.0259437020868063</v>
       </c>
       <c r="C166" s="1">
         <v>30</v>
@@ -8298,7 +8298,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.02594639547169209</v>
+        <v>0.0259437020868063</v>
       </c>
       <c r="C167" s="1">
         <v>30</v>
@@ -8324,7 +8324,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.02248687483370304</v>
+        <v>0.0224845428019762</v>
       </c>
       <c r="C168" s="1">
         <v>26</v>
@@ -8350,7 +8350,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.02075711637735367</v>
+        <v>0.02075496129691601</v>
       </c>
       <c r="C169" s="1">
         <v>24</v>
@@ -8376,7 +8376,7 @@
         <v>47</v>
       </c>
       <c r="B170" s="2">
-        <v>0.01383807696402073</v>
+        <v>0.01383664086461067</v>
       </c>
       <c r="C170" s="1">
         <v>16</v>
@@ -8402,7 +8402,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="2">
-        <v>0.006919038482010365</v>
+        <v>0.006918320432305336</v>
       </c>
       <c r="C171" s="1">
         <v>8</v>
@@ -8428,7 +8428,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2">
-        <v>0.006919038482010365</v>
+        <v>0.006918320432305336</v>
       </c>
       <c r="C172" s="1">
         <v>8</v>
@@ -8454,7 +8454,7 @@
         <v>46</v>
       </c>
       <c r="B173" s="2">
-        <v>0.003459519241005182</v>
+        <v>0.003459160216152668</v>
       </c>
       <c r="C173" s="1">
         <v>4</v>
@@ -8480,7 +8480,7 @@
         <v>172</v>
       </c>
       <c r="B174" s="2">
-        <v>0.003459519241005182</v>
+        <v>0.003459160216152668</v>
       </c>
       <c r="C174" s="1">
         <v>4</v>
@@ -8506,7 +8506,7 @@
         <v>173</v>
       </c>
       <c r="B175" s="2">
-        <v>0.003459519241005182</v>
+        <v>0.003459160216152668</v>
       </c>
       <c r="C175" s="1">
         <v>4</v>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="186">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -125,186 +125,195 @@
     <t>stm32g4xx_hal_flash.o</t>
   </si>
   <si>
+    <t>dev_eeprom.o</t>
+  </si>
+  <si>
+    <t>thread_management.o</t>
+  </si>
+  <si>
+    <t>jm_host_commun.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal.o</t>
+  </si>
+  <si>
+    <t>port.o</t>
+  </si>
+  <si>
+    <t>calib_level6_system.o</t>
+  </si>
+  <si>
+    <t>calib_level1_driver.o</t>
+  </si>
+  <si>
+    <t>mc_w.l</t>
+  </si>
+  <si>
+    <t>led_manager.o</t>
+  </si>
+  <si>
+    <t>calib_level4_torque.o</t>
+  </si>
+  <si>
+    <t>stdout.o</t>
+  </si>
+  <si>
+    <t>errno.o</t>
+  </si>
+  <si>
+    <t>system_stm32g4xx.o</t>
+  </si>
+  <si>
+    <t>system_state.o</t>
+  </si>
+  <si>
+    <t>jm_proto_uart.o</t>
+  </si>
+  <si>
+    <t>calib_hw.o</t>
+  </si>
+  <si>
+    <t>app_freertos.o</t>
+  </si>
+  <si>
+    <t>motor_pid_load.o</t>
+  </si>
+  <si>
+    <t>motor_info.o</t>
+  </si>
+  <si>
+    <t>jm_proto.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_adc.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_uart.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_tim.o</t>
+  </si>
+  <si>
+    <t>motor_param.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_fdcan.o</t>
+  </si>
+  <si>
+    <t>m_wm.l</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_adc_ex.o</t>
+  </si>
+  <si>
+    <t>arm_cortexM4lf_math.lib</t>
+  </si>
+  <si>
+    <t>printfa.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_i2c.o</t>
+  </si>
+  <si>
+    <t>arm_common_tables.o</t>
+  </si>
+  <si>
+    <t>jm_proto_can.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_rcc.o</t>
+  </si>
+  <si>
+    <t>motion_param.o</t>
+  </si>
+  <si>
+    <t>queue.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_spi.o</t>
+  </si>
+  <si>
+    <t>mf_w.l</t>
+  </si>
+  <si>
+    <t>motor_pid_autotune.o</t>
+  </si>
+  <si>
+    <t>dev_motor_phase_current.o</t>
+  </si>
+  <si>
+    <t>ctrl_transition.o</t>
+  </si>
+  <si>
+    <t>calib_config_runtime.o</t>
+  </si>
+  <si>
+    <t>foc_core.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_dma.o</t>
+  </si>
+  <si>
+    <t>current_loop.o</t>
+  </si>
+  <si>
+    <t>dev_mt6835.o</t>
+  </si>
+  <si>
+    <t>multiturn_counter.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_rcc_ex.o</t>
+  </si>
+  <si>
+    <t>motor_profile.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_tim_ex.o</t>
+  </si>
+  <si>
+    <t>atan2f.o</t>
+  </si>
+  <si>
+    <t>dev_half_bridge.o</t>
+  </si>
+  <si>
+    <t>cascade_control.o</t>
+  </si>
+  <si>
+    <t>foc_decoupling.o</t>
+  </si>
+  <si>
+    <t>crc16.o</t>
+  </si>
+  <si>
+    <t>motor_control.o</t>
+  </si>
+  <si>
+    <t>calib_ac_injection.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_flash_ex.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_gpio.o</t>
+  </si>
+  <si>
+    <t>ctrl_transition_mgr.o</t>
+  </si>
+  <si>
     <t>dev_motor.o</t>
   </si>
   <si>
-    <t>thread_management.o</t>
-  </si>
-  <si>
-    <t>jm_host_commun.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal.o</t>
-  </si>
-  <si>
-    <t>port.o</t>
-  </si>
-  <si>
-    <t>calib_level6_system.o</t>
-  </si>
-  <si>
-    <t>calib_level1_driver.o</t>
-  </si>
-  <si>
-    <t>mc_w.l</t>
-  </si>
-  <si>
-    <t>led_manager.o</t>
-  </si>
-  <si>
-    <t>calib_level4_torque.o</t>
-  </si>
-  <si>
-    <t>stdout.o</t>
-  </si>
-  <si>
-    <t>errno.o</t>
-  </si>
-  <si>
-    <t>system_stm32g4xx.o</t>
-  </si>
-  <si>
-    <t>system_state.o</t>
-  </si>
-  <si>
-    <t>jm_proto_uart.o</t>
-  </si>
-  <si>
-    <t>calib_hw.o</t>
-  </si>
-  <si>
-    <t>app_freertos.o</t>
-  </si>
-  <si>
-    <t>motor_pid_load.o</t>
-  </si>
-  <si>
-    <t>motor_info.o</t>
-  </si>
-  <si>
-    <t>jm_proto.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_adc.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_uart.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_tim.o</t>
-  </si>
-  <si>
-    <t>motor_param.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_fdcan.o</t>
-  </si>
-  <si>
-    <t>m_wm.l</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_adc_ex.o</t>
-  </si>
-  <si>
-    <t>arm_cortexM4lf_math.lib</t>
-  </si>
-  <si>
-    <t>printfa.o</t>
-  </si>
-  <si>
-    <t>arm_common_tables.o</t>
-  </si>
-  <si>
-    <t>jm_proto_can.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_rcc.o</t>
-  </si>
-  <si>
-    <t>motion_param.o</t>
-  </si>
-  <si>
-    <t>queue.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_spi.o</t>
-  </si>
-  <si>
-    <t>mf_w.l</t>
-  </si>
-  <si>
-    <t>motor_pid_autotune.o</t>
-  </si>
-  <si>
-    <t>dev_motor_phase_current.o</t>
-  </si>
-  <si>
-    <t>ctrl_transition.o</t>
-  </si>
-  <si>
-    <t>calib_config_runtime.o</t>
-  </si>
-  <si>
-    <t>foc_core.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_dma.o</t>
-  </si>
-  <si>
-    <t>current_loop.o</t>
-  </si>
-  <si>
-    <t>dev_mt6835.o</t>
-  </si>
-  <si>
-    <t>multiturn_counter.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_rcc_ex.o</t>
-  </si>
-  <si>
-    <t>motor_profile.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_tim_ex.o</t>
-  </si>
-  <si>
-    <t>atan2f.o</t>
-  </si>
-  <si>
-    <t>dev_half_bridge.o</t>
-  </si>
-  <si>
-    <t>cascade_control.o</t>
-  </si>
-  <si>
-    <t>foc_decoupling.o</t>
-  </si>
-  <si>
-    <t>crc16.o</t>
-  </si>
-  <si>
-    <t>motor_control.o</t>
-  </si>
-  <si>
-    <t>calib_ac_injection.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_flash_ex.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_gpio.o</t>
-  </si>
-  <si>
-    <t>ctrl_transition_mgr.o</t>
-  </si>
-  <si>
     <t>motor_info_calib.o</t>
   </si>
   <si>
     <t>drv_tim.o</t>
   </si>
   <si>
+    <t>dev_config.o</t>
+  </si>
+  <si>
     <t>sinf.o</t>
   </si>
   <si>
@@ -314,9 +323,6 @@
     <t>pid_core.o</t>
   </si>
   <si>
-    <t>dev_config.o</t>
-  </si>
-  <si>
     <t>cosf.o</t>
   </si>
   <si>
@@ -335,6 +341,9 @@
     <t>drv_adc.o</t>
   </si>
   <si>
+    <t>drv_i2c.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
@@ -353,9 +362,6 @@
     <t>drv_spi.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_i2c.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_it.o</t>
   </si>
   <si>
@@ -389,6 +395,9 @@
     <t>motor_mode_mit.o</t>
   </si>
   <si>
+    <t>user_interface.o</t>
+  </si>
+  <si>
     <t>motor_mode_velocity.o</t>
   </si>
   <si>
@@ -405,9 +414,6 @@
   </si>
   <si>
     <t>fepilogue.o</t>
-  </si>
-  <si>
-    <t>user_interface.o</t>
   </si>
   <si>
     <t>uldiv.o</t>
@@ -656,9 +662,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$176</c:f>
+              <c:f>ram_percent!$A$3:$A$178</c:f>
               <c:strCache>
-                <c:ptCount val="174"/>
+                <c:ptCount val="176"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -765,7 +771,7 @@
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>dev_motor.o</c:v>
+                  <c:v>dev_eeprom.o</c:v>
                 </c:pt>
                 <c:pt idx="36">
                   <c:v>thread_management.o</c:v>
@@ -818,7 +824,7 @@
                 <c:pt idx="52">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="173">
+                <c:pt idx="175">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -826,170 +832,170 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$176</c:f>
+              <c:f>ram_percent!$B$3:$B$178</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="174"/>
+                <c:ptCount val="176"/>
                 <c:pt idx="0">
-                  <c:v>35.27819061279297</c:v>
+                  <c:v>35.26833724975586</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.111813545227051</c:v>
+                  <c:v>9.109268188476563</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.802355766296387</c:v>
+                  <c:v>8.799897193908691</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.802355766296387</c:v>
+                  <c:v>8.799897193908691</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.063095092773438</c:v>
+                  <c:v>8.060843467712402</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.495734214782715</c:v>
+                  <c:v>4.503072261810303</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.392581462860107</c:v>
+                  <c:v>4.391354560852051</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.61034107208252</c:v>
+                  <c:v>3.609332799911499</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.541572570800781</c:v>
+                  <c:v>3.540583610534668</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.21563196182251</c:v>
+                  <c:v>2.215013027191162</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.200588941574097</c:v>
+                  <c:v>2.199974298477173</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.538692951202393</c:v>
+                  <c:v>1.538263201713562</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8424128890037537</c:v>
+                  <c:v>0.8421776294708252</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.7650484442710877</c:v>
+                  <c:v>0.7648347616195679</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.7306642532348633</c:v>
+                  <c:v>0.7304601669311523</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.64470374584198</c:v>
+                  <c:v>0.6445236802101135</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.5759353637695313</c:v>
+                  <c:v>0.5757744908332825</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.489974856376648</c:v>
+                  <c:v>0.4898380041122437</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.4813787937164307</c:v>
+                  <c:v>0.4812443554401398</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.4383985698223114</c:v>
+                  <c:v>0.4382761120796204</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.4298025071620941</c:v>
+                  <c:v>0.4296824634075165</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.283669650554657</c:v>
+                  <c:v>0.2835904359817505</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2750736176967621</c:v>
+                  <c:v>0.2749967873096466</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2149012535810471</c:v>
+                  <c:v>0.2148412317037582</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1805170476436615</c:v>
+                  <c:v>0.1804666370153427</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1633249521255493</c:v>
+                  <c:v>0.163279339671135</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1547289043664932</c:v>
+                  <c:v>0.1546856909990311</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1547289043664932</c:v>
+                  <c:v>0.1546856909990311</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1547289043664932</c:v>
+                  <c:v>0.1546856909990311</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1461328566074371</c:v>
+                  <c:v>0.1460920423269272</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.137536808848381</c:v>
+                  <c:v>0.1374983936548233</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.0945565477013588</c:v>
+                  <c:v>0.0945301428437233</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.0859604999423027</c:v>
+                  <c:v>0.08593649417161942</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.07736445218324661</c:v>
+                  <c:v>0.07734284549951553</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.06876840442419052</c:v>
+                  <c:v>0.06874919682741165</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.04942728951573372</c:v>
+                  <c:v>0.06874919682741165</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.04298024997115135</c:v>
+                  <c:v>0.04296824708580971</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.04298024997115135</c:v>
+                  <c:v>0.04296824708580971</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.02578815072774887</c:v>
+                  <c:v>0.0257809478789568</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.02578815072774887</c:v>
+                  <c:v>0.0257809478789568</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.02578815072774887</c:v>
+                  <c:v>0.0257809478789568</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.02578815072774887</c:v>
+                  <c:v>0.0257809478789568</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01719210110604763</c:v>
+                  <c:v>0.01718729920685291</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01719210110604763</c:v>
+                  <c:v>0.01718729920685291</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01719210110604763</c:v>
+                  <c:v>0.01718729920685291</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.008596050553023815</c:v>
+                  <c:v>0.008593649603426457</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.008596050553023815</c:v>
+                  <c:v>0.008593649603426457</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.008596050553023815</c:v>
+                  <c:v>0.008593649603426457</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.008596050553023815</c:v>
+                  <c:v>0.008593649603426457</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.008596050553023815</c:v>
+                  <c:v>0.008593649603426457</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.008596050553023815</c:v>
+                  <c:v>0.008593649603426457</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.008596050553023815</c:v>
+                  <c:v>0.008593649603426457</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.006447037681937218</c:v>
-                </c:pt>
-                <c:pt idx="173">
+                  <c:v>0.006445236969739199</c:v>
+                </c:pt>
+                <c:pt idx="175">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1057,9 +1063,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$176</c:f>
+              <c:f>flash_percent!$A$3:$A$178</c:f>
               <c:strCache>
-                <c:ptCount val="174"/>
+                <c:ptCount val="176"/>
                 <c:pt idx="0">
                   <c:v>motor_info.o</c:v>
                 </c:pt>
@@ -1106,58 +1112,58 @@
                   <c:v>printfa.o</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>stm32g4xx_hal_i2c.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>dev_commun_can.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>arm_common_tables.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>jm_proto_can.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>motion_param.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>dev_power_monitor.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>motor_observer.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>motor_pid_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>stm32g4xx_hal_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>motor_pid_autotune.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>dev_motor_phase_current.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>ctrl_transition.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>calib_config_runtime.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>jm_host_commun.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>foc_core.o</c:v>
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>drv_can.o</c:v>
@@ -1172,414 +1178,420 @@
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>foc_core.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>drv_flash_g4.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
+                  <c:v>motor_info_storage.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="44">
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>multiturn_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="46">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="47">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="48">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="49">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="50">
                   <c:v>motor_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="51">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="52">
                   <c:v>atan2f.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="53">
+                  <c:v>dev_eeprom.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>dev_half_bridge.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="55">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="56">
                   <c:v>cascade_control.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
-                  <c:v>motor_info_storage.o</c:v>
-                </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="57">
                   <c:v>foc_decoupling.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="58">
                   <c:v>crc16.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="59">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="60">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="61">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="62">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="63">
                   <c:v>calib_ac_injection.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="64">
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="65">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="66">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="67">
                   <c:v>stm32g4xx_hal_flash_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="68">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="69">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="70">
+                  <c:v>ctrl_transition_mgr.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
-                  <c:v>ctrl_transition_mgr.o</c:v>
-                </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="72">
                   <c:v>motor_info_calib.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="73">
                   <c:v>led_manager.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="74">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="75">
+                  <c:v>dev_config.o</c:v>
+                </c:pt>
+                <c:pt idx="76">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="77">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="78">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="79">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="80">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="81">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
-                  <c:v>dev_config.o</c:v>
-                </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="82">
                   <c:v>cosf.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="83">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="84">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="85">
                   <c:v>cmsis_os.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="86">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="87">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="88">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="89">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="90">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="91">
                   <c:v>drv_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="92">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="93">
+                  <c:v>drv_i2c.o</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="95">
                   <c:v>drv_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="96">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="97">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="98">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="99">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="100">
                   <c:v>drv_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
-                  <c:v>stm32g4xx_hal_i2c.o</c:v>
-                </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="101">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="102">
                   <c:v>stm32g4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="103">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="104">
                   <c:v>fmodf.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="105">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="106">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="107">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="108">
                   <c:v>roundf.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="109">
                   <c:v>arm_cos_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="110">
                   <c:v>arm_sin_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="111">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="112">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="113">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="114">
                   <c:v>thread_period.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="115">
                   <c:v>motor_mode_mit.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="116">
+                  <c:v>user_interface.o</c:v>
+                </c:pt>
+                <c:pt idx="117">
                   <c:v>motor_mode_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="118">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="119">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="120">
                   <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="121">
                   <c:v>floorf.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="122">
                   <c:v>motor_mode_position.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="123">
                   <c:v>motor_mode_current.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="124">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
-                  <c:v>user_interface.o</c:v>
-                </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="125">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="126">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="127">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="128">
                   <c:v>motor_mode_test_sweep.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="129">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="130">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="131">
                   <c:v>motor_mode_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="132">
                   <c:v>motor_mode_profile_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="133">
                   <c:v>assert_report.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="134">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="135">
                   <c:v>frem.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="136">
                   <c:v>motor_mode_profile_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="137">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="138">
                   <c:v>motor_mode_duty.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="139">
                   <c:v>frnd.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="140">
                   <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="141">
                   <c:v>control_irq.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="142">
                   <c:v>sqrtf.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="143">
                   <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="144">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="145">
                   <c:v>utils.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="146">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="147">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="146">
+                <c:pt idx="148">
                   <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="149">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="148">
+                <c:pt idx="150">
                   <c:v>funder.o</c:v>
                 </c:pt>
-                <c:pt idx="149">
+                <c:pt idx="151">
                   <c:v>thread_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="150">
+                <c:pt idx="152">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="151">
+                <c:pt idx="153">
                   <c:v>motor_mode_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="152">
+                <c:pt idx="154">
                   <c:v>motor_mode_hold.o</c:v>
                 </c:pt>
-                <c:pt idx="153">
+                <c:pt idx="155">
                   <c:v>drv_delay.o</c:v>
                 </c:pt>
-                <c:pt idx="154">
+                <c:pt idx="156">
                   <c:v>fpclassifyf.o</c:v>
                 </c:pt>
-                <c:pt idx="155">
+                <c:pt idx="157">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="156">
+                <c:pt idx="158">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="157">
+                <c:pt idx="159">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="158">
+                <c:pt idx="160">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="159">
+                <c:pt idx="161">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="160">
+                <c:pt idx="162">
                   <c:v>thread_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="161">
+                <c:pt idx="163">
                   <c:v>thread_display.o</c:v>
                 </c:pt>
-                <c:pt idx="162">
+                <c:pt idx="164">
                   <c:v>thread_control.o</c:v>
                 </c:pt>
-                <c:pt idx="163">
+                <c:pt idx="165">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="164">
+                <c:pt idx="166">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="165">
+                <c:pt idx="167">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="166">
+                <c:pt idx="168">
                   <c:v>strncpy.o</c:v>
                 </c:pt>
-                <c:pt idx="167">
+                <c:pt idx="169">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="168">
+                <c:pt idx="170">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="169">
+                <c:pt idx="171">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="170">
+                <c:pt idx="172">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="171">
+                <c:pt idx="173">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="172">
+                <c:pt idx="174">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="173">
+                <c:pt idx="175">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1587,530 +1599,536 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$176</c:f>
+              <c:f>flash_percent!$B$3:$B$178</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="174"/>
+                <c:ptCount val="176"/>
                 <c:pt idx="0">
-                  <c:v>4.102564334869385</c:v>
+                  <c:v>3.990268468856812</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.920958280563355</c:v>
+                  <c:v>3.867361545562744</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.675357818603516</c:v>
+                  <c:v>3.577772378921509</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.229126214981079</c:v>
+                  <c:v>3.166960000991821</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.182427406311035</c:v>
+                  <c:v>3.097929954528809</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.865914344787598</c:v>
+                  <c:v>2.789820671081543</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.75868034362793</c:v>
+                  <c:v>2.685433864593506</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.485406637191773</c:v>
+                  <c:v>2.419415950775147</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.464651823043823</c:v>
+                  <c:v>2.399212121963501</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.075496196746826</c:v>
+                  <c:v>2.020389080047607</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.053011655807495</c:v>
+                  <c:v>1.998501539230347</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.033986330032349</c:v>
+                  <c:v>1.979981303215027</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.030527114868164</c:v>
+                  <c:v>1.976613998413086</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.02706789970398</c:v>
+                  <c:v>1.973246693611145</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.918104410171509</c:v>
+                  <c:v>1.867176294326782</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.850650787353516</c:v>
+                  <c:v>1.808248281478882</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.774549245834351</c:v>
+                  <c:v>1.80151355266571</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.681151866912842</c:v>
+                  <c:v>1.727432727813721</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.643101096153259</c:v>
+                  <c:v>1.636515140533447</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.561810851097107</c:v>
+                  <c:v>1.599474668502808</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.40441906452179</c:v>
+                  <c:v>1.520342826843262</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.39058244228363</c:v>
+                  <c:v>1.367129921913147</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.387123227119446</c:v>
+                  <c:v>1.353660702705383</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.364638686180115</c:v>
+                  <c:v>1.350293397903442</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.243568181991577</c:v>
+                  <c:v>1.328405857086182</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.205517411231995</c:v>
+                  <c:v>1.210549831390381</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.139793276786804</c:v>
+                  <c:v>1.173509359359741</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.079257965087891</c:v>
+                  <c:v>1.109530329704285</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.055043935775757</c:v>
+                  <c:v>1.050602316856384</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.037748098373413</c:v>
+                  <c:v>1.027031064033508</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.034288883209229</c:v>
+                  <c:v>1.010194540023804</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.027370572090149</c:v>
+                  <c:v>1.006827235221863</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.011804342269898</c:v>
+                  <c:v>1.000092625617981</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9945085644721985</c:v>
+                  <c:v>0.9681031107902527</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9357028603553772</c:v>
+                  <c:v>0.9108587503433228</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8890041708946228</c:v>
+                  <c:v>0.8654000163078308</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8743027448654175</c:v>
+                  <c:v>0.8510888814926148</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8613309264183044</c:v>
+                  <c:v>0.8418287634849548</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.8388463854789734</c:v>
+                  <c:v>0.8384614586830139</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.8301984667778015</c:v>
+                  <c:v>0.8165739178657532</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.8267393112182617</c:v>
+                  <c:v>0.8081556558609009</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7402603030204773</c:v>
+                  <c:v>0.80478835105896</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7350715398788452</c:v>
+                  <c:v>0.7862681150436401</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7195053696632385</c:v>
+                  <c:v>0.7172381281852722</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.7091278433799744</c:v>
+                  <c:v>0.7155544757843018</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.6901024580001831</c:v>
+                  <c:v>0.7004015445709229</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6779954433441162</c:v>
+                  <c:v>0.6902996301651001</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6537812948226929</c:v>
+                  <c:v>0.6717793941497803</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6330263614654541</c:v>
+                  <c:v>0.6599937677383423</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.6226488351821899</c:v>
+                  <c:v>0.6364225745201111</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.5915164351463318</c:v>
+                  <c:v>0.6094840168952942</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5569248199462891</c:v>
+                  <c:v>0.6061167120933533</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5361698269844055</c:v>
+                  <c:v>0.5758109092712402</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.534440279006958</c:v>
+                  <c:v>0.5539233684539795</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5050374269485474</c:v>
+                  <c:v>0.5421377420425415</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.4946599304676056</c:v>
+                  <c:v>0.5219338536262512</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.480823278427124</c:v>
+                  <c:v>0.5202502012252808</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4739049673080444</c:v>
+                  <c:v>0.4815260767936707</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4496908485889435</c:v>
+                  <c:v>0.4680567979812622</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4427725076675415</c:v>
+                  <c:v>0.4613221883773804</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4393133521080017</c:v>
+                  <c:v>0.4377509653568268</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4358541965484619</c:v>
+                  <c:v>0.4310163259506226</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.434124618768692</c:v>
+                  <c:v>0.4276490211486816</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.434124618768692</c:v>
+                  <c:v>0.4242817163467407</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.4306654632091522</c:v>
+                  <c:v>0.4225980639457703</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.411640077829361</c:v>
+                  <c:v>0.4225980639457703</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.4047217667102814</c:v>
+                  <c:v>0.419230729341507</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3943442702293396</c:v>
+                  <c:v>0.4007104933261871</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3934794962406158</c:v>
+                  <c:v>0.3939758837223053</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3856963813304901</c:v>
+                  <c:v>0.3838739395141602</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3684005737304688</c:v>
+                  <c:v>0.3754556477069855</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3684005737304688</c:v>
+                  <c:v>0.3636700510978699</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3545639216899872</c:v>
+                  <c:v>0.3586190640926361</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3528343439102173</c:v>
+                  <c:v>0.3586190640926361</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3459160327911377</c:v>
+                  <c:v>0.3451498150825501</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3459160327911377</c:v>
+                  <c:v>0.3451498150825501</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.3217019140720367</c:v>
+                  <c:v>0.3434661328792572</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.3165131807327271</c:v>
+                  <c:v>0.3367315232753754</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.2974877953529358</c:v>
+                  <c:v>0.3367315232753754</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.2966229915618897</c:v>
+                  <c:v>0.3131603002548218</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.2905694544315338</c:v>
+                  <c:v>0.3081093430519104</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.2888398766517639</c:v>
+                  <c:v>0.2895891070365906</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.287110298871994</c:v>
+                  <c:v>0.2828544676303864</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2801919877529144</c:v>
+                  <c:v>0.2811708152294159</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2663553357124329</c:v>
+                  <c:v>0.2794871628284454</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2525187134742737</c:v>
+                  <c:v>0.2727525234222412</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2352229058742523</c:v>
+                  <c:v>0.2592832744121552</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2352229058742523</c:v>
+                  <c:v>0.2458140105009079</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.217927098274231</c:v>
+                  <c:v>0.2289774268865585</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2127383649349213</c:v>
+                  <c:v>0.2289774268865585</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2092791944742203</c:v>
+                  <c:v>0.2121408581733704</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2023608833551407</c:v>
+                  <c:v>0.2070898860692978</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2006312906742096</c:v>
+                  <c:v>0.2037225663661957</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.1971721351146698</c:v>
+                  <c:v>0.2020389139652252</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1971721351146698</c:v>
+                  <c:v>0.1969879418611527</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1919834017753601</c:v>
+                  <c:v>0.195304274559021</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.190253809094429</c:v>
+                  <c:v>0.1919369697570801</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.190253809094429</c:v>
+                  <c:v>0.1919369697570801</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1764171719551086</c:v>
+                  <c:v>0.1868859976530075</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1660396903753281</c:v>
+                  <c:v>0.1852023303508759</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1625805348157883</c:v>
+                  <c:v>0.1852023303508759</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1608509570360184</c:v>
+                  <c:v>0.1616311222314835</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1522030532360077</c:v>
+                  <c:v>0.1582638174295425</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1522030532360077</c:v>
+                  <c:v>0.1565801501274109</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1487438976764679</c:v>
+                  <c:v>0.1481618732213974</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1366368383169174</c:v>
+                  <c:v>0.1481618732213974</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1331776678562164</c:v>
+                  <c:v>0.1447945535182953</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1314480900764465</c:v>
+                  <c:v>0.1330089420080185</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1245297715067864</c:v>
+                  <c:v>0.1296416372060776</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1228001937270165</c:v>
+                  <c:v>0.1279579699039459</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1193410307168961</c:v>
+                  <c:v>0.1212233453989029</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1176114529371262</c:v>
+                  <c:v>0.1195396855473518</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1106931269168854</c:v>
+                  <c:v>0.1161723732948303</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1106931269168854</c:v>
+                  <c:v>0.1144887134432793</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1089635491371155</c:v>
+                  <c:v>0.1077540814876556</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1089635491371155</c:v>
+                  <c:v>0.1077540814876556</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1037748083472252</c:v>
+                  <c:v>0.1060704290866852</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.0985860675573349</c:v>
+                  <c:v>0.1060704290866852</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.096856489777565</c:v>
+                  <c:v>0.1060704290866852</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.096856489777565</c:v>
+                  <c:v>0.1010194569826126</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.096856489777565</c:v>
+                  <c:v>0.09596848487854004</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.09512690454721451</c:v>
+                  <c:v>0.09428482502698898</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.09512690454721451</c:v>
+                  <c:v>0.09428482502698898</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.09339732676744461</c:v>
+                  <c:v>0.09428482502698898</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.08474943041801453</c:v>
+                  <c:v>0.09260116517543793</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.08474943041801453</c:v>
+                  <c:v>0.09091751277446747</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.07956068962812424</c:v>
+                  <c:v>0.08249922096729279</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.07956068962812424</c:v>
+                  <c:v>0.08249922096729279</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.07437194883823395</c:v>
+                  <c:v>0.07744824886322022</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.07264236360788345</c:v>
+                  <c:v>0.07744824886322022</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.07264236360788345</c:v>
+                  <c:v>0.07239727675914764</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07264236360788345</c:v>
+                  <c:v>0.07071361690759659</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07264236360788345</c:v>
+                  <c:v>0.07071361690759659</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.07091278582811356</c:v>
+                  <c:v>0.07071361690759659</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06745362281799316</c:v>
+                  <c:v>0.07071361690759659</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06572404503822327</c:v>
+                  <c:v>0.06902995705604553</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.05707614496350288</c:v>
+                  <c:v>0.06566264480352402</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.0518874041736126</c:v>
+                  <c:v>0.06397898495197296</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.0518874041736126</c:v>
+                  <c:v>0.05556070059537888</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.0518874041736126</c:v>
+                  <c:v>0.05050972849130631</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.0501578226685524</c:v>
+                  <c:v>0.05050972849130631</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.04669866338372231</c:v>
+                  <c:v>0.05050972849130631</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.04669866338372231</c:v>
+                  <c:v>0.04882606863975525</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.04496908560395241</c:v>
+                  <c:v>0.04545875638723373</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04150992259383202</c:v>
+                  <c:v>0.04545875638723373</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04150992259383202</c:v>
+                  <c:v>0.04377509653568268</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04150992259383202</c:v>
+                  <c:v>0.04040778055787087</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.03805076330900192</c:v>
+                  <c:v>0.04040778055787087</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.03805076330900192</c:v>
+                  <c:v>0.04040778055787087</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.03805076330900192</c:v>
+                  <c:v>0.03704046830534935</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03805076330900192</c:v>
+                  <c:v>0.03704046830534935</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03805076330900192</c:v>
+                  <c:v>0.03704046830534935</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03805076330900192</c:v>
+                  <c:v>0.03704046830534935</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03459160402417183</c:v>
+                  <c:v>0.03704046830534935</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.03286202251911163</c:v>
+                  <c:v>0.03704046830534935</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.03113244287669659</c:v>
+                  <c:v>0.03367315232753754</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.03113244287669659</c:v>
+                  <c:v>0.03198949247598648</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.03113244287669659</c:v>
+                  <c:v>0.03030583634972572</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.03113244287669659</c:v>
+                  <c:v>0.03030583634972572</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.02767328172922134</c:v>
+                  <c:v>0.03030583634972572</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.02767328172922134</c:v>
+                  <c:v>0.03030583634972572</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.02767328172922134</c:v>
+                  <c:v>0.02693852037191391</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.02767328172922134</c:v>
+                  <c:v>0.02693852037191391</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.0259437020868063</c:v>
+                  <c:v>0.02693852037191391</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.0259437020868063</c:v>
+                  <c:v>0.02693852037191391</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.0224845428019762</c:v>
+                  <c:v>0.02525486424565315</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02075496129691601</c:v>
+                  <c:v>0.02525486424565315</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.01383664086461067</c:v>
+                  <c:v>0.02188754826784134</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.006918320432305336</c:v>
+                  <c:v>0.02020389027893543</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.006918320432305336</c:v>
+                  <c:v>0.01346926018595696</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.003459160216152668</c:v>
+                  <c:v>0.006734630092978478</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.003459160216152668</c:v>
+                  <c:v>0.006734630092978478</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.003459160216152668</c:v>
+                  <c:v>0.003367315046489239</c:v>
                 </c:pt>
                 <c:pt idx="173">
+                  <c:v>0.003367315046489239</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.003367315046489239</c:v>
+                </c:pt>
+                <c:pt idx="175">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2215,8 +2233,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H176" totalsRowCount="1">
-  <autoFilter ref="A2:H175"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H178" totalsRowCount="1">
+  <autoFilter ref="A2:H177"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -2232,8 +2250,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H176" totalsRowCount="1">
-  <autoFilter ref="A2:H175"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H178" totalsRowCount="1">
+  <autoFilter ref="A2:H177"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2533,7 +2551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2546,28 +2564,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2575,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>35.27819061279297</v>
+        <v>35.26833724975586</v>
       </c>
       <c r="C3" s="1">
         <v>16416</v>
@@ -2601,7 +2619,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>9.111813545227051</v>
+        <v>9.109268188476563</v>
       </c>
       <c r="C4" s="1">
         <v>4240</v>
@@ -2627,7 +2645,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>8.802355766296387</v>
+        <v>8.799897193908691</v>
       </c>
       <c r="C5" s="1">
         <v>4096</v>
@@ -2653,7 +2671,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>8.802355766296387</v>
+        <v>8.799897193908691</v>
       </c>
       <c r="C6" s="1">
         <v>4096</v>
@@ -2679,7 +2697,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>8.063095092773438</v>
+        <v>8.060843467712402</v>
       </c>
       <c r="C7" s="1">
         <v>3752</v>
@@ -2705,16 +2723,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.495734214782715</v>
+        <v>4.503072261810303</v>
       </c>
       <c r="C8" s="1">
-        <v>2092</v>
+        <v>2096</v>
       </c>
       <c r="D8" s="1">
-        <v>584</v>
+        <v>934</v>
       </c>
       <c r="E8" s="1">
-        <v>568</v>
+        <v>918</v>
       </c>
       <c r="F8" s="1">
         <v>16</v>
@@ -2723,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>2092</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2731,7 +2749,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>4.392581462860107</v>
+        <v>4.391354560852051</v>
       </c>
       <c r="C9" s="1">
         <v>2044</v>
@@ -2757,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>3.61034107208252</v>
+        <v>3.609332799911499</v>
       </c>
       <c r="C10" s="1">
         <v>1680</v>
@@ -2783,7 +2801,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.541572570800781</v>
+        <v>3.540583610534668</v>
       </c>
       <c r="C11" s="1">
         <v>1648</v>
@@ -2809,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>2.21563196182251</v>
+        <v>2.215013027191162</v>
       </c>
       <c r="C12" s="1">
         <v>1031</v>
@@ -2835,7 +2853,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>2.200588941574097</v>
+        <v>2.199974298477173</v>
       </c>
       <c r="C13" s="1">
         <v>1024</v>
@@ -2861,7 +2879,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>1.538692951202393</v>
+        <v>1.538263201713562</v>
       </c>
       <c r="C14" s="1">
         <v>716</v>
@@ -2887,16 +2905,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.8424128890037537</v>
+        <v>0.8421776294708252</v>
       </c>
       <c r="C15" s="1">
         <v>392</v>
       </c>
       <c r="D15" s="1">
-        <v>4534</v>
+        <v>4594</v>
       </c>
       <c r="E15" s="1">
-        <v>4042</v>
+        <v>4102</v>
       </c>
       <c r="F15" s="1">
         <v>464</v>
@@ -2913,7 +2931,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.7650484442710877</v>
+        <v>0.7648347616195679</v>
       </c>
       <c r="C16" s="1">
         <v>356</v>
@@ -2939,7 +2957,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.7306642532348633</v>
+        <v>0.7304601669311523</v>
       </c>
       <c r="C17" s="1">
         <v>340</v>
@@ -2965,7 +2983,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.64470374584198</v>
+        <v>0.6445236802101135</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -2991,7 +3009,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.5759353637695313</v>
+        <v>0.5757744908332825</v>
       </c>
       <c r="C19" s="1">
         <v>268</v>
@@ -3017,7 +3035,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.489974856376648</v>
+        <v>0.4898380041122437</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -3043,7 +3061,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.4813787937164307</v>
+        <v>0.4812443554401398</v>
       </c>
       <c r="C21" s="1">
         <v>224</v>
@@ -3069,7 +3087,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.4383985698223114</v>
+        <v>0.4382761120796204</v>
       </c>
       <c r="C22" s="1">
         <v>204</v>
@@ -3095,7 +3113,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.4298025071620941</v>
+        <v>0.4296824634075165</v>
       </c>
       <c r="C23" s="1">
         <v>200</v>
@@ -3121,7 +3139,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.283669650554657</v>
+        <v>0.2835904359817505</v>
       </c>
       <c r="C24" s="1">
         <v>132</v>
@@ -3147,7 +3165,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2750736176967621</v>
+        <v>0.2749967873096466</v>
       </c>
       <c r="C25" s="1">
         <v>128</v>
@@ -3173,7 +3191,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2149012535810471</v>
+        <v>0.2148412317037582</v>
       </c>
       <c r="C26" s="1">
         <v>100</v>
@@ -3199,7 +3217,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1805170476436615</v>
+        <v>0.1804666370153427</v>
       </c>
       <c r="C27" s="1">
         <v>84</v>
@@ -3225,7 +3243,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1633249521255493</v>
+        <v>0.163279339671135</v>
       </c>
       <c r="C28" s="1">
         <v>76</v>
@@ -3251,7 +3269,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1547289043664932</v>
+        <v>0.1546856909990311</v>
       </c>
       <c r="C29" s="1">
         <v>72</v>
@@ -3277,7 +3295,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1547289043664932</v>
+        <v>0.1546856909990311</v>
       </c>
       <c r="C30" s="1">
         <v>72</v>
@@ -3303,7 +3321,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1547289043664932</v>
+        <v>0.1546856909990311</v>
       </c>
       <c r="C31" s="1">
         <v>72</v>
@@ -3329,7 +3347,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1461328566074371</v>
+        <v>0.1460920423269272</v>
       </c>
       <c r="C32" s="1">
         <v>68</v>
@@ -3355,7 +3373,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.137536808848381</v>
+        <v>0.1374983936548233</v>
       </c>
       <c r="C33" s="1">
         <v>64</v>
@@ -3381,7 +3399,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0945565477013588</v>
+        <v>0.0945301428437233</v>
       </c>
       <c r="C34" s="1">
         <v>44</v>
@@ -3407,7 +3425,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.0859604999423027</v>
+        <v>0.08593649417161942</v>
       </c>
       <c r="C35" s="1">
         <v>40</v>
@@ -3433,7 +3451,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.07736445218324661</v>
+        <v>0.07734284549951553</v>
       </c>
       <c r="C36" s="1">
         <v>36</v>
@@ -3459,7 +3477,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.06876840442419052</v>
+        <v>0.06874919682741165</v>
       </c>
       <c r="C37" s="1">
         <v>32</v>
@@ -3485,25 +3503,25 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.04942728951573372</v>
+        <v>0.06874919682741165</v>
       </c>
       <c r="C38" s="1">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D38" s="1">
-        <v>455</v>
+        <v>658</v>
       </c>
       <c r="E38" s="1">
-        <v>420</v>
+        <v>658</v>
       </c>
       <c r="F38" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3511,7 +3529,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.04298024997115135</v>
+        <v>0.04296824708580971</v>
       </c>
       <c r="C39" s="1">
         <v>20</v>
@@ -3537,7 +3555,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.04298024997115135</v>
+        <v>0.04296824708580971</v>
       </c>
       <c r="C40" s="1">
         <v>20</v>
@@ -3563,7 +3581,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.02578815072774887</v>
+        <v>0.0257809478789568</v>
       </c>
       <c r="C41" s="1">
         <v>12</v>
@@ -3589,7 +3607,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.02578815072774887</v>
+        <v>0.0257809478789568</v>
       </c>
       <c r="C42" s="1">
         <v>12</v>
@@ -3615,7 +3633,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.02578815072774887</v>
+        <v>0.0257809478789568</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
@@ -3641,7 +3659,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.02578815072774887</v>
+        <v>0.0257809478789568</v>
       </c>
       <c r="C44" s="1">
         <v>12</v>
@@ -3667,7 +3685,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01719210110604763</v>
+        <v>0.01718729920685291</v>
       </c>
       <c r="C45" s="1">
         <v>8</v>
@@ -3693,7 +3711,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01719210110604763</v>
+        <v>0.01718729920685291</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
@@ -3719,7 +3737,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01719210110604763</v>
+        <v>0.01718729920685291</v>
       </c>
       <c r="C47" s="1">
         <v>8</v>
@@ -3745,7 +3763,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.008596050553023815</v>
+        <v>0.008593649603426457</v>
       </c>
       <c r="C48" s="1">
         <v>4</v>
@@ -3771,7 +3789,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.008596050553023815</v>
+        <v>0.008593649603426457</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
@@ -3797,7 +3815,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.008596050553023815</v>
+        <v>0.008593649603426457</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
@@ -3823,7 +3841,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.008596050553023815</v>
+        <v>0.008593649603426457</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
@@ -3849,7 +3867,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.008596050553023815</v>
+        <v>0.008593649603426457</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
@@ -3875,7 +3893,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.008596050553023815</v>
+        <v>0.008593649603426457</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -3901,7 +3919,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.008596050553023815</v>
+        <v>0.008593649603426457</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
@@ -3927,7 +3945,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.006447037681937218</v>
+        <v>0.006445236969739199</v>
       </c>
       <c r="C55" s="1">
         <v>3</v>
@@ -3948,35 +3966,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
-      <c r="A176" t="s">
-        <v>175</v>
-      </c>
-      <c r="B176">
+    <row r="178" spans="1:8">
+      <c r="A178" t="s">
+        <v>177</v>
+      </c>
+      <c r="B178">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C176">
+      <c r="C178">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D176">
+      <c r="D178">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E176">
+      <c r="E178">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F176">
+      <c r="F178">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G176">
+      <c r="G178">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H176">
+      <c r="H178">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -3992,7 +4010,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -4005,28 +4023,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" t="s">
         <v>183</v>
       </c>
-      <c r="C2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G2" t="s">
-        <v>181</v>
-      </c>
       <c r="H2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4034,19 +4052,19 @@
         <v>54</v>
       </c>
       <c r="B3" s="2">
-        <v>4.102564334869385</v>
+        <v>3.990268468856812</v>
       </c>
       <c r="C3" s="1">
-        <v>4744</v>
+        <v>4740</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3" s="1">
-        <v>3132</v>
+        <v>3112</v>
       </c>
       <c r="F3" s="1">
-        <v>1612</v>
+        <v>1628</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -4060,16 +4078,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>3.920958280563355</v>
+        <v>3.867361545562744</v>
       </c>
       <c r="C4" s="1">
-        <v>4534</v>
+        <v>4594</v>
       </c>
       <c r="D4" s="1">
         <v>392</v>
       </c>
       <c r="E4" s="1">
-        <v>4042</v>
+        <v>4102</v>
       </c>
       <c r="F4" s="1">
         <v>464</v>
@@ -4086,7 +4104,7 @@
         <v>22</v>
       </c>
       <c r="B5" s="2">
-        <v>3.675357818603516</v>
+        <v>3.577772378921509</v>
       </c>
       <c r="C5" s="1">
         <v>4250</v>
@@ -4112,16 +4130,16 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>3.229126214981079</v>
+        <v>3.166960000991821</v>
       </c>
       <c r="C6" s="1">
-        <v>3734</v>
+        <v>3762</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>3734</v>
+        <v>3762</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -4138,7 +4156,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>3.182427406311035</v>
+        <v>3.097929954528809</v>
       </c>
       <c r="C7" s="1">
         <v>3680</v>
@@ -4164,7 +4182,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>2.865914344787598</v>
+        <v>2.789820671081543</v>
       </c>
       <c r="C8" s="1">
         <v>3314</v>
@@ -4190,7 +4208,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>2.75868034362793</v>
+        <v>2.685433864593506</v>
       </c>
       <c r="C9" s="1">
         <v>3190</v>
@@ -4216,7 +4234,7 @@
         <v>43</v>
       </c>
       <c r="B10" s="2">
-        <v>2.485406637191773</v>
+        <v>2.419415950775147</v>
       </c>
       <c r="C10" s="1">
         <v>2874</v>
@@ -4242,7 +4260,7 @@
         <v>59</v>
       </c>
       <c r="B11" s="2">
-        <v>2.464651823043823</v>
+        <v>2.399212121963501</v>
       </c>
       <c r="C11" s="1">
         <v>2850</v>
@@ -4268,7 +4286,7 @@
         <v>60</v>
       </c>
       <c r="B12" s="2">
-        <v>2.075496196746826</v>
+        <v>2.020389080047607</v>
       </c>
       <c r="C12" s="1">
         <v>2400</v>
@@ -4294,7 +4312,7 @@
         <v>61</v>
       </c>
       <c r="B13" s="2">
-        <v>2.053011655807495</v>
+        <v>1.998501539230347</v>
       </c>
       <c r="C13" s="1">
         <v>2374</v>
@@ -4320,7 +4338,7 @@
         <v>62</v>
       </c>
       <c r="B14" s="2">
-        <v>2.033986330032349</v>
+        <v>1.979981303215027</v>
       </c>
       <c r="C14" s="1">
         <v>2352</v>
@@ -4346,7 +4364,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="2">
-        <v>2.030527114868164</v>
+        <v>1.976613998413086</v>
       </c>
       <c r="C15" s="1">
         <v>2348</v>
@@ -4372,7 +4390,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2">
-        <v>2.02706789970398</v>
+        <v>1.973246693611145</v>
       </c>
       <c r="C16" s="1">
         <v>2344</v>
@@ -4398,7 +4416,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="2">
-        <v>1.918104410171509</v>
+        <v>1.867176294326782</v>
       </c>
       <c r="C17" s="1">
         <v>2218</v>
@@ -4421,54 +4439,54 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2">
-        <v>1.850650787353516</v>
+        <v>1.808248281478882</v>
       </c>
       <c r="C18" s="1">
-        <v>2140</v>
+        <v>2148</v>
       </c>
       <c r="D18" s="1">
-        <v>3752</v>
+        <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>2136</v>
+        <v>2148</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1">
-        <v>3748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2">
-        <v>1.774549245834351</v>
+        <v>1.80151355266571</v>
       </c>
       <c r="C19" s="1">
-        <v>2052</v>
+        <v>2140</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>3752</v>
       </c>
       <c r="E19" s="1">
-        <v>0</v>
+        <v>2136</v>
       </c>
       <c r="F19" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4476,19 +4494,19 @@
         <v>66</v>
       </c>
       <c r="B20" s="2">
-        <v>1.681151866912842</v>
+        <v>1.727432727813721</v>
       </c>
       <c r="C20" s="1">
-        <v>1944</v>
+        <v>2052</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>1930</v>
+        <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>14</v>
+        <v>2052</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -4502,19 +4520,19 @@
         <v>67</v>
       </c>
       <c r="B21" s="2">
-        <v>1.643101096153259</v>
+        <v>1.636515140533447</v>
       </c>
       <c r="C21" s="1">
-        <v>1900</v>
+        <v>1944</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>1900</v>
+        <v>1930</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -4528,16 +4546,16 @@
         <v>68</v>
       </c>
       <c r="B22" s="2">
-        <v>1.561810851097107</v>
+        <v>1.599474668502808</v>
       </c>
       <c r="C22" s="1">
-        <v>1806</v>
+        <v>1900</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>1806</v>
+        <v>1900</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -4551,25 +4569,25 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B23" s="2">
-        <v>1.40441906452179</v>
+        <v>1.520342826843262</v>
       </c>
       <c r="C23" s="1">
-        <v>1624</v>
+        <v>1806</v>
       </c>
       <c r="D23" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>1284</v>
+        <v>1806</v>
       </c>
       <c r="F23" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -4577,25 +4595,25 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2">
-        <v>1.39058244228363</v>
+        <v>1.367129921913147</v>
       </c>
       <c r="C24" s="1">
-        <v>1608</v>
+        <v>1624</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E24" s="1">
-        <v>1608</v>
+        <v>1284</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -4603,19 +4621,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="B25" s="2">
-        <v>1.387123227119446</v>
+        <v>1.353660702705383</v>
       </c>
       <c r="C25" s="1">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="D25" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>1604</v>
+        <v>1608</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -4624,85 +4642,85 @@
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2">
-        <v>1.364638686180115</v>
+        <v>1.350293397903442</v>
       </c>
       <c r="C26" s="1">
-        <v>1578</v>
+        <v>1604</v>
       </c>
       <c r="D26" s="1">
-        <v>4240</v>
+        <v>268</v>
       </c>
       <c r="E26" s="1">
-        <v>1530</v>
+        <v>1604</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>4192</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B27" s="2">
-        <v>1.243568181991577</v>
+        <v>1.328405857086182</v>
       </c>
       <c r="C27" s="1">
-        <v>1438</v>
+        <v>1578</v>
       </c>
       <c r="D27" s="1">
-        <v>356</v>
+        <v>4240</v>
       </c>
       <c r="E27" s="1">
-        <v>1082</v>
+        <v>1530</v>
       </c>
       <c r="F27" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H27" s="1">
-        <v>352</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="B28" s="2">
-        <v>1.205517411231995</v>
+        <v>1.210549831390381</v>
       </c>
       <c r="C28" s="1">
-        <v>1394</v>
+        <v>1438</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E28" s="1">
-        <v>1394</v>
+        <v>1082</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4710,16 +4728,16 @@
         <v>71</v>
       </c>
       <c r="B29" s="2">
-        <v>1.139793276786804</v>
+        <v>1.173509359359741</v>
       </c>
       <c r="C29" s="1">
-        <v>1318</v>
+        <v>1394</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>1318</v>
+        <v>1394</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -4736,16 +4754,16 @@
         <v>72</v>
       </c>
       <c r="B30" s="2">
-        <v>1.079257965087891</v>
+        <v>1.109530329704285</v>
       </c>
       <c r="C30" s="1">
-        <v>1248</v>
+        <v>1318</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>1248</v>
+        <v>1318</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -4762,16 +4780,16 @@
         <v>73</v>
       </c>
       <c r="B31" s="2">
-        <v>1.055043935775757</v>
+        <v>1.050602316856384</v>
       </c>
       <c r="C31" s="1">
-        <v>1220</v>
+        <v>1248</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>1220</v>
+        <v>1248</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -4788,16 +4806,16 @@
         <v>74</v>
       </c>
       <c r="B32" s="2">
-        <v>1.037748098373413</v>
+        <v>1.027031064033508</v>
       </c>
       <c r="C32" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -4814,19 +4832,19 @@
         <v>75</v>
       </c>
       <c r="B33" s="2">
-        <v>1.034288883209229</v>
+        <v>1.010194540023804</v>
       </c>
       <c r="C33" s="1">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>1168</v>
+        <v>1200</v>
       </c>
       <c r="F33" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
@@ -4837,25 +4855,25 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B34" s="2">
-        <v>1.027370572090149</v>
+        <v>1.006827235221863</v>
       </c>
       <c r="C34" s="1">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="D34" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E34" s="1">
         <v>1168</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G34" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
@@ -4863,25 +4881,25 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2">
-        <v>1.011804342269898</v>
+        <v>1.000092625617981</v>
       </c>
       <c r="C35" s="1">
-        <v>1170</v>
+        <v>1188</v>
       </c>
       <c r="D35" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -4892,7 +4910,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9945085644721985</v>
+        <v>0.9681031107902527</v>
       </c>
       <c r="C36" s="1">
         <v>1150</v>
@@ -4918,7 +4936,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9357028603553772</v>
+        <v>0.9108587503433228</v>
       </c>
       <c r="C37" s="1">
         <v>1082</v>
@@ -4944,7 +4962,7 @@
         <v>28</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8890041708946228</v>
+        <v>0.8654000163078308</v>
       </c>
       <c r="C38" s="1">
         <v>1028</v>
@@ -4970,7 +4988,7 @@
         <v>53</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8743027448654175</v>
+        <v>0.8510888814926148</v>
       </c>
       <c r="C39" s="1">
         <v>1011</v>
@@ -4993,19 +5011,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="B40" s="2">
-        <v>0.8613309264183044</v>
+        <v>0.8418287634849548</v>
       </c>
       <c r="C40" s="1">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D40" s="1">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -5014,76 +5032,76 @@
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>1680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B41" s="2">
-        <v>0.8388463854789734</v>
+        <v>0.8384614586830139</v>
       </c>
       <c r="C41" s="1">
-        <v>970</v>
+        <v>996</v>
       </c>
       <c r="D41" s="1">
-        <v>72</v>
+        <v>1680</v>
       </c>
       <c r="E41" s="1">
-        <v>958</v>
+        <v>996</v>
       </c>
       <c r="F41" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>72</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2">
-        <v>0.8301984667778015</v>
+        <v>0.8165739178657532</v>
       </c>
       <c r="C42" s="1">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="D42" s="1">
-        <v>4096</v>
+        <v>72</v>
       </c>
       <c r="E42" s="1">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>4096</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="B43" s="2">
-        <v>0.8267393112182617</v>
+        <v>0.8081556558609009</v>
       </c>
       <c r="C43" s="1">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="E43" s="1">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -5092,7 +5110,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5100,16 +5118,16 @@
         <v>78</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7402603030204773</v>
+        <v>0.80478835105896</v>
       </c>
       <c r="C44" s="1">
-        <v>856</v>
+        <v>956</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>856</v>
+        <v>956</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -5123,45 +5141,45 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7350715398788452</v>
+        <v>0.7862681150436401</v>
       </c>
       <c r="C45" s="1">
-        <v>850</v>
+        <v>934</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
       <c r="E45" s="1">
-        <v>850</v>
+        <v>918</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7195053696632385</v>
+        <v>0.7172381281852722</v>
       </c>
       <c r="C46" s="1">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -5175,51 +5193,51 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7091278433799744</v>
+        <v>0.7155544757843018</v>
       </c>
       <c r="C47" s="1">
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="D47" s="1">
-        <v>1648</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>816</v>
+        <v>850</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>1644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="B48" s="2">
-        <v>0.6901024580001831</v>
+        <v>0.7004015445709229</v>
       </c>
       <c r="C48" s="1">
-        <v>798</v>
+        <v>832</v>
       </c>
       <c r="D48" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>786</v>
+        <v>832</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -5227,54 +5245,54 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>81</v>
+        <v>9</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6779954433441162</v>
+        <v>0.6902996301651001</v>
       </c>
       <c r="C49" s="1">
-        <v>784</v>
+        <v>820</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>1648</v>
       </c>
       <c r="E49" s="1">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6537812948226929</v>
+        <v>0.6717793941497803</v>
       </c>
       <c r="C50" s="1">
-        <v>756</v>
+        <v>798</v>
       </c>
       <c r="D50" s="1">
-        <v>228</v>
+        <v>12</v>
       </c>
       <c r="E50" s="1">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H50" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -5282,16 +5300,16 @@
         <v>82</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6330263614654541</v>
+        <v>0.6599937677383423</v>
       </c>
       <c r="C51" s="1">
-        <v>732</v>
+        <v>784</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>732</v>
+        <v>784</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -5305,19 +5323,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6226488351821899</v>
+        <v>0.6364225745201111</v>
       </c>
       <c r="C52" s="1">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="D52" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E52" s="1">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -5326,24 +5344,24 @@
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B53" s="2">
-        <v>0.5915164351463318</v>
+        <v>0.6094840168952942</v>
       </c>
       <c r="C53" s="1">
-        <v>684</v>
+        <v>724</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>684</v>
+        <v>724</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -5357,19 +5375,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B54" s="2">
-        <v>0.5569248199462891</v>
+        <v>0.6061167120933533</v>
       </c>
       <c r="C54" s="1">
-        <v>644</v>
+        <v>720</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>644</v>
+        <v>720</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -5383,45 +5401,45 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5361698269844055</v>
+        <v>0.5758109092712402</v>
       </c>
       <c r="C55" s="1">
-        <v>620</v>
+        <v>684</v>
       </c>
       <c r="D55" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>564</v>
+        <v>684</v>
       </c>
       <c r="F55" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B56" s="2">
-        <v>0.534440279006958</v>
+        <v>0.5539233684539795</v>
       </c>
       <c r="C56" s="1">
-        <v>618</v>
+        <v>658</v>
       </c>
       <c r="D56" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E56" s="1">
-        <v>618</v>
+        <v>658</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -5430,79 +5448,79 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5050374269485474</v>
+        <v>0.5421377420425415</v>
       </c>
       <c r="C57" s="1">
-        <v>584</v>
+        <v>644</v>
       </c>
       <c r="D57" s="1">
-        <v>2092</v>
+        <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>568</v>
+        <v>644</v>
       </c>
       <c r="F57" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>2092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="B58" s="2">
-        <v>0.4946599304676056</v>
+        <v>0.5219338536262512</v>
       </c>
       <c r="C58" s="1">
-        <v>572</v>
+        <v>620</v>
       </c>
       <c r="D58" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
       <c r="E58" s="1">
         <v>564</v>
       </c>
       <c r="F58" s="1">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B59" s="2">
-        <v>0.480823278427124</v>
+        <v>0.5202502012252808</v>
       </c>
       <c r="C59" s="1">
-        <v>556</v>
+        <v>618</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>44</v>
+        <v>618</v>
       </c>
       <c r="F59" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
@@ -5513,28 +5531,28 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4739049673080444</v>
+        <v>0.4815260767936707</v>
       </c>
       <c r="C60" s="1">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="D60" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="F60" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -5542,19 +5560,19 @@
         <v>89</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4496908485889435</v>
+        <v>0.4680567979812622</v>
       </c>
       <c r="C61" s="1">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>328</v>
+        <v>44</v>
       </c>
       <c r="F61" s="1">
-        <v>192</v>
+        <v>512</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
@@ -5565,129 +5583,129 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4427725076675415</v>
+        <v>0.4613221883773804</v>
       </c>
       <c r="C62" s="1">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="D62" s="1">
-        <v>16416</v>
+        <v>204</v>
       </c>
       <c r="E62" s="1">
-        <v>480</v>
+        <v>548</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>16384</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4393133521080017</v>
+        <v>0.4377509653568268</v>
       </c>
       <c r="C63" s="1">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="D63" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>36</v>
+        <v>328</v>
       </c>
       <c r="F63" s="1">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4358541965484619</v>
+        <v>0.4310163259506226</v>
       </c>
       <c r="C64" s="1">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="D64" s="1">
-        <v>0</v>
+        <v>16416</v>
       </c>
       <c r="E64" s="1">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H64" s="1">
-        <v>0</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B65" s="2">
-        <v>0.434124618768692</v>
+        <v>0.4276490211486816</v>
       </c>
       <c r="C65" s="1">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D65" s="1">
-        <v>4096</v>
+        <v>1024</v>
       </c>
       <c r="E65" s="1">
-        <v>502</v>
+        <v>36</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>4096</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="B66" s="2">
-        <v>0.434124618768692</v>
+        <v>0.4242817163467407</v>
       </c>
       <c r="C66" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D66" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H66" s="1">
         <v>0</v>
@@ -5695,19 +5713,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>0.4306654632091522</v>
+        <v>0.4225980639457703</v>
       </c>
       <c r="C67" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D67" s="1">
-        <v>1031</v>
+        <v>4096</v>
       </c>
       <c r="E67" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -5716,30 +5734,30 @@
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>1031</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B68" s="2">
-        <v>0.411640077829361</v>
+        <v>0.4225980639457703</v>
       </c>
       <c r="C68" s="1">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E68" s="1">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -5747,19 +5765,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="B69" s="2">
-        <v>0.4047217667102814</v>
+        <v>0.419230729341507</v>
       </c>
       <c r="C69" s="1">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="E69" s="1">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -5768,30 +5786,30 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3943442702293396</v>
+        <v>0.4007104933261871</v>
       </c>
       <c r="C70" s="1">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="D70" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>424</v>
+        <v>476</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -5799,25 +5817,25 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3934794962406158</v>
+        <v>0.3939758837223053</v>
       </c>
       <c r="C71" s="1">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="D71" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="F71" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -5825,25 +5843,25 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3856963813304901</v>
+        <v>0.3838739395141602</v>
       </c>
       <c r="C72" s="1">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E72" s="1">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -5854,16 +5872,16 @@
         <v>94</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3684005737304688</v>
+        <v>0.3754556477069855</v>
       </c>
       <c r="C73" s="1">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -5877,25 +5895,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3684005737304688</v>
+        <v>0.3636700510978699</v>
       </c>
       <c r="C74" s="1">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D74" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F74" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G74" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -5903,22 +5921,22 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3545639216899872</v>
+        <v>0.3586190640926361</v>
       </c>
       <c r="C75" s="1">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>330</v>
+        <v>426</v>
       </c>
       <c r="F75" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
@@ -5929,25 +5947,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3528343439102173</v>
+        <v>0.3586190640926361</v>
       </c>
       <c r="C76" s="1">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="D76" s="1">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E76" s="1">
-        <v>344</v>
+        <v>418</v>
       </c>
       <c r="F76" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -5955,22 +5973,22 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3459160327911377</v>
+        <v>0.3451498150825501</v>
       </c>
       <c r="C77" s="1">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="F77" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
@@ -5981,51 +5999,51 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3459160327911377</v>
+        <v>0.3451498150825501</v>
       </c>
       <c r="C78" s="1">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D78" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="G78" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H78" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="B79" s="2">
-        <v>0.3217019140720367</v>
+        <v>0.3434661328792572</v>
       </c>
       <c r="C79" s="1">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="D79" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E79" s="1">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F79" s="1">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G79" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -6033,19 +6051,19 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B80" s="2">
-        <v>0.3165131807327271</v>
+        <v>0.3367315232753754</v>
       </c>
       <c r="C80" s="1">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="F80" s="1">
         <v>0</v>
@@ -6059,48 +6077,48 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B81" s="2">
-        <v>0.2974877953529358</v>
+        <v>0.3367315232753754</v>
       </c>
       <c r="C81" s="1">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="D81" s="1">
-        <v>340</v>
+        <v>72</v>
       </c>
       <c r="E81" s="1">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="F81" s="1">
         <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H81" s="1">
-        <v>340</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B82" s="2">
-        <v>0.2966229915618897</v>
+        <v>0.3131603002548218</v>
       </c>
       <c r="C82" s="1">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="F82" s="1">
-        <v>343</v>
+        <v>32</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -6111,19 +6129,19 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B83" s="2">
-        <v>0.2905694544315338</v>
+        <v>0.3081093430519104</v>
       </c>
       <c r="C83" s="1">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -6137,19 +6155,19 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="B84" s="2">
-        <v>0.2888398766517639</v>
+        <v>0.2895891070365906</v>
       </c>
       <c r="C84" s="1">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="D84" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E84" s="1">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
@@ -6158,24 +6176,24 @@
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="B85" s="2">
-        <v>0.287110298871994</v>
+        <v>0.2828544676303864</v>
       </c>
       <c r="C85" s="1">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D85" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
@@ -6184,24 +6202,24 @@
         <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2801919877529144</v>
+        <v>0.2811708152294159</v>
       </c>
       <c r="C86" s="1">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -6215,45 +6233,45 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2663553357124329</v>
+        <v>0.2794871628284454</v>
       </c>
       <c r="C87" s="1">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="D87" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E87" s="1">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="F87" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2525187134742737</v>
+        <v>0.2727525234222412</v>
       </c>
       <c r="C88" s="1">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="D88" s="1">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -6262,30 +6280,30 @@
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2352229058742523</v>
+        <v>0.2592832744121552</v>
       </c>
       <c r="C89" s="1">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="D89" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="F89" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G89" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H89" s="1">
         <v>0</v>
@@ -6293,19 +6311,19 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2352229058742523</v>
+        <v>0.2458140105009079</v>
       </c>
       <c r="C90" s="1">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="D90" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="E90" s="1">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -6314,53 +6332,53 @@
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B91" s="2">
-        <v>0.217927098274231</v>
+        <v>0.2289774268865585</v>
       </c>
       <c r="C91" s="1">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="D91" s="1">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="E91" s="1">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H91" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2127383649349213</v>
+        <v>0.2289774268865585</v>
       </c>
       <c r="C92" s="1">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>210</v>
+        <v>272</v>
       </c>
       <c r="F92" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G92" s="1">
         <v>0</v>
@@ -6371,19 +6389,19 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2092791944742203</v>
+        <v>0.2121408581733704</v>
       </c>
       <c r="C93" s="1">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="D93" s="1">
-        <v>224</v>
+        <v>84</v>
       </c>
       <c r="E93" s="1">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -6392,27 +6410,27 @@
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>224</v>
+        <v>84</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2023608833551407</v>
+        <v>0.2070898860692978</v>
       </c>
       <c r="C94" s="1">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="F94" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G94" s="1">
         <v>0</v>
@@ -6423,28 +6441,28 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2006312906742096</v>
+        <v>0.2037225663661957</v>
       </c>
       <c r="C95" s="1">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D95" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E95" s="1">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="F95" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G95" s="1">
         <v>0</v>
       </c>
       <c r="H95" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -6452,19 +6470,19 @@
         <v>108</v>
       </c>
       <c r="B96" s="2">
-        <v>0.1971721351146698</v>
+        <v>0.2020389139652252</v>
       </c>
       <c r="C96" s="1">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F96" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G96" s="1">
         <v>0</v>
@@ -6475,19 +6493,19 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1971721351146698</v>
+        <v>0.1969879418611527</v>
       </c>
       <c r="C97" s="1">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D97" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -6496,27 +6514,27 @@
         <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1919834017753601</v>
+        <v>0.195304274559021</v>
       </c>
       <c r="C98" s="1">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="F98" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G98" s="1">
         <v>0</v>
@@ -6527,19 +6545,19 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B99" s="2">
-        <v>0.190253809094429</v>
+        <v>0.1919369697570801</v>
       </c>
       <c r="C99" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F99" s="1">
         <v>0</v>
@@ -6553,28 +6571,28 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="B100" s="2">
-        <v>0.190253809094429</v>
+        <v>0.1919369697570801</v>
       </c>
       <c r="C100" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D100" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="1">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="F100" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G100" s="1">
         <v>0</v>
       </c>
       <c r="H100" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -6582,16 +6600,16 @@
         <v>112</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1764171719551086</v>
+        <v>0.1868859976530075</v>
       </c>
       <c r="C101" s="1">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="F101" s="1">
         <v>0</v>
@@ -6605,19 +6623,19 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1660396903753281</v>
+        <v>0.1852023303508759</v>
       </c>
       <c r="C102" s="1">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="D102" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -6626,27 +6644,27 @@
         <v>0</v>
       </c>
       <c r="H102" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1625805348157883</v>
+        <v>0.1852023303508759</v>
       </c>
       <c r="C103" s="1">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="D103" s="1">
         <v>0</v>
       </c>
       <c r="E103" s="1">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="F103" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G103" s="1">
         <v>0</v>
@@ -6657,19 +6675,19 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1608509570360184</v>
+        <v>0.1616311222314835</v>
       </c>
       <c r="C104" s="1">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D104" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E104" s="1">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -6678,7 +6696,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -6686,16 +6704,16 @@
         <v>115</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1522030532360077</v>
+        <v>0.1582638174295425</v>
       </c>
       <c r="C105" s="1">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -6712,16 +6730,16 @@
         <v>116</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1522030532360077</v>
+        <v>0.1565801501274109</v>
       </c>
       <c r="C106" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F106" s="1">
         <v>0</v>
@@ -6735,25 +6753,25 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1487438976764679</v>
+        <v>0.1481618732213974</v>
       </c>
       <c r="C107" s="1">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D107" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="F107" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G107" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -6761,19 +6779,19 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1366368383169174</v>
+        <v>0.1481618732213974</v>
       </c>
       <c r="C108" s="1">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -6787,25 +6805,25 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1331776678562164</v>
+        <v>0.1447945535182953</v>
       </c>
       <c r="C109" s="1">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="D109" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E109" s="1">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F109" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G109" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -6816,16 +6834,16 @@
         <v>119</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1314480900764465</v>
+        <v>0.1330089420080185</v>
       </c>
       <c r="C110" s="1">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -6842,16 +6860,16 @@
         <v>120</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1245297715067864</v>
+        <v>0.1296416372060776</v>
       </c>
       <c r="C111" s="1">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -6865,25 +6883,25 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1228001937270165</v>
+        <v>0.1279579699039459</v>
       </c>
       <c r="C112" s="1">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D112" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -6891,19 +6909,19 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1193410307168961</v>
+        <v>0.1212233453989029</v>
       </c>
       <c r="C113" s="1">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -6917,45 +6935,45 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1176114529371262</v>
+        <v>0.1195396855473518</v>
       </c>
       <c r="C114" s="1">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D114" s="1">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="E114" s="1">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
       </c>
       <c r="G114" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H114" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1106931269168854</v>
+        <v>0.1161723732948303</v>
       </c>
       <c r="C115" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -6969,19 +6987,19 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1106931269168854</v>
+        <v>0.1144887134432793</v>
       </c>
       <c r="C116" s="1">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D116" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E116" s="1">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -6990,7 +7008,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6998,16 +7016,16 @@
         <v>124</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1089635491371155</v>
+        <v>0.1077540814876556</v>
       </c>
       <c r="C117" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
       </c>
       <c r="E117" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -7021,25 +7039,25 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1089635491371155</v>
+        <v>0.1077540814876556</v>
       </c>
       <c r="C118" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D118" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E118" s="1">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="F118" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G118" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -7047,19 +7065,19 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1037748083472252</v>
+        <v>0.1060704290866852</v>
       </c>
       <c r="C119" s="1">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D119" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="E119" s="1">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -7068,24 +7086,24 @@
         <v>0</v>
       </c>
       <c r="H119" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B120" s="2">
-        <v>0.0985860675573349</v>
+        <v>0.1060704290866852</v>
       </c>
       <c r="C120" s="1">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -7099,25 +7117,25 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B121" s="2">
+        <v>0.1060704290866852</v>
+      </c>
+      <c r="C121" s="1">
         <v>126</v>
       </c>
-      <c r="B121" s="2">
-        <v>0.096856489777565</v>
-      </c>
-      <c r="C121" s="1">
-        <v>112</v>
-      </c>
       <c r="D121" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E121" s="1">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F121" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G121" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -7125,19 +7143,19 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="B122" s="2">
-        <v>0.096856489777565</v>
+        <v>0.1010194569826126</v>
       </c>
       <c r="C122" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D122" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E122" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -7146,7 +7164,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -7154,16 +7172,16 @@
         <v>128</v>
       </c>
       <c r="B123" s="2">
-        <v>0.096856489777565</v>
+        <v>0.09596848487854004</v>
       </c>
       <c r="C123" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -7180,16 +7198,16 @@
         <v>129</v>
       </c>
       <c r="B124" s="2">
-        <v>0.09512690454721451</v>
+        <v>0.09428482502698898</v>
       </c>
       <c r="C124" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
       </c>
       <c r="E124" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
@@ -7206,16 +7224,16 @@
         <v>130</v>
       </c>
       <c r="B125" s="2">
-        <v>0.09512690454721451</v>
+        <v>0.09428482502698898</v>
       </c>
       <c r="C125" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D125" s="1">
         <v>0</v>
       </c>
       <c r="E125" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -7229,19 +7247,19 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
-        <v>12</v>
+        <v>131</v>
       </c>
       <c r="B126" s="2">
-        <v>0.09339732676744461</v>
+        <v>0.09428482502698898</v>
       </c>
       <c r="C126" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D126" s="1">
-        <v>716</v>
+        <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -7250,24 +7268,24 @@
         <v>0</v>
       </c>
       <c r="H126" s="1">
-        <v>716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B127" s="2">
-        <v>0.08474943041801453</v>
+        <v>0.09260116517543793</v>
       </c>
       <c r="C127" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -7281,19 +7299,19 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="B128" s="2">
-        <v>0.08474943041801453</v>
+        <v>0.09091751277446747</v>
       </c>
       <c r="C128" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D128" s="1">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="E128" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -7302,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="1">
-        <v>0</v>
+        <v>716</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -7310,16 +7328,16 @@
         <v>133</v>
       </c>
       <c r="B129" s="2">
-        <v>0.07956068962812424</v>
+        <v>0.08249922096729279</v>
       </c>
       <c r="C129" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
       </c>
       <c r="E129" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
@@ -7336,16 +7354,16 @@
         <v>134</v>
       </c>
       <c r="B130" s="2">
-        <v>0.07956068962812424</v>
+        <v>0.08249922096729279</v>
       </c>
       <c r="C130" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -7362,16 +7380,16 @@
         <v>135</v>
       </c>
       <c r="B131" s="2">
-        <v>0.07437194883823395</v>
+        <v>0.07744824886322022</v>
       </c>
       <c r="C131" s="1">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -7388,16 +7406,16 @@
         <v>136</v>
       </c>
       <c r="B132" s="2">
-        <v>0.07264236360788345</v>
+        <v>0.07744824886322022</v>
       </c>
       <c r="C132" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D132" s="1">
         <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -7414,16 +7432,16 @@
         <v>137</v>
       </c>
       <c r="B133" s="2">
-        <v>0.07264236360788345</v>
+        <v>0.07239727675914764</v>
       </c>
       <c r="C133" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D133" s="1">
         <v>0</v>
       </c>
       <c r="E133" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -7440,7 +7458,7 @@
         <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07264236360788345</v>
+        <v>0.07071361690759659</v>
       </c>
       <c r="C134" s="1">
         <v>84</v>
@@ -7463,25 +7481,25 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07264236360788345</v>
+        <v>0.07071361690759659</v>
       </c>
       <c r="C135" s="1">
         <v>84</v>
       </c>
       <c r="D135" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E135" s="1">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F135" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G135" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H135" s="1">
         <v>0</v>
@@ -7489,19 +7507,19 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B136" s="2">
-        <v>0.07091278582811356</v>
+        <v>0.07071361690759659</v>
       </c>
       <c r="C136" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -7515,25 +7533,25 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="B137" s="2">
-        <v>0.06745362281799316</v>
+        <v>0.07071361690759659</v>
       </c>
       <c r="C137" s="1">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D137" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E137" s="1">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="F137" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G137" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H137" s="1">
         <v>0</v>
@@ -7541,19 +7559,19 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>33</v>
+        <v>141</v>
       </c>
       <c r="B138" s="2">
-        <v>0.06572404503822327</v>
+        <v>0.06902995705604553</v>
       </c>
       <c r="C138" s="1">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D138" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E138" s="1">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -7562,24 +7580,24 @@
         <v>0</v>
       </c>
       <c r="H138" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B139" s="2">
-        <v>0.05707614496350288</v>
+        <v>0.06566264480352402</v>
       </c>
       <c r="C139" s="1">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D139" s="1">
         <v>0</v>
       </c>
       <c r="E139" s="1">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
@@ -7593,19 +7611,19 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="B140" s="2">
-        <v>0.0518874041736126</v>
+        <v>0.06397898495197296</v>
       </c>
       <c r="C140" s="1">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D140" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E140" s="1">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -7614,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7622,16 +7640,16 @@
         <v>143</v>
       </c>
       <c r="B141" s="2">
-        <v>0.0518874041736126</v>
+        <v>0.05556070059537888</v>
       </c>
       <c r="C141" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
       </c>
       <c r="E141" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -7648,7 +7666,7 @@
         <v>144</v>
       </c>
       <c r="B142" s="2">
-        <v>0.0518874041736126</v>
+        <v>0.05050972849130631</v>
       </c>
       <c r="C142" s="1">
         <v>60</v>
@@ -7674,16 +7692,16 @@
         <v>145</v>
       </c>
       <c r="B143" s="2">
-        <v>0.0501578226685524</v>
+        <v>0.05050972849130631</v>
       </c>
       <c r="C143" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D143" s="1">
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -7700,16 +7718,16 @@
         <v>146</v>
       </c>
       <c r="B144" s="2">
-        <v>0.04669866338372231</v>
+        <v>0.05050972849130631</v>
       </c>
       <c r="C144" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D144" s="1">
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7723,25 +7741,25 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
-        <v>45</v>
+        <v>147</v>
       </c>
       <c r="B145" s="2">
-        <v>0.04669866338372231</v>
+        <v>0.04882606863975525</v>
       </c>
       <c r="C145" s="1">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D145" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="F145" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G145" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
@@ -7749,19 +7767,19 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B146" s="2">
-        <v>0.04496908560395241</v>
+        <v>0.04545875638723373</v>
       </c>
       <c r="C146" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -7775,25 +7793,25 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04150992259383202</v>
+        <v>0.04545875638723373</v>
       </c>
       <c r="C147" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D147" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E147" s="1">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F147" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G147" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
@@ -7804,16 +7822,16 @@
         <v>149</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04150992259383202</v>
+        <v>0.04377509653568268</v>
       </c>
       <c r="C148" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D148" s="1">
         <v>0</v>
       </c>
       <c r="E148" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F148" s="1">
         <v>0</v>
@@ -7830,7 +7848,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04150992259383202</v>
+        <v>0.04040778055787087</v>
       </c>
       <c r="C149" s="1">
         <v>48</v>
@@ -7856,16 +7874,16 @@
         <v>151</v>
       </c>
       <c r="B150" s="2">
-        <v>0.03805076330900192</v>
+        <v>0.04040778055787087</v>
       </c>
       <c r="C150" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
       </c>
       <c r="E150" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F150" s="1">
         <v>0</v>
@@ -7882,16 +7900,16 @@
         <v>152</v>
       </c>
       <c r="B151" s="2">
-        <v>0.03805076330900192</v>
+        <v>0.04040778055787087</v>
       </c>
       <c r="C151" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D151" s="1">
         <v>0</v>
       </c>
       <c r="E151" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F151" s="1">
         <v>0</v>
@@ -7908,7 +7926,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="2">
-        <v>0.03805076330900192</v>
+        <v>0.03704046830534935</v>
       </c>
       <c r="C152" s="1">
         <v>44</v>
@@ -7931,25 +7949,25 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="1" t="s">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03805076330900192</v>
+        <v>0.03704046830534935</v>
       </c>
       <c r="C153" s="1">
         <v>44</v>
       </c>
       <c r="D153" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E153" s="1">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F153" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G153" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H153" s="1">
         <v>0</v>
@@ -7957,10 +7975,10 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03805076330900192</v>
+        <v>0.03704046830534935</v>
       </c>
       <c r="C154" s="1">
         <v>44</v>
@@ -7983,25 +8001,25 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="B155" s="2">
-        <v>0.03805076330900192</v>
+        <v>0.03704046830534935</v>
       </c>
       <c r="C155" s="1">
         <v>44</v>
       </c>
       <c r="D155" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E155" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F155" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G155" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
@@ -8012,16 +8030,16 @@
         <v>156</v>
       </c>
       <c r="B156" s="2">
-        <v>0.03459160402417183</v>
+        <v>0.03704046830534935</v>
       </c>
       <c r="C156" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D156" s="1">
         <v>0</v>
       </c>
       <c r="E156" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -8038,16 +8056,16 @@
         <v>157</v>
       </c>
       <c r="B157" s="2">
-        <v>0.03286202251911163</v>
+        <v>0.03704046830534935</v>
       </c>
       <c r="C157" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
       </c>
       <c r="E157" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -8064,16 +8082,16 @@
         <v>158</v>
       </c>
       <c r="B158" s="2">
-        <v>0.03113244287669659</v>
+        <v>0.03367315232753754</v>
       </c>
       <c r="C158" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D158" s="1">
         <v>0</v>
       </c>
       <c r="E158" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F158" s="1">
         <v>0</v>
@@ -8090,16 +8108,16 @@
         <v>159</v>
       </c>
       <c r="B159" s="2">
-        <v>0.03113244287669659</v>
+        <v>0.03198949247598648</v>
       </c>
       <c r="C159" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D159" s="1">
         <v>0</v>
       </c>
       <c r="E159" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F159" s="1">
         <v>0</v>
@@ -8116,7 +8134,7 @@
         <v>160</v>
       </c>
       <c r="B160" s="2">
-        <v>0.03113244287669659</v>
+        <v>0.03030583634972572</v>
       </c>
       <c r="C160" s="1">
         <v>36</v>
@@ -8142,7 +8160,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.03113244287669659</v>
+        <v>0.03030583634972572</v>
       </c>
       <c r="C161" s="1">
         <v>36</v>
@@ -8168,16 +8186,16 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.02767328172922134</v>
+        <v>0.03030583634972572</v>
       </c>
       <c r="C162" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
       </c>
       <c r="E162" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F162" s="1">
         <v>0</v>
@@ -8194,16 +8212,16 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.02767328172922134</v>
+        <v>0.03030583634972572</v>
       </c>
       <c r="C163" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D163" s="1">
         <v>0</v>
       </c>
       <c r="E163" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F163" s="1">
         <v>0</v>
@@ -8220,7 +8238,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.02767328172922134</v>
+        <v>0.02693852037191391</v>
       </c>
       <c r="C164" s="1">
         <v>32</v>
@@ -8246,7 +8264,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.02767328172922134</v>
+        <v>0.02693852037191391</v>
       </c>
       <c r="C165" s="1">
         <v>32</v>
@@ -8272,16 +8290,16 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.0259437020868063</v>
+        <v>0.02693852037191391</v>
       </c>
       <c r="C166" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
       </c>
       <c r="E166" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F166" s="1">
         <v>0</v>
@@ -8298,16 +8316,16 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.0259437020868063</v>
+        <v>0.02693852037191391</v>
       </c>
       <c r="C167" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
       </c>
       <c r="E167" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F167" s="1">
         <v>0</v>
@@ -8324,16 +8342,16 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.0224845428019762</v>
+        <v>0.02525486424565315</v>
       </c>
       <c r="C168" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D168" s="1">
         <v>0</v>
       </c>
       <c r="E168" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F168" s="1">
         <v>0</v>
@@ -8350,16 +8368,16 @@
         <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.02075496129691601</v>
+        <v>0.02525486424565315</v>
       </c>
       <c r="C169" s="1">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
       </c>
       <c r="E169" s="1">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F169" s="1">
         <v>0</v>
@@ -8373,25 +8391,25 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B170" s="2">
-        <v>0.01383664086461067</v>
+        <v>0.02188754826784134</v>
       </c>
       <c r="C170" s="1">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D170" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E170" s="1">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F170" s="1">
         <v>0</v>
       </c>
       <c r="G170" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H170" s="1">
         <v>0</v>
@@ -8399,19 +8417,19 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B171" s="2">
-        <v>0.006918320432305336</v>
+        <v>0.02020389027893543</v>
       </c>
       <c r="C171" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D171" s="1">
         <v>0</v>
       </c>
       <c r="E171" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F171" s="1">
         <v>0</v>
@@ -8425,25 +8443,25 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1" t="s">
-        <v>171</v>
+        <v>47</v>
       </c>
       <c r="B172" s="2">
-        <v>0.006918320432305336</v>
+        <v>0.01346926018595696</v>
       </c>
       <c r="C172" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D172" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E172" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F172" s="1">
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
@@ -8451,25 +8469,25 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="B173" s="2">
-        <v>0.003459160216152668</v>
+        <v>0.006734630092978478</v>
       </c>
       <c r="C173" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D173" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E173" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1">
         <v>0</v>
       </c>
       <c r="G173" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H173" s="1">
         <v>0</v>
@@ -8477,19 +8495,19 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B174" s="2">
-        <v>0.003459160216152668</v>
+        <v>0.006734630092978478</v>
       </c>
       <c r="C174" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D174" s="1">
         <v>0</v>
       </c>
       <c r="E174" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1">
         <v>0</v>
@@ -8503,59 +8521,111 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="1" t="s">
-        <v>173</v>
+        <v>46</v>
       </c>
       <c r="B175" s="2">
-        <v>0.003459160216152668</v>
+        <v>0.003367315046489239</v>
       </c>
       <c r="C175" s="1">
         <v>4</v>
       </c>
       <c r="D175" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E175" s="1">
+        <v>0</v>
+      </c>
+      <c r="F175" s="1">
+        <v>0</v>
+      </c>
+      <c r="G175" s="1">
         <v>4</v>
       </c>
-      <c r="F175" s="1">
-        <v>0</v>
-      </c>
-      <c r="G175" s="1">
-        <v>0</v>
-      </c>
       <c r="H175" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:8">
-      <c r="A176" t="s">
+      <c r="A176" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B176" s="2">
+        <v>0.003367315046489239</v>
+      </c>
+      <c r="C176" s="1">
+        <v>4</v>
+      </c>
+      <c r="D176" s="1">
+        <v>0</v>
+      </c>
+      <c r="E176" s="1">
+        <v>4</v>
+      </c>
+      <c r="F176" s="1">
+        <v>0</v>
+      </c>
+      <c r="G176" s="1">
+        <v>0</v>
+      </c>
+      <c r="H176" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B176">
+      <c r="B177" s="2">
+        <v>0.003367315046489239</v>
+      </c>
+      <c r="C177" s="1">
+        <v>4</v>
+      </c>
+      <c r="D177" s="1">
+        <v>0</v>
+      </c>
+      <c r="E177" s="1">
+        <v>4</v>
+      </c>
+      <c r="F177" s="1">
+        <v>0</v>
+      </c>
+      <c r="G177" s="1">
+        <v>0</v>
+      </c>
+      <c r="H177" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" t="s">
+        <v>177</v>
+      </c>
+      <c r="B178">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C176">
+      <c r="C178">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D176">
+      <c r="D178">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E176">
+      <c r="E178">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F176">
+      <c r="F178">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G176">
+      <c r="G178">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H176">
+      <c r="H178">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,17 +15,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="194">
   <si>
     <t>JointMotorApp</t>
   </si>
   <si>
+    <t>motor_observer.o</t>
+  </si>
+  <si>
     <t>heap_4.o</t>
   </si>
   <si>
-    <t>motor_observer.o</t>
-  </si>
-  <si>
     <t>drv_flash_g4.o</t>
   </si>
   <si>
@@ -35,15 +35,15 @@
     <t>dev_commun_can.o</t>
   </si>
   <si>
+    <t>motor_loop.o</t>
+  </si>
+  <si>
     <t>motor_info_storage.o</t>
   </si>
   <si>
     <t>drv_usart.o</t>
   </si>
   <si>
-    <t>motor_loop.o</t>
-  </si>
-  <si>
     <t>dev_commun_uart.o</t>
   </si>
   <si>
@@ -179,6 +179,9 @@
     <t>motor_pid_load.o</t>
   </si>
   <si>
+    <t>m_wm.l</t>
+  </si>
+  <si>
     <t>motor_info.o</t>
   </si>
   <si>
@@ -200,9 +203,6 @@
     <t>stm32g4xx_hal_fdcan.o</t>
   </si>
   <si>
-    <t>m_wm.l</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_adc_ex.o</t>
   </si>
   <si>
@@ -218,6 +218,9 @@
     <t>arm_common_tables.o</t>
   </si>
   <si>
+    <t>powf.o</t>
+  </si>
+  <si>
     <t>jm_proto_can.o</t>
   </si>
   <si>
@@ -227,15 +230,18 @@
     <t>motion_param.o</t>
   </si>
   <si>
+    <t>motor_mode_test_sweep.o</t>
+  </si>
+  <si>
     <t>queue.o</t>
   </si>
   <si>
+    <t>mf_w.l</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_spi.o</t>
   </si>
   <si>
-    <t>mf_w.l</t>
-  </si>
-  <si>
     <t>motor_pid_autotune.o</t>
   </si>
   <si>
@@ -299,6 +305,9 @@
     <t>stm32g4xx_hal_gpio.o</t>
   </si>
   <si>
+    <t>log10f.o</t>
+  </si>
+  <si>
     <t>ctrl_transition_mgr.o</t>
   </si>
   <si>
@@ -416,15 +425,15 @@
     <t>fepilogue.o</t>
   </si>
   <si>
+    <t>ceilf.o</t>
+  </si>
+  <si>
     <t>uldiv.o</t>
   </si>
   <si>
     <t>ldiv.o</t>
   </si>
   <si>
-    <t>motor_mode_test_sweep.o</t>
-  </si>
-  <si>
     <t>dma.o</t>
   </si>
   <si>
@@ -443,6 +452,9 @@
     <t>frem.o</t>
   </si>
   <si>
+    <t>funder.o</t>
+  </si>
+  <si>
     <t>motor_mode_profile_velocity.o</t>
   </si>
   <si>
@@ -467,6 +479,9 @@
     <t>utils.o</t>
   </si>
   <si>
+    <t>dfixui.o</t>
+  </si>
+  <si>
     <t>dfixul.o</t>
   </si>
   <si>
@@ -479,9 +494,6 @@
     <t>uidiv.o</t>
   </si>
   <si>
-    <t>funder.o</t>
-  </si>
-  <si>
     <t>thread_commun.o</t>
   </si>
   <si>
@@ -494,6 +506,9 @@
     <t>drv_delay.o</t>
   </si>
   <si>
+    <t>f2d.o</t>
+  </si>
+  <si>
     <t>fpclassifyf.o</t>
   </si>
   <si>
@@ -527,9 +542,15 @@
     <t>handlers.o</t>
   </si>
   <si>
+    <t>dfltui.o</t>
+  </si>
+  <si>
     <t>memcmp.o</t>
   </si>
   <si>
+    <t>dfltul.o</t>
+  </si>
+  <si>
     <t>strncpy.o</t>
   </si>
   <si>
@@ -537,6 +558,9 @@
   </si>
   <si>
     <t>entry2.o</t>
+  </si>
+  <si>
+    <t>fpstat.o</t>
   </si>
   <si>
     <t>entry5.o</t>
@@ -662,14 +686,14 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$178</c:f>
+              <c:f>ram_percent!$A$3:$A$186</c:f>
               <c:strCache>
-                <c:ptCount val="176"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
+                  <c:v>motor_observer.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>heap_4.o</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>motor_observer.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>drv_flash_g4.o</c:v>
@@ -681,13 +705,13 @@
                   <c:v>dev_commun_can.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>motor_info_storage.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>drv_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>motor_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>dev_commun_uart.o</c:v>
@@ -824,7 +848,7 @@
                 <c:pt idx="52">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="175">
+                <c:pt idx="183">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -832,170 +856,170 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$178</c:f>
+              <c:f>ram_percent!$B$3:$B$186</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="176"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
-                  <c:v>35.26833724975586</c:v>
+                  <c:v>30.81194496154785</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.109268188476563</c:v>
+                  <c:v>26.49878883361816</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.799897193908691</c:v>
+                  <c:v>6.611783504486084</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.799897193908691</c:v>
+                  <c:v>6.611783504486084</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.060843467712402</c:v>
+                  <c:v>6.056497097015381</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.503072261810303</c:v>
+                  <c:v>3.609362363815308</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.391354560852051</c:v>
+                  <c:v>3.383373737335205</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.609332799911499</c:v>
+                  <c:v>3.299435138702393</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.540583610534668</c:v>
+                  <c:v>2.660209894180298</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.215013027191162</c:v>
+                  <c:v>1.664245367050171</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.199974298477173</c:v>
+                  <c:v>1.652945876121521</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.538263201713562</c:v>
+                  <c:v>1.155770778656006</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.8421776294708252</c:v>
+                  <c:v>0.6327683329582214</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.7648347616195679</c:v>
+                  <c:v>0.5746569633483887</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.7304601669311523</c:v>
+                  <c:v>0.5488296747207642</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.6445236802101135</c:v>
+                  <c:v>0.4842615127563477</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.5757744908332825</c:v>
+                  <c:v>0.4326069355010986</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.4898380041122437</c:v>
+                  <c:v>0.3680387437343597</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.4812443554401398</c:v>
+                  <c:v>0.3615819215774536</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.4382761120796204</c:v>
+                  <c:v>0.329297810792923</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.4296824634075165</c:v>
+                  <c:v>0.3228409886360169</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2835904359817505</c:v>
+                  <c:v>0.2130750566720963</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2749967873096466</c:v>
+                  <c:v>0.2066182345151901</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2148412317037582</c:v>
+                  <c:v>0.1614204943180084</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1804666370153427</c:v>
+                  <c:v>0.1355932205915451</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.163279339671135</c:v>
+                  <c:v>0.1226795837283135</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1546856909990311</c:v>
+                  <c:v>0.1162227615714073</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1546856909990311</c:v>
+                  <c:v>0.1162227615714073</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1546856909990311</c:v>
+                  <c:v>0.1162227615714073</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1460920423269272</c:v>
+                  <c:v>0.1097659394145012</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1374983936548233</c:v>
+                  <c:v>0.1033091172575951</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.0945301428437233</c:v>
+                  <c:v>0.07102502137422562</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.08593649417161942</c:v>
+                  <c:v>0.06456819921731949</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.07734284549951553</c:v>
+                  <c:v>0.05811138078570366</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.06874919682741165</c:v>
+                  <c:v>0.05165455862879753</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.06874919682741165</c:v>
+                  <c:v>0.05165455862879753</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.04296824708580971</c:v>
+                  <c:v>0.03228409960865974</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.04296824708580971</c:v>
+                  <c:v>0.03228409960865974</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.0257809478789568</c:v>
+                  <c:v>0.01937046088278294</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.0257809478789568</c:v>
+                  <c:v>0.01937046088278294</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.0257809478789568</c:v>
+                  <c:v>0.01937046088278294</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.0257809478789568</c:v>
+                  <c:v>0.01937046088278294</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01718729920685291</c:v>
+                  <c:v>0.01291363965719938</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01718729920685291</c:v>
+                  <c:v>0.01291363965719938</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01718729920685291</c:v>
+                  <c:v>0.01291363965719938</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.008593649603426457</c:v>
+                  <c:v>0.006456819828599691</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.008593649603426457</c:v>
+                  <c:v>0.006456819828599691</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.008593649603426457</c:v>
+                  <c:v>0.006456819828599691</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.008593649603426457</c:v>
+                  <c:v>0.006456819828599691</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.008593649603426457</c:v>
+                  <c:v>0.006456819828599691</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.008593649603426457</c:v>
+                  <c:v>0.006456819828599691</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.008593649603426457</c:v>
+                  <c:v>0.006456819828599691</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.006445236969739199</c:v>
-                </c:pt>
-                <c:pt idx="175">
+                  <c:v>0.004842615220695734</c:v>
+                </c:pt>
+                <c:pt idx="183">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1063,535 +1087,559 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$178</c:f>
+              <c:f>flash_percent!$A$3:$A$186</c:f>
               <c:strCache>
-                <c:ptCount val="176"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
+                  <c:v>jm_proto_ops.o</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>m_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>motor_info.o</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>jm_proto_ops.o</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>jm_proto.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>stm32g4xx_hal_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>stm32g4xx_hal_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>stm32g4xx_hal_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>motor_param.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
+                  <c:v>motor_observer.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>stm32g4xx_hal_fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>m_wm.l</c:v>
-                </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>stm32g4xx_hal_adc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>arm_cortexM4lf_math.lib</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>printfa.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>stm32g4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>dev_commun_can.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>arm_common_tables.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
+                  <c:v>powf.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>jm_proto_can.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>motion_param.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
+                  <c:v>motor_mode_test_sweep.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>dev_power_monitor.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>motor_observer.o</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>motor_pid_profile.o</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>stm32g4xx_hal_spi.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>motor_pid_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>stm32g4xx_hal_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>motor_pid_autotune.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>dev_motor_phase_current.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>ctrl_transition.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>calib_config_runtime.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="35">
                   <c:v>drv_can.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="36">
                   <c:v>calib_level3_encoder.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="37">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="38">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="39">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="40">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="41">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="42">
                   <c:v>drv_flash_g4.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="43">
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="44">
                   <c:v>motor_info_storage.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="46">
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="47">
                   <c:v>multiturn_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="48">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="49">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="50">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="51">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="52">
                   <c:v>motor_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="53">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="54">
                   <c:v>atan2f.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="55">
                   <c:v>dev_eeprom.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="56">
                   <c:v>dev_half_bridge.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="57">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="58">
                   <c:v>cascade_control.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="59">
                   <c:v>foc_decoupling.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="60">
                   <c:v>crc16.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="61">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="62">
+                  <c:v>heap_4.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>startup_stm32g474xx.o</c:v>
+                </c:pt>
+                <c:pt idx="64">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
-                  <c:v>heap_4.o</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>startup_stm32g474xx.o</c:v>
-                </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="65">
                   <c:v>calib_ac_injection.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="66">
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="67">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="68">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="69">
                   <c:v>stm32g4xx_hal_flash_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="70">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="71">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="72">
+                  <c:v>log10f.o</c:v>
+                </c:pt>
+                <c:pt idx="73">
                   <c:v>ctrl_transition_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="74">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="75">
                   <c:v>motor_info_calib.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="76">
                   <c:v>led_manager.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="77">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="78">
                   <c:v>dev_config.o</c:v>
                 </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="79">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="80">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="81">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="82">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="83">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="84">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="85">
                   <c:v>cosf.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="86">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="87">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="88">
                   <c:v>cmsis_os.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="89">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="90">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="91">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="92">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="93">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="94">
                   <c:v>drv_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="95">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="96">
                   <c:v>drv_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="97">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="98">
                   <c:v>drv_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="99">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="100">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="101">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="102">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="103">
                   <c:v>drv_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="104">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="105">
                   <c:v>stm32g4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="106">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="107">
                   <c:v>fmodf.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="108">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="109">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="110">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="111">
                   <c:v>roundf.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="112">
                   <c:v>arm_cos_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="113">
                   <c:v>arm_sin_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="114">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="115">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="116">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="117">
                   <c:v>thread_period.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="118">
                   <c:v>motor_mode_mit.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="119">
                   <c:v>user_interface.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="120">
                   <c:v>motor_mode_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="121">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="122">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="123">
                   <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="124">
                   <c:v>floorf.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="125">
                   <c:v>motor_mode_position.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="126">
                   <c:v>motor_mode_current.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="127">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="128">
+                  <c:v>ceilf.o</c:v>
+                </c:pt>
+                <c:pt idx="129">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="130">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="131">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
-                  <c:v>motor_mode_test_sweep.o</c:v>
-                </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="132">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="133">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="134">
                   <c:v>motor_mode_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="135">
                   <c:v>motor_mode_profile_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="136">
                   <c:v>assert_report.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="137">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="138">
                   <c:v>frem.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="139">
+                  <c:v>funder.o</c:v>
+                </c:pt>
+                <c:pt idx="140">
                   <c:v>motor_mode_profile_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="141">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="142">
                   <c:v>motor_mode_duty.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="143">
                   <c:v>frnd.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="144">
                   <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="145">
                   <c:v>control_irq.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="146">
                   <c:v>sqrtf.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="147">
                   <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="148">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="149">
                   <c:v>utils.o</c:v>
                 </c:pt>
-                <c:pt idx="146">
+                <c:pt idx="150">
+                  <c:v>dfixui.o</c:v>
+                </c:pt>
+                <c:pt idx="151">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="152">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="148">
+                <c:pt idx="153">
                   <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="149">
+                <c:pt idx="154">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="150">
-                  <c:v>funder.o</c:v>
-                </c:pt>
-                <c:pt idx="151">
+                <c:pt idx="155">
                   <c:v>thread_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="152">
+                <c:pt idx="156">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="153">
+                <c:pt idx="157">
                   <c:v>motor_mode_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="154">
+                <c:pt idx="158">
                   <c:v>motor_mode_hold.o</c:v>
                 </c:pt>
-                <c:pt idx="155">
+                <c:pt idx="159">
                   <c:v>drv_delay.o</c:v>
                 </c:pt>
-                <c:pt idx="156">
+                <c:pt idx="160">
+                  <c:v>f2d.o</c:v>
+                </c:pt>
+                <c:pt idx="161">
                   <c:v>fpclassifyf.o</c:v>
                 </c:pt>
-                <c:pt idx="157">
+                <c:pt idx="162">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="158">
+                <c:pt idx="163">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="159">
+                <c:pt idx="164">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="160">
+                <c:pt idx="165">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="161">
+                <c:pt idx="166">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="162">
+                <c:pt idx="167">
                   <c:v>thread_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="163">
+                <c:pt idx="168">
                   <c:v>thread_display.o</c:v>
                 </c:pt>
-                <c:pt idx="164">
+                <c:pt idx="169">
                   <c:v>thread_control.o</c:v>
                 </c:pt>
-                <c:pt idx="165">
+                <c:pt idx="170">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="166">
+                <c:pt idx="171">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="167">
+                <c:pt idx="172">
+                  <c:v>dfltui.o</c:v>
+                </c:pt>
+                <c:pt idx="173">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="168">
+                <c:pt idx="174">
+                  <c:v>dfltul.o</c:v>
+                </c:pt>
+                <c:pt idx="175">
                   <c:v>strncpy.o</c:v>
                 </c:pt>
-                <c:pt idx="169">
+                <c:pt idx="176">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="170">
+                <c:pt idx="177">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="171">
+                <c:pt idx="178">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="172">
+                <c:pt idx="179">
+                  <c:v>fpstat.o</c:v>
+                </c:pt>
+                <c:pt idx="180">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="173">
+                <c:pt idx="181">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="174">
+                <c:pt idx="182">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="175">
+                <c:pt idx="183">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1599,536 +1647,560 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$178</c:f>
+              <c:f>flash_percent!$B$3:$B$186</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="176"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
-                  <c:v>3.990268468856812</c:v>
+                  <c:v>4.309946537017822</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.867361545562744</c:v>
+                  <c:v>3.852807521820068</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.577772378921509</c:v>
+                  <c:v>3.710342884063721</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.166960000991821</c:v>
+                  <c:v>3.326784133911133</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.097929954528809</c:v>
+                  <c:v>3.063772439956665</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.789820671081543</c:v>
+                  <c:v>2.880603790283203</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.685433864593506</c:v>
+                  <c:v>2.594108819961548</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.419415950775147</c:v>
+                  <c:v>2.497045040130615</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.399212121963501</c:v>
+                  <c:v>2.249688863754273</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.020389080047607</c:v>
+                  <c:v>2.230902194976807</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.998501539230347</c:v>
+                  <c:v>1.908399939537048</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.979981303215027</c:v>
+                  <c:v>1.878654599189758</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.976613998413086</c:v>
+                  <c:v>1.841081500053406</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.973246693611145</c:v>
+                  <c:v>1.837950348854065</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.867176294326782</c:v>
+                  <c:v>1.834819316864014</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.808248281478882</c:v>
+                  <c:v>1.736189961433411</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.80151355266571</c:v>
+                  <c:v>1.681395888328552</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.727432727813721</c:v>
+                  <c:v>1.67513370513916</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.636515140533447</c:v>
+                  <c:v>1.606249690055847</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.599474668502808</c:v>
+                  <c:v>1.531103491783142</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.520342826843262</c:v>
+                  <c:v>1.521710157394409</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.367129921913147</c:v>
+                  <c:v>1.487268209457398</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.353660702705383</c:v>
+                  <c:v>1.413687586784363</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.350293397903442</c:v>
+                  <c:v>1.34480357170105</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.328405857086182</c:v>
+                  <c:v>1.308796048164368</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.210549831390381</c:v>
+                  <c:v>1.258698582649231</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.173509359359741</c:v>
+                  <c:v>1.25556743144989</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.109530329704285</c:v>
+                  <c:v>1.142848253250122</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.050602316856384</c:v>
+                  <c:v>1.125627160072327</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.027031064033508</c:v>
+                  <c:v>1.091185212135315</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.010194540023804</c:v>
+                  <c:v>0.9769003987312317</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.006827235221863</c:v>
+                  <c:v>0.9549827575683594</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.000092625617981</c:v>
+                  <c:v>0.9393272995948792</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9681031107902527</c:v>
+                  <c:v>0.9361962080001831</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9108587503433228</c:v>
+                  <c:v>0.929934024810791</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8654000163078308</c:v>
+                  <c:v>0.9001886248588562</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8510888814926148</c:v>
+                  <c:v>0.8469601273536682</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8418287634849548</c:v>
+                  <c:v>0.8046903610229492</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.8384614586830139</c:v>
+                  <c:v>0.7913832664489746</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.8165739178657532</c:v>
+                  <c:v>0.7827727198600769</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.8081556558609009</c:v>
+                  <c:v>0.7796416282653809</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.80478835105896</c:v>
+                  <c:v>0.759289562702179</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7862681150436401</c:v>
+                  <c:v>0.7514618039131165</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7172381281852722</c:v>
+                  <c:v>0.7483307123184204</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.7155544757843018</c:v>
+                  <c:v>0.7311097383499146</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.7004015445709229</c:v>
+                  <c:v>0.666922390460968</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6902996301651001</c:v>
+                  <c:v>0.6653568148612976</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6717793941497803</c:v>
+                  <c:v>0.6512669324874878</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6599937677383423</c:v>
+                  <c:v>0.6418736577033997</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.6364225745201111</c:v>
+                  <c:v>0.624652624130249</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.6094840168952942</c:v>
+                  <c:v>0.6136938333511353</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.6061167120933533</c:v>
+                  <c:v>0.5917761921882629</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5758109092712402</c:v>
+                  <c:v>0.5667274594306946</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5539233684539795</c:v>
+                  <c:v>0.5635963678359985</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5421377420425415</c:v>
+                  <c:v>0.5354165434837341</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.5219338536262512</c:v>
+                  <c:v>0.5150644779205322</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.5202502012252808</c:v>
+                  <c:v>0.5041056275367737</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4815260767936707</c:v>
+                  <c:v>0.4853191077709198</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4680567979812622</c:v>
+                  <c:v>0.4837535619735718</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4613221883773804</c:v>
+                  <c:v>0.4477460086345673</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4377509653568268</c:v>
+                  <c:v>0.4352216422557831</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4310163259506226</c:v>
+                  <c:v>0.428959459066391</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4276490211486816</c:v>
+                  <c:v>0.4007796347141266</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4242817163467407</c:v>
+                  <c:v>0.3976485431194305</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.4225980639457703</c:v>
+                  <c:v>0.3945174515247345</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.4225980639457703</c:v>
+                  <c:v>0.3945174515247345</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.419230729341507</c:v>
+                  <c:v>0.3929519057273865</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.4007104933261871</c:v>
+                  <c:v>0.3929519057273865</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3939758837223053</c:v>
+                  <c:v>0.3898208141326904</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3838739395141602</c:v>
+                  <c:v>0.3725998103618622</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3754556477069855</c:v>
+                  <c:v>0.3663376271724701</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3636700510978699</c:v>
+                  <c:v>0.3569443821907044</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3586190640926361</c:v>
+                  <c:v>0.3506821990013123</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3586190640926361</c:v>
+                  <c:v>0.3491166532039642</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3451498150825501</c:v>
+                  <c:v>0.3381578326225281</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3451498150825501</c:v>
+                  <c:v>0.333461195230484</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.3434661328792572</c:v>
+                  <c:v>0.333461195230484</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.3367315232753754</c:v>
+                  <c:v>0.3209368288516998</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.3367315232753754</c:v>
+                  <c:v>0.3209368288516998</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.3131603002548218</c:v>
+                  <c:v>0.3193712830543518</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.3081093430519104</c:v>
+                  <c:v>0.3131090998649597</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.2895891070365906</c:v>
+                  <c:v>0.3131090998649597</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.2828544676303864</c:v>
+                  <c:v>0.2911914587020874</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2811708152294159</c:v>
+                  <c:v>0.2864948213100433</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2794871628284454</c:v>
+                  <c:v>0.2692738175392151</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2727525234222412</c:v>
+                  <c:v>0.263011634349823</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2592832744121552</c:v>
+                  <c:v>0.261446088552475</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2458140105009079</c:v>
+                  <c:v>0.259880542755127</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2289774268865585</c:v>
+                  <c:v>0.2536183595657349</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2289774268865585</c:v>
+                  <c:v>0.2410940080881119</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2121408581733704</c:v>
+                  <c:v>0.2285696417093277</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2070898860692978</c:v>
+                  <c:v>0.2129141837358475</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2037225663661957</c:v>
+                  <c:v>0.2129141837358475</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.2020389139652252</c:v>
+                  <c:v>0.1972587257623673</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1969879418611527</c:v>
+                  <c:v>0.1925620883703232</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.195304274559021</c:v>
+                  <c:v>0.1894309967756271</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1919369697570801</c:v>
+                  <c:v>0.1878654509782791</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1919369697570801</c:v>
+                  <c:v>0.1831688135862351</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1868859976530075</c:v>
+                  <c:v>0.181603267788887</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1852023303508759</c:v>
+                  <c:v>0.1784721910953522</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1852023303508759</c:v>
+                  <c:v>0.1784721910953522</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1616311222314835</c:v>
+                  <c:v>0.1737755537033081</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1582638174295425</c:v>
+                  <c:v>0.1722100079059601</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1565801501274109</c:v>
+                  <c:v>0.1722100079059601</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1481618732213974</c:v>
+                  <c:v>0.1502923667430878</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1481618732213974</c:v>
+                  <c:v>0.1471612751483917</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1447945535182953</c:v>
+                  <c:v>0.1455957293510437</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1330089420080185</c:v>
+                  <c:v>0.1377680003643036</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1296416372060776</c:v>
+                  <c:v>0.1377680003643036</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1279579699039459</c:v>
+                  <c:v>0.1346369087696075</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1212233453989029</c:v>
+                  <c:v>0.123678095638752</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1195396855473518</c:v>
+                  <c:v>0.1205470040440559</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1161723732948303</c:v>
+                  <c:v>0.1189814582467079</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1144887134432793</c:v>
+                  <c:v>0.1127192750573158</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1077540814876556</c:v>
+                  <c:v>0.1111537292599678</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1077540814876556</c:v>
+                  <c:v>0.1080226376652718</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1060704290866852</c:v>
+                  <c:v>0.1064570918679237</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.1060704290866852</c:v>
+                  <c:v>0.1001949086785317</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.1060704290866852</c:v>
+                  <c:v>0.1001949086785317</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.1010194569826126</c:v>
+                  <c:v>0.09862936288118362</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.09596848487854004</c:v>
+                  <c:v>0.09862936288118362</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.09428482502698898</c:v>
+                  <c:v>0.09862936288118362</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.09428482502698898</c:v>
+                  <c:v>0.09393272548913956</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.09428482502698898</c:v>
+                  <c:v>0.08923609554767609</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.09260116517543793</c:v>
+                  <c:v>0.08767054975032806</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.09091751277446747</c:v>
+                  <c:v>0.08767054975032806</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.08249922096729279</c:v>
+                  <c:v>0.08767054975032806</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.08249922096729279</c:v>
+                  <c:v>0.08610500395298004</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.07744824886322022</c:v>
+                  <c:v>0.08453945815563202</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.07744824886322022</c:v>
+                  <c:v>0.08453945815563202</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.07239727675914764</c:v>
+                  <c:v>0.07671172916889191</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07071361690759659</c:v>
+                  <c:v>0.07671172916889191</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07071361690759659</c:v>
+                  <c:v>0.07201509177684784</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.07071361690759659</c:v>
+                  <c:v>0.06731845438480377</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.07071361690759659</c:v>
+                  <c:v>0.06575290858745575</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06902995705604553</c:v>
+                  <c:v>0.06575290858745575</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.06566264480352402</c:v>
+                  <c:v>0.06575290858745575</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.06397898495197296</c:v>
+                  <c:v>0.06575290858745575</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.05556070059537888</c:v>
+                  <c:v>0.06418736279010773</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.05050972849130631</c:v>
+                  <c:v>0.06262181699275971</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.05050972849130631</c:v>
+                  <c:v>0.06105627492070198</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.05050972849130631</c:v>
+                  <c:v>0.05949072912335396</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.04882606863975525</c:v>
+                  <c:v>0.05166300013661385</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.04545875638723373</c:v>
+                  <c:v>0.04696636274456978</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04545875638723373</c:v>
+                  <c:v>0.04696636274456978</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04377509653568268</c:v>
+                  <c:v>0.04696636274456978</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04040778055787087</c:v>
+                  <c:v>0.04540081694722176</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.04040778055787087</c:v>
+                  <c:v>0.04226972907781601</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.04040778055787087</c:v>
+                  <c:v>0.04226972907781601</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.03704046830534935</c:v>
+                  <c:v>0.04070418328046799</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03704046830534935</c:v>
+                  <c:v>0.03913863748311997</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03704046830534935</c:v>
+                  <c:v>0.03757309168577194</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03704046830534935</c:v>
+                  <c:v>0.03757309168577194</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03704046830534935</c:v>
+                  <c:v>0.03757309168577194</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.03704046830534935</c:v>
+                  <c:v>0.0344420000910759</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.03367315232753754</c:v>
+                  <c:v>0.0344420000910759</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.03198949247598648</c:v>
+                  <c:v>0.0344420000910759</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.03030583634972572</c:v>
+                  <c:v>0.0344420000910759</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.03030583634972572</c:v>
+                  <c:v>0.0344420000910759</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.03030583634972572</c:v>
+                  <c:v>0.03131090849637985</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.03030583634972572</c:v>
+                  <c:v>0.02974536456167698</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.02693852037191391</c:v>
+                  <c:v>0.02974536456167698</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.02693852037191391</c:v>
+                  <c:v>0.02817981876432896</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.02693852037191391</c:v>
+                  <c:v>0.02817981876432896</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02693852037191391</c:v>
+                  <c:v>0.02817981876432896</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02525486424565315</c:v>
+                  <c:v>0.02817981876432896</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02525486424565315</c:v>
+                  <c:v>0.02504872716963291</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.02188754826784134</c:v>
+                  <c:v>0.02504872716963291</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.02020389027893543</c:v>
+                  <c:v>0.02504872716963291</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.01346926018595696</c:v>
+                  <c:v>0.02504872716963291</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.006734630092978478</c:v>
+                  <c:v>0.02348318137228489</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.006734630092978478</c:v>
+                  <c:v>0.02348318137228489</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.003367315046489239</c:v>
+                  <c:v>0.02035209164023399</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>0.003367315046489239</c:v>
+                  <c:v>0.02035209164023399</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>0.003367315046489239</c:v>
+                  <c:v>0.01878654584288597</c:v>
                 </c:pt>
                 <c:pt idx="175">
+                  <c:v>0.01878654584288597</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0.01252436358481646</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.006262181792408228</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.006262181792408228</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.003131090896204114</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.003131090896204114</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.003131090896204114</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.003131090896204114</c:v>
+                </c:pt>
+                <c:pt idx="183">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2233,8 +2305,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H178" totalsRowCount="1">
-  <autoFilter ref="A2:H177"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H186" totalsRowCount="1">
+  <autoFilter ref="A2:H185"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -2250,8 +2322,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H178" totalsRowCount="1">
-  <autoFilter ref="A2:H177"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H186" totalsRowCount="1">
+  <autoFilter ref="A2:H185"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2551,7 +2623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2564,28 +2636,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2593,25 +2665,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>35.26833724975586</v>
+        <v>30.81194496154785</v>
       </c>
       <c r="C3" s="1">
-        <v>16416</v>
+        <v>19088</v>
       </c>
       <c r="D3" s="1">
-        <v>512</v>
+        <v>2438</v>
       </c>
       <c r="E3" s="1">
-        <v>480</v>
+        <v>2390</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H3" s="1">
-        <v>16384</v>
+        <v>19040</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2619,25 +2691,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>9.109268188476563</v>
+        <v>26.49878883361816</v>
       </c>
       <c r="C4" s="1">
-        <v>4240</v>
+        <v>16416</v>
       </c>
       <c r="D4" s="1">
-        <v>1578</v>
+        <v>512</v>
       </c>
       <c r="E4" s="1">
-        <v>1530</v>
+        <v>480</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H4" s="1">
-        <v>4192</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -2645,7 +2717,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>8.799897193908691</v>
+        <v>6.611783504486084</v>
       </c>
       <c r="C5" s="1">
         <v>4096</v>
@@ -2671,7 +2743,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>8.799897193908691</v>
+        <v>6.611783504486084</v>
       </c>
       <c r="C6" s="1">
         <v>4096</v>
@@ -2697,7 +2769,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>8.060843467712402</v>
+        <v>6.056497097015381</v>
       </c>
       <c r="C7" s="1">
         <v>3752</v>
@@ -2723,25 +2795,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.503072261810303</v>
+        <v>3.609362363815308</v>
       </c>
       <c r="C8" s="1">
-        <v>2096</v>
+        <v>2236</v>
       </c>
       <c r="D8" s="1">
-        <v>934</v>
+        <v>996</v>
       </c>
       <c r="E8" s="1">
-        <v>918</v>
+        <v>996</v>
       </c>
       <c r="F8" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>2096</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2749,25 +2821,25 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>4.391354560852051</v>
+        <v>3.383373737335205</v>
       </c>
       <c r="C9" s="1">
-        <v>2044</v>
+        <v>2096</v>
       </c>
       <c r="D9" s="1">
-        <v>620</v>
+        <v>934</v>
       </c>
       <c r="E9" s="1">
-        <v>564</v>
+        <v>918</v>
       </c>
       <c r="F9" s="1">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>2044</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -2775,25 +2847,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>3.609332799911499</v>
+        <v>3.299435138702393</v>
       </c>
       <c r="C10" s="1">
-        <v>1680</v>
+        <v>2044</v>
       </c>
       <c r="D10" s="1">
-        <v>996</v>
+        <v>620</v>
       </c>
       <c r="E10" s="1">
-        <v>996</v>
+        <v>564</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>1680</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -2801,7 +2873,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>3.540583610534668</v>
+        <v>2.660209894180298</v>
       </c>
       <c r="C11" s="1">
         <v>1648</v>
@@ -2827,7 +2899,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>2.215013027191162</v>
+        <v>1.664245367050171</v>
       </c>
       <c r="C12" s="1">
         <v>1031</v>
@@ -2853,7 +2925,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>2.199974298477173</v>
+        <v>1.652945876121521</v>
       </c>
       <c r="C13" s="1">
         <v>1024</v>
@@ -2879,7 +2951,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>1.538263201713562</v>
+        <v>1.155770778656006</v>
       </c>
       <c r="C14" s="1">
         <v>716</v>
@@ -2905,19 +2977,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.8421776294708252</v>
+        <v>0.6327683329582214</v>
       </c>
       <c r="C15" s="1">
         <v>392</v>
       </c>
       <c r="D15" s="1">
-        <v>4594</v>
+        <v>5506</v>
       </c>
       <c r="E15" s="1">
-        <v>4102</v>
+        <v>5010</v>
       </c>
       <c r="F15" s="1">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G15" s="1">
         <v>28</v>
@@ -2931,7 +3003,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.7648347616195679</v>
+        <v>0.5746569633483887</v>
       </c>
       <c r="C16" s="1">
         <v>356</v>
@@ -2957,7 +3029,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.7304601669311523</v>
+        <v>0.5488296747207642</v>
       </c>
       <c r="C17" s="1">
         <v>340</v>
@@ -2983,7 +3055,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.6445236802101135</v>
+        <v>0.4842615127563477</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -3009,7 +3081,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.5757744908332825</v>
+        <v>0.4326069355010986</v>
       </c>
       <c r="C19" s="1">
         <v>268</v>
@@ -3035,7 +3107,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.4898380041122437</v>
+        <v>0.3680387437343597</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -3061,7 +3133,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.4812443554401398</v>
+        <v>0.3615819215774536</v>
       </c>
       <c r="C21" s="1">
         <v>224</v>
@@ -3087,7 +3159,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.4382761120796204</v>
+        <v>0.329297810792923</v>
       </c>
       <c r="C22" s="1">
         <v>204</v>
@@ -3113,7 +3185,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.4296824634075165</v>
+        <v>0.3228409886360169</v>
       </c>
       <c r="C23" s="1">
         <v>200</v>
@@ -3139,7 +3211,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2835904359817505</v>
+        <v>0.2130750566720963</v>
       </c>
       <c r="C24" s="1">
         <v>132</v>
@@ -3165,7 +3237,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2749967873096466</v>
+        <v>0.2066182345151901</v>
       </c>
       <c r="C25" s="1">
         <v>128</v>
@@ -3191,7 +3263,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2148412317037582</v>
+        <v>0.1614204943180084</v>
       </c>
       <c r="C26" s="1">
         <v>100</v>
@@ -3217,7 +3289,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1804666370153427</v>
+        <v>0.1355932205915451</v>
       </c>
       <c r="C27" s="1">
         <v>84</v>
@@ -3243,7 +3315,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.163279339671135</v>
+        <v>0.1226795837283135</v>
       </c>
       <c r="C28" s="1">
         <v>76</v>
@@ -3269,7 +3341,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1546856909990311</v>
+        <v>0.1162227615714073</v>
       </c>
       <c r="C29" s="1">
         <v>72</v>
@@ -3295,7 +3367,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1546856909990311</v>
+        <v>0.1162227615714073</v>
       </c>
       <c r="C30" s="1">
         <v>72</v>
@@ -3321,7 +3393,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1546856909990311</v>
+        <v>0.1162227615714073</v>
       </c>
       <c r="C31" s="1">
         <v>72</v>
@@ -3347,7 +3419,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1460920423269272</v>
+        <v>0.1097659394145012</v>
       </c>
       <c r="C32" s="1">
         <v>68</v>
@@ -3373,7 +3445,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1374983936548233</v>
+        <v>0.1033091172575951</v>
       </c>
       <c r="C33" s="1">
         <v>64</v>
@@ -3399,7 +3471,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.0945301428437233</v>
+        <v>0.07102502137422562</v>
       </c>
       <c r="C34" s="1">
         <v>44</v>
@@ -3425,7 +3497,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.08593649417161942</v>
+        <v>0.06456819921731949</v>
       </c>
       <c r="C35" s="1">
         <v>40</v>
@@ -3451,7 +3523,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.07734284549951553</v>
+        <v>0.05811138078570366</v>
       </c>
       <c r="C36" s="1">
         <v>36</v>
@@ -3477,7 +3549,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.06874919682741165</v>
+        <v>0.05165455862879753</v>
       </c>
       <c r="C37" s="1">
         <v>32</v>
@@ -3503,7 +3575,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.06874919682741165</v>
+        <v>0.05165455862879753</v>
       </c>
       <c r="C38" s="1">
         <v>32</v>
@@ -3529,7 +3601,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.04296824708580971</v>
+        <v>0.03228409960865974</v>
       </c>
       <c r="C39" s="1">
         <v>20</v>
@@ -3555,7 +3627,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.04296824708580971</v>
+        <v>0.03228409960865974</v>
       </c>
       <c r="C40" s="1">
         <v>20</v>
@@ -3581,7 +3653,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.0257809478789568</v>
+        <v>0.01937046088278294</v>
       </c>
       <c r="C41" s="1">
         <v>12</v>
@@ -3607,7 +3679,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.0257809478789568</v>
+        <v>0.01937046088278294</v>
       </c>
       <c r="C42" s="1">
         <v>12</v>
@@ -3633,7 +3705,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.0257809478789568</v>
+        <v>0.01937046088278294</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
@@ -3659,7 +3731,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.0257809478789568</v>
+        <v>0.01937046088278294</v>
       </c>
       <c r="C44" s="1">
         <v>12</v>
@@ -3685,7 +3757,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01718729920685291</v>
+        <v>0.01291363965719938</v>
       </c>
       <c r="C45" s="1">
         <v>8</v>
@@ -3711,7 +3783,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01718729920685291</v>
+        <v>0.01291363965719938</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
@@ -3737,7 +3809,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01718729920685291</v>
+        <v>0.01291363965719938</v>
       </c>
       <c r="C47" s="1">
         <v>8</v>
@@ -3763,7 +3835,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.008593649603426457</v>
+        <v>0.006456819828599691</v>
       </c>
       <c r="C48" s="1">
         <v>4</v>
@@ -3789,7 +3861,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.008593649603426457</v>
+        <v>0.006456819828599691</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
@@ -3815,7 +3887,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.008593649603426457</v>
+        <v>0.006456819828599691</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
@@ -3841,16 +3913,16 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.008593649603426457</v>
+        <v>0.006456819828599691</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
       </c>
       <c r="D51" s="1">
-        <v>1624</v>
+        <v>1718</v>
       </c>
       <c r="E51" s="1">
-        <v>1284</v>
+        <v>1378</v>
       </c>
       <c r="F51" s="1">
         <v>336</v>
@@ -3867,7 +3939,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.008593649603426457</v>
+        <v>0.006456819828599691</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
@@ -3893,7 +3965,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.008593649603426457</v>
+        <v>0.006456819828599691</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -3919,7 +3991,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.008593649603426457</v>
+        <v>0.006456819828599691</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
@@ -3945,7 +4017,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.006445236969739199</v>
+        <v>0.004842615220695734</v>
       </c>
       <c r="C55" s="1">
         <v>3</v>
@@ -3966,35 +4038,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8">
-      <c r="A178" t="s">
-        <v>177</v>
-      </c>
-      <c r="B178">
+    <row r="186" spans="1:8">
+      <c r="A186" t="s">
+        <v>185</v>
+      </c>
+      <c r="B186">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C178">
+      <c r="C186">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D178">
+      <c r="D186">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E178">
+      <c r="E186">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F178">
+      <c r="F186">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G178">
+      <c r="G186">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H178">
+      <c r="H186">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -4010,7 +4082,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -4023,132 +4095,132 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="H2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>3.990268468856812</v>
+        <v>4.309946537017822</v>
       </c>
       <c r="C3" s="1">
-        <v>4740</v>
+        <v>5506</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="E3" s="1">
-        <v>3112</v>
+        <v>5010</v>
       </c>
       <c r="F3" s="1">
-        <v>1628</v>
+        <v>468</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2">
-        <v>3.867361545562744</v>
+        <v>3.852807521820068</v>
       </c>
       <c r="C4" s="1">
-        <v>4594</v>
+        <v>4922</v>
       </c>
       <c r="D4" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>4102</v>
+        <v>4506</v>
       </c>
       <c r="F4" s="1">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="G4" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2">
-        <v>3.577772378921509</v>
+        <v>3.710342884063721</v>
       </c>
       <c r="C5" s="1">
-        <v>4250</v>
+        <v>4740</v>
       </c>
       <c r="D5" s="1">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1">
-        <v>4238</v>
+        <v>3112</v>
       </c>
       <c r="F5" s="1">
-        <v>12</v>
+        <v>1628</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>3.166960000991821</v>
+        <v>3.326784133911133</v>
       </c>
       <c r="C6" s="1">
-        <v>3762</v>
+        <v>4250</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E6" s="1">
-        <v>3762</v>
+        <v>4238</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4156,16 +4228,16 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>3.097929954528809</v>
+        <v>3.063772439956665</v>
       </c>
       <c r="C7" s="1">
-        <v>3680</v>
+        <v>3914</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>3680</v>
+        <v>3914</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -4182,19 +4254,19 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>2.789820671081543</v>
+        <v>2.880603790283203</v>
       </c>
       <c r="C8" s="1">
-        <v>3314</v>
+        <v>3680</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" s="1">
-        <v>3290</v>
+        <v>3680</v>
       </c>
       <c r="F8" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -4208,19 +4280,19 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>2.685433864593506</v>
+        <v>2.594108819961548</v>
       </c>
       <c r="C9" s="1">
-        <v>3190</v>
+        <v>3314</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>3190</v>
+        <v>3290</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -4231,25 +4303,25 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>2.419415950775147</v>
+        <v>2.497045040130615</v>
       </c>
       <c r="C10" s="1">
-        <v>2874</v>
+        <v>3190</v>
       </c>
       <c r="D10" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>2866</v>
+        <v>3190</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -4257,25 +4329,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2">
-        <v>2.399212121963501</v>
+        <v>2.249688863754273</v>
       </c>
       <c r="C11" s="1">
-        <v>2850</v>
+        <v>2874</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1">
-        <v>2506</v>
+        <v>2866</v>
       </c>
       <c r="F11" s="1">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -4286,19 +4358,19 @@
         <v>60</v>
       </c>
       <c r="B12" s="2">
-        <v>2.020389080047607</v>
+        <v>2.230902194976807</v>
       </c>
       <c r="C12" s="1">
-        <v>2400</v>
+        <v>2850</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>2384</v>
+        <v>2506</v>
       </c>
       <c r="F12" s="1">
-        <v>16</v>
+        <v>344</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -4309,48 +4381,48 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>1.998501539230347</v>
+        <v>1.908399939537048</v>
       </c>
       <c r="C13" s="1">
-        <v>2374</v>
+        <v>2438</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>19088</v>
       </c>
       <c r="E13" s="1">
-        <v>2342</v>
+        <v>2390</v>
       </c>
       <c r="F13" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>19040</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2">
-        <v>1.979981303215027</v>
+        <v>1.878654599189758</v>
       </c>
       <c r="C14" s="1">
-        <v>2352</v>
+        <v>2400</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>2352</v>
+        <v>2384</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -4361,22 +4433,22 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2">
-        <v>1.976613998413086</v>
+        <v>1.841081500053406</v>
       </c>
       <c r="C15" s="1">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>296</v>
+        <v>2352</v>
       </c>
       <c r="F15" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -4387,71 +4459,71 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2">
-        <v>1.973246693611145</v>
+        <v>1.837950348854065</v>
       </c>
       <c r="C16" s="1">
-        <v>2344</v>
+        <v>2348</v>
       </c>
       <c r="D16" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>2284</v>
+        <v>296</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G16" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>1.867176294326782</v>
+        <v>1.834819316864014</v>
       </c>
       <c r="C17" s="1">
-        <v>2218</v>
+        <v>2344</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E17" s="1">
-        <v>2218</v>
+        <v>2284</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2">
-        <v>1.808248281478882</v>
+        <v>1.736189961433411</v>
       </c>
       <c r="C18" s="1">
-        <v>2148</v>
+        <v>2218</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>2148</v>
+        <v>2218</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -4465,74 +4537,74 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2">
-        <v>1.80151355266571</v>
+        <v>1.681395888328552</v>
       </c>
       <c r="C19" s="1">
-        <v>2140</v>
+        <v>2148</v>
       </c>
       <c r="D19" s="1">
-        <v>3752</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>2136</v>
+        <v>2148</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>3748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="B20" s="2">
-        <v>1.727432727813721</v>
+        <v>1.67513370513916</v>
       </c>
       <c r="C20" s="1">
-        <v>2052</v>
+        <v>2140</v>
       </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>3752</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>2136</v>
       </c>
       <c r="F20" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2">
-        <v>1.636515140533447</v>
+        <v>1.606249690055847</v>
       </c>
       <c r="C21" s="1">
-        <v>1944</v>
+        <v>2052</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>1930</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>14</v>
+        <v>2052</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -4543,22 +4615,22 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2">
-        <v>1.599474668502808</v>
+        <v>1.531103491783142</v>
       </c>
       <c r="C22" s="1">
-        <v>1900</v>
+        <v>1956</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>1900</v>
+        <v>1636</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -4569,22 +4641,22 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="2">
-        <v>1.520342826843262</v>
+        <v>1.521710157394409</v>
       </c>
       <c r="C23" s="1">
-        <v>1806</v>
+        <v>1944</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>1806</v>
+        <v>1930</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -4595,25 +4667,25 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B24" s="2">
-        <v>1.367129921913147</v>
+        <v>1.487268209457398</v>
       </c>
       <c r="C24" s="1">
-        <v>1624</v>
+        <v>1900</v>
       </c>
       <c r="D24" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1284</v>
+        <v>1900</v>
       </c>
       <c r="F24" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -4624,16 +4696,16 @@
         <v>70</v>
       </c>
       <c r="B25" s="2">
-        <v>1.353660702705383</v>
+        <v>1.413687586784363</v>
       </c>
       <c r="C25" s="1">
-        <v>1608</v>
+        <v>1806</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>1608</v>
+        <v>1806</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -4647,97 +4719,97 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2">
-        <v>1.350293397903442</v>
+        <v>1.34480357170105</v>
       </c>
       <c r="C26" s="1">
-        <v>1604</v>
+        <v>1718</v>
       </c>
       <c r="D26" s="1">
-        <v>268</v>
+        <v>4</v>
       </c>
       <c r="E26" s="1">
-        <v>1604</v>
+        <v>1378</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="B27" s="2">
-        <v>1.328405857086182</v>
+        <v>1.308796048164368</v>
       </c>
       <c r="C27" s="1">
-        <v>1578</v>
+        <v>1672</v>
       </c>
       <c r="D27" s="1">
-        <v>4240</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>1530</v>
+        <v>1672</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>4192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="B28" s="2">
-        <v>1.210549831390381</v>
+        <v>1.258698582649231</v>
       </c>
       <c r="C28" s="1">
-        <v>1438</v>
+        <v>1608</v>
       </c>
       <c r="D28" s="1">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>1082</v>
+        <v>1608</v>
       </c>
       <c r="F28" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>352</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="B29" s="2">
-        <v>1.173509359359741</v>
+        <v>1.25556743144989</v>
       </c>
       <c r="C29" s="1">
-        <v>1394</v>
+        <v>1604</v>
       </c>
       <c r="D29" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="E29" s="1">
-        <v>1394</v>
+        <v>1604</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -4746,24 +4818,24 @@
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B30" s="2">
-        <v>1.109530329704285</v>
+        <v>1.142848253250122</v>
       </c>
       <c r="C30" s="1">
-        <v>1318</v>
+        <v>1460</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>1318</v>
+        <v>1460</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -4777,28 +4849,28 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B31" s="2">
-        <v>1.050602316856384</v>
+        <v>1.125627160072327</v>
       </c>
       <c r="C31" s="1">
-        <v>1248</v>
+        <v>1438</v>
       </c>
       <c r="D31" s="1">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E31" s="1">
-        <v>1248</v>
+        <v>1082</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H31" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4806,16 +4878,16 @@
         <v>74</v>
       </c>
       <c r="B32" s="2">
-        <v>1.027031064033508</v>
+        <v>1.091185212135315</v>
       </c>
       <c r="C32" s="1">
-        <v>1220</v>
+        <v>1394</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>1220</v>
+        <v>1394</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -4832,16 +4904,16 @@
         <v>75</v>
       </c>
       <c r="B33" s="2">
-        <v>1.010194540023804</v>
+        <v>0.9769003987312317</v>
       </c>
       <c r="C33" s="1">
-        <v>1200</v>
+        <v>1248</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>1200</v>
+        <v>1248</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -4858,19 +4930,19 @@
         <v>76</v>
       </c>
       <c r="B34" s="2">
-        <v>1.006827235221863</v>
+        <v>0.9549827575683594</v>
       </c>
       <c r="C34" s="1">
-        <v>1196</v>
+        <v>1220</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>1168</v>
+        <v>1220</v>
       </c>
       <c r="F34" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
@@ -4881,25 +4953,25 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="B35" s="2">
-        <v>1.000092625617981</v>
+        <v>0.9393272995948792</v>
       </c>
       <c r="C35" s="1">
-        <v>1188</v>
+        <v>1200</v>
       </c>
       <c r="D35" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>1168</v>
+        <v>1200</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -4907,201 +4979,201 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9681031107902527</v>
+        <v>0.9361962080001831</v>
       </c>
       <c r="C36" s="1">
-        <v>1150</v>
+        <v>1196</v>
       </c>
       <c r="D36" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>1126</v>
+        <v>1168</v>
       </c>
       <c r="F36" s="1">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G36" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9108587503433228</v>
+        <v>0.929934024810791</v>
       </c>
       <c r="C37" s="1">
-        <v>1082</v>
+        <v>1188</v>
       </c>
       <c r="D37" s="1">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E37" s="1">
-        <v>1070</v>
+        <v>1168</v>
       </c>
       <c r="F37" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H37" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8654000163078308</v>
+        <v>0.9001886248588562</v>
       </c>
       <c r="C38" s="1">
-        <v>1028</v>
+        <v>1150</v>
       </c>
       <c r="D38" s="1">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E38" s="1">
-        <v>468</v>
+        <v>1126</v>
       </c>
       <c r="F38" s="1">
-        <v>512</v>
+        <v>8</v>
       </c>
       <c r="G38" s="1">
+        <v>16</v>
+      </c>
+      <c r="H38" s="1">
         <v>48</v>
-      </c>
-      <c r="H38" s="1">
-        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8510888814926148</v>
+        <v>0.8469601273536682</v>
       </c>
       <c r="C39" s="1">
-        <v>1011</v>
+        <v>1082</v>
       </c>
       <c r="D39" s="1">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E39" s="1">
-        <v>1008</v>
+        <v>1070</v>
       </c>
       <c r="F39" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G39" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="B40" s="2">
-        <v>0.8418287634849548</v>
+        <v>0.8046903610229492</v>
       </c>
       <c r="C40" s="1">
-        <v>1000</v>
+        <v>1028</v>
       </c>
       <c r="D40" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E40" s="1">
-        <v>1000</v>
+        <v>468</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H40" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B41" s="2">
-        <v>0.8384614586830139</v>
+        <v>0.7913832664489746</v>
       </c>
       <c r="C41" s="1">
-        <v>996</v>
+        <v>1011</v>
       </c>
       <c r="D41" s="1">
-        <v>1680</v>
+        <v>3</v>
       </c>
       <c r="E41" s="1">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" s="1">
-        <v>1680</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="B42" s="2">
-        <v>0.8165739178657532</v>
+        <v>0.7827727198600769</v>
       </c>
       <c r="C42" s="1">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="D42" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>958</v>
+        <v>1000</v>
       </c>
       <c r="F42" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B43" s="2">
-        <v>0.8081556558609009</v>
+        <v>0.7796416282653809</v>
       </c>
       <c r="C43" s="1">
-        <v>960</v>
+        <v>996</v>
       </c>
       <c r="D43" s="1">
-        <v>4096</v>
+        <v>2236</v>
       </c>
       <c r="E43" s="1">
-        <v>960</v>
+        <v>996</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -5110,76 +5182,76 @@
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>4096</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="B44" s="2">
-        <v>0.80478835105896</v>
+        <v>0.759289562702179</v>
       </c>
       <c r="C44" s="1">
-        <v>956</v>
+        <v>970</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E44" s="1">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="F44" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7862681150436401</v>
+        <v>0.7514618039131165</v>
       </c>
       <c r="C45" s="1">
-        <v>934</v>
+        <v>960</v>
       </c>
       <c r="D45" s="1">
-        <v>2096</v>
+        <v>4096</v>
       </c>
       <c r="E45" s="1">
-        <v>918</v>
+        <v>960</v>
       </c>
       <c r="F45" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>2096</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7172381281852722</v>
+        <v>0.7483307123184204</v>
       </c>
       <c r="C46" s="1">
-        <v>852</v>
+        <v>956</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>852</v>
+        <v>956</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -5193,28 +5265,28 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7155544757843018</v>
+        <v>0.7311097383499146</v>
       </c>
       <c r="C47" s="1">
-        <v>850</v>
+        <v>934</v>
       </c>
       <c r="D47" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
       <c r="E47" s="1">
-        <v>850</v>
+        <v>918</v>
       </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5222,16 +5294,16 @@
         <v>81</v>
       </c>
       <c r="B48" s="2">
-        <v>0.7004015445709229</v>
+        <v>0.666922390460968</v>
       </c>
       <c r="C48" s="1">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -5245,51 +5317,51 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6902996301651001</v>
+        <v>0.6653568148612976</v>
       </c>
       <c r="C49" s="1">
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="D49" s="1">
-        <v>1648</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>816</v>
+        <v>850</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>1644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6717793941497803</v>
+        <v>0.6512669324874878</v>
       </c>
       <c r="C50" s="1">
-        <v>798</v>
+        <v>832</v>
       </c>
       <c r="D50" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>786</v>
+        <v>832</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -5297,71 +5369,71 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6599937677383423</v>
+        <v>0.6418736577033997</v>
       </c>
       <c r="C51" s="1">
-        <v>784</v>
+        <v>820</v>
       </c>
       <c r="D51" s="1">
-        <v>0</v>
+        <v>1648</v>
       </c>
       <c r="E51" s="1">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6364225745201111</v>
+        <v>0.624652624130249</v>
       </c>
       <c r="C52" s="1">
-        <v>756</v>
+        <v>798</v>
       </c>
       <c r="D52" s="1">
-        <v>228</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1">
-        <v>756</v>
+        <v>786</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H52" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B53" s="2">
-        <v>0.6094840168952942</v>
+        <v>0.6136938333511353</v>
       </c>
       <c r="C53" s="1">
-        <v>724</v>
+        <v>784</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>724</v>
+        <v>784</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -5375,19 +5447,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="B54" s="2">
-        <v>0.6061167120933533</v>
+        <v>0.5917761921882629</v>
       </c>
       <c r="C54" s="1">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E54" s="1">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -5396,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -5404,16 +5476,16 @@
         <v>85</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5758109092712402</v>
+        <v>0.5667274594306946</v>
       </c>
       <c r="C55" s="1">
-        <v>684</v>
+        <v>724</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>684</v>
+        <v>724</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -5427,19 +5499,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5539233684539795</v>
+        <v>0.5635963678359985</v>
       </c>
       <c r="C56" s="1">
-        <v>658</v>
+        <v>720</v>
       </c>
       <c r="D56" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>658</v>
+        <v>720</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -5448,24 +5520,24 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5421377420425415</v>
+        <v>0.5354165434837341</v>
       </c>
       <c r="C57" s="1">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>644</v>
+        <v>684</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -5479,45 +5551,45 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B58" s="2">
-        <v>0.5219338536262512</v>
+        <v>0.5150644779205322</v>
       </c>
       <c r="C58" s="1">
-        <v>620</v>
+        <v>658</v>
       </c>
       <c r="D58" s="1">
-        <v>2044</v>
+        <v>32</v>
       </c>
       <c r="E58" s="1">
-        <v>564</v>
+        <v>658</v>
       </c>
       <c r="F58" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>2044</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B59" s="2">
-        <v>0.5202502012252808</v>
+        <v>0.5041056275367737</v>
       </c>
       <c r="C59" s="1">
-        <v>618</v>
+        <v>644</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>618</v>
+        <v>644</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -5531,28 +5603,28 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>88</v>
+        <v>8</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4815260767936707</v>
+        <v>0.4853191077709198</v>
       </c>
       <c r="C60" s="1">
-        <v>572</v>
+        <v>620</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
       <c r="E60" s="1">
         <v>564</v>
       </c>
       <c r="F60" s="1">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -5560,19 +5632,19 @@
         <v>89</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4680567979812622</v>
+        <v>0.4837535619735718</v>
       </c>
       <c r="C61" s="1">
-        <v>556</v>
+        <v>618</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>44</v>
+        <v>618</v>
       </c>
       <c r="F61" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
@@ -5583,48 +5655,48 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4613221883773804</v>
+        <v>0.4477460086345673</v>
       </c>
       <c r="C62" s="1">
-        <v>548</v>
+        <v>572</v>
       </c>
       <c r="D62" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="F62" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4377509653568268</v>
+        <v>0.4352216422557831</v>
       </c>
       <c r="C63" s="1">
-        <v>520</v>
+        <v>556</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>328</v>
+        <v>44</v>
       </c>
       <c r="F63" s="1">
-        <v>192</v>
+        <v>512</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -5635,129 +5707,129 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4310163259506226</v>
+        <v>0.428959459066391</v>
       </c>
       <c r="C64" s="1">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="D64" s="1">
-        <v>16416</v>
+        <v>204</v>
       </c>
       <c r="E64" s="1">
-        <v>480</v>
+        <v>548</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>16384</v>
+        <v>204</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4276490211486816</v>
+        <v>0.4007796347141266</v>
       </c>
       <c r="C65" s="1">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D65" s="1">
-        <v>1024</v>
+        <v>16416</v>
       </c>
       <c r="E65" s="1">
-        <v>36</v>
+        <v>480</v>
       </c>
       <c r="F65" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G65" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H65" s="1">
-        <v>1024</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4242817163467407</v>
+        <v>0.3976485431194305</v>
       </c>
       <c r="C66" s="1">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D66" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E66" s="1">
-        <v>504</v>
+        <v>36</v>
       </c>
       <c r="F66" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
       </c>
       <c r="H66" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
       <c r="B67" s="2">
-        <v>0.4225980639457703</v>
+        <v>0.3945174515247345</v>
       </c>
       <c r="C67" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D67" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>502</v>
+        <v>312</v>
       </c>
       <c r="F67" s="1">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="B68" s="2">
-        <v>0.4225980639457703</v>
+        <v>0.3945174515247345</v>
       </c>
       <c r="C68" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
       </c>
       <c r="G68" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68" s="1">
         <v>0</v>
@@ -5765,19 +5837,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>0.419230729341507</v>
+        <v>0.3929519057273865</v>
       </c>
       <c r="C69" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D69" s="1">
-        <v>1031</v>
+        <v>4096</v>
       </c>
       <c r="E69" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -5786,30 +5858,30 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>1031</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="B70" s="2">
-        <v>0.4007104933261871</v>
+        <v>0.3929519057273865</v>
       </c>
       <c r="C70" s="1">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="D70" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E70" s="1">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -5817,19 +5889,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3939758837223053</v>
+        <v>0.3898208141326904</v>
       </c>
       <c r="C71" s="1">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="D71" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="E71" s="1">
-        <v>468</v>
+        <v>498</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -5838,30 +5910,30 @@
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3838739395141602</v>
+        <v>0.3725998103618622</v>
       </c>
       <c r="C72" s="1">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="D72" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>424</v>
+        <v>476</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -5869,19 +5941,19 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3754556477069855</v>
+        <v>0.3663376271724701</v>
       </c>
       <c r="C73" s="1">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -5895,25 +5967,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3636700510978699</v>
+        <v>0.3569443821907044</v>
       </c>
       <c r="C74" s="1">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="D74" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E74" s="1">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F74" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -5924,19 +5996,19 @@
         <v>96</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3586190640926361</v>
+        <v>0.3506821990013123</v>
       </c>
       <c r="C75" s="1">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F75" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
@@ -5947,25 +6019,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3586190640926361</v>
+        <v>0.3491166532039642</v>
       </c>
       <c r="C76" s="1">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="D76" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>418</v>
+        <v>446</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -5973,22 +6045,22 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3451498150825501</v>
+        <v>0.3381578326225281</v>
       </c>
       <c r="C77" s="1">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="F77" s="1">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
@@ -5999,22 +6071,22 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3451498150825501</v>
+        <v>0.333461195230484</v>
       </c>
       <c r="C78" s="1">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="F78" s="1">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -6025,25 +6097,25 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B79" s="2">
-        <v>0.3434661328792572</v>
+        <v>0.333461195230484</v>
       </c>
       <c r="C79" s="1">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="D79" s="1">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E79" s="1">
-        <v>344</v>
+        <v>418</v>
       </c>
       <c r="F79" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -6051,22 +6123,22 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B80" s="2">
-        <v>0.3367315232753754</v>
+        <v>0.3209368288516998</v>
       </c>
       <c r="C80" s="1">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="F80" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
@@ -6077,51 +6149,51 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="B81" s="2">
-        <v>0.3367315232753754</v>
+        <v>0.3209368288516998</v>
       </c>
       <c r="C81" s="1">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D81" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="F81" s="1">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="G81" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H81" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="B82" s="2">
-        <v>0.3131603002548218</v>
+        <v>0.3193712830543518</v>
       </c>
       <c r="C82" s="1">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="D82" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E82" s="1">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F82" s="1">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G82" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -6129,19 +6201,19 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B83" s="2">
-        <v>0.3081093430519104</v>
+        <v>0.3131090998649597</v>
       </c>
       <c r="C83" s="1">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="F83" s="1">
         <v>0</v>
@@ -6155,48 +6227,48 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B84" s="2">
-        <v>0.2895891070365906</v>
+        <v>0.3131090998649597</v>
       </c>
       <c r="C84" s="1">
-        <v>344</v>
+        <v>400</v>
       </c>
       <c r="D84" s="1">
-        <v>340</v>
+        <v>72</v>
       </c>
       <c r="E84" s="1">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
       </c>
       <c r="G84" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H84" s="1">
-        <v>340</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B85" s="2">
-        <v>0.2828544676303864</v>
+        <v>0.2911914587020874</v>
       </c>
       <c r="C85" s="1">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F85" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G85" s="1">
         <v>0</v>
@@ -6207,19 +6279,19 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2811708152294159</v>
+        <v>0.2864948213100433</v>
       </c>
       <c r="C86" s="1">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
@@ -6233,19 +6305,19 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2794871628284454</v>
+        <v>0.2692738175392151</v>
       </c>
       <c r="C87" s="1">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="D87" s="1">
-        <v>200</v>
+        <v>340</v>
       </c>
       <c r="E87" s="1">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -6254,24 +6326,24 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>200</v>
+        <v>340</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2727525234222412</v>
+        <v>0.263011634349823</v>
       </c>
       <c r="C88" s="1">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -6285,22 +6357,22 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2592832744121552</v>
+        <v>0.261446088552475</v>
       </c>
       <c r="C89" s="1">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="F89" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G89" s="1">
         <v>0</v>
@@ -6311,19 +6383,19 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2458140105009079</v>
+        <v>0.259880542755127</v>
       </c>
       <c r="C90" s="1">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="D90" s="1">
-        <v>68</v>
+        <v>200</v>
       </c>
       <c r="E90" s="1">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -6332,30 +6404,30 @@
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>68</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2289774268865585</v>
+        <v>0.2536183595657349</v>
       </c>
       <c r="C91" s="1">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="D91" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E91" s="1">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -6363,22 +6435,22 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2289774268865585</v>
+        <v>0.2410940080881119</v>
       </c>
       <c r="C92" s="1">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="F92" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G92" s="1">
         <v>0</v>
@@ -6389,19 +6461,19 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2121408581733704</v>
+        <v>0.2285696417093277</v>
       </c>
       <c r="C93" s="1">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="D93" s="1">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E93" s="1">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
@@ -6410,30 +6482,30 @@
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>84</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2070898860692978</v>
+        <v>0.2129141837358475</v>
       </c>
       <c r="C94" s="1">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="D94" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E94" s="1">
-        <v>210</v>
+        <v>268</v>
       </c>
       <c r="F94" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -6441,19 +6513,19 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2037225663661957</v>
+        <v>0.2129141837358475</v>
       </c>
       <c r="C95" s="1">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="D95" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="E95" s="1">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
@@ -6462,53 +6534,53 @@
         <v>0</v>
       </c>
       <c r="H95" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="B96" s="2">
-        <v>0.2020389139652252</v>
+        <v>0.1972587257623673</v>
       </c>
       <c r="C96" s="1">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="D96" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E96" s="1">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="F96" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G96" s="1">
         <v>0</v>
       </c>
       <c r="H96" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1969879418611527</v>
+        <v>0.1925620883703232</v>
       </c>
       <c r="C97" s="1">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="F97" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G97" s="1">
         <v>0</v>
@@ -6519,28 +6591,28 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="B98" s="2">
-        <v>0.195304274559021</v>
+        <v>0.1894309967756271</v>
       </c>
       <c r="C98" s="1">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="D98" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E98" s="1">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="F98" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G98" s="1">
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -6548,19 +6620,19 @@
         <v>111</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1919369697570801</v>
+        <v>0.1878654509782791</v>
       </c>
       <c r="C99" s="1">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F99" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
@@ -6571,19 +6643,19 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1919369697570801</v>
+        <v>0.1831688135862351</v>
       </c>
       <c r="C100" s="1">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D100" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="F100" s="1">
         <v>0</v>
@@ -6592,27 +6664,27 @@
         <v>0</v>
       </c>
       <c r="H100" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1868859976530075</v>
+        <v>0.181603267788887</v>
       </c>
       <c r="C101" s="1">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="F101" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G101" s="1">
         <v>0</v>
@@ -6623,19 +6695,19 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1852023303508759</v>
+        <v>0.1784721910953522</v>
       </c>
       <c r="C102" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F102" s="1">
         <v>0</v>
@@ -6649,45 +6721,45 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1852023303508759</v>
+        <v>0.1784721910953522</v>
       </c>
       <c r="C103" s="1">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D103" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E103" s="1">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="F103" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G103" s="1">
         <v>0</v>
       </c>
       <c r="H103" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1616311222314835</v>
+        <v>0.1737755537033081</v>
       </c>
       <c r="C104" s="1">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="D104" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E104" s="1">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -6696,24 +6768,24 @@
         <v>0</v>
       </c>
       <c r="H104" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1582638174295425</v>
+        <v>0.1722100079059601</v>
       </c>
       <c r="C105" s="1">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -6727,22 +6799,22 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1565801501274109</v>
+        <v>0.1722100079059601</v>
       </c>
       <c r="C106" s="1">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="D106" s="1">
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="F106" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G106" s="1">
         <v>0</v>
@@ -6753,19 +6825,19 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1481618732213974</v>
+        <v>0.1502923667430878</v>
       </c>
       <c r="C107" s="1">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D107" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E107" s="1">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
@@ -6774,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -6782,16 +6854,16 @@
         <v>118</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1481618732213974</v>
+        <v>0.1471612751483917</v>
       </c>
       <c r="C108" s="1">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="D108" s="1">
         <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -6805,25 +6877,25 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1447945535182953</v>
+        <v>0.1455957293510437</v>
       </c>
       <c r="C109" s="1">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D109" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="F109" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G109" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -6831,19 +6903,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1330089420080185</v>
+        <v>0.1377680003643036</v>
       </c>
       <c r="C110" s="1">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -6857,19 +6929,19 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1296416372060776</v>
+        <v>0.1377680003643036</v>
       </c>
       <c r="C111" s="1">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="D111" s="1">
         <v>0</v>
       </c>
       <c r="E111" s="1">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="F111" s="1">
         <v>0</v>
@@ -6883,25 +6955,25 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>121</v>
+        <v>42</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1279579699039459</v>
+        <v>0.1346369087696075</v>
       </c>
       <c r="C112" s="1">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="D112" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E112" s="1">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F112" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G112" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -6912,16 +6984,16 @@
         <v>122</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1212233453989029</v>
+        <v>0.123678095638752</v>
       </c>
       <c r="C113" s="1">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="D113" s="1">
         <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
@@ -6935,25 +7007,25 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1195396855473518</v>
+        <v>0.1205470040440559</v>
       </c>
       <c r="C114" s="1">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D114" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
       </c>
       <c r="G114" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -6961,19 +7033,19 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1161723732948303</v>
+        <v>0.1189814582467079</v>
       </c>
       <c r="C115" s="1">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -6987,19 +7059,19 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1144887134432793</v>
+        <v>0.1127192750573158</v>
       </c>
       <c r="C116" s="1">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D116" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -7008,30 +7080,30 @@
         <v>0</v>
       </c>
       <c r="H116" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1077540814876556</v>
+        <v>0.1111537292599678</v>
       </c>
       <c r="C117" s="1">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D117" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E117" s="1">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -7039,19 +7111,19 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1077540814876556</v>
+        <v>0.1080226376652718</v>
       </c>
       <c r="C118" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D118" s="1">
         <v>0</v>
       </c>
       <c r="E118" s="1">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
@@ -7065,19 +7137,19 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1060704290866852</v>
+        <v>0.1064570918679237</v>
       </c>
       <c r="C119" s="1">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D119" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E119" s="1">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -7086,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="H119" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -7094,16 +7166,16 @@
         <v>127</v>
       </c>
       <c r="B120" s="2">
-        <v>0.1060704290866852</v>
+        <v>0.1001949086785317</v>
       </c>
       <c r="C120" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D120" s="1">
         <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -7117,25 +7189,25 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B121" s="2">
-        <v>0.1060704290866852</v>
+        <v>0.1001949086785317</v>
       </c>
       <c r="C121" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D121" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E121" s="1">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="F121" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G121" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -7143,19 +7215,19 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="B122" s="2">
-        <v>0.1010194569826126</v>
+        <v>0.09862936288118362</v>
       </c>
       <c r="C122" s="1">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D122" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="E122" s="1">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -7164,24 +7236,24 @@
         <v>0</v>
       </c>
       <c r="H122" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B123" s="2">
-        <v>0.09596848487854004</v>
+        <v>0.09862936288118362</v>
       </c>
       <c r="C123" s="1">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -7195,25 +7267,25 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1" t="s">
-        <v>129</v>
+        <v>41</v>
       </c>
       <c r="B124" s="2">
-        <v>0.09428482502698898</v>
+        <v>0.09862936288118362</v>
       </c>
       <c r="C124" s="1">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="D124" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E124" s="1">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="F124" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G124" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
@@ -7221,19 +7293,19 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="B125" s="2">
-        <v>0.09428482502698898</v>
+        <v>0.09393272548913956</v>
       </c>
       <c r="C125" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D125" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E125" s="1">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F125" s="1">
         <v>0</v>
@@ -7242,7 +7314,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -7250,16 +7322,16 @@
         <v>131</v>
       </c>
       <c r="B126" s="2">
-        <v>0.09428482502698898</v>
+        <v>0.08923609554767609</v>
       </c>
       <c r="C126" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D126" s="1">
         <v>0</v>
       </c>
       <c r="E126" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -7276,16 +7348,16 @@
         <v>132</v>
       </c>
       <c r="B127" s="2">
-        <v>0.09260116517543793</v>
+        <v>0.08767054975032806</v>
       </c>
       <c r="C127" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -7299,19 +7371,19 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="B128" s="2">
-        <v>0.09091751277446747</v>
+        <v>0.08767054975032806</v>
       </c>
       <c r="C128" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D128" s="1">
-        <v>716</v>
+        <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -7320,24 +7392,24 @@
         <v>0</v>
       </c>
       <c r="H128" s="1">
-        <v>716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B129" s="2">
-        <v>0.08249922096729279</v>
+        <v>0.08767054975032806</v>
       </c>
       <c r="C129" s="1">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D129" s="1">
         <v>0</v>
       </c>
       <c r="E129" s="1">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
@@ -7351,19 +7423,19 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B130" s="2">
-        <v>0.08249922096729279</v>
+        <v>0.08610500395298004</v>
       </c>
       <c r="C130" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -7377,19 +7449,19 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B131" s="2">
-        <v>0.07744824886322022</v>
+        <v>0.08453945815563202</v>
       </c>
       <c r="C131" s="1">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -7403,19 +7475,19 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
-        <v>136</v>
+        <v>12</v>
       </c>
       <c r="B132" s="2">
-        <v>0.07744824886322022</v>
+        <v>0.08453945815563202</v>
       </c>
       <c r="C132" s="1">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D132" s="1">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="E132" s="1">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -7424,7 +7496,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="1">
-        <v>0</v>
+        <v>716</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -7432,16 +7504,16 @@
         <v>137</v>
       </c>
       <c r="B133" s="2">
-        <v>0.07239727675914764</v>
+        <v>0.07671172916889191</v>
       </c>
       <c r="C133" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D133" s="1">
         <v>0</v>
       </c>
       <c r="E133" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -7458,16 +7530,16 @@
         <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07071361690759659</v>
+        <v>0.07671172916889191</v>
       </c>
       <c r="C134" s="1">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D134" s="1">
         <v>0</v>
       </c>
       <c r="E134" s="1">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -7484,16 +7556,16 @@
         <v>139</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07071361690759659</v>
+        <v>0.07201509177684784</v>
       </c>
       <c r="C135" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D135" s="1">
         <v>0</v>
       </c>
       <c r="E135" s="1">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -7510,16 +7582,16 @@
         <v>140</v>
       </c>
       <c r="B136" s="2">
-        <v>0.07071361690759659</v>
+        <v>0.06731845438480377</v>
       </c>
       <c r="C136" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -7533,25 +7605,25 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="B137" s="2">
-        <v>0.07071361690759659</v>
+        <v>0.06575290858745575</v>
       </c>
       <c r="C137" s="1">
         <v>84</v>
       </c>
       <c r="D137" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F137" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G137" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H137" s="1">
         <v>0</v>
@@ -7559,19 +7631,19 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B138" s="2">
-        <v>0.06902995705604553</v>
+        <v>0.06575290858745575</v>
       </c>
       <c r="C138" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D138" s="1">
         <v>0</v>
       </c>
       <c r="E138" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F138" s="1">
         <v>0</v>
@@ -7585,19 +7657,19 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B139" s="2">
-        <v>0.06566264480352402</v>
+        <v>0.06575290858745575</v>
       </c>
       <c r="C139" s="1">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D139" s="1">
         <v>0</v>
       </c>
       <c r="E139" s="1">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
@@ -7611,45 +7683,45 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B140" s="2">
-        <v>0.06397898495197296</v>
+        <v>0.06575290858745575</v>
       </c>
       <c r="C140" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D140" s="1">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="E140" s="1">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="F140" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G140" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H140" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B141" s="2">
-        <v>0.05556070059537888</v>
+        <v>0.06418736279010773</v>
       </c>
       <c r="C141" s="1">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D141" s="1">
         <v>0</v>
       </c>
       <c r="E141" s="1">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F141" s="1">
         <v>0</v>
@@ -7663,19 +7735,19 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B142" s="2">
-        <v>0.05050972849130631</v>
+        <v>0.06262181699275971</v>
       </c>
       <c r="C142" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -7689,19 +7761,19 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B143" s="2">
-        <v>0.05050972849130631</v>
+        <v>0.06105627492070198</v>
       </c>
       <c r="C143" s="1">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D143" s="1">
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -7715,19 +7787,19 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
-        <v>146</v>
+        <v>33</v>
       </c>
       <c r="B144" s="2">
-        <v>0.05050972849130631</v>
+        <v>0.05949072912335396</v>
       </c>
       <c r="C144" s="1">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D144" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E144" s="1">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7736,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -7744,16 +7816,16 @@
         <v>147</v>
       </c>
       <c r="B145" s="2">
-        <v>0.04882606863975525</v>
+        <v>0.05166300013661385</v>
       </c>
       <c r="C145" s="1">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D145" s="1">
         <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F145" s="1">
         <v>0</v>
@@ -7770,16 +7842,16 @@
         <v>148</v>
       </c>
       <c r="B146" s="2">
-        <v>0.04545875638723373</v>
+        <v>0.04696636274456978</v>
       </c>
       <c r="C146" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -7793,25 +7865,25 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="1" t="s">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04545875638723373</v>
+        <v>0.04696636274456978</v>
       </c>
       <c r="C147" s="1">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D147" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E147" s="1">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="F147" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G147" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
@@ -7819,19 +7891,19 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04377509653568268</v>
+        <v>0.04696636274456978</v>
       </c>
       <c r="C148" s="1">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D148" s="1">
         <v>0</v>
       </c>
       <c r="E148" s="1">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F148" s="1">
         <v>0</v>
@@ -7845,19 +7917,19 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04040778055787087</v>
+        <v>0.04540081694722176</v>
       </c>
       <c r="C149" s="1">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D149" s="1">
         <v>0</v>
       </c>
       <c r="E149" s="1">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F149" s="1">
         <v>0</v>
@@ -7871,19 +7943,19 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B150" s="2">
-        <v>0.04040778055787087</v>
+        <v>0.04226972907781601</v>
       </c>
       <c r="C150" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
       </c>
       <c r="E150" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F150" s="1">
         <v>0</v>
@@ -7897,25 +7969,25 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1" t="s">
-        <v>152</v>
+        <v>45</v>
       </c>
       <c r="B151" s="2">
-        <v>0.04040778055787087</v>
+        <v>0.04226972907781601</v>
       </c>
       <c r="C151" s="1">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D151" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E151" s="1">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F151" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G151" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
@@ -7926,16 +7998,16 @@
         <v>153</v>
       </c>
       <c r="B152" s="2">
-        <v>0.03704046830534935</v>
+        <v>0.04070418328046799</v>
       </c>
       <c r="C152" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D152" s="1">
         <v>0</v>
       </c>
       <c r="E152" s="1">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F152" s="1">
         <v>0</v>
@@ -7952,16 +8024,16 @@
         <v>154</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03704046830534935</v>
+        <v>0.03913863748311997</v>
       </c>
       <c r="C153" s="1">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D153" s="1">
         <v>0</v>
       </c>
       <c r="E153" s="1">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F153" s="1">
         <v>0</v>
@@ -7978,16 +8050,16 @@
         <v>155</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03704046830534935</v>
+        <v>0.03757309168577194</v>
       </c>
       <c r="C154" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D154" s="1">
         <v>0</v>
       </c>
       <c r="E154" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F154" s="1">
         <v>0</v>
@@ -8001,25 +8073,25 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" s="2">
+        <v>0.03757309168577194</v>
+      </c>
+      <c r="C155" s="1">
         <v>48</v>
       </c>
-      <c r="B155" s="2">
-        <v>0.03704046830534935</v>
-      </c>
-      <c r="C155" s="1">
-        <v>44</v>
-      </c>
       <c r="D155" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E155" s="1">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F155" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G155" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
@@ -8027,19 +8099,19 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B156" s="2">
-        <v>0.03704046830534935</v>
+        <v>0.03757309168577194</v>
       </c>
       <c r="C156" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D156" s="1">
         <v>0</v>
       </c>
       <c r="E156" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F156" s="1">
         <v>0</v>
@@ -8053,10 +8125,10 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B157" s="2">
-        <v>0.03704046830534935</v>
+        <v>0.0344420000910759</v>
       </c>
       <c r="C157" s="1">
         <v>44</v>
@@ -8079,19 +8151,19 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B158" s="2">
-        <v>0.03367315232753754</v>
+        <v>0.0344420000910759</v>
       </c>
       <c r="C158" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D158" s="1">
         <v>0</v>
       </c>
       <c r="E158" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F158" s="1">
         <v>0</v>
@@ -8105,25 +8177,25 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1" t="s">
-        <v>159</v>
+        <v>48</v>
       </c>
       <c r="B159" s="2">
-        <v>0.03198949247598648</v>
+        <v>0.0344420000910759</v>
       </c>
       <c r="C159" s="1">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D159" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E159" s="1">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F159" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G159" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -8134,16 +8206,16 @@
         <v>160</v>
       </c>
       <c r="B160" s="2">
-        <v>0.03030583634972572</v>
+        <v>0.0344420000910759</v>
       </c>
       <c r="C160" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D160" s="1">
         <v>0</v>
       </c>
       <c r="E160" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F160" s="1">
         <v>0</v>
@@ -8160,16 +8232,16 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.03030583634972572</v>
+        <v>0.0344420000910759</v>
       </c>
       <c r="C161" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D161" s="1">
         <v>0</v>
       </c>
       <c r="E161" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F161" s="1">
         <v>0</v>
@@ -8186,16 +8258,16 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.03030583634972572</v>
+        <v>0.03131090849637985</v>
       </c>
       <c r="C162" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
       </c>
       <c r="E162" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F162" s="1">
         <v>0</v>
@@ -8212,16 +8284,16 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.03030583634972572</v>
+        <v>0.02974536456167698</v>
       </c>
       <c r="C163" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D163" s="1">
         <v>0</v>
       </c>
       <c r="E163" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F163" s="1">
         <v>0</v>
@@ -8238,16 +8310,16 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.02693852037191391</v>
+        <v>0.02974536456167698</v>
       </c>
       <c r="C164" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
       </c>
       <c r="E164" s="1">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F164" s="1">
         <v>0</v>
@@ -8264,16 +8336,16 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.02693852037191391</v>
+        <v>0.02817981876432896</v>
       </c>
       <c r="C165" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
       </c>
       <c r="E165" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F165" s="1">
         <v>0</v>
@@ -8290,16 +8362,16 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.02693852037191391</v>
+        <v>0.02817981876432896</v>
       </c>
       <c r="C166" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
       </c>
       <c r="E166" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F166" s="1">
         <v>0</v>
@@ -8316,16 +8388,16 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.02693852037191391</v>
+        <v>0.02817981876432896</v>
       </c>
       <c r="C167" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
       </c>
       <c r="E167" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F167" s="1">
         <v>0</v>
@@ -8342,16 +8414,16 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.02525486424565315</v>
+        <v>0.02817981876432896</v>
       </c>
       <c r="C168" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D168" s="1">
         <v>0</v>
       </c>
       <c r="E168" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F168" s="1">
         <v>0</v>
@@ -8368,16 +8440,16 @@
         <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.02525486424565315</v>
+        <v>0.02504872716963291</v>
       </c>
       <c r="C169" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
       </c>
       <c r="E169" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F169" s="1">
         <v>0</v>
@@ -8394,16 +8466,16 @@
         <v>170</v>
       </c>
       <c r="B170" s="2">
-        <v>0.02188754826784134</v>
+        <v>0.02504872716963291</v>
       </c>
       <c r="C170" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D170" s="1">
         <v>0</v>
       </c>
       <c r="E170" s="1">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F170" s="1">
         <v>0</v>
@@ -8420,16 +8492,16 @@
         <v>171</v>
       </c>
       <c r="B171" s="2">
-        <v>0.02020389027893543</v>
+        <v>0.02504872716963291</v>
       </c>
       <c r="C171" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D171" s="1">
         <v>0</v>
       </c>
       <c r="E171" s="1">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F171" s="1">
         <v>0</v>
@@ -8443,25 +8515,25 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="1" t="s">
-        <v>47</v>
+        <v>172</v>
       </c>
       <c r="B172" s="2">
-        <v>0.01346926018595696</v>
+        <v>0.02504872716963291</v>
       </c>
       <c r="C172" s="1">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D172" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E172" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F172" s="1">
         <v>0</v>
       </c>
       <c r="G172" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
@@ -8469,19 +8541,19 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B173" s="2">
-        <v>0.006734630092978478</v>
+        <v>0.02348318137228489</v>
       </c>
       <c r="C173" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D173" s="1">
         <v>0</v>
       </c>
       <c r="E173" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F173" s="1">
         <v>0</v>
@@ -8495,19 +8567,19 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B174" s="2">
-        <v>0.006734630092978478</v>
+        <v>0.02348318137228489</v>
       </c>
       <c r="C174" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D174" s="1">
         <v>0</v>
       </c>
       <c r="E174" s="1">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F174" s="1">
         <v>0</v>
@@ -8521,25 +8593,25 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="1" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="B175" s="2">
-        <v>0.003367315046489239</v>
+        <v>0.02035209164023399</v>
       </c>
       <c r="C175" s="1">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D175" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E175" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F175" s="1">
         <v>0</v>
       </c>
       <c r="G175" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
@@ -8547,19 +8619,19 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B176" s="2">
-        <v>0.003367315046489239</v>
+        <v>0.02035209164023399</v>
       </c>
       <c r="C176" s="1">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D176" s="1">
         <v>0</v>
       </c>
       <c r="E176" s="1">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F176" s="1">
         <v>0</v>
@@ -8573,59 +8645,267 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B177" s="2">
-        <v>0.003367315046489239</v>
+        <v>0.01878654584288597</v>
       </c>
       <c r="C177" s="1">
+        <v>24</v>
+      </c>
+      <c r="D177" s="1">
+        <v>0</v>
+      </c>
+      <c r="E177" s="1">
+        <v>24</v>
+      </c>
+      <c r="F177" s="1">
+        <v>0</v>
+      </c>
+      <c r="G177" s="1">
+        <v>0</v>
+      </c>
+      <c r="H177" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B178" s="2">
+        <v>0.01878654584288597</v>
+      </c>
+      <c r="C178" s="1">
+        <v>24</v>
+      </c>
+      <c r="D178" s="1">
+        <v>0</v>
+      </c>
+      <c r="E178" s="1">
+        <v>24</v>
+      </c>
+      <c r="F178" s="1">
+        <v>0</v>
+      </c>
+      <c r="G178" s="1">
+        <v>0</v>
+      </c>
+      <c r="H178" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B179" s="2">
+        <v>0.01252436358481646</v>
+      </c>
+      <c r="C179" s="1">
+        <v>16</v>
+      </c>
+      <c r="D179" s="1">
         <v>4</v>
       </c>
-      <c r="D177" s="1">
-        <v>0</v>
-      </c>
-      <c r="E177" s="1">
+      <c r="E179" s="1">
+        <v>12</v>
+      </c>
+      <c r="F179" s="1">
+        <v>0</v>
+      </c>
+      <c r="G179" s="1">
         <v>4</v>
       </c>
-      <c r="F177" s="1">
-        <v>0</v>
-      </c>
-      <c r="G177" s="1">
-        <v>0</v>
-      </c>
-      <c r="H177" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
-      <c r="A178" t="s">
-        <v>177</v>
-      </c>
-      <c r="B178">
+      <c r="H179" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2">
+        <v>0.006262181792408228</v>
+      </c>
+      <c r="C180" s="1">
+        <v>8</v>
+      </c>
+      <c r="D180" s="1">
+        <v>0</v>
+      </c>
+      <c r="E180" s="1">
+        <v>8</v>
+      </c>
+      <c r="F180" s="1">
+        <v>0</v>
+      </c>
+      <c r="G180" s="1">
+        <v>0</v>
+      </c>
+      <c r="H180" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2">
+        <v>0.006262181792408228</v>
+      </c>
+      <c r="C181" s="1">
+        <v>8</v>
+      </c>
+      <c r="D181" s="1">
+        <v>0</v>
+      </c>
+      <c r="E181" s="1">
+        <v>8</v>
+      </c>
+      <c r="F181" s="1">
+        <v>0</v>
+      </c>
+      <c r="G181" s="1">
+        <v>0</v>
+      </c>
+      <c r="H181" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2">
+        <v>0.003131090896204114</v>
+      </c>
+      <c r="C182" s="1">
+        <v>4</v>
+      </c>
+      <c r="D182" s="1">
+        <v>0</v>
+      </c>
+      <c r="E182" s="1">
+        <v>4</v>
+      </c>
+      <c r="F182" s="1">
+        <v>0</v>
+      </c>
+      <c r="G182" s="1">
+        <v>0</v>
+      </c>
+      <c r="H182" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B183" s="2">
+        <v>0.003131090896204114</v>
+      </c>
+      <c r="C183" s="1">
+        <v>4</v>
+      </c>
+      <c r="D183" s="1">
+        <v>4</v>
+      </c>
+      <c r="E183" s="1">
+        <v>0</v>
+      </c>
+      <c r="F183" s="1">
+        <v>0</v>
+      </c>
+      <c r="G183" s="1">
+        <v>4</v>
+      </c>
+      <c r="H183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B184" s="2">
+        <v>0.003131090896204114</v>
+      </c>
+      <c r="C184" s="1">
+        <v>4</v>
+      </c>
+      <c r="D184" s="1">
+        <v>0</v>
+      </c>
+      <c r="E184" s="1">
+        <v>4</v>
+      </c>
+      <c r="F184" s="1">
+        <v>0</v>
+      </c>
+      <c r="G184" s="1">
+        <v>0</v>
+      </c>
+      <c r="H184" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B185" s="2">
+        <v>0.003131090896204114</v>
+      </c>
+      <c r="C185" s="1">
+        <v>4</v>
+      </c>
+      <c r="D185" s="1">
+        <v>0</v>
+      </c>
+      <c r="E185" s="1">
+        <v>4</v>
+      </c>
+      <c r="F185" s="1">
+        <v>0</v>
+      </c>
+      <c r="G185" s="1">
+        <v>0</v>
+      </c>
+      <c r="H185" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" t="s">
+        <v>185</v>
+      </c>
+      <c r="B186">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C178">
+      <c r="C186">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D178">
+      <c r="D186">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E178">
+      <c r="E186">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F178">
+      <c r="F186">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G178">
+      <c r="G186">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H178">
+      <c r="H186">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="196">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -26,6 +26,9 @@
     <t>heap_4.o</t>
   </si>
   <si>
+    <t>motor_loop.o</t>
+  </si>
+  <si>
     <t>drv_flash_g4.o</t>
   </si>
   <si>
@@ -35,9 +38,6 @@
     <t>dev_commun_can.o</t>
   </si>
   <si>
-    <t>motor_loop.o</t>
-  </si>
-  <si>
     <t>motor_info_storage.o</t>
   </si>
   <si>
@@ -128,6 +128,9 @@
     <t>dev_eeprom.o</t>
   </si>
   <si>
+    <t>calib_config_runtime.o</t>
+  </si>
+  <si>
     <t>thread_management.o</t>
   </si>
   <si>
@@ -224,15 +227,15 @@
     <t>jm_proto_can.o</t>
   </si>
   <si>
+    <t>motor_mode_test_sweep.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_rcc.o</t>
   </si>
   <si>
     <t>motion_param.o</t>
   </si>
   <si>
-    <t>motor_mode_test_sweep.o</t>
-  </si>
-  <si>
     <t>queue.o</t>
   </si>
   <si>
@@ -251,24 +254,21 @@
     <t>ctrl_transition.o</t>
   </si>
   <si>
-    <t>calib_config_runtime.o</t>
-  </si>
-  <si>
     <t>foc_core.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_dma.o</t>
   </si>
   <si>
+    <t>multiturn_counter.o</t>
+  </si>
+  <si>
     <t>current_loop.o</t>
   </si>
   <si>
     <t>dev_mt6835.o</t>
   </si>
   <si>
-    <t>multiturn_counter.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_rcc_ex.o</t>
   </si>
   <si>
@@ -299,6 +299,9 @@
     <t>calib_ac_injection.o</t>
   </si>
   <si>
+    <t>ctrl_transition_mgr.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_flash_ex.o</t>
   </si>
   <si>
@@ -308,9 +311,6 @@
     <t>log10f.o</t>
   </si>
   <si>
-    <t>ctrl_transition_mgr.o</t>
-  </si>
-  <si>
     <t>dev_motor.o</t>
   </si>
   <si>
@@ -365,6 +365,9 @@
     <t>ddiv.o</t>
   </si>
   <si>
+    <t>motor_mode_load_sim.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_pwr_ex.o</t>
   </si>
   <si>
@@ -401,27 +404,27 @@
     <t>thread_period.o</t>
   </si>
   <si>
+    <t>motor_mode_velocity.o</t>
+  </si>
+  <si>
     <t>motor_mode_mit.o</t>
   </si>
   <si>
     <t>user_interface.o</t>
   </si>
   <si>
-    <t>motor_mode_velocity.o</t>
-  </si>
-  <si>
     <t>motor_mode_open_loop.o</t>
   </si>
   <si>
+    <t>motor_mode_current.o</t>
+  </si>
+  <si>
     <t>floorf.o</t>
   </si>
   <si>
     <t>motor_mode_position.o</t>
   </si>
   <si>
-    <t>motor_mode_current.o</t>
-  </si>
-  <si>
     <t>fepilogue.o</t>
   </si>
   <si>
@@ -534,6 +537,9 @@
   </si>
   <si>
     <t>thread_control.o</t>
+  </si>
+  <si>
+    <t>motor_mode_zero_force.o</t>
   </si>
   <si>
     <t>llshl.o</t>
@@ -686,9 +692,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$186</c:f>
+              <c:f>ram_percent!$A$3:$A$188</c:f>
               <c:strCache>
-                <c:ptCount val="184"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
                   <c:v>motor_observer.o</c:v>
                 </c:pt>
@@ -696,16 +702,16 @@
                   <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>drv_flash_g4.o</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>dev_commun_can.o</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>motor_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>motor_info_storage.o</c:v>
@@ -798,57 +804,60 @@
                   <c:v>dev_eeprom.o</c:v>
                 </c:pt>
                 <c:pt idx="36">
+                  <c:v>calib_config_runtime.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>led_manager.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="183">
+                <c:pt idx="185">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -856,170 +865,173 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$186</c:f>
+              <c:f>ram_percent!$B$3:$B$188</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="184"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
-                  <c:v>30.81194496154785</c:v>
+                  <c:v>34.56700897216797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.49878883361816</c:v>
+                  <c:v>21.19889450073242</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.611783504486084</c:v>
+                  <c:v>12.92905330657959</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.611783504486084</c:v>
+                  <c:v>5.289392948150635</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.056497097015381</c:v>
+                  <c:v>5.289392948150635</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.609362363815308</c:v>
+                  <c:v>4.845166683197022</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.383373737335205</c:v>
+                  <c:v>2.706681489944458</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.299435138702393</c:v>
+                  <c:v>2.639530897140503</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.660209894180298</c:v>
+                  <c:v>2.128154039382935</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.664245367050171</c:v>
+                  <c:v>1.331387639045715</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.652945876121521</c:v>
+                  <c:v>1.322348237037659</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.155770778656006</c:v>
+                  <c:v>0.9297760725021362</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.6327683329582214</c:v>
+                  <c:v>0.5062114000320435</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.5746569633483887</c:v>
+                  <c:v>0.4597226083278656</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.5488296747207642</c:v>
+                  <c:v>0.4390609264373779</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.4842615127563477</c:v>
+                  <c:v>0.3874067068099976</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.4326069355010986</c:v>
+                  <c:v>0.3460833132266998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.3680387437343597</c:v>
+                  <c:v>0.2944290935993195</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.3615819215774536</c:v>
+                  <c:v>0.2892636656761169</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.329297810792923</c:v>
+                  <c:v>0.2634365558624268</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.3228409886360169</c:v>
+                  <c:v>0.2582711279392242</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2130750566720963</c:v>
+                  <c:v>0.1704589426517487</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2066182345151901</c:v>
+                  <c:v>0.1652935296297073</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.1614204943180084</c:v>
+                  <c:v>0.1291355639696121</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1355932205915451</c:v>
+                  <c:v>0.1084738746285439</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1226795837283135</c:v>
+                  <c:v>0.09814303368330002</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.1162227615714073</c:v>
+                  <c:v>0.0929776057600975</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.1162227615714073</c:v>
+                  <c:v>0.0929776057600975</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.1162227615714073</c:v>
+                  <c:v>0.0929776057600975</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.1097659394145012</c:v>
+                  <c:v>0.08781218528747559</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.1033091172575951</c:v>
+                  <c:v>0.08264676481485367</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.07102502137422562</c:v>
+                  <c:v>0.05681964755058289</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.06456819921731949</c:v>
+                  <c:v>0.05165422707796097</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.05811138078570366</c:v>
+                  <c:v>0.04648880288004875</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.05165455862879753</c:v>
+                  <c:v>0.04132338240742683</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.05165455862879753</c:v>
+                  <c:v>0.04132338240742683</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03228409960865974</c:v>
+                  <c:v>0.03615795820951462</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.03228409960865974</c:v>
+                  <c:v>0.02582711353898048</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.01937046088278294</c:v>
+                  <c:v>0.02582711353898048</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.01937046088278294</c:v>
+                  <c:v>0.01549626793712378</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.01937046088278294</c:v>
+                  <c:v>0.01549626793712378</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.01937046088278294</c:v>
+                  <c:v>0.01549626793712378</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01291363965719938</c:v>
+                  <c:v>0.01549626793712378</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01291363965719938</c:v>
+                  <c:v>0.01033084560185671</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01291363965719938</c:v>
+                  <c:v>0.01033084560185671</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.006456819828599691</c:v>
+                  <c:v>0.01033084560185671</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.006456819828599691</c:v>
+                  <c:v>0.005165422800928354</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.006456819828599691</c:v>
+                  <c:v>0.005165422800928354</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.006456819828599691</c:v>
+                  <c:v>0.005165422800928354</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.006456819828599691</c:v>
+                  <c:v>0.005165422800928354</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.006456819828599691</c:v>
+                  <c:v>0.005165422800928354</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.006456819828599691</c:v>
+                  <c:v>0.005165422800928354</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.004842615220695734</c:v>
-                </c:pt>
-                <c:pt idx="183">
+                  <c:v>0.005165422800928354</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.003874066984280944</c:v>
+                </c:pt>
+                <c:pt idx="185">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1087,9 +1099,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$186</c:f>
+              <c:f>flash_percent!$A$3:$A$188</c:f>
               <c:strCache>
-                <c:ptCount val="184"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
                   <c:v>jm_proto_ops.o</c:v>
                 </c:pt>
@@ -1115,10 +1127,10 @@
                   <c:v>stm32g4xx_hal_tim.o</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>motor_param.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>mc_w.l</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>motor_param.o</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>motor_observer.o</c:v>
@@ -1154,16 +1166,16 @@
                   <c:v>jm_proto_can.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>motor_mode_test_sweep.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>motion_param.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>system_state.o</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>motor_mode_test_sweep.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>queue.o</c:v>
@@ -1181,16 +1193,16 @@
                   <c:v>stm32g4xx_hal_spi.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>calib_config_runtime.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>motor_pid_autotune.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>dev_motor_phase_current.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>ctrl_transition.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>calib_config_runtime.o</c:v>
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>jm_host_commun.o</c:v>
@@ -1205,13 +1217,13 @@
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
                 <c:pt idx="38">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>foc_core.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>motor_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>calib_level5_nonlinear.o</c:v>
@@ -1226,13 +1238,13 @@
                   <c:v>motor_info_storage.o</c:v>
                 </c:pt>
                 <c:pt idx="45">
+                  <c:v>multiturn_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>dev_mt6835.o</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>multiturn_counter.o</c:v>
                 </c:pt>
                 <c:pt idx="48">
                   <c:v>dev_commun_uart.o</c:v>
@@ -1277,13 +1289,13 @@
                   <c:v>adc.o</c:v>
                 </c:pt>
                 <c:pt idx="62">
+                  <c:v>motor_control.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>startup_stm32g474xx.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>motor_control.o</c:v>
                 </c:pt>
                 <c:pt idx="65">
                   <c:v>calib_ac_injection.o</c:v>
@@ -1298,19 +1310,19 @@
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
                 <c:pt idx="69">
+                  <c:v>ctrl_transition_mgr.o</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>stm32g4xx_hal_flash_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>log10f.o</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>ctrl_transition_mgr.o</c:v>
                 </c:pt>
                 <c:pt idx="74">
                   <c:v>dev_motor.o</c:v>
@@ -1397,249 +1409,255 @@
                   <c:v>ddiv.o</c:v>
                 </c:pt>
                 <c:pt idx="102">
+                  <c:v>motor_mode_load_sim.o</c:v>
+                </c:pt>
+                <c:pt idx="103">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="104">
                   <c:v>drv_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="105">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="106">
                   <c:v>stm32g4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="107">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="108">
                   <c:v>fmodf.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="109">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="110">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="111">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="112">
                   <c:v>roundf.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="113">
                   <c:v>arm_cos_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="114">
                   <c:v>arm_sin_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="115">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="116">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="117">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="118">
                   <c:v>thread_period.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="119">
+                  <c:v>motor_mode_velocity.o</c:v>
+                </c:pt>
+                <c:pt idx="120">
                   <c:v>motor_mode_mit.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="121">
                   <c:v>user_interface.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
-                  <c:v>motor_mode_velocity.o</c:v>
-                </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="122">
                   <c:v>calib_level6_system.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="123">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="124">
                   <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="125">
+                  <c:v>motor_mode_current.o</c:v>
+                </c:pt>
+                <c:pt idx="126">
                   <c:v>floorf.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="127">
                   <c:v>motor_mode_position.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
-                  <c:v>motor_mode_current.o</c:v>
-                </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="128">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="129">
                   <c:v>ceilf.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="130">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="131">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="132">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="133">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="134">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="135">
                   <c:v>motor_mode_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="136">
                   <c:v>motor_mode_profile_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="137">
                   <c:v>assert_report.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
+                <c:pt idx="138">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="139">
                   <c:v>frem.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="140">
                   <c:v>funder.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="141">
                   <c:v>motor_mode_profile_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="142">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="143">
                   <c:v>motor_mode_duty.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="144">
                   <c:v>frnd.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="145">
                   <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="146">
                   <c:v>control_irq.o</c:v>
                 </c:pt>
-                <c:pt idx="146">
+                <c:pt idx="147">
                   <c:v>sqrtf.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="148">
                   <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="148">
+                <c:pt idx="149">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="149">
+                <c:pt idx="150">
                   <c:v>utils.o</c:v>
                 </c:pt>
-                <c:pt idx="150">
+                <c:pt idx="151">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="151">
+                <c:pt idx="152">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="152">
+                <c:pt idx="153">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="153">
+                <c:pt idx="154">
                   <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="154">
+                <c:pt idx="155">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="155">
+                <c:pt idx="156">
                   <c:v>thread_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="156">
+                <c:pt idx="157">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="157">
+                <c:pt idx="158">
                   <c:v>motor_mode_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="158">
+                <c:pt idx="159">
                   <c:v>motor_mode_hold.o</c:v>
                 </c:pt>
-                <c:pt idx="159">
+                <c:pt idx="160">
                   <c:v>drv_delay.o</c:v>
                 </c:pt>
-                <c:pt idx="160">
+                <c:pt idx="161">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="161">
+                <c:pt idx="162">
                   <c:v>fpclassifyf.o</c:v>
                 </c:pt>
-                <c:pt idx="162">
+                <c:pt idx="163">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="163">
+                <c:pt idx="164">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="164">
+                <c:pt idx="165">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="165">
+                <c:pt idx="166">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="166">
+                <c:pt idx="167">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="167">
+                <c:pt idx="168">
                   <c:v>thread_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="168">
+                <c:pt idx="169">
                   <c:v>thread_display.o</c:v>
                 </c:pt>
-                <c:pt idx="169">
+                <c:pt idx="170">
                   <c:v>thread_control.o</c:v>
                 </c:pt>
-                <c:pt idx="170">
+                <c:pt idx="171">
+                  <c:v>motor_mode_zero_force.o</c:v>
+                </c:pt>
+                <c:pt idx="172">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="171">
+                <c:pt idx="173">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="172">
+                <c:pt idx="174">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="173">
+                <c:pt idx="175">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="174">
+                <c:pt idx="176">
                   <c:v>dfltul.o</c:v>
                 </c:pt>
-                <c:pt idx="175">
+                <c:pt idx="177">
                   <c:v>strncpy.o</c:v>
                 </c:pt>
-                <c:pt idx="176">
+                <c:pt idx="178">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="177">
+                <c:pt idx="179">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="178">
+                <c:pt idx="180">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="179">
+                <c:pt idx="181">
                   <c:v>fpstat.o</c:v>
                 </c:pt>
-                <c:pt idx="180">
+                <c:pt idx="182">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="181">
+                <c:pt idx="183">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="182">
+                <c:pt idx="184">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="183">
+                <c:pt idx="185">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1647,560 +1665,566 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$186</c:f>
+              <c:f>flash_percent!$B$3:$B$188</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="184"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
-                  <c:v>4.309946537017822</c:v>
+                  <c:v>4.491837501525879</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.852807521820068</c:v>
+                  <c:v>3.817131280899048</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.710342884063721</c:v>
+                  <c:v>3.675985813140869</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.326784133911133</c:v>
+                  <c:v>3.295979022979736</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.063772439956665</c:v>
+                  <c:v>3.035402774810791</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.880603790283203</c:v>
+                  <c:v>2.853929996490479</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.594108819961548</c:v>
+                  <c:v>2.570087909698486</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.497045040130615</c:v>
+                  <c:v>2.473922967910767</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.249688863754273</c:v>
+                  <c:v>2.238163471221924</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.230902194976807</c:v>
+                  <c:v>2.228857278823853</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.908399939537048</c:v>
+                  <c:v>1.89383065700531</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.878654599189758</c:v>
+                  <c:v>1.861258625984192</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.841081500053406</c:v>
+                  <c:v>1.824033498764038</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.837950348854065</c:v>
+                  <c:v>1.820931434631348</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.834819316864014</c:v>
+                  <c:v>1.817829251289368</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.736189961433411</c:v>
+                  <c:v>1.720113277435303</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.681395888328552</c:v>
+                  <c:v>1.665826559066773</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.67513370513916</c:v>
+                  <c:v>1.659622311592102</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.606249690055847</c:v>
+                  <c:v>1.591376185417175</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.531103491783142</c:v>
+                  <c:v>1.516925811767578</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.521710157394409</c:v>
+                  <c:v>1.507619500160217</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.487268209457398</c:v>
+                  <c:v>1.49055802822113</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.413687586784363</c:v>
+                  <c:v>1.473496437072754</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.34480357170105</c:v>
+                  <c:v>1.400597095489502</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.308796048164368</c:v>
+                  <c:v>1.364923000335693</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.258698582649231</c:v>
+                  <c:v>1.247043371200562</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.25556743144989</c:v>
+                  <c:v>1.243941187858582</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.142848253250122</c:v>
+                  <c:v>1.132265686988831</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.125627160072327</c:v>
+                  <c:v>1.115204215049744</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.091185212135315</c:v>
+                  <c:v>1.081081032752991</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.9769003987312317</c:v>
+                  <c:v>1.076427936553955</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.9549827575683594</c:v>
+                  <c:v>0.9678544998168945</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.9393272995948792</c:v>
+                  <c:v>0.9461398124694824</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9361962080001831</c:v>
+                  <c:v>0.941486656665802</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.929934024810791</c:v>
+                  <c:v>0.912016749382019</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.9001886248588562</c:v>
+                  <c:v>0.8918530941009522</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8469601273536682</c:v>
+                  <c:v>0.8391174674034119</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8046903610229492</c:v>
+                  <c:v>0.7972391247749329</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.7913832664489746</c:v>
+                  <c:v>0.7848307490348816</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7827727198600769</c:v>
+                  <c:v>0.784055233001709</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.7796416282653809</c:v>
+                  <c:v>0.7755244374275208</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.759289562702179</c:v>
+                  <c:v>0.7522587180137634</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7514618039131165</c:v>
+                  <c:v>0.7445034980773926</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7483307123184204</c:v>
+                  <c:v>0.7414013743400574</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.7311097383499146</c:v>
+                  <c:v>0.7243398427963257</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.666922390460968</c:v>
+                  <c:v>0.6700531244277954</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6653568148612976</c:v>
+                  <c:v>0.6607468128204346</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6512669324874878</c:v>
+                  <c:v>0.6591957807540894</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6418736577033997</c:v>
+                  <c:v>0.635930061340332</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.624652624130249</c:v>
+                  <c:v>0.6188685297966003</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.6136938333511353</c:v>
+                  <c:v>0.6080111861228943</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5917761921882629</c:v>
+                  <c:v>0.5862964987754822</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5667274594306946</c:v>
+                  <c:v>0.5614796876907349</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5635963678359985</c:v>
+                  <c:v>0.5583776235580444</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5354165434837341</c:v>
+                  <c:v>0.5304587483406067</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.5150644779205322</c:v>
+                  <c:v>0.5102950930595398</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.5041056275367737</c:v>
+                  <c:v>0.4994377493858337</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4853191077709198</c:v>
+                  <c:v>0.4808251559734345</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4837535619735718</c:v>
+                  <c:v>0.4792741239070892</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4477460086345673</c:v>
+                  <c:v>0.4435999989509583</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4352216422557831</c:v>
+                  <c:v>0.4311915934085846</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.428959459066391</c:v>
+                  <c:v>0.424987405538559</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4007796347141266</c:v>
+                  <c:v>0.4218853116035461</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.3976485431194305</c:v>
+                  <c:v>0.3970685303211212</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.3945174515247345</c:v>
+                  <c:v>0.393966406583786</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.3945174515247345</c:v>
+                  <c:v>0.3908643126487732</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.3929519057273865</c:v>
+                  <c:v>0.389313280582428</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3929519057273865</c:v>
+                  <c:v>0.389313280582428</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3898208141326904</c:v>
+                  <c:v>0.3862111866474152</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3725998103618622</c:v>
+                  <c:v>0.3707006871700287</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3663376271724701</c:v>
+                  <c:v>0.3691496253013611</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3569443821907044</c:v>
+                  <c:v>0.3629454374313355</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3506821990013123</c:v>
+                  <c:v>0.353639155626297</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3491166532039642</c:v>
+                  <c:v>0.3474349677562714</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3381578326225281</c:v>
+                  <c:v>0.3350265622138977</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.333461195230484</c:v>
+                  <c:v>0.3303734064102173</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.333461195230484</c:v>
+                  <c:v>0.3303734064102173</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.3209368288516998</c:v>
+                  <c:v>0.317965030670166</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.3209368288516998</c:v>
+                  <c:v>0.317965030670166</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.3193712830543518</c:v>
+                  <c:v>0.3164139688014984</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.3131090998649597</c:v>
+                  <c:v>0.3102097809314728</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.3131090998649597</c:v>
+                  <c:v>0.3102097809314728</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.2911914587020874</c:v>
+                  <c:v>0.2884950935840607</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2864948213100433</c:v>
+                  <c:v>0.2838419377803803</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2692738175392151</c:v>
+                  <c:v>0.2667804062366486</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.263011634349823</c:v>
+                  <c:v>0.2605762183666229</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.261446088552475</c:v>
+                  <c:v>0.2590251564979553</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.259880542755127</c:v>
+                  <c:v>0.2574741244316101</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2536183595657349</c:v>
+                  <c:v>0.2512699067592621</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2410940080881119</c:v>
+                  <c:v>0.2388615310192108</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2285696417093277</c:v>
+                  <c:v>0.2264531403779984</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2129141837358475</c:v>
+                  <c:v>0.2109426558017731</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2129141837358475</c:v>
+                  <c:v>0.2109426558017731</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.1972587257623673</c:v>
+                  <c:v>0.1954321563243866</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1925620883703232</c:v>
+                  <c:v>0.1907790154218674</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1894309967756271</c:v>
+                  <c:v>0.1876769214868546</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1878654509782791</c:v>
+                  <c:v>0.1861258745193481</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1831688135862351</c:v>
+                  <c:v>0.1814727187156677</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.181603267788887</c:v>
+                  <c:v>0.1799216717481613</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1784721910953522</c:v>
+                  <c:v>0.1768195778131485</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1784721910953522</c:v>
+                  <c:v>0.1768195778131485</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1737755537033081</c:v>
+                  <c:v>0.1721664220094681</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1722100079059601</c:v>
+                  <c:v>0.1721664220094681</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1722100079059601</c:v>
+                  <c:v>0.1706153750419617</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1502923667430878</c:v>
+                  <c:v>0.1706153750419617</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1471612751483917</c:v>
+                  <c:v>0.1489006876945496</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1455957293510437</c:v>
+                  <c:v>0.1457985937595367</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1377680003643036</c:v>
+                  <c:v>0.1442475467920303</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1377680003643036</c:v>
+                  <c:v>0.1364922970533371</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1346369087696075</c:v>
+                  <c:v>0.1364922970533371</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.123678095638752</c:v>
+                  <c:v>0.1333902031183243</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1205470040440559</c:v>
+                  <c:v>0.1225328594446182</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1189814582467079</c:v>
+                  <c:v>0.1194307655096054</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1127192750573158</c:v>
+                  <c:v>0.117879718542099</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1111537292599678</c:v>
+                  <c:v>0.1116755232214928</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1080226376652718</c:v>
+                  <c:v>0.1101244688034058</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1064570918679237</c:v>
+                  <c:v>0.1070223748683929</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.1001949086785317</c:v>
+                  <c:v>0.1054713279008865</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.1001949086785317</c:v>
+                  <c:v>0.0992671325802803</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.09862936288118362</c:v>
+                  <c:v>0.0992671325802803</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.09862936288118362</c:v>
+                  <c:v>0.0992671325802803</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.09862936288118362</c:v>
+                  <c:v>0.0977160781621933</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.09393272548913956</c:v>
+                  <c:v>0.0977160781621933</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.08923609554767609</c:v>
+                  <c:v>0.09306293725967407</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.08767054975032806</c:v>
+                  <c:v>0.08996083587408066</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.08767054975032806</c:v>
+                  <c:v>0.08840978890657425</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.08767054975032806</c:v>
+                  <c:v>0.08685874193906784</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.08610500395298004</c:v>
+                  <c:v>0.08685874193906784</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.08453945815563202</c:v>
+                  <c:v>0.08530768752098084</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.08453945815563202</c:v>
+                  <c:v>0.08375664055347443</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.07671172916889191</c:v>
+                  <c:v>0.08375664055347443</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07671172916889191</c:v>
+                  <c:v>0.07600139826536179</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07201509177684784</c:v>
+                  <c:v>0.07600139826536179</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.06731845438480377</c:v>
+                  <c:v>0.07134824991226196</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06575290858745575</c:v>
+                  <c:v>0.06669510155916214</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06575290858745575</c:v>
+                  <c:v>0.06514405459165573</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.06575290858745575</c:v>
+                  <c:v>0.06514405459165573</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.06575290858745575</c:v>
+                  <c:v>0.06514405459165573</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.06418736279010773</c:v>
+                  <c:v>0.06514405459165573</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.06262181699275971</c:v>
+                  <c:v>0.06359300762414932</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.06105627492070198</c:v>
+                  <c:v>0.06204195693135262</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.05949072912335396</c:v>
+                  <c:v>0.06204195693135262</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.05166300013661385</c:v>
+                  <c:v>0.0589398592710495</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.04696636274456978</c:v>
+                  <c:v>0.05118461325764656</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04696636274456978</c:v>
+                  <c:v>0.04653146862983704</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04696636274456978</c:v>
+                  <c:v>0.04653146862983704</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04540081694722176</c:v>
+                  <c:v>0.04653146862983704</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.04226972907781601</c:v>
+                  <c:v>0.04498041793704033</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.04226972907781601</c:v>
+                  <c:v>0.04187832027673721</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.04070418328046799</c:v>
+                  <c:v>0.04187832027673721</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03913863748311997</c:v>
+                  <c:v>0.04032726958394051</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03757309168577194</c:v>
+                  <c:v>0.0387762226164341</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03757309168577194</c:v>
+                  <c:v>0.03722517192363739</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03757309168577194</c:v>
+                  <c:v>0.03722517192363739</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.0344420000910759</c:v>
+                  <c:v>0.03722517192363739</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.0344420000910759</c:v>
+                  <c:v>0.03412307426333427</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.0344420000910759</c:v>
+                  <c:v>0.03412307426333427</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.0344420000910759</c:v>
+                  <c:v>0.03412307426333427</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.0344420000910759</c:v>
+                  <c:v>0.03412307426333427</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.03131090849637985</c:v>
+                  <c:v>0.03412307426333427</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.02974536456167698</c:v>
+                  <c:v>0.03102097846567631</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.02974536456167698</c:v>
+                  <c:v>0.02946992963552475</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.02817981876432896</c:v>
+                  <c:v>0.02946992963552475</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.02817981876432896</c:v>
+                  <c:v>0.02791888080537319</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02817981876432896</c:v>
+                  <c:v>0.02791888080537319</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02817981876432896</c:v>
+                  <c:v>0.02791888080537319</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02504872716963291</c:v>
+                  <c:v>0.02791888080537319</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.02504872716963291</c:v>
+                  <c:v>0.02481678314507008</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.02504872716963291</c:v>
+                  <c:v>0.02481678314507008</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.02504872716963291</c:v>
+                  <c:v>0.02481678314507008</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.02348318137228489</c:v>
+                  <c:v>0.02481678314507008</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.02348318137228489</c:v>
+                  <c:v>0.02481678314507008</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.02035209164023399</c:v>
+                  <c:v>0.02326573431491852</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>0.02035209164023399</c:v>
+                  <c:v>0.02326573431491852</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>0.01878654584288597</c:v>
+                  <c:v>0.02016363479197025</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>0.01878654584288597</c:v>
+                  <c:v>0.02016363479197025</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>0.01252436358481646</c:v>
+                  <c:v>0.0186125859618187</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>0.006262181792408228</c:v>
+                  <c:v>0.0186125859618187</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>0.006262181792408228</c:v>
+                  <c:v>0.01240839157253504</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>0.003131090896204114</c:v>
+                  <c:v>0.006204195786267519</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>0.003131090896204114</c:v>
+                  <c:v>0.006204195786267519</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>0.003131090896204114</c:v>
+                  <c:v>0.00310209789313376</c:v>
                 </c:pt>
                 <c:pt idx="182">
-                  <c:v>0.003131090896204114</c:v>
+                  <c:v>0.00310209789313376</c:v>
                 </c:pt>
                 <c:pt idx="183">
+                  <c:v>0.00310209789313376</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.00310209789313376</c:v>
+                </c:pt>
+                <c:pt idx="185">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2305,8 +2329,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H186" totalsRowCount="1">
-  <autoFilter ref="A2:H185"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H188" totalsRowCount="1">
+  <autoFilter ref="A2:H187"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -2322,8 +2346,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H186" totalsRowCount="1">
-  <autoFilter ref="A2:H185"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H188" totalsRowCount="1">
+  <autoFilter ref="A2:H187"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2623,7 +2647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2636,28 +2660,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2665,16 +2689,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>30.81194496154785</v>
+        <v>34.56700897216797</v>
       </c>
       <c r="C3" s="1">
-        <v>19088</v>
+        <v>26768</v>
       </c>
       <c r="D3" s="1">
-        <v>2438</v>
+        <v>2442</v>
       </c>
       <c r="E3" s="1">
-        <v>2390</v>
+        <v>2394</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -2683,7 +2707,7 @@
         <v>48</v>
       </c>
       <c r="H3" s="1">
-        <v>19040</v>
+        <v>26720</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2691,7 +2715,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>26.49878883361816</v>
+        <v>21.19889450073242</v>
       </c>
       <c r="C4" s="1">
         <v>16416</v>
@@ -2717,16 +2741,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>6.611783504486084</v>
+        <v>12.92905330657959</v>
       </c>
       <c r="C5" s="1">
-        <v>4096</v>
+        <v>10012</v>
       </c>
       <c r="D5" s="1">
-        <v>960</v>
+        <v>1012</v>
       </c>
       <c r="E5" s="1">
-        <v>960</v>
+        <v>1012</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2735,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>4096</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2743,16 +2767,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>6.611783504486084</v>
+        <v>5.289392948150635</v>
       </c>
       <c r="C6" s="1">
         <v>4096</v>
       </c>
       <c r="D6" s="1">
-        <v>502</v>
+        <v>960</v>
       </c>
       <c r="E6" s="1">
-        <v>502</v>
+        <v>960</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -2769,25 +2793,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>6.056497097015381</v>
+        <v>5.289392948150635</v>
       </c>
       <c r="C7" s="1">
-        <v>3752</v>
+        <v>4096</v>
       </c>
       <c r="D7" s="1">
-        <v>2140</v>
+        <v>502</v>
       </c>
       <c r="E7" s="1">
-        <v>2136</v>
+        <v>502</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>3748</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -2795,25 +2819,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>3.609362363815308</v>
+        <v>4.845166683197022</v>
       </c>
       <c r="C8" s="1">
-        <v>2236</v>
+        <v>3752</v>
       </c>
       <c r="D8" s="1">
-        <v>996</v>
+        <v>2140</v>
       </c>
       <c r="E8" s="1">
-        <v>996</v>
+        <v>2136</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="1">
-        <v>2236</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -2821,7 +2845,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>3.383373737335205</v>
+        <v>2.706681489944458</v>
       </c>
       <c r="C9" s="1">
         <v>2096</v>
@@ -2847,7 +2871,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>3.299435138702393</v>
+        <v>2.639530897140503</v>
       </c>
       <c r="C10" s="1">
         <v>2044</v>
@@ -2873,7 +2897,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.660209894180298</v>
+        <v>2.128154039382935</v>
       </c>
       <c r="C11" s="1">
         <v>1648</v>
@@ -2899,7 +2923,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.664245367050171</v>
+        <v>1.331387639045715</v>
       </c>
       <c r="C12" s="1">
         <v>1031</v>
@@ -2925,7 +2949,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.652945876121521</v>
+        <v>1.322348237037659</v>
       </c>
       <c r="C13" s="1">
         <v>1024</v>
@@ -2951,10 +2975,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>1.155770778656006</v>
+        <v>0.9297760725021362</v>
       </c>
       <c r="C14" s="1">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D14" s="1">
         <v>108</v>
@@ -2969,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>716</v>
+        <v>720</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2977,19 +3001,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.6327683329582214</v>
+        <v>0.5062114000320435</v>
       </c>
       <c r="C15" s="1">
         <v>392</v>
       </c>
       <c r="D15" s="1">
-        <v>5506</v>
+        <v>5792</v>
       </c>
       <c r="E15" s="1">
-        <v>5010</v>
+        <v>5292</v>
       </c>
       <c r="F15" s="1">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G15" s="1">
         <v>28</v>
@@ -3003,7 +3027,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.5746569633483887</v>
+        <v>0.4597226083278656</v>
       </c>
       <c r="C16" s="1">
         <v>356</v>
@@ -3029,7 +3053,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.5488296747207642</v>
+        <v>0.4390609264373779</v>
       </c>
       <c r="C17" s="1">
         <v>340</v>
@@ -3055,7 +3079,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.4842615127563477</v>
+        <v>0.3874067068099976</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -3081,7 +3105,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.4326069355010986</v>
+        <v>0.3460833132266998</v>
       </c>
       <c r="C19" s="1">
         <v>268</v>
@@ -3107,7 +3131,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.3680387437343597</v>
+        <v>0.2944290935993195</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -3133,7 +3157,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.3615819215774536</v>
+        <v>0.2892636656761169</v>
       </c>
       <c r="C21" s="1">
         <v>224</v>
@@ -3159,7 +3183,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.329297810792923</v>
+        <v>0.2634365558624268</v>
       </c>
       <c r="C22" s="1">
         <v>204</v>
@@ -3185,7 +3209,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.3228409886360169</v>
+        <v>0.2582711279392242</v>
       </c>
       <c r="C23" s="1">
         <v>200</v>
@@ -3211,7 +3235,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2130750566720963</v>
+        <v>0.1704589426517487</v>
       </c>
       <c r="C24" s="1">
         <v>132</v>
@@ -3237,7 +3261,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2066182345151901</v>
+        <v>0.1652935296297073</v>
       </c>
       <c r="C25" s="1">
         <v>128</v>
@@ -3263,7 +3287,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.1614204943180084</v>
+        <v>0.1291355639696121</v>
       </c>
       <c r="C26" s="1">
         <v>100</v>
@@ -3289,7 +3313,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1355932205915451</v>
+        <v>0.1084738746285439</v>
       </c>
       <c r="C27" s="1">
         <v>84</v>
@@ -3315,7 +3339,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1226795837283135</v>
+        <v>0.09814303368330002</v>
       </c>
       <c r="C28" s="1">
         <v>76</v>
@@ -3341,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.1162227615714073</v>
+        <v>0.0929776057600975</v>
       </c>
       <c r="C29" s="1">
         <v>72</v>
@@ -3367,7 +3391,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1162227615714073</v>
+        <v>0.0929776057600975</v>
       </c>
       <c r="C30" s="1">
         <v>72</v>
@@ -3393,7 +3417,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.1162227615714073</v>
+        <v>0.0929776057600975</v>
       </c>
       <c r="C31" s="1">
         <v>72</v>
@@ -3419,7 +3443,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.1097659394145012</v>
+        <v>0.08781218528747559</v>
       </c>
       <c r="C32" s="1">
         <v>68</v>
@@ -3445,7 +3469,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.1033091172575951</v>
+        <v>0.08264676481485367</v>
       </c>
       <c r="C33" s="1">
         <v>64</v>
@@ -3471,7 +3495,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.07102502137422562</v>
+        <v>0.05681964755058289</v>
       </c>
       <c r="C34" s="1">
         <v>44</v>
@@ -3497,7 +3521,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.06456819921731949</v>
+        <v>0.05165422707796097</v>
       </c>
       <c r="C35" s="1">
         <v>40</v>
@@ -3523,7 +3547,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.05811138078570366</v>
+        <v>0.04648880288004875</v>
       </c>
       <c r="C36" s="1">
         <v>36</v>
@@ -3549,7 +3573,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.05165455862879753</v>
+        <v>0.04132338240742683</v>
       </c>
       <c r="C37" s="1">
         <v>32</v>
@@ -3575,7 +3599,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.05165455862879753</v>
+        <v>0.04132338240742683</v>
       </c>
       <c r="C38" s="1">
         <v>32</v>
@@ -3601,25 +3625,25 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03228409960865974</v>
+        <v>0.03615795820951462</v>
       </c>
       <c r="C39" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D39" s="1">
-        <v>192</v>
+        <v>1388</v>
       </c>
       <c r="E39" s="1">
-        <v>192</v>
+        <v>1360</v>
       </c>
       <c r="F39" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G39" s="1">
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3627,25 +3651,25 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.03228409960865974</v>
+        <v>0.02582711353898048</v>
       </c>
       <c r="C40" s="1">
         <v>20</v>
       </c>
       <c r="D40" s="1">
-        <v>1188</v>
+        <v>192</v>
       </c>
       <c r="E40" s="1">
-        <v>1168</v>
+        <v>192</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1">
+        <v>0</v>
+      </c>
+      <c r="H40" s="1">
         <v>20</v>
-      </c>
-      <c r="H40" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3653,22 +3677,22 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.01937046088278294</v>
+        <v>0.02582711353898048</v>
       </c>
       <c r="C41" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D41" s="1">
-        <v>142</v>
+        <v>1176</v>
       </c>
       <c r="E41" s="1">
-        <v>130</v>
+        <v>1156</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H41" s="1">
         <v>0</v>
@@ -3679,16 +3703,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.01937046088278294</v>
+        <v>0.01549626793712378</v>
       </c>
       <c r="C42" s="1">
         <v>12</v>
       </c>
       <c r="D42" s="1">
-        <v>798</v>
+        <v>142</v>
       </c>
       <c r="E42" s="1">
-        <v>786</v>
+        <v>130</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -3705,19 +3729,19 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.01937046088278294</v>
+        <v>0.01549626793712378</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
       </c>
       <c r="D43" s="1">
-        <v>126</v>
+        <v>798</v>
       </c>
       <c r="E43" s="1">
-        <v>102</v>
+        <v>786</v>
       </c>
       <c r="F43" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
         <v>12</v>
@@ -3731,16 +3755,16 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.01937046088278294</v>
+        <v>0.01549626793712378</v>
       </c>
       <c r="C44" s="1">
         <v>12</v>
       </c>
       <c r="D44" s="1">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="E44" s="1">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="F44" s="1">
         <v>12</v>
@@ -3757,22 +3781,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01291363965719938</v>
+        <v>0.01549626793712378</v>
       </c>
       <c r="C45" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D45" s="1">
-        <v>2874</v>
+        <v>172</v>
       </c>
       <c r="E45" s="1">
-        <v>2866</v>
+        <v>148</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G45" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -3783,16 +3807,16 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01291363965719938</v>
+        <v>0.01033084560185671</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
       </c>
       <c r="D46" s="1">
-        <v>426</v>
+        <v>2874</v>
       </c>
       <c r="E46" s="1">
-        <v>418</v>
+        <v>2866</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3809,19 +3833,19 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01291363965719938</v>
+        <v>0.01033084560185671</v>
       </c>
       <c r="C47" s="1">
         <v>8</v>
       </c>
       <c r="D47" s="1">
-        <v>54</v>
+        <v>426</v>
       </c>
       <c r="E47" s="1">
-        <v>34</v>
+        <v>418</v>
       </c>
       <c r="F47" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1">
         <v>8</v>
@@ -3835,22 +3859,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.006456819828599691</v>
+        <v>0.01033084560185671</v>
       </c>
       <c r="C48" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D48" s="1">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="E48" s="1">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F48" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G48" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H48" s="1">
         <v>0</v>
@@ -3861,16 +3885,16 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.006456819828599691</v>
+        <v>0.005165422800928354</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
       </c>
       <c r="D49" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E49" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3887,19 +3911,19 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.006456819828599691</v>
+        <v>0.005165422800928354</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
       </c>
       <c r="D50" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E50" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
         <v>4</v>
@@ -3913,19 +3937,19 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.006456819828599691</v>
+        <v>0.005165422800928354</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
       </c>
       <c r="D51" s="1">
-        <v>1718</v>
+        <v>44</v>
       </c>
       <c r="E51" s="1">
-        <v>1378</v>
+        <v>16</v>
       </c>
       <c r="F51" s="1">
-        <v>336</v>
+        <v>24</v>
       </c>
       <c r="G51" s="1">
         <v>4</v>
@@ -3939,19 +3963,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.006456819828599691</v>
+        <v>0.005165422800928354</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
       </c>
       <c r="D52" s="1">
-        <v>272</v>
+        <v>1760</v>
       </c>
       <c r="E52" s="1">
-        <v>268</v>
+        <v>1420</v>
       </c>
       <c r="F52" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G52" s="1">
         <v>4</v>
@@ -3965,16 +3989,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.006456819828599691</v>
+        <v>0.005165422800928354</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
       </c>
       <c r="D53" s="1">
-        <v>502</v>
+        <v>272</v>
       </c>
       <c r="E53" s="1">
-        <v>498</v>
+        <v>268</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3991,19 +4015,19 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.006456819828599691</v>
+        <v>0.005165422800928354</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
       </c>
       <c r="D54" s="1">
-        <v>84</v>
+        <v>502</v>
       </c>
       <c r="E54" s="1">
-        <v>48</v>
+        <v>498</v>
       </c>
       <c r="F54" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1">
         <v>4</v>
@@ -4017,56 +4041,82 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.004842615220695734</v>
+        <v>0.005165422800928354</v>
       </c>
       <c r="C55" s="1">
+        <v>4</v>
+      </c>
+      <c r="D55" s="1">
+        <v>84</v>
+      </c>
+      <c r="E55" s="1">
+        <v>48</v>
+      </c>
+      <c r="F55" s="1">
+        <v>32</v>
+      </c>
+      <c r="G55" s="1">
+        <v>4</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.003874066984280944</v>
+      </c>
+      <c r="C56" s="1">
         <v>3</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D56" s="1">
         <v>1011</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E56" s="1">
         <v>1008</v>
       </c>
-      <c r="F55" s="1">
-        <v>0</v>
-      </c>
-      <c r="G55" s="1">
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
         <v>3</v>
       </c>
-      <c r="H55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8">
-      <c r="A186" t="s">
-        <v>185</v>
-      </c>
-      <c r="B186">
+      <c r="H56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" t="s">
+        <v>187</v>
+      </c>
+      <c r="B188">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C186">
+      <c r="C188">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D186">
+      <c r="D188">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E186">
+      <c r="E188">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F186">
+      <c r="F188">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G186">
+      <c r="G188">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H186">
+      <c r="H188">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -4082,7 +4132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -4095,28 +4145,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" t="s">
         <v>193</v>
       </c>
-      <c r="C2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G2" t="s">
-        <v>191</v>
-      </c>
       <c r="H2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4124,19 +4174,19 @@
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>4.309946537017822</v>
+        <v>4.491837501525879</v>
       </c>
       <c r="C3" s="1">
-        <v>5506</v>
+        <v>5792</v>
       </c>
       <c r="D3" s="1">
         <v>392</v>
       </c>
       <c r="E3" s="1">
-        <v>5010</v>
+        <v>5292</v>
       </c>
       <c r="F3" s="1">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G3" s="1">
         <v>28</v>
@@ -4147,10 +4197,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2">
-        <v>3.852807521820068</v>
+        <v>3.817131280899048</v>
       </c>
       <c r="C4" s="1">
         <v>4922</v>
@@ -4173,10 +4223,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2">
-        <v>3.710342884063721</v>
+        <v>3.675985813140869</v>
       </c>
       <c r="C5" s="1">
         <v>4740</v>
@@ -4202,7 +4252,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>3.326784133911133</v>
+        <v>3.295979022979736</v>
       </c>
       <c r="C6" s="1">
         <v>4250</v>
@@ -4225,10 +4275,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2">
-        <v>3.063772439956665</v>
+        <v>3.035402774810791</v>
       </c>
       <c r="C7" s="1">
         <v>3914</v>
@@ -4251,10 +4301,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="2">
-        <v>2.880603790283203</v>
+        <v>2.853929996490479</v>
       </c>
       <c r="C8" s="1">
         <v>3680</v>
@@ -4277,10 +4327,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2">
-        <v>2.594108819961548</v>
+        <v>2.570087909698486</v>
       </c>
       <c r="C9" s="1">
         <v>3314</v>
@@ -4303,10 +4353,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2">
-        <v>2.497045040130615</v>
+        <v>2.473922967910767</v>
       </c>
       <c r="C10" s="1">
         <v>3190</v>
@@ -4329,25 +4379,25 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B11" s="2">
-        <v>2.249688863754273</v>
+        <v>2.238163471221924</v>
       </c>
       <c r="C11" s="1">
-        <v>2874</v>
+        <v>2886</v>
       </c>
       <c r="D11" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>2866</v>
+        <v>2538</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="G11" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -4355,25 +4405,25 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2">
-        <v>2.230902194976807</v>
+        <v>2.228857278823853</v>
       </c>
       <c r="C12" s="1">
-        <v>2850</v>
+        <v>2874</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1">
-        <v>2506</v>
+        <v>2866</v>
       </c>
       <c r="F12" s="1">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -4384,16 +4434,16 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>1.908399939537048</v>
+        <v>1.89383065700531</v>
       </c>
       <c r="C13" s="1">
-        <v>2438</v>
+        <v>2442</v>
       </c>
       <c r="D13" s="1">
-        <v>19088</v>
+        <v>26768</v>
       </c>
       <c r="E13" s="1">
-        <v>2390</v>
+        <v>2394</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -4402,15 +4452,15 @@
         <v>48</v>
       </c>
       <c r="H13" s="1">
-        <v>19040</v>
+        <v>26720</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2">
-        <v>1.878654599189758</v>
+        <v>1.861258625984192</v>
       </c>
       <c r="C14" s="1">
         <v>2400</v>
@@ -4433,10 +4483,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2">
-        <v>1.841081500053406</v>
+        <v>1.824033498764038</v>
       </c>
       <c r="C15" s="1">
         <v>2352</v>
@@ -4459,10 +4509,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2">
-        <v>1.837950348854065</v>
+        <v>1.820931434631348</v>
       </c>
       <c r="C16" s="1">
         <v>2348</v>
@@ -4488,7 +4538,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>1.834819316864014</v>
+        <v>1.817829251289368</v>
       </c>
       <c r="C17" s="1">
         <v>2344</v>
@@ -4511,10 +4561,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2">
-        <v>1.736189961433411</v>
+        <v>1.720113277435303</v>
       </c>
       <c r="C18" s="1">
         <v>2218</v>
@@ -4537,10 +4587,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2">
-        <v>1.681395888328552</v>
+        <v>1.665826559066773</v>
       </c>
       <c r="C19" s="1">
         <v>2148</v>
@@ -4563,10 +4613,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>1.67513370513916</v>
+        <v>1.659622311592102</v>
       </c>
       <c r="C20" s="1">
         <v>2140</v>
@@ -4589,10 +4639,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2">
-        <v>1.606249690055847</v>
+        <v>1.591376185417175</v>
       </c>
       <c r="C21" s="1">
         <v>2052</v>
@@ -4615,10 +4665,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22" s="2">
-        <v>1.531103491783142</v>
+        <v>1.516925811767578</v>
       </c>
       <c r="C22" s="1">
         <v>1956</v>
@@ -4641,10 +4691,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="2">
-        <v>1.521710157394409</v>
+        <v>1.507619500160217</v>
       </c>
       <c r="C23" s="1">
         <v>1944</v>
@@ -4667,19 +4717,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="2">
-        <v>1.487268209457398</v>
+        <v>1.49055802822113</v>
       </c>
       <c r="C24" s="1">
-        <v>1900</v>
+        <v>1922</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1900</v>
+        <v>1922</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -4693,19 +4743,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="2">
-        <v>1.413687586784363</v>
+        <v>1.473496437072754</v>
       </c>
       <c r="C25" s="1">
-        <v>1806</v>
+        <v>1900</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>1806</v>
+        <v>1900</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -4719,25 +4769,25 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="B26" s="2">
-        <v>1.34480357170105</v>
+        <v>1.400597095489502</v>
       </c>
       <c r="C26" s="1">
-        <v>1718</v>
+        <v>1806</v>
       </c>
       <c r="D26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>1378</v>
+        <v>1806</v>
       </c>
       <c r="F26" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -4745,25 +4795,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>1.308796048164368</v>
+        <v>1.364923000335693</v>
       </c>
       <c r="C27" s="1">
-        <v>1672</v>
+        <v>1760</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27" s="1">
-        <v>1672</v>
+        <v>1420</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -4771,10 +4821,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B28" s="2">
-        <v>1.258698582649231</v>
+        <v>1.247043371200562</v>
       </c>
       <c r="C28" s="1">
         <v>1608</v>
@@ -4800,7 +4850,7 @@
         <v>17</v>
       </c>
       <c r="B29" s="2">
-        <v>1.25556743144989</v>
+        <v>1.243941187858582</v>
       </c>
       <c r="C29" s="1">
         <v>1604</v>
@@ -4823,10 +4873,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="2">
-        <v>1.142848253250122</v>
+        <v>1.132265686988831</v>
       </c>
       <c r="C30" s="1">
         <v>1460</v>
@@ -4852,7 +4902,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="2">
-        <v>1.125627160072327</v>
+        <v>1.115204215049744</v>
       </c>
       <c r="C31" s="1">
         <v>1438</v>
@@ -4875,10 +4925,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" s="2">
-        <v>1.091185212135315</v>
+        <v>1.081081032752991</v>
       </c>
       <c r="C32" s="1">
         <v>1394</v>
@@ -4901,28 +4951,28 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2">
-        <v>0.9769003987312317</v>
+        <v>1.076427936553955</v>
       </c>
       <c r="C33" s="1">
-        <v>1248</v>
+        <v>1388</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E33" s="1">
-        <v>1248</v>
+        <v>1360</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -4930,16 +4980,16 @@
         <v>76</v>
       </c>
       <c r="B34" s="2">
-        <v>0.9549827575683594</v>
+        <v>0.9678544998168945</v>
       </c>
       <c r="C34" s="1">
-        <v>1220</v>
+        <v>1248</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>1220</v>
+        <v>1248</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -4956,16 +5006,16 @@
         <v>77</v>
       </c>
       <c r="B35" s="2">
-        <v>0.9393272995948792</v>
+        <v>0.9461398124694824</v>
       </c>
       <c r="C35" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -4982,19 +5032,19 @@
         <v>78</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9361962080001831</v>
+        <v>0.941486656665802</v>
       </c>
       <c r="C36" s="1">
-        <v>1196</v>
+        <v>1214</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>1168</v>
+        <v>1214</v>
       </c>
       <c r="F36" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -5005,19 +5055,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="2">
-        <v>0.929934024810791</v>
+        <v>0.912016749382019</v>
       </c>
       <c r="C37" s="1">
-        <v>1188</v>
+        <v>1176</v>
       </c>
       <c r="D37" s="1">
         <v>20</v>
       </c>
       <c r="E37" s="1">
-        <v>1168</v>
+        <v>1156</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -5034,7 +5084,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="2">
-        <v>0.9001886248588562</v>
+        <v>0.8918530941009522</v>
       </c>
       <c r="C38" s="1">
         <v>1150</v>
@@ -5060,7 +5110,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8469601273536682</v>
+        <v>0.8391174674034119</v>
       </c>
       <c r="C39" s="1">
         <v>1082</v>
@@ -5086,7 +5136,7 @@
         <v>28</v>
       </c>
       <c r="B40" s="2">
-        <v>0.8046903610229492</v>
+        <v>0.7972391247749329</v>
       </c>
       <c r="C40" s="1">
         <v>1028</v>
@@ -5109,51 +5159,51 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="B41" s="2">
-        <v>0.7913832664489746</v>
+        <v>0.7848307490348816</v>
       </c>
       <c r="C41" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D41" s="1">
-        <v>3</v>
+        <v>10012</v>
       </c>
       <c r="E41" s="1">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>10012</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7827727198600769</v>
+        <v>0.784055233001709</v>
       </c>
       <c r="C42" s="1">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E42" s="1">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -5161,19 +5211,19 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="B43" s="2">
-        <v>0.7796416282653809</v>
+        <v>0.7755244374275208</v>
       </c>
       <c r="C43" s="1">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D43" s="1">
-        <v>2236</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -5182,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>2236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5190,7 +5240,7 @@
         <v>29</v>
       </c>
       <c r="B44" s="2">
-        <v>0.759289562702179</v>
+        <v>0.7522587180137634</v>
       </c>
       <c r="C44" s="1">
         <v>970</v>
@@ -5213,10 +5263,10 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7514618039131165</v>
+        <v>0.7445034980773926</v>
       </c>
       <c r="C45" s="1">
         <v>960</v>
@@ -5242,7 +5292,7 @@
         <v>80</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7483307123184204</v>
+        <v>0.7414013743400574</v>
       </c>
       <c r="C46" s="1">
         <v>956</v>
@@ -5268,7 +5318,7 @@
         <v>7</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7311097383499146</v>
+        <v>0.7243398427963257</v>
       </c>
       <c r="C47" s="1">
         <v>934</v>
@@ -5294,16 +5344,16 @@
         <v>81</v>
       </c>
       <c r="B48" s="2">
-        <v>0.666922390460968</v>
+        <v>0.6700531244277954</v>
       </c>
       <c r="C48" s="1">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -5320,16 +5370,16 @@
         <v>82</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6653568148612976</v>
+        <v>0.6607468128204346</v>
       </c>
       <c r="C49" s="1">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -5346,16 +5396,16 @@
         <v>83</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6512669324874878</v>
+        <v>0.6591957807540894</v>
       </c>
       <c r="C50" s="1">
-        <v>832</v>
+        <v>850</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>832</v>
+        <v>850</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -5372,7 +5422,7 @@
         <v>9</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6418736577033997</v>
+        <v>0.635930061340332</v>
       </c>
       <c r="C51" s="1">
         <v>820</v>
@@ -5395,10 +5445,10 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B52" s="2">
-        <v>0.624652624130249</v>
+        <v>0.6188685297966003</v>
       </c>
       <c r="C52" s="1">
         <v>798</v>
@@ -5424,7 +5474,7 @@
         <v>84</v>
       </c>
       <c r="B53" s="2">
-        <v>0.6136938333511353</v>
+        <v>0.6080111861228943</v>
       </c>
       <c r="C53" s="1">
         <v>784</v>
@@ -5450,7 +5500,7 @@
         <v>18</v>
       </c>
       <c r="B54" s="2">
-        <v>0.5917761921882629</v>
+        <v>0.5862964987754822</v>
       </c>
       <c r="C54" s="1">
         <v>756</v>
@@ -5476,7 +5526,7 @@
         <v>85</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5667274594306946</v>
+        <v>0.5614796876907349</v>
       </c>
       <c r="C55" s="1">
         <v>724</v>
@@ -5502,7 +5552,7 @@
         <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5635963678359985</v>
+        <v>0.5583776235580444</v>
       </c>
       <c r="C56" s="1">
         <v>720</v>
@@ -5528,7 +5578,7 @@
         <v>87</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5354165434837341</v>
+        <v>0.5304587483406067</v>
       </c>
       <c r="C57" s="1">
         <v>684</v>
@@ -5554,7 +5604,7 @@
         <v>36</v>
       </c>
       <c r="B58" s="2">
-        <v>0.5150644779205322</v>
+        <v>0.5102950930595398</v>
       </c>
       <c r="C58" s="1">
         <v>658</v>
@@ -5580,7 +5630,7 @@
         <v>88</v>
       </c>
       <c r="B59" s="2">
-        <v>0.5041056275367737</v>
+        <v>0.4994377493858337</v>
       </c>
       <c r="C59" s="1">
         <v>644</v>
@@ -5606,7 +5656,7 @@
         <v>8</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4853191077709198</v>
+        <v>0.4808251559734345</v>
       </c>
       <c r="C60" s="1">
         <v>620</v>
@@ -5632,7 +5682,7 @@
         <v>89</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4837535619735718</v>
+        <v>0.4792741239070892</v>
       </c>
       <c r="C61" s="1">
         <v>618</v>
@@ -5658,7 +5708,7 @@
         <v>90</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4477460086345673</v>
+        <v>0.4435999989509583</v>
       </c>
       <c r="C62" s="1">
         <v>572</v>
@@ -5684,7 +5734,7 @@
         <v>91</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4352216422557831</v>
+        <v>0.4311915934085846</v>
       </c>
       <c r="C63" s="1">
         <v>556</v>
@@ -5710,7 +5760,7 @@
         <v>20</v>
       </c>
       <c r="B64" s="2">
-        <v>0.428959459066391</v>
+        <v>0.424987405538559</v>
       </c>
       <c r="C64" s="1">
         <v>548</v>
@@ -5733,80 +5783,80 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4007796347141266</v>
+        <v>0.4218853116035461</v>
       </c>
       <c r="C65" s="1">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="D65" s="1">
-        <v>16416</v>
+        <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="G65" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>16384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B66" s="2">
-        <v>0.3976485431194305</v>
+        <v>0.3970685303211212</v>
       </c>
       <c r="C66" s="1">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D66" s="1">
-        <v>1024</v>
+        <v>16416</v>
       </c>
       <c r="E66" s="1">
-        <v>36</v>
+        <v>480</v>
       </c>
       <c r="F66" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G66" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H66" s="1">
-        <v>1024</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="B67" s="2">
-        <v>0.3945174515247345</v>
+        <v>0.393966406583786</v>
       </c>
       <c r="C67" s="1">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D67" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E67" s="1">
-        <v>312</v>
+        <v>36</v>
       </c>
       <c r="F67" s="1">
-        <v>192</v>
+        <v>472</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -5814,7 +5864,7 @@
         <v>93</v>
       </c>
       <c r="B68" s="2">
-        <v>0.3945174515247345</v>
+        <v>0.3908643126487732</v>
       </c>
       <c r="C68" s="1">
         <v>504</v>
@@ -5837,10 +5887,10 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B69" s="2">
-        <v>0.3929519057273865</v>
+        <v>0.389313280582428</v>
       </c>
       <c r="C69" s="1">
         <v>502</v>
@@ -5863,10 +5913,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3929519057273865</v>
+        <v>0.389313280582428</v>
       </c>
       <c r="C70" s="1">
         <v>502</v>
@@ -5892,7 +5942,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3898208141326904</v>
+        <v>0.3862111866474152</v>
       </c>
       <c r="C71" s="1">
         <v>498</v>
@@ -5918,16 +5968,16 @@
         <v>94</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3725998103618622</v>
+        <v>0.3707006871700287</v>
       </c>
       <c r="C72" s="1">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -5944,16 +5994,16 @@
         <v>95</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3663376271724701</v>
+        <v>0.3691496253013611</v>
       </c>
       <c r="C73" s="1">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -5967,25 +6017,25 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3569443821907044</v>
+        <v>0.3629454374313355</v>
       </c>
       <c r="C74" s="1">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="D74" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -5993,25 +6043,25 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3506821990013123</v>
+        <v>0.353639155626297</v>
       </c>
       <c r="C75" s="1">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D75" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E75" s="1">
-        <v>384</v>
+        <v>424</v>
       </c>
       <c r="F75" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -6022,19 +6072,19 @@
         <v>97</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3491166532039642</v>
+        <v>0.3474349677562714</v>
       </c>
       <c r="C76" s="1">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>446</v>
+        <v>384</v>
       </c>
       <c r="F76" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
@@ -6048,7 +6098,7 @@
         <v>98</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3381578326225281</v>
+        <v>0.3350265622138977</v>
       </c>
       <c r="C77" s="1">
         <v>432</v>
@@ -6074,7 +6124,7 @@
         <v>99</v>
       </c>
       <c r="B78" s="2">
-        <v>0.333461195230484</v>
+        <v>0.3303734064102173</v>
       </c>
       <c r="C78" s="1">
         <v>426</v>
@@ -6097,10 +6147,10 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B79" s="2">
-        <v>0.333461195230484</v>
+        <v>0.3303734064102173</v>
       </c>
       <c r="C79" s="1">
         <v>426</v>
@@ -6126,7 +6176,7 @@
         <v>100</v>
       </c>
       <c r="B80" s="2">
-        <v>0.3209368288516998</v>
+        <v>0.317965030670166</v>
       </c>
       <c r="C80" s="1">
         <v>410</v>
@@ -6152,7 +6202,7 @@
         <v>101</v>
       </c>
       <c r="B81" s="2">
-        <v>0.3209368288516998</v>
+        <v>0.317965030670166</v>
       </c>
       <c r="C81" s="1">
         <v>410</v>
@@ -6178,7 +6228,7 @@
         <v>32</v>
       </c>
       <c r="B82" s="2">
-        <v>0.3193712830543518</v>
+        <v>0.3164139688014984</v>
       </c>
       <c r="C82" s="1">
         <v>408</v>
@@ -6204,7 +6254,7 @@
         <v>102</v>
       </c>
       <c r="B83" s="2">
-        <v>0.3131090998649597</v>
+        <v>0.3102097809314728</v>
       </c>
       <c r="C83" s="1">
         <v>400</v>
@@ -6230,7 +6280,7 @@
         <v>27</v>
       </c>
       <c r="B84" s="2">
-        <v>0.3131090998649597</v>
+        <v>0.3102097809314728</v>
       </c>
       <c r="C84" s="1">
         <v>400</v>
@@ -6256,7 +6306,7 @@
         <v>103</v>
       </c>
       <c r="B85" s="2">
-        <v>0.2911914587020874</v>
+        <v>0.2884950935840607</v>
       </c>
       <c r="C85" s="1">
         <v>372</v>
@@ -6282,7 +6332,7 @@
         <v>104</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2864948213100433</v>
+        <v>0.2838419377803803</v>
       </c>
       <c r="C86" s="1">
         <v>366</v>
@@ -6308,7 +6358,7 @@
         <v>15</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2692738175392151</v>
+        <v>0.2667804062366486</v>
       </c>
       <c r="C87" s="1">
         <v>344</v>
@@ -6334,7 +6384,7 @@
         <v>105</v>
       </c>
       <c r="B88" s="2">
-        <v>0.263011634349823</v>
+        <v>0.2605762183666229</v>
       </c>
       <c r="C88" s="1">
         <v>336</v>
@@ -6360,7 +6410,7 @@
         <v>106</v>
       </c>
       <c r="B89" s="2">
-        <v>0.261446088552475</v>
+        <v>0.2590251564979553</v>
       </c>
       <c r="C89" s="1">
         <v>334</v>
@@ -6386,7 +6436,7 @@
         <v>21</v>
       </c>
       <c r="B90" s="2">
-        <v>0.259880542755127</v>
+        <v>0.2574741244316101</v>
       </c>
       <c r="C90" s="1">
         <v>332</v>
@@ -6412,7 +6462,7 @@
         <v>107</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2536183595657349</v>
+        <v>0.2512699067592621</v>
       </c>
       <c r="C91" s="1">
         <v>324</v>
@@ -6438,7 +6488,7 @@
         <v>108</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2410940080881119</v>
+        <v>0.2388615310192108</v>
       </c>
       <c r="C92" s="1">
         <v>308</v>
@@ -6464,7 +6514,7 @@
         <v>30</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2285696417093277</v>
+        <v>0.2264531403779984</v>
       </c>
       <c r="C93" s="1">
         <v>292</v>
@@ -6487,10 +6537,10 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2129141837358475</v>
+        <v>0.2109426558017731</v>
       </c>
       <c r="C94" s="1">
         <v>272</v>
@@ -6516,7 +6566,7 @@
         <v>109</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2129141837358475</v>
+        <v>0.2109426558017731</v>
       </c>
       <c r="C95" s="1">
         <v>272</v>
@@ -6542,7 +6592,7 @@
         <v>25</v>
       </c>
       <c r="B96" s="2">
-        <v>0.1972587257623673</v>
+        <v>0.1954321563243866</v>
       </c>
       <c r="C96" s="1">
         <v>252</v>
@@ -6568,7 +6618,7 @@
         <v>110</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1925620883703232</v>
+        <v>0.1907790154218674</v>
       </c>
       <c r="C97" s="1">
         <v>246</v>
@@ -6594,7 +6644,7 @@
         <v>19</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1894309967756271</v>
+        <v>0.1876769214868546</v>
       </c>
       <c r="C98" s="1">
         <v>242</v>
@@ -6620,7 +6670,7 @@
         <v>111</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1878654509782791</v>
+        <v>0.1861258745193481</v>
       </c>
       <c r="C99" s="1">
         <v>240</v>
@@ -6646,7 +6696,7 @@
         <v>112</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1831688135862351</v>
+        <v>0.1814727187156677</v>
       </c>
       <c r="C100" s="1">
         <v>234</v>
@@ -6672,7 +6722,7 @@
         <v>113</v>
       </c>
       <c r="B101" s="2">
-        <v>0.181603267788887</v>
+        <v>0.1799216717481613</v>
       </c>
       <c r="C101" s="1">
         <v>232</v>
@@ -6698,7 +6748,7 @@
         <v>114</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1784721910953522</v>
+        <v>0.1768195778131485</v>
       </c>
       <c r="C102" s="1">
         <v>228</v>
@@ -6724,7 +6774,7 @@
         <v>24</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1784721910953522</v>
+        <v>0.1768195778131485</v>
       </c>
       <c r="C103" s="1">
         <v>228</v>
@@ -6750,7 +6800,7 @@
         <v>115</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1737755537033081</v>
+        <v>0.1721664220094681</v>
       </c>
       <c r="C104" s="1">
         <v>222</v>
@@ -6776,16 +6826,16 @@
         <v>116</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1722100079059601</v>
+        <v>0.1721664220094681</v>
       </c>
       <c r="C105" s="1">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
       </c>
       <c r="E105" s="1">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F105" s="1">
         <v>0</v>
@@ -6802,7 +6852,7 @@
         <v>117</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1722100079059601</v>
+        <v>0.1706153750419617</v>
       </c>
       <c r="C106" s="1">
         <v>220</v>
@@ -6811,10 +6861,10 @@
         <v>0</v>
       </c>
       <c r="E106" s="1">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="F106" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G106" s="1">
         <v>0</v>
@@ -6825,45 +6875,45 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1502923667430878</v>
+        <v>0.1706153750419617</v>
       </c>
       <c r="C107" s="1">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="D107" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E107" s="1">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="F107" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G107" s="1">
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1471612751483917</v>
+        <v>0.1489006876945496</v>
       </c>
       <c r="C108" s="1">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D108" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E108" s="1">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -6872,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="H108" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -6880,16 +6930,16 @@
         <v>119</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1455957293510437</v>
+        <v>0.1457985937595367</v>
       </c>
       <c r="C109" s="1">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -6906,16 +6956,16 @@
         <v>120</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1377680003643036</v>
+        <v>0.1442475467920303</v>
       </c>
       <c r="C110" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -6932,7 +6982,7 @@
         <v>121</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1377680003643036</v>
+        <v>0.1364922970533371</v>
       </c>
       <c r="C111" s="1">
         <v>176</v>
@@ -6955,25 +7005,25 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1346369087696075</v>
+        <v>0.1364922970533371</v>
       </c>
       <c r="C112" s="1">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D112" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="F112" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
@@ -6981,25 +7031,25 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B113" s="2">
-        <v>0.123678095638752</v>
+        <v>0.1333902031183243</v>
       </c>
       <c r="C113" s="1">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="D113" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E113" s="1">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F113" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G113" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -7010,16 +7060,16 @@
         <v>123</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1205470040440559</v>
+        <v>0.1225328594446182</v>
       </c>
       <c r="C114" s="1">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -7036,16 +7086,16 @@
         <v>124</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1189814582467079</v>
+        <v>0.1194307655096054</v>
       </c>
       <c r="C115" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -7062,16 +7112,16 @@
         <v>125</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1127192750573158</v>
+        <v>0.117879718542099</v>
       </c>
       <c r="C116" s="1">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="D116" s="1">
         <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
@@ -7085,25 +7135,25 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1111537292599678</v>
+        <v>0.1116755232214928</v>
       </c>
       <c r="C117" s="1">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D117" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E117" s="1">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
       </c>
       <c r="G117" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
@@ -7111,25 +7161,25 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1080226376652718</v>
+        <v>0.1101244688034058</v>
       </c>
       <c r="C118" s="1">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D118" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E118" s="1">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
       </c>
       <c r="G118" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
@@ -7137,19 +7187,19 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1064570918679237</v>
+        <v>0.1070223748683929</v>
       </c>
       <c r="C119" s="1">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D119" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E119" s="1">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -7158,24 +7208,24 @@
         <v>0</v>
       </c>
       <c r="H119" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="B120" s="2">
-        <v>0.1001949086785317</v>
+        <v>0.1054713279008865</v>
       </c>
       <c r="C120" s="1">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D120" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E120" s="1">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -7184,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -7192,7 +7242,7 @@
         <v>128</v>
       </c>
       <c r="B121" s="2">
-        <v>0.1001949086785317</v>
+        <v>0.0992671325802803</v>
       </c>
       <c r="C121" s="1">
         <v>128</v>
@@ -7218,16 +7268,16 @@
         <v>129</v>
       </c>
       <c r="B122" s="2">
-        <v>0.09862936288118362</v>
+        <v>0.0992671325802803</v>
       </c>
       <c r="C122" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D122" s="1">
         <v>0</v>
       </c>
       <c r="E122" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -7244,16 +7294,16 @@
         <v>130</v>
       </c>
       <c r="B123" s="2">
-        <v>0.09862936288118362</v>
+        <v>0.0992671325802803</v>
       </c>
       <c r="C123" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -7267,25 +7317,25 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="B124" s="2">
-        <v>0.09862936288118362</v>
+        <v>0.0977160781621933</v>
       </c>
       <c r="C124" s="1">
         <v>126</v>
       </c>
       <c r="D124" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E124" s="1">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="F124" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G124" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
@@ -7293,45 +7343,45 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="B125" s="2">
-        <v>0.09393272548913956</v>
+        <v>0.0977160781621933</v>
       </c>
       <c r="C125" s="1">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D125" s="1">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="E125" s="1">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F125" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G125" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H125" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="B126" s="2">
-        <v>0.08923609554767609</v>
+        <v>0.09306293725967407</v>
       </c>
       <c r="C126" s="1">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D126" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E126" s="1">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -7340,7 +7390,7 @@
         <v>0</v>
       </c>
       <c r="H126" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -7348,16 +7398,16 @@
         <v>132</v>
       </c>
       <c r="B127" s="2">
-        <v>0.08767054975032806</v>
+        <v>0.08996083587408066</v>
       </c>
       <c r="C127" s="1">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -7374,16 +7424,16 @@
         <v>133</v>
       </c>
       <c r="B128" s="2">
-        <v>0.08767054975032806</v>
+        <v>0.08840978890657425</v>
       </c>
       <c r="C128" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -7400,7 +7450,7 @@
         <v>134</v>
       </c>
       <c r="B129" s="2">
-        <v>0.08767054975032806</v>
+        <v>0.08685874193906784</v>
       </c>
       <c r="C129" s="1">
         <v>112</v>
@@ -7426,16 +7476,16 @@
         <v>135</v>
       </c>
       <c r="B130" s="2">
-        <v>0.08610500395298004</v>
+        <v>0.08685874193906784</v>
       </c>
       <c r="C130" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -7452,16 +7502,16 @@
         <v>136</v>
       </c>
       <c r="B131" s="2">
-        <v>0.08453945815563202</v>
+        <v>0.08530768752098084</v>
       </c>
       <c r="C131" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -7475,16 +7525,16 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="B132" s="2">
-        <v>0.08453945815563202</v>
+        <v>0.08375664055347443</v>
       </c>
       <c r="C132" s="1">
         <v>108</v>
       </c>
       <c r="D132" s="1">
-        <v>716</v>
+        <v>0</v>
       </c>
       <c r="E132" s="1">
         <v>108</v>
@@ -7496,24 +7546,24 @@
         <v>0</v>
       </c>
       <c r="H132" s="1">
-        <v>716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="B133" s="2">
-        <v>0.07671172916889191</v>
+        <v>0.08375664055347443</v>
       </c>
       <c r="C133" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D133" s="1">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="E133" s="1">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -7522,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="1">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7530,7 +7580,7 @@
         <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07671172916889191</v>
+        <v>0.07600139826536179</v>
       </c>
       <c r="C134" s="1">
         <v>98</v>
@@ -7556,16 +7606,16 @@
         <v>139</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07201509177684784</v>
+        <v>0.07600139826536179</v>
       </c>
       <c r="C135" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D135" s="1">
         <v>0</v>
       </c>
       <c r="E135" s="1">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -7582,16 +7632,16 @@
         <v>140</v>
       </c>
       <c r="B136" s="2">
-        <v>0.06731845438480377</v>
+        <v>0.07134824991226196</v>
       </c>
       <c r="C136" s="1">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -7608,16 +7658,16 @@
         <v>141</v>
       </c>
       <c r="B137" s="2">
-        <v>0.06575290858745575</v>
+        <v>0.06669510155916214</v>
       </c>
       <c r="C137" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D137" s="1">
         <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -7634,7 +7684,7 @@
         <v>142</v>
       </c>
       <c r="B138" s="2">
-        <v>0.06575290858745575</v>
+        <v>0.06514405459165573</v>
       </c>
       <c r="C138" s="1">
         <v>84</v>
@@ -7660,7 +7710,7 @@
         <v>143</v>
       </c>
       <c r="B139" s="2">
-        <v>0.06575290858745575</v>
+        <v>0.06514405459165573</v>
       </c>
       <c r="C139" s="1">
         <v>84</v>
@@ -7683,25 +7733,25 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
-        <v>52</v>
+        <v>144</v>
       </c>
       <c r="B140" s="2">
-        <v>0.06575290858745575</v>
+        <v>0.06514405459165573</v>
       </c>
       <c r="C140" s="1">
         <v>84</v>
       </c>
       <c r="D140" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F140" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G140" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H140" s="1">
         <v>0</v>
@@ -7709,25 +7759,25 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
-        <v>144</v>
+        <v>53</v>
       </c>
       <c r="B141" s="2">
-        <v>0.06418736279010773</v>
+        <v>0.06514405459165573</v>
       </c>
       <c r="C141" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D141" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E141" s="1">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="F141" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G141" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H141" s="1">
         <v>0</v>
@@ -7738,16 +7788,16 @@
         <v>145</v>
       </c>
       <c r="B142" s="2">
-        <v>0.06262181699275971</v>
+        <v>0.06359300762414932</v>
       </c>
       <c r="C142" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -7764,16 +7814,16 @@
         <v>146</v>
       </c>
       <c r="B143" s="2">
-        <v>0.06105627492070198</v>
+        <v>0.06204195693135262</v>
       </c>
       <c r="C143" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D143" s="1">
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -7787,19 +7837,19 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="B144" s="2">
-        <v>0.05949072912335396</v>
+        <v>0.06204195693135262</v>
       </c>
       <c r="C144" s="1">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D144" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7808,24 +7858,24 @@
         <v>0</v>
       </c>
       <c r="H144" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="B145" s="2">
-        <v>0.05166300013661385</v>
+        <v>0.0589398592710495</v>
       </c>
       <c r="C145" s="1">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D145" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E145" s="1">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F145" s="1">
         <v>0</v>
@@ -7834,7 +7884,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -7842,16 +7892,16 @@
         <v>148</v>
       </c>
       <c r="B146" s="2">
-        <v>0.04696636274456978</v>
+        <v>0.05118461325764656</v>
       </c>
       <c r="C146" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -7868,7 +7918,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04696636274456978</v>
+        <v>0.04653146862983704</v>
       </c>
       <c r="C147" s="1">
         <v>60</v>
@@ -7894,7 +7944,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04696636274456978</v>
+        <v>0.04653146862983704</v>
       </c>
       <c r="C148" s="1">
         <v>60</v>
@@ -7920,16 +7970,16 @@
         <v>151</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04540081694722176</v>
+        <v>0.04653146862983704</v>
       </c>
       <c r="C149" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D149" s="1">
         <v>0</v>
       </c>
       <c r="E149" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F149" s="1">
         <v>0</v>
@@ -7946,16 +7996,16 @@
         <v>152</v>
       </c>
       <c r="B150" s="2">
-        <v>0.04226972907781601</v>
+        <v>0.04498041793704033</v>
       </c>
       <c r="C150" s="1">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
       </c>
       <c r="E150" s="1">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F150" s="1">
         <v>0</v>
@@ -7969,25 +8019,25 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
       <c r="B151" s="2">
-        <v>0.04226972907781601</v>
+        <v>0.04187832027673721</v>
       </c>
       <c r="C151" s="1">
         <v>54</v>
       </c>
       <c r="D151" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E151" s="1">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F151" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G151" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
@@ -7995,25 +8045,25 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1" t="s">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="B152" s="2">
-        <v>0.04070418328046799</v>
+        <v>0.04187832027673721</v>
       </c>
       <c r="C152" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D152" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E152" s="1">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="F152" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G152" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
@@ -8024,16 +8074,16 @@
         <v>154</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03913863748311997</v>
+        <v>0.04032726958394051</v>
       </c>
       <c r="C153" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D153" s="1">
         <v>0</v>
       </c>
       <c r="E153" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F153" s="1">
         <v>0</v>
@@ -8050,16 +8100,16 @@
         <v>155</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03757309168577194</v>
+        <v>0.0387762226164341</v>
       </c>
       <c r="C154" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D154" s="1">
         <v>0</v>
       </c>
       <c r="E154" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F154" s="1">
         <v>0</v>
@@ -8076,7 +8126,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="2">
-        <v>0.03757309168577194</v>
+        <v>0.03722517192363739</v>
       </c>
       <c r="C155" s="1">
         <v>48</v>
@@ -8102,7 +8152,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="2">
-        <v>0.03757309168577194</v>
+        <v>0.03722517192363739</v>
       </c>
       <c r="C156" s="1">
         <v>48</v>
@@ -8128,16 +8178,16 @@
         <v>158</v>
       </c>
       <c r="B157" s="2">
-        <v>0.0344420000910759</v>
+        <v>0.03722517192363739</v>
       </c>
       <c r="C157" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
       </c>
       <c r="E157" s="1">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -8154,7 +8204,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="2">
-        <v>0.0344420000910759</v>
+        <v>0.03412307426333427</v>
       </c>
       <c r="C158" s="1">
         <v>44</v>
@@ -8177,25 +8227,25 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1" t="s">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="B159" s="2">
-        <v>0.0344420000910759</v>
+        <v>0.03412307426333427</v>
       </c>
       <c r="C159" s="1">
         <v>44</v>
       </c>
       <c r="D159" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E159" s="1">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F159" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G159" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
@@ -8203,25 +8253,25 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1" t="s">
-        <v>160</v>
+        <v>49</v>
       </c>
       <c r="B160" s="2">
-        <v>0.0344420000910759</v>
+        <v>0.03412307426333427</v>
       </c>
       <c r="C160" s="1">
         <v>44</v>
       </c>
       <c r="D160" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E160" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F160" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G160" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H160" s="1">
         <v>0</v>
@@ -8232,7 +8282,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.0344420000910759</v>
+        <v>0.03412307426333427</v>
       </c>
       <c r="C161" s="1">
         <v>44</v>
@@ -8258,16 +8308,16 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.03131090849637985</v>
+        <v>0.03412307426333427</v>
       </c>
       <c r="C162" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
       </c>
       <c r="E162" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F162" s="1">
         <v>0</v>
@@ -8284,16 +8334,16 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.02974536456167698</v>
+        <v>0.03102097846567631</v>
       </c>
       <c r="C163" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D163" s="1">
         <v>0</v>
       </c>
       <c r="E163" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F163" s="1">
         <v>0</v>
@@ -8310,7 +8360,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.02974536456167698</v>
+        <v>0.02946992963552475</v>
       </c>
       <c r="C164" s="1">
         <v>38</v>
@@ -8336,16 +8386,16 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.02817981876432896</v>
+        <v>0.02946992963552475</v>
       </c>
       <c r="C165" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
       </c>
       <c r="E165" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F165" s="1">
         <v>0</v>
@@ -8362,7 +8412,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.02817981876432896</v>
+        <v>0.02791888080537319</v>
       </c>
       <c r="C166" s="1">
         <v>36</v>
@@ -8388,7 +8438,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.02817981876432896</v>
+        <v>0.02791888080537319</v>
       </c>
       <c r="C167" s="1">
         <v>36</v>
@@ -8414,7 +8464,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.02817981876432896</v>
+        <v>0.02791888080537319</v>
       </c>
       <c r="C168" s="1">
         <v>36</v>
@@ -8440,16 +8490,16 @@
         <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.02504872716963291</v>
+        <v>0.02791888080537319</v>
       </c>
       <c r="C169" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
       </c>
       <c r="E169" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F169" s="1">
         <v>0</v>
@@ -8466,7 +8516,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="2">
-        <v>0.02504872716963291</v>
+        <v>0.02481678314507008</v>
       </c>
       <c r="C170" s="1">
         <v>32</v>
@@ -8492,7 +8542,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="2">
-        <v>0.02504872716963291</v>
+        <v>0.02481678314507008</v>
       </c>
       <c r="C171" s="1">
         <v>32</v>
@@ -8518,7 +8568,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="2">
-        <v>0.02504872716963291</v>
+        <v>0.02481678314507008</v>
       </c>
       <c r="C172" s="1">
         <v>32</v>
@@ -8544,16 +8594,16 @@
         <v>173</v>
       </c>
       <c r="B173" s="2">
-        <v>0.02348318137228489</v>
+        <v>0.02481678314507008</v>
       </c>
       <c r="C173" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D173" s="1">
         <v>0</v>
       </c>
       <c r="E173" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F173" s="1">
         <v>0</v>
@@ -8570,16 +8620,16 @@
         <v>174</v>
       </c>
       <c r="B174" s="2">
-        <v>0.02348318137228489</v>
+        <v>0.02481678314507008</v>
       </c>
       <c r="C174" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D174" s="1">
         <v>0</v>
       </c>
       <c r="E174" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F174" s="1">
         <v>0</v>
@@ -8596,16 +8646,16 @@
         <v>175</v>
       </c>
       <c r="B175" s="2">
-        <v>0.02035209164023399</v>
+        <v>0.02326573431491852</v>
       </c>
       <c r="C175" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D175" s="1">
         <v>0</v>
       </c>
       <c r="E175" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F175" s="1">
         <v>0</v>
@@ -8622,16 +8672,16 @@
         <v>176</v>
       </c>
       <c r="B176" s="2">
-        <v>0.02035209164023399</v>
+        <v>0.02326573431491852</v>
       </c>
       <c r="C176" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D176" s="1">
         <v>0</v>
       </c>
       <c r="E176" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F176" s="1">
         <v>0</v>
@@ -8648,16 +8698,16 @@
         <v>177</v>
       </c>
       <c r="B177" s="2">
-        <v>0.01878654584288597</v>
+        <v>0.02016363479197025</v>
       </c>
       <c r="C177" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D177" s="1">
         <v>0</v>
       </c>
       <c r="E177" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F177" s="1">
         <v>0</v>
@@ -8674,16 +8724,16 @@
         <v>178</v>
       </c>
       <c r="B178" s="2">
-        <v>0.01878654584288597</v>
+        <v>0.02016363479197025</v>
       </c>
       <c r="C178" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D178" s="1">
         <v>0</v>
       </c>
       <c r="E178" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F178" s="1">
         <v>0</v>
@@ -8697,25 +8747,25 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="1" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="B179" s="2">
-        <v>0.01252436358481646</v>
+        <v>0.0186125859618187</v>
       </c>
       <c r="C179" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D179" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E179" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F179" s="1">
         <v>0</v>
       </c>
       <c r="G179" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
@@ -8723,19 +8773,19 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B180" s="2">
-        <v>0.006262181792408228</v>
+        <v>0.0186125859618187</v>
       </c>
       <c r="C180" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D180" s="1">
         <v>0</v>
       </c>
       <c r="E180" s="1">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F180" s="1">
         <v>0</v>
@@ -8749,25 +8799,25 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="1" t="s">
-        <v>180</v>
+        <v>48</v>
       </c>
       <c r="B181" s="2">
-        <v>0.006262181792408228</v>
+        <v>0.01240839157253504</v>
       </c>
       <c r="C181" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D181" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E181" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F181" s="1">
         <v>0</v>
       </c>
       <c r="G181" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
@@ -8778,16 +8828,16 @@
         <v>181</v>
       </c>
       <c r="B182" s="2">
-        <v>0.003131090896204114</v>
+        <v>0.006204195786267519</v>
       </c>
       <c r="C182" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D182" s="1">
         <v>0</v>
       </c>
       <c r="E182" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1">
         <v>0</v>
@@ -8801,25 +8851,25 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="1" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
       <c r="B183" s="2">
-        <v>0.003131090896204114</v>
+        <v>0.006204195786267519</v>
       </c>
       <c r="C183" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D183" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E183" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1">
         <v>0</v>
       </c>
       <c r="G183" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
@@ -8827,10 +8877,10 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B184" s="2">
-        <v>0.003131090896204114</v>
+        <v>0.00310209789313376</v>
       </c>
       <c r="C184" s="1">
         <v>4</v>
@@ -8853,59 +8903,111 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="1" t="s">
-        <v>183</v>
+        <v>47</v>
       </c>
       <c r="B185" s="2">
-        <v>0.003131090896204114</v>
+        <v>0.00310209789313376</v>
       </c>
       <c r="C185" s="1">
         <v>4</v>
       </c>
       <c r="D185" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E185" s="1">
+        <v>0</v>
+      </c>
+      <c r="F185" s="1">
+        <v>0</v>
+      </c>
+      <c r="G185" s="1">
         <v>4</v>
       </c>
-      <c r="F185" s="1">
-        <v>0</v>
-      </c>
-      <c r="G185" s="1">
-        <v>0</v>
-      </c>
       <c r="H185" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="186" spans="1:8">
-      <c r="A186" t="s">
+      <c r="A186" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B186" s="2">
+        <v>0.00310209789313376</v>
+      </c>
+      <c r="C186" s="1">
+        <v>4</v>
+      </c>
+      <c r="D186" s="1">
+        <v>0</v>
+      </c>
+      <c r="E186" s="1">
+        <v>4</v>
+      </c>
+      <c r="F186" s="1">
+        <v>0</v>
+      </c>
+      <c r="G186" s="1">
+        <v>0</v>
+      </c>
+      <c r="H186" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B186">
+      <c r="B187" s="2">
+        <v>0.00310209789313376</v>
+      </c>
+      <c r="C187" s="1">
+        <v>4</v>
+      </c>
+      <c r="D187" s="1">
+        <v>0</v>
+      </c>
+      <c r="E187" s="1">
+        <v>4</v>
+      </c>
+      <c r="F187" s="1">
+        <v>0</v>
+      </c>
+      <c r="G187" s="1">
+        <v>0</v>
+      </c>
+      <c r="H187" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" t="s">
+        <v>187</v>
+      </c>
+      <c r="B188">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C186">
+      <c r="C188">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D186">
+      <c r="D188">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E186">
+      <c r="E188">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F186">
+      <c r="F188">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G186">
+      <c r="G188">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H186">
+      <c r="H188">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -254,6 +254,9 @@
     <t>ctrl_transition.o</t>
   </si>
   <si>
+    <t>motor_mode_load_sim.o</t>
+  </si>
+  <si>
     <t>foc_core.o</t>
   </si>
   <si>
@@ -308,15 +311,15 @@
     <t>stm32g4xx_hal_gpio.o</t>
   </si>
   <si>
+    <t>motor_info_calib.o</t>
+  </si>
+  <si>
     <t>log10f.o</t>
   </si>
   <si>
     <t>dev_motor.o</t>
   </si>
   <si>
-    <t>motor_info_calib.o</t>
-  </si>
-  <si>
     <t>drv_tim.o</t>
   </si>
   <si>
@@ -365,9 +368,6 @@
     <t>ddiv.o</t>
   </si>
   <si>
-    <t>motor_mode_load_sim.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_pwr_ex.o</t>
   </si>
   <si>
@@ -404,25 +404,25 @@
     <t>thread_period.o</t>
   </si>
   <si>
+    <t>motor_mode_mit.o</t>
+  </si>
+  <si>
+    <t>user_interface.o</t>
+  </si>
+  <si>
     <t>motor_mode_velocity.o</t>
   </si>
   <si>
-    <t>motor_mode_mit.o</t>
-  </si>
-  <si>
-    <t>user_interface.o</t>
-  </si>
-  <si>
     <t>motor_mode_open_loop.o</t>
   </si>
   <si>
+    <t>floorf.o</t>
+  </si>
+  <si>
+    <t>motor_mode_position.o</t>
+  </si>
+  <si>
     <t>motor_mode_current.o</t>
-  </si>
-  <si>
-    <t>floorf.o</t>
-  </si>
-  <si>
-    <t>motor_mode_position.o</t>
   </si>
   <si>
     <t>fepilogue.o</t>
@@ -870,166 +870,166 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="186"/>
                 <c:pt idx="0">
-                  <c:v>34.56700897216797</c:v>
+                  <c:v>34.55629730224609</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.19889450073242</c:v>
+                  <c:v>21.19232749938965</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.92905330657959</c:v>
+                  <c:v>12.95602989196777</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.289392948150635</c:v>
+                  <c:v>5.287754058837891</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.289392948150635</c:v>
+                  <c:v>5.287754058837891</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.845166683197022</c:v>
+                  <c:v>4.84366512298584</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.706681489944458</c:v>
+                  <c:v>2.705842971801758</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.639530897140503</c:v>
+                  <c:v>2.638713121414185</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.128154039382935</c:v>
+                  <c:v>2.127494812011719</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.331387639045715</c:v>
+                  <c:v>1.33097517490387</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.322348237037659</c:v>
+                  <c:v>1.321938514709473</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9297760725021362</c:v>
+                  <c:v>0.9294880032539368</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5062114000320435</c:v>
+                  <c:v>0.5060545802116394</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4597226083278656</c:v>
+                  <c:v>0.4595801830291748</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.4390609264373779</c:v>
+                  <c:v>0.4389248788356781</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3874067068099976</c:v>
+                  <c:v>0.3872866630554199</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3460833132266998</c:v>
+                  <c:v>0.3459760844707489</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2944290935993195</c:v>
+                  <c:v>0.2943378686904907</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.2892636656761169</c:v>
+                  <c:v>0.2891740500926971</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.2634365558624268</c:v>
+                  <c:v>0.2633549273014069</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2582711279392242</c:v>
+                  <c:v>0.2581911087036133</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.1704589426517487</c:v>
+                  <c:v>0.1704061329364777</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1652935296297073</c:v>
+                  <c:v>0.1652423143386841</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.1291355639696121</c:v>
+                  <c:v>0.1290955543518066</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1084738746285439</c:v>
+                  <c:v>0.1084402650594711</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.09814303368330002</c:v>
+                  <c:v>0.09811262041330338</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.0929776057600975</c:v>
+                  <c:v>0.0929488018155098</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.0929776057600975</c:v>
+                  <c:v>0.0929488018155098</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.0929776057600975</c:v>
+                  <c:v>0.0929488018155098</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.08781218528747559</c:v>
+                  <c:v>0.08778497576713562</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.08264676481485367</c:v>
+                  <c:v>0.08262115716934204</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.05681964755058289</c:v>
+                  <c:v>0.05680204555392265</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.05165422707796097</c:v>
+                  <c:v>0.05163822323083878</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.04648880288004875</c:v>
+                  <c:v>0.0464744009077549</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.04132338240742683</c:v>
+                  <c:v>0.04131057858467102</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.04132338240742683</c:v>
+                  <c:v>0.04131057858467102</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03615795820951462</c:v>
+                  <c:v>0.03614675626158714</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.02582711353898048</c:v>
+                  <c:v>0.02581911161541939</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.02582711353898048</c:v>
+                  <c:v>0.02581911161541939</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.01549626793712378</c:v>
+                  <c:v>0.01549146696925163</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.01549626793712378</c:v>
+                  <c:v>0.01549146696925163</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.01549626793712378</c:v>
+                  <c:v>0.01549146696925163</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01549626793712378</c:v>
+                  <c:v>0.01549146696925163</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01033084560185671</c:v>
+                  <c:v>0.01032764464616776</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01033084560185671</c:v>
+                  <c:v>0.01032764464616776</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.01033084560185671</c:v>
+                  <c:v>0.01032764464616776</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.005165422800928354</c:v>
+                  <c:v>0.005163822323083878</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.005165422800928354</c:v>
+                  <c:v>0.005163822323083878</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.005165422800928354</c:v>
+                  <c:v>0.005163822323083878</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.005165422800928354</c:v>
+                  <c:v>0.005163822323083878</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.005165422800928354</c:v>
+                  <c:v>0.005163822323083878</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.005165422800928354</c:v>
+                  <c:v>0.005163822323083878</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.005165422800928354</c:v>
+                  <c:v>0.005163822323083878</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.003874066984280944</c:v>
+                  <c:v>0.003872866742312908</c:v>
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>0</c:v>
@@ -1217,199 +1217,199 @@
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>motor_loop.o</c:v>
+                  <c:v>motor_mode_load_sim.o</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
                 <c:pt idx="40">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>drv_flash_g4.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>motor_info_storage.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>multiturn_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>motor_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>atan2f.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>dev_eeprom.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>dev_half_bridge.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>drv_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="59">
                   <c:v>cascade_control.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="60">
                   <c:v>foc_decoupling.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="61">
                   <c:v>crc16.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="63">
                   <c:v>motor_control.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="64">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="66">
                   <c:v>calib_ac_injection.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="67">
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="68">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="69">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="70">
                   <c:v>ctrl_transition_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="71">
                   <c:v>stm32g4xx_hal_flash_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="72">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="73">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="74">
+                  <c:v>motor_info_calib.o</c:v>
+                </c:pt>
+                <c:pt idx="75">
                   <c:v>log10f.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="76">
                   <c:v>dev_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
-                  <c:v>motor_info_calib.o</c:v>
-                </c:pt>
-                <c:pt idx="76">
+                <c:pt idx="77">
                   <c:v>led_manager.o</c:v>
                 </c:pt>
-                <c:pt idx="77">
+                <c:pt idx="78">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="78">
+                <c:pt idx="79">
                   <c:v>dev_config.o</c:v>
                 </c:pt>
-                <c:pt idx="79">
+                <c:pt idx="80">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="81">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="82">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="83">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>cosf.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="89">
                   <c:v>cmsis_os.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="90">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="91">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="92">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="93">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="94">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="95">
                   <c:v>drv_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="96">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="97">
                   <c:v>drv_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="98">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="98">
+                <c:pt idx="99">
                   <c:v>drv_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="99">
+                <c:pt idx="100">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="101">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="102">
                   <c:v>ddiv.o</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>motor_mode_load_sim.o</c:v>
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
@@ -1460,13 +1460,13 @@
                   <c:v>thread_period.o</c:v>
                 </c:pt>
                 <c:pt idx="119">
+                  <c:v>motor_mode_mit.o</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>user_interface.o</c:v>
+                </c:pt>
+                <c:pt idx="121">
                   <c:v>motor_mode_velocity.o</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>motor_mode_mit.o</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>user_interface.o</c:v>
                 </c:pt>
                 <c:pt idx="122">
                   <c:v>calib_level6_system.o</c:v>
@@ -1478,13 +1478,13 @@
                   <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="125">
+                  <c:v>floorf.o</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>motor_mode_position.o</c:v>
+                </c:pt>
+                <c:pt idx="127">
                   <c:v>motor_mode_current.o</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>floorf.o</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>motor_mode_position.o</c:v>
                 </c:pt>
                 <c:pt idx="128">
                   <c:v>fepilogue.o</c:v>
@@ -1670,559 +1670,559 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="186"/>
                 <c:pt idx="0">
-                  <c:v>4.491837501525879</c:v>
+                  <c:v>4.509890079498291</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.817131280899048</c:v>
+                  <c:v>3.786707401275635</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.675985813140869</c:v>
+                  <c:v>3.646686792373657</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.295979022979736</c:v>
+                  <c:v>3.377416610717773</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.035402774810791</c:v>
+                  <c:v>3.01120924949646</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.853929996490479</c:v>
+                  <c:v>2.831182956695557</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.570087909698486</c:v>
+                  <c:v>2.549603462219238</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.473922967910767</c:v>
+                  <c:v>2.454204797744751</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.238163471221924</c:v>
+                  <c:v>2.220324516296387</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.228857278823853</c:v>
+                  <c:v>2.211092472076416</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.89383065700531</c:v>
+                  <c:v>1.878736138343811</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.861258625984192</c:v>
+                  <c:v>1.846423745155335</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.824033498764038</c:v>
+                  <c:v>1.809495210647583</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.820931434631348</c:v>
+                  <c:v>1.80641782283783</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.817829251289368</c:v>
+                  <c:v>1.803340435028076</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.720113277435303</c:v>
+                  <c:v>1.706403255462647</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.665826559066773</c:v>
+                  <c:v>1.652549266815186</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.659622311592102</c:v>
+                  <c:v>1.646394491195679</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.591376185417175</c:v>
+                  <c:v>1.578692317008972</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.516925811767578</c:v>
+                  <c:v>1.504835367202759</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.507619500160217</c:v>
+                  <c:v>1.495603203773499</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.49055802822113</c:v>
+                  <c:v>1.470984220504761</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.473496437072754</c:v>
+                  <c:v>1.461752057075501</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.400597095489502</c:v>
+                  <c:v>1.389433860778809</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.364923000335693</c:v>
+                  <c:v>1.363276124000549</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.247043371200562</c:v>
+                  <c:v>1.237103939056397</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.243941187858582</c:v>
+                  <c:v>1.234026551246643</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.132265686988831</c:v>
+                  <c:v>1.123241066932678</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.115204215049744</c:v>
+                  <c:v>1.106315493583679</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.081081032752991</c:v>
+                  <c:v>1.072464466094971</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.076427936553955</c:v>
+                  <c:v>1.072464466094971</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.9678544998168945</c:v>
+                  <c:v>0.9601403474807739</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.9461398124694824</c:v>
+                  <c:v>0.9385986924171448</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.941486656665802</c:v>
+                  <c:v>0.9339826703071594</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.912016749382019</c:v>
+                  <c:v>0.9109023809432983</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8918530941009522</c:v>
+                  <c:v>0.8847447037696838</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8391174674034119</c:v>
+                  <c:v>0.8324293494224548</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7972391247749329</c:v>
+                  <c:v>0.790884792804718</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.7848307490348816</c:v>
+                  <c:v>0.7785753011703491</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.784055233001709</c:v>
+                  <c:v>0.7778059840202332</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.7755244374275208</c:v>
+                  <c:v>0.7754979729652405</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7522587180137634</c:v>
+                  <c:v>0.7693431973457336</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7445034980773926</c:v>
+                  <c:v>0.7462629079818726</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7414013743400574</c:v>
+                  <c:v>0.7385694980621338</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.7243398427963257</c:v>
+                  <c:v>0.7354921102523804</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.6700531244277954</c:v>
+                  <c:v>0.7185665369033814</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6607468128204346</c:v>
+                  <c:v>0.6647125482559204</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6591957807540894</c:v>
+                  <c:v>0.6554804444313049</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.635930061340332</c:v>
+                  <c:v>0.6539417505264282</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.6188685297966003</c:v>
+                  <c:v>0.6308614611625671</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.6080111861228943</c:v>
+                  <c:v>0.6139358878135681</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.5862964987754822</c:v>
+                  <c:v>0.6031650900840759</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5614796876907349</c:v>
+                  <c:v>0.5816234946250916</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5583776235580444</c:v>
+                  <c:v>0.5570045113563538</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5304587483406067</c:v>
+                  <c:v>0.5539271235466003</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.5102950930595398</c:v>
+                  <c:v>0.5262307524681091</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.4994377493858337</c:v>
+                  <c:v>0.5062278509140015</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4808251559734345</c:v>
+                  <c:v>0.4954570233821869</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4792741239070892</c:v>
+                  <c:v>0.4769927859306335</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4435999989509583</c:v>
+                  <c:v>0.4754540920257568</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4311915934085846</c:v>
+                  <c:v>0.4400643110275269</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.424987405538559</c:v>
+                  <c:v>0.427754819393158</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4218853116035461</c:v>
+                  <c:v>0.4216000735759735</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.3970685303211212</c:v>
+                  <c:v>0.4185227155685425</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.393966406583786</c:v>
+                  <c:v>0.3939037322998047</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.3908643126487732</c:v>
+                  <c:v>0.3908263444900513</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.389313280582428</c:v>
+                  <c:v>0.3877489864826202</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.389313280582428</c:v>
+                  <c:v>0.3862102925777435</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3862111866474152</c:v>
+                  <c:v>0.3862102925777435</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3707006871700287</c:v>
+                  <c:v>0.3831329047679901</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3691496253013611</c:v>
+                  <c:v>0.3708234429359436</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3629454374313355</c:v>
+                  <c:v>0.3662073612213135</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.353639155626297</c:v>
+                  <c:v>0.360052615404129</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3474349677562714</c:v>
+                  <c:v>0.3508205115795136</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3350265622138977</c:v>
+                  <c:v>0.3492818176746368</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3303734064102173</c:v>
+                  <c:v>0.3446657657623291</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.3303734064102173</c:v>
+                  <c:v>0.3323562741279602</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.317965030670166</c:v>
+                  <c:v>0.3277402222156525</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.317965030670166</c:v>
+                  <c:v>0.3154307305812836</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.3164139688014984</c:v>
+                  <c:v>0.3154307305812836</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.3102097809314728</c:v>
+                  <c:v>0.3138920366764069</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.3102097809314728</c:v>
+                  <c:v>0.3077372908592224</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.2884950935840607</c:v>
+                  <c:v>0.3077372908592224</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2838419377803803</c:v>
+                  <c:v>0.2861956655979157</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2667804062366486</c:v>
+                  <c:v>0.2815796136856079</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2605762183666229</c:v>
+                  <c:v>0.2646540701389313</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2590251564979553</c:v>
+                  <c:v>0.2584993243217468</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2574741244316101</c:v>
+                  <c:v>0.2569606304168701</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2512699067592621</c:v>
+                  <c:v>0.2554219365119934</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2388615310192108</c:v>
+                  <c:v>0.2492672055959702</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2264531403779984</c:v>
+                  <c:v>0.2369577139616013</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2109426558017731</c:v>
+                  <c:v>0.2246482223272324</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2109426558017731</c:v>
+                  <c:v>0.2092613577842712</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.1954321563243866</c:v>
+                  <c:v>0.2092613577842712</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1907790154218674</c:v>
+                  <c:v>0.1938744932413101</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1876769214868546</c:v>
+                  <c:v>0.1892584264278412</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1861258745193481</c:v>
+                  <c:v>0.186181053519249</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1814727187156677</c:v>
+                  <c:v>0.1846423745155335</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1799216717481613</c:v>
+                  <c:v>0.1800263077020645</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1768195778131485</c:v>
+                  <c:v>0.178487628698349</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1768195778131485</c:v>
+                  <c:v>0.1754102557897568</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1721664220094681</c:v>
+                  <c:v>0.1754102557897568</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1721664220094681</c:v>
+                  <c:v>0.1707941889762878</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1706153750419617</c:v>
+                  <c:v>0.1692555099725723</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1706153750419617</c:v>
+                  <c:v>0.1692555099725723</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1489006876945496</c:v>
+                  <c:v>0.1477138996124268</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1457985937595367</c:v>
+                  <c:v>0.1446365267038345</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1442475467920303</c:v>
+                  <c:v>0.1430978327989578</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1364922970533371</c:v>
+                  <c:v>0.1354044079780579</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1364922970533371</c:v>
+                  <c:v>0.1354044079780579</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1333902031183243</c:v>
+                  <c:v>0.1323270350694656</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1225328594446182</c:v>
+                  <c:v>0.1215562298893929</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1194307655096054</c:v>
+                  <c:v>0.1184788569808006</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.117879718542099</c:v>
+                  <c:v>0.1169401705265045</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1116755232214928</c:v>
+                  <c:v>0.1107854247093201</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1101244688034058</c:v>
+                  <c:v>0.109246738255024</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1070223748683929</c:v>
+                  <c:v>0.1061693653464317</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.1054713279008865</c:v>
+                  <c:v>0.1046306788921356</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.0992671325802803</c:v>
+                  <c:v>0.09847593307495117</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.0992671325802803</c:v>
+                  <c:v>0.09847593307495117</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.0992671325802803</c:v>
+                  <c:v>0.09693724662065506</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.0977160781621933</c:v>
+                  <c:v>0.09693724662065506</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.0977160781621933</c:v>
+                  <c:v>0.09693724662065506</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.09306293725967407</c:v>
+                  <c:v>0.09232118725776672</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.08996083587408066</c:v>
+                  <c:v>0.08770512789487839</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.08840978890657425</c:v>
+                  <c:v>0.08616644144058228</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.08685874193906784</c:v>
+                  <c:v>0.08616644144058228</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.08685874193906784</c:v>
+                  <c:v>0.08616644144058228</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.08530768752098084</c:v>
+                  <c:v>0.08462775498628616</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.08375664055347443</c:v>
+                  <c:v>0.08308906853199005</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.08375664055347443</c:v>
+                  <c:v>0.08308906853199005</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07600139826536179</c:v>
+                  <c:v>0.07539563626050949</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07600139826536179</c:v>
+                  <c:v>0.07539563626050949</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.07134824991226196</c:v>
+                  <c:v>0.07077957689762116</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06669510155916214</c:v>
+                  <c:v>0.06616351753473282</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06514405459165573</c:v>
+                  <c:v>0.06462483108043671</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.06514405459165573</c:v>
+                  <c:v>0.06462483108043671</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.06514405459165573</c:v>
+                  <c:v>0.06462483108043671</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.06514405459165573</c:v>
+                  <c:v>0.06462483108043671</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.06359300762414932</c:v>
+                  <c:v>0.06308614462614059</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.06204195693135262</c:v>
+                  <c:v>0.06154745817184448</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.06204195693135262</c:v>
+                  <c:v>0.06000877171754837</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.0589398592710495</c:v>
+                  <c:v>0.05847008526325226</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.05118461325764656</c:v>
+                  <c:v>0.0507766529917717</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04653146862983704</c:v>
+                  <c:v>0.04616059362888336</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04653146862983704</c:v>
+                  <c:v>0.04616059362888336</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04653146862983704</c:v>
+                  <c:v>0.04616059362888336</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.04498041793704033</c:v>
+                  <c:v>0.04462190717458725</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.04187832027673721</c:v>
+                  <c:v>0.04154453426599503</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.04187832027673721</c:v>
+                  <c:v>0.04154453426599503</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.04032726958394051</c:v>
+                  <c:v>0.04000584781169891</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.0387762226164341</c:v>
+                  <c:v>0.0384671613574028</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03722517192363739</c:v>
+                  <c:v>0.03692847490310669</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03722517192363739</c:v>
+                  <c:v>0.03692847490310669</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.03722517192363739</c:v>
+                  <c:v>0.03692847490310669</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.03412307426333427</c:v>
+                  <c:v>0.03385110199451447</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.03412307426333427</c:v>
+                  <c:v>0.03385110199451447</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.03412307426333427</c:v>
+                  <c:v>0.03385110199451447</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.03412307426333427</c:v>
+                  <c:v>0.03385110199451447</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.03412307426333427</c:v>
+                  <c:v>0.03385110199451447</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.03102097846567631</c:v>
+                  <c:v>0.03077372908592224</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.02946992963552475</c:v>
+                  <c:v>0.02923504263162613</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.02946992963552475</c:v>
+                  <c:v>0.02923504263162613</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.02791888080537319</c:v>
+                  <c:v>0.02769635617733002</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02791888080537319</c:v>
+                  <c:v>0.02769635617733002</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02791888080537319</c:v>
+                  <c:v>0.02769635617733002</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02791888080537319</c:v>
+                  <c:v>0.02769635617733002</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.02481678314507008</c:v>
+                  <c:v>0.02461898326873779</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.02481678314507008</c:v>
+                  <c:v>0.02461898326873779</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.02481678314507008</c:v>
+                  <c:v>0.02461898326873779</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.02481678314507008</c:v>
+                  <c:v>0.02461898326873779</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.02481678314507008</c:v>
+                  <c:v>0.02461898326873779</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.02326573431491852</c:v>
+                  <c:v>0.02308029681444168</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>0.02326573431491852</c:v>
+                  <c:v>0.02308029681444168</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>0.02016363479197025</c:v>
+                  <c:v>0.02000292390584946</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>0.02016363479197025</c:v>
+                  <c:v>0.02000292390584946</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>0.0186125859618187</c:v>
+                  <c:v>0.01846423745155335</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>0.0186125859618187</c:v>
+                  <c:v>0.01846423745155335</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>0.01240839157253504</c:v>
+                  <c:v>0.0123094916343689</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>0.006204195786267519</c:v>
+                  <c:v>0.006154745817184448</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>0.006204195786267519</c:v>
+                  <c:v>0.006154745817184448</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>0.00310209789313376</c:v>
+                  <c:v>0.003077372908592224</c:v>
                 </c:pt>
                 <c:pt idx="182">
-                  <c:v>0.00310209789313376</c:v>
+                  <c:v>0.003077372908592224</c:v>
                 </c:pt>
                 <c:pt idx="183">
-                  <c:v>0.00310209789313376</c:v>
+                  <c:v>0.003077372908592224</c:v>
                 </c:pt>
                 <c:pt idx="184">
-                  <c:v>0.00310209789313376</c:v>
+                  <c:v>0.003077372908592224</c:v>
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>0</c:v>
@@ -2689,7 +2689,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>34.56700897216797</v>
+        <v>34.55629730224609</v>
       </c>
       <c r="C3" s="1">
         <v>26768</v>
@@ -2715,7 +2715,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>21.19889450073242</v>
+        <v>21.19232749938965</v>
       </c>
       <c r="C4" s="1">
         <v>16416</v>
@@ -2741,16 +2741,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>12.92905330657959</v>
+        <v>12.95602989196777</v>
       </c>
       <c r="C5" s="1">
-        <v>10012</v>
+        <v>10036</v>
       </c>
       <c r="D5" s="1">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="E5" s="1">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>10012</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2767,7 +2767,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>5.289392948150635</v>
+        <v>5.287754058837891</v>
       </c>
       <c r="C6" s="1">
         <v>4096</v>
@@ -2793,7 +2793,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>5.289392948150635</v>
+        <v>5.287754058837891</v>
       </c>
       <c r="C7" s="1">
         <v>4096</v>
@@ -2819,7 +2819,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.845166683197022</v>
+        <v>4.84366512298584</v>
       </c>
       <c r="C8" s="1">
         <v>3752</v>
@@ -2845,7 +2845,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.706681489944458</v>
+        <v>2.705842971801758</v>
       </c>
       <c r="C9" s="1">
         <v>2096</v>
@@ -2871,7 +2871,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.639530897140503</v>
+        <v>2.638713121414185</v>
       </c>
       <c r="C10" s="1">
         <v>2044</v>
@@ -2897,7 +2897,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.128154039382935</v>
+        <v>2.127494812011719</v>
       </c>
       <c r="C11" s="1">
         <v>1648</v>
@@ -2923,7 +2923,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.331387639045715</v>
+        <v>1.33097517490387</v>
       </c>
       <c r="C12" s="1">
         <v>1031</v>
@@ -2949,7 +2949,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.322348237037659</v>
+        <v>1.321938514709473</v>
       </c>
       <c r="C13" s="1">
         <v>1024</v>
@@ -2975,7 +2975,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.9297760725021362</v>
+        <v>0.9294880032539368</v>
       </c>
       <c r="C14" s="1">
         <v>720</v>
@@ -3001,16 +3001,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.5062114000320435</v>
+        <v>0.5060545802116394</v>
       </c>
       <c r="C15" s="1">
         <v>392</v>
       </c>
       <c r="D15" s="1">
-        <v>5792</v>
+        <v>5862</v>
       </c>
       <c r="E15" s="1">
-        <v>5292</v>
+        <v>5362</v>
       </c>
       <c r="F15" s="1">
         <v>472</v>
@@ -3027,7 +3027,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.4597226083278656</v>
+        <v>0.4595801830291748</v>
       </c>
       <c r="C16" s="1">
         <v>356</v>
@@ -3053,7 +3053,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.4390609264373779</v>
+        <v>0.4389248788356781</v>
       </c>
       <c r="C17" s="1">
         <v>340</v>
@@ -3079,7 +3079,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3874067068099976</v>
+        <v>0.3872866630554199</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -3105,7 +3105,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3460833132266998</v>
+        <v>0.3459760844707489</v>
       </c>
       <c r="C19" s="1">
         <v>268</v>
@@ -3131,7 +3131,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.2944290935993195</v>
+        <v>0.2943378686904907</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -3157,7 +3157,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.2892636656761169</v>
+        <v>0.2891740500926971</v>
       </c>
       <c r="C21" s="1">
         <v>224</v>
@@ -3183,7 +3183,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.2634365558624268</v>
+        <v>0.2633549273014069</v>
       </c>
       <c r="C22" s="1">
         <v>204</v>
@@ -3209,7 +3209,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2582711279392242</v>
+        <v>0.2581911087036133</v>
       </c>
       <c r="C23" s="1">
         <v>200</v>
@@ -3235,16 +3235,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.1704589426517487</v>
+        <v>0.1704061329364777</v>
       </c>
       <c r="C24" s="1">
         <v>132</v>
       </c>
       <c r="D24" s="1">
-        <v>4250</v>
+        <v>4390</v>
       </c>
       <c r="E24" s="1">
-        <v>4238</v>
+        <v>4378</v>
       </c>
       <c r="F24" s="1">
         <v>12</v>
@@ -3261,7 +3261,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.1652935296297073</v>
+        <v>0.1652423143386841</v>
       </c>
       <c r="C25" s="1">
         <v>128</v>
@@ -3287,7 +3287,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.1291355639696121</v>
+        <v>0.1290955543518066</v>
       </c>
       <c r="C26" s="1">
         <v>100</v>
@@ -3313,7 +3313,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1084738746285439</v>
+        <v>0.1084402650594711</v>
       </c>
       <c r="C27" s="1">
         <v>84</v>
@@ -3339,7 +3339,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.09814303368330002</v>
+        <v>0.09811262041330338</v>
       </c>
       <c r="C28" s="1">
         <v>76</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0929776057600975</v>
+        <v>0.0929488018155098</v>
       </c>
       <c r="C29" s="1">
         <v>72</v>
@@ -3391,7 +3391,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0929776057600975</v>
+        <v>0.0929488018155098</v>
       </c>
       <c r="C30" s="1">
         <v>72</v>
@@ -3417,7 +3417,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0929776057600975</v>
+        <v>0.0929488018155098</v>
       </c>
       <c r="C31" s="1">
         <v>72</v>
@@ -3443,7 +3443,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.08781218528747559</v>
+        <v>0.08778497576713562</v>
       </c>
       <c r="C32" s="1">
         <v>68</v>
@@ -3469,7 +3469,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.08264676481485367</v>
+        <v>0.08262115716934204</v>
       </c>
       <c r="C33" s="1">
         <v>64</v>
@@ -3495,7 +3495,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.05681964755058289</v>
+        <v>0.05680204555392265</v>
       </c>
       <c r="C34" s="1">
         <v>44</v>
@@ -3521,7 +3521,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.05165422707796097</v>
+        <v>0.05163822323083878</v>
       </c>
       <c r="C35" s="1">
         <v>40</v>
@@ -3547,7 +3547,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.04648880288004875</v>
+        <v>0.0464744009077549</v>
       </c>
       <c r="C36" s="1">
         <v>36</v>
@@ -3573,7 +3573,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.04132338240742683</v>
+        <v>0.04131057858467102</v>
       </c>
       <c r="C37" s="1">
         <v>32</v>
@@ -3599,7 +3599,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.04132338240742683</v>
+        <v>0.04131057858467102</v>
       </c>
       <c r="C38" s="1">
         <v>32</v>
@@ -3625,16 +3625,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03615795820951462</v>
+        <v>0.03614675626158714</v>
       </c>
       <c r="C39" s="1">
         <v>28</v>
       </c>
       <c r="D39" s="1">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="E39" s="1">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="F39" s="1">
         <v>28</v>
@@ -3651,7 +3651,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.02582711353898048</v>
+        <v>0.02581911161541939</v>
       </c>
       <c r="C40" s="1">
         <v>20</v>
@@ -3677,16 +3677,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.02582711353898048</v>
+        <v>0.02581911161541939</v>
       </c>
       <c r="C41" s="1">
         <v>20</v>
       </c>
       <c r="D41" s="1">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="E41" s="1">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.01549626793712378</v>
+        <v>0.01549146696925163</v>
       </c>
       <c r="C42" s="1">
         <v>12</v>
@@ -3729,7 +3729,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.01549626793712378</v>
+        <v>0.01549146696925163</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
@@ -3755,7 +3755,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.01549626793712378</v>
+        <v>0.01549146696925163</v>
       </c>
       <c r="C44" s="1">
         <v>12</v>
@@ -3781,7 +3781,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01549626793712378</v>
+        <v>0.01549146696925163</v>
       </c>
       <c r="C45" s="1">
         <v>12</v>
@@ -3807,7 +3807,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01033084560185671</v>
+        <v>0.01032764464616776</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
@@ -3833,7 +3833,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01033084560185671</v>
+        <v>0.01032764464616776</v>
       </c>
       <c r="C47" s="1">
         <v>8</v>
@@ -3859,7 +3859,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.01033084560185671</v>
+        <v>0.01032764464616776</v>
       </c>
       <c r="C48" s="1">
         <v>8</v>
@@ -3885,7 +3885,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.005165422800928354</v>
+        <v>0.005163822323083878</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
@@ -3911,7 +3911,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.005165422800928354</v>
+        <v>0.005163822323083878</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
@@ -3937,7 +3937,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.005165422800928354</v>
+        <v>0.005163822323083878</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
@@ -3963,16 +3963,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.005165422800928354</v>
+        <v>0.005163822323083878</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
       </c>
       <c r="D52" s="1">
-        <v>1760</v>
+        <v>1772</v>
       </c>
       <c r="E52" s="1">
-        <v>1420</v>
+        <v>1432</v>
       </c>
       <c r="F52" s="1">
         <v>336</v>
@@ -3989,7 +3989,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.005165422800928354</v>
+        <v>0.005163822323083878</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -4015,7 +4015,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.005165422800928354</v>
+        <v>0.005163822323083878</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
@@ -4041,7 +4041,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.005165422800928354</v>
+        <v>0.005163822323083878</v>
       </c>
       <c r="C55" s="1">
         <v>4</v>
@@ -4067,7 +4067,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.003874066984280944</v>
+        <v>0.003872866742312908</v>
       </c>
       <c r="C56" s="1">
         <v>3</v>
@@ -4174,16 +4174,16 @@
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>4.491837501525879</v>
+        <v>4.509890079498291</v>
       </c>
       <c r="C3" s="1">
-        <v>5792</v>
+        <v>5862</v>
       </c>
       <c r="D3" s="1">
         <v>392</v>
       </c>
       <c r="E3" s="1">
-        <v>5292</v>
+        <v>5362</v>
       </c>
       <c r="F3" s="1">
         <v>472</v>
@@ -4200,7 +4200,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="2">
-        <v>3.817131280899048</v>
+        <v>3.786707401275635</v>
       </c>
       <c r="C4" s="1">
         <v>4922</v>
@@ -4226,7 +4226,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="2">
-        <v>3.675985813140869</v>
+        <v>3.646686792373657</v>
       </c>
       <c r="C5" s="1">
         <v>4740</v>
@@ -4252,16 +4252,16 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>3.295979022979736</v>
+        <v>3.377416610717773</v>
       </c>
       <c r="C6" s="1">
-        <v>4250</v>
+        <v>4390</v>
       </c>
       <c r="D6" s="1">
         <v>132</v>
       </c>
       <c r="E6" s="1">
-        <v>4238</v>
+        <v>4378</v>
       </c>
       <c r="F6" s="1">
         <v>12</v>
@@ -4278,7 +4278,7 @@
         <v>57</v>
       </c>
       <c r="B7" s="2">
-        <v>3.035402774810791</v>
+        <v>3.01120924949646</v>
       </c>
       <c r="C7" s="1">
         <v>3914</v>
@@ -4304,7 +4304,7 @@
         <v>58</v>
       </c>
       <c r="B8" s="2">
-        <v>2.853929996490479</v>
+        <v>2.831182956695557</v>
       </c>
       <c r="C8" s="1">
         <v>3680</v>
@@ -4330,7 +4330,7 @@
         <v>59</v>
       </c>
       <c r="B9" s="2">
-        <v>2.570087909698486</v>
+        <v>2.549603462219238</v>
       </c>
       <c r="C9" s="1">
         <v>3314</v>
@@ -4356,7 +4356,7 @@
         <v>60</v>
       </c>
       <c r="B10" s="2">
-        <v>2.473922967910767</v>
+        <v>2.454204797744751</v>
       </c>
       <c r="C10" s="1">
         <v>3190</v>
@@ -4382,7 +4382,7 @@
         <v>61</v>
       </c>
       <c r="B11" s="2">
-        <v>2.238163471221924</v>
+        <v>2.220324516296387</v>
       </c>
       <c r="C11" s="1">
         <v>2886</v>
@@ -4408,7 +4408,7 @@
         <v>44</v>
       </c>
       <c r="B12" s="2">
-        <v>2.228857278823853</v>
+        <v>2.211092472076416</v>
       </c>
       <c r="C12" s="1">
         <v>2874</v>
@@ -4434,7 +4434,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>1.89383065700531</v>
+        <v>1.878736138343811</v>
       </c>
       <c r="C13" s="1">
         <v>2442</v>
@@ -4460,7 +4460,7 @@
         <v>62</v>
       </c>
       <c r="B14" s="2">
-        <v>1.861258625984192</v>
+        <v>1.846423745155335</v>
       </c>
       <c r="C14" s="1">
         <v>2400</v>
@@ -4486,7 +4486,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="2">
-        <v>1.824033498764038</v>
+        <v>1.809495210647583</v>
       </c>
       <c r="C15" s="1">
         <v>2352</v>
@@ -4512,7 +4512,7 @@
         <v>64</v>
       </c>
       <c r="B16" s="2">
-        <v>1.820931434631348</v>
+        <v>1.80641782283783</v>
       </c>
       <c r="C16" s="1">
         <v>2348</v>
@@ -4538,7 +4538,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>1.817829251289368</v>
+        <v>1.803340435028076</v>
       </c>
       <c r="C17" s="1">
         <v>2344</v>
@@ -4564,7 +4564,7 @@
         <v>65</v>
       </c>
       <c r="B18" s="2">
-        <v>1.720113277435303</v>
+        <v>1.706403255462647</v>
       </c>
       <c r="C18" s="1">
         <v>2218</v>
@@ -4590,7 +4590,7 @@
         <v>66</v>
       </c>
       <c r="B19" s="2">
-        <v>1.665826559066773</v>
+        <v>1.652549266815186</v>
       </c>
       <c r="C19" s="1">
         <v>2148</v>
@@ -4616,7 +4616,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>1.659622311592102</v>
+        <v>1.646394491195679</v>
       </c>
       <c r="C20" s="1">
         <v>2140</v>
@@ -4642,7 +4642,7 @@
         <v>67</v>
       </c>
       <c r="B21" s="2">
-        <v>1.591376185417175</v>
+        <v>1.578692317008972</v>
       </c>
       <c r="C21" s="1">
         <v>2052</v>
@@ -4668,7 +4668,7 @@
         <v>68</v>
       </c>
       <c r="B22" s="2">
-        <v>1.516925811767578</v>
+        <v>1.504835367202759</v>
       </c>
       <c r="C22" s="1">
         <v>1956</v>
@@ -4694,7 +4694,7 @@
         <v>69</v>
       </c>
       <c r="B23" s="2">
-        <v>1.507619500160217</v>
+        <v>1.495603203773499</v>
       </c>
       <c r="C23" s="1">
         <v>1944</v>
@@ -4720,16 +4720,16 @@
         <v>70</v>
       </c>
       <c r="B24" s="2">
-        <v>1.49055802822113</v>
+        <v>1.470984220504761</v>
       </c>
       <c r="C24" s="1">
-        <v>1922</v>
+        <v>1912</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1922</v>
+        <v>1912</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -4746,7 +4746,7 @@
         <v>71</v>
       </c>
       <c r="B25" s="2">
-        <v>1.473496437072754</v>
+        <v>1.461752057075501</v>
       </c>
       <c r="C25" s="1">
         <v>1900</v>
@@ -4772,7 +4772,7 @@
         <v>72</v>
       </c>
       <c r="B26" s="2">
-        <v>1.400597095489502</v>
+        <v>1.389433860778809</v>
       </c>
       <c r="C26" s="1">
         <v>1806</v>
@@ -4798,16 +4798,16 @@
         <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>1.364923000335693</v>
+        <v>1.363276124000549</v>
       </c>
       <c r="C27" s="1">
-        <v>1760</v>
+        <v>1772</v>
       </c>
       <c r="D27" s="1">
         <v>4</v>
       </c>
       <c r="E27" s="1">
-        <v>1420</v>
+        <v>1432</v>
       </c>
       <c r="F27" s="1">
         <v>336</v>
@@ -4824,7 +4824,7 @@
         <v>73</v>
       </c>
       <c r="B28" s="2">
-        <v>1.247043371200562</v>
+        <v>1.237103939056397</v>
       </c>
       <c r="C28" s="1">
         <v>1608</v>
@@ -4850,7 +4850,7 @@
         <v>17</v>
       </c>
       <c r="B29" s="2">
-        <v>1.243941187858582</v>
+        <v>1.234026551246643</v>
       </c>
       <c r="C29" s="1">
         <v>1604</v>
@@ -4876,7 +4876,7 @@
         <v>74</v>
       </c>
       <c r="B30" s="2">
-        <v>1.132265686988831</v>
+        <v>1.123241066932678</v>
       </c>
       <c r="C30" s="1">
         <v>1460</v>
@@ -4902,7 +4902,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="2">
-        <v>1.115204215049744</v>
+        <v>1.106315493583679</v>
       </c>
       <c r="C31" s="1">
         <v>1438</v>
@@ -4928,7 +4928,7 @@
         <v>75</v>
       </c>
       <c r="B32" s="2">
-        <v>1.081081032752991</v>
+        <v>1.072464466094971</v>
       </c>
       <c r="C32" s="1">
         <v>1394</v>
@@ -4954,16 +4954,16 @@
         <v>37</v>
       </c>
       <c r="B33" s="2">
-        <v>1.076427936553955</v>
+        <v>1.072464466094971</v>
       </c>
       <c r="C33" s="1">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="D33" s="1">
         <v>28</v>
       </c>
       <c r="E33" s="1">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="F33" s="1">
         <v>28</v>
@@ -4980,7 +4980,7 @@
         <v>76</v>
       </c>
       <c r="B34" s="2">
-        <v>0.9678544998168945</v>
+        <v>0.9601403474807739</v>
       </c>
       <c r="C34" s="1">
         <v>1248</v>
@@ -5006,7 +5006,7 @@
         <v>77</v>
       </c>
       <c r="B35" s="2">
-        <v>0.9461398124694824</v>
+        <v>0.9385986924171448</v>
       </c>
       <c r="C35" s="1">
         <v>1220</v>
@@ -5032,7 +5032,7 @@
         <v>78</v>
       </c>
       <c r="B36" s="2">
-        <v>0.941486656665802</v>
+        <v>0.9339826703071594</v>
       </c>
       <c r="C36" s="1">
         <v>1214</v>
@@ -5058,16 +5058,16 @@
         <v>39</v>
       </c>
       <c r="B37" s="2">
-        <v>0.912016749382019</v>
+        <v>0.9109023809432983</v>
       </c>
       <c r="C37" s="1">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="D37" s="1">
         <v>20</v>
       </c>
       <c r="E37" s="1">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8918530941009522</v>
+        <v>0.8847447037696838</v>
       </c>
       <c r="C38" s="1">
         <v>1150</v>
@@ -5110,7 +5110,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8391174674034119</v>
+        <v>0.8324293494224548</v>
       </c>
       <c r="C39" s="1">
         <v>1082</v>
@@ -5136,7 +5136,7 @@
         <v>28</v>
       </c>
       <c r="B40" s="2">
-        <v>0.7972391247749329</v>
+        <v>0.790884792804718</v>
       </c>
       <c r="C40" s="1">
         <v>1028</v>
@@ -5159,16 +5159,16 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B41" s="2">
-        <v>0.7848307490348816</v>
+        <v>0.7785753011703491</v>
       </c>
       <c r="C41" s="1">
         <v>1012</v>
       </c>
       <c r="D41" s="1">
-        <v>10012</v>
+        <v>0</v>
       </c>
       <c r="E41" s="1">
         <v>1012</v>
@@ -5180,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>10012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -5188,7 +5188,7 @@
         <v>54</v>
       </c>
       <c r="B42" s="2">
-        <v>0.784055233001709</v>
+        <v>0.7778059840202332</v>
       </c>
       <c r="C42" s="1">
         <v>1011</v>
@@ -5211,19 +5211,19 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="B43" s="2">
-        <v>0.7755244374275208</v>
+        <v>0.7754979729652405</v>
       </c>
       <c r="C43" s="1">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>10036</v>
       </c>
       <c r="E43" s="1">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -5232,76 +5232,76 @@
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7522587180137634</v>
+        <v>0.7693431973457336</v>
       </c>
       <c r="C44" s="1">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="D44" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>958</v>
+        <v>1000</v>
       </c>
       <c r="F44" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7445034980773926</v>
+        <v>0.7462629079818726</v>
       </c>
       <c r="C45" s="1">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="D45" s="1">
-        <v>4096</v>
+        <v>72</v>
       </c>
       <c r="E45" s="1">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>4096</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7414013743400574</v>
+        <v>0.7385694980621338</v>
       </c>
       <c r="C46" s="1">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D46" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="E46" s="1">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -5310,59 +5310,59 @@
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7243398427963257</v>
+        <v>0.7354921102523804</v>
       </c>
       <c r="C47" s="1">
-        <v>934</v>
+        <v>956</v>
       </c>
       <c r="D47" s="1">
-        <v>2096</v>
+        <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>918</v>
+        <v>956</v>
       </c>
       <c r="F47" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>2096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="B48" s="2">
-        <v>0.6700531244277954</v>
+        <v>0.7185665369033814</v>
       </c>
       <c r="C48" s="1">
-        <v>864</v>
+        <v>934</v>
       </c>
       <c r="D48" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
       <c r="E48" s="1">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F48" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -5370,16 +5370,16 @@
         <v>82</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6607468128204346</v>
+        <v>0.6647125482559204</v>
       </c>
       <c r="C49" s="1">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -5396,16 +5396,16 @@
         <v>83</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6591957807540894</v>
+        <v>0.6554804444313049</v>
       </c>
       <c r="C50" s="1">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -5419,77 +5419,77 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="B51" s="2">
-        <v>0.635930061340332</v>
+        <v>0.6539417505264282</v>
       </c>
       <c r="C51" s="1">
-        <v>820</v>
+        <v>850</v>
       </c>
       <c r="D51" s="1">
-        <v>1648</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>816</v>
+        <v>850</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>1644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6188685297966003</v>
+        <v>0.6308614611625671</v>
       </c>
       <c r="C52" s="1">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="D52" s="1">
-        <v>12</v>
+        <v>1648</v>
       </c>
       <c r="E52" s="1">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="B53" s="2">
-        <v>0.6080111861228943</v>
+        <v>0.6139358878135681</v>
       </c>
       <c r="C53" s="1">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E53" s="1">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -5497,19 +5497,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="B54" s="2">
-        <v>0.5862964987754822</v>
+        <v>0.6031650900840759</v>
       </c>
       <c r="C54" s="1">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="D54" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -5518,24 +5518,24 @@
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5614796876907349</v>
+        <v>0.5816234946250916</v>
       </c>
       <c r="C55" s="1">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="D55" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E55" s="1">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -5544,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -5552,16 +5552,16 @@
         <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5583776235580444</v>
+        <v>0.5570045113563538</v>
       </c>
       <c r="C56" s="1">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -5578,16 +5578,16 @@
         <v>87</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5304587483406067</v>
+        <v>0.5539271235466003</v>
       </c>
       <c r="C57" s="1">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -5601,19 +5601,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="B58" s="2">
-        <v>0.5102950930595398</v>
+        <v>0.5262307524681091</v>
       </c>
       <c r="C58" s="1">
-        <v>658</v>
+        <v>684</v>
       </c>
       <c r="D58" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>658</v>
+        <v>684</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -5622,24 +5622,24 @@
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="B59" s="2">
-        <v>0.4994377493858337</v>
+        <v>0.5062278509140015</v>
       </c>
       <c r="C59" s="1">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E59" s="1">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -5648,59 +5648,59 @@
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4808251559734345</v>
+        <v>0.4954570233821869</v>
       </c>
       <c r="C60" s="1">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="D60" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>564</v>
+        <v>644</v>
       </c>
       <c r="F60" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4792741239070892</v>
+        <v>0.4769927859306335</v>
       </c>
       <c r="C61" s="1">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D61" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
       <c r="E61" s="1">
-        <v>618</v>
+        <v>564</v>
       </c>
       <c r="F61" s="1">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -5708,19 +5708,19 @@
         <v>90</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4435999989509583</v>
+        <v>0.4754540920257568</v>
       </c>
       <c r="C62" s="1">
-        <v>572</v>
+        <v>618</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>564</v>
+        <v>618</v>
       </c>
       <c r="F62" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -5734,19 +5734,19 @@
         <v>91</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4311915934085846</v>
+        <v>0.4400643110275269</v>
       </c>
       <c r="C63" s="1">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>44</v>
+        <v>564</v>
       </c>
       <c r="F63" s="1">
-        <v>512</v>
+        <v>8</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -5757,149 +5757,149 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B64" s="2">
-        <v>0.424987405538559</v>
+        <v>0.427754819393158</v>
       </c>
       <c r="C64" s="1">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="D64" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>548</v>
+        <v>44</v>
       </c>
       <c r="F64" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4218853116035461</v>
+        <v>0.4216000735759735</v>
       </c>
       <c r="C65" s="1">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D65" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="E65" s="1">
-        <v>320</v>
+        <v>548</v>
       </c>
       <c r="F65" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="B66" s="2">
-        <v>0.3970685303211212</v>
+        <v>0.4185227155685425</v>
       </c>
       <c r="C66" s="1">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="D66" s="1">
-        <v>16416</v>
+        <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="F66" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="G66" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H66" s="1">
-        <v>16384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B67" s="2">
-        <v>0.393966406583786</v>
+        <v>0.3939037322998047</v>
       </c>
       <c r="C67" s="1">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D67" s="1">
-        <v>1024</v>
+        <v>16416</v>
       </c>
       <c r="E67" s="1">
-        <v>36</v>
+        <v>480</v>
       </c>
       <c r="F67" s="1">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H67" s="1">
-        <v>1024</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>93</v>
+        <v>11</v>
       </c>
       <c r="B68" s="2">
-        <v>0.3908643126487732</v>
+        <v>0.3908263444900513</v>
       </c>
       <c r="C68" s="1">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D68" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E68" s="1">
-        <v>504</v>
+        <v>36</v>
       </c>
       <c r="F68" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
       </c>
       <c r="H68" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="B69" s="2">
-        <v>0.389313280582428</v>
+        <v>0.3877489864826202</v>
       </c>
       <c r="C69" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D69" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -5908,47 +5908,47 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="B70" s="2">
-        <v>0.389313280582428</v>
+        <v>0.3862102925777435</v>
       </c>
       <c r="C70" s="1">
         <v>502</v>
       </c>
       <c r="D70" s="1">
-        <v>4</v>
+        <v>4096</v>
       </c>
       <c r="E70" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3862111866474152</v>
+        <v>0.3862102925777435</v>
       </c>
       <c r="C71" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D71" s="1">
-        <v>1031</v>
+        <v>4</v>
       </c>
       <c r="E71" s="1">
         <v>498</v>
@@ -5957,27 +5957,27 @@
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H71" s="1">
-        <v>1031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3707006871700287</v>
+        <v>0.3831329047679901</v>
       </c>
       <c r="C72" s="1">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="E72" s="1">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -5986,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -5994,16 +5994,16 @@
         <v>95</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3691496253013611</v>
+        <v>0.3708234429359436</v>
       </c>
       <c r="C73" s="1">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -6020,16 +6020,16 @@
         <v>96</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3629454374313355</v>
+        <v>0.3662073612213135</v>
       </c>
       <c r="C74" s="1">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -6043,25 +6043,25 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="B75" s="2">
-        <v>0.353639155626297</v>
+        <v>0.360052615404129</v>
       </c>
       <c r="C75" s="1">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="D75" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>424</v>
+        <v>468</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
       </c>
       <c r="G75" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H75" s="1">
         <v>0</v>
@@ -6069,25 +6069,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3474349677562714</v>
+        <v>0.3508205115795136</v>
       </c>
       <c r="C76" s="1">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D76" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E76" s="1">
-        <v>384</v>
+        <v>424</v>
       </c>
       <c r="F76" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -6098,19 +6098,19 @@
         <v>98</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3350265622138977</v>
+        <v>0.3492818176746368</v>
       </c>
       <c r="C77" s="1">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="F77" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
@@ -6124,19 +6124,19 @@
         <v>99</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3303734064102173</v>
+        <v>0.3446657657623291</v>
       </c>
       <c r="C78" s="1">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="F78" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
@@ -6147,25 +6147,25 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="B79" s="2">
-        <v>0.3303734064102173</v>
+        <v>0.3323562741279602</v>
       </c>
       <c r="C79" s="1">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D79" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F79" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G79" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H79" s="1">
         <v>0</v>
@@ -6173,25 +6173,25 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="B80" s="2">
-        <v>0.317965030670166</v>
+        <v>0.3277402222156525</v>
       </c>
       <c r="C80" s="1">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="D80" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E80" s="1">
-        <v>330</v>
+        <v>418</v>
       </c>
       <c r="F80" s="1">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
@@ -6202,7 +6202,7 @@
         <v>101</v>
       </c>
       <c r="B81" s="2">
-        <v>0.317965030670166</v>
+        <v>0.3154307305812836</v>
       </c>
       <c r="C81" s="1">
         <v>410</v>
@@ -6211,10 +6211,10 @@
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="F81" s="1">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
@@ -6225,25 +6225,25 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B82" s="2">
-        <v>0.3164139688014984</v>
+        <v>0.3154307305812836</v>
       </c>
       <c r="C82" s="1">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D82" s="1">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="F82" s="1">
-        <v>20</v>
+        <v>410</v>
       </c>
       <c r="G82" s="1">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -6251,25 +6251,25 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="B83" s="2">
-        <v>0.3102097809314728</v>
+        <v>0.3138920366764069</v>
       </c>
       <c r="C83" s="1">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="D83" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="E83" s="1">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="F83" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G83" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H83" s="1">
         <v>0</v>
@@ -6277,54 +6277,54 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="B84" s="2">
-        <v>0.3102097809314728</v>
+        <v>0.3077372908592224</v>
       </c>
       <c r="C84" s="1">
         <v>400</v>
       </c>
       <c r="D84" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E84" s="1">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
       </c>
       <c r="G84" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="B85" s="2">
-        <v>0.2884950935840607</v>
+        <v>0.3077372908592224</v>
       </c>
       <c r="C85" s="1">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="D85" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E85" s="1">
-        <v>340</v>
+        <v>392</v>
       </c>
       <c r="F85" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H85" s="1">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -6332,19 +6332,19 @@
         <v>104</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2838419377803803</v>
+        <v>0.2861956655979157</v>
       </c>
       <c r="C86" s="1">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="F86" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G86" s="1">
         <v>0</v>
@@ -6355,19 +6355,19 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2667804062366486</v>
+        <v>0.2815796136856079</v>
       </c>
       <c r="C87" s="1">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="D87" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="F87" s="1">
         <v>0</v>
@@ -6376,24 +6376,24 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2605762183666229</v>
+        <v>0.2646540701389313</v>
       </c>
       <c r="C88" s="1">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D88" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E88" s="1">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -6410,16 +6410,16 @@
         <v>106</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2590251564979553</v>
+        <v>0.2584993243217468</v>
       </c>
       <c r="C89" s="1">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -6433,19 +6433,19 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2574741244316101</v>
+        <v>0.2569606304168701</v>
       </c>
       <c r="C90" s="1">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D90" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E90" s="1">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F90" s="1">
         <v>0</v>
@@ -6454,24 +6454,24 @@
         <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2512699067592621</v>
+        <v>0.2554219365119934</v>
       </c>
       <c r="C91" s="1">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="D91" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E91" s="1">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
@@ -6480,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="1">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6488,19 +6488,19 @@
         <v>108</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2388615310192108</v>
+        <v>0.2492672055959702</v>
       </c>
       <c r="C92" s="1">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
       </c>
       <c r="E92" s="1">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="F92" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G92" s="1">
         <v>0</v>
@@ -6511,77 +6511,77 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2264531403779984</v>
+        <v>0.2369577139616013</v>
       </c>
       <c r="C93" s="1">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="D93" s="1">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="E93" s="1">
         <v>292</v>
       </c>
       <c r="F93" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G93" s="1">
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2109426558017731</v>
+        <v>0.2246482223272324</v>
       </c>
       <c r="C94" s="1">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="D94" s="1">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="E94" s="1">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="F94" s="1">
         <v>0</v>
       </c>
       <c r="G94" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H94" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2109426558017731</v>
+        <v>0.2092613577842712</v>
       </c>
       <c r="C95" s="1">
         <v>272</v>
       </c>
       <c r="D95" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E95" s="1">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
       </c>
       <c r="G95" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -6589,19 +6589,19 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="B96" s="2">
-        <v>0.1954321563243866</v>
+        <v>0.2092613577842712</v>
       </c>
       <c r="C96" s="1">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="D96" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="F96" s="1">
         <v>0</v>
@@ -6610,85 +6610,85 @@
         <v>0</v>
       </c>
       <c r="H96" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1907790154218674</v>
+        <v>0.1938744932413101</v>
       </c>
       <c r="C97" s="1">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D97" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E97" s="1">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="F97" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G97" s="1">
         <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1876769214868546</v>
+        <v>0.1892584264278412</v>
       </c>
       <c r="C98" s="1">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D98" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="E98" s="1">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F98" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G98" s="1">
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1861258745193481</v>
+        <v>0.186181053519249</v>
       </c>
       <c r="C99" s="1">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D99" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E99" s="1">
+        <v>242</v>
+      </c>
+      <c r="F99" s="1">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>0</v>
+      </c>
+      <c r="H99" s="1">
         <v>224</v>
-      </c>
-      <c r="F99" s="1">
-        <v>16</v>
-      </c>
-      <c r="G99" s="1">
-        <v>0</v>
-      </c>
-      <c r="H99" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -6696,19 +6696,19 @@
         <v>112</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1814727187156677</v>
+        <v>0.1846423745155335</v>
       </c>
       <c r="C100" s="1">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="F100" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G100" s="1">
         <v>0</v>
@@ -6722,19 +6722,19 @@
         <v>113</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1799216717481613</v>
+        <v>0.1800263077020645</v>
       </c>
       <c r="C101" s="1">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="F101" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G101" s="1">
         <v>0</v>
@@ -6748,19 +6748,19 @@
         <v>114</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1768195778131485</v>
+        <v>0.178487628698349</v>
       </c>
       <c r="C102" s="1">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D102" s="1">
         <v>0</v>
       </c>
       <c r="E102" s="1">
-        <v>228</v>
+        <v>200</v>
       </c>
       <c r="F102" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G102" s="1">
         <v>0</v>
@@ -6771,16 +6771,16 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1768195778131485</v>
+        <v>0.1754102557897568</v>
       </c>
       <c r="C103" s="1">
         <v>228</v>
       </c>
       <c r="D103" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E103" s="1">
         <v>228</v>
@@ -6792,24 +6792,24 @@
         <v>0</v>
       </c>
       <c r="H103" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1721664220094681</v>
+        <v>0.1754102557897568</v>
       </c>
       <c r="C104" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D104" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E104" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F104" s="1">
         <v>0</v>
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -6826,7 +6826,7 @@
         <v>116</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1721664220094681</v>
+        <v>0.1707941889762878</v>
       </c>
       <c r="C105" s="1">
         <v>222</v>
@@ -6852,7 +6852,7 @@
         <v>117</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1706153750419617</v>
+        <v>0.1692555099725723</v>
       </c>
       <c r="C106" s="1">
         <v>220</v>
@@ -6878,7 +6878,7 @@
         <v>118</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1706153750419617</v>
+        <v>0.1692555099725723</v>
       </c>
       <c r="C107" s="1">
         <v>220</v>
@@ -6904,7 +6904,7 @@
         <v>38</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1489006876945496</v>
+        <v>0.1477138996124268</v>
       </c>
       <c r="C108" s="1">
         <v>192</v>
@@ -6930,7 +6930,7 @@
         <v>119</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1457985937595367</v>
+        <v>0.1446365267038345</v>
       </c>
       <c r="C109" s="1">
         <v>188</v>
@@ -6956,7 +6956,7 @@
         <v>120</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1442475467920303</v>
+        <v>0.1430978327989578</v>
       </c>
       <c r="C110" s="1">
         <v>186</v>
@@ -6982,7 +6982,7 @@
         <v>121</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1364922970533371</v>
+        <v>0.1354044079780579</v>
       </c>
       <c r="C111" s="1">
         <v>176</v>
@@ -7008,7 +7008,7 @@
         <v>122</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1364922970533371</v>
+        <v>0.1354044079780579</v>
       </c>
       <c r="C112" s="1">
         <v>176</v>
@@ -7034,7 +7034,7 @@
         <v>43</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1333902031183243</v>
+        <v>0.1323270350694656</v>
       </c>
       <c r="C113" s="1">
         <v>172</v>
@@ -7060,7 +7060,7 @@
         <v>123</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1225328594446182</v>
+        <v>0.1215562298893929</v>
       </c>
       <c r="C114" s="1">
         <v>158</v>
@@ -7086,7 +7086,7 @@
         <v>124</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1194307655096054</v>
+        <v>0.1184788569808006</v>
       </c>
       <c r="C115" s="1">
         <v>154</v>
@@ -7112,7 +7112,7 @@
         <v>125</v>
       </c>
       <c r="B116" s="2">
-        <v>0.117879718542099</v>
+        <v>0.1169401705265045</v>
       </c>
       <c r="C116" s="1">
         <v>152</v>
@@ -7138,7 +7138,7 @@
         <v>126</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1116755232214928</v>
+        <v>0.1107854247093201</v>
       </c>
       <c r="C117" s="1">
         <v>144</v>
@@ -7164,7 +7164,7 @@
         <v>40</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1101244688034058</v>
+        <v>0.109246738255024</v>
       </c>
       <c r="C118" s="1">
         <v>142</v>
@@ -7190,7 +7190,7 @@
         <v>127</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1070223748683929</v>
+        <v>0.1061693653464317</v>
       </c>
       <c r="C119" s="1">
         <v>138</v>
@@ -7216,7 +7216,7 @@
         <v>26</v>
       </c>
       <c r="B120" s="2">
-        <v>0.1054713279008865</v>
+        <v>0.1046306788921356</v>
       </c>
       <c r="C120" s="1">
         <v>136</v>
@@ -7242,7 +7242,7 @@
         <v>128</v>
       </c>
       <c r="B121" s="2">
-        <v>0.0992671325802803</v>
+        <v>0.09847593307495117</v>
       </c>
       <c r="C121" s="1">
         <v>128</v>
@@ -7268,7 +7268,7 @@
         <v>129</v>
       </c>
       <c r="B122" s="2">
-        <v>0.0992671325802803</v>
+        <v>0.09847593307495117</v>
       </c>
       <c r="C122" s="1">
         <v>128</v>
@@ -7294,16 +7294,16 @@
         <v>130</v>
       </c>
       <c r="B123" s="2">
-        <v>0.0992671325802803</v>
+        <v>0.09693724662065506</v>
       </c>
       <c r="C123" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D123" s="1">
         <v>0</v>
       </c>
       <c r="E123" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -7320,7 +7320,7 @@
         <v>131</v>
       </c>
       <c r="B124" s="2">
-        <v>0.0977160781621933</v>
+        <v>0.09693724662065506</v>
       </c>
       <c r="C124" s="1">
         <v>126</v>
@@ -7346,7 +7346,7 @@
         <v>42</v>
       </c>
       <c r="B125" s="2">
-        <v>0.0977160781621933</v>
+        <v>0.09693724662065506</v>
       </c>
       <c r="C125" s="1">
         <v>126</v>
@@ -7372,7 +7372,7 @@
         <v>23</v>
       </c>
       <c r="B126" s="2">
-        <v>0.09306293725967407</v>
+        <v>0.09232118725776672</v>
       </c>
       <c r="C126" s="1">
         <v>120</v>
@@ -7398,16 +7398,16 @@
         <v>132</v>
       </c>
       <c r="B127" s="2">
-        <v>0.08996083587408066</v>
+        <v>0.08770512789487839</v>
       </c>
       <c r="C127" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -7424,16 +7424,16 @@
         <v>133</v>
       </c>
       <c r="B128" s="2">
-        <v>0.08840978890657425</v>
+        <v>0.08616644144058228</v>
       </c>
       <c r="C128" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D128" s="1">
         <v>0</v>
       </c>
       <c r="E128" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F128" s="1">
         <v>0</v>
@@ -7450,7 +7450,7 @@
         <v>134</v>
       </c>
       <c r="B129" s="2">
-        <v>0.08685874193906784</v>
+        <v>0.08616644144058228</v>
       </c>
       <c r="C129" s="1">
         <v>112</v>
@@ -7476,7 +7476,7 @@
         <v>135</v>
       </c>
       <c r="B130" s="2">
-        <v>0.08685874193906784</v>
+        <v>0.08616644144058228</v>
       </c>
       <c r="C130" s="1">
         <v>112</v>
@@ -7502,7 +7502,7 @@
         <v>136</v>
       </c>
       <c r="B131" s="2">
-        <v>0.08530768752098084</v>
+        <v>0.08462775498628616</v>
       </c>
       <c r="C131" s="1">
         <v>110</v>
@@ -7528,7 +7528,7 @@
         <v>137</v>
       </c>
       <c r="B132" s="2">
-        <v>0.08375664055347443</v>
+        <v>0.08308906853199005</v>
       </c>
       <c r="C132" s="1">
         <v>108</v>
@@ -7554,7 +7554,7 @@
         <v>12</v>
       </c>
       <c r="B133" s="2">
-        <v>0.08375664055347443</v>
+        <v>0.08308906853199005</v>
       </c>
       <c r="C133" s="1">
         <v>108</v>
@@ -7580,7 +7580,7 @@
         <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07600139826536179</v>
+        <v>0.07539563626050949</v>
       </c>
       <c r="C134" s="1">
         <v>98</v>
@@ -7606,7 +7606,7 @@
         <v>139</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07600139826536179</v>
+        <v>0.07539563626050949</v>
       </c>
       <c r="C135" s="1">
         <v>98</v>
@@ -7632,7 +7632,7 @@
         <v>140</v>
       </c>
       <c r="B136" s="2">
-        <v>0.07134824991226196</v>
+        <v>0.07077957689762116</v>
       </c>
       <c r="C136" s="1">
         <v>92</v>
@@ -7658,7 +7658,7 @@
         <v>141</v>
       </c>
       <c r="B137" s="2">
-        <v>0.06669510155916214</v>
+        <v>0.06616351753473282</v>
       </c>
       <c r="C137" s="1">
         <v>86</v>
@@ -7684,7 +7684,7 @@
         <v>142</v>
       </c>
       <c r="B138" s="2">
-        <v>0.06514405459165573</v>
+        <v>0.06462483108043671</v>
       </c>
       <c r="C138" s="1">
         <v>84</v>
@@ -7710,7 +7710,7 @@
         <v>143</v>
       </c>
       <c r="B139" s="2">
-        <v>0.06514405459165573</v>
+        <v>0.06462483108043671</v>
       </c>
       <c r="C139" s="1">
         <v>84</v>
@@ -7736,7 +7736,7 @@
         <v>144</v>
       </c>
       <c r="B140" s="2">
-        <v>0.06514405459165573</v>
+        <v>0.06462483108043671</v>
       </c>
       <c r="C140" s="1">
         <v>84</v>
@@ -7762,7 +7762,7 @@
         <v>53</v>
       </c>
       <c r="B141" s="2">
-        <v>0.06514405459165573</v>
+        <v>0.06462483108043671</v>
       </c>
       <c r="C141" s="1">
         <v>84</v>
@@ -7788,7 +7788,7 @@
         <v>145</v>
       </c>
       <c r="B142" s="2">
-        <v>0.06359300762414932</v>
+        <v>0.06308614462614059</v>
       </c>
       <c r="C142" s="1">
         <v>82</v>
@@ -7814,7 +7814,7 @@
         <v>146</v>
       </c>
       <c r="B143" s="2">
-        <v>0.06204195693135262</v>
+        <v>0.06154745817184448</v>
       </c>
       <c r="C143" s="1">
         <v>80</v>
@@ -7840,16 +7840,16 @@
         <v>147</v>
       </c>
       <c r="B144" s="2">
-        <v>0.06204195693135262</v>
+        <v>0.06000877171754837</v>
       </c>
       <c r="C144" s="1">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D144" s="1">
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>33</v>
       </c>
       <c r="B145" s="2">
-        <v>0.0589398592710495</v>
+        <v>0.05847008526325226</v>
       </c>
       <c r="C145" s="1">
         <v>76</v>
@@ -7892,7 +7892,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="2">
-        <v>0.05118461325764656</v>
+        <v>0.0507766529917717</v>
       </c>
       <c r="C146" s="1">
         <v>66</v>
@@ -7918,7 +7918,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04653146862983704</v>
+        <v>0.04616059362888336</v>
       </c>
       <c r="C147" s="1">
         <v>60</v>
@@ -7944,7 +7944,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04653146862983704</v>
+        <v>0.04616059362888336</v>
       </c>
       <c r="C148" s="1">
         <v>60</v>
@@ -7970,7 +7970,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04653146862983704</v>
+        <v>0.04616059362888336</v>
       </c>
       <c r="C149" s="1">
         <v>60</v>
@@ -7996,7 +7996,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="2">
-        <v>0.04498041793704033</v>
+        <v>0.04462190717458725</v>
       </c>
       <c r="C150" s="1">
         <v>58</v>
@@ -8022,7 +8022,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="2">
-        <v>0.04187832027673721</v>
+        <v>0.04154453426599503</v>
       </c>
       <c r="C151" s="1">
         <v>54</v>
@@ -8048,7 +8048,7 @@
         <v>46</v>
       </c>
       <c r="B152" s="2">
-        <v>0.04187832027673721</v>
+        <v>0.04154453426599503</v>
       </c>
       <c r="C152" s="1">
         <v>54</v>
@@ -8074,7 +8074,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="2">
-        <v>0.04032726958394051</v>
+        <v>0.04000584781169891</v>
       </c>
       <c r="C153" s="1">
         <v>52</v>
@@ -8100,7 +8100,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="2">
-        <v>0.0387762226164341</v>
+        <v>0.0384671613574028</v>
       </c>
       <c r="C154" s="1">
         <v>50</v>
@@ -8126,7 +8126,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="2">
-        <v>0.03722517192363739</v>
+        <v>0.03692847490310669</v>
       </c>
       <c r="C155" s="1">
         <v>48</v>
@@ -8152,7 +8152,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="2">
-        <v>0.03722517192363739</v>
+        <v>0.03692847490310669</v>
       </c>
       <c r="C156" s="1">
         <v>48</v>
@@ -8178,7 +8178,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="2">
-        <v>0.03722517192363739</v>
+        <v>0.03692847490310669</v>
       </c>
       <c r="C157" s="1">
         <v>48</v>
@@ -8204,7 +8204,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="2">
-        <v>0.03412307426333427</v>
+        <v>0.03385110199451447</v>
       </c>
       <c r="C158" s="1">
         <v>44</v>
@@ -8230,7 +8230,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="2">
-        <v>0.03412307426333427</v>
+        <v>0.03385110199451447</v>
       </c>
       <c r="C159" s="1">
         <v>44</v>
@@ -8256,7 +8256,7 @@
         <v>49</v>
       </c>
       <c r="B160" s="2">
-        <v>0.03412307426333427</v>
+        <v>0.03385110199451447</v>
       </c>
       <c r="C160" s="1">
         <v>44</v>
@@ -8282,7 +8282,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.03412307426333427</v>
+        <v>0.03385110199451447</v>
       </c>
       <c r="C161" s="1">
         <v>44</v>
@@ -8308,7 +8308,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.03412307426333427</v>
+        <v>0.03385110199451447</v>
       </c>
       <c r="C162" s="1">
         <v>44</v>
@@ -8334,7 +8334,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.03102097846567631</v>
+        <v>0.03077372908592224</v>
       </c>
       <c r="C163" s="1">
         <v>40</v>
@@ -8360,7 +8360,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.02946992963552475</v>
+        <v>0.02923504263162613</v>
       </c>
       <c r="C164" s="1">
         <v>38</v>
@@ -8386,7 +8386,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.02946992963552475</v>
+        <v>0.02923504263162613</v>
       </c>
       <c r="C165" s="1">
         <v>38</v>
@@ -8412,7 +8412,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.02791888080537319</v>
+        <v>0.02769635617733002</v>
       </c>
       <c r="C166" s="1">
         <v>36</v>
@@ -8438,7 +8438,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.02791888080537319</v>
+        <v>0.02769635617733002</v>
       </c>
       <c r="C167" s="1">
         <v>36</v>
@@ -8464,7 +8464,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.02791888080537319</v>
+        <v>0.02769635617733002</v>
       </c>
       <c r="C168" s="1">
         <v>36</v>
@@ -8490,7 +8490,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.02791888080537319</v>
+        <v>0.02769635617733002</v>
       </c>
       <c r="C169" s="1">
         <v>36</v>
@@ -8516,7 +8516,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="2">
-        <v>0.02481678314507008</v>
+        <v>0.02461898326873779</v>
       </c>
       <c r="C170" s="1">
         <v>32</v>
@@ -8542,7 +8542,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="2">
-        <v>0.02481678314507008</v>
+        <v>0.02461898326873779</v>
       </c>
       <c r="C171" s="1">
         <v>32</v>
@@ -8568,7 +8568,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="2">
-        <v>0.02481678314507008</v>
+        <v>0.02461898326873779</v>
       </c>
       <c r="C172" s="1">
         <v>32</v>
@@ -8594,7 +8594,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="2">
-        <v>0.02481678314507008</v>
+        <v>0.02461898326873779</v>
       </c>
       <c r="C173" s="1">
         <v>32</v>
@@ -8620,7 +8620,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="2">
-        <v>0.02481678314507008</v>
+        <v>0.02461898326873779</v>
       </c>
       <c r="C174" s="1">
         <v>32</v>
@@ -8646,7 +8646,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="2">
-        <v>0.02326573431491852</v>
+        <v>0.02308029681444168</v>
       </c>
       <c r="C175" s="1">
         <v>30</v>
@@ -8672,7 +8672,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="2">
-        <v>0.02326573431491852</v>
+        <v>0.02308029681444168</v>
       </c>
       <c r="C176" s="1">
         <v>30</v>
@@ -8698,7 +8698,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="2">
-        <v>0.02016363479197025</v>
+        <v>0.02000292390584946</v>
       </c>
       <c r="C177" s="1">
         <v>26</v>
@@ -8724,7 +8724,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="2">
-        <v>0.02016363479197025</v>
+        <v>0.02000292390584946</v>
       </c>
       <c r="C178" s="1">
         <v>26</v>
@@ -8750,7 +8750,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="2">
-        <v>0.0186125859618187</v>
+        <v>0.01846423745155335</v>
       </c>
       <c r="C179" s="1">
         <v>24</v>
@@ -8776,7 +8776,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="2">
-        <v>0.0186125859618187</v>
+        <v>0.01846423745155335</v>
       </c>
       <c r="C180" s="1">
         <v>24</v>
@@ -8802,7 +8802,7 @@
         <v>48</v>
       </c>
       <c r="B181" s="2">
-        <v>0.01240839157253504</v>
+        <v>0.0123094916343689</v>
       </c>
       <c r="C181" s="1">
         <v>16</v>
@@ -8828,7 +8828,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2">
-        <v>0.006204195786267519</v>
+        <v>0.006154745817184448</v>
       </c>
       <c r="C182" s="1">
         <v>8</v>
@@ -8854,7 +8854,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="2">
-        <v>0.006204195786267519</v>
+        <v>0.006154745817184448</v>
       </c>
       <c r="C183" s="1">
         <v>8</v>
@@ -8880,7 +8880,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="2">
-        <v>0.00310209789313376</v>
+        <v>0.003077372908592224</v>
       </c>
       <c r="C184" s="1">
         <v>4</v>
@@ -8906,7 +8906,7 @@
         <v>47</v>
       </c>
       <c r="B185" s="2">
-        <v>0.00310209789313376</v>
+        <v>0.003077372908592224</v>
       </c>
       <c r="C185" s="1">
         <v>4</v>
@@ -8932,7 +8932,7 @@
         <v>184</v>
       </c>
       <c r="B186" s="2">
-        <v>0.00310209789313376</v>
+        <v>0.003077372908592224</v>
       </c>
       <c r="C186" s="1">
         <v>4</v>
@@ -8958,7 +8958,7 @@
         <v>185</v>
       </c>
       <c r="B187" s="2">
-        <v>0.00310209789313376</v>
+        <v>0.003077372908592224</v>
       </c>
       <c r="C187" s="1">
         <v>4</v>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -221,13 +221,13 @@
     <t>arm_common_tables.o</t>
   </si>
   <si>
+    <t>motor_mode_test_sweep.o</t>
+  </si>
+  <si>
     <t>powf.o</t>
   </si>
   <si>
     <t>jm_proto_can.o</t>
-  </si>
-  <si>
-    <t>motor_mode_test_sweep.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_rcc.o</t>
@@ -870,166 +870,166 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="186"/>
                 <c:pt idx="0">
-                  <c:v>34.55629730224609</c:v>
+                  <c:v>36.23833465576172</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21.19232749938965</c:v>
+                  <c:v>20.64438247680664</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.95602989196777</c:v>
+                  <c:v>12.63110256195068</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.287754058837891</c:v>
+                  <c:v>5.151034832000732</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.287754058837891</c:v>
+                  <c:v>5.151034832000732</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.84366512298584</c:v>
+                  <c:v>4.718428611755371</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.705842971801758</c:v>
+                  <c:v>2.635881185531616</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.638713121414185</c:v>
+                  <c:v>2.570487260818481</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.127494812011719</c:v>
+                  <c:v>2.072486639022827</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.33097517490387</c:v>
+                  <c:v>1.29656183719635</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.321938514709473</c:v>
+                  <c:v>1.287758708000183</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9294880032539368</c:v>
+                  <c:v>0.9054553508758545</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5060545802116394</c:v>
+                  <c:v>0.4929701387882233</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4595801830291748</c:v>
+                  <c:v>0.4476973712444305</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.4389248788356781</c:v>
+                  <c:v>0.4275761544704437</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3872866630554199</c:v>
+                  <c:v>0.3772730827331543</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3459760844707489</c:v>
+                  <c:v>0.3370306193828583</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2943378686904907</c:v>
+                  <c:v>0.2867275476455689</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.2891740500926971</c:v>
+                  <c:v>0.2816972136497498</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.2633549273014069</c:v>
+                  <c:v>0.2565456926822662</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2581911087036133</c:v>
+                  <c:v>0.2515153884887695</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.1704061329364777</c:v>
+                  <c:v>0.1660001575946808</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1652423143386841</c:v>
+                  <c:v>0.1609698385000229</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.1290955543518066</c:v>
+                  <c:v>0.1257576942443848</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1084402650594711</c:v>
+                  <c:v>0.1056364625692368</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.09811262041330338</c:v>
+                  <c:v>0.09557584673166275</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.0929488018155098</c:v>
+                  <c:v>0.09054553508758545</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.0929488018155098</c:v>
+                  <c:v>0.09054553508758545</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.0929488018155098</c:v>
+                  <c:v>0.09054553508758545</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.08778497576713562</c:v>
+                  <c:v>0.08551523089408875</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.08262115716934204</c:v>
+                  <c:v>0.08048491925001144</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.05680204555392265</c:v>
+                  <c:v>0.05533338338136673</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.05163822323083878</c:v>
+                  <c:v>0.05030307546257973</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.0464744009077549</c:v>
+                  <c:v>0.04527276754379273</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.04131057858467102</c:v>
+                  <c:v>0.04024245962500572</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.04131057858467102</c:v>
+                  <c:v>0.04024245962500572</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03614675626158714</c:v>
+                  <c:v>0.03521215170621872</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.02581911161541939</c:v>
+                  <c:v>0.02515153773128986</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.02581911161541939</c:v>
+                  <c:v>0.02515153773128986</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.01549146696925163</c:v>
+                  <c:v>0.01509092282503843</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.01549146696925163</c:v>
+                  <c:v>0.01509092282503843</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.01549146696925163</c:v>
+                  <c:v>0.01509092282503843</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01549146696925163</c:v>
+                  <c:v>0.01509092282503843</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01032764464616776</c:v>
+                  <c:v>0.01006061490625143</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01032764464616776</c:v>
+                  <c:v>0.01006061490625143</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.01032764464616776</c:v>
+                  <c:v>0.01006061490625143</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.005163822323083878</c:v>
+                  <c:v>0.005030307453125715</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.005163822323083878</c:v>
+                  <c:v>0.005030307453125715</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.005163822323083878</c:v>
+                  <c:v>0.005030307453125715</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.005163822323083878</c:v>
+                  <c:v>0.005030307453125715</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.005163822323083878</c:v>
+                  <c:v>0.005030307453125715</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.005163822323083878</c:v>
+                  <c:v>0.005030307453125715</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.005163822323083878</c:v>
+                  <c:v>0.005030307453125715</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.003872866742312908</c:v>
+                  <c:v>0.003772730706259608</c:v>
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>0</c:v>
@@ -1160,13 +1160,13 @@
                   <c:v>arm_common_tables.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
+                  <c:v>motor_mode_test_sweep.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
                   <c:v>powf.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>jm_proto_can.o</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>motor_mode_test_sweep.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
@@ -1220,10 +1220,10 @@
                   <c:v>motor_mode_load_sim.o</c:v>
                 </c:pt>
                 <c:pt idx="39">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="40">
                   <c:v>motor_pid_load.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>motor_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>foc_core.o</c:v>
@@ -1481,19 +1481,19 @@
                   <c:v>floorf.o</c:v>
                 </c:pt>
                 <c:pt idx="126">
+                  <c:v>runtime_param.o</c:v>
+                </c:pt>
+                <c:pt idx="127">
                   <c:v>motor_mode_position.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="128">
                   <c:v>motor_mode_current.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="129">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="130">
                   <c:v>ceilf.o</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>runtime_param.o</c:v>
                 </c:pt>
                 <c:pt idx="131">
                   <c:v>uldiv.o</c:v>
@@ -1670,559 +1670,559 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="186"/>
                 <c:pt idx="0">
-                  <c:v>4.509890079498291</c:v>
+                  <c:v>4.513896942138672</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.786707401275635</c:v>
+                  <c:v>3.775900840759277</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.646686792373657</c:v>
+                  <c:v>3.636280059814453</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.377416610717773</c:v>
+                  <c:v>3.367778301239014</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.01120924949646</c:v>
+                  <c:v>3.002615928649902</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.831182956695557</c:v>
+                  <c:v>2.823103427886963</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.549603462219238</c:v>
+                  <c:v>2.542327404022217</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.454204797744751</c:v>
+                  <c:v>2.447201013565064</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.220324516296387</c:v>
+                  <c:v>2.213988065719605</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.211092472076416</c:v>
+                  <c:v>2.204782485961914</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.878736138343811</c:v>
+                  <c:v>2.066695928573608</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.846423745155335</c:v>
+                  <c:v>1.841154456138611</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.809495210647583</c:v>
+                  <c:v>1.804331302642822</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.80641782283783</c:v>
+                  <c:v>1.801262736320496</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.803340435028076</c:v>
+                  <c:v>1.798194169998169</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.706403255462647</c:v>
+                  <c:v>1.701533555984497</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.652549266815186</c:v>
+                  <c:v>1.647833228111267</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.646394491195679</c:v>
+                  <c:v>1.641695976257324</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.578692317008972</c:v>
+                  <c:v>1.57418704032898</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.504835367202759</c:v>
+                  <c:v>1.526623845100403</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.495603203773499</c:v>
+                  <c:v>1.500540852546692</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.470984220504761</c:v>
+                  <c:v>1.491335034370422</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.461752057075501</c:v>
+                  <c:v>1.45758056640625</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.389433860778809</c:v>
+                  <c:v>1.385468721389771</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.363276124000549</c:v>
+                  <c:v>1.36859142780304</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.237103939056397</c:v>
+                  <c:v>1.233573436737061</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.234026551246643</c:v>
+                  <c:v>1.230504870414734</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.123241066932678</c:v>
+                  <c:v>1.120035648345947</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.106315493583679</c:v>
+                  <c:v>1.103158354759216</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.072464466094971</c:v>
+                  <c:v>1.069403886795044</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.072464466094971</c:v>
+                  <c:v>1.069403886795044</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.9601403474807739</c:v>
+                  <c:v>0.9574002623558044</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.9385986924171448</c:v>
+                  <c:v>0.9359201788902283</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9339826703071594</c:v>
+                  <c:v>0.9313172698020935</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9109023809432983</c:v>
+                  <c:v>0.9083028435707092</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8847447037696838</c:v>
+                  <c:v>0.8822197914123535</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8324293494224548</c:v>
+                  <c:v>0.8300538063049316</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.790884792804718</c:v>
+                  <c:v>0.7886278033256531</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.7785753011703491</c:v>
+                  <c:v>0.7763534188270569</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7778059840202332</c:v>
+                  <c:v>0.7763534188270569</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.7754979729652405</c:v>
+                  <c:v>0.7755863070487976</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7693431973457336</c:v>
+                  <c:v>0.7671476602554321</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7462629079818726</c:v>
+                  <c:v>0.7441332340240479</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7385694980621338</c:v>
+                  <c:v>0.7364617586135864</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.7354921102523804</c:v>
+                  <c:v>0.7333931922912598</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.7185665369033814</c:v>
+                  <c:v>0.7165158987045288</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6647125482559204</c:v>
+                  <c:v>0.6628155708312988</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6554804444313049</c:v>
+                  <c:v>0.6536098122596741</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6539417505264282</c:v>
+                  <c:v>0.6520755290985107</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.6308614611625671</c:v>
+                  <c:v>0.6290611028671265</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.6139358878135681</c:v>
+                  <c:v>0.6121838688850403</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.6031650900840759</c:v>
+                  <c:v>0.6014437675476074</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5816234946250916</c:v>
+                  <c:v>0.5799636244773865</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5570045113563538</c:v>
+                  <c:v>0.5554149150848389</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5539271235466003</c:v>
+                  <c:v>0.5523463487625122</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.5262307524681091</c:v>
+                  <c:v>0.5247290134429932</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.5062278509140015</c:v>
+                  <c:v>0.5047831535339356</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4954570233821869</c:v>
+                  <c:v>0.4940431118011475</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4769927859306335</c:v>
+                  <c:v>0.4756315648555756</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4754540920257568</c:v>
+                  <c:v>0.4740972518920898</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4400643110275269</c:v>
+                  <c:v>0.4388084709644318</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.427754819393158</c:v>
+                  <c:v>0.426534116268158</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4216000735759735</c:v>
+                  <c:v>0.4203969240188599</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4185227155685425</c:v>
+                  <c:v>0.4173283278942108</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.3939037322998047</c:v>
+                  <c:v>0.3927796185016632</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.3908263444900513</c:v>
+                  <c:v>0.3897110223770142</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.3877489864826202</c:v>
+                  <c:v>0.3866424262523651</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3862102925777435</c:v>
+                  <c:v>0.3851081430912018</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3862102925777435</c:v>
+                  <c:v>0.3851081430912018</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3831329047679901</c:v>
+                  <c:v>0.3820395469665527</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3708234429359436</c:v>
+                  <c:v>0.3697651624679565</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3662073612213135</c:v>
+                  <c:v>0.3651622831821442</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.360052615404129</c:v>
+                  <c:v>0.3590251207351685</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3508205115795136</c:v>
+                  <c:v>0.3498193323612213</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3492818176746368</c:v>
+                  <c:v>0.348285049200058</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3446657657623291</c:v>
+                  <c:v>0.3436821699142456</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.3323562741279602</c:v>
+                  <c:v>0.3314077854156494</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.3277402222156525</c:v>
+                  <c:v>0.326804906129837</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.3154307305812836</c:v>
+                  <c:v>0.3145305514335632</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.3154307305812836</c:v>
+                  <c:v>0.3145305514335632</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.3138920366764069</c:v>
+                  <c:v>0.3129962384700775</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.3077372908592224</c:v>
+                  <c:v>0.3068590760231018</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.3077372908592224</c:v>
+                  <c:v>0.3068590760231018</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2861956655979157</c:v>
+                  <c:v>0.2853789329528809</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2815796136856079</c:v>
+                  <c:v>0.2807760536670685</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2646540701389313</c:v>
+                  <c:v>0.2638987898826599</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2584993243217468</c:v>
+                  <c:v>0.2577616274356842</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2569606304168701</c:v>
+                  <c:v>0.2562273144721985</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2554219365119934</c:v>
+                  <c:v>0.2546930313110352</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2492672055959702</c:v>
+                  <c:v>0.2485558390617371</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2369577139616013</c:v>
+                  <c:v>0.2362814843654633</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2246482223272324</c:v>
+                  <c:v>0.2240071147680283</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2092613577842712</c:v>
+                  <c:v>0.2086641639471054</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.2092613577842712</c:v>
+                  <c:v>0.2086641639471054</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1938744932413101</c:v>
+                  <c:v>0.1933212131261826</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1892584264278412</c:v>
+                  <c:v>0.1887183338403702</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.186181053519249</c:v>
+                  <c:v>0.1856497377157211</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1846423745155335</c:v>
+                  <c:v>0.1841154396533966</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1800263077020645</c:v>
+                  <c:v>0.1795125603675842</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.178487628698349</c:v>
+                  <c:v>0.1779782623052597</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1754102557897568</c:v>
+                  <c:v>0.1749096661806107</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1754102557897568</c:v>
+                  <c:v>0.1749096661806107</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1707941889762878</c:v>
+                  <c:v>0.1703067868947983</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1692555099725723</c:v>
+                  <c:v>0.1687724888324738</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1692555099725723</c:v>
+                  <c:v>0.1687724888324738</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1477138996124268</c:v>
+                  <c:v>0.1472923457622528</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1446365267038345</c:v>
+                  <c:v>0.144223764538765</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1430978327989578</c:v>
+                  <c:v>0.1426894664764404</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.1354044079780579</c:v>
+                  <c:v>0.135017991065979</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1354044079780579</c:v>
+                  <c:v>0.135017991065979</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1323270350694656</c:v>
+                  <c:v>0.13194939494133</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1215562298893929</c:v>
+                  <c:v>0.1212093308568001</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1184788569808006</c:v>
+                  <c:v>0.1181407421827316</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1169401705265045</c:v>
+                  <c:v>0.1166064441204071</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1107854247093201</c:v>
+                  <c:v>0.1104692667722702</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.109246738255024</c:v>
+                  <c:v>0.1089349687099457</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1061693653464317</c:v>
+                  <c:v>0.1058663800358772</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.1046306788921356</c:v>
+                  <c:v>0.1043320819735527</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.09847593307495117</c:v>
+                  <c:v>0.0981949046254158</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.09847593307495117</c:v>
+                  <c:v>0.0981949046254158</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.09693724662065506</c:v>
+                  <c:v>0.09666060656309128</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.09693724662065506</c:v>
+                  <c:v>0.09666060656309128</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.09693724662065506</c:v>
+                  <c:v>0.09666060656309128</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.09232118725776672</c:v>
+                  <c:v>0.0920577198266983</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.08770512789487839</c:v>
+                  <c:v>0.08745483309030533</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.08616644144058228</c:v>
+                  <c:v>0.0859205424785614</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.08616644144058228</c:v>
+                  <c:v>0.0859205424785614</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.08616644144058228</c:v>
+                  <c:v>0.0859205424785614</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.08462775498628616</c:v>
+                  <c:v>0.0859205424785614</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.08308906853199005</c:v>
+                  <c:v>0.08438624441623688</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.08308906853199005</c:v>
+                  <c:v>0.08285194635391235</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07539563626050949</c:v>
+                  <c:v>0.07518047094345093</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07539563626050949</c:v>
+                  <c:v>0.07518047094345093</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.07077957689762116</c:v>
+                  <c:v>0.07057758420705795</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06616351753473282</c:v>
+                  <c:v>0.06597469747066498</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06462483108043671</c:v>
+                  <c:v>0.06444040685892105</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.06462483108043671</c:v>
+                  <c:v>0.06444040685892105</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.06462483108043671</c:v>
+                  <c:v>0.06444040685892105</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.06462483108043671</c:v>
+                  <c:v>0.06444040685892105</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.06308614462614059</c:v>
+                  <c:v>0.06290610879659653</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.06154745817184448</c:v>
+                  <c:v>0.0613718144595623</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.06000877171754837</c:v>
+                  <c:v>0.05983751639723778</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.05847008526325226</c:v>
+                  <c:v>0.05830322206020355</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.0507766529917717</c:v>
+                  <c:v>0.05063174664974213</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04616059362888336</c:v>
+                  <c:v>0.04602885991334915</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04616059362888336</c:v>
+                  <c:v>0.04602885991334915</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04616059362888336</c:v>
+                  <c:v>0.04602885991334915</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.04462190717458725</c:v>
+                  <c:v>0.04449456557631493</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.04154453426599503</c:v>
+                  <c:v>0.04142597317695618</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.04154453426599503</c:v>
+                  <c:v>0.04142597317695618</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.04000584781169891</c:v>
+                  <c:v>0.03989167883992195</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.0384671613574028</c:v>
+                  <c:v>0.03835738450288773</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03692847490310669</c:v>
+                  <c:v>0.0368230864405632</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03692847490310669</c:v>
+                  <c:v>0.0368230864405632</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.03692847490310669</c:v>
+                  <c:v>0.0368230864405632</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.03385110199451447</c:v>
+                  <c:v>0.03375449776649475</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.03385110199451447</c:v>
+                  <c:v>0.03375449776649475</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.03385110199451447</c:v>
+                  <c:v>0.03375449776649475</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.03385110199451447</c:v>
+                  <c:v>0.03375449776649475</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.03385110199451447</c:v>
+                  <c:v>0.03375449776649475</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.03077372908592224</c:v>
+                  <c:v>0.03068590722978115</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.02923504263162613</c:v>
+                  <c:v>0.02915161103010178</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.02923504263162613</c:v>
+                  <c:v>0.02915161103010178</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.02769635617733002</c:v>
+                  <c:v>0.02761731669306755</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02769635617733002</c:v>
+                  <c:v>0.02761731669306755</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02769635617733002</c:v>
+                  <c:v>0.02761731669306755</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02769635617733002</c:v>
+                  <c:v>0.02761731669306755</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.02461898326873779</c:v>
+                  <c:v>0.02454872615635395</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.02461898326873779</c:v>
+                  <c:v>0.02454872615635395</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.02461898326873779</c:v>
+                  <c:v>0.02454872615635395</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.02461898326873779</c:v>
+                  <c:v>0.02454872615635395</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.02461898326873779</c:v>
+                  <c:v>0.02454872615635395</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.02308029681444168</c:v>
+                  <c:v>0.02301442995667458</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>0.02308029681444168</c:v>
+                  <c:v>0.02301442995667458</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>0.02000292390584946</c:v>
+                  <c:v>0.01994583941996098</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>0.02000292390584946</c:v>
+                  <c:v>0.01994583941996098</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>0.01846423745155335</c:v>
+                  <c:v>0.0184115432202816</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>0.01846423745155335</c:v>
+                  <c:v>0.0184115432202816</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>0.0123094916343689</c:v>
+                  <c:v>0.01227436307817698</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>0.006154745817184448</c:v>
+                  <c:v>0.006137181539088488</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>0.006154745817184448</c:v>
+                  <c:v>0.006137181539088488</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>0.003077372908592224</c:v>
+                  <c:v>0.003068590769544244</c:v>
                 </c:pt>
                 <c:pt idx="182">
-                  <c:v>0.003077372908592224</c:v>
+                  <c:v>0.003068590769544244</c:v>
                 </c:pt>
                 <c:pt idx="183">
-                  <c:v>0.003077372908592224</c:v>
+                  <c:v>0.003068590769544244</c:v>
                 </c:pt>
                 <c:pt idx="184">
-                  <c:v>0.003077372908592224</c:v>
+                  <c:v>0.003068590769544244</c:v>
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>0</c:v>
@@ -2689,16 +2689,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>34.55629730224609</v>
+        <v>36.23833465576172</v>
       </c>
       <c r="C3" s="1">
-        <v>26768</v>
+        <v>28816</v>
       </c>
       <c r="D3" s="1">
-        <v>2442</v>
+        <v>2694</v>
       </c>
       <c r="E3" s="1">
-        <v>2394</v>
+        <v>2646</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>48</v>
       </c>
       <c r="H3" s="1">
-        <v>26720</v>
+        <v>28768</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2715,7 +2715,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>21.19232749938965</v>
+        <v>20.64438247680664</v>
       </c>
       <c r="C4" s="1">
         <v>16416</v>
@@ -2741,16 +2741,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>12.95602989196777</v>
+        <v>12.63110256195068</v>
       </c>
       <c r="C5" s="1">
-        <v>10036</v>
+        <v>10044</v>
       </c>
       <c r="D5" s="1">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="E5" s="1">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>10036</v>
+        <v>10044</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2767,7 +2767,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>5.287754058837891</v>
+        <v>5.151034832000732</v>
       </c>
       <c r="C6" s="1">
         <v>4096</v>
@@ -2793,7 +2793,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>5.287754058837891</v>
+        <v>5.151034832000732</v>
       </c>
       <c r="C7" s="1">
         <v>4096</v>
@@ -2819,7 +2819,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.84366512298584</v>
+        <v>4.718428611755371</v>
       </c>
       <c r="C8" s="1">
         <v>3752</v>
@@ -2845,7 +2845,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.705842971801758</v>
+        <v>2.635881185531616</v>
       </c>
       <c r="C9" s="1">
         <v>2096</v>
@@ -2871,7 +2871,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.638713121414185</v>
+        <v>2.570487260818481</v>
       </c>
       <c r="C10" s="1">
         <v>2044</v>
@@ -2897,7 +2897,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.127494812011719</v>
+        <v>2.072486639022827</v>
       </c>
       <c r="C11" s="1">
         <v>1648</v>
@@ -2923,7 +2923,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.33097517490387</v>
+        <v>1.29656183719635</v>
       </c>
       <c r="C12" s="1">
         <v>1031</v>
@@ -2949,7 +2949,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.321938514709473</v>
+        <v>1.287758708000183</v>
       </c>
       <c r="C13" s="1">
         <v>1024</v>
@@ -2975,16 +2975,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.9294880032539368</v>
+        <v>0.9054553508758545</v>
       </c>
       <c r="C14" s="1">
         <v>720</v>
       </c>
       <c r="D14" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E14" s="1">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -3001,16 +3001,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.5060545802116394</v>
+        <v>0.4929701387882233</v>
       </c>
       <c r="C15" s="1">
         <v>392</v>
       </c>
       <c r="D15" s="1">
-        <v>5862</v>
+        <v>5884</v>
       </c>
       <c r="E15" s="1">
-        <v>5362</v>
+        <v>5384</v>
       </c>
       <c r="F15" s="1">
         <v>472</v>
@@ -3027,7 +3027,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.4595801830291748</v>
+        <v>0.4476973712444305</v>
       </c>
       <c r="C16" s="1">
         <v>356</v>
@@ -3053,7 +3053,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.4389248788356781</v>
+        <v>0.4275761544704437</v>
       </c>
       <c r="C17" s="1">
         <v>340</v>
@@ -3079,7 +3079,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3872866630554199</v>
+        <v>0.3772730827331543</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -3105,7 +3105,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3459760844707489</v>
+        <v>0.3370306193828583</v>
       </c>
       <c r="C19" s="1">
         <v>268</v>
@@ -3131,7 +3131,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.2943378686904907</v>
+        <v>0.2867275476455689</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -3157,7 +3157,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.2891740500926971</v>
+        <v>0.2816972136497498</v>
       </c>
       <c r="C21" s="1">
         <v>224</v>
@@ -3183,7 +3183,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.2633549273014069</v>
+        <v>0.2565456926822662</v>
       </c>
       <c r="C22" s="1">
         <v>204</v>
@@ -3209,7 +3209,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2581911087036133</v>
+        <v>0.2515153884887695</v>
       </c>
       <c r="C23" s="1">
         <v>200</v>
@@ -3235,7 +3235,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.1704061329364777</v>
+        <v>0.1660001575946808</v>
       </c>
       <c r="C24" s="1">
         <v>132</v>
@@ -3261,7 +3261,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.1652423143386841</v>
+        <v>0.1609698385000229</v>
       </c>
       <c r="C25" s="1">
         <v>128</v>
@@ -3287,7 +3287,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.1290955543518066</v>
+        <v>0.1257576942443848</v>
       </c>
       <c r="C26" s="1">
         <v>100</v>
@@ -3313,7 +3313,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1084402650594711</v>
+        <v>0.1056364625692368</v>
       </c>
       <c r="C27" s="1">
         <v>84</v>
@@ -3339,7 +3339,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.09811262041330338</v>
+        <v>0.09557584673166275</v>
       </c>
       <c r="C28" s="1">
         <v>76</v>
@@ -3365,7 +3365,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0929488018155098</v>
+        <v>0.09054553508758545</v>
       </c>
       <c r="C29" s="1">
         <v>72</v>
@@ -3391,7 +3391,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0929488018155098</v>
+        <v>0.09054553508758545</v>
       </c>
       <c r="C30" s="1">
         <v>72</v>
@@ -3417,7 +3417,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0929488018155098</v>
+        <v>0.09054553508758545</v>
       </c>
       <c r="C31" s="1">
         <v>72</v>
@@ -3443,7 +3443,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.08778497576713562</v>
+        <v>0.08551523089408875</v>
       </c>
       <c r="C32" s="1">
         <v>68</v>
@@ -3469,7 +3469,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.08262115716934204</v>
+        <v>0.08048491925001144</v>
       </c>
       <c r="C33" s="1">
         <v>64</v>
@@ -3495,7 +3495,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.05680204555392265</v>
+        <v>0.05533338338136673</v>
       </c>
       <c r="C34" s="1">
         <v>44</v>
@@ -3521,7 +3521,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.05163822323083878</v>
+        <v>0.05030307546257973</v>
       </c>
       <c r="C35" s="1">
         <v>40</v>
@@ -3547,7 +3547,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.0464744009077549</v>
+        <v>0.04527276754379273</v>
       </c>
       <c r="C36" s="1">
         <v>36</v>
@@ -3573,7 +3573,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.04131057858467102</v>
+        <v>0.04024245962500572</v>
       </c>
       <c r="C37" s="1">
         <v>32</v>
@@ -3599,7 +3599,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.04131057858467102</v>
+        <v>0.04024245962500572</v>
       </c>
       <c r="C38" s="1">
         <v>32</v>
@@ -3625,7 +3625,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03614675626158714</v>
+        <v>0.03521215170621872</v>
       </c>
       <c r="C39" s="1">
         <v>28</v>
@@ -3651,7 +3651,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.02581911161541939</v>
+        <v>0.02515153773128986</v>
       </c>
       <c r="C40" s="1">
         <v>20</v>
@@ -3677,7 +3677,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.02581911161541939</v>
+        <v>0.02515153773128986</v>
       </c>
       <c r="C41" s="1">
         <v>20</v>
@@ -3703,7 +3703,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.01549146696925163</v>
+        <v>0.01509092282503843</v>
       </c>
       <c r="C42" s="1">
         <v>12</v>
@@ -3729,7 +3729,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.01549146696925163</v>
+        <v>0.01509092282503843</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
@@ -3755,7 +3755,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.01549146696925163</v>
+        <v>0.01509092282503843</v>
       </c>
       <c r="C44" s="1">
         <v>12</v>
@@ -3781,7 +3781,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01549146696925163</v>
+        <v>0.01509092282503843</v>
       </c>
       <c r="C45" s="1">
         <v>12</v>
@@ -3807,7 +3807,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01032764464616776</v>
+        <v>0.01006061490625143</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
@@ -3833,7 +3833,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01032764464616776</v>
+        <v>0.01006061490625143</v>
       </c>
       <c r="C47" s="1">
         <v>8</v>
@@ -3859,7 +3859,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.01032764464616776</v>
+        <v>0.01006061490625143</v>
       </c>
       <c r="C48" s="1">
         <v>8</v>
@@ -3885,7 +3885,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.005163822323083878</v>
+        <v>0.005030307453125715</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
@@ -3911,7 +3911,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.005163822323083878</v>
+        <v>0.005030307453125715</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
@@ -3937,7 +3937,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.005163822323083878</v>
+        <v>0.005030307453125715</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
@@ -3963,16 +3963,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.005163822323083878</v>
+        <v>0.005030307453125715</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
       </c>
       <c r="D52" s="1">
-        <v>1772</v>
+        <v>1784</v>
       </c>
       <c r="E52" s="1">
-        <v>1432</v>
+        <v>1444</v>
       </c>
       <c r="F52" s="1">
         <v>336</v>
@@ -3989,7 +3989,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.005163822323083878</v>
+        <v>0.005030307453125715</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -4015,7 +4015,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.005163822323083878</v>
+        <v>0.005030307453125715</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
@@ -4041,7 +4041,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.005163822323083878</v>
+        <v>0.005030307453125715</v>
       </c>
       <c r="C55" s="1">
         <v>4</v>
@@ -4067,7 +4067,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.003872866742312908</v>
+        <v>0.003772730706259608</v>
       </c>
       <c r="C56" s="1">
         <v>3</v>
@@ -4174,16 +4174,16 @@
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>4.509890079498291</v>
+        <v>4.513896942138672</v>
       </c>
       <c r="C3" s="1">
-        <v>5862</v>
+        <v>5884</v>
       </c>
       <c r="D3" s="1">
         <v>392</v>
       </c>
       <c r="E3" s="1">
-        <v>5362</v>
+        <v>5384</v>
       </c>
       <c r="F3" s="1">
         <v>472</v>
@@ -4200,7 +4200,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="2">
-        <v>3.786707401275635</v>
+        <v>3.775900840759277</v>
       </c>
       <c r="C4" s="1">
         <v>4922</v>
@@ -4226,7 +4226,7 @@
         <v>56</v>
       </c>
       <c r="B5" s="2">
-        <v>3.646686792373657</v>
+        <v>3.636280059814453</v>
       </c>
       <c r="C5" s="1">
         <v>4740</v>
@@ -4252,7 +4252,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="2">
-        <v>3.377416610717773</v>
+        <v>3.367778301239014</v>
       </c>
       <c r="C6" s="1">
         <v>4390</v>
@@ -4278,7 +4278,7 @@
         <v>57</v>
       </c>
       <c r="B7" s="2">
-        <v>3.01120924949646</v>
+        <v>3.002615928649902</v>
       </c>
       <c r="C7" s="1">
         <v>3914</v>
@@ -4304,7 +4304,7 @@
         <v>58</v>
       </c>
       <c r="B8" s="2">
-        <v>2.831182956695557</v>
+        <v>2.823103427886963</v>
       </c>
       <c r="C8" s="1">
         <v>3680</v>
@@ -4330,7 +4330,7 @@
         <v>59</v>
       </c>
       <c r="B9" s="2">
-        <v>2.549603462219238</v>
+        <v>2.542327404022217</v>
       </c>
       <c r="C9" s="1">
         <v>3314</v>
@@ -4356,7 +4356,7 @@
         <v>60</v>
       </c>
       <c r="B10" s="2">
-        <v>2.454204797744751</v>
+        <v>2.447201013565064</v>
       </c>
       <c r="C10" s="1">
         <v>3190</v>
@@ -4382,7 +4382,7 @@
         <v>61</v>
       </c>
       <c r="B11" s="2">
-        <v>2.220324516296387</v>
+        <v>2.213988065719605</v>
       </c>
       <c r="C11" s="1">
         <v>2886</v>
@@ -4408,7 +4408,7 @@
         <v>44</v>
       </c>
       <c r="B12" s="2">
-        <v>2.211092472076416</v>
+        <v>2.204782485961914</v>
       </c>
       <c r="C12" s="1">
         <v>2874</v>
@@ -4434,16 +4434,16 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>1.878736138343811</v>
+        <v>2.066695928573608</v>
       </c>
       <c r="C13" s="1">
-        <v>2442</v>
+        <v>2694</v>
       </c>
       <c r="D13" s="1">
-        <v>26768</v>
+        <v>28816</v>
       </c>
       <c r="E13" s="1">
-        <v>2394</v>
+        <v>2646</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -4452,7 +4452,7 @@
         <v>48</v>
       </c>
       <c r="H13" s="1">
-        <v>26720</v>
+        <v>28768</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4460,7 +4460,7 @@
         <v>62</v>
       </c>
       <c r="B14" s="2">
-        <v>1.846423745155335</v>
+        <v>1.841154456138611</v>
       </c>
       <c r="C14" s="1">
         <v>2400</v>
@@ -4486,7 +4486,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="2">
-        <v>1.809495210647583</v>
+        <v>1.804331302642822</v>
       </c>
       <c r="C15" s="1">
         <v>2352</v>
@@ -4512,7 +4512,7 @@
         <v>64</v>
       </c>
       <c r="B16" s="2">
-        <v>1.80641782283783</v>
+        <v>1.801262736320496</v>
       </c>
       <c r="C16" s="1">
         <v>2348</v>
@@ -4538,7 +4538,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>1.803340435028076</v>
+        <v>1.798194169998169</v>
       </c>
       <c r="C17" s="1">
         <v>2344</v>
@@ -4564,7 +4564,7 @@
         <v>65</v>
       </c>
       <c r="B18" s="2">
-        <v>1.706403255462647</v>
+        <v>1.701533555984497</v>
       </c>
       <c r="C18" s="1">
         <v>2218</v>
@@ -4590,7 +4590,7 @@
         <v>66</v>
       </c>
       <c r="B19" s="2">
-        <v>1.652549266815186</v>
+        <v>1.647833228111267</v>
       </c>
       <c r="C19" s="1">
         <v>2148</v>
@@ -4616,7 +4616,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="2">
-        <v>1.646394491195679</v>
+        <v>1.641695976257324</v>
       </c>
       <c r="C20" s="1">
         <v>2140</v>
@@ -4642,7 +4642,7 @@
         <v>67</v>
       </c>
       <c r="B21" s="2">
-        <v>1.578692317008972</v>
+        <v>1.57418704032898</v>
       </c>
       <c r="C21" s="1">
         <v>2052</v>
@@ -4668,19 +4668,19 @@
         <v>68</v>
       </c>
       <c r="B22" s="2">
-        <v>1.504835367202759</v>
+        <v>1.526623845100403</v>
       </c>
       <c r="C22" s="1">
-        <v>1956</v>
+        <v>1990</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>1636</v>
+        <v>1990</v>
       </c>
       <c r="F22" s="1">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
         <v>0</v>
@@ -4694,19 +4694,19 @@
         <v>69</v>
       </c>
       <c r="B23" s="2">
-        <v>1.495603203773499</v>
+        <v>1.500540852546692</v>
       </c>
       <c r="C23" s="1">
-        <v>1944</v>
+        <v>1956</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>1930</v>
+        <v>1636</v>
       </c>
       <c r="F23" s="1">
-        <v>14</v>
+        <v>320</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -4720,19 +4720,19 @@
         <v>70</v>
       </c>
       <c r="B24" s="2">
-        <v>1.470984220504761</v>
+        <v>1.491335034370422</v>
       </c>
       <c r="C24" s="1">
-        <v>1912</v>
+        <v>1944</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1912</v>
+        <v>1930</v>
       </c>
       <c r="F24" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -4746,7 +4746,7 @@
         <v>71</v>
       </c>
       <c r="B25" s="2">
-        <v>1.461752057075501</v>
+        <v>1.45758056640625</v>
       </c>
       <c r="C25" s="1">
         <v>1900</v>
@@ -4772,7 +4772,7 @@
         <v>72</v>
       </c>
       <c r="B26" s="2">
-        <v>1.389433860778809</v>
+        <v>1.385468721389771</v>
       </c>
       <c r="C26" s="1">
         <v>1806</v>
@@ -4798,16 +4798,16 @@
         <v>50</v>
       </c>
       <c r="B27" s="2">
-        <v>1.363276124000549</v>
+        <v>1.36859142780304</v>
       </c>
       <c r="C27" s="1">
-        <v>1772</v>
+        <v>1784</v>
       </c>
       <c r="D27" s="1">
         <v>4</v>
       </c>
       <c r="E27" s="1">
-        <v>1432</v>
+        <v>1444</v>
       </c>
       <c r="F27" s="1">
         <v>336</v>
@@ -4824,7 +4824,7 @@
         <v>73</v>
       </c>
       <c r="B28" s="2">
-        <v>1.237103939056397</v>
+        <v>1.233573436737061</v>
       </c>
       <c r="C28" s="1">
         <v>1608</v>
@@ -4850,7 +4850,7 @@
         <v>17</v>
       </c>
       <c r="B29" s="2">
-        <v>1.234026551246643</v>
+        <v>1.230504870414734</v>
       </c>
       <c r="C29" s="1">
         <v>1604</v>
@@ -4876,7 +4876,7 @@
         <v>74</v>
       </c>
       <c r="B30" s="2">
-        <v>1.123241066932678</v>
+        <v>1.120035648345947</v>
       </c>
       <c r="C30" s="1">
         <v>1460</v>
@@ -4902,7 +4902,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="2">
-        <v>1.106315493583679</v>
+        <v>1.103158354759216</v>
       </c>
       <c r="C31" s="1">
         <v>1438</v>
@@ -4928,7 +4928,7 @@
         <v>75</v>
       </c>
       <c r="B32" s="2">
-        <v>1.072464466094971</v>
+        <v>1.069403886795044</v>
       </c>
       <c r="C32" s="1">
         <v>1394</v>
@@ -4954,7 +4954,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="2">
-        <v>1.072464466094971</v>
+        <v>1.069403886795044</v>
       </c>
       <c r="C33" s="1">
         <v>1394</v>
@@ -4980,7 +4980,7 @@
         <v>76</v>
       </c>
       <c r="B34" s="2">
-        <v>0.9601403474807739</v>
+        <v>0.9574002623558044</v>
       </c>
       <c r="C34" s="1">
         <v>1248</v>
@@ -5006,7 +5006,7 @@
         <v>77</v>
       </c>
       <c r="B35" s="2">
-        <v>0.9385986924171448</v>
+        <v>0.9359201788902283</v>
       </c>
       <c r="C35" s="1">
         <v>1220</v>
@@ -5032,7 +5032,7 @@
         <v>78</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9339826703071594</v>
+        <v>0.9313172698020935</v>
       </c>
       <c r="C36" s="1">
         <v>1214</v>
@@ -5058,7 +5058,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9109023809432983</v>
+        <v>0.9083028435707092</v>
       </c>
       <c r="C37" s="1">
         <v>1184</v>
@@ -5084,7 +5084,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8847447037696838</v>
+        <v>0.8822197914123535</v>
       </c>
       <c r="C38" s="1">
         <v>1150</v>
@@ -5110,7 +5110,7 @@
         <v>34</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8324293494224548</v>
+        <v>0.8300538063049316</v>
       </c>
       <c r="C39" s="1">
         <v>1082</v>
@@ -5136,7 +5136,7 @@
         <v>28</v>
       </c>
       <c r="B40" s="2">
-        <v>0.790884792804718</v>
+        <v>0.7886278033256531</v>
       </c>
       <c r="C40" s="1">
         <v>1028</v>
@@ -5162,7 +5162,7 @@
         <v>79</v>
       </c>
       <c r="B41" s="2">
-        <v>0.7785753011703491</v>
+        <v>0.7763534188270569</v>
       </c>
       <c r="C41" s="1">
         <v>1012</v>
@@ -5185,42 +5185,42 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7778059840202332</v>
+        <v>0.7763534188270569</v>
       </c>
       <c r="C42" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D42" s="1">
-        <v>3</v>
+        <v>10044</v>
       </c>
       <c r="E42" s="1">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>10044</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.7755863070487976</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1011</v>
+      </c>
+      <c r="D43" s="1">
         <v>3</v>
-      </c>
-      <c r="B43" s="2">
-        <v>0.7754979729652405</v>
-      </c>
-      <c r="C43" s="1">
-        <v>1008</v>
-      </c>
-      <c r="D43" s="1">
-        <v>10036</v>
       </c>
       <c r="E43" s="1">
         <v>1008</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H43" s="1">
-        <v>10036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5240,7 +5240,7 @@
         <v>80</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7693431973457336</v>
+        <v>0.7671476602554321</v>
       </c>
       <c r="C44" s="1">
         <v>1000</v>
@@ -5266,7 +5266,7 @@
         <v>29</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7462629079818726</v>
+        <v>0.7441332340240479</v>
       </c>
       <c r="C45" s="1">
         <v>970</v>
@@ -5292,7 +5292,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7385694980621338</v>
+        <v>0.7364617586135864</v>
       </c>
       <c r="C46" s="1">
         <v>960</v>
@@ -5318,7 +5318,7 @@
         <v>81</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7354921102523804</v>
+        <v>0.7333931922912598</v>
       </c>
       <c r="C47" s="1">
         <v>956</v>
@@ -5344,7 +5344,7 @@
         <v>7</v>
       </c>
       <c r="B48" s="2">
-        <v>0.7185665369033814</v>
+        <v>0.7165158987045288</v>
       </c>
       <c r="C48" s="1">
         <v>934</v>
@@ -5370,7 +5370,7 @@
         <v>82</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6647125482559204</v>
+        <v>0.6628155708312988</v>
       </c>
       <c r="C49" s="1">
         <v>864</v>
@@ -5396,7 +5396,7 @@
         <v>83</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6554804444313049</v>
+        <v>0.6536098122596741</v>
       </c>
       <c r="C50" s="1">
         <v>852</v>
@@ -5422,7 +5422,7 @@
         <v>84</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6539417505264282</v>
+        <v>0.6520755290985107</v>
       </c>
       <c r="C51" s="1">
         <v>850</v>
@@ -5448,7 +5448,7 @@
         <v>9</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6308614611625671</v>
+        <v>0.6290611028671265</v>
       </c>
       <c r="C52" s="1">
         <v>820</v>
@@ -5474,7 +5474,7 @@
         <v>41</v>
       </c>
       <c r="B53" s="2">
-        <v>0.6139358878135681</v>
+        <v>0.6121838688850403</v>
       </c>
       <c r="C53" s="1">
         <v>798</v>
@@ -5500,7 +5500,7 @@
         <v>85</v>
       </c>
       <c r="B54" s="2">
-        <v>0.6031650900840759</v>
+        <v>0.6014437675476074</v>
       </c>
       <c r="C54" s="1">
         <v>784</v>
@@ -5526,7 +5526,7 @@
         <v>18</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5816234946250916</v>
+        <v>0.5799636244773865</v>
       </c>
       <c r="C55" s="1">
         <v>756</v>
@@ -5552,7 +5552,7 @@
         <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5570045113563538</v>
+        <v>0.5554149150848389</v>
       </c>
       <c r="C56" s="1">
         <v>724</v>
@@ -5578,7 +5578,7 @@
         <v>87</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5539271235466003</v>
+        <v>0.5523463487625122</v>
       </c>
       <c r="C57" s="1">
         <v>720</v>
@@ -5604,7 +5604,7 @@
         <v>88</v>
       </c>
       <c r="B58" s="2">
-        <v>0.5262307524681091</v>
+        <v>0.5247290134429932</v>
       </c>
       <c r="C58" s="1">
         <v>684</v>
@@ -5630,7 +5630,7 @@
         <v>36</v>
       </c>
       <c r="B59" s="2">
-        <v>0.5062278509140015</v>
+        <v>0.5047831535339356</v>
       </c>
       <c r="C59" s="1">
         <v>658</v>
@@ -5656,7 +5656,7 @@
         <v>89</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4954570233821869</v>
+        <v>0.4940431118011475</v>
       </c>
       <c r="C60" s="1">
         <v>644</v>
@@ -5682,7 +5682,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4769927859306335</v>
+        <v>0.4756315648555756</v>
       </c>
       <c r="C61" s="1">
         <v>620</v>
@@ -5708,7 +5708,7 @@
         <v>90</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4754540920257568</v>
+        <v>0.4740972518920898</v>
       </c>
       <c r="C62" s="1">
         <v>618</v>
@@ -5734,7 +5734,7 @@
         <v>91</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4400643110275269</v>
+        <v>0.4388084709644318</v>
       </c>
       <c r="C63" s="1">
         <v>572</v>
@@ -5760,7 +5760,7 @@
         <v>92</v>
       </c>
       <c r="B64" s="2">
-        <v>0.427754819393158</v>
+        <v>0.426534116268158</v>
       </c>
       <c r="C64" s="1">
         <v>556</v>
@@ -5786,7 +5786,7 @@
         <v>20</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4216000735759735</v>
+        <v>0.4203969240188599</v>
       </c>
       <c r="C65" s="1">
         <v>548</v>
@@ -5812,7 +5812,7 @@
         <v>93</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4185227155685425</v>
+        <v>0.4173283278942108</v>
       </c>
       <c r="C66" s="1">
         <v>544</v>
@@ -5838,7 +5838,7 @@
         <v>2</v>
       </c>
       <c r="B67" s="2">
-        <v>0.3939037322998047</v>
+        <v>0.3927796185016632</v>
       </c>
       <c r="C67" s="1">
         <v>512</v>
@@ -5864,7 +5864,7 @@
         <v>11</v>
       </c>
       <c r="B68" s="2">
-        <v>0.3908263444900513</v>
+        <v>0.3897110223770142</v>
       </c>
       <c r="C68" s="1">
         <v>508</v>
@@ -5890,7 +5890,7 @@
         <v>94</v>
       </c>
       <c r="B69" s="2">
-        <v>0.3877489864826202</v>
+        <v>0.3866424262523651</v>
       </c>
       <c r="C69" s="1">
         <v>504</v>
@@ -5916,7 +5916,7 @@
         <v>5</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3862102925777435</v>
+        <v>0.3851081430912018</v>
       </c>
       <c r="C70" s="1">
         <v>502</v>
@@ -5942,7 +5942,7 @@
         <v>52</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3862102925777435</v>
+        <v>0.3851081430912018</v>
       </c>
       <c r="C71" s="1">
         <v>502</v>
@@ -5968,7 +5968,7 @@
         <v>10</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3831329047679901</v>
+        <v>0.3820395469665527</v>
       </c>
       <c r="C72" s="1">
         <v>498</v>
@@ -5994,7 +5994,7 @@
         <v>95</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3708234429359436</v>
+        <v>0.3697651624679565</v>
       </c>
       <c r="C73" s="1">
         <v>482</v>
@@ -6020,7 +6020,7 @@
         <v>96</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3662073612213135</v>
+        <v>0.3651622831821442</v>
       </c>
       <c r="C74" s="1">
         <v>476</v>
@@ -6046,7 +6046,7 @@
         <v>97</v>
       </c>
       <c r="B75" s="2">
-        <v>0.360052615404129</v>
+        <v>0.3590251207351685</v>
       </c>
       <c r="C75" s="1">
         <v>468</v>
@@ -6072,7 +6072,7 @@
         <v>35</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3508205115795136</v>
+        <v>0.3498193323612213</v>
       </c>
       <c r="C76" s="1">
         <v>456</v>
@@ -6098,7 +6098,7 @@
         <v>98</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3492818176746368</v>
+        <v>0.348285049200058</v>
       </c>
       <c r="C77" s="1">
         <v>454</v>
@@ -6124,7 +6124,7 @@
         <v>99</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3446657657623291</v>
+        <v>0.3436821699142456</v>
       </c>
       <c r="C78" s="1">
         <v>448</v>
@@ -6150,7 +6150,7 @@
         <v>100</v>
       </c>
       <c r="B79" s="2">
-        <v>0.3323562741279602</v>
+        <v>0.3314077854156494</v>
       </c>
       <c r="C79" s="1">
         <v>432</v>
@@ -6176,7 +6176,7 @@
         <v>45</v>
       </c>
       <c r="B80" s="2">
-        <v>0.3277402222156525</v>
+        <v>0.326804906129837</v>
       </c>
       <c r="C80" s="1">
         <v>426</v>
@@ -6202,7 +6202,7 @@
         <v>101</v>
       </c>
       <c r="B81" s="2">
-        <v>0.3154307305812836</v>
+        <v>0.3145305514335632</v>
       </c>
       <c r="C81" s="1">
         <v>410</v>
@@ -6228,7 +6228,7 @@
         <v>102</v>
       </c>
       <c r="B82" s="2">
-        <v>0.3154307305812836</v>
+        <v>0.3145305514335632</v>
       </c>
       <c r="C82" s="1">
         <v>410</v>
@@ -6254,7 +6254,7 @@
         <v>32</v>
       </c>
       <c r="B83" s="2">
-        <v>0.3138920366764069</v>
+        <v>0.3129962384700775</v>
       </c>
       <c r="C83" s="1">
         <v>408</v>
@@ -6280,7 +6280,7 @@
         <v>103</v>
       </c>
       <c r="B84" s="2">
-        <v>0.3077372908592224</v>
+        <v>0.3068590760231018</v>
       </c>
       <c r="C84" s="1">
         <v>400</v>
@@ -6306,7 +6306,7 @@
         <v>27</v>
       </c>
       <c r="B85" s="2">
-        <v>0.3077372908592224</v>
+        <v>0.3068590760231018</v>
       </c>
       <c r="C85" s="1">
         <v>400</v>
@@ -6332,7 +6332,7 @@
         <v>104</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2861956655979157</v>
+        <v>0.2853789329528809</v>
       </c>
       <c r="C86" s="1">
         <v>372</v>
@@ -6358,7 +6358,7 @@
         <v>105</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2815796136856079</v>
+        <v>0.2807760536670685</v>
       </c>
       <c r="C87" s="1">
         <v>366</v>
@@ -6384,7 +6384,7 @@
         <v>15</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2646540701389313</v>
+        <v>0.2638987898826599</v>
       </c>
       <c r="C88" s="1">
         <v>344</v>
@@ -6410,7 +6410,7 @@
         <v>106</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2584993243217468</v>
+        <v>0.2577616274356842</v>
       </c>
       <c r="C89" s="1">
         <v>336</v>
@@ -6436,7 +6436,7 @@
         <v>107</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2569606304168701</v>
+        <v>0.2562273144721985</v>
       </c>
       <c r="C90" s="1">
         <v>334</v>
@@ -6462,7 +6462,7 @@
         <v>21</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2554219365119934</v>
+        <v>0.2546930313110352</v>
       </c>
       <c r="C91" s="1">
         <v>332</v>
@@ -6488,7 +6488,7 @@
         <v>108</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2492672055959702</v>
+        <v>0.2485558390617371</v>
       </c>
       <c r="C92" s="1">
         <v>324</v>
@@ -6514,7 +6514,7 @@
         <v>109</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2369577139616013</v>
+        <v>0.2362814843654633</v>
       </c>
       <c r="C93" s="1">
         <v>308</v>
@@ -6540,7 +6540,7 @@
         <v>30</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2246482223272324</v>
+        <v>0.2240071147680283</v>
       </c>
       <c r="C94" s="1">
         <v>292</v>
@@ -6566,7 +6566,7 @@
         <v>51</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2092613577842712</v>
+        <v>0.2086641639471054</v>
       </c>
       <c r="C95" s="1">
         <v>272</v>
@@ -6592,7 +6592,7 @@
         <v>110</v>
       </c>
       <c r="B96" s="2">
-        <v>0.2092613577842712</v>
+        <v>0.2086641639471054</v>
       </c>
       <c r="C96" s="1">
         <v>272</v>
@@ -6618,7 +6618,7 @@
         <v>25</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1938744932413101</v>
+        <v>0.1933212131261826</v>
       </c>
       <c r="C97" s="1">
         <v>252</v>
@@ -6644,7 +6644,7 @@
         <v>111</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1892584264278412</v>
+        <v>0.1887183338403702</v>
       </c>
       <c r="C98" s="1">
         <v>246</v>
@@ -6670,7 +6670,7 @@
         <v>19</v>
       </c>
       <c r="B99" s="2">
-        <v>0.186181053519249</v>
+        <v>0.1856497377157211</v>
       </c>
       <c r="C99" s="1">
         <v>242</v>
@@ -6696,7 +6696,7 @@
         <v>112</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1846423745155335</v>
+        <v>0.1841154396533966</v>
       </c>
       <c r="C100" s="1">
         <v>240</v>
@@ -6722,7 +6722,7 @@
         <v>113</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1800263077020645</v>
+        <v>0.1795125603675842</v>
       </c>
       <c r="C101" s="1">
         <v>234</v>
@@ -6748,7 +6748,7 @@
         <v>114</v>
       </c>
       <c r="B102" s="2">
-        <v>0.178487628698349</v>
+        <v>0.1779782623052597</v>
       </c>
       <c r="C102" s="1">
         <v>232</v>
@@ -6774,7 +6774,7 @@
         <v>115</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1754102557897568</v>
+        <v>0.1749096661806107</v>
       </c>
       <c r="C103" s="1">
         <v>228</v>
@@ -6800,7 +6800,7 @@
         <v>24</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1754102557897568</v>
+        <v>0.1749096661806107</v>
       </c>
       <c r="C104" s="1">
         <v>228</v>
@@ -6826,7 +6826,7 @@
         <v>116</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1707941889762878</v>
+        <v>0.1703067868947983</v>
       </c>
       <c r="C105" s="1">
         <v>222</v>
@@ -6852,7 +6852,7 @@
         <v>117</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1692555099725723</v>
+        <v>0.1687724888324738</v>
       </c>
       <c r="C106" s="1">
         <v>220</v>
@@ -6878,7 +6878,7 @@
         <v>118</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1692555099725723</v>
+        <v>0.1687724888324738</v>
       </c>
       <c r="C107" s="1">
         <v>220</v>
@@ -6904,7 +6904,7 @@
         <v>38</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1477138996124268</v>
+        <v>0.1472923457622528</v>
       </c>
       <c r="C108" s="1">
         <v>192</v>
@@ -6930,7 +6930,7 @@
         <v>119</v>
       </c>
       <c r="B109" s="2">
-        <v>0.1446365267038345</v>
+        <v>0.144223764538765</v>
       </c>
       <c r="C109" s="1">
         <v>188</v>
@@ -6956,7 +6956,7 @@
         <v>120</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1430978327989578</v>
+        <v>0.1426894664764404</v>
       </c>
       <c r="C110" s="1">
         <v>186</v>
@@ -6982,7 +6982,7 @@
         <v>121</v>
       </c>
       <c r="B111" s="2">
-        <v>0.1354044079780579</v>
+        <v>0.135017991065979</v>
       </c>
       <c r="C111" s="1">
         <v>176</v>
@@ -7008,7 +7008,7 @@
         <v>122</v>
       </c>
       <c r="B112" s="2">
-        <v>0.1354044079780579</v>
+        <v>0.135017991065979</v>
       </c>
       <c r="C112" s="1">
         <v>176</v>
@@ -7034,7 +7034,7 @@
         <v>43</v>
       </c>
       <c r="B113" s="2">
-        <v>0.1323270350694656</v>
+        <v>0.13194939494133</v>
       </c>
       <c r="C113" s="1">
         <v>172</v>
@@ -7060,7 +7060,7 @@
         <v>123</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1215562298893929</v>
+        <v>0.1212093308568001</v>
       </c>
       <c r="C114" s="1">
         <v>158</v>
@@ -7086,7 +7086,7 @@
         <v>124</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1184788569808006</v>
+        <v>0.1181407421827316</v>
       </c>
       <c r="C115" s="1">
         <v>154</v>
@@ -7112,7 +7112,7 @@
         <v>125</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1169401705265045</v>
+        <v>0.1166064441204071</v>
       </c>
       <c r="C116" s="1">
         <v>152</v>
@@ -7138,7 +7138,7 @@
         <v>126</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1107854247093201</v>
+        <v>0.1104692667722702</v>
       </c>
       <c r="C117" s="1">
         <v>144</v>
@@ -7164,7 +7164,7 @@
         <v>40</v>
       </c>
       <c r="B118" s="2">
-        <v>0.109246738255024</v>
+        <v>0.1089349687099457</v>
       </c>
       <c r="C118" s="1">
         <v>142</v>
@@ -7190,7 +7190,7 @@
         <v>127</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1061693653464317</v>
+        <v>0.1058663800358772</v>
       </c>
       <c r="C119" s="1">
         <v>138</v>
@@ -7216,7 +7216,7 @@
         <v>26</v>
       </c>
       <c r="B120" s="2">
-        <v>0.1046306788921356</v>
+        <v>0.1043320819735527</v>
       </c>
       <c r="C120" s="1">
         <v>136</v>
@@ -7242,7 +7242,7 @@
         <v>128</v>
       </c>
       <c r="B121" s="2">
-        <v>0.09847593307495117</v>
+        <v>0.0981949046254158</v>
       </c>
       <c r="C121" s="1">
         <v>128</v>
@@ -7268,7 +7268,7 @@
         <v>129</v>
       </c>
       <c r="B122" s="2">
-        <v>0.09847593307495117</v>
+        <v>0.0981949046254158</v>
       </c>
       <c r="C122" s="1">
         <v>128</v>
@@ -7294,7 +7294,7 @@
         <v>130</v>
       </c>
       <c r="B123" s="2">
-        <v>0.09693724662065506</v>
+        <v>0.09666060656309128</v>
       </c>
       <c r="C123" s="1">
         <v>126</v>
@@ -7320,7 +7320,7 @@
         <v>131</v>
       </c>
       <c r="B124" s="2">
-        <v>0.09693724662065506</v>
+        <v>0.09666060656309128</v>
       </c>
       <c r="C124" s="1">
         <v>126</v>
@@ -7346,7 +7346,7 @@
         <v>42</v>
       </c>
       <c r="B125" s="2">
-        <v>0.09693724662065506</v>
+        <v>0.09666060656309128</v>
       </c>
       <c r="C125" s="1">
         <v>126</v>
@@ -7372,7 +7372,7 @@
         <v>23</v>
       </c>
       <c r="B126" s="2">
-        <v>0.09232118725776672</v>
+        <v>0.0920577198266983</v>
       </c>
       <c r="C126" s="1">
         <v>120</v>
@@ -7398,7 +7398,7 @@
         <v>132</v>
       </c>
       <c r="B127" s="2">
-        <v>0.08770512789487839</v>
+        <v>0.08745483309030533</v>
       </c>
       <c r="C127" s="1">
         <v>114</v>
@@ -7424,7 +7424,7 @@
         <v>133</v>
       </c>
       <c r="B128" s="2">
-        <v>0.08616644144058228</v>
+        <v>0.0859205424785614</v>
       </c>
       <c r="C128" s="1">
         <v>112</v>
@@ -7447,16 +7447,16 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
-        <v>134</v>
+        <v>12</v>
       </c>
       <c r="B129" s="2">
-        <v>0.08616644144058228</v>
+        <v>0.0859205424785614</v>
       </c>
       <c r="C129" s="1">
         <v>112</v>
       </c>
       <c r="D129" s="1">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="E129" s="1">
         <v>112</v>
@@ -7468,15 +7468,15 @@
         <v>0</v>
       </c>
       <c r="H129" s="1">
-        <v>0</v>
+        <v>720</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B130" s="2">
-        <v>0.08616644144058228</v>
+        <v>0.0859205424785614</v>
       </c>
       <c r="C130" s="1">
         <v>112</v>
@@ -7499,19 +7499,19 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B131" s="2">
-        <v>0.08462775498628616</v>
+        <v>0.0859205424785614</v>
       </c>
       <c r="C131" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -7525,19 +7525,19 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B132" s="2">
-        <v>0.08308906853199005</v>
+        <v>0.08438624441623688</v>
       </c>
       <c r="C132" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D132" s="1">
         <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -7551,16 +7551,16 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="1" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="B133" s="2">
-        <v>0.08308906853199005</v>
+        <v>0.08285194635391235</v>
       </c>
       <c r="C133" s="1">
         <v>108</v>
       </c>
       <c r="D133" s="1">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="E133" s="1">
         <v>108</v>
@@ -7572,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="1">
-        <v>720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -7580,7 +7580,7 @@
         <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07539563626050949</v>
+        <v>0.07518047094345093</v>
       </c>
       <c r="C134" s="1">
         <v>98</v>
@@ -7606,7 +7606,7 @@
         <v>139</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07539563626050949</v>
+        <v>0.07518047094345093</v>
       </c>
       <c r="C135" s="1">
         <v>98</v>
@@ -7632,7 +7632,7 @@
         <v>140</v>
       </c>
       <c r="B136" s="2">
-        <v>0.07077957689762116</v>
+        <v>0.07057758420705795</v>
       </c>
       <c r="C136" s="1">
         <v>92</v>
@@ -7658,7 +7658,7 @@
         <v>141</v>
       </c>
       <c r="B137" s="2">
-        <v>0.06616351753473282</v>
+        <v>0.06597469747066498</v>
       </c>
       <c r="C137" s="1">
         <v>86</v>
@@ -7684,7 +7684,7 @@
         <v>142</v>
       </c>
       <c r="B138" s="2">
-        <v>0.06462483108043671</v>
+        <v>0.06444040685892105</v>
       </c>
       <c r="C138" s="1">
         <v>84</v>
@@ -7710,7 +7710,7 @@
         <v>143</v>
       </c>
       <c r="B139" s="2">
-        <v>0.06462483108043671</v>
+        <v>0.06444040685892105</v>
       </c>
       <c r="C139" s="1">
         <v>84</v>
@@ -7736,7 +7736,7 @@
         <v>144</v>
       </c>
       <c r="B140" s="2">
-        <v>0.06462483108043671</v>
+        <v>0.06444040685892105</v>
       </c>
       <c r="C140" s="1">
         <v>84</v>
@@ -7762,7 +7762,7 @@
         <v>53</v>
       </c>
       <c r="B141" s="2">
-        <v>0.06462483108043671</v>
+        <v>0.06444040685892105</v>
       </c>
       <c r="C141" s="1">
         <v>84</v>
@@ -7788,7 +7788,7 @@
         <v>145</v>
       </c>
       <c r="B142" s="2">
-        <v>0.06308614462614059</v>
+        <v>0.06290610879659653</v>
       </c>
       <c r="C142" s="1">
         <v>82</v>
@@ -7814,7 +7814,7 @@
         <v>146</v>
       </c>
       <c r="B143" s="2">
-        <v>0.06154745817184448</v>
+        <v>0.0613718144595623</v>
       </c>
       <c r="C143" s="1">
         <v>80</v>
@@ -7840,7 +7840,7 @@
         <v>147</v>
       </c>
       <c r="B144" s="2">
-        <v>0.06000877171754837</v>
+        <v>0.05983751639723778</v>
       </c>
       <c r="C144" s="1">
         <v>78</v>
@@ -7866,7 +7866,7 @@
         <v>33</v>
       </c>
       <c r="B145" s="2">
-        <v>0.05847008526325226</v>
+        <v>0.05830322206020355</v>
       </c>
       <c r="C145" s="1">
         <v>76</v>
@@ -7892,7 +7892,7 @@
         <v>148</v>
       </c>
       <c r="B146" s="2">
-        <v>0.0507766529917717</v>
+        <v>0.05063174664974213</v>
       </c>
       <c r="C146" s="1">
         <v>66</v>
@@ -7918,7 +7918,7 @@
         <v>149</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04616059362888336</v>
+        <v>0.04602885991334915</v>
       </c>
       <c r="C147" s="1">
         <v>60</v>
@@ -7944,7 +7944,7 @@
         <v>150</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04616059362888336</v>
+        <v>0.04602885991334915</v>
       </c>
       <c r="C148" s="1">
         <v>60</v>
@@ -7970,7 +7970,7 @@
         <v>151</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04616059362888336</v>
+        <v>0.04602885991334915</v>
       </c>
       <c r="C149" s="1">
         <v>60</v>
@@ -7996,7 +7996,7 @@
         <v>152</v>
       </c>
       <c r="B150" s="2">
-        <v>0.04462190717458725</v>
+        <v>0.04449456557631493</v>
       </c>
       <c r="C150" s="1">
         <v>58</v>
@@ -8022,7 +8022,7 @@
         <v>153</v>
       </c>
       <c r="B151" s="2">
-        <v>0.04154453426599503</v>
+        <v>0.04142597317695618</v>
       </c>
       <c r="C151" s="1">
         <v>54</v>
@@ -8048,7 +8048,7 @@
         <v>46</v>
       </c>
       <c r="B152" s="2">
-        <v>0.04154453426599503</v>
+        <v>0.04142597317695618</v>
       </c>
       <c r="C152" s="1">
         <v>54</v>
@@ -8074,7 +8074,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="2">
-        <v>0.04000584781169891</v>
+        <v>0.03989167883992195</v>
       </c>
       <c r="C153" s="1">
         <v>52</v>
@@ -8100,7 +8100,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="2">
-        <v>0.0384671613574028</v>
+        <v>0.03835738450288773</v>
       </c>
       <c r="C154" s="1">
         <v>50</v>
@@ -8126,7 +8126,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="2">
-        <v>0.03692847490310669</v>
+        <v>0.0368230864405632</v>
       </c>
       <c r="C155" s="1">
         <v>48</v>
@@ -8152,7 +8152,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="2">
-        <v>0.03692847490310669</v>
+        <v>0.0368230864405632</v>
       </c>
       <c r="C156" s="1">
         <v>48</v>
@@ -8178,7 +8178,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="2">
-        <v>0.03692847490310669</v>
+        <v>0.0368230864405632</v>
       </c>
       <c r="C157" s="1">
         <v>48</v>
@@ -8204,7 +8204,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="2">
-        <v>0.03385110199451447</v>
+        <v>0.03375449776649475</v>
       </c>
       <c r="C158" s="1">
         <v>44</v>
@@ -8230,7 +8230,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="2">
-        <v>0.03385110199451447</v>
+        <v>0.03375449776649475</v>
       </c>
       <c r="C159" s="1">
         <v>44</v>
@@ -8256,7 +8256,7 @@
         <v>49</v>
       </c>
       <c r="B160" s="2">
-        <v>0.03385110199451447</v>
+        <v>0.03375449776649475</v>
       </c>
       <c r="C160" s="1">
         <v>44</v>
@@ -8282,7 +8282,7 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.03385110199451447</v>
+        <v>0.03375449776649475</v>
       </c>
       <c r="C161" s="1">
         <v>44</v>
@@ -8308,7 +8308,7 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.03385110199451447</v>
+        <v>0.03375449776649475</v>
       </c>
       <c r="C162" s="1">
         <v>44</v>
@@ -8334,7 +8334,7 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.03077372908592224</v>
+        <v>0.03068590722978115</v>
       </c>
       <c r="C163" s="1">
         <v>40</v>
@@ -8360,7 +8360,7 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.02923504263162613</v>
+        <v>0.02915161103010178</v>
       </c>
       <c r="C164" s="1">
         <v>38</v>
@@ -8386,7 +8386,7 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.02923504263162613</v>
+        <v>0.02915161103010178</v>
       </c>
       <c r="C165" s="1">
         <v>38</v>
@@ -8412,7 +8412,7 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.02769635617733002</v>
+        <v>0.02761731669306755</v>
       </c>
       <c r="C166" s="1">
         <v>36</v>
@@ -8438,7 +8438,7 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.02769635617733002</v>
+        <v>0.02761731669306755</v>
       </c>
       <c r="C167" s="1">
         <v>36</v>
@@ -8464,7 +8464,7 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.02769635617733002</v>
+        <v>0.02761731669306755</v>
       </c>
       <c r="C168" s="1">
         <v>36</v>
@@ -8490,7 +8490,7 @@
         <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.02769635617733002</v>
+        <v>0.02761731669306755</v>
       </c>
       <c r="C169" s="1">
         <v>36</v>
@@ -8516,7 +8516,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="2">
-        <v>0.02461898326873779</v>
+        <v>0.02454872615635395</v>
       </c>
       <c r="C170" s="1">
         <v>32</v>
@@ -8542,7 +8542,7 @@
         <v>171</v>
       </c>
       <c r="B171" s="2">
-        <v>0.02461898326873779</v>
+        <v>0.02454872615635395</v>
       </c>
       <c r="C171" s="1">
         <v>32</v>
@@ -8568,7 +8568,7 @@
         <v>172</v>
       </c>
       <c r="B172" s="2">
-        <v>0.02461898326873779</v>
+        <v>0.02454872615635395</v>
       </c>
       <c r="C172" s="1">
         <v>32</v>
@@ -8594,7 +8594,7 @@
         <v>173</v>
       </c>
       <c r="B173" s="2">
-        <v>0.02461898326873779</v>
+        <v>0.02454872615635395</v>
       </c>
       <c r="C173" s="1">
         <v>32</v>
@@ -8620,7 +8620,7 @@
         <v>174</v>
       </c>
       <c r="B174" s="2">
-        <v>0.02461898326873779</v>
+        <v>0.02454872615635395</v>
       </c>
       <c r="C174" s="1">
         <v>32</v>
@@ -8646,7 +8646,7 @@
         <v>175</v>
       </c>
       <c r="B175" s="2">
-        <v>0.02308029681444168</v>
+        <v>0.02301442995667458</v>
       </c>
       <c r="C175" s="1">
         <v>30</v>
@@ -8672,7 +8672,7 @@
         <v>176</v>
       </c>
       <c r="B176" s="2">
-        <v>0.02308029681444168</v>
+        <v>0.02301442995667458</v>
       </c>
       <c r="C176" s="1">
         <v>30</v>
@@ -8698,7 +8698,7 @@
         <v>177</v>
       </c>
       <c r="B177" s="2">
-        <v>0.02000292390584946</v>
+        <v>0.01994583941996098</v>
       </c>
       <c r="C177" s="1">
         <v>26</v>
@@ -8724,7 +8724,7 @@
         <v>178</v>
       </c>
       <c r="B178" s="2">
-        <v>0.02000292390584946</v>
+        <v>0.01994583941996098</v>
       </c>
       <c r="C178" s="1">
         <v>26</v>
@@ -8750,7 +8750,7 @@
         <v>179</v>
       </c>
       <c r="B179" s="2">
-        <v>0.01846423745155335</v>
+        <v>0.0184115432202816</v>
       </c>
       <c r="C179" s="1">
         <v>24</v>
@@ -8776,7 +8776,7 @@
         <v>180</v>
       </c>
       <c r="B180" s="2">
-        <v>0.01846423745155335</v>
+        <v>0.0184115432202816</v>
       </c>
       <c r="C180" s="1">
         <v>24</v>
@@ -8802,7 +8802,7 @@
         <v>48</v>
       </c>
       <c r="B181" s="2">
-        <v>0.0123094916343689</v>
+        <v>0.01227436307817698</v>
       </c>
       <c r="C181" s="1">
         <v>16</v>
@@ -8828,7 +8828,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2">
-        <v>0.006154745817184448</v>
+        <v>0.006137181539088488</v>
       </c>
       <c r="C182" s="1">
         <v>8</v>
@@ -8854,7 +8854,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="2">
-        <v>0.006154745817184448</v>
+        <v>0.006137181539088488</v>
       </c>
       <c r="C183" s="1">
         <v>8</v>
@@ -8880,7 +8880,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="2">
-        <v>0.003077372908592224</v>
+        <v>0.003068590769544244</v>
       </c>
       <c r="C184" s="1">
         <v>4</v>
@@ -8906,7 +8906,7 @@
         <v>47</v>
       </c>
       <c r="B185" s="2">
-        <v>0.003077372908592224</v>
+        <v>0.003068590769544244</v>
       </c>
       <c r="C185" s="1">
         <v>4</v>
@@ -8932,7 +8932,7 @@
         <v>184</v>
       </c>
       <c r="B186" s="2">
-        <v>0.003077372908592224</v>
+        <v>0.003068590769544244</v>
       </c>
       <c r="C186" s="1">
         <v>4</v>
@@ -8958,7 +8958,7 @@
         <v>185</v>
       </c>
       <c r="B187" s="2">
-        <v>0.003077372908592224</v>
+        <v>0.003068590769544244</v>
       </c>
       <c r="C187" s="1">
         <v>4</v>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="192">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -83,6 +83,9 @@
     <t>spi.o</t>
   </si>
   <si>
+    <t>calib_level6_system.o</t>
+  </si>
+  <si>
     <t>calib_level2_motor.o</t>
   </si>
   <si>
@@ -122,15 +125,15 @@
     <t>calib_level3_encoder.o</t>
   </si>
   <si>
+    <t>calib_config_runtime.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_flash.o</t>
   </si>
   <si>
     <t>dev_eeprom.o</t>
   </si>
   <si>
-    <t>calib_config_runtime.o</t>
-  </si>
-  <si>
     <t>thread_management.o</t>
   </si>
   <si>
@@ -143,9 +146,6 @@
     <t>port.o</t>
   </si>
   <si>
-    <t>calib_level6_system.o</t>
-  </si>
-  <si>
     <t>calib_level1_driver.o</t>
   </si>
   <si>
@@ -182,15 +182,15 @@
     <t>motor_pid_load.o</t>
   </si>
   <si>
+    <t>motor_info.o</t>
+  </si>
+  <si>
+    <t>jm_proto.o</t>
+  </si>
+  <si>
     <t>m_wm.l</t>
   </si>
   <si>
-    <t>motor_info.o</t>
-  </si>
-  <si>
-    <t>jm_proto.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_adc.o</t>
   </si>
   <si>
@@ -239,21 +239,21 @@
     <t>queue.o</t>
   </si>
   <si>
+    <t>ctrl_transition.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_spi.o</t>
+  </si>
+  <si>
     <t>mf_w.l</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_spi.o</t>
-  </si>
-  <si>
     <t>motor_pid_autotune.o</t>
   </si>
   <si>
     <t>dev_motor_phase_current.o</t>
   </si>
   <si>
-    <t>ctrl_transition.o</t>
-  </si>
-  <si>
     <t>motor_mode_load_sim.o</t>
   </si>
   <si>
@@ -263,15 +263,15 @@
     <t>stm32g4xx_hal_dma.o</t>
   </si>
   <si>
+    <t>current_loop.o</t>
+  </si>
+  <si>
+    <t>dev_mt6835.o</t>
+  </si>
+  <si>
     <t>multiturn_counter.o</t>
   </si>
   <si>
-    <t>current_loop.o</t>
-  </si>
-  <si>
-    <t>dev_mt6835.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_rcc_ex.o</t>
   </si>
   <si>
@@ -281,9 +281,6 @@
     <t>stm32g4xx_hal_tim_ex.o</t>
   </si>
   <si>
-    <t>atan2f.o</t>
-  </si>
-  <si>
     <t>dev_half_bridge.o</t>
   </si>
   <si>
@@ -299,45 +296,45 @@
     <t>motor_control.o</t>
   </si>
   <si>
+    <t>motor_info_calib.o</t>
+  </si>
+  <si>
+    <t>ctrl_transition_mgr.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_flash_ex.o</t>
+  </si>
+  <si>
+    <t>stm32g4xx_hal_gpio.o</t>
+  </si>
+  <si>
     <t>calib_ac_injection.o</t>
   </si>
   <si>
-    <t>ctrl_transition_mgr.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_flash_ex.o</t>
-  </si>
-  <si>
-    <t>stm32g4xx_hal_gpio.o</t>
-  </si>
-  <si>
-    <t>motor_info_calib.o</t>
-  </si>
-  <si>
     <t>log10f.o</t>
   </si>
   <si>
     <t>dev_motor.o</t>
   </si>
   <si>
+    <t>dev_config.o</t>
+  </si>
+  <si>
     <t>drv_tim.o</t>
   </si>
   <si>
-    <t>dev_config.o</t>
-  </si>
-  <si>
     <t>sinf.o</t>
   </si>
   <si>
+    <t>drv_spi.o</t>
+  </si>
+  <si>
     <t>rredf.o</t>
   </si>
   <si>
     <t>pid_core.o</t>
   </si>
   <si>
-    <t>cosf.o</t>
-  </si>
-  <si>
     <t>dadd.o</t>
   </si>
   <si>
@@ -350,15 +347,15 @@
     <t>gpio.o</t>
   </si>
   <si>
+    <t>main.o</t>
+  </si>
+  <si>
     <t>drv_adc.o</t>
   </si>
   <si>
     <t>drv_i2c.o</t>
   </si>
   <si>
-    <t>main.o</t>
-  </si>
-  <si>
     <t>drv_gpio.o</t>
   </si>
   <si>
@@ -371,18 +368,12 @@
     <t>stm32g4xx_hal_pwr_ex.o</t>
   </si>
   <si>
-    <t>drv_spi.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_it.o</t>
   </si>
   <si>
     <t>depilogue.o</t>
   </si>
   <si>
-    <t>fmodf.o</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_i2c_ex.o</t>
   </si>
   <si>
@@ -452,15 +443,15 @@
     <t>assert_report.o</t>
   </si>
   <si>
-    <t>frem.o</t>
-  </si>
-  <si>
     <t>funder.o</t>
   </si>
   <si>
     <t>motor_mode_profile_velocity.o</t>
   </si>
   <si>
+    <t>control_irq.o</t>
+  </si>
+  <si>
     <t>motor_mode_duty.o</t>
   </si>
   <si>
@@ -468,9 +459,6 @@
   </si>
   <si>
     <t>stm32g4xx_hal_msp.o</t>
-  </si>
-  <si>
-    <t>control_irq.o</t>
   </si>
   <si>
     <t>sqrtf.o</t>
@@ -692,9 +680,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$188</c:f>
+              <c:f>ram_percent!$A$3:$A$184</c:f>
               <c:strCache>
-                <c:ptCount val="186"/>
+                <c:ptCount val="182"/>
                 <c:pt idx="0">
                   <c:v>motor_observer.o</c:v>
                 </c:pt>
@@ -759,67 +747,67 @@
                   <c:v>spi.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>calib_level6_system.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>drv_can.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="33">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>calib_level3_encoder.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
+                  <c:v>calib_config_runtime.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="37">
                   <c:v>dev_eeprom.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
-                  <c:v>calib_config_runtime.o</c:v>
-                </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>calib_level6_system.o</c:v>
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>calib_level1_driver.o</c:v>
@@ -857,7 +845,7 @@
                 <c:pt idx="53">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="185">
+                <c:pt idx="181">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -865,173 +853,173 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$188</c:f>
+              <c:f>ram_percent!$B$3:$B$184</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="186"/>
+                <c:ptCount val="182"/>
                 <c:pt idx="0">
-                  <c:v>36.23833465576172</c:v>
+                  <c:v>36.17101287841797</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.64438247680664</c:v>
+                  <c:v>20.60602951049805</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.63110256195068</c:v>
+                  <c:v>12.61767864227295</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.151034832000732</c:v>
+                  <c:v>5.141465663909912</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.151034832000732</c:v>
+                  <c:v>5.141465663909912</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.718428611755371</c:v>
+                  <c:v>4.709662914276123</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.635881185531616</c:v>
+                  <c:v>2.630984306335449</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.570487260818481</c:v>
+                  <c:v>2.565711736679077</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.072486639022827</c:v>
+                  <c:v>2.068636655807495</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.29656183719635</c:v>
+                  <c:v>1.294153094291687</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.287758708000183</c:v>
+                  <c:v>1.285366415977478</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9054553508758545</c:v>
+                  <c:v>0.9037732481956482</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.4929701387882233</c:v>
+                  <c:v>0.5020962357521057</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4476973712444305</c:v>
+                  <c:v>0.4468656778335571</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.4275761544704437</c:v>
+                  <c:v>0.4267818033695221</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3772730827331543</c:v>
+                  <c:v>0.3765721917152405</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3370306193828583</c:v>
+                  <c:v>0.3364045023918152</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2867275476455689</c:v>
+                  <c:v>0.2861948609352112</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.2816972136497498</c:v>
+                  <c:v>0.2811739146709442</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.2565456926822662</c:v>
+                  <c:v>0.2560690939426422</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2515153884887695</c:v>
+                  <c:v>0.2510481178760529</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.1660001575946808</c:v>
+                  <c:v>0.1707127243280411</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1609698385000229</c:v>
+                  <c:v>0.1656917631626129</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.1257576942443848</c:v>
+                  <c:v>0.1606708019971848</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1056364625692368</c:v>
+                  <c:v>0.1255240589380264</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.09557584673166275</c:v>
+                  <c:v>0.1054402142763138</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.09054553508758545</c:v>
+                  <c:v>0.09539828449487686</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.09054553508758545</c:v>
+                  <c:v>0.0903773233294487</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.09054553508758545</c:v>
+                  <c:v>0.0903773233294487</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.08551523089408875</c:v>
+                  <c:v>0.0903773233294487</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.08048491925001144</c:v>
+                  <c:v>0.08535636216402054</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.05533338338136673</c:v>
+                  <c:v>0.08033540099859238</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.05030307546257973</c:v>
+                  <c:v>0.05523058772087097</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.04527276754379273</c:v>
+                  <c:v>0.05020962655544281</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.04024245962500572</c:v>
+                  <c:v>0.04518866166472435</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.04024245962500572</c:v>
+                  <c:v>0.04518866166472435</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.03521215170621872</c:v>
+                  <c:v>0.04016770049929619</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.02515153773128986</c:v>
+                  <c:v>0.04016770049929619</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.02515153773128986</c:v>
+                  <c:v>0.02510481327772141</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.01509092282503843</c:v>
+                  <c:v>0.02510481327772141</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.01509092282503843</c:v>
+                  <c:v>0.01506288722157478</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.01509092282503843</c:v>
+                  <c:v>0.01506288722157478</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01509092282503843</c:v>
+                  <c:v>0.01506288722157478</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01006061490625143</c:v>
+                  <c:v>0.01004192512482405</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01006061490625143</c:v>
+                  <c:v>0.01004192512482405</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.01006061490625143</c:v>
+                  <c:v>0.01004192512482405</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.005030307453125715</c:v>
+                  <c:v>0.005020962562412024</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.005030307453125715</c:v>
+                  <c:v>0.005020962562412024</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.005030307453125715</c:v>
+                  <c:v>0.005020962562412024</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.005030307453125715</c:v>
+                  <c:v>0.005020962562412024</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.005030307453125715</c:v>
+                  <c:v>0.005020962562412024</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.005030307453125715</c:v>
+                  <c:v>0.005020962562412024</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.005030307453125715</c:v>
+                  <c:v>0.005020962562412024</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.003772730706259608</c:v>
-                </c:pt>
-                <c:pt idx="185">
+                  <c:v>0.003765721805393696</c:v>
+                </c:pt>
+                <c:pt idx="181">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1099,23 +1087,23 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$188</c:f>
+              <c:f>flash_percent!$A$3:$A$184</c:f>
               <c:strCache>
-                <c:ptCount val="186"/>
+                <c:ptCount val="182"/>
                 <c:pt idx="0">
                   <c:v>jm_proto_ops.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>motor_info.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>calib_level2_motor.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>jm_proto.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>m_wm.l</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>motor_info.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>calib_level2_motor.o</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>jm_proto.o</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>stm32g4xx_hal_adc.o</c:v>
@@ -1136,112 +1124,112 @@
                   <c:v>motor_observer.o</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>calib_level6_system.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>stm32g4xx_hal_fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>stm32g4xx_hal_adc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>arm_cortexM4lf_math.lib</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>tasks.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
+                  <c:v>dev_power_monitor.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>printfa.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="18">
                   <c:v>stm32g4xx_hal_i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="19">
                   <c:v>dev_commun_can.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="20">
                   <c:v>arm_common_tables.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="21">
                   <c:v>motor_mode_test_sweep.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="22">
                   <c:v>powf.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="23">
                   <c:v>jm_proto_can.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>stm32g4xx_hal_rcc.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>motion_param.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>system_state.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>queue.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
-                  <c:v>dev_power_monitor.o</c:v>
-                </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
+                  <c:v>calib_config_runtime.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>motor_pid_profile.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>ctrl_transition.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>stm32g4xx_hal_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="28">
-                  <c:v>motor_pid_profile.o</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>stm32g4xx_hal_spi.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>calib_config_runtime.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>motor_pid_autotune.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>dev_motor_phase_current.o</c:v>
                 </c:pt>
-                <c:pt idx="33">
-                  <c:v>ctrl_transition.o</c:v>
-                </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>jm_host_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>drv_can.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>calib_level3_encoder.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
+                  <c:v>motor_loop.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
                   <c:v>calib_mgr.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="40">
                   <c:v>motor_mode_load_sim.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
-                  <c:v>motor_loop.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>drv_flash_g4.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>motor_info_storage.o</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>multiturn_counter.o</c:v>
                 </c:pt>
                 <c:pt idx="47">
                   <c:v>current_loop.o</c:v>
@@ -1250,25 +1238,25 @@
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
                 <c:pt idx="49">
+                  <c:v>multiturn_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="50">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>motor_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>atan2f.o</c:v>
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>dev_eeprom.o</c:v>
@@ -1301,16 +1289,16 @@
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>calib_ac_injection.o</c:v>
+                  <c:v>dev_flash.o</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>dev_flash.o</c:v>
+                  <c:v>calib_hw.o</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>calib_hw.o</c:v>
+                  <c:v>packer_parser.o</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>packer_parser.o</c:v>
+                  <c:v>motor_info_calib.o</c:v>
                 </c:pt>
                 <c:pt idx="70">
                   <c:v>ctrl_transition_mgr.o</c:v>
@@ -1322,10 +1310,10 @@
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
                 <c:pt idx="73">
+                  <c:v>calib_ac_injection.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>motor_info_calib.o</c:v>
                 </c:pt>
                 <c:pt idx="75">
                   <c:v>log10f.o</c:v>
@@ -1337,10 +1325,10 @@
                   <c:v>led_manager.o</c:v>
                 </c:pt>
                 <c:pt idx="78">
+                  <c:v>dev_config.o</c:v>
+                </c:pt>
+                <c:pt idx="79">
                   <c:v>drv_tim.o</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>dev_config.o</c:v>
                 </c:pt>
                 <c:pt idx="80">
                   <c:v>calib_level7_auto.o</c:v>
@@ -1352,16 +1340,16 @@
                   <c:v>dev_led.o</c:v>
                 </c:pt>
                 <c:pt idx="83">
+                  <c:v>drv_spi.o</c:v>
+                </c:pt>
+                <c:pt idx="84">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>usart.o</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>cosf.o</c:v>
                 </c:pt>
                 <c:pt idx="87">
                   <c:v>dadd.o</c:v>
@@ -1385,19 +1373,19 @@
                   <c:v>gpio.o</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>i2c.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
+                <c:pt idx="96">
                   <c:v>drv_adc.o</c:v>
                 </c:pt>
-                <c:pt idx="96">
+                <c:pt idx="97">
                   <c:v>drv_rtos.o</c:v>
                 </c:pt>
-                <c:pt idx="97">
+                <c:pt idx="98">
                   <c:v>drv_i2c.o</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="99">
                   <c:v>drv_gpio.o</c:v>
@@ -1415,249 +1403,237 @@
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>drv_spi.o</c:v>
+                  <c:v>thread_management.o</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>thread_management.o</c:v>
+                  <c:v>stm32g4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>stm32g4xx_it.o</c:v>
+                  <c:v>depilogue.o</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>depilogue.o</c:v>
+                  <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>fmodf.o</c:v>
+                  <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
+                  <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>calib_level1_driver.o</c:v>
+                  <c:v>roundf.o</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>stm32g4xx_hal_cortex.o</c:v>
+                  <c:v>arm_cos_f32.o</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>roundf.o</c:v>
+                  <c:v>arm_sin_f32.o</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>arm_cos_f32.o</c:v>
+                  <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>arm_sin_f32.o</c:v>
+                  <c:v>list.o</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>stm32g4xx_hal.o</c:v>
+                  <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>list.o</c:v>
+                  <c:v>thread_period.o</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
+                  <c:v>motor_mode_mit.o</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>thread_period.o</c:v>
+                  <c:v>user_interface.o</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>motor_mode_mit.o</c:v>
+                  <c:v>motor_mode_velocity.o</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>user_interface.o</c:v>
+                  <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>motor_mode_velocity.o</c:v>
+                  <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>calib_level6_system.o</c:v>
+                  <c:v>floorf.o</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>dev_dwt_counter.o</c:v>
+                  <c:v>runtime_param.o</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>motor_mode_open_loop.o</c:v>
+                  <c:v>motor_mode_position.o</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>floorf.o</c:v>
+                  <c:v>motor_mode_current.o</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>runtime_param.o</c:v>
+                  <c:v>fepilogue.o</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>motor_mode_position.o</c:v>
+                  <c:v>ceilf.o</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>motor_mode_current.o</c:v>
+                  <c:v>uldiv.o</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>fepilogue.o</c:v>
+                  <c:v>ldiv.o</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>ceilf.o</c:v>
+                  <c:v>dma.o</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>uldiv.o</c:v>
+                  <c:v>__dczerorl2.o</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>ldiv.o</c:v>
+                  <c:v>motor_mode_torque.o</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>dma.o</c:v>
+                  <c:v>motor_mode_profile_torque.o</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>__dczerorl2.o</c:v>
+                  <c:v>assert_report.o</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>motor_mode_torque.o</c:v>
+                  <c:v>app_freertos.o</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>motor_mode_profile_torque.o</c:v>
+                  <c:v>funder.o</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>assert_report.o</c:v>
+                  <c:v>motor_mode_profile_velocity.o</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>app_freertos.o</c:v>
+                  <c:v>cordic.o</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>frem.o</c:v>
+                  <c:v>control_irq.o</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>funder.o</c:v>
+                  <c:v>motor_mode_duty.o</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>motor_mode_profile_velocity.o</c:v>
+                  <c:v>frnd.o</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>cordic.o</c:v>
+                  <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>motor_mode_duty.o</c:v>
+                  <c:v>sqrtf.o</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>frnd.o</c:v>
+                  <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>stm32g4xx_hal_msp.o</c:v>
+                  <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>control_irq.o</c:v>
+                  <c:v>utils.o</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>sqrtf.o</c:v>
+                  <c:v>dfixui.o</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>stm32g4xx_hal_cordic.o</c:v>
+                  <c:v>dfixul.o</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>calib_level4_torque.o</c:v>
+                  <c:v>cdrcmple.o</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>utils.o</c:v>
+                  <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>dfixui.o</c:v>
+                  <c:v>uidiv.o</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>dfixul.o</c:v>
+                  <c:v>thread_commun.o</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>cdrcmple.o</c:v>
+                  <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>drv_dwt_timer.o</c:v>
+                  <c:v>motor_mode_idle.o</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>uidiv.o</c:v>
+                  <c:v>motor_mode_hold.o</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>thread_commun.o</c:v>
+                  <c:v>drv_delay.o</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>system_stm32g4xx.o</c:v>
+                  <c:v>f2d.o</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>motor_mode_idle.o</c:v>
+                  <c:v>fpclassifyf.o</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>motor_mode_hold.o</c:v>
+                  <c:v>memseta.o</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>drv_delay.o</c:v>
+                  <c:v>memcpya.o</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>f2d.o</c:v>
+                  <c:v>llsshr.o</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>fpclassifyf.o</c:v>
+                  <c:v>init.o</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>memseta.o</c:v>
+                  <c:v>llushr.o</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>memcpya.o</c:v>
+                  <c:v>thread_idle.o</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>llsshr.o</c:v>
+                  <c:v>thread_display.o</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>init.o</c:v>
+                  <c:v>thread_control.o</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>llushr.o</c:v>
+                  <c:v>motor_mode_zero_force.o</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>thread_idle.o</c:v>
+                  <c:v>llshl.o</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>thread_display.o</c:v>
+                  <c:v>handlers.o</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>thread_control.o</c:v>
+                  <c:v>dfltui.o</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>motor_mode_zero_force.o</c:v>
+                  <c:v>memcmp.o</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>llshl.o</c:v>
+                  <c:v>dfltul.o</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>handlers.o</c:v>
+                  <c:v>strncpy.o</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>dfltui.o</c:v>
+                  <c:v>errno.o</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>memcmp.o</c:v>
+                  <c:v>entry9a.o</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>dfltul.o</c:v>
+                  <c:v>entry2.o</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>strncpy.o</c:v>
+                  <c:v>fpstat.o</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>errno.o</c:v>
+                  <c:v>stdout.o</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>entry9a.o</c:v>
+                  <c:v>entry5.o</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>entry2.o</c:v>
+                  <c:v>entry12b.o</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>fpstat.o</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>stdout.o</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>entry5.o</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>entry12b.o</c:v>
-                </c:pt>
-                <c:pt idx="185">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1665,566 +1641,554 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$188</c:f>
+              <c:f>flash_percent!$B$3:$B$184</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="186"/>
+                <c:ptCount val="182"/>
                 <c:pt idx="0">
-                  <c:v>4.513896942138672</c:v>
+                  <c:v>4.56882381439209</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.775900840759277</c:v>
+                  <c:v>3.589032888412476</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.636280059814453</c:v>
+                  <c:v>3.357336044311523</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.367778301239014</c:v>
+                  <c:v>3.033262968063355</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.002615928649902</c:v>
+                  <c:v>2.821252584457398</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.823103427886963</c:v>
+                  <c:v>2.786422252655029</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.542327404022217</c:v>
+                  <c:v>2.509294271469116</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.447201013565064</c:v>
+                  <c:v>2.415404081344605</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.213988065719605</c:v>
+                  <c:v>2.185221433639526</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.204782485961914</c:v>
+                  <c:v>2.176135301589966</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.066695928573608</c:v>
+                  <c:v>2.039842844009399</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.841154456138611</c:v>
+                  <c:v>2.026213645935059</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.804331302642822</c:v>
+                  <c:v>1.817231893539429</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.801262736320496</c:v>
+                  <c:v>1.780887246131897</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.798194169998169</c:v>
+                  <c:v>1.77785849571228</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.701533555984497</c:v>
+                  <c:v>1.774829864501953</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.647833228111267</c:v>
+                  <c:v>1.723341584205627</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.641695976257324</c:v>
+                  <c:v>1.679425120353699</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.57418704032898</c:v>
+                  <c:v>1.62642252445221</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.526623845100403</c:v>
+                  <c:v>1.620365142822266</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.500540852546692</c:v>
+                  <c:v>1.553733229637146</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.491335034370422</c:v>
+                  <c:v>1.50678813457489</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.45758056640625</c:v>
+                  <c:v>1.481044054031372</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.385468721389771</c:v>
+                  <c:v>1.471957802772522</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.36859142780304</c:v>
+                  <c:v>1.438641905784607</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.233573436737061</c:v>
+                  <c:v>1.400782942771912</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.230504870414734</c:v>
+                  <c:v>1.350809097290039</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.120035648345947</c:v>
+                  <c:v>1.217545390129089</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.103158354759216</c:v>
+                  <c:v>1.128198146820068</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.069403886795044</c:v>
+                  <c:v>1.08882474899292</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.069403886795044</c:v>
+                  <c:v>1.085796117782593</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.9574002623558044</c:v>
+                  <c:v>1.055508852005005</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.9359201788902283</c:v>
+                  <c:v>1.043393969535828</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9313172698020935</c:v>
+                  <c:v>0.9449605941772461</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9083028435707092</c:v>
+                  <c:v>0.9237595796585083</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.8822197914123535</c:v>
+                  <c:v>0.9025585055351257</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8300538063049316</c:v>
+                  <c:v>0.8707569241523743</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.7886278033256531</c:v>
+                  <c:v>0.8192687034606934</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.7763534188270569</c:v>
+                  <c:v>0.8026107549667358</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7763534188270569</c:v>
+                  <c:v>0.7783809900283814</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.7755863070487976</c:v>
+                  <c:v>0.7662661075592041</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7671476602554321</c:v>
+                  <c:v>0.7655089497566223</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7441332340240479</c:v>
+                  <c:v>0.7571799755096436</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7364617586135864</c:v>
+                  <c:v>0.7344645857810974</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.7333931922912598</c:v>
+                  <c:v>0.7268927693367004</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.7165158987045288</c:v>
+                  <c:v>0.7238640189170837</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.6628155708312988</c:v>
+                  <c:v>0.7072060704231262</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6536098122596741</c:v>
+                  <c:v>0.6814619898796082</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6520755290985107</c:v>
+                  <c:v>0.6769188642501831</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.6290611028671265</c:v>
+                  <c:v>0.654203474521637</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.6121838688850403</c:v>
+                  <c:v>0.6208875775337219</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.6014437675476074</c:v>
+                  <c:v>0.6042296290397644</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5799636244773865</c:v>
+                  <c:v>0.5936290621757507</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5554149150848389</c:v>
+                  <c:v>0.5724280476570129</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5523463487625122</c:v>
+                  <c:v>0.5663706064224243</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.5247290134429932</c:v>
+                  <c:v>0.5451695919036865</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.5047831535339356</c:v>
+                  <c:v>0.4982244074344635</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4940431118011475</c:v>
+                  <c:v>0.4876239001750946</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4756315648555756</c:v>
+                  <c:v>0.4694515764713287</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4740972518920898</c:v>
+                  <c:v>0.4679372012615204</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.4388084709644318</c:v>
+                  <c:v>0.433106929063797</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.426534116268158</c:v>
+                  <c:v>0.4209920465946198</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4203969240188599</c:v>
+                  <c:v>0.4149346053600311</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4173283278942108</c:v>
+                  <c:v>0.4119058847427368</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.3927796185016632</c:v>
+                  <c:v>0.3876761496067047</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.3897110223770142</c:v>
+                  <c:v>0.3846474289894104</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.3866424262523651</c:v>
+                  <c:v>0.3801043331623077</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3851081430912018</c:v>
+                  <c:v>0.3801043331623077</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3851081430912018</c:v>
+                  <c:v>0.3770756125450134</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3820395469665527</c:v>
+                  <c:v>0.3770756125450134</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3697651624679565</c:v>
+                  <c:v>0.3679894506931305</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3651622831821442</c:v>
+                  <c:v>0.3604176640510559</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3590251207351685</c:v>
+                  <c:v>0.3543602228164673</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.3498193323612213</c:v>
+                  <c:v>0.351331502199173</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.348285049200058</c:v>
+                  <c:v>0.3452740609645844</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3436821699142456</c:v>
+                  <c:v>0.3392166197299957</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.3314077854156494</c:v>
+                  <c:v>0.3271017372608185</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.326804906129837</c:v>
+                  <c:v>0.3225586712360382</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.3145305514335632</c:v>
+                  <c:v>0.3225586712360382</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.3145305514335632</c:v>
+                  <c:v>0.310443788766861</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.3129962384700775</c:v>
+                  <c:v>0.3089294135570526</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.3068590760231018</c:v>
+                  <c:v>0.302871972322464</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.3068590760231018</c:v>
+                  <c:v>0.302871972322464</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2853789329528809</c:v>
+                  <c:v>0.2922714650630951</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2807760536670685</c:v>
+                  <c:v>0.2816709578037262</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2638987898826599</c:v>
+                  <c:v>0.2771278619766235</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.2577616274356842</c:v>
+                  <c:v>0.260469913482666</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.2562273144721985</c:v>
+                  <c:v>0.252898097038269</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2546930313110352</c:v>
+                  <c:v>0.2513837516307831</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2485558390617371</c:v>
+                  <c:v>0.2453263103961945</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2362814843654633</c:v>
+                  <c:v>0.2332114279270172</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.2240071147680283</c:v>
+                  <c:v>0.22109654545784</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2086641639471054</c:v>
+                  <c:v>0.2059529423713684</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.2086641639471054</c:v>
+                  <c:v>0.2059529423713684</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.1933212131261826</c:v>
+                  <c:v>0.199895516037941</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.1887183338403702</c:v>
+                  <c:v>0.190809354186058</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1856497377157211</c:v>
+                  <c:v>0.1862662732601166</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1841154396533966</c:v>
+                  <c:v>0.1832375526428223</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1795125603675842</c:v>
+                  <c:v>0.1817231923341751</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1779782623052597</c:v>
+                  <c:v>0.1756657510995865</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1749096661806107</c:v>
+                  <c:v>0.1726370304822922</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1749096661806107</c:v>
+                  <c:v>0.1726370304822922</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1703067868947983</c:v>
+                  <c:v>0.1680939495563507</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1687724888324738</c:v>
+                  <c:v>0.1665795892477036</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1687724888324738</c:v>
+                  <c:v>0.1453785449266434</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1472923457622528</c:v>
+                  <c:v>0.1423498392105103</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.144223764538765</c:v>
+                  <c:v>0.1408354789018631</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1426894664764404</c:v>
+                  <c:v>0.1332636773586273</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.135017991065979</c:v>
+                  <c:v>0.130234956741333</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.135017991065979</c:v>
+                  <c:v>0.1196344345808029</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.13194939494133</c:v>
+                  <c:v>0.1166057139635086</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1212093308568001</c:v>
+                  <c:v>0.1150913536548615</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1181407421827316</c:v>
+                  <c:v>0.1090339124202728</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1166064441204071</c:v>
+                  <c:v>0.1075195521116257</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1104692667722702</c:v>
+                  <c:v>0.1044908314943314</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1089349687099457</c:v>
+                  <c:v>0.1029764711856842</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.1058663800358772</c:v>
+                  <c:v>0.09691903740167618</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.1043320819735527</c:v>
+                  <c:v>0.09691903740167618</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.0981949046254158</c:v>
+                  <c:v>0.09540467709302902</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.0981949046254158</c:v>
+                  <c:v>0.09540467709302902</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.09666060656309128</c:v>
+                  <c:v>0.09086159616708756</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.09666060656309128</c:v>
+                  <c:v>0.08631851524114609</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.09666060656309128</c:v>
+                  <c:v>0.08480415493249893</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.0920577198266983</c:v>
+                  <c:v>0.08480415493249893</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.08745483309030533</c:v>
+                  <c:v>0.08480415493249893</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.0859205424785614</c:v>
+                  <c:v>0.08480415493249893</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.0859205424785614</c:v>
+                  <c:v>0.08328979462385178</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.0859205424785614</c:v>
+                  <c:v>0.08177543431520462</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.0859205424785614</c:v>
+                  <c:v>0.07420363277196884</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.08438624441623688</c:v>
+                  <c:v>0.07420363277196884</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.08285194635391235</c:v>
+                  <c:v>0.06966055929660797</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.07518047094345093</c:v>
+                  <c:v>0.0651174783706665</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.07518047094345093</c:v>
+                  <c:v>0.06360311806201935</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.07057758420705795</c:v>
+                  <c:v>0.06360311806201935</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06597469747066498</c:v>
+                  <c:v>0.06360311806201935</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06444040685892105</c:v>
+                  <c:v>0.06360311806201935</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.06444040685892105</c:v>
+                  <c:v>0.06057439744472504</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.06444040685892105</c:v>
+                  <c:v>0.05906003713607788</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.06444040685892105</c:v>
+                  <c:v>0.05754567682743073</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.06290610879659653</c:v>
+                  <c:v>0.05451695621013641</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.0613718144595623</c:v>
+                  <c:v>0.04997387900948525</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.05983751639723778</c:v>
+                  <c:v>0.04543079808354378</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.05830322206020355</c:v>
+                  <c:v>0.04543079808354378</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.05063174664974213</c:v>
+                  <c:v>0.04391643777489662</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04602885991334915</c:v>
+                  <c:v>0.04088771715760231</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04602885991334915</c:v>
+                  <c:v>0.04088771715760231</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.04602885991334915</c:v>
+                  <c:v>0.03937335684895515</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.04449456557631493</c:v>
+                  <c:v>0.037858996540308</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.04142597317695618</c:v>
+                  <c:v>0.03634463623166084</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.04142597317695618</c:v>
+                  <c:v>0.03634463623166084</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03989167883992195</c:v>
+                  <c:v>0.03634463623166084</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03835738450288773</c:v>
+                  <c:v>0.03331591933965683</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.0368230864405632</c:v>
+                  <c:v>0.03331591933965683</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.0368230864405632</c:v>
+                  <c:v>0.03331591933965683</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.0368230864405632</c:v>
+                  <c:v>0.03331591933965683</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.03375449776649475</c:v>
+                  <c:v>0.03331591933965683</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.03375449776649475</c:v>
+                  <c:v>0.03028719872236252</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.03375449776649475</c:v>
+                  <c:v>0.02877283841371536</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.03375449776649475</c:v>
+                  <c:v>0.02877283841371536</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.03375449776649475</c:v>
+                  <c:v>0.02725847810506821</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.03068590722978115</c:v>
+                  <c:v>0.02725847810506821</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.02915161103010178</c:v>
+                  <c:v>0.02725847810506821</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.02915161103010178</c:v>
+                  <c:v>0.02725847810506821</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.02761731669306755</c:v>
+                  <c:v>0.02422975935041904</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02761731669306755</c:v>
+                  <c:v>0.02422975935041904</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02761731669306755</c:v>
+                  <c:v>0.02422975935041904</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02761731669306755</c:v>
+                  <c:v>0.02422975935041904</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.02454872615635395</c:v>
+                  <c:v>0.02422975935041904</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.02454872615635395</c:v>
+                  <c:v>0.02271539904177189</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.02454872615635395</c:v>
+                  <c:v>0.02271539904177189</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.02454872615635395</c:v>
+                  <c:v>0.01968667842447758</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.02454872615635395</c:v>
+                  <c:v>0.01968667842447758</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.02301442995667458</c:v>
+                  <c:v>0.01817231811583042</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>0.02301442995667458</c:v>
+                  <c:v>0.01817231811583042</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>0.01994583941996098</c:v>
+                  <c:v>0.01211487967520952</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>0.01994583941996098</c:v>
+                  <c:v>0.006057439837604761</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>0.0184115432202816</c:v>
+                  <c:v>0.006057439837604761</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>0.0184115432202816</c:v>
+                  <c:v>0.003028719918802381</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>0.01227436307817698</c:v>
+                  <c:v>0.003028719918802381</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>0.006137181539088488</c:v>
+                  <c:v>0.003028719918802381</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>0.006137181539088488</c:v>
+                  <c:v>0.003028719918802381</c:v>
                 </c:pt>
                 <c:pt idx="181">
-                  <c:v>0.003068590769544244</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.003068590769544244</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.003068590769544244</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.003068590769544244</c:v>
-                </c:pt>
-                <c:pt idx="185">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2329,8 +2293,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H188" totalsRowCount="1">
-  <autoFilter ref="A2:H187"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H184" totalsRowCount="1">
+  <autoFilter ref="A2:H183"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -2346,8 +2310,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H188" totalsRowCount="1">
-  <autoFilter ref="A2:H187"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H184" totalsRowCount="1">
+  <autoFilter ref="A2:H183"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2647,7 +2611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2660,28 +2624,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" t="s">
         <v>186</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" t="s">
         <v>188</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G2" t="s">
         <v>189</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>190</v>
-      </c>
-      <c r="E2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2689,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>36.23833465576172</v>
+        <v>36.17101287841797</v>
       </c>
       <c r="C3" s="1">
         <v>28816</v>
@@ -2715,7 +2679,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>20.64438247680664</v>
+        <v>20.60602951049805</v>
       </c>
       <c r="C4" s="1">
         <v>16416</v>
@@ -2741,16 +2705,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>12.63110256195068</v>
+        <v>12.61767864227295</v>
       </c>
       <c r="C5" s="1">
-        <v>10044</v>
+        <v>10052</v>
       </c>
       <c r="D5" s="1">
-        <v>1012</v>
+        <v>1060</v>
       </c>
       <c r="E5" s="1">
-        <v>1012</v>
+        <v>1060</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2759,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>10044</v>
+        <v>10052</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2767,7 +2731,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>5.151034832000732</v>
+        <v>5.141465663909912</v>
       </c>
       <c r="C6" s="1">
         <v>4096</v>
@@ -2793,7 +2757,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>5.151034832000732</v>
+        <v>5.141465663909912</v>
       </c>
       <c r="C7" s="1">
         <v>4096</v>
@@ -2819,7 +2783,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.718428611755371</v>
+        <v>4.709662914276123</v>
       </c>
       <c r="C8" s="1">
         <v>3752</v>
@@ -2845,7 +2809,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.635881185531616</v>
+        <v>2.630984306335449</v>
       </c>
       <c r="C9" s="1">
         <v>2096</v>
@@ -2871,7 +2835,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.570487260818481</v>
+        <v>2.565711736679077</v>
       </c>
       <c r="C10" s="1">
         <v>2044</v>
@@ -2897,7 +2861,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.072486639022827</v>
+        <v>2.068636655807495</v>
       </c>
       <c r="C11" s="1">
         <v>1648</v>
@@ -2923,7 +2887,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.29656183719635</v>
+        <v>1.294153094291687</v>
       </c>
       <c r="C12" s="1">
         <v>1031</v>
@@ -2949,7 +2913,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.287758708000183</v>
+        <v>1.285366415977478</v>
       </c>
       <c r="C13" s="1">
         <v>1024</v>
@@ -2975,7 +2939,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.9054553508758545</v>
+        <v>0.9037732481956482</v>
       </c>
       <c r="C14" s="1">
         <v>720</v>
@@ -3001,22 +2965,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.4929701387882233</v>
+        <v>0.5020962357521057</v>
       </c>
       <c r="C15" s="1">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="D15" s="1">
-        <v>5884</v>
+        <v>6034</v>
       </c>
       <c r="E15" s="1">
-        <v>5384</v>
+        <v>5522</v>
       </c>
       <c r="F15" s="1">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G15" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H15" s="1">
         <v>364</v>
@@ -3027,7 +2991,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.4476973712444305</v>
+        <v>0.4468656778335571</v>
       </c>
       <c r="C16" s="1">
         <v>356</v>
@@ -3053,7 +3017,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.4275761544704437</v>
+        <v>0.4267818033695221</v>
       </c>
       <c r="C17" s="1">
         <v>340</v>
@@ -3079,7 +3043,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3772730827331543</v>
+        <v>0.3765721917152405</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -3105,19 +3069,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3370306193828583</v>
+        <v>0.3364045023918152</v>
       </c>
       <c r="C19" s="1">
         <v>268</v>
       </c>
       <c r="D19" s="1">
-        <v>1604</v>
+        <v>2276</v>
       </c>
       <c r="E19" s="1">
-        <v>1604</v>
+        <v>1912</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
@@ -3131,7 +3095,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.2867275476455689</v>
+        <v>0.2861948609352112</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -3157,7 +3121,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.2816972136497498</v>
+        <v>0.2811739146709442</v>
       </c>
       <c r="C21" s="1">
         <v>224</v>
@@ -3183,7 +3147,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.2565456926822662</v>
+        <v>0.2560690939426422</v>
       </c>
       <c r="C22" s="1">
         <v>204</v>
@@ -3209,7 +3173,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2515153884887695</v>
+        <v>0.2510481178760529</v>
       </c>
       <c r="C23" s="1">
         <v>200</v>
@@ -3235,16 +3199,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.1660001575946808</v>
+        <v>0.1707127243280411</v>
       </c>
       <c r="C24" s="1">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D24" s="1">
-        <v>4390</v>
+        <v>2676</v>
       </c>
       <c r="E24" s="1">
-        <v>4378</v>
+        <v>2664</v>
       </c>
       <c r="F24" s="1">
         <v>12</v>
@@ -3253,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3261,25 +3225,25 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.1609698385000229</v>
+        <v>0.1656917631626129</v>
       </c>
       <c r="C25" s="1">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D25" s="1">
-        <v>120</v>
+        <v>4434</v>
       </c>
       <c r="E25" s="1">
-        <v>120</v>
+        <v>4422</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
       <c r="H25" s="1">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3287,16 +3251,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.1257576942443848</v>
+        <v>0.1606708019971848</v>
       </c>
       <c r="C26" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="D26" s="1">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="E26" s="1">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -3305,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3313,16 +3277,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1056364625692368</v>
+        <v>0.1255240589380264</v>
       </c>
       <c r="C27" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D27" s="1">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="E27" s="1">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -3331,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -3339,16 +3303,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.09557584673166275</v>
+        <v>0.1054402142763138</v>
       </c>
       <c r="C28" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D28" s="1">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="E28" s="1">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -3357,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -3365,25 +3329,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.09054553508758545</v>
+        <v>0.09539828449487686</v>
       </c>
       <c r="C29" s="1">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D29" s="1">
-        <v>400</v>
+        <v>136</v>
       </c>
       <c r="E29" s="1">
-        <v>392</v>
+        <v>136</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -3391,25 +3355,25 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.09054553508758545</v>
+        <v>0.0903773233294487</v>
       </c>
       <c r="C30" s="1">
         <v>72</v>
       </c>
       <c r="D30" s="1">
-        <v>1028</v>
+        <v>400</v>
       </c>
       <c r="E30" s="1">
-        <v>468</v>
+        <v>392</v>
       </c>
       <c r="F30" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="H30" s="1">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -3417,25 +3381,25 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.09054553508758545</v>
+        <v>0.0903773233294487</v>
       </c>
       <c r="C31" s="1">
         <v>72</v>
       </c>
       <c r="D31" s="1">
-        <v>970</v>
+        <v>1028</v>
       </c>
       <c r="E31" s="1">
-        <v>958</v>
+        <v>468</v>
       </c>
       <c r="F31" s="1">
-        <v>12</v>
+        <v>512</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H31" s="1">
-        <v>72</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -3443,25 +3407,25 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.08551523089408875</v>
+        <v>0.0903773233294487</v>
       </c>
       <c r="C32" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D32" s="1">
-        <v>292</v>
+        <v>970</v>
       </c>
       <c r="E32" s="1">
-        <v>292</v>
+        <v>958</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -3469,25 +3433,25 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.08048491925001144</v>
+        <v>0.08535636216402054</v>
       </c>
       <c r="C33" s="1">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D33" s="1">
-        <v>1150</v>
+        <v>292</v>
       </c>
       <c r="E33" s="1">
-        <v>1126</v>
+        <v>292</v>
       </c>
       <c r="F33" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -3495,25 +3459,25 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.05533338338136673</v>
+        <v>0.08033540099859238</v>
       </c>
       <c r="C34" s="1">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D34" s="1">
-        <v>408</v>
+        <v>1150</v>
       </c>
       <c r="E34" s="1">
-        <v>344</v>
+        <v>1126</v>
       </c>
       <c r="F34" s="1">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G34" s="1">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3521,25 +3485,25 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.05030307546257973</v>
+        <v>0.05523058772087097</v>
       </c>
       <c r="C35" s="1">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D35" s="1">
-        <v>76</v>
+        <v>408</v>
       </c>
       <c r="E35" s="1">
-        <v>76</v>
+        <v>344</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H35" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -3547,25 +3511,25 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.04527276754379273</v>
+        <v>0.05020962655544281</v>
       </c>
       <c r="C36" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D36" s="1">
-        <v>1082</v>
+        <v>76</v>
       </c>
       <c r="E36" s="1">
-        <v>1070</v>
+        <v>76</v>
       </c>
       <c r="F36" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -3573,25 +3537,25 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.04024245962500572</v>
+        <v>0.04518866166472435</v>
       </c>
       <c r="C37" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D37" s="1">
-        <v>456</v>
+        <v>1082</v>
       </c>
       <c r="E37" s="1">
-        <v>424</v>
+        <v>1070</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G37" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -3599,25 +3563,25 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.04024245962500572</v>
+        <v>0.04518866166472435</v>
       </c>
       <c r="C38" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D38" s="1">
-        <v>658</v>
+        <v>1490</v>
       </c>
       <c r="E38" s="1">
-        <v>658</v>
+        <v>1454</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -3625,25 +3589,25 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.03521215170621872</v>
+        <v>0.04016770049929619</v>
       </c>
       <c r="C39" s="1">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D39" s="1">
-        <v>1394</v>
+        <v>456</v>
       </c>
       <c r="E39" s="1">
-        <v>1366</v>
+        <v>424</v>
       </c>
       <c r="F39" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H39" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -3651,16 +3615,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.02515153773128986</v>
+        <v>0.04016770049929619</v>
       </c>
       <c r="C40" s="1">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D40" s="1">
-        <v>192</v>
+        <v>658</v>
       </c>
       <c r="E40" s="1">
-        <v>192</v>
+        <v>658</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -3669,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -3677,25 +3641,25 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.02515153773128986</v>
+        <v>0.02510481327772141</v>
       </c>
       <c r="C41" s="1">
         <v>20</v>
       </c>
       <c r="D41" s="1">
-        <v>1184</v>
+        <v>192</v>
       </c>
       <c r="E41" s="1">
-        <v>1164</v>
+        <v>192</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
       </c>
       <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
         <v>20</v>
-      </c>
-      <c r="H41" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -3703,22 +3667,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.01509092282503843</v>
+        <v>0.02510481327772141</v>
       </c>
       <c r="C42" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D42" s="1">
-        <v>142</v>
+        <v>1192</v>
       </c>
       <c r="E42" s="1">
-        <v>130</v>
+        <v>1172</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -3729,16 +3693,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.01509092282503843</v>
+        <v>0.01506288722157478</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
       </c>
       <c r="D43" s="1">
-        <v>798</v>
+        <v>142</v>
       </c>
       <c r="E43" s="1">
-        <v>786</v>
+        <v>130</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3755,19 +3719,19 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.01509092282503843</v>
+        <v>0.01506288722157478</v>
       </c>
       <c r="C44" s="1">
         <v>12</v>
       </c>
       <c r="D44" s="1">
-        <v>126</v>
+        <v>798</v>
       </c>
       <c r="E44" s="1">
-        <v>102</v>
+        <v>786</v>
       </c>
       <c r="F44" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
         <v>12</v>
@@ -3781,7 +3745,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01509092282503843</v>
+        <v>0.01506288722157478</v>
       </c>
       <c r="C45" s="1">
         <v>12</v>
@@ -3807,7 +3771,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01006061490625143</v>
+        <v>0.01004192512482405</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
@@ -3833,7 +3797,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01006061490625143</v>
+        <v>0.01004192512482405</v>
       </c>
       <c r="C47" s="1">
         <v>8</v>
@@ -3859,7 +3823,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.01006061490625143</v>
+        <v>0.01004192512482405</v>
       </c>
       <c r="C48" s="1">
         <v>8</v>
@@ -3885,7 +3849,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.005030307453125715</v>
+        <v>0.005020962562412024</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
@@ -3911,7 +3875,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.005030307453125715</v>
+        <v>0.005020962562412024</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
@@ -3937,7 +3901,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.005030307453125715</v>
+        <v>0.005020962562412024</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
@@ -3963,7 +3927,7 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.005030307453125715</v>
+        <v>0.005020962562412024</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
@@ -3989,7 +3953,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.005030307453125715</v>
+        <v>0.005020962562412024</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -4015,7 +3979,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.005030307453125715</v>
+        <v>0.005020962562412024</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
@@ -4041,7 +4005,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.005030307453125715</v>
+        <v>0.005020962562412024</v>
       </c>
       <c r="C55" s="1">
         <v>4</v>
@@ -4067,7 +4031,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.003772730706259608</v>
+        <v>0.003765721805393696</v>
       </c>
       <c r="C56" s="1">
         <v>3</v>
@@ -4088,35 +4052,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8">
-      <c r="A188" t="s">
-        <v>187</v>
-      </c>
-      <c r="B188">
+    <row r="184" spans="1:8">
+      <c r="A184" t="s">
+        <v>183</v>
+      </c>
+      <c r="B184">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C188">
+      <c r="C184">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D188">
+      <c r="D184">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E188">
+      <c r="E184">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F188">
+      <c r="F184">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G188">
+      <c r="G184">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H188">
+      <c r="H184">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -4132,7 +4096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -4145,28 +4109,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" t="s">
         <v>186</v>
       </c>
-      <c r="B2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H2" t="s">
         <v>190</v>
-      </c>
-      <c r="D2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4174,22 +4138,22 @@
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>4.513896942138672</v>
+        <v>4.56882381439209</v>
       </c>
       <c r="C3" s="1">
-        <v>5884</v>
+        <v>6034</v>
       </c>
       <c r="D3" s="1">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="E3" s="1">
-        <v>5384</v>
+        <v>5522</v>
       </c>
       <c r="F3" s="1">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="G3" s="1">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H3" s="1">
         <v>364</v>
@@ -4200,19 +4164,19 @@
         <v>55</v>
       </c>
       <c r="B4" s="2">
-        <v>3.775900840759277</v>
+        <v>3.589032888412476</v>
       </c>
       <c r="C4" s="1">
-        <v>4922</v>
+        <v>4740</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>4506</v>
+        <v>3112</v>
       </c>
       <c r="F4" s="1">
-        <v>416</v>
+        <v>1628</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -4223,54 +4187,54 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2">
-        <v>3.636280059814453</v>
+        <v>3.357336044311523</v>
       </c>
       <c r="C5" s="1">
-        <v>4740</v>
+        <v>4434</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="E5" s="1">
-        <v>3112</v>
+        <v>4422</v>
       </c>
       <c r="F5" s="1">
-        <v>1628</v>
+        <v>12</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2">
-        <v>3.367778301239014</v>
+        <v>3.033262968063355</v>
       </c>
       <c r="C6" s="1">
-        <v>4390</v>
+        <v>4006</v>
       </c>
       <c r="D6" s="1">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>4378</v>
+        <v>4006</v>
       </c>
       <c r="F6" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4278,19 +4242,19 @@
         <v>57</v>
       </c>
       <c r="B7" s="2">
-        <v>3.002615928649902</v>
+        <v>2.821252584457398</v>
       </c>
       <c r="C7" s="1">
-        <v>3914</v>
+        <v>3726</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>3914</v>
+        <v>3310</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -4304,7 +4268,7 @@
         <v>58</v>
       </c>
       <c r="B8" s="2">
-        <v>2.823103427886963</v>
+        <v>2.786422252655029</v>
       </c>
       <c r="C8" s="1">
         <v>3680</v>
@@ -4330,7 +4294,7 @@
         <v>59</v>
       </c>
       <c r="B9" s="2">
-        <v>2.542327404022217</v>
+        <v>2.509294271469116</v>
       </c>
       <c r="C9" s="1">
         <v>3314</v>
@@ -4356,7 +4320,7 @@
         <v>60</v>
       </c>
       <c r="B10" s="2">
-        <v>2.447201013565064</v>
+        <v>2.415404081344605</v>
       </c>
       <c r="C10" s="1">
         <v>3190</v>
@@ -4382,7 +4346,7 @@
         <v>61</v>
       </c>
       <c r="B11" s="2">
-        <v>2.213988065719605</v>
+        <v>2.185221433639526</v>
       </c>
       <c r="C11" s="1">
         <v>2886</v>
@@ -4408,7 +4372,7 @@
         <v>44</v>
       </c>
       <c r="B12" s="2">
-        <v>2.204782485961914</v>
+        <v>2.176135301589966</v>
       </c>
       <c r="C12" s="1">
         <v>2874</v>
@@ -4434,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>2.066695928573608</v>
+        <v>2.039842844009399</v>
       </c>
       <c r="C13" s="1">
         <v>2694</v>
@@ -4457,48 +4421,48 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>1.841154456138611</v>
+        <v>2.026213645935059</v>
       </c>
       <c r="C14" s="1">
-        <v>2400</v>
+        <v>2676</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="E14" s="1">
-        <v>2384</v>
+        <v>2664</v>
       </c>
       <c r="F14" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2">
-        <v>1.804331302642822</v>
+        <v>1.817231893539429</v>
       </c>
       <c r="C15" s="1">
-        <v>2352</v>
+        <v>2400</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>2352</v>
+        <v>2384</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -4509,22 +4473,22 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2">
-        <v>1.801262736320496</v>
+        <v>1.780887246131897</v>
       </c>
       <c r="C16" s="1">
-        <v>2348</v>
+        <v>2352</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
       <c r="E16" s="1">
-        <v>296</v>
+        <v>2352</v>
       </c>
       <c r="F16" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
@@ -4535,126 +4499,126 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2">
-        <v>1.798194169998169</v>
+        <v>1.77785849571228</v>
       </c>
       <c r="C17" s="1">
-        <v>2344</v>
+        <v>2348</v>
       </c>
       <c r="D17" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
-        <v>2284</v>
+        <v>296</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>2052</v>
       </c>
       <c r="G17" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>1.701533555984497</v>
+        <v>1.774829864501953</v>
       </c>
       <c r="C18" s="1">
-        <v>2218</v>
+        <v>2344</v>
       </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E18" s="1">
-        <v>2218</v>
+        <v>2284</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H18" s="1">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>1.647833228111267</v>
+        <v>1.723341584205627</v>
       </c>
       <c r="C19" s="1">
-        <v>2148</v>
+        <v>2276</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="E19" s="1">
-        <v>2148</v>
+        <v>1912</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>364</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2">
-        <v>1.641695976257324</v>
+        <v>1.679425120353699</v>
       </c>
       <c r="C20" s="1">
-        <v>2140</v>
+        <v>2218</v>
       </c>
       <c r="D20" s="1">
-        <v>3752</v>
+        <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>2136</v>
+        <v>2218</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>3748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2">
-        <v>1.57418704032898</v>
+        <v>1.62642252445221</v>
       </c>
       <c r="C21" s="1">
-        <v>2052</v>
+        <v>2148</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>0</v>
+        <v>2148</v>
       </c>
       <c r="F21" s="1">
-        <v>2052</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
@@ -4665,48 +4629,48 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2">
-        <v>1.526623845100403</v>
+        <v>1.620365142822266</v>
       </c>
       <c r="C22" s="1">
-        <v>1990</v>
+        <v>2140</v>
       </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>3752</v>
       </c>
       <c r="E22" s="1">
-        <v>1990</v>
+        <v>2136</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B23" s="2">
-        <v>1.500540852546692</v>
+        <v>1.553733229637146</v>
       </c>
       <c r="C23" s="1">
-        <v>1956</v>
+        <v>2052</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>1636</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>320</v>
+        <v>2052</v>
       </c>
       <c r="G23" s="1">
         <v>0</v>
@@ -4717,22 +4681,22 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B24" s="2">
-        <v>1.491335034370422</v>
+        <v>1.50678813457489</v>
       </c>
       <c r="C24" s="1">
-        <v>1944</v>
+        <v>1990</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1930</v>
+        <v>1990</v>
       </c>
       <c r="F24" s="1">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -4743,22 +4707,22 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B25" s="2">
-        <v>1.45758056640625</v>
+        <v>1.481044054031372</v>
       </c>
       <c r="C25" s="1">
-        <v>1900</v>
+        <v>1956</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>1900</v>
+        <v>1636</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
@@ -4769,22 +4733,22 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B26" s="2">
-        <v>1.385468721389771</v>
+        <v>1.471957802772522</v>
       </c>
       <c r="C26" s="1">
-        <v>1806</v>
+        <v>1944</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>1806</v>
+        <v>1930</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
@@ -4795,25 +4759,25 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="B27" s="2">
-        <v>1.36859142780304</v>
+        <v>1.438641905784607</v>
       </c>
       <c r="C27" s="1">
-        <v>1784</v>
+        <v>1900</v>
       </c>
       <c r="D27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>1444</v>
+        <v>1900</v>
       </c>
       <c r="F27" s="1">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -4821,19 +4785,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="2">
-        <v>1.233573436737061</v>
+        <v>1.400782942771912</v>
       </c>
       <c r="C28" s="1">
-        <v>1608</v>
+        <v>1850</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>1608</v>
+        <v>1850</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -4847,45 +4811,45 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2">
-        <v>1.230504870414734</v>
+        <v>1.350809097290039</v>
       </c>
       <c r="C29" s="1">
-        <v>1604</v>
+        <v>1784</v>
       </c>
       <c r="D29" s="1">
-        <v>268</v>
+        <v>4</v>
       </c>
       <c r="E29" s="1">
-        <v>1604</v>
+        <v>1444</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H29" s="1">
-        <v>268</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B30" s="2">
-        <v>1.120035648345947</v>
+        <v>1.217545390129089</v>
       </c>
       <c r="C30" s="1">
-        <v>1460</v>
+        <v>1608</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>1460</v>
+        <v>1608</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -4899,97 +4863,97 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2">
-        <v>1.103158354759216</v>
+        <v>1.128198146820068</v>
       </c>
       <c r="C31" s="1">
-        <v>1438</v>
+        <v>1490</v>
       </c>
       <c r="D31" s="1">
-        <v>356</v>
+        <v>36</v>
       </c>
       <c r="E31" s="1">
-        <v>1082</v>
+        <v>1454</v>
       </c>
       <c r="F31" s="1">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="G31" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>352</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="B32" s="2">
-        <v>1.069403886795044</v>
+        <v>1.08882474899292</v>
       </c>
       <c r="C32" s="1">
-        <v>1394</v>
+        <v>1438</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E32" s="1">
-        <v>1394</v>
+        <v>1082</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B33" s="2">
-        <v>1.069403886795044</v>
+        <v>1.085796117782593</v>
       </c>
       <c r="C33" s="1">
-        <v>1394</v>
+        <v>1434</v>
       </c>
       <c r="D33" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>1366</v>
+        <v>1434</v>
       </c>
       <c r="F33" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
         <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" s="2">
-        <v>0.9574002623558044</v>
+        <v>1.055508852005005</v>
       </c>
       <c r="C34" s="1">
-        <v>1248</v>
+        <v>1394</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>1248</v>
+        <v>1394</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -5003,19 +4967,19 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B35" s="2">
-        <v>0.9359201788902283</v>
+        <v>1.043393969535828</v>
       </c>
       <c r="C35" s="1">
-        <v>1220</v>
+        <v>1378</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>1220</v>
+        <v>1378</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -5029,19 +4993,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9313172698020935</v>
+        <v>0.9449605941772461</v>
       </c>
       <c r="C36" s="1">
-        <v>1214</v>
+        <v>1248</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>1214</v>
+        <v>1248</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -5055,25 +5019,25 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9083028435707092</v>
+        <v>0.9237595796585083</v>
       </c>
       <c r="C37" s="1">
-        <v>1184</v>
+        <v>1220</v>
       </c>
       <c r="D37" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1">
-        <v>1164</v>
+        <v>1220</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -5081,97 +5045,97 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2">
-        <v>0.8822197914123535</v>
+        <v>0.9025585055351257</v>
       </c>
       <c r="C38" s="1">
-        <v>1150</v>
+        <v>1192</v>
       </c>
       <c r="D38" s="1">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="E38" s="1">
-        <v>1126</v>
+        <v>1172</v>
       </c>
       <c r="F38" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H38" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8300538063049316</v>
+        <v>0.8707569241523743</v>
       </c>
       <c r="C39" s="1">
-        <v>1082</v>
+        <v>1150</v>
       </c>
       <c r="D39" s="1">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E39" s="1">
-        <v>1070</v>
+        <v>1126</v>
       </c>
       <c r="F39" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H39" s="1">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B40" s="2">
-        <v>0.7886278033256531</v>
+        <v>0.8192687034606934</v>
       </c>
       <c r="C40" s="1">
-        <v>1028</v>
+        <v>1082</v>
       </c>
       <c r="D40" s="1">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="E40" s="1">
-        <v>468</v>
+        <v>1070</v>
       </c>
       <c r="F40" s="1">
-        <v>512</v>
+        <v>12</v>
       </c>
       <c r="G40" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>79</v>
+        <v>3</v>
       </c>
       <c r="B41" s="2">
-        <v>0.7763534188270569</v>
+        <v>0.8026107549667358</v>
       </c>
       <c r="C41" s="1">
-        <v>1012</v>
+        <v>1060</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>10052</v>
       </c>
       <c r="E41" s="1">
-        <v>1012</v>
+        <v>1060</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -5180,56 +5144,56 @@
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>10052</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7763534188270569</v>
+        <v>0.7783809900283814</v>
       </c>
       <c r="C42" s="1">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="D42" s="1">
-        <v>10044</v>
+        <v>72</v>
       </c>
       <c r="E42" s="1">
-        <v>1012</v>
+        <v>468</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H42" s="1">
-        <v>10044</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B43" s="2">
-        <v>0.7755863070487976</v>
+        <v>0.7662661075592041</v>
       </c>
       <c r="C43" s="1">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D43" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -5237,25 +5201,25 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7671476602554321</v>
+        <v>0.7655089497566223</v>
       </c>
       <c r="C44" s="1">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="D44" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E44" s="1">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -5263,71 +5227,71 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7441332340240479</v>
+        <v>0.7571799755096436</v>
       </c>
       <c r="C45" s="1">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="D45" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>958</v>
+        <v>1000</v>
       </c>
       <c r="F45" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7364617586135864</v>
+        <v>0.7344645857810974</v>
       </c>
       <c r="C46" s="1">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="D46" s="1">
-        <v>4096</v>
+        <v>72</v>
       </c>
       <c r="E46" s="1">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="F46" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>4096</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7333931922912598</v>
+        <v>0.7268927693367004</v>
       </c>
       <c r="C47" s="1">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="D47" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="E47" s="1">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -5336,76 +5300,76 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="B48" s="2">
-        <v>0.7165158987045288</v>
+        <v>0.7238640189170837</v>
       </c>
       <c r="C48" s="1">
-        <v>934</v>
+        <v>956</v>
       </c>
       <c r="D48" s="1">
-        <v>2096</v>
+        <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>918</v>
+        <v>956</v>
       </c>
       <c r="F48" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>2096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="B49" s="2">
-        <v>0.6628155708312988</v>
+        <v>0.7072060704231262</v>
       </c>
       <c r="C49" s="1">
-        <v>864</v>
+        <v>934</v>
       </c>
       <c r="D49" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
       <c r="E49" s="1">
-        <v>864</v>
+        <v>918</v>
       </c>
       <c r="F49" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6536098122596741</v>
+        <v>0.6814619898796082</v>
       </c>
       <c r="C50" s="1">
-        <v>852</v>
+        <v>900</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>852</v>
+        <v>900</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -5419,19 +5383,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6520755290985107</v>
+        <v>0.6769188642501831</v>
       </c>
       <c r="C51" s="1">
-        <v>850</v>
+        <v>894</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>850</v>
+        <v>894</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -5445,77 +5409,77 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="B52" s="2">
-        <v>0.6290611028671265</v>
+        <v>0.654203474521637</v>
       </c>
       <c r="C52" s="1">
-        <v>820</v>
+        <v>864</v>
       </c>
       <c r="D52" s="1">
-        <v>1648</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>816</v>
+        <v>864</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>1644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B53" s="2">
-        <v>0.6121838688850403</v>
+        <v>0.6208875775337219</v>
       </c>
       <c r="C53" s="1">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="D53" s="1">
-        <v>12</v>
+        <v>1648</v>
       </c>
       <c r="E53" s="1">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="B54" s="2">
-        <v>0.6014437675476074</v>
+        <v>0.6042296290397644</v>
       </c>
       <c r="C54" s="1">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="D54" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E54" s="1">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H54" s="1">
         <v>0</v>
@@ -5523,19 +5487,19 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5799636244773865</v>
+        <v>0.5936290621757507</v>
       </c>
       <c r="C55" s="1">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="D55" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -5544,24 +5508,24 @@
         <v>0</v>
       </c>
       <c r="H55" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5554149150848389</v>
+        <v>0.5724280476570129</v>
       </c>
       <c r="C56" s="1">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="D56" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E56" s="1">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -5570,24 +5534,24 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5523463487625122</v>
+        <v>0.5663706064224243</v>
       </c>
       <c r="C57" s="1">
-        <v>720</v>
+        <v>748</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>720</v>
+        <v>748</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -5601,19 +5565,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B58" s="2">
-        <v>0.5247290134429932</v>
+        <v>0.5451695919036865</v>
       </c>
       <c r="C58" s="1">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -5627,10 +5591,10 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B59" s="2">
-        <v>0.5047831535339356</v>
+        <v>0.4982244074344635</v>
       </c>
       <c r="C59" s="1">
         <v>658</v>
@@ -5653,10 +5617,10 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4940431118011475</v>
+        <v>0.4876239001750946</v>
       </c>
       <c r="C60" s="1">
         <v>644</v>
@@ -5682,7 +5646,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4756315648555756</v>
+        <v>0.4694515764713287</v>
       </c>
       <c r="C61" s="1">
         <v>620</v>
@@ -5705,10 +5669,10 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4740972518920898</v>
+        <v>0.4679372012615204</v>
       </c>
       <c r="C62" s="1">
         <v>618</v>
@@ -5731,10 +5695,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B63" s="2">
-        <v>0.4388084709644318</v>
+        <v>0.433106929063797</v>
       </c>
       <c r="C63" s="1">
         <v>572</v>
@@ -5757,10 +5721,10 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B64" s="2">
-        <v>0.426534116268158</v>
+        <v>0.4209920465946198</v>
       </c>
       <c r="C64" s="1">
         <v>556</v>
@@ -5786,7 +5750,7 @@
         <v>20</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4203969240188599</v>
+        <v>0.4149346053600311</v>
       </c>
       <c r="C65" s="1">
         <v>548</v>
@@ -5809,10 +5773,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4173283278942108</v>
+        <v>0.4119058847427368</v>
       </c>
       <c r="C66" s="1">
         <v>544</v>
@@ -5838,7 +5802,7 @@
         <v>2</v>
       </c>
       <c r="B67" s="2">
-        <v>0.3927796185016632</v>
+        <v>0.3876761496067047</v>
       </c>
       <c r="C67" s="1">
         <v>512</v>
@@ -5864,7 +5828,7 @@
         <v>11</v>
       </c>
       <c r="B68" s="2">
-        <v>0.3897110223770142</v>
+        <v>0.3846474289894104</v>
       </c>
       <c r="C68" s="1">
         <v>508</v>
@@ -5887,19 +5851,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
       <c r="B69" s="2">
-        <v>0.3866424262523651</v>
+        <v>0.3801043331623077</v>
       </c>
       <c r="C69" s="1">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D69" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
       <c r="E69" s="1">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -5908,47 +5872,47 @@
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>0</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3851081430912018</v>
+        <v>0.3801043331623077</v>
       </c>
       <c r="C70" s="1">
         <v>502</v>
       </c>
       <c r="D70" s="1">
-        <v>4096</v>
+        <v>4</v>
       </c>
       <c r="E70" s="1">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70" s="1">
-        <v>4096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3851081430912018</v>
+        <v>0.3770756125450134</v>
       </c>
       <c r="C71" s="1">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="D71" s="1">
-        <v>4</v>
+        <v>1031</v>
       </c>
       <c r="E71" s="1">
         <v>498</v>
@@ -5957,24 +5921,24 @@
         <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3820395469665527</v>
+        <v>0.3770756125450134</v>
       </c>
       <c r="C72" s="1">
         <v>498</v>
       </c>
       <c r="D72" s="1">
-        <v>1031</v>
+        <v>0</v>
       </c>
       <c r="E72" s="1">
         <v>498</v>
@@ -5986,24 +5950,24 @@
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>1031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3697651624679565</v>
+        <v>0.3679894506931305</v>
       </c>
       <c r="C73" s="1">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -6017,10 +5981,10 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3651622831821442</v>
+        <v>0.3604176640510559</v>
       </c>
       <c r="C74" s="1">
         <v>476</v>
@@ -6043,10 +6007,10 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3590251207351685</v>
+        <v>0.3543602228164673</v>
       </c>
       <c r="C75" s="1">
         <v>468</v>
@@ -6069,25 +6033,25 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="B76" s="2">
-        <v>0.3498193323612213</v>
+        <v>0.351331502199173</v>
       </c>
       <c r="C76" s="1">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="D76" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -6095,25 +6059,25 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="B77" s="2">
-        <v>0.348285049200058</v>
+        <v>0.3452740609645844</v>
       </c>
       <c r="C77" s="1">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D77" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E77" s="1">
-        <v>454</v>
+        <v>424</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
       </c>
       <c r="G77" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H77" s="1">
         <v>0</v>
@@ -6121,10 +6085,10 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B78" s="2">
-        <v>0.3436821699142456</v>
+        <v>0.3392166197299957</v>
       </c>
       <c r="C78" s="1">
         <v>448</v>
@@ -6147,10 +6111,10 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B79" s="2">
-        <v>0.3314077854156494</v>
+        <v>0.3271017372608185</v>
       </c>
       <c r="C79" s="1">
         <v>432</v>
@@ -6176,7 +6140,7 @@
         <v>45</v>
       </c>
       <c r="B80" s="2">
-        <v>0.326804906129837</v>
+        <v>0.3225586712360382</v>
       </c>
       <c r="C80" s="1">
         <v>426</v>
@@ -6199,22 +6163,22 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B81" s="2">
-        <v>0.3145305514335632</v>
+        <v>0.3225586712360382</v>
       </c>
       <c r="C81" s="1">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="F81" s="1">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
@@ -6225,10 +6189,10 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B82" s="2">
-        <v>0.3145305514335632</v>
+        <v>0.310443788766861</v>
       </c>
       <c r="C82" s="1">
         <v>410</v>
@@ -6237,10 +6201,10 @@
         <v>0</v>
       </c>
       <c r="E82" s="1">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="F82" s="1">
-        <v>410</v>
+        <v>80</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
@@ -6251,10 +6215,10 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B83" s="2">
-        <v>0.3129962384700775</v>
+        <v>0.3089294135570526</v>
       </c>
       <c r="C83" s="1">
         <v>408</v>
@@ -6277,10 +6241,10 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B84" s="2">
-        <v>0.3068590760231018</v>
+        <v>0.302871972322464</v>
       </c>
       <c r="C84" s="1">
         <v>400</v>
@@ -6303,10 +6267,10 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B85" s="2">
-        <v>0.3068590760231018</v>
+        <v>0.302871972322464</v>
       </c>
       <c r="C85" s="1">
         <v>400</v>
@@ -6329,22 +6293,22 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B86" s="2">
-        <v>0.2853789329528809</v>
+        <v>0.2922714650630951</v>
       </c>
       <c r="C86" s="1">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="F86" s="1">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G86" s="1">
         <v>0</v>
@@ -6355,22 +6319,22 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B87" s="2">
-        <v>0.2807760536670685</v>
+        <v>0.2816709578037262</v>
       </c>
       <c r="C87" s="1">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="F87" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G87" s="1">
         <v>0</v>
@@ -6381,19 +6345,19 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="B88" s="2">
-        <v>0.2638987898826599</v>
+        <v>0.2771278619766235</v>
       </c>
       <c r="C88" s="1">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="D88" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="E88" s="1">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="F88" s="1">
         <v>0</v>
@@ -6402,24 +6366,24 @@
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="B89" s="2">
-        <v>0.2577616274356842</v>
+        <v>0.260469913482666</v>
       </c>
       <c r="C89" s="1">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="D89" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="E89" s="1">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
@@ -6428,15 +6392,15 @@
         <v>0</v>
       </c>
       <c r="H89" s="1">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B90" s="2">
-        <v>0.2562273144721985</v>
+        <v>0.252898097038269</v>
       </c>
       <c r="C90" s="1">
         <v>334</v>
@@ -6462,7 +6426,7 @@
         <v>21</v>
       </c>
       <c r="B91" s="2">
-        <v>0.2546930313110352</v>
+        <v>0.2513837516307831</v>
       </c>
       <c r="C91" s="1">
         <v>332</v>
@@ -6485,10 +6449,10 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B92" s="2">
-        <v>0.2485558390617371</v>
+        <v>0.2453263103961945</v>
       </c>
       <c r="C92" s="1">
         <v>324</v>
@@ -6511,10 +6475,10 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B93" s="2">
-        <v>0.2362814843654633</v>
+        <v>0.2332114279270172</v>
       </c>
       <c r="C93" s="1">
         <v>308</v>
@@ -6537,10 +6501,10 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B94" s="2">
-        <v>0.2240071147680283</v>
+        <v>0.22109654545784</v>
       </c>
       <c r="C94" s="1">
         <v>292</v>
@@ -6566,7 +6530,7 @@
         <v>51</v>
       </c>
       <c r="B95" s="2">
-        <v>0.2086641639471054</v>
+        <v>0.2059529423713684</v>
       </c>
       <c r="C95" s="1">
         <v>272</v>
@@ -6589,10 +6553,10 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B96" s="2">
-        <v>0.2086641639471054</v>
+        <v>0.2059529423713684</v>
       </c>
       <c r="C96" s="1">
         <v>272</v>
@@ -6615,19 +6579,19 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="B97" s="2">
-        <v>0.1933212131261826</v>
+        <v>0.199895516037941</v>
       </c>
       <c r="C97" s="1">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D97" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="E97" s="1">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="F97" s="1">
         <v>0</v>
@@ -6636,105 +6600,105 @@
         <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
-        <v>111</v>
+        <v>26</v>
       </c>
       <c r="B98" s="2">
-        <v>0.1887183338403702</v>
+        <v>0.190809354186058</v>
       </c>
       <c r="C98" s="1">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="D98" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E98" s="1">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="F98" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G98" s="1">
         <v>0</v>
       </c>
       <c r="H98" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="B99" s="2">
-        <v>0.1856497377157211</v>
+        <v>0.1862662732601166</v>
       </c>
       <c r="C99" s="1">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D99" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="E99" s="1">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F99" s="1">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G99" s="1">
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="B100" s="2">
-        <v>0.1841154396533966</v>
+        <v>0.1832375526428223</v>
       </c>
       <c r="C100" s="1">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D100" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E100" s="1">
+        <v>242</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1">
+        <v>0</v>
+      </c>
+      <c r="H100" s="1">
         <v>224</v>
-      </c>
-      <c r="F100" s="1">
-        <v>16</v>
-      </c>
-      <c r="G100" s="1">
-        <v>0</v>
-      </c>
-      <c r="H100" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B101" s="2">
-        <v>0.1795125603675842</v>
+        <v>0.1817231923341751</v>
       </c>
       <c r="C101" s="1">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D101" s="1">
         <v>0</v>
       </c>
       <c r="E101" s="1">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="F101" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G101" s="1">
         <v>0</v>
@@ -6745,10 +6709,10 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B102" s="2">
-        <v>0.1779782623052597</v>
+        <v>0.1756657510995865</v>
       </c>
       <c r="C102" s="1">
         <v>232</v>
@@ -6771,10 +6735,10 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B103" s="2">
-        <v>0.1749096661806107</v>
+        <v>0.1726370304822922</v>
       </c>
       <c r="C103" s="1">
         <v>228</v>
@@ -6797,10 +6761,10 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B104" s="2">
-        <v>0.1749096661806107</v>
+        <v>0.1726370304822922</v>
       </c>
       <c r="C104" s="1">
         <v>228</v>
@@ -6823,10 +6787,10 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B105" s="2">
-        <v>0.1703067868947983</v>
+        <v>0.1680939495563507</v>
       </c>
       <c r="C105" s="1">
         <v>222</v>
@@ -6849,10 +6813,10 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B106" s="2">
-        <v>0.1687724888324738</v>
+        <v>0.1665795892477036</v>
       </c>
       <c r="C106" s="1">
         <v>220</v>
@@ -6875,45 +6839,45 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="B107" s="2">
-        <v>0.1687724888324738</v>
+        <v>0.1453785449266434</v>
       </c>
       <c r="C107" s="1">
-        <v>220</v>
+        <v>192</v>
       </c>
       <c r="D107" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E107" s="1">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F107" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G107" s="1">
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
-        <v>38</v>
+        <v>117</v>
       </c>
       <c r="B108" s="2">
-        <v>0.1472923457622528</v>
+        <v>0.1423498392105103</v>
       </c>
       <c r="C108" s="1">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D108" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E108" s="1">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F108" s="1">
         <v>0</v>
@@ -6922,24 +6886,24 @@
         <v>0</v>
       </c>
       <c r="H108" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B109" s="2">
-        <v>0.144223764538765</v>
+        <v>0.1408354789018631</v>
       </c>
       <c r="C109" s="1">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D109" s="1">
         <v>0</v>
       </c>
       <c r="E109" s="1">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F109" s="1">
         <v>0</v>
@@ -6953,19 +6917,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B110" s="2">
-        <v>0.1426894664764404</v>
+        <v>0.1332636773586273</v>
       </c>
       <c r="C110" s="1">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D110" s="1">
         <v>0</v>
       </c>
       <c r="E110" s="1">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="F110" s="1">
         <v>0</v>
@@ -6979,25 +6943,25 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="B111" s="2">
-        <v>0.135017991065979</v>
+        <v>0.130234956741333</v>
       </c>
       <c r="C111" s="1">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D111" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E111" s="1">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="F111" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G111" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -7005,19 +6969,19 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B112" s="2">
-        <v>0.135017991065979</v>
+        <v>0.1196344345808029</v>
       </c>
       <c r="C112" s="1">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
       </c>
       <c r="E112" s="1">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
@@ -7031,25 +6995,25 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="B113" s="2">
-        <v>0.13194939494133</v>
+        <v>0.1166057139635086</v>
       </c>
       <c r="C113" s="1">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="D113" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E113" s="1">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F113" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G113" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -7057,19 +7021,19 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B114" s="2">
-        <v>0.1212093308568001</v>
+        <v>0.1150913536548615</v>
       </c>
       <c r="C114" s="1">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
       </c>
       <c r="E114" s="1">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F114" s="1">
         <v>0</v>
@@ -7083,19 +7047,19 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B115" s="2">
-        <v>0.1181407421827316</v>
+        <v>0.1090339124202728</v>
       </c>
       <c r="C115" s="1">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
       </c>
       <c r="E115" s="1">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F115" s="1">
         <v>0</v>
@@ -7109,25 +7073,25 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="B116" s="2">
-        <v>0.1166064441204071</v>
+        <v>0.1075195521116257</v>
       </c>
       <c r="C116" s="1">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D116" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E116" s="1">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="F116" s="1">
         <v>0</v>
       </c>
       <c r="G116" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
@@ -7135,19 +7099,19 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B117" s="2">
-        <v>0.1104692667722702</v>
+        <v>0.1044908314943314</v>
       </c>
       <c r="C117" s="1">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D117" s="1">
         <v>0</v>
       </c>
       <c r="E117" s="1">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F117" s="1">
         <v>0</v>
@@ -7161,45 +7125,45 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B118" s="2">
-        <v>0.1089349687099457</v>
+        <v>0.1029764711856842</v>
       </c>
       <c r="C118" s="1">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D118" s="1">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="E118" s="1">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F118" s="1">
         <v>0</v>
       </c>
       <c r="G118" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H118" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B119" s="2">
-        <v>0.1058663800358772</v>
+        <v>0.09691903740167618</v>
       </c>
       <c r="C119" s="1">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
       </c>
       <c r="E119" s="1">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F119" s="1">
         <v>0</v>
@@ -7213,19 +7177,19 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="B120" s="2">
-        <v>0.1043320819735527</v>
+        <v>0.09691903740167618</v>
       </c>
       <c r="C120" s="1">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D120" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E120" s="1">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F120" s="1">
         <v>0</v>
@@ -7234,24 +7198,24 @@
         <v>0</v>
       </c>
       <c r="H120" s="1">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B121" s="2">
-        <v>0.0981949046254158</v>
+        <v>0.09540467709302902</v>
       </c>
       <c r="C121" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D121" s="1">
         <v>0</v>
       </c>
       <c r="E121" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F121" s="1">
         <v>0</v>
@@ -7265,19 +7229,19 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B122" s="2">
-        <v>0.0981949046254158</v>
+        <v>0.09540467709302902</v>
       </c>
       <c r="C122" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D122" s="1">
         <v>0</v>
       </c>
       <c r="E122" s="1">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F122" s="1">
         <v>0</v>
@@ -7291,19 +7255,19 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="B123" s="2">
-        <v>0.09666060656309128</v>
+        <v>0.09086159616708756</v>
       </c>
       <c r="C123" s="1">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D123" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E123" s="1">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F123" s="1">
         <v>0</v>
@@ -7312,24 +7276,24 @@
         <v>0</v>
       </c>
       <c r="H123" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B124" s="2">
-        <v>0.09666060656309128</v>
+        <v>0.08631851524114609</v>
       </c>
       <c r="C124" s="1">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D124" s="1">
         <v>0</v>
       </c>
       <c r="E124" s="1">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="F124" s="1">
         <v>0</v>
@@ -7343,25 +7307,25 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="B125" s="2">
-        <v>0.09666060656309128</v>
+        <v>0.08480415493249893</v>
       </c>
       <c r="C125" s="1">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D125" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E125" s="1">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F125" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G125" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
@@ -7369,19 +7333,19 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B126" s="2">
-        <v>0.0920577198266983</v>
+        <v>0.08480415493249893</v>
       </c>
       <c r="C126" s="1">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D126" s="1">
-        <v>128</v>
+        <v>720</v>
       </c>
       <c r="E126" s="1">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F126" s="1">
         <v>0</v>
@@ -7390,24 +7354,24 @@
         <v>0</v>
       </c>
       <c r="H126" s="1">
-        <v>128</v>
+        <v>720</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B127" s="2">
-        <v>0.08745483309030533</v>
+        <v>0.08480415493249893</v>
       </c>
       <c r="C127" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D127" s="1">
         <v>0</v>
       </c>
       <c r="E127" s="1">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F127" s="1">
         <v>0</v>
@@ -7421,10 +7385,10 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B128" s="2">
-        <v>0.0859205424785614</v>
+        <v>0.08480415493249893</v>
       </c>
       <c r="C128" s="1">
         <v>112</v>
@@ -7447,19 +7411,19 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="B129" s="2">
-        <v>0.0859205424785614</v>
+        <v>0.08328979462385178</v>
       </c>
       <c r="C129" s="1">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D129" s="1">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="E129" s="1">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F129" s="1">
         <v>0</v>
@@ -7468,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="H129" s="1">
-        <v>720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -7476,16 +7440,16 @@
         <v>134</v>
       </c>
       <c r="B130" s="2">
-        <v>0.0859205424785614</v>
+        <v>0.08177543431520462</v>
       </c>
       <c r="C130" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D130" s="1">
         <v>0</v>
       </c>
       <c r="E130" s="1">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F130" s="1">
         <v>0</v>
@@ -7502,16 +7466,16 @@
         <v>135</v>
       </c>
       <c r="B131" s="2">
-        <v>0.0859205424785614</v>
+        <v>0.07420363277196884</v>
       </c>
       <c r="C131" s="1">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D131" s="1">
         <v>0</v>
       </c>
       <c r="E131" s="1">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F131" s="1">
         <v>0</v>
@@ -7528,16 +7492,16 @@
         <v>136</v>
       </c>
       <c r="B132" s="2">
-        <v>0.08438624441623688</v>
+        <v>0.07420363277196884</v>
       </c>
       <c r="C132" s="1">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D132" s="1">
         <v>0</v>
       </c>
       <c r="E132" s="1">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F132" s="1">
         <v>0</v>
@@ -7554,16 +7518,16 @@
         <v>137</v>
       </c>
       <c r="B133" s="2">
-        <v>0.08285194635391235</v>
+        <v>0.06966055929660797</v>
       </c>
       <c r="C133" s="1">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D133" s="1">
         <v>0</v>
       </c>
       <c r="E133" s="1">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="F133" s="1">
         <v>0</v>
@@ -7580,16 +7544,16 @@
         <v>138</v>
       </c>
       <c r="B134" s="2">
-        <v>0.07518047094345093</v>
+        <v>0.0651174783706665</v>
       </c>
       <c r="C134" s="1">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D134" s="1">
         <v>0</v>
       </c>
       <c r="E134" s="1">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F134" s="1">
         <v>0</v>
@@ -7606,16 +7570,16 @@
         <v>139</v>
       </c>
       <c r="B135" s="2">
-        <v>0.07518047094345093</v>
+        <v>0.06360311806201935</v>
       </c>
       <c r="C135" s="1">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D135" s="1">
         <v>0</v>
       </c>
       <c r="E135" s="1">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F135" s="1">
         <v>0</v>
@@ -7632,16 +7596,16 @@
         <v>140</v>
       </c>
       <c r="B136" s="2">
-        <v>0.07057758420705795</v>
+        <v>0.06360311806201935</v>
       </c>
       <c r="C136" s="1">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D136" s="1">
         <v>0</v>
       </c>
       <c r="E136" s="1">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F136" s="1">
         <v>0</v>
@@ -7658,16 +7622,16 @@
         <v>141</v>
       </c>
       <c r="B137" s="2">
-        <v>0.06597469747066498</v>
+        <v>0.06360311806201935</v>
       </c>
       <c r="C137" s="1">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D137" s="1">
         <v>0</v>
       </c>
       <c r="E137" s="1">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F137" s="1">
         <v>0</v>
@@ -7681,25 +7645,25 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
-        <v>142</v>
+        <v>53</v>
       </c>
       <c r="B138" s="2">
-        <v>0.06444040685892105</v>
+        <v>0.06360311806201935</v>
       </c>
       <c r="C138" s="1">
         <v>84</v>
       </c>
       <c r="D138" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E138" s="1">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="F138" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G138" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H138" s="1">
         <v>0</v>
@@ -7707,19 +7671,19 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B139" s="2">
-        <v>0.06444040685892105</v>
+        <v>0.06057439744472504</v>
       </c>
       <c r="C139" s="1">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D139" s="1">
         <v>0</v>
       </c>
       <c r="E139" s="1">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F139" s="1">
         <v>0</v>
@@ -7733,19 +7697,19 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B140" s="2">
-        <v>0.06444040685892105</v>
+        <v>0.05906003713607788</v>
       </c>
       <c r="C140" s="1">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D140" s="1">
         <v>0</v>
       </c>
       <c r="E140" s="1">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F140" s="1">
         <v>0</v>
@@ -7759,45 +7723,45 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="B141" s="2">
-        <v>0.06444040685892105</v>
+        <v>0.05754567682743073</v>
       </c>
       <c r="C141" s="1">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D141" s="1">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E141" s="1">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="F141" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G141" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H141" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B142" s="2">
-        <v>0.06290610879659653</v>
+        <v>0.05451695621013641</v>
       </c>
       <c r="C142" s="1">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D142" s="1">
         <v>0</v>
       </c>
       <c r="E142" s="1">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F142" s="1">
         <v>0</v>
@@ -7811,19 +7775,19 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B143" s="2">
-        <v>0.0613718144595623</v>
+        <v>0.04997387900948525</v>
       </c>
       <c r="C143" s="1">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D143" s="1">
         <v>0</v>
       </c>
       <c r="E143" s="1">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F143" s="1">
         <v>0</v>
@@ -7837,19 +7801,19 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B144" s="2">
-        <v>0.05983751639723778</v>
+        <v>0.04543079808354378</v>
       </c>
       <c r="C144" s="1">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D144" s="1">
         <v>0</v>
       </c>
       <c r="E144" s="1">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F144" s="1">
         <v>0</v>
@@ -7863,19 +7827,19 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="B145" s="2">
-        <v>0.05830322206020355</v>
+        <v>0.04543079808354378</v>
       </c>
       <c r="C145" s="1">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D145" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E145" s="1">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F145" s="1">
         <v>0</v>
@@ -7884,7 +7848,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -7892,16 +7856,16 @@
         <v>148</v>
       </c>
       <c r="B146" s="2">
-        <v>0.05063174664974213</v>
+        <v>0.04391643777489662</v>
       </c>
       <c r="C146" s="1">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D146" s="1">
         <v>0</v>
       </c>
       <c r="E146" s="1">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F146" s="1">
         <v>0</v>
@@ -7918,16 +7882,16 @@
         <v>149</v>
       </c>
       <c r="B147" s="2">
-        <v>0.04602885991334915</v>
+        <v>0.04088771715760231</v>
       </c>
       <c r="C147" s="1">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D147" s="1">
         <v>0</v>
       </c>
       <c r="E147" s="1">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F147" s="1">
         <v>0</v>
@@ -7941,25 +7905,25 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="1" t="s">
-        <v>150</v>
+        <v>46</v>
       </c>
       <c r="B148" s="2">
-        <v>0.04602885991334915</v>
+        <v>0.04088771715760231</v>
       </c>
       <c r="C148" s="1">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D148" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E148" s="1">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="F148" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G148" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H148" s="1">
         <v>0</v>
@@ -7967,19 +7931,19 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B149" s="2">
-        <v>0.04602885991334915</v>
+        <v>0.03937335684895515</v>
       </c>
       <c r="C149" s="1">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D149" s="1">
         <v>0</v>
       </c>
       <c r="E149" s="1">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F149" s="1">
         <v>0</v>
@@ -7993,19 +7957,19 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B150" s="2">
-        <v>0.04449456557631493</v>
+        <v>0.037858996540308</v>
       </c>
       <c r="C150" s="1">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D150" s="1">
         <v>0</v>
       </c>
       <c r="E150" s="1">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F150" s="1">
         <v>0</v>
@@ -8019,19 +7983,19 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B151" s="2">
-        <v>0.04142597317695618</v>
+        <v>0.03634463623166084</v>
       </c>
       <c r="C151" s="1">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D151" s="1">
         <v>0</v>
       </c>
       <c r="E151" s="1">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F151" s="1">
         <v>0</v>
@@ -8045,25 +8009,25 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="1" t="s">
-        <v>46</v>
+        <v>153</v>
       </c>
       <c r="B152" s="2">
-        <v>0.04142597317695618</v>
+        <v>0.03634463623166084</v>
       </c>
       <c r="C152" s="1">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D152" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E152" s="1">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F152" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G152" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
@@ -8074,16 +8038,16 @@
         <v>154</v>
       </c>
       <c r="B153" s="2">
-        <v>0.03989167883992195</v>
+        <v>0.03634463623166084</v>
       </c>
       <c r="C153" s="1">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D153" s="1">
         <v>0</v>
       </c>
       <c r="E153" s="1">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F153" s="1">
         <v>0</v>
@@ -8100,16 +8064,16 @@
         <v>155</v>
       </c>
       <c r="B154" s="2">
-        <v>0.03835738450288773</v>
+        <v>0.03331591933965683</v>
       </c>
       <c r="C154" s="1">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D154" s="1">
         <v>0</v>
       </c>
       <c r="E154" s="1">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F154" s="1">
         <v>0</v>
@@ -8126,16 +8090,16 @@
         <v>156</v>
       </c>
       <c r="B155" s="2">
-        <v>0.0368230864405632</v>
+        <v>0.03331591933965683</v>
       </c>
       <c r="C155" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D155" s="1">
         <v>0</v>
       </c>
       <c r="E155" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F155" s="1">
         <v>0</v>
@@ -8149,25 +8113,25 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="1" t="s">
-        <v>157</v>
+        <v>49</v>
       </c>
       <c r="B156" s="2">
-        <v>0.0368230864405632</v>
+        <v>0.03331591933965683</v>
       </c>
       <c r="C156" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D156" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E156" s="1">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="F156" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G156" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H156" s="1">
         <v>0</v>
@@ -8175,19 +8139,19 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B157" s="2">
-        <v>0.0368230864405632</v>
+        <v>0.03331591933965683</v>
       </c>
       <c r="C157" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D157" s="1">
         <v>0</v>
       </c>
       <c r="E157" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F157" s="1">
         <v>0</v>
@@ -8201,10 +8165,10 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B158" s="2">
-        <v>0.03375449776649475</v>
+        <v>0.03331591933965683</v>
       </c>
       <c r="C158" s="1">
         <v>44</v>
@@ -8227,19 +8191,19 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B159" s="2">
-        <v>0.03375449776649475</v>
+        <v>0.03028719872236252</v>
       </c>
       <c r="C159" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D159" s="1">
         <v>0</v>
       </c>
       <c r="E159" s="1">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F159" s="1">
         <v>0</v>
@@ -8253,25 +8217,25 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="1" t="s">
-        <v>49</v>
+        <v>160</v>
       </c>
       <c r="B160" s="2">
-        <v>0.03375449776649475</v>
+        <v>0.02877283841371536</v>
       </c>
       <c r="C160" s="1">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D160" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E160" s="1">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F160" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G160" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H160" s="1">
         <v>0</v>
@@ -8282,16 +8246,16 @@
         <v>161</v>
       </c>
       <c r="B161" s="2">
-        <v>0.03375449776649475</v>
+        <v>0.02877283841371536</v>
       </c>
       <c r="C161" s="1">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D161" s="1">
         <v>0</v>
       </c>
       <c r="E161" s="1">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F161" s="1">
         <v>0</v>
@@ -8308,16 +8272,16 @@
         <v>162</v>
       </c>
       <c r="B162" s="2">
-        <v>0.03375449776649475</v>
+        <v>0.02725847810506821</v>
       </c>
       <c r="C162" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D162" s="1">
         <v>0</v>
       </c>
       <c r="E162" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F162" s="1">
         <v>0</v>
@@ -8334,16 +8298,16 @@
         <v>163</v>
       </c>
       <c r="B163" s="2">
-        <v>0.03068590722978115</v>
+        <v>0.02725847810506821</v>
       </c>
       <c r="C163" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D163" s="1">
         <v>0</v>
       </c>
       <c r="E163" s="1">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F163" s="1">
         <v>0</v>
@@ -8360,16 +8324,16 @@
         <v>164</v>
       </c>
       <c r="B164" s="2">
-        <v>0.02915161103010178</v>
+        <v>0.02725847810506821</v>
       </c>
       <c r="C164" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D164" s="1">
         <v>0</v>
       </c>
       <c r="E164" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F164" s="1">
         <v>0</v>
@@ -8386,16 +8350,16 @@
         <v>165</v>
       </c>
       <c r="B165" s="2">
-        <v>0.02915161103010178</v>
+        <v>0.02725847810506821</v>
       </c>
       <c r="C165" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D165" s="1">
         <v>0</v>
       </c>
       <c r="E165" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F165" s="1">
         <v>0</v>
@@ -8412,16 +8376,16 @@
         <v>166</v>
       </c>
       <c r="B166" s="2">
-        <v>0.02761731669306755</v>
+        <v>0.02422975935041904</v>
       </c>
       <c r="C166" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D166" s="1">
         <v>0</v>
       </c>
       <c r="E166" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F166" s="1">
         <v>0</v>
@@ -8438,16 +8402,16 @@
         <v>167</v>
       </c>
       <c r="B167" s="2">
-        <v>0.02761731669306755</v>
+        <v>0.02422975935041904</v>
       </c>
       <c r="C167" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D167" s="1">
         <v>0</v>
       </c>
       <c r="E167" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F167" s="1">
         <v>0</v>
@@ -8464,16 +8428,16 @@
         <v>168</v>
       </c>
       <c r="B168" s="2">
-        <v>0.02761731669306755</v>
+        <v>0.02422975935041904</v>
       </c>
       <c r="C168" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D168" s="1">
         <v>0</v>
       </c>
       <c r="E168" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F168" s="1">
         <v>0</v>
@@ -8490,16 +8454,16 @@
         <v>169</v>
       </c>
       <c r="B169" s="2">
-        <v>0.02761731669306755</v>
+        <v>0.02422975935041904</v>
       </c>
       <c r="C169" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D169" s="1">
         <v>0</v>
       </c>
       <c r="E169" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F169" s="1">
         <v>0</v>
@@ -8516,7 +8480,7 @@
         <v>170</v>
       </c>
       <c r="B170" s="2">
-        <v>0.02454872615635395</v>
+        <v>0.02422975935041904</v>
       </c>
       <c r="C170" s="1">
         <v>32</v>
@@ -8542,16 +8506,16 @@
         <v>171</v>
       </c>
       <c r="B171" s="2">
-        <v>0.02454872615635395</v>
+        <v>0.02271539904177189</v>
       </c>
       <c r="C171" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D171" s="1">
         <v>0</v>
       </c>
       <c r="E171" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F171" s="1">
         <v>0</v>
@@ -8568,16 +8532,16 @@
         <v>172</v>
       </c>
       <c r="B172" s="2">
-        <v>0.02454872615635395</v>
+        <v>0.02271539904177189</v>
       </c>
       <c r="C172" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D172" s="1">
         <v>0</v>
       </c>
       <c r="E172" s="1">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F172" s="1">
         <v>0</v>
@@ -8594,16 +8558,16 @@
         <v>173</v>
       </c>
       <c r="B173" s="2">
-        <v>0.02454872615635395</v>
+        <v>0.01968667842447758</v>
       </c>
       <c r="C173" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D173" s="1">
         <v>0</v>
       </c>
       <c r="E173" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F173" s="1">
         <v>0</v>
@@ -8620,16 +8584,16 @@
         <v>174</v>
       </c>
       <c r="B174" s="2">
-        <v>0.02454872615635395</v>
+        <v>0.01968667842447758</v>
       </c>
       <c r="C174" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D174" s="1">
         <v>0</v>
       </c>
       <c r="E174" s="1">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F174" s="1">
         <v>0</v>
@@ -8646,16 +8610,16 @@
         <v>175</v>
       </c>
       <c r="B175" s="2">
-        <v>0.02301442995667458</v>
+        <v>0.01817231811583042</v>
       </c>
       <c r="C175" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D175" s="1">
         <v>0</v>
       </c>
       <c r="E175" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F175" s="1">
         <v>0</v>
@@ -8672,16 +8636,16 @@
         <v>176</v>
       </c>
       <c r="B176" s="2">
-        <v>0.02301442995667458</v>
+        <v>0.01817231811583042</v>
       </c>
       <c r="C176" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D176" s="1">
         <v>0</v>
       </c>
       <c r="E176" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F176" s="1">
         <v>0</v>
@@ -8695,25 +8659,25 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="1" t="s">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="B177" s="2">
-        <v>0.01994583941996098</v>
+        <v>0.01211487967520952</v>
       </c>
       <c r="C177" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D177" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E177" s="1">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F177" s="1">
         <v>0</v>
       </c>
       <c r="G177" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
@@ -8721,19 +8685,19 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B178" s="2">
-        <v>0.01994583941996098</v>
+        <v>0.006057439837604761</v>
       </c>
       <c r="C178" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D178" s="1">
         <v>0</v>
       </c>
       <c r="E178" s="1">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1">
         <v>0</v>
@@ -8747,19 +8711,19 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B179" s="2">
-        <v>0.0184115432202816</v>
+        <v>0.006057439837604761</v>
       </c>
       <c r="C179" s="1">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D179" s="1">
         <v>0</v>
       </c>
       <c r="E179" s="1">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1">
         <v>0</v>
@@ -8773,19 +8737,19 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B180" s="2">
-        <v>0.0184115432202816</v>
+        <v>0.003028719918802381</v>
       </c>
       <c r="C180" s="1">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D180" s="1">
         <v>0</v>
       </c>
       <c r="E180" s="1">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1">
         <v>0</v>
@@ -8799,19 +8763,19 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B181" s="2">
-        <v>0.01227436307817698</v>
+        <v>0.003028719918802381</v>
       </c>
       <c r="C181" s="1">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D181" s="1">
         <v>4</v>
       </c>
       <c r="E181" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F181" s="1">
         <v>0</v>
@@ -8825,19 +8789,19 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B182" s="2">
-        <v>0.006137181539088488</v>
+        <v>0.003028719918802381</v>
       </c>
       <c r="C182" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D182" s="1">
         <v>0</v>
       </c>
       <c r="E182" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1">
         <v>0</v>
@@ -8851,19 +8815,19 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B183" s="2">
-        <v>0.006137181539088488</v>
+        <v>0.003028719918802381</v>
       </c>
       <c r="C183" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D183" s="1">
         <v>0</v>
       </c>
       <c r="E183" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1">
         <v>0</v>
@@ -8876,138 +8840,34 @@
       </c>
     </row>
     <row r="184" spans="1:8">
-      <c r="A184" s="1" t="s">
+      <c r="A184" t="s">
         <v>183</v>
       </c>
-      <c r="B184" s="2">
-        <v>0.003068590769544244</v>
-      </c>
-      <c r="C184" s="1">
-        <v>4</v>
-      </c>
-      <c r="D184" s="1">
-        <v>0</v>
-      </c>
-      <c r="E184" s="1">
-        <v>4</v>
-      </c>
-      <c r="F184" s="1">
-        <v>0</v>
-      </c>
-      <c r="G184" s="1">
-        <v>0</v>
-      </c>
-      <c r="H184" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8">
-      <c r="A185" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B185" s="2">
-        <v>0.003068590769544244</v>
-      </c>
-      <c r="C185" s="1">
-        <v>4</v>
-      </c>
-      <c r="D185" s="1">
-        <v>4</v>
-      </c>
-      <c r="E185" s="1">
-        <v>0</v>
-      </c>
-      <c r="F185" s="1">
-        <v>0</v>
-      </c>
-      <c r="G185" s="1">
-        <v>4</v>
-      </c>
-      <c r="H185" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8">
-      <c r="A186" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B186" s="2">
-        <v>0.003068590769544244</v>
-      </c>
-      <c r="C186" s="1">
-        <v>4</v>
-      </c>
-      <c r="D186" s="1">
-        <v>0</v>
-      </c>
-      <c r="E186" s="1">
-        <v>4</v>
-      </c>
-      <c r="F186" s="1">
-        <v>0</v>
-      </c>
-      <c r="G186" s="1">
-        <v>0</v>
-      </c>
-      <c r="H186" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8">
-      <c r="A187" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B187" s="2">
-        <v>0.003068590769544244</v>
-      </c>
-      <c r="C187" s="1">
-        <v>4</v>
-      </c>
-      <c r="D187" s="1">
-        <v>0</v>
-      </c>
-      <c r="E187" s="1">
-        <v>4</v>
-      </c>
-      <c r="F187" s="1">
-        <v>0</v>
-      </c>
-      <c r="G187" s="1">
-        <v>0</v>
-      </c>
-      <c r="H187" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8">
-      <c r="A188" t="s">
-        <v>187</v>
-      </c>
-      <c r="B188">
+      <c r="B184">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C188">
+      <c r="C184">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D188">
+      <c r="D184">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E188">
+      <c r="E184">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F188">
+      <c r="F184">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G188">
+      <c r="G184">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H188">
+      <c r="H184">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
+++ b/Board/V1/MDK-ARM/JointMotorApp_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="193">
   <si>
     <t>JointMotorApp</t>
   </si>
@@ -185,12 +185,12 @@
     <t>motor_info.o</t>
   </si>
   <si>
+    <t>m_wm.l</t>
+  </si>
+  <si>
     <t>jm_proto.o</t>
   </si>
   <si>
-    <t>m_wm.l</t>
-  </si>
-  <si>
     <t>stm32g4xx_hal_adc.o</t>
   </si>
   <si>
@@ -260,6 +260,9 @@
     <t>foc_core.o</t>
   </si>
   <si>
+    <t>ctrl_transition_mgr.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_hal_dma.o</t>
   </si>
   <si>
@@ -290,33 +293,33 @@
     <t>foc_decoupling.o</t>
   </si>
   <si>
+    <t>motor_control.o</t>
+  </si>
+  <si>
     <t>crc16.o</t>
   </si>
   <si>
-    <t>motor_control.o</t>
+    <t>dev_motor.o</t>
   </si>
   <si>
     <t>motor_info_calib.o</t>
   </si>
   <si>
-    <t>ctrl_transition_mgr.o</t>
+    <t>stm32g4xx_hal_gpio.o</t>
   </si>
   <si>
     <t>stm32g4xx_hal_flash_ex.o</t>
   </si>
   <si>
-    <t>stm32g4xx_hal_gpio.o</t>
-  </si>
-  <si>
     <t>calib_ac_injection.o</t>
   </si>
   <si>
+    <t>drv_gpio.o</t>
+  </si>
+  <si>
     <t>log10f.o</t>
   </si>
   <si>
-    <t>dev_motor.o</t>
-  </si>
-  <si>
     <t>dev_config.o</t>
   </si>
   <si>
@@ -335,6 +338,9 @@
     <t>pid_core.o</t>
   </si>
   <si>
+    <t>cosf.o</t>
+  </si>
+  <si>
     <t>dadd.o</t>
   </si>
   <si>
@@ -347,18 +353,15 @@
     <t>gpio.o</t>
   </si>
   <si>
+    <t>drv_adc.o</t>
+  </si>
+  <si>
+    <t>drv_i2c.o</t>
+  </si>
+  <si>
     <t>main.o</t>
   </si>
   <si>
-    <t>drv_adc.o</t>
-  </si>
-  <si>
-    <t>drv_i2c.o</t>
-  </si>
-  <si>
-    <t>drv_gpio.o</t>
-  </si>
-  <si>
     <t>dmul.o</t>
   </si>
   <si>
@@ -368,6 +371,9 @@
     <t>stm32g4xx_hal_pwr_ex.o</t>
   </si>
   <si>
+    <t>motor_mode_profile_velocity.o</t>
+  </si>
+  <si>
     <t>stm32g4xx_it.o</t>
   </si>
   <si>
@@ -444,9 +450,6 @@
   </si>
   <si>
     <t>funder.o</t>
-  </si>
-  <si>
-    <t>motor_mode_profile_velocity.o</t>
   </si>
   <si>
     <t>control_irq.o</t>
@@ -680,9 +683,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$184</c:f>
+              <c:f>ram_percent!$A$3:$A$185</c:f>
               <c:strCache>
-                <c:ptCount val="182"/>
+                <c:ptCount val="183"/>
                 <c:pt idx="0">
                   <c:v>motor_observer.o</c:v>
                 </c:pt>
@@ -845,7 +848,7 @@
                 <c:pt idx="53">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
-                <c:pt idx="181">
+                <c:pt idx="182">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -853,173 +856,173 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$184</c:f>
+              <c:f>ram_percent!$B$3:$B$185</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="182"/>
+                <c:ptCount val="183"/>
                 <c:pt idx="0">
-                  <c:v>36.17101287841797</c:v>
+                  <c:v>36.13472747802734</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.60602951049805</c:v>
+                  <c:v>20.58535766601563</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.61767864227295</c:v>
+                  <c:v>12.7053394317627</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.141465663909912</c:v>
+                  <c:v>5.136307716369629</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.141465663909912</c:v>
+                  <c:v>5.136307716369629</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.709662914276123</c:v>
+                  <c:v>4.704938411712647</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.630984306335449</c:v>
+                  <c:v>2.628345012664795</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.565711736679077</c:v>
+                  <c:v>2.563138008117676</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.068636655807495</c:v>
+                  <c:v>2.066561222076416</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.294153094291687</c:v>
+                  <c:v>1.29285478591919</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.285366415977478</c:v>
+                  <c:v>1.284076929092407</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9037732481956482</c:v>
+                  <c:v>0.9028666019439697</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.5020962357521057</c:v>
+                  <c:v>0.5015925765037537</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.4468656778335571</c:v>
+                  <c:v>0.446417361497879</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.4267818033695221</c:v>
+                  <c:v>0.4263536632061005</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.3765721917152405</c:v>
+                  <c:v>0.3761944174766541</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.3364045023918152</c:v>
+                  <c:v>0.3360670208930969</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2861948609352112</c:v>
+                  <c:v>0.2859077453613281</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.2811739146709442</c:v>
+                  <c:v>0.2808918356895447</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.2560690939426422</c:v>
+                  <c:v>0.2558121979236603</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.2510481178760529</c:v>
+                  <c:v>0.2507962882518768</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.1707127243280411</c:v>
+                  <c:v>0.1705414652824402</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.1656917631626129</c:v>
+                  <c:v>0.1655255407094955</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.1606708019971848</c:v>
+                  <c:v>0.1605096161365509</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.1255240589380264</c:v>
+                  <c:v>0.1253981441259384</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.1054402142763138</c:v>
+                  <c:v>0.1053344383835793</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.09539828449487686</c:v>
+                  <c:v>0.09530258923768997</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.0903773233294487</c:v>
+                  <c:v>0.09028665721416473</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.0903773233294487</c:v>
+                  <c:v>0.09028665721416473</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.0903773233294487</c:v>
+                  <c:v>0.09028665721416473</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.08535636216402054</c:v>
+                  <c:v>0.08527073264122009</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.08033540099859238</c:v>
+                  <c:v>0.08025480806827545</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.05523058772087097</c:v>
+                  <c:v>0.05517518147826195</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.05020962655544281</c:v>
+                  <c:v>0.05015925690531731</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.04518866166472435</c:v>
+                  <c:v>0.04514332860708237</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.04518866166472435</c:v>
+                  <c:v>0.04514332860708237</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.04016770049929619</c:v>
+                  <c:v>0.04012740403413773</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.04016770049929619</c:v>
+                  <c:v>0.04012740403413773</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.02510481327772141</c:v>
+                  <c:v>0.02507962845265865</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.02510481327772141</c:v>
+                  <c:v>0.02507962845265865</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.01506288722157478</c:v>
+                  <c:v>0.01504777651280165</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.01506288722157478</c:v>
+                  <c:v>0.01504777651280165</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.01506288722157478</c:v>
+                  <c:v>0.01504777651280165</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.01004192512482405</c:v>
+                  <c:v>0.01003185100853443</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.01004192512482405</c:v>
+                  <c:v>0.01003185100853443</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.01004192512482405</c:v>
+                  <c:v>0.01003185100853443</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.005020962562412024</c:v>
+                  <c:v>0.005015925504267216</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.005020962562412024</c:v>
+                  <c:v>0.005015925504267216</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.005020962562412024</c:v>
+                  <c:v>0.005015925504267216</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.005020962562412024</c:v>
+                  <c:v>0.005015925504267216</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.005020962562412024</c:v>
+                  <c:v>0.005015925504267216</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.005020962562412024</c:v>
+                  <c:v>0.005015925504267216</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.005020962562412024</c:v>
+                  <c:v>0.005015925504267216</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.003765721805393696</c:v>
-                </c:pt>
-                <c:pt idx="181">
+                  <c:v>0.003761944128200412</c:v>
+                </c:pt>
+                <c:pt idx="182">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1087,9 +1090,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$184</c:f>
+              <c:f>flash_percent!$A$3:$A$185</c:f>
               <c:strCache>
-                <c:ptCount val="182"/>
+                <c:ptCount val="183"/>
                 <c:pt idx="0">
                   <c:v>jm_proto_ops.o</c:v>
                 </c:pt>
@@ -1100,10 +1103,10 @@
                   <c:v>calib_level2_motor.o</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>m_wm.l</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>jm_proto.o</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>m_wm.l</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>stm32g4xx_hal_adc.o</c:v>
@@ -1121,10 +1124,10 @@
                   <c:v>mc_w.l</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>calib_level6_system.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>motor_observer.o</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>calib_level6_system.o</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>stm32g4xx_hal_fdcan.o</c:v>
@@ -1175,13 +1178,13 @@
                   <c:v>queue.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>ctrl_transition.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>calib_config_runtime.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>motor_pid_profile.o</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>ctrl_transition.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>stm32g4xx_hal_spi.o</c:v>
@@ -1202,438 +1205,441 @@
                   <c:v>drv_can.o</c:v>
                 </c:pt>
                 <c:pt idx="37">
+                  <c:v>drv_flash_g4.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>calib_level3_encoder.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>motor_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>calib_mgr.o</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>motor_mode_load_sim.o</c:v>
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>motor_pid_load.o</c:v>
                 </c:pt>
                 <c:pt idx="42">
+                  <c:v>motor_mode_load_sim.o</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>foc_core.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>calib_level5_nonlinear.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
-                  <c:v>drv_flash_g4.o</c:v>
-                </c:pt>
                 <c:pt idx="45">
+                  <c:v>ctrl_transition_mgr.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>stm32g4xx_hal_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
                   <c:v>motor_info_storage.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="48">
                   <c:v>current_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="49">
                   <c:v>dev_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="50">
                   <c:v>multiturn_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="51">
                   <c:v>dev_commun_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="52">
                   <c:v>port.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="53">
                   <c:v>stm32g4xx_hal_rcc_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="54">
                   <c:v>tim.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="55">
                   <c:v>motor_profile.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="56">
                   <c:v>stm32g4xx_hal_tim_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="57">
                   <c:v>dev_eeprom.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="58">
                   <c:v>dev_half_bridge.o</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>drv_usart.o</c:v>
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>cascade_control.o</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>drv_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>foc_decoupling.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="62">
+                  <c:v>motor_control.o</c:v>
+                </c:pt>
+                <c:pt idx="63">
                   <c:v>crc16.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="64">
                   <c:v>adc.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
-                  <c:v>motor_control.o</c:v>
-                </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="65">
+                  <c:v>dev_motor.o</c:v>
+                </c:pt>
+                <c:pt idx="66">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="67">
                   <c:v>startup_stm32g474xx.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="68">
                   <c:v>dev_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="69">
                   <c:v>calib_hw.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="70">
                   <c:v>packer_parser.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="71">
                   <c:v>motor_info_calib.o</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>ctrl_transition_mgr.o</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>stm32g4xx_hal_flash_ex.o</c:v>
                 </c:pt>
                 <c:pt idx="72">
                   <c:v>stm32g4xx_hal_gpio.o</c:v>
                 </c:pt>
                 <c:pt idx="73">
+                  <c:v>stm32g4xx_hal_flash_ex.o</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>calib_ac_injection.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="75">
+                  <c:v>drv_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="76">
                   <c:v>stm32g4xx_hal_flash.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="77">
                   <c:v>log10f.o</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>dev_motor.o</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>led_manager.o</c:v>
                 </c:pt>
                 <c:pt idx="78">
                   <c:v>dev_config.o</c:v>
                 </c:pt>
                 <c:pt idx="79">
+                  <c:v>led_manager.o</c:v>
+                </c:pt>
+                <c:pt idx="80">
                   <c:v>drv_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="80">
+                <c:pt idx="81">
                   <c:v>calib_level7_auto.o</c:v>
                 </c:pt>
-                <c:pt idx="81">
+                <c:pt idx="82">
                   <c:v>sinf.o</c:v>
                 </c:pt>
-                <c:pt idx="82">
+                <c:pt idx="83">
                   <c:v>dev_led.o</c:v>
                 </c:pt>
-                <c:pt idx="83">
+                <c:pt idx="84">
                   <c:v>drv_spi.o</c:v>
                 </c:pt>
-                <c:pt idx="84">
+                <c:pt idx="85">
                   <c:v>rredf.o</c:v>
                 </c:pt>
-                <c:pt idx="85">
+                <c:pt idx="86">
                   <c:v>pid_core.o</c:v>
                 </c:pt>
-                <c:pt idx="86">
+                <c:pt idx="87">
                   <c:v>usart.o</c:v>
                 </c:pt>
-                <c:pt idx="87">
+                <c:pt idx="88">
+                  <c:v>cosf.o</c:v>
+                </c:pt>
+                <c:pt idx="89">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="88">
+                <c:pt idx="90">
                   <c:v>spi.o</c:v>
                 </c:pt>
-                <c:pt idx="89">
+                <c:pt idx="91">
                   <c:v>cmsis_os.o</c:v>
                 </c:pt>
-                <c:pt idx="90">
+                <c:pt idx="92">
                   <c:v>stm32g4xx_hal_uart_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="91">
+                <c:pt idx="93">
                   <c:v>dev_encoder_mt6835.o</c:v>
                 </c:pt>
-                <c:pt idx="92">
+                <c:pt idx="94">
                   <c:v>jm_proto_uart.o</c:v>
                 </c:pt>
-                <c:pt idx="93">
+                <c:pt idx="95">
                   <c:v>gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="94">
+                <c:pt idx="96">
+                  <c:v>i2c.o</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>drv_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>drv_rtos.o</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>drv_i2c.o</c:v>
+                </c:pt>
+                <c:pt idx="100">
                   <c:v>main.o</c:v>
                 </c:pt>
-                <c:pt idx="95">
-                  <c:v>i2c.o</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>drv_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>drv_rtos.o</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>drv_i2c.o</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>drv_gpio.o</c:v>
-                </c:pt>
-                <c:pt idx="100">
+                <c:pt idx="101">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="101">
+                <c:pt idx="102">
                   <c:v>fdcan.o</c:v>
                 </c:pt>
-                <c:pt idx="102">
+                <c:pt idx="103">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="103">
+                <c:pt idx="104">
                   <c:v>stm32g4xx_hal_pwr_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="104">
+                <c:pt idx="105">
+                  <c:v>motor_mode_profile_velocity.o</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>thread_management.o</c:v>
                 </c:pt>
-                <c:pt idx="105">
+                <c:pt idx="107">
                   <c:v>stm32g4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="106">
+                <c:pt idx="108">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="107">
+                <c:pt idx="109">
                   <c:v>stm32g4xx_hal_i2c_ex.o</c:v>
                 </c:pt>
-                <c:pt idx="108">
+                <c:pt idx="110">
                   <c:v>calib_level1_driver.o</c:v>
                 </c:pt>
-                <c:pt idx="109">
+                <c:pt idx="111">
                   <c:v>stm32g4xx_hal_cortex.o</c:v>
                 </c:pt>
-                <c:pt idx="110">
+                <c:pt idx="112">
                   <c:v>roundf.o</c:v>
                 </c:pt>
-                <c:pt idx="111">
+                <c:pt idx="113">
                   <c:v>arm_cos_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="112">
+                <c:pt idx="114">
                   <c:v>arm_sin_f32.o</c:v>
                 </c:pt>
-                <c:pt idx="113">
+                <c:pt idx="115">
                   <c:v>stm32g4xx_hal.o</c:v>
                 </c:pt>
-                <c:pt idx="114">
+                <c:pt idx="116">
                   <c:v>list.o</c:v>
                 </c:pt>
-                <c:pt idx="115">
+                <c:pt idx="117">
                   <c:v>stm32g4xx_hal_timebase_tim.o</c:v>
                 </c:pt>
-                <c:pt idx="116">
+                <c:pt idx="118">
                   <c:v>thread_period.o</c:v>
                 </c:pt>
-                <c:pt idx="117">
+                <c:pt idx="119">
                   <c:v>motor_mode_mit.o</c:v>
                 </c:pt>
-                <c:pt idx="118">
+                <c:pt idx="120">
                   <c:v>user_interface.o</c:v>
                 </c:pt>
-                <c:pt idx="119">
+                <c:pt idx="121">
                   <c:v>motor_mode_velocity.o</c:v>
                 </c:pt>
-                <c:pt idx="120">
+                <c:pt idx="122">
                   <c:v>dev_dwt_counter.o</c:v>
                 </c:pt>
-                <c:pt idx="121">
+                <c:pt idx="123">
                   <c:v>motor_mode_open_loop.o</c:v>
                 </c:pt>
-                <c:pt idx="122">
+                <c:pt idx="124">
                   <c:v>floorf.o</c:v>
                 </c:pt>
-                <c:pt idx="123">
+                <c:pt idx="125">
                   <c:v>runtime_param.o</c:v>
                 </c:pt>
-                <c:pt idx="124">
+                <c:pt idx="126">
                   <c:v>motor_mode_position.o</c:v>
                 </c:pt>
-                <c:pt idx="125">
+                <c:pt idx="127">
                   <c:v>motor_mode_current.o</c:v>
                 </c:pt>
-                <c:pt idx="126">
+                <c:pt idx="128">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="127">
+                <c:pt idx="129">
                   <c:v>ceilf.o</c:v>
                 </c:pt>
-                <c:pt idx="128">
+                <c:pt idx="130">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="129">
+                <c:pt idx="131">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="130">
+                <c:pt idx="132">
                   <c:v>dma.o</c:v>
                 </c:pt>
-                <c:pt idx="131">
+                <c:pt idx="133">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="132">
+                <c:pt idx="134">
                   <c:v>motor_mode_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="133">
+                <c:pt idx="135">
                   <c:v>motor_mode_profile_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="134">
+                <c:pt idx="136">
                   <c:v>assert_report.o</c:v>
                 </c:pt>
-                <c:pt idx="135">
+                <c:pt idx="137">
                   <c:v>app_freertos.o</c:v>
                 </c:pt>
-                <c:pt idx="136">
+                <c:pt idx="138">
                   <c:v>funder.o</c:v>
                 </c:pt>
-                <c:pt idx="137">
-                  <c:v>motor_mode_profile_velocity.o</c:v>
-                </c:pt>
-                <c:pt idx="138">
+                <c:pt idx="139">
                   <c:v>cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="139">
+                <c:pt idx="140">
                   <c:v>control_irq.o</c:v>
                 </c:pt>
-                <c:pt idx="140">
+                <c:pt idx="141">
                   <c:v>motor_mode_duty.o</c:v>
                 </c:pt>
-                <c:pt idx="141">
+                <c:pt idx="142">
                   <c:v>frnd.o</c:v>
                 </c:pt>
-                <c:pt idx="142">
+                <c:pt idx="143">
                   <c:v>stm32g4xx_hal_msp.o</c:v>
                 </c:pt>
-                <c:pt idx="143">
+                <c:pt idx="144">
                   <c:v>sqrtf.o</c:v>
                 </c:pt>
-                <c:pt idx="144">
+                <c:pt idx="145">
                   <c:v>stm32g4xx_hal_cordic.o</c:v>
                 </c:pt>
-                <c:pt idx="145">
+                <c:pt idx="146">
                   <c:v>calib_level4_torque.o</c:v>
                 </c:pt>
-                <c:pt idx="146">
+                <c:pt idx="147">
                   <c:v>utils.o</c:v>
                 </c:pt>
-                <c:pt idx="147">
+                <c:pt idx="148">
                   <c:v>dfixui.o</c:v>
                 </c:pt>
-                <c:pt idx="148">
+                <c:pt idx="149">
                   <c:v>dfixul.o</c:v>
                 </c:pt>
-                <c:pt idx="149">
+                <c:pt idx="150">
                   <c:v>cdrcmple.o</c:v>
                 </c:pt>
-                <c:pt idx="150">
+                <c:pt idx="151">
                   <c:v>drv_dwt_timer.o</c:v>
                 </c:pt>
-                <c:pt idx="151">
+                <c:pt idx="152">
                   <c:v>uidiv.o</c:v>
                 </c:pt>
-                <c:pt idx="152">
+                <c:pt idx="153">
                   <c:v>thread_commun.o</c:v>
                 </c:pt>
-                <c:pt idx="153">
+                <c:pt idx="154">
                   <c:v>system_stm32g4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="154">
+                <c:pt idx="155">
                   <c:v>motor_mode_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="155">
+                <c:pt idx="156">
                   <c:v>motor_mode_hold.o</c:v>
                 </c:pt>
-                <c:pt idx="156">
+                <c:pt idx="157">
                   <c:v>drv_delay.o</c:v>
                 </c:pt>
-                <c:pt idx="157">
+                <c:pt idx="158">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="158">
+                <c:pt idx="159">
                   <c:v>fpclassifyf.o</c:v>
                 </c:pt>
-                <c:pt idx="159">
+                <c:pt idx="160">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="160">
+                <c:pt idx="161">
                   <c:v>memcpya.o</c:v>
                 </c:pt>
-                <c:pt idx="161">
+                <c:pt idx="162">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="162">
+                <c:pt idx="163">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="163">
+                <c:pt idx="164">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="164">
+                <c:pt idx="165">
                   <c:v>thread_idle.o</c:v>
                 </c:pt>
-                <c:pt idx="165">
+                <c:pt idx="166">
                   <c:v>thread_display.o</c:v>
                 </c:pt>
-                <c:pt idx="166">
+                <c:pt idx="167">
                   <c:v>thread_control.o</c:v>
                 </c:pt>
-                <c:pt idx="167">
+                <c:pt idx="168">
                   <c:v>motor_mode_zero_force.o</c:v>
                 </c:pt>
-                <c:pt idx="168">
+                <c:pt idx="169">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="169">
+                <c:pt idx="170">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="170">
+                <c:pt idx="171">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="171">
+                <c:pt idx="172">
                   <c:v>memcmp.o</c:v>
                 </c:pt>
-                <c:pt idx="172">
+                <c:pt idx="173">
                   <c:v>dfltul.o</c:v>
                 </c:pt>
-                <c:pt idx="173">
+                <c:pt idx="174">
                   <c:v>strncpy.o</c:v>
                 </c:pt>
-                <c:pt idx="174">
+                <c:pt idx="175">
                   <c:v>errno.o</c:v>
                 </c:pt>
-                <c:pt idx="175">
+                <c:pt idx="176">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="176">
+                <c:pt idx="177">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="177">
+                <c:pt idx="178">
                   <c:v>fpstat.o</c:v>
                 </c:pt>
-                <c:pt idx="178">
+                <c:pt idx="179">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="179">
+                <c:pt idx="180">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="180">
+                <c:pt idx="181">
                   <c:v>entry12b.o</c:v>
                 </c:pt>
-                <c:pt idx="181">
+                <c:pt idx="182">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -1641,554 +1647,557 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$184</c:f>
+              <c:f>flash_percent!$B$3:$B$185</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="182"/>
+                <c:ptCount val="183"/>
                 <c:pt idx="0">
-                  <c:v>4.56882381439209</c:v>
+                  <c:v>4.496542453765869</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.589032888412476</c:v>
+                  <c:v>3.532252311706543</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.357336044311523</c:v>
+                  <c:v>3.304220914840698</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.033262968063355</c:v>
+                  <c:v>3.027006149291992</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.821252584457398</c:v>
+                  <c:v>2.985274791717529</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.786422252655029</c:v>
+                  <c:v>2.742339372634888</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.509294271469116</c:v>
+                  <c:v>2.469595909118652</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.415404081344605</c:v>
+                  <c:v>2.377190828323364</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.185221433639526</c:v>
+                  <c:v>2.150649785995483</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.176135301589966</c:v>
+                  <c:v>2.141707420349121</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.039842844009399</c:v>
+                  <c:v>2.047811985015869</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.026213645935059</c:v>
+                  <c:v>2.007571220397949</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.817231893539429</c:v>
+                  <c:v>1.788482189178467</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.780887246131897</c:v>
+                  <c:v>1.752712488174439</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.77785849571228</c:v>
+                  <c:v>1.749731779098511</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.774829864501953</c:v>
+                  <c:v>1.746750950813294</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.723341584205627</c:v>
+                  <c:v>1.696077227592468</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.679425120353699</c:v>
+                  <c:v>1.652855634689331</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.62642252445221</c:v>
+                  <c:v>1.600691556930542</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.620365142822266</c:v>
+                  <c:v>1.594729900360107</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.553733229637146</c:v>
+                  <c:v>1.529152274131775</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.50678813457489</c:v>
+                  <c:v>1.524681091308594</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.481044054031372</c:v>
+                  <c:v>1.457612991333008</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.471957802772522</c:v>
+                  <c:v>1.448670506477356</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.438641905784607</c:v>
+                  <c:v>1.415881752967835</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.400782942771912</c:v>
+                  <c:v>1.378621697425842</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.350809097290039</c:v>
+                  <c:v>1.371169686317444</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.217545390129089</c:v>
+                  <c:v>1.198283076286316</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.128198146820068</c:v>
+                  <c:v>1.181888580322266</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>1.08882474899292</c:v>
+                  <c:v>1.110349297523499</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.085796117782593</c:v>
+                  <c:v>1.071598887443543</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.055508852005005</c:v>
+                  <c:v>1.038810014724731</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.043393969535828</c:v>
+                  <c:v>1.026886820793152</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.9449605941772461</c:v>
+                  <c:v>0.9240491390228272</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.9237595796585083</c:v>
+                  <c:v>0.9091451168060303</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.9025585055351257</c:v>
+                  <c:v>0.8882794976234436</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.8707569241523743</c:v>
+                  <c:v>0.8569810390472412</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8192687034606934</c:v>
+                  <c:v>0.8286634087562561</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.8026107549667358</c:v>
+                  <c:v>0.8063073754310608</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.7783809900283814</c:v>
+                  <c:v>0.7839513421058655</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.7662661075592041</c:v>
+                  <c:v>0.7660665512084961</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.7655089497566223</c:v>
+                  <c:v>0.7653213143348694</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7571799755096436</c:v>
+                  <c:v>0.7541432976722717</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.7344645857810974</c:v>
+                  <c:v>0.7452009320259094</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.7268927693367004</c:v>
+                  <c:v>0.7228448987007141</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.7238640189170837</c:v>
+                  <c:v>0.7198640704154968</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.7072060704231262</c:v>
+                  <c:v>0.7124120593070984</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.6814619898796082</c:v>
+                  <c:v>0.6960176229476929</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.6769188642501831</c:v>
+                  <c:v>0.6706808209419251</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.654203474521637</c:v>
+                  <c:v>0.6662096381187439</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.6208875775337219</c:v>
+                  <c:v>0.6438536047935486</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.6042296290397644</c:v>
+                  <c:v>0.6110647320747376</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.5936290621757507</c:v>
+                  <c:v>0.594670295715332</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.5724280476570129</c:v>
+                  <c:v>0.5842375159263611</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.5663706064224243</c:v>
+                  <c:v>0.5633718967437744</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.5451695919036865</c:v>
+                  <c:v>0.5574102997779846</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.4982244074344635</c:v>
+                  <c:v>0.536544680595398</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.4876239001750946</c:v>
+                  <c:v>0.4903421998023987</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.4694515764713287</c:v>
+                  <c:v>0.4799093902111054</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.4679372012615204</c:v>
+                  <c:v>0.4635149538516998</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.433106929063797</c:v>
+                  <c:v>0.4620245695114136</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.4209920465946198</c:v>
+                  <c:v>0.42625492811203</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.4149346053600311</c:v>
+                  <c:v>0.4143317043781281</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.4119058847427368</c:v>
+                  <c:v>0.4143317043781281</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.3876761496067047</c:v>
+                  <c:v>0.4083701074123383</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.3846474289894104</c:v>
+                  <c:v>0.405389279127121</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.3801043331623077</c:v>
+                  <c:v>0.3815428614616394</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.3801043331623077</c:v>
+                  <c:v>0.3785620629787445</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.3770756125450134</c:v>
+                  <c:v>0.374090850353241</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.3770756125450134</c:v>
+                  <c:v>0.374090850353241</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.3679894506931305</c:v>
+                  <c:v>0.3711100518703461</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.3604176640510559</c:v>
+                  <c:v>0.3711100518703461</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.3543602228164673</c:v>
+                  <c:v>0.3591868281364441</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.351331502199173</c:v>
+                  <c:v>0.3547156453132629</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3452740609645844</c:v>
+                  <c:v>0.3457732200622559</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.3392166197299957</c:v>
+                  <c:v>0.3413020074367523</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.3271017372608185</c:v>
+                  <c:v>0.3398116230964661</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.3225586712360382</c:v>
+                  <c:v>0.3338499963283539</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.3225586712360382</c:v>
+                  <c:v>0.3196911811828613</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.310443788766861</c:v>
+                  <c:v>0.3174555897712708</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.3089294135570526</c:v>
+                  <c:v>0.3055323660373688</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.302871972322464</c:v>
+                  <c:v>0.3040419816970825</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.302871972322464</c:v>
+                  <c:v>0.2980803549289703</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.2922714650630951</c:v>
+                  <c:v>0.2980803549289703</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.2816709578037262</c:v>
+                  <c:v>0.287647545337677</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.2771278619766235</c:v>
+                  <c:v>0.2772147357463837</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.260469913482666</c:v>
+                  <c:v>0.2727435231208801</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.252898097038269</c:v>
+                  <c:v>0.256349116563797</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.2513837516307831</c:v>
+                  <c:v>0.2503874897956848</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.2453263103961945</c:v>
+                  <c:v>0.2488971054553986</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.2332114279270172</c:v>
+                  <c:v>0.2474067062139511</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.22109654545784</c:v>
+                  <c:v>0.2414450943470001</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.2059529423713684</c:v>
+                  <c:v>0.2295218855142593</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.2059529423713684</c:v>
+                  <c:v>0.2175986617803574</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.199895516037941</c:v>
+                  <c:v>0.2026946395635605</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.190809354186058</c:v>
+                  <c:v>0.2026946395635605</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.1862662732601166</c:v>
+                  <c:v>0.1877906322479248</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1832375526428223</c:v>
+                  <c:v>0.1833194196224213</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.1817231923341751</c:v>
+                  <c:v>0.1803386211395264</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.1756657510995865</c:v>
+                  <c:v>0.1788482218980789</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1726370304822922</c:v>
+                  <c:v>0.1743770092725754</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.1726370304822922</c:v>
+                  <c:v>0.169905811548233</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.1680939495563507</c:v>
+                  <c:v>0.169905811548233</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.1665795892477036</c:v>
+                  <c:v>0.1654345989227295</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.1453785449266434</c:v>
+                  <c:v>0.163944199681282</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.1423498392105103</c:v>
+                  <c:v>0.163944199681282</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.1408354789018631</c:v>
+                  <c:v>0.1430785804986954</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.1332636773586273</c:v>
+                  <c:v>0.1400977671146393</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.130234956741333</c:v>
+                  <c:v>0.1386073678731918</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.1196344345808029</c:v>
+                  <c:v>0.1311553567647934</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.1166057139635086</c:v>
+                  <c:v>0.1281745582818985</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.1150913536548615</c:v>
+                  <c:v>0.1177417412400246</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.1090339124202728</c:v>
+                  <c:v>0.1147609427571297</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.1075195521116257</c:v>
+                  <c:v>0.1132705360651016</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.1044908314943314</c:v>
+                  <c:v>0.1073089316487312</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.1029764711856842</c:v>
+                  <c:v>0.1058185249567032</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.09691903740167618</c:v>
+                  <c:v>0.1028377264738083</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.09691903740167618</c:v>
+                  <c:v>0.1013473197817802</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.09540467709302902</c:v>
+                  <c:v>0.09538571536540985</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.09540467709302902</c:v>
+                  <c:v>0.09538571536540985</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.09086159616708756</c:v>
+                  <c:v>0.0938953161239624</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.08631851524114609</c:v>
+                  <c:v>0.0938953161239624</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.08480415493249893</c:v>
+                  <c:v>0.08942411094903946</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.08480415493249893</c:v>
+                  <c:v>0.08495290577411652</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.08480415493249893</c:v>
+                  <c:v>0.08346249908208847</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.08480415493249893</c:v>
+                  <c:v>0.08346249908208847</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.08328979462385178</c:v>
+                  <c:v>0.08346249908208847</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.08177543431520462</c:v>
+                  <c:v>0.08346249908208847</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.07420363277196884</c:v>
+                  <c:v>0.08197209984064102</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.07420363277196884</c:v>
+                  <c:v>0.08048170059919357</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.06966055929660797</c:v>
+                  <c:v>0.07302968949079514</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.0651174783706665</c:v>
+                  <c:v>0.07302968949079514</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.06360311806201935</c:v>
+                  <c:v>0.06855848431587219</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.06360311806201935</c:v>
+                  <c:v>0.06408727914094925</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.06360311806201935</c:v>
+                  <c:v>0.0625968724489212</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.06360311806201935</c:v>
+                  <c:v>0.0625968724489212</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.06057439744472504</c:v>
+                  <c:v>0.0625968724489212</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.05906003713607788</c:v>
+                  <c:v>0.0625968724489212</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.05754567682743073</c:v>
+                  <c:v>0.05961607396602631</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.05451695621013641</c:v>
+                  <c:v>0.05663526803255081</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.04997387900948525</c:v>
+                  <c:v>0.05365446582436562</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.04543079808354378</c:v>
+                  <c:v>0.04918326064944267</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.04543079808354378</c:v>
+                  <c:v>0.04471205547451973</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.04391643777489662</c:v>
+                  <c:v>0.04471205547451973</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.04088771715760231</c:v>
+                  <c:v>0.04322165250778198</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.04088771715760231</c:v>
+                  <c:v>0.04024085029959679</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.03937335684895515</c:v>
+                  <c:v>0.04024085029959679</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.037858996540308</c:v>
+                  <c:v>0.03875044733285904</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.03634463623166084</c:v>
+                  <c:v>0.03726004436612129</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.03634463623166084</c:v>
+                  <c:v>0.03576964512467384</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.03634463623166084</c:v>
+                  <c:v>0.03576964512467384</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.03331591933965683</c:v>
+                  <c:v>0.03576964512467384</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.03331591933965683</c:v>
+                  <c:v>0.03278883919119835</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.03331591933965683</c:v>
+                  <c:v>0.03278883919119835</c:v>
                 </c:pt>
                 <c:pt idx="154">
-                  <c:v>0.03331591933965683</c:v>
+                  <c:v>0.03278883919119835</c:v>
                 </c:pt>
                 <c:pt idx="155">
-                  <c:v>0.03331591933965683</c:v>
+                  <c:v>0.03278883919119835</c:v>
                 </c:pt>
                 <c:pt idx="156">
-                  <c:v>0.03028719872236252</c:v>
+                  <c:v>0.03278883919119835</c:v>
                 </c:pt>
                 <c:pt idx="157">
-                  <c:v>0.02877283841371536</c:v>
+                  <c:v>0.02980803698301315</c:v>
                 </c:pt>
                 <c:pt idx="158">
-                  <c:v>0.02877283841371536</c:v>
+                  <c:v>0.02831763401627541</c:v>
                 </c:pt>
                 <c:pt idx="159">
-                  <c:v>0.02725847810506821</c:v>
+                  <c:v>0.02831763401627541</c:v>
                 </c:pt>
                 <c:pt idx="160">
-                  <c:v>0.02725847810506821</c:v>
+                  <c:v>0.02682723291218281</c:v>
                 </c:pt>
                 <c:pt idx="161">
-                  <c:v>0.02725847810506821</c:v>
+                  <c:v>0.02682723291218281</c:v>
                 </c:pt>
                 <c:pt idx="162">
-                  <c:v>0.02725847810506821</c:v>
+                  <c:v>0.02682723291218281</c:v>
                 </c:pt>
                 <c:pt idx="163">
-                  <c:v>0.02422975935041904</c:v>
+                  <c:v>0.02682723291218281</c:v>
                 </c:pt>
                 <c:pt idx="164">
-                  <c:v>0.02422975935041904</c:v>
+                  <c:v>0.02384642884135246</c:v>
                 </c:pt>
                 <c:pt idx="165">
-                  <c:v>0.02422975935041904</c:v>
+                  <c:v>0.02384642884135246</c:v>
                 </c:pt>
                 <c:pt idx="166">
-                  <c:v>0.02422975935041904</c:v>
+                  <c:v>0.02384642884135246</c:v>
                 </c:pt>
                 <c:pt idx="167">
-                  <c:v>0.02422975935041904</c:v>
+                  <c:v>0.02384642884135246</c:v>
                 </c:pt>
                 <c:pt idx="168">
-                  <c:v>0.02271539904177189</c:v>
+                  <c:v>0.02384642884135246</c:v>
                 </c:pt>
                 <c:pt idx="169">
-                  <c:v>0.02271539904177189</c:v>
+                  <c:v>0.02235602773725987</c:v>
                 </c:pt>
                 <c:pt idx="170">
-                  <c:v>0.01968667842447758</c:v>
+                  <c:v>0.02235602773725987</c:v>
                 </c:pt>
                 <c:pt idx="171">
-                  <c:v>0.01968667842447758</c:v>
+                  <c:v>0.01937522366642952</c:v>
                 </c:pt>
                 <c:pt idx="172">
-                  <c:v>0.01817231811583042</c:v>
+                  <c:v>0.01937522366642952</c:v>
                 </c:pt>
                 <c:pt idx="173">
-                  <c:v>0.01817231811583042</c:v>
+                  <c:v>0.01788482256233692</c:v>
                 </c:pt>
                 <c:pt idx="174">
-                  <c:v>0.01211487967520952</c:v>
+                  <c:v>0.01788482256233692</c:v>
                 </c:pt>
                 <c:pt idx="175">
-                  <c:v>0.006057439837604761</c:v>
+                  <c:v>0.01192321442067623</c:v>
                 </c:pt>
                 <c:pt idx="176">
-                  <c:v>0.006057439837604761</c:v>
+                  <c:v>0.005961607210338116</c:v>
                 </c:pt>
                 <c:pt idx="177">
-                  <c:v>0.003028719918802381</c:v>
+                  <c:v>0.005961607210338116</c:v>
                 </c:pt>
                 <c:pt idx="178">
-                  <c:v>0.003028719918802381</c:v>
+                  <c:v>0.002980803605169058</c:v>
                 </c:pt>
                 <c:pt idx="179">
-                  <c:v>0.003028719918802381</c:v>
+                  <c:v>0.002980803605169058</c:v>
                 </c:pt>
                 <c:pt idx="180">
-                  <c:v>0.003028719918802381</c:v>
+                  <c:v>0.002980803605169058</c:v>
                 </c:pt>
                 <c:pt idx="181">
+                  <c:v>0.002980803605169058</c:v>
+                </c:pt>
+                <c:pt idx="182">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2293,8 +2302,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H184" totalsRowCount="1">
-  <autoFilter ref="A2:H183"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H185" totalsRowCount="1">
+  <autoFilter ref="A2:H184"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -2310,8 +2319,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H184" totalsRowCount="1">
-  <autoFilter ref="A2:H183"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H185" totalsRowCount="1">
+  <autoFilter ref="A2:H184"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -2611,7 +2620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2624,28 +2633,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2653,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>36.17101287841797</v>
+        <v>36.13472747802734</v>
       </c>
       <c r="C3" s="1">
         <v>28816</v>
@@ -2679,7 +2688,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>20.60602951049805</v>
+        <v>20.58535766601563</v>
       </c>
       <c r="C4" s="1">
         <v>16416</v>
@@ -2705,16 +2714,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>12.61767864227295</v>
+        <v>12.7053394317627</v>
       </c>
       <c r="C5" s="1">
-        <v>10052</v>
+        <v>10132</v>
       </c>
       <c r="D5" s="1">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="E5" s="1">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2723,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>10052</v>
+        <v>10132</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -2731,16 +2740,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>5.141465663909912</v>
+        <v>5.136307716369629</v>
       </c>
       <c r="C6" s="1">
         <v>4096</v>
       </c>
       <c r="D6" s="1">
-        <v>960</v>
+        <v>1112</v>
       </c>
       <c r="E6" s="1">
-        <v>960</v>
+        <v>1112</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -2757,7 +2766,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>5.141465663909912</v>
+        <v>5.136307716369629</v>
       </c>
       <c r="C7" s="1">
         <v>4096</v>
@@ -2783,7 +2792,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>4.709662914276123</v>
+        <v>4.704938411712647</v>
       </c>
       <c r="C8" s="1">
         <v>3752</v>
@@ -2809,7 +2818,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.630984306335449</v>
+        <v>2.628345012664795</v>
       </c>
       <c r="C9" s="1">
         <v>2096</v>
@@ -2835,7 +2844,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.565711736679077</v>
+        <v>2.563138008117676</v>
       </c>
       <c r="C10" s="1">
         <v>2044</v>
@@ -2861,7 +2870,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>2.068636655807495</v>
+        <v>2.066561222076416</v>
       </c>
       <c r="C11" s="1">
         <v>1648</v>
@@ -2887,7 +2896,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.294153094291687</v>
+        <v>1.29285478591919</v>
       </c>
       <c r="C12" s="1">
         <v>1031</v>
@@ -2913,7 +2922,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.285366415977478</v>
+        <v>1.284076929092407</v>
       </c>
       <c r="C13" s="1">
         <v>1024</v>
@@ -2939,7 +2948,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.9037732481956482</v>
+        <v>0.9028666019439697</v>
       </c>
       <c r="C14" s="1">
         <v>720</v>
@@ -2965,7 +2974,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.5020962357521057</v>
+        <v>0.5015925765037537</v>
       </c>
       <c r="C15" s="1">
         <v>400</v>
@@ -2991,7 +3000,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.4468656778335571</v>
+        <v>0.446417361497879</v>
       </c>
       <c r="C16" s="1">
         <v>356</v>
@@ -3017,7 +3026,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.4267818033695221</v>
+        <v>0.4263536632061005</v>
       </c>
       <c r="C17" s="1">
         <v>340</v>
@@ -3043,7 +3052,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.3765721917152405</v>
+        <v>0.3761944174766541</v>
       </c>
       <c r="C18" s="1">
         <v>300</v>
@@ -3069,7 +3078,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.3364045023918152</v>
+        <v>0.3360670208930969</v>
       </c>
       <c r="C19" s="1">
         <v>268</v>
@@ -3095,7 +3104,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.2861948609352112</v>
+        <v>0.2859077453613281</v>
       </c>
       <c r="C20" s="1">
         <v>228</v>
@@ -3121,7 +3130,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.2811739146709442</v>
+        <v>0.2808918356895447</v>
       </c>
       <c r="C21" s="1">
         <v>224</v>
@@ -3147,7 +3156,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.2560690939426422</v>
+        <v>0.2558121979236603</v>
       </c>
       <c r="C22" s="1">
         <v>204</v>
@@ -3173,7 +3182,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.2510481178760529</v>
+        <v>0.2507962882518768</v>
       </c>
       <c r="C23" s="1">
         <v>200</v>
@@ -3199,16 +3208,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.1707127243280411</v>
+        <v>0.1705414652824402</v>
       </c>
       <c r="C24" s="1">
         <v>136</v>
       </c>
       <c r="D24" s="1">
-        <v>2676</v>
+        <v>2748</v>
       </c>
       <c r="E24" s="1">
-        <v>2664</v>
+        <v>2736</v>
       </c>
       <c r="F24" s="1">
         <v>12</v>
@@ -3225,7 +3234,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.1656917631626129</v>
+        <v>0.1655255407094955</v>
       </c>
       <c r="C25" s="1">
         <v>132</v>
@@ -3251,7 +3260,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.1606708019971848</v>
+        <v>0.1605096161365509</v>
       </c>
       <c r="C26" s="1">
         <v>128</v>
@@ -3277,7 +3286,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.1255240589380264</v>
+        <v>0.1253981441259384</v>
       </c>
       <c r="C27" s="1">
         <v>100</v>
@@ -3303,7 +3312,7 @@
         <v>26</v>
       </c>
       <c r="B28" s="2">
-        <v>0.1054402142763138</v>
+        <v>0.1053344383835793</v>
       </c>
       <c r="C28" s="1">
         <v>84</v>
@@ -3329,7 +3338,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="2">
-        <v>0.09539828449487686</v>
+        <v>0.09530258923768997</v>
       </c>
       <c r="C29" s="1">
         <v>76</v>
@@ -3355,7 +3364,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="2">
-        <v>0.0903773233294487</v>
+        <v>0.09028665721416473</v>
       </c>
       <c r="C30" s="1">
         <v>72</v>
@@ -3381,7 +3390,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2">
-        <v>0.0903773233294487</v>
+        <v>0.09028665721416473</v>
       </c>
       <c r="C31" s="1">
         <v>72</v>
@@ -3407,7 +3416,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2">
-        <v>0.0903773233294487</v>
+        <v>0.09028665721416473</v>
       </c>
       <c r="C32" s="1">
         <v>72</v>
@@ -3433,7 +3442,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.08535636216402054</v>
+        <v>0.08527073264122009</v>
       </c>
       <c r="C33" s="1">
         <v>68</v>
@@ -3459,7 +3468,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="2">
-        <v>0.08033540099859238</v>
+        <v>0.08025480806827545</v>
       </c>
       <c r="C34" s="1">
         <v>64</v>
@@ -3485,7 +3494,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="2">
-        <v>0.05523058772087097</v>
+        <v>0.05517518147826195</v>
       </c>
       <c r="C35" s="1">
         <v>44</v>
@@ -3511,7 +3520,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>0.05020962655544281</v>
+        <v>0.05015925690531731</v>
       </c>
       <c r="C36" s="1">
         <v>40</v>
@@ -3537,7 +3546,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="2">
-        <v>0.04518866166472435</v>
+        <v>0.04514332860708237</v>
       </c>
       <c r="C37" s="1">
         <v>36</v>
@@ -3563,7 +3572,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>0.04518866166472435</v>
+        <v>0.04514332860708237</v>
       </c>
       <c r="C38" s="1">
         <v>36</v>
@@ -3589,7 +3598,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>0.04016770049929619</v>
+        <v>0.04012740403413773</v>
       </c>
       <c r="C39" s="1">
         <v>32</v>
@@ -3615,7 +3624,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>0.04016770049929619</v>
+        <v>0.04012740403413773</v>
       </c>
       <c r="C40" s="1">
         <v>32</v>
@@ -3641,7 +3650,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>0.02510481327772141</v>
+        <v>0.02507962845265865</v>
       </c>
       <c r="C41" s="1">
         <v>20</v>
@@ -3667,7 +3676,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>0.02510481327772141</v>
+        <v>0.02507962845265865</v>
       </c>
       <c r="C42" s="1">
         <v>20</v>
@@ -3693,7 +3702,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>0.01506288722157478</v>
+        <v>0.01504777651280165</v>
       </c>
       <c r="C43" s="1">
         <v>12</v>
@@ -3719,7 +3728,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>0.01506288722157478</v>
+        <v>0.01504777651280165</v>
       </c>
       <c r="C44" s="1">
         <v>12</v>
@@ -3745,7 +3754,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>0.01506288722157478</v>
+        <v>0.01504777651280165</v>
       </c>
       <c r="C45" s="1">
         <v>12</v>
@@ -3771,7 +3780,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>0.01004192512482405</v>
+        <v>0.01003185100853443</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
@@ -3797,7 +3806,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>0.01004192512482405</v>
+        <v>0.01003185100853443</v>
       </c>
       <c r="C47" s="1">
         <v>8</v>
@@ -3823,7 +3832,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>0.01004192512482405</v>
+        <v>0.01003185100853443</v>
       </c>
       <c r="C48" s="1">
         <v>8</v>
@@ -3849,7 +3858,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>0.005020962562412024</v>
+        <v>0.005015925504267216</v>
       </c>
       <c r="C49" s="1">
         <v>4</v>
@@ -3875,7 +3884,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>0.005020962562412024</v>
+        <v>0.005015925504267216</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
@@ -3901,7 +3910,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>0.005020962562412024</v>
+        <v>0.005015925504267216</v>
       </c>
       <c r="C51" s="1">
         <v>4</v>
@@ -3927,16 +3936,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>0.005020962562412024</v>
+        <v>0.005015925504267216</v>
       </c>
       <c r="C52" s="1">
         <v>4</v>
       </c>
       <c r="D52" s="1">
-        <v>1784</v>
+        <v>1840</v>
       </c>
       <c r="E52" s="1">
-        <v>1444</v>
+        <v>1500</v>
       </c>
       <c r="F52" s="1">
         <v>336</v>
@@ -3953,7 +3962,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="2">
-        <v>0.005020962562412024</v>
+        <v>0.005015925504267216</v>
       </c>
       <c r="C53" s="1">
         <v>4</v>
@@ -3979,7 +3988,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>0.005020962562412024</v>
+        <v>0.005015925504267216</v>
       </c>
       <c r="C54" s="1">
         <v>4</v>
@@ -4005,7 +4014,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>0.005020962562412024</v>
+        <v>0.005015925504267216</v>
       </c>
       <c r="C55" s="1">
         <v>4</v>
@@ -4031,16 +4040,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>0.003765721805393696</v>
+        <v>0.003761944128200412</v>
       </c>
       <c r="C56" s="1">
         <v>3</v>
       </c>
       <c r="D56" s="1">
-        <v>1011</v>
+        <v>1027</v>
       </c>
       <c r="E56" s="1">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -4052,35 +4061,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8">
-      <c r="A184" t="s">
-        <v>183</v>
-      </c>
-      <c r="B184">
+    <row r="185" spans="1:8">
+      <c r="A185" t="s">
+        <v>184</v>
+      </c>
+      <c r="B185">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C184">
+      <c r="C185">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D184">
+      <c r="D185">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E184">
+      <c r="E185">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F184">
+      <c r="F185">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G184">
+      <c r="G185">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H184">
+      <c r="H185">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -4096,7 +4105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -4109,28 +4118,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" t="s">
         <v>191</v>
-      </c>
-      <c r="C2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4138,7 +4147,7 @@
         <v>13</v>
       </c>
       <c r="B3" s="2">
-        <v>4.56882381439209</v>
+        <v>4.496542453765869</v>
       </c>
       <c r="C3" s="1">
         <v>6034</v>
@@ -4164,7 +4173,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="2">
-        <v>3.589032888412476</v>
+        <v>3.532252311706543</v>
       </c>
       <c r="C4" s="1">
         <v>4740</v>
@@ -4190,7 +4199,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="2">
-        <v>3.357336044311523</v>
+        <v>3.304220914840698</v>
       </c>
       <c r="C5" s="1">
         <v>4434</v>
@@ -4216,19 +4225,19 @@
         <v>56</v>
       </c>
       <c r="B6" s="2">
-        <v>3.033262968063355</v>
+        <v>3.027006149291992</v>
       </c>
       <c r="C6" s="1">
-        <v>4006</v>
+        <v>4062</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>4006</v>
+        <v>3646</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -4242,19 +4251,19 @@
         <v>57</v>
       </c>
       <c r="B7" s="2">
-        <v>2.821252584457398</v>
+        <v>2.985274791717529</v>
       </c>
       <c r="C7" s="1">
-        <v>3726</v>
+        <v>4006</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
       <c r="E7" s="1">
-        <v>3310</v>
+        <v>4006</v>
       </c>
       <c r="F7" s="1">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -4268,7 +4277,7 @@
         <v>58</v>
       </c>
       <c r="B8" s="2">
-        <v>2.786422252655029</v>
+        <v>2.742339372634888</v>
       </c>
       <c r="C8" s="1">
         <v>3680</v>
@@ -4294,7 +4303,7 @@
         <v>59</v>
       </c>
       <c r="B9" s="2">
-        <v>2.509294271469116</v>
+        <v>2.469595909118652</v>
       </c>
       <c r="C9" s="1">
         <v>3314</v>
@@ -4320,7 +4329,7 @@
         <v>60</v>
       </c>
       <c r="B10" s="2">
-        <v>2.415404081344605</v>
+        <v>2.377190828323364</v>
       </c>
       <c r="C10" s="1">
         <v>3190</v>
@@ -4346,7 +4355,7 @@
         <v>61</v>
       </c>
       <c r="B11" s="2">
-        <v>2.185221433639526</v>
+        <v>2.150649785995483</v>
       </c>
       <c r="C11" s="1">
         <v>2886</v>
@@ -4372,7 +4381,7 @@
         <v>44</v>
       </c>
       <c r="B12" s="2">
-        <v>2.176135301589966</v>
+        <v>2.141707420349121</v>
       </c>
       <c r="C12" s="1">
         <v>2874</v>
@@ -4395,54 +4404,54 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2">
-        <v>2.039842844009399</v>
+        <v>2.047811985015869</v>
       </c>
       <c r="C13" s="1">
-        <v>2694</v>
+        <v>2748</v>
       </c>
       <c r="D13" s="1">
-        <v>28816</v>
+        <v>136</v>
       </c>
       <c r="E13" s="1">
-        <v>2646</v>
+        <v>2736</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>28768</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>2.026213645935059</v>
+        <v>2.007571220397949</v>
       </c>
       <c r="C14" s="1">
-        <v>2676</v>
+        <v>2694</v>
       </c>
       <c r="D14" s="1">
-        <v>136</v>
+        <v>28816</v>
       </c>
       <c r="E14" s="1">
-        <v>2664</v>
+        <v>2646</v>
       </c>
       <c r="F14" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H14" s="1">
-        <v>136</v>
+        <v>28768</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -4450,7 +4459,7 @@
         <v>62</v>
       </c>
       <c r="B15" s="2">
-        <v>1.817231893539429</v>
+        <v>1.788482189178467</v>
       </c>
       <c r="C15" s="1">
         <v>2400</v>
@@ -4476,7 +4485,7 @@
         <v>63</v>
       </c>
       <c r="B16" s="2">
-        <v>1.780887246131897</v>
+        <v>1.752712488174439</v>
       </c>
       <c r="C16" s="1">
         <v>2352</v>
@@ -4502,7 +4511,7 @@
         <v>64</v>
       </c>
       <c r="B17" s="2">
-        <v>1.77785849571228</v>
+        <v>1.749731779098511</v>
       </c>
       <c r="C17" s="1">
         <v>2348</v>
@@ -4528,7 +4537,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>1.774829864501953</v>
+        <v>1.746750950813294</v>
       </c>
       <c r="C18" s="1">
         <v>2344</v>
@@ -4554,7 +4563,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>1.723341584205627</v>
+        <v>1.696077227592468</v>
       </c>
       <c r="C19" s="1">
         <v>2276</v>
@@ -4580,7 +4589,7 @@
         <v>65</v>
       </c>
       <c r="B20" s="2">
-        <v>1.679425120353699</v>
+        <v>1.652855634689331</v>
       </c>
       <c r="C20" s="1">
         <v>2218</v>
@@ -4606,7 +4615,7 @@
         <v>66</v>
       </c>
       <c r="B21" s="2">
-        <v>1.62642252445221</v>
+        <v>1.600691556930542</v>
       </c>
       <c r="C21" s="1">
         <v>2148</v>
@@ -4632,7 +4641,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="2">
-        <v>1.620365142822266</v>
+        <v>1.594729900360107</v>
       </c>
       <c r="C22" s="1">
         <v>2140</v>
@@ -4658,7 +4667,7 @@
         <v>67</v>
       </c>
       <c r="B23" s="2">
-        <v>1.553733229637146</v>
+        <v>1.529152274131775</v>
       </c>
       <c r="C23" s="1">
         <v>2052</v>
@@ -4684,16 +4693,16 @@
         <v>68</v>
       </c>
       <c r="B24" s="2">
-        <v>1.50678813457489</v>
+        <v>1.524681091308594</v>
       </c>
       <c r="C24" s="1">
-        <v>1990</v>
+        <v>2046</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>1990</v>
+        <v>2046</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -4710,7 +4719,7 @@
         <v>69</v>
       </c>
       <c r="B25" s="2">
-        <v>1.481044054031372</v>
+        <v>1.457612991333008</v>
       </c>
       <c r="C25" s="1">
         <v>1956</v>
@@ -4736,7 +4745,7 @@
         <v>70</v>
       </c>
       <c r="B26" s="2">
-        <v>1.471957802772522</v>
+        <v>1.448670506477356</v>
       </c>
       <c r="C26" s="1">
         <v>1944</v>
@@ -4762,7 +4771,7 @@
         <v>71</v>
       </c>
       <c r="B27" s="2">
-        <v>1.438641905784607</v>
+        <v>1.415881752967835</v>
       </c>
       <c r="C27" s="1">
         <v>1900</v>
@@ -4788,7 +4797,7 @@
         <v>72</v>
       </c>
       <c r="B28" s="2">
-        <v>1.400782942771912</v>
+        <v>1.378621697425842</v>
       </c>
       <c r="C28" s="1">
         <v>1850</v>
@@ -4814,16 +4823,16 @@
         <v>50</v>
       </c>
       <c r="B29" s="2">
-        <v>1.350809097290039</v>
+        <v>1.371169686317444</v>
       </c>
       <c r="C29" s="1">
-        <v>1784</v>
+        <v>1840</v>
       </c>
       <c r="D29" s="1">
         <v>4</v>
       </c>
       <c r="E29" s="1">
-        <v>1444</v>
+        <v>1500</v>
       </c>
       <c r="F29" s="1">
         <v>336</v>
@@ -4840,7 +4849,7 @@
         <v>73</v>
       </c>
       <c r="B30" s="2">
-        <v>1.217545390129089</v>
+        <v>1.198283076286316</v>
       </c>
       <c r="C30" s="1">
         <v>1608</v>
@@ -4863,80 +4872,80 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B31" s="2">
-        <v>1.128198146820068</v>
+        <v>1.181888580322266</v>
       </c>
       <c r="C31" s="1">
-        <v>1490</v>
+        <v>1586</v>
       </c>
       <c r="D31" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>1454</v>
+        <v>1586</v>
       </c>
       <c r="F31" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
         <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B32" s="2">
-        <v>1.08882474899292</v>
+        <v>1.110349297523499</v>
       </c>
       <c r="C32" s="1">
-        <v>1438</v>
+        <v>1490</v>
       </c>
       <c r="D32" s="1">
-        <v>356</v>
+        <v>36</v>
       </c>
       <c r="E32" s="1">
-        <v>1082</v>
+        <v>1454</v>
       </c>
       <c r="F32" s="1">
-        <v>352</v>
+        <v>36</v>
       </c>
       <c r="G32" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>352</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B33" s="2">
-        <v>1.085796117782593</v>
+        <v>1.071598887443543</v>
       </c>
       <c r="C33" s="1">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="E33" s="1">
-        <v>1434</v>
+        <v>1082</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>352</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -4944,7 +4953,7 @@
         <v>75</v>
       </c>
       <c r="B34" s="2">
-        <v>1.055508852005005</v>
+        <v>1.038810014724731</v>
       </c>
       <c r="C34" s="1">
         <v>1394</v>
@@ -4970,7 +4979,7 @@
         <v>76</v>
       </c>
       <c r="B35" s="2">
-        <v>1.043393969535828</v>
+        <v>1.026886820793152</v>
       </c>
       <c r="C35" s="1">
         <v>1378</v>
@@ -4996,16 +5005,16 @@
         <v>77</v>
       </c>
       <c r="B36" s="2">
-        <v>0.9449605941772461</v>
+        <v>0.9240491390228272</v>
       </c>
       <c r="C36" s="1">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -5022,7 +5031,7 @@
         <v>78</v>
       </c>
       <c r="B37" s="2">
-        <v>0.9237595796585083</v>
+        <v>0.9091451168060303</v>
       </c>
       <c r="C37" s="1">
         <v>1220</v>
@@ -5048,7 +5057,7 @@
         <v>40</v>
       </c>
       <c r="B38" s="2">
-        <v>0.9025585055351257</v>
+        <v>0.8882794976234436</v>
       </c>
       <c r="C38" s="1">
         <v>1192</v>
@@ -5074,7 +5083,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="2">
-        <v>0.8707569241523743</v>
+        <v>0.8569810390472412</v>
       </c>
       <c r="C39" s="1">
         <v>1150</v>
@@ -5097,106 +5106,106 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>0.8192687034606934</v>
+        <v>0.8286634087562561</v>
       </c>
       <c r="C40" s="1">
-        <v>1082</v>
+        <v>1112</v>
       </c>
       <c r="D40" s="1">
-        <v>36</v>
+        <v>4096</v>
       </c>
       <c r="E40" s="1">
-        <v>1070</v>
+        <v>1112</v>
       </c>
       <c r="F40" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>36</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="B41" s="2">
-        <v>0.8026107549667358</v>
+        <v>0.8063073754310608</v>
       </c>
       <c r="C41" s="1">
-        <v>1060</v>
+        <v>1082</v>
       </c>
       <c r="D41" s="1">
-        <v>10052</v>
+        <v>36</v>
       </c>
       <c r="E41" s="1">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="F41" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G41" s="1">
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>10052</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B42" s="2">
-        <v>0.7783809900283814</v>
+        <v>0.7839513421058655</v>
       </c>
       <c r="C42" s="1">
-        <v>1028</v>
+        <v>1052</v>
       </c>
       <c r="D42" s="1">
-        <v>72</v>
+        <v>10132</v>
       </c>
       <c r="E42" s="1">
-        <v>468</v>
+        <v>1052</v>
       </c>
       <c r="F42" s="1">
-        <v>512</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>24</v>
+        <v>10132</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2">
-        <v>0.7662661075592041</v>
+        <v>0.7660665512084961</v>
       </c>
       <c r="C43" s="1">
-        <v>1012</v>
+        <v>1028</v>
       </c>
       <c r="D43" s="1">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E43" s="1">
-        <v>1012</v>
+        <v>468</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -5204,16 +5213,16 @@
         <v>54</v>
       </c>
       <c r="B44" s="2">
-        <v>0.7655089497566223</v>
+        <v>0.7653213143348694</v>
       </c>
       <c r="C44" s="1">
-        <v>1011</v>
+        <v>1027</v>
       </c>
       <c r="D44" s="1">
         <v>3</v>
       </c>
       <c r="E44" s="1">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -5227,19 +5236,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B45" s="2">
-        <v>0.7571799755096436</v>
+        <v>0.7541432976722717</v>
       </c>
       <c r="C45" s="1">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -5253,54 +5262,54 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="B46" s="2">
-        <v>0.7344645857810974</v>
+        <v>0.7452009320259094</v>
       </c>
       <c r="C46" s="1">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="D46" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>958</v>
+        <v>1000</v>
       </c>
       <c r="F46" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G46" s="1">
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7268927693367004</v>
+        <v>0.7228448987007141</v>
       </c>
       <c r="C47" s="1">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="D47" s="1">
-        <v>4096</v>
+        <v>72</v>
       </c>
       <c r="E47" s="1">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>4096</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -5308,16 +5317,16 @@
         <v>81</v>
       </c>
       <c r="B48" s="2">
-        <v>0.7238640189170837</v>
+        <v>0.7198640704154968</v>
       </c>
       <c r="C48" s="1">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>956</v>
+        <v>966</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -5331,54 +5340,54 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="B49" s="2">
-        <v>0.7072060704231262</v>
+        <v>0.7124120593070984</v>
       </c>
       <c r="C49" s="1">
-        <v>934</v>
+        <v>956</v>
       </c>
       <c r="D49" s="1">
-        <v>2096</v>
+        <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>918</v>
+        <v>956</v>
       </c>
       <c r="F49" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>2096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="B50" s="2">
-        <v>0.6814619898796082</v>
+        <v>0.6960176229476929</v>
       </c>
       <c r="C50" s="1">
-        <v>900</v>
+        <v>934</v>
       </c>
       <c r="D50" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
       <c r="E50" s="1">
-        <v>900</v>
+        <v>918</v>
       </c>
       <c r="F50" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>0</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -5386,16 +5395,16 @@
         <v>83</v>
       </c>
       <c r="B51" s="2">
-        <v>0.6769188642501831</v>
+        <v>0.6706808209419251</v>
       </c>
       <c r="C51" s="1">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -5412,16 +5421,16 @@
         <v>84</v>
       </c>
       <c r="B52" s="2">
-        <v>0.654203474521637</v>
+        <v>0.6662096381187439</v>
       </c>
       <c r="C52" s="1">
-        <v>864</v>
+        <v>894</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>864</v>
+        <v>894</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -5435,77 +5444,77 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="B53" s="2">
-        <v>0.6208875775337219</v>
+        <v>0.6438536047935486</v>
       </c>
       <c r="C53" s="1">
-        <v>820</v>
+        <v>864</v>
       </c>
       <c r="D53" s="1">
-        <v>1648</v>
+        <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>816</v>
+        <v>864</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
       </c>
       <c r="G53" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>1644</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B54" s="2">
-        <v>0.6042296290397644</v>
+        <v>0.6110647320747376</v>
       </c>
       <c r="C54" s="1">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="D54" s="1">
-        <v>12</v>
+        <v>1648</v>
       </c>
       <c r="E54" s="1">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H54" s="1">
-        <v>0</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="B55" s="2">
-        <v>0.5936290621757507</v>
+        <v>0.594670295715332</v>
       </c>
       <c r="C55" s="1">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="D55" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E55" s="1">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
       </c>
       <c r="G55" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H55" s="1">
         <v>0</v>
@@ -5513,19 +5522,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="B56" s="2">
-        <v>0.5724280476570129</v>
+        <v>0.5842375159263611</v>
       </c>
       <c r="C56" s="1">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="D56" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -5534,24 +5543,24 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="B57" s="2">
-        <v>0.5663706064224243</v>
+        <v>0.5633718967437744</v>
       </c>
       <c r="C57" s="1">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="D57" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="E57" s="1">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -5560,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5568,16 +5577,16 @@
         <v>87</v>
       </c>
       <c r="B58" s="2">
-        <v>0.5451695919036865</v>
+        <v>0.5574102997779846</v>
       </c>
       <c r="C58" s="1">
-        <v>720</v>
+        <v>748</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>720</v>
+        <v>748</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -5591,19 +5600,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="B59" s="2">
-        <v>0.4982244074344635</v>
+        <v>0.536544680595398</v>
       </c>
       <c r="C59" s="1">
-        <v>658</v>
+        <v>720</v>
       </c>
       <c r="D59" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>658</v>
+        <v>720</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -5612,24 +5621,24 @@
         <v>0</v>
       </c>
       <c r="H59" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B60" s="2">
-        <v>0.4876239001750946</v>
+        <v>0.4903421998023987</v>
       </c>
       <c r="C60" s="1">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E60" s="1">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -5638,50 +5647,50 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="B61" s="2">
-        <v>0.4694515764713287</v>
+        <v>0.4799093902111054</v>
       </c>
       <c r="C61" s="1">
-        <v>620</v>
+        <v>644</v>
       </c>
       <c r="D61" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>564</v>
+        <v>644</v>
       </c>
       <c r="F61" s="1">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>2044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B62" s="2">
-        <v>0.4679372012615204</v>
+        <v>0.4635149538516998</v>
       </c>
       <c r="C62" s="1">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -5695,28 +5704,28 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="B63" s="2">
-        <v>0.433106929063797</v>
+        <v>0.4620245695114136</v>
       </c>
       <c r="C63" s="1">
-        <v>572</v>
+        <v>620</v>
       </c>
       <c r="D63" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
       <c r="E63" s="1">
         <v>564</v>
       </c>
       <c r="F63" s="1">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
       </c>
       <c r="H63" s="1">
-        <v>0</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -5724,19 +5733,19 @@
         <v>91</v>
       </c>
       <c r="B64" s="2">
-        <v>0.4209920465946198</v>
+        <v>0.42625492811203</v>
       </c>
       <c r="C64" s="1">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>44</v>
+        <v>564</v>
       </c>
       <c r="F64" s="1">
-        <v>512</v>
+        <v>8</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -5747,48 +5756,48 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B65" s="2">
-        <v>0.4149346053600311</v>
+        <v>0.4143317043781281</v>
       </c>
       <c r="C65" s="1">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="D65" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>548</v>
+        <v>332</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
       </c>
       <c r="H65" s="1">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B66" s="2">
-        <v>0.4119058847427368</v>
+        <v>0.4143317043781281</v>
       </c>
       <c r="C66" s="1">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>320</v>
+        <v>44</v>
       </c>
       <c r="F66" s="1">
-        <v>224</v>
+        <v>512</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
@@ -5799,123 +5808,123 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B67" s="2">
-        <v>0.3876761496067047</v>
+        <v>0.4083701074123383</v>
       </c>
       <c r="C67" s="1">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="D67" s="1">
-        <v>16416</v>
+        <v>204</v>
       </c>
       <c r="E67" s="1">
-        <v>480</v>
+        <v>548</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
       </c>
       <c r="G67" s="1">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>16384</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="B68" s="2">
-        <v>0.3846474289894104</v>
+        <v>0.405389279127121</v>
       </c>
       <c r="C68" s="1">
-        <v>508</v>
+        <v>544</v>
       </c>
       <c r="D68" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>36</v>
+        <v>528</v>
       </c>
       <c r="F68" s="1">
-        <v>472</v>
+        <v>16</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
       </c>
       <c r="H68" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B69" s="2">
-        <v>0.3801043331623077</v>
+        <v>0.3815428614616394</v>
       </c>
       <c r="C69" s="1">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="D69" s="1">
-        <v>4096</v>
+        <v>16416</v>
       </c>
       <c r="E69" s="1">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H69" s="1">
-        <v>4096</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="B70" s="2">
-        <v>0.3801043331623077</v>
+        <v>0.3785620629787445</v>
       </c>
       <c r="C70" s="1">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D70" s="1">
-        <v>4</v>
+        <v>1024</v>
       </c>
       <c r="E70" s="1">
-        <v>498</v>
+        <v>36</v>
       </c>
       <c r="F70" s="1">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="G70" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B71" s="2">
-        <v>0.3770756125450134</v>
+        <v>0.374090850353241</v>
       </c>
       <c r="C71" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D71" s="1">
-        <v>1031</v>
+        <v>4096</v>
       </c>
       <c r="E71" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -5924,21 +5933,21 @@
         <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>1031</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="B72" s="2">
-        <v>0.3770756125450134</v>
+        <v>0.374090850353241</v>
       </c>
       <c r="C72" s="1">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E72" s="1">
         <v>498</v>
@@ -5947,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -5955,19 +5964,19 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="B73" s="2">
-        <v>0.3679894506931305</v>
+        <v>0.3711100518703461</v>
       </c>
       <c r="C73" s="1">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="D73" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
       <c r="E73" s="1">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -5976,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>0</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -5984,16 +5993,16 @@
         <v>95</v>
       </c>
       <c r="B74" s="2">
-        <v>0.3604176640510559</v>
+        <v>0.3711100518703461</v>
       </c>
       <c r="C74" s="1">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -6010,16 +6019,16 @@
         <v>96</v>
       </c>
       <c r="B75" s="2">
-        <v>0.3543602228164673</v>
+        <v>0.3591868281364441</v>
       </c>
       <c r="C75" s="1">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -6036,16 +6045,16 @@
         <v>97</v>
       </c>
       <c r="B76" s="2">
-        <v>0.351331502199173</v>
+        <v>0.3547156453132629</v>
       </c>
       <c r="C76" s="1">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -6059,25 +6068,25 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="B77" s="2">
-        <v>0.3452740609645844</v>
+        <v>0.3457732200622559</v>
       </c>
       <c r="C77" s="1">
-        <v>456</v>
+     